--- a/services/costar/MASTER/COSTAR_MASTER_MERCADOS.xlsx
+++ b/services/costar/MASTER/COSTAR_MASTER_MERCADOS.xlsx
@@ -1650,7 +1650,7 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>Schema/rules version applied at ingestion time. Today: v1.0.</t>
+          <t>Schema/rules version applied at ingestion time. Today: v1.1.</t>
         </is>
       </c>
     </row>
@@ -2087,7 +2087,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A34"/>
+  <dimension ref="A1:A37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="110" customWidth="1" min="1" max="1"/>
@@ -2113,7 +2113,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Built 2026-05-11T20:02:16+00:00. Normalization version: v1.0.</t>
+          <t>Built 2026-05-11T20:16:06+00:00. Normalization version: v1.1.</t>
         </is>
       </c>
     </row>
@@ -2130,14 +2130,14 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t xml:space="preserve">  • COSTAR_MASTER_PAIS.xlsx       — country aggregates</t>
+          <t xml:space="preserve">  • COSTAR_MASTER_PAIS.xlsx        — country aggregates</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t xml:space="preserve">  • COSTAR_MASTER_MERCADOS.xlsx   — market aggregates</t>
+          <t xml:space="preserve">  • COSTAR_MASTER_MERCADOS.xlsx    — market aggregates</t>
         </is>
       </c>
     </row>
@@ -2151,7 +2151,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t xml:space="preserve">  • COSTAR_MASTER_COMPSETS.xlsx   — compset (peer-set) benchmarks per target hotel</t>
+          <t xml:space="preserve">  • COSTAR_MASTER_CLASS.xlsx       — chain-scale time series (country or market level)</t>
         </is>
       </c>
     </row>
@@ -2161,147 +2161,164 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Operating contract:</t>
+          <t xml:space="preserve">  CompSet workbooks now live in the OPERATIONAL workspace at services/compset/</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t xml:space="preserve">  1. The Data Ingestion Agent appends new rows. It NEVER edits in place.</t>
+          <t xml:space="preserve">  (different purpose — hotel-specific underwriting outputs, not warehouse ingestion).</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  2. Corrections → insert a new row with</t>
-        </is>
-      </c>
+      <c r="A14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t xml:space="preserve">     supersedes_id = &lt;old canonical_id&gt; and ingestion_status='superseded'.</t>
+          <t>Operating contract:</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t xml:space="preserve">  3. Manual edits follow the same contract — track who, when, why</t>
+          <t xml:space="preserve">  1. The Data Ingestion Agent appends new rows. It NEVER edits in place.</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t xml:space="preserve">     in ingested_by + notes.</t>
+          <t xml:space="preserve">  2. Corrections → insert a new row with</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" t="inlineStr"/>
+      <c r="A18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">     supersedes_id = &lt;old canonical_id&gt; and ingestion_status='superseded'.</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Sheets:</t>
+          <t xml:space="preserve">  3. Manual edits follow the same contract — track who, when, why</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t xml:space="preserve">  • DATA              — canonical row corpus</t>
+          <t xml:space="preserve">     in ingested_by + notes.</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  • DICTIONARY        — column schema + required flags + notes</t>
-        </is>
-      </c>
+      <c r="A21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t xml:space="preserve">  • INGESTION_LOG     — one row per processed import file</t>
+          <t>Sheets:</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t xml:space="preserve">  • SOURCES_REGISTRY  — labels + reliability tiers per source_kind</t>
+          <t xml:space="preserve">  • DATA              — canonical row corpus</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t xml:space="preserve">  • README            — this sheet</t>
+          <t xml:space="preserve">  • DICTIONARY        — column schema + required flags + notes</t>
         </is>
       </c>
     </row>
     <row r="25">
-      <c r="A25" t="inlineStr"/>
+      <c r="A25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  • INGESTION_LOG     — one row per processed import file</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Reference docs:</t>
+          <t xml:space="preserve">  • SOURCES_REGISTRY  — labels + reliability tiers per source_kind</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t xml:space="preserve">  • docs/intelligence/costar-market-schema.md</t>
+          <t xml:space="preserve">  • README            — this sheet</t>
         </is>
       </c>
     </row>
     <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  • docs/intelligence/costar-master-dataset-architecture.md</t>
-        </is>
-      </c>
+      <c r="A28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t xml:space="preserve">  • docs/intelligence/costar-normalization-rules.md</t>
+          <t>Reference docs:</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t xml:space="preserve">  • docs/intelligence/costar-ingestion-workflow.md</t>
+          <t xml:space="preserve">  • docs/intelligence/costar-market-schema.md</t>
         </is>
       </c>
     </row>
     <row r="31">
-      <c r="A31" t="inlineStr"/>
+      <c r="A31" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  • docs/intelligence/costar-master-dataset-architecture.md</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Regenerating this workbook:</t>
+          <t xml:space="preserve">  • docs/intelligence/costar-normalization-rules.md</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
+          <t xml:space="preserve">  • docs/intelligence/costar-ingestion-workflow.md</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Regenerating this workbook:</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
           <t xml:space="preserve">  python services/costar/scripts/build_masters.py</t>
         </is>
       </c>
     </row>
-    <row r="34">
-      <c r="A34" t="inlineStr">
+    <row r="37">
+      <c r="A37" t="inlineStr">
         <is>
           <t xml:space="preserve">  (Idempotent. Run when the schema evolves; commit both the script and the regenerated .xlsx.)</t>
         </is>

--- a/services/costar/MASTER/COSTAR_MASTER_MERCADOS.xlsx
+++ b/services/costar/MASTER/COSTAR_MASTER_MERCADOS.xlsx
@@ -745,7 +745,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>batch_04ef5ec3e6b54457</t>
+          <t>batch_976be391c94a4aae</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
@@ -761,7 +761,7 @@
       <c r="AE2" t="inlineStr"/>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>2026-05-14T02:33:19+00:00</t>
+          <t>2026-05-14T02:59:23+00:00</t>
         </is>
       </c>
       <c r="AG2" t="inlineStr">
@@ -846,7 +846,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>batch_04ef5ec3e6b54457</t>
+          <t>batch_976be391c94a4aae</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
@@ -862,7 +862,7 @@
       <c r="AE3" t="inlineStr"/>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>2026-05-14T02:33:19+00:00</t>
+          <t>2026-05-14T02:59:23+00:00</t>
         </is>
       </c>
       <c r="AG3" t="inlineStr">
@@ -947,7 +947,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>batch_04ef5ec3e6b54457</t>
+          <t>batch_976be391c94a4aae</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
@@ -963,7 +963,7 @@
       <c r="AE4" t="inlineStr"/>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>2026-05-14T02:33:19+00:00</t>
+          <t>2026-05-14T02:59:23+00:00</t>
         </is>
       </c>
       <c r="AG4" t="inlineStr">
@@ -1048,7 +1048,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>batch_04ef5ec3e6b54457</t>
+          <t>batch_976be391c94a4aae</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
@@ -1064,7 +1064,7 @@
       <c r="AE5" t="inlineStr"/>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>2026-05-14T02:33:19+00:00</t>
+          <t>2026-05-14T02:59:23+00:00</t>
         </is>
       </c>
       <c r="AG5" t="inlineStr">
@@ -1149,7 +1149,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>batch_04ef5ec3e6b54457</t>
+          <t>batch_976be391c94a4aae</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
@@ -1165,7 +1165,7 @@
       <c r="AE6" t="inlineStr"/>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>2026-05-14T02:33:19+00:00</t>
+          <t>2026-05-14T02:59:23+00:00</t>
         </is>
       </c>
       <c r="AG6" t="inlineStr">
@@ -1250,7 +1250,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>batch_04ef5ec3e6b54457</t>
+          <t>batch_976be391c94a4aae</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
@@ -1266,7 +1266,7 @@
       <c r="AE7" t="inlineStr"/>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>2026-05-14T02:33:19+00:00</t>
+          <t>2026-05-14T02:59:23+00:00</t>
         </is>
       </c>
       <c r="AG7" t="inlineStr">
@@ -1330,7 +1330,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>batch_04ef5ec3e6b54457</t>
+          <t>batch_976be391c94a4aae</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
@@ -1346,7 +1346,7 @@
       <c r="AE8" t="inlineStr"/>
       <c r="AF8" t="inlineStr">
         <is>
-          <t>2026-05-14T02:33:19+00:00</t>
+          <t>2026-05-14T02:59:23+00:00</t>
         </is>
       </c>
       <c r="AG8" t="inlineStr">
@@ -1413,7 +1413,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>batch_04ef5ec3e6b54457</t>
+          <t>batch_976be391c94a4aae</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
@@ -1429,7 +1429,7 @@
       <c r="AE9" t="inlineStr"/>
       <c r="AF9" t="inlineStr">
         <is>
-          <t>2026-05-14T02:33:19+00:00</t>
+          <t>2026-05-14T02:59:23+00:00</t>
         </is>
       </c>
       <c r="AG9" t="inlineStr">
@@ -1496,7 +1496,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>batch_04ef5ec3e6b54457</t>
+          <t>batch_976be391c94a4aae</t>
         </is>
       </c>
       <c r="AC10" t="inlineStr">
@@ -1512,7 +1512,7 @@
       <c r="AE10" t="inlineStr"/>
       <c r="AF10" t="inlineStr">
         <is>
-          <t>2026-05-14T02:33:19+00:00</t>
+          <t>2026-05-14T02:59:23+00:00</t>
         </is>
       </c>
       <c r="AG10" t="inlineStr">
@@ -1579,7 +1579,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>batch_04ef5ec3e6b54457</t>
+          <t>batch_976be391c94a4aae</t>
         </is>
       </c>
       <c r="AC11" t="inlineStr">
@@ -1595,7 +1595,7 @@
       <c r="AE11" t="inlineStr"/>
       <c r="AF11" t="inlineStr">
         <is>
-          <t>2026-05-14T02:33:19+00:00</t>
+          <t>2026-05-14T02:59:23+00:00</t>
         </is>
       </c>
       <c r="AG11" t="inlineStr">
@@ -1662,7 +1662,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>batch_04ef5ec3e6b54457</t>
+          <t>batch_976be391c94a4aae</t>
         </is>
       </c>
       <c r="AC12" t="inlineStr">
@@ -1678,7 +1678,7 @@
       <c r="AE12" t="inlineStr"/>
       <c r="AF12" t="inlineStr">
         <is>
-          <t>2026-05-14T02:33:19+00:00</t>
+          <t>2026-05-14T02:59:23+00:00</t>
         </is>
       </c>
       <c r="AG12" t="inlineStr">
@@ -1745,7 +1745,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>batch_04ef5ec3e6b54457</t>
+          <t>batch_976be391c94a4aae</t>
         </is>
       </c>
       <c r="AC13" t="inlineStr">
@@ -1761,7 +1761,7 @@
       <c r="AE13" t="inlineStr"/>
       <c r="AF13" t="inlineStr">
         <is>
-          <t>2026-05-14T02:33:19+00:00</t>
+          <t>2026-05-14T02:59:23+00:00</t>
         </is>
       </c>
       <c r="AG13" t="inlineStr">
@@ -1828,7 +1828,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>batch_04ef5ec3e6b54457</t>
+          <t>batch_976be391c94a4aae</t>
         </is>
       </c>
       <c r="AC14" t="inlineStr">
@@ -1844,7 +1844,7 @@
       <c r="AE14" t="inlineStr"/>
       <c r="AF14" t="inlineStr">
         <is>
-          <t>2026-05-14T02:33:19+00:00</t>
+          <t>2026-05-14T02:59:23+00:00</t>
         </is>
       </c>
       <c r="AG14" t="inlineStr">
@@ -1911,7 +1911,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>batch_04ef5ec3e6b54457</t>
+          <t>batch_976be391c94a4aae</t>
         </is>
       </c>
       <c r="AC15" t="inlineStr">
@@ -1927,7 +1927,7 @@
       <c r="AE15" t="inlineStr"/>
       <c r="AF15" t="inlineStr">
         <is>
-          <t>2026-05-14T02:33:19+00:00</t>
+          <t>2026-05-14T02:59:23+00:00</t>
         </is>
       </c>
       <c r="AG15" t="inlineStr">
@@ -1994,7 +1994,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>batch_04ef5ec3e6b54457</t>
+          <t>batch_976be391c94a4aae</t>
         </is>
       </c>
       <c r="AC16" t="inlineStr">
@@ -2010,7 +2010,7 @@
       <c r="AE16" t="inlineStr"/>
       <c r="AF16" t="inlineStr">
         <is>
-          <t>2026-05-14T02:33:19+00:00</t>
+          <t>2026-05-14T02:59:23+00:00</t>
         </is>
       </c>
       <c r="AG16" t="inlineStr">
@@ -2113,7 +2113,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>batch_04ef5ec3e6b54457</t>
+          <t>batch_976be391c94a4aae</t>
         </is>
       </c>
       <c r="AC17" t="inlineStr">
@@ -2129,7 +2129,7 @@
       <c r="AE17" t="inlineStr"/>
       <c r="AF17" t="inlineStr">
         <is>
-          <t>2026-05-14T02:33:19+00:00</t>
+          <t>2026-05-14T02:59:23+00:00</t>
         </is>
       </c>
       <c r="AG17" t="inlineStr">
@@ -2232,7 +2232,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>batch_04ef5ec3e6b54457</t>
+          <t>batch_976be391c94a4aae</t>
         </is>
       </c>
       <c r="AC18" t="inlineStr">
@@ -2248,7 +2248,7 @@
       <c r="AE18" t="inlineStr"/>
       <c r="AF18" t="inlineStr">
         <is>
-          <t>2026-05-14T02:33:19+00:00</t>
+          <t>2026-05-14T02:59:23+00:00</t>
         </is>
       </c>
       <c r="AG18" t="inlineStr">
@@ -2351,7 +2351,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>batch_04ef5ec3e6b54457</t>
+          <t>batch_976be391c94a4aae</t>
         </is>
       </c>
       <c r="AC19" t="inlineStr">
@@ -2367,7 +2367,7 @@
       <c r="AE19" t="inlineStr"/>
       <c r="AF19" t="inlineStr">
         <is>
-          <t>2026-05-14T02:33:19+00:00</t>
+          <t>2026-05-14T02:59:23+00:00</t>
         </is>
       </c>
       <c r="AG19" t="inlineStr">
@@ -2470,7 +2470,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>batch_04ef5ec3e6b54457</t>
+          <t>batch_976be391c94a4aae</t>
         </is>
       </c>
       <c r="AC20" t="inlineStr">
@@ -2486,7 +2486,7 @@
       <c r="AE20" t="inlineStr"/>
       <c r="AF20" t="inlineStr">
         <is>
-          <t>2026-05-14T02:33:19+00:00</t>
+          <t>2026-05-14T02:59:23+00:00</t>
         </is>
       </c>
       <c r="AG20" t="inlineStr">
@@ -2589,7 +2589,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>batch_04ef5ec3e6b54457</t>
+          <t>batch_976be391c94a4aae</t>
         </is>
       </c>
       <c r="AC21" t="inlineStr">
@@ -2605,7 +2605,7 @@
       <c r="AE21" t="inlineStr"/>
       <c r="AF21" t="inlineStr">
         <is>
-          <t>2026-05-14T02:33:19+00:00</t>
+          <t>2026-05-14T02:59:23+00:00</t>
         </is>
       </c>
       <c r="AG21" t="inlineStr">
@@ -2708,7 +2708,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>batch_04ef5ec3e6b54457</t>
+          <t>batch_976be391c94a4aae</t>
         </is>
       </c>
       <c r="AC22" t="inlineStr">
@@ -2724,7 +2724,7 @@
       <c r="AE22" t="inlineStr"/>
       <c r="AF22" t="inlineStr">
         <is>
-          <t>2026-05-14T02:33:19+00:00</t>
+          <t>2026-05-14T02:59:23+00:00</t>
         </is>
       </c>
       <c r="AG22" t="inlineStr">
@@ -2827,7 +2827,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>batch_04ef5ec3e6b54457</t>
+          <t>batch_976be391c94a4aae</t>
         </is>
       </c>
       <c r="AC23" t="inlineStr">
@@ -2843,7 +2843,7 @@
       <c r="AE23" t="inlineStr"/>
       <c r="AF23" t="inlineStr">
         <is>
-          <t>2026-05-14T02:33:19+00:00</t>
+          <t>2026-05-14T02:59:23+00:00</t>
         </is>
       </c>
       <c r="AG23" t="inlineStr">
@@ -2946,7 +2946,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>batch_04ef5ec3e6b54457</t>
+          <t>batch_976be391c94a4aae</t>
         </is>
       </c>
       <c r="AC24" t="inlineStr">
@@ -2962,7 +2962,7 @@
       <c r="AE24" t="inlineStr"/>
       <c r="AF24" t="inlineStr">
         <is>
-          <t>2026-05-14T02:33:19+00:00</t>
+          <t>2026-05-14T02:59:23+00:00</t>
         </is>
       </c>
       <c r="AG24" t="inlineStr">
@@ -3065,7 +3065,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>batch_04ef5ec3e6b54457</t>
+          <t>batch_976be391c94a4aae</t>
         </is>
       </c>
       <c r="AC25" t="inlineStr">
@@ -3081,7 +3081,7 @@
       <c r="AE25" t="inlineStr"/>
       <c r="AF25" t="inlineStr">
         <is>
-          <t>2026-05-14T02:33:19+00:00</t>
+          <t>2026-05-14T02:59:23+00:00</t>
         </is>
       </c>
       <c r="AG25" t="inlineStr">
@@ -3184,7 +3184,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>batch_04ef5ec3e6b54457</t>
+          <t>batch_976be391c94a4aae</t>
         </is>
       </c>
       <c r="AC26" t="inlineStr">
@@ -3200,7 +3200,7 @@
       <c r="AE26" t="inlineStr"/>
       <c r="AF26" t="inlineStr">
         <is>
-          <t>2026-05-14T02:33:19+00:00</t>
+          <t>2026-05-14T02:59:23+00:00</t>
         </is>
       </c>
       <c r="AG26" t="inlineStr">
@@ -3303,7 +3303,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>batch_04ef5ec3e6b54457</t>
+          <t>batch_976be391c94a4aae</t>
         </is>
       </c>
       <c r="AC27" t="inlineStr">
@@ -3319,7 +3319,7 @@
       <c r="AE27" t="inlineStr"/>
       <c r="AF27" t="inlineStr">
         <is>
-          <t>2026-05-14T02:33:19+00:00</t>
+          <t>2026-05-14T02:59:23+00:00</t>
         </is>
       </c>
       <c r="AG27" t="inlineStr">
@@ -3422,7 +3422,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>batch_04ef5ec3e6b54457</t>
+          <t>batch_976be391c94a4aae</t>
         </is>
       </c>
       <c r="AC28" t="inlineStr">
@@ -3438,7 +3438,7 @@
       <c r="AE28" t="inlineStr"/>
       <c r="AF28" t="inlineStr">
         <is>
-          <t>2026-05-14T02:33:19+00:00</t>
+          <t>2026-05-14T02:59:23+00:00</t>
         </is>
       </c>
       <c r="AG28" t="inlineStr">
@@ -3541,7 +3541,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>batch_04ef5ec3e6b54457</t>
+          <t>batch_976be391c94a4aae</t>
         </is>
       </c>
       <c r="AC29" t="inlineStr">
@@ -3557,7 +3557,7 @@
       <c r="AE29" t="inlineStr"/>
       <c r="AF29" t="inlineStr">
         <is>
-          <t>2026-05-14T02:33:19+00:00</t>
+          <t>2026-05-14T02:59:23+00:00</t>
         </is>
       </c>
       <c r="AG29" t="inlineStr">
@@ -3660,7 +3660,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>batch_04ef5ec3e6b54457</t>
+          <t>batch_976be391c94a4aae</t>
         </is>
       </c>
       <c r="AC30" t="inlineStr">
@@ -3676,7 +3676,7 @@
       <c r="AE30" t="inlineStr"/>
       <c r="AF30" t="inlineStr">
         <is>
-          <t>2026-05-14T02:33:19+00:00</t>
+          <t>2026-05-14T02:59:23+00:00</t>
         </is>
       </c>
       <c r="AG30" t="inlineStr">
@@ -3779,7 +3779,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>batch_04ef5ec3e6b54457</t>
+          <t>batch_976be391c94a4aae</t>
         </is>
       </c>
       <c r="AC31" t="inlineStr">
@@ -3795,7 +3795,7 @@
       <c r="AE31" t="inlineStr"/>
       <c r="AF31" t="inlineStr">
         <is>
-          <t>2026-05-14T02:33:19+00:00</t>
+          <t>2026-05-14T02:59:23+00:00</t>
         </is>
       </c>
       <c r="AG31" t="inlineStr">
@@ -3898,7 +3898,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>batch_04ef5ec3e6b54457</t>
+          <t>batch_976be391c94a4aae</t>
         </is>
       </c>
       <c r="AC32" t="inlineStr">
@@ -3914,7 +3914,7 @@
       <c r="AE32" t="inlineStr"/>
       <c r="AF32" t="inlineStr">
         <is>
-          <t>2026-05-14T02:33:19+00:00</t>
+          <t>2026-05-14T02:59:23+00:00</t>
         </is>
       </c>
       <c r="AG32" t="inlineStr">
@@ -4017,7 +4017,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>batch_04ef5ec3e6b54457</t>
+          <t>batch_976be391c94a4aae</t>
         </is>
       </c>
       <c r="AC33" t="inlineStr">
@@ -4033,7 +4033,7 @@
       <c r="AE33" t="inlineStr"/>
       <c r="AF33" t="inlineStr">
         <is>
-          <t>2026-05-14T02:33:19+00:00</t>
+          <t>2026-05-14T02:59:23+00:00</t>
         </is>
       </c>
       <c r="AG33" t="inlineStr">
@@ -4136,7 +4136,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>batch_04ef5ec3e6b54457</t>
+          <t>batch_976be391c94a4aae</t>
         </is>
       </c>
       <c r="AC34" t="inlineStr">
@@ -4152,7 +4152,7 @@
       <c r="AE34" t="inlineStr"/>
       <c r="AF34" t="inlineStr">
         <is>
-          <t>2026-05-14T02:33:19+00:00</t>
+          <t>2026-05-14T02:59:23+00:00</t>
         </is>
       </c>
       <c r="AG34" t="inlineStr">
@@ -4255,7 +4255,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>batch_04ef5ec3e6b54457</t>
+          <t>batch_976be391c94a4aae</t>
         </is>
       </c>
       <c r="AC35" t="inlineStr">
@@ -4271,7 +4271,7 @@
       <c r="AE35" t="inlineStr"/>
       <c r="AF35" t="inlineStr">
         <is>
-          <t>2026-05-14T02:33:19+00:00</t>
+          <t>2026-05-14T02:59:23+00:00</t>
         </is>
       </c>
       <c r="AG35" t="inlineStr">
@@ -4374,7 +4374,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>batch_04ef5ec3e6b54457</t>
+          <t>batch_976be391c94a4aae</t>
         </is>
       </c>
       <c r="AC36" t="inlineStr">
@@ -4390,7 +4390,7 @@
       <c r="AE36" t="inlineStr"/>
       <c r="AF36" t="inlineStr">
         <is>
-          <t>2026-05-14T02:33:19+00:00</t>
+          <t>2026-05-14T02:59:23+00:00</t>
         </is>
       </c>
       <c r="AG36" t="inlineStr">
@@ -4493,7 +4493,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>batch_04ef5ec3e6b54457</t>
+          <t>batch_976be391c94a4aae</t>
         </is>
       </c>
       <c r="AC37" t="inlineStr">
@@ -4509,7 +4509,7 @@
       <c r="AE37" t="inlineStr"/>
       <c r="AF37" t="inlineStr">
         <is>
-          <t>2026-05-14T02:33:19+00:00</t>
+          <t>2026-05-14T02:59:23+00:00</t>
         </is>
       </c>
       <c r="AG37" t="inlineStr">
@@ -4612,7 +4612,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>batch_04ef5ec3e6b54457</t>
+          <t>batch_976be391c94a4aae</t>
         </is>
       </c>
       <c r="AC38" t="inlineStr">
@@ -4628,7 +4628,7 @@
       <c r="AE38" t="inlineStr"/>
       <c r="AF38" t="inlineStr">
         <is>
-          <t>2026-05-14T02:33:19+00:00</t>
+          <t>2026-05-14T02:59:23+00:00</t>
         </is>
       </c>
       <c r="AG38" t="inlineStr">
@@ -4731,7 +4731,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>batch_04ef5ec3e6b54457</t>
+          <t>batch_976be391c94a4aae</t>
         </is>
       </c>
       <c r="AC39" t="inlineStr">
@@ -4747,7 +4747,7 @@
       <c r="AE39" t="inlineStr"/>
       <c r="AF39" t="inlineStr">
         <is>
-          <t>2026-05-14T02:33:19+00:00</t>
+          <t>2026-05-14T02:59:23+00:00</t>
         </is>
       </c>
       <c r="AG39" t="inlineStr">
@@ -4850,7 +4850,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>batch_04ef5ec3e6b54457</t>
+          <t>batch_976be391c94a4aae</t>
         </is>
       </c>
       <c r="AC40" t="inlineStr">
@@ -4866,7 +4866,7 @@
       <c r="AE40" t="inlineStr"/>
       <c r="AF40" t="inlineStr">
         <is>
-          <t>2026-05-14T02:33:19+00:00</t>
+          <t>2026-05-14T02:59:23+00:00</t>
         </is>
       </c>
       <c r="AG40" t="inlineStr">
@@ -4969,7 +4969,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>batch_04ef5ec3e6b54457</t>
+          <t>batch_976be391c94a4aae</t>
         </is>
       </c>
       <c r="AC41" t="inlineStr">
@@ -4985,7 +4985,7 @@
       <c r="AE41" t="inlineStr"/>
       <c r="AF41" t="inlineStr">
         <is>
-          <t>2026-05-14T02:33:19+00:00</t>
+          <t>2026-05-14T02:59:23+00:00</t>
         </is>
       </c>
       <c r="AG41" t="inlineStr">
@@ -5088,7 +5088,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>batch_04ef5ec3e6b54457</t>
+          <t>batch_976be391c94a4aae</t>
         </is>
       </c>
       <c r="AC42" t="inlineStr">
@@ -5104,7 +5104,7 @@
       <c r="AE42" t="inlineStr"/>
       <c r="AF42" t="inlineStr">
         <is>
-          <t>2026-05-14T02:33:19+00:00</t>
+          <t>2026-05-14T02:59:23+00:00</t>
         </is>
       </c>
       <c r="AG42" t="inlineStr">
@@ -5207,7 +5207,7 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>batch_04ef5ec3e6b54457</t>
+          <t>batch_976be391c94a4aae</t>
         </is>
       </c>
       <c r="AC43" t="inlineStr">
@@ -5223,7 +5223,7 @@
       <c r="AE43" t="inlineStr"/>
       <c r="AF43" t="inlineStr">
         <is>
-          <t>2026-05-14T02:33:19+00:00</t>
+          <t>2026-05-14T02:59:23+00:00</t>
         </is>
       </c>
       <c r="AG43" t="inlineStr">
@@ -5326,7 +5326,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>batch_04ef5ec3e6b54457</t>
+          <t>batch_976be391c94a4aae</t>
         </is>
       </c>
       <c r="AC44" t="inlineStr">
@@ -5342,7 +5342,7 @@
       <c r="AE44" t="inlineStr"/>
       <c r="AF44" t="inlineStr">
         <is>
-          <t>2026-05-14T02:33:19+00:00</t>
+          <t>2026-05-14T02:59:23+00:00</t>
         </is>
       </c>
       <c r="AG44" t="inlineStr">
@@ -5445,7 +5445,7 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>batch_04ef5ec3e6b54457</t>
+          <t>batch_976be391c94a4aae</t>
         </is>
       </c>
       <c r="AC45" t="inlineStr">
@@ -5461,7 +5461,7 @@
       <c r="AE45" t="inlineStr"/>
       <c r="AF45" t="inlineStr">
         <is>
-          <t>2026-05-14T02:33:19+00:00</t>
+          <t>2026-05-14T02:59:23+00:00</t>
         </is>
       </c>
       <c r="AG45" t="inlineStr">
@@ -5564,7 +5564,7 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>batch_04ef5ec3e6b54457</t>
+          <t>batch_976be391c94a4aae</t>
         </is>
       </c>
       <c r="AC46" t="inlineStr">
@@ -5580,7 +5580,7 @@
       <c r="AE46" t="inlineStr"/>
       <c r="AF46" t="inlineStr">
         <is>
-          <t>2026-05-14T02:33:19+00:00</t>
+          <t>2026-05-14T02:59:23+00:00</t>
         </is>
       </c>
       <c r="AG46" t="inlineStr">
@@ -5683,7 +5683,7 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>batch_04ef5ec3e6b54457</t>
+          <t>batch_976be391c94a4aae</t>
         </is>
       </c>
       <c r="AC47" t="inlineStr">
@@ -5699,7 +5699,7 @@
       <c r="AE47" t="inlineStr"/>
       <c r="AF47" t="inlineStr">
         <is>
-          <t>2026-05-14T02:33:19+00:00</t>
+          <t>2026-05-14T02:59:23+00:00</t>
         </is>
       </c>
       <c r="AG47" t="inlineStr">
@@ -5802,7 +5802,7 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>batch_04ef5ec3e6b54457</t>
+          <t>batch_976be391c94a4aae</t>
         </is>
       </c>
       <c r="AC48" t="inlineStr">
@@ -5818,7 +5818,7 @@
       <c r="AE48" t="inlineStr"/>
       <c r="AF48" t="inlineStr">
         <is>
-          <t>2026-05-14T02:33:19+00:00</t>
+          <t>2026-05-14T02:59:23+00:00</t>
         </is>
       </c>
       <c r="AG48" t="inlineStr">
@@ -5921,7 +5921,7 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>batch_04ef5ec3e6b54457</t>
+          <t>batch_976be391c94a4aae</t>
         </is>
       </c>
       <c r="AC49" t="inlineStr">
@@ -5937,7 +5937,7 @@
       <c r="AE49" t="inlineStr"/>
       <c r="AF49" t="inlineStr">
         <is>
-          <t>2026-05-14T02:33:19+00:00</t>
+          <t>2026-05-14T02:59:23+00:00</t>
         </is>
       </c>
       <c r="AG49" t="inlineStr">
@@ -6040,7 +6040,7 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>batch_04ef5ec3e6b54457</t>
+          <t>batch_976be391c94a4aae</t>
         </is>
       </c>
       <c r="AC50" t="inlineStr">
@@ -6056,7 +6056,7 @@
       <c r="AE50" t="inlineStr"/>
       <c r="AF50" t="inlineStr">
         <is>
-          <t>2026-05-14T02:33:19+00:00</t>
+          <t>2026-05-14T02:59:23+00:00</t>
         </is>
       </c>
       <c r="AG50" t="inlineStr">
@@ -6159,7 +6159,7 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>batch_04ef5ec3e6b54457</t>
+          <t>batch_976be391c94a4aae</t>
         </is>
       </c>
       <c r="AC51" t="inlineStr">
@@ -6175,7 +6175,7 @@
       <c r="AE51" t="inlineStr"/>
       <c r="AF51" t="inlineStr">
         <is>
-          <t>2026-05-14T02:33:19+00:00</t>
+          <t>2026-05-14T02:59:23+00:00</t>
         </is>
       </c>
       <c r="AG51" t="inlineStr">
@@ -6278,7 +6278,7 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>batch_04ef5ec3e6b54457</t>
+          <t>batch_976be391c94a4aae</t>
         </is>
       </c>
       <c r="AC52" t="inlineStr">
@@ -6294,7 +6294,7 @@
       <c r="AE52" t="inlineStr"/>
       <c r="AF52" t="inlineStr">
         <is>
-          <t>2026-05-14T02:33:19+00:00</t>
+          <t>2026-05-14T02:59:23+00:00</t>
         </is>
       </c>
       <c r="AG52" t="inlineStr">
@@ -6397,7 +6397,7 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>batch_04ef5ec3e6b54457</t>
+          <t>batch_976be391c94a4aae</t>
         </is>
       </c>
       <c r="AC53" t="inlineStr">
@@ -6413,7 +6413,7 @@
       <c r="AE53" t="inlineStr"/>
       <c r="AF53" t="inlineStr">
         <is>
-          <t>2026-05-14T02:33:19+00:00</t>
+          <t>2026-05-14T02:59:23+00:00</t>
         </is>
       </c>
       <c r="AG53" t="inlineStr">
@@ -6516,7 +6516,7 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>batch_04ef5ec3e6b54457</t>
+          <t>batch_976be391c94a4aae</t>
         </is>
       </c>
       <c r="AC54" t="inlineStr">
@@ -6532,7 +6532,7 @@
       <c r="AE54" t="inlineStr"/>
       <c r="AF54" t="inlineStr">
         <is>
-          <t>2026-05-14T02:33:19+00:00</t>
+          <t>2026-05-14T02:59:23+00:00</t>
         </is>
       </c>
       <c r="AG54" t="inlineStr">
@@ -6635,7 +6635,7 @@
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>batch_04ef5ec3e6b54457</t>
+          <t>batch_976be391c94a4aae</t>
         </is>
       </c>
       <c r="AC55" t="inlineStr">
@@ -6651,7 +6651,7 @@
       <c r="AE55" t="inlineStr"/>
       <c r="AF55" t="inlineStr">
         <is>
-          <t>2026-05-14T02:33:19+00:00</t>
+          <t>2026-05-14T02:59:23+00:00</t>
         </is>
       </c>
       <c r="AG55" t="inlineStr">
@@ -6754,7 +6754,7 @@
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>batch_04ef5ec3e6b54457</t>
+          <t>batch_976be391c94a4aae</t>
         </is>
       </c>
       <c r="AC56" t="inlineStr">
@@ -6770,7 +6770,7 @@
       <c r="AE56" t="inlineStr"/>
       <c r="AF56" t="inlineStr">
         <is>
-          <t>2026-05-14T02:33:19+00:00</t>
+          <t>2026-05-14T02:59:23+00:00</t>
         </is>
       </c>
       <c r="AG56" t="inlineStr">
@@ -6873,7 +6873,7 @@
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>batch_04ef5ec3e6b54457</t>
+          <t>batch_976be391c94a4aae</t>
         </is>
       </c>
       <c r="AC57" t="inlineStr">
@@ -6889,7 +6889,7 @@
       <c r="AE57" t="inlineStr"/>
       <c r="AF57" t="inlineStr">
         <is>
-          <t>2026-05-14T02:33:19+00:00</t>
+          <t>2026-05-14T02:59:23+00:00</t>
         </is>
       </c>
       <c r="AG57" t="inlineStr">
@@ -6992,7 +6992,7 @@
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>batch_04ef5ec3e6b54457</t>
+          <t>batch_976be391c94a4aae</t>
         </is>
       </c>
       <c r="AC58" t="inlineStr">
@@ -7008,7 +7008,7 @@
       <c r="AE58" t="inlineStr"/>
       <c r="AF58" t="inlineStr">
         <is>
-          <t>2026-05-14T02:33:19+00:00</t>
+          <t>2026-05-14T02:59:23+00:00</t>
         </is>
       </c>
       <c r="AG58" t="inlineStr">
@@ -7111,7 +7111,7 @@
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>batch_04ef5ec3e6b54457</t>
+          <t>batch_976be391c94a4aae</t>
         </is>
       </c>
       <c r="AC59" t="inlineStr">
@@ -7127,7 +7127,7 @@
       <c r="AE59" t="inlineStr"/>
       <c r="AF59" t="inlineStr">
         <is>
-          <t>2026-05-14T02:33:19+00:00</t>
+          <t>2026-05-14T02:59:23+00:00</t>
         </is>
       </c>
       <c r="AG59" t="inlineStr">
@@ -7230,7 +7230,7 @@
       </c>
       <c r="AB60" t="inlineStr">
         <is>
-          <t>batch_04ef5ec3e6b54457</t>
+          <t>batch_976be391c94a4aae</t>
         </is>
       </c>
       <c r="AC60" t="inlineStr">
@@ -7246,7 +7246,7 @@
       <c r="AE60" t="inlineStr"/>
       <c r="AF60" t="inlineStr">
         <is>
-          <t>2026-05-14T02:33:19+00:00</t>
+          <t>2026-05-14T02:59:23+00:00</t>
         </is>
       </c>
       <c r="AG60" t="inlineStr">
@@ -7349,7 +7349,7 @@
       </c>
       <c r="AB61" t="inlineStr">
         <is>
-          <t>batch_04ef5ec3e6b54457</t>
+          <t>batch_976be391c94a4aae</t>
         </is>
       </c>
       <c r="AC61" t="inlineStr">
@@ -7365,7 +7365,7 @@
       <c r="AE61" t="inlineStr"/>
       <c r="AF61" t="inlineStr">
         <is>
-          <t>2026-05-14T02:33:19+00:00</t>
+          <t>2026-05-14T02:59:23+00:00</t>
         </is>
       </c>
       <c r="AG61" t="inlineStr">
@@ -7468,7 +7468,7 @@
       </c>
       <c r="AB62" t="inlineStr">
         <is>
-          <t>batch_04ef5ec3e6b54457</t>
+          <t>batch_976be391c94a4aae</t>
         </is>
       </c>
       <c r="AC62" t="inlineStr">
@@ -7484,7 +7484,7 @@
       <c r="AE62" t="inlineStr"/>
       <c r="AF62" t="inlineStr">
         <is>
-          <t>2026-05-14T02:33:19+00:00</t>
+          <t>2026-05-14T02:59:23+00:00</t>
         </is>
       </c>
       <c r="AG62" t="inlineStr">
@@ -7587,7 +7587,7 @@
       </c>
       <c r="AB63" t="inlineStr">
         <is>
-          <t>batch_04ef5ec3e6b54457</t>
+          <t>batch_976be391c94a4aae</t>
         </is>
       </c>
       <c r="AC63" t="inlineStr">
@@ -7603,7 +7603,7 @@
       <c r="AE63" t="inlineStr"/>
       <c r="AF63" t="inlineStr">
         <is>
-          <t>2026-05-14T02:33:19+00:00</t>
+          <t>2026-05-14T02:59:23+00:00</t>
         </is>
       </c>
       <c r="AG63" t="inlineStr">
@@ -7706,7 +7706,7 @@
       </c>
       <c r="AB64" t="inlineStr">
         <is>
-          <t>batch_04ef5ec3e6b54457</t>
+          <t>batch_976be391c94a4aae</t>
         </is>
       </c>
       <c r="AC64" t="inlineStr">
@@ -7722,7 +7722,7 @@
       <c r="AE64" t="inlineStr"/>
       <c r="AF64" t="inlineStr">
         <is>
-          <t>2026-05-14T02:33:19+00:00</t>
+          <t>2026-05-14T02:59:23+00:00</t>
         </is>
       </c>
       <c r="AG64" t="inlineStr">
@@ -7825,7 +7825,7 @@
       </c>
       <c r="AB65" t="inlineStr">
         <is>
-          <t>batch_04ef5ec3e6b54457</t>
+          <t>batch_976be391c94a4aae</t>
         </is>
       </c>
       <c r="AC65" t="inlineStr">
@@ -7841,7 +7841,7 @@
       <c r="AE65" t="inlineStr"/>
       <c r="AF65" t="inlineStr">
         <is>
-          <t>2026-05-14T02:33:19+00:00</t>
+          <t>2026-05-14T02:59:23+00:00</t>
         </is>
       </c>
       <c r="AG65" t="inlineStr">
@@ -7944,7 +7944,7 @@
       </c>
       <c r="AB66" t="inlineStr">
         <is>
-          <t>batch_04ef5ec3e6b54457</t>
+          <t>batch_976be391c94a4aae</t>
         </is>
       </c>
       <c r="AC66" t="inlineStr">
@@ -7960,7 +7960,7 @@
       <c r="AE66" t="inlineStr"/>
       <c r="AF66" t="inlineStr">
         <is>
-          <t>2026-05-14T02:33:19+00:00</t>
+          <t>2026-05-14T02:59:23+00:00</t>
         </is>
       </c>
       <c r="AG66" t="inlineStr">
@@ -8063,7 +8063,7 @@
       </c>
       <c r="AB67" t="inlineStr">
         <is>
-          <t>batch_04ef5ec3e6b54457</t>
+          <t>batch_976be391c94a4aae</t>
         </is>
       </c>
       <c r="AC67" t="inlineStr">
@@ -8079,7 +8079,7 @@
       <c r="AE67" t="inlineStr"/>
       <c r="AF67" t="inlineStr">
         <is>
-          <t>2026-05-14T02:33:19+00:00</t>
+          <t>2026-05-14T02:59:23+00:00</t>
         </is>
       </c>
       <c r="AG67" t="inlineStr">
@@ -8182,7 +8182,7 @@
       </c>
       <c r="AB68" t="inlineStr">
         <is>
-          <t>batch_04ef5ec3e6b54457</t>
+          <t>batch_976be391c94a4aae</t>
         </is>
       </c>
       <c r="AC68" t="inlineStr">
@@ -8198,7 +8198,7 @@
       <c r="AE68" t="inlineStr"/>
       <c r="AF68" t="inlineStr">
         <is>
-          <t>2026-05-14T02:33:19+00:00</t>
+          <t>2026-05-14T02:59:23+00:00</t>
         </is>
       </c>
       <c r="AG68" t="inlineStr">
@@ -8301,7 +8301,7 @@
       </c>
       <c r="AB69" t="inlineStr">
         <is>
-          <t>batch_04ef5ec3e6b54457</t>
+          <t>batch_976be391c94a4aae</t>
         </is>
       </c>
       <c r="AC69" t="inlineStr">
@@ -8317,7 +8317,7 @@
       <c r="AE69" t="inlineStr"/>
       <c r="AF69" t="inlineStr">
         <is>
-          <t>2026-05-14T02:33:19+00:00</t>
+          <t>2026-05-14T02:59:23+00:00</t>
         </is>
       </c>
       <c r="AG69" t="inlineStr">
@@ -8420,7 +8420,7 @@
       </c>
       <c r="AB70" t="inlineStr">
         <is>
-          <t>batch_04ef5ec3e6b54457</t>
+          <t>batch_976be391c94a4aae</t>
         </is>
       </c>
       <c r="AC70" t="inlineStr">
@@ -8436,7 +8436,7 @@
       <c r="AE70" t="inlineStr"/>
       <c r="AF70" t="inlineStr">
         <is>
-          <t>2026-05-14T02:33:19+00:00</t>
+          <t>2026-05-14T02:59:23+00:00</t>
         </is>
       </c>
       <c r="AG70" t="inlineStr">
@@ -8539,7 +8539,7 @@
       </c>
       <c r="AB71" t="inlineStr">
         <is>
-          <t>batch_04ef5ec3e6b54457</t>
+          <t>batch_976be391c94a4aae</t>
         </is>
       </c>
       <c r="AC71" t="inlineStr">
@@ -8555,7 +8555,7 @@
       <c r="AE71" t="inlineStr"/>
       <c r="AF71" t="inlineStr">
         <is>
-          <t>2026-05-14T02:33:19+00:00</t>
+          <t>2026-05-14T02:59:23+00:00</t>
         </is>
       </c>
       <c r="AG71" t="inlineStr">
@@ -8658,7 +8658,7 @@
       </c>
       <c r="AB72" t="inlineStr">
         <is>
-          <t>batch_04ef5ec3e6b54457</t>
+          <t>batch_976be391c94a4aae</t>
         </is>
       </c>
       <c r="AC72" t="inlineStr">
@@ -8674,7 +8674,7 @@
       <c r="AE72" t="inlineStr"/>
       <c r="AF72" t="inlineStr">
         <is>
-          <t>2026-05-14T02:33:19+00:00</t>
+          <t>2026-05-14T02:59:23+00:00</t>
         </is>
       </c>
       <c r="AG72" t="inlineStr">
@@ -8777,7 +8777,7 @@
       </c>
       <c r="AB73" t="inlineStr">
         <is>
-          <t>batch_04ef5ec3e6b54457</t>
+          <t>batch_976be391c94a4aae</t>
         </is>
       </c>
       <c r="AC73" t="inlineStr">
@@ -8793,7 +8793,7 @@
       <c r="AE73" t="inlineStr"/>
       <c r="AF73" t="inlineStr">
         <is>
-          <t>2026-05-14T02:33:19+00:00</t>
+          <t>2026-05-14T02:59:23+00:00</t>
         </is>
       </c>
       <c r="AG73" t="inlineStr">
@@ -8896,7 +8896,7 @@
       </c>
       <c r="AB74" t="inlineStr">
         <is>
-          <t>batch_04ef5ec3e6b54457</t>
+          <t>batch_976be391c94a4aae</t>
         </is>
       </c>
       <c r="AC74" t="inlineStr">
@@ -8912,7 +8912,7 @@
       <c r="AE74" t="inlineStr"/>
       <c r="AF74" t="inlineStr">
         <is>
-          <t>2026-05-14T02:33:19+00:00</t>
+          <t>2026-05-14T02:59:23+00:00</t>
         </is>
       </c>
       <c r="AG74" t="inlineStr">
@@ -9015,7 +9015,7 @@
       </c>
       <c r="AB75" t="inlineStr">
         <is>
-          <t>batch_04ef5ec3e6b54457</t>
+          <t>batch_976be391c94a4aae</t>
         </is>
       </c>
       <c r="AC75" t="inlineStr">
@@ -9031,7 +9031,7 @@
       <c r="AE75" t="inlineStr"/>
       <c r="AF75" t="inlineStr">
         <is>
-          <t>2026-05-14T02:33:19+00:00</t>
+          <t>2026-05-14T02:59:23+00:00</t>
         </is>
       </c>
       <c r="AG75" t="inlineStr">
@@ -9134,7 +9134,7 @@
       </c>
       <c r="AB76" t="inlineStr">
         <is>
-          <t>batch_04ef5ec3e6b54457</t>
+          <t>batch_976be391c94a4aae</t>
         </is>
       </c>
       <c r="AC76" t="inlineStr">
@@ -9150,7 +9150,7 @@
       <c r="AE76" t="inlineStr"/>
       <c r="AF76" t="inlineStr">
         <is>
-          <t>2026-05-14T02:33:19+00:00</t>
+          <t>2026-05-14T02:59:23+00:00</t>
         </is>
       </c>
       <c r="AG76" t="inlineStr">
@@ -9253,7 +9253,7 @@
       </c>
       <c r="AB77" t="inlineStr">
         <is>
-          <t>batch_04ef5ec3e6b54457</t>
+          <t>batch_976be391c94a4aae</t>
         </is>
       </c>
       <c r="AC77" t="inlineStr">
@@ -9269,7 +9269,7 @@
       <c r="AE77" t="inlineStr"/>
       <c r="AF77" t="inlineStr">
         <is>
-          <t>2026-05-14T02:33:19+00:00</t>
+          <t>2026-05-14T02:59:23+00:00</t>
         </is>
       </c>
       <c r="AG77" t="inlineStr">
@@ -9372,7 +9372,7 @@
       </c>
       <c r="AB78" t="inlineStr">
         <is>
-          <t>batch_04ef5ec3e6b54457</t>
+          <t>batch_976be391c94a4aae</t>
         </is>
       </c>
       <c r="AC78" t="inlineStr">
@@ -9388,7 +9388,7 @@
       <c r="AE78" t="inlineStr"/>
       <c r="AF78" t="inlineStr">
         <is>
-          <t>2026-05-14T02:33:19+00:00</t>
+          <t>2026-05-14T02:59:23+00:00</t>
         </is>
       </c>
       <c r="AG78" t="inlineStr">
@@ -9491,7 +9491,7 @@
       </c>
       <c r="AB79" t="inlineStr">
         <is>
-          <t>batch_04ef5ec3e6b54457</t>
+          <t>batch_976be391c94a4aae</t>
         </is>
       </c>
       <c r="AC79" t="inlineStr">
@@ -9507,7 +9507,7 @@
       <c r="AE79" t="inlineStr"/>
       <c r="AF79" t="inlineStr">
         <is>
-          <t>2026-05-14T02:33:19+00:00</t>
+          <t>2026-05-14T02:59:23+00:00</t>
         </is>
       </c>
       <c r="AG79" t="inlineStr">
@@ -9610,7 +9610,7 @@
       </c>
       <c r="AB80" t="inlineStr">
         <is>
-          <t>batch_04ef5ec3e6b54457</t>
+          <t>batch_976be391c94a4aae</t>
         </is>
       </c>
       <c r="AC80" t="inlineStr">
@@ -9626,7 +9626,7 @@
       <c r="AE80" t="inlineStr"/>
       <c r="AF80" t="inlineStr">
         <is>
-          <t>2026-05-14T02:33:19+00:00</t>
+          <t>2026-05-14T02:59:23+00:00</t>
         </is>
       </c>
       <c r="AG80" t="inlineStr">
@@ -9729,7 +9729,7 @@
       </c>
       <c r="AB81" t="inlineStr">
         <is>
-          <t>batch_04ef5ec3e6b54457</t>
+          <t>batch_976be391c94a4aae</t>
         </is>
       </c>
       <c r="AC81" t="inlineStr">
@@ -9745,7 +9745,7 @@
       <c r="AE81" t="inlineStr"/>
       <c r="AF81" t="inlineStr">
         <is>
-          <t>2026-05-14T02:33:19+00:00</t>
+          <t>2026-05-14T02:59:23+00:00</t>
         </is>
       </c>
       <c r="AG81" t="inlineStr">
@@ -9848,7 +9848,7 @@
       </c>
       <c r="AB82" t="inlineStr">
         <is>
-          <t>batch_04ef5ec3e6b54457</t>
+          <t>batch_976be391c94a4aae</t>
         </is>
       </c>
       <c r="AC82" t="inlineStr">
@@ -9864,7 +9864,7 @@
       <c r="AE82" t="inlineStr"/>
       <c r="AF82" t="inlineStr">
         <is>
-          <t>2026-05-14T02:33:19+00:00</t>
+          <t>2026-05-14T02:59:23+00:00</t>
         </is>
       </c>
       <c r="AG82" t="inlineStr">
@@ -9967,7 +9967,7 @@
       </c>
       <c r="AB83" t="inlineStr">
         <is>
-          <t>batch_04ef5ec3e6b54457</t>
+          <t>batch_976be391c94a4aae</t>
         </is>
       </c>
       <c r="AC83" t="inlineStr">
@@ -9983,7 +9983,7 @@
       <c r="AE83" t="inlineStr"/>
       <c r="AF83" t="inlineStr">
         <is>
-          <t>2026-05-14T02:33:19+00:00</t>
+          <t>2026-05-14T02:59:23+00:00</t>
         </is>
       </c>
       <c r="AG83" t="inlineStr">
@@ -10086,7 +10086,7 @@
       </c>
       <c r="AB84" t="inlineStr">
         <is>
-          <t>batch_04ef5ec3e6b54457</t>
+          <t>batch_976be391c94a4aae</t>
         </is>
       </c>
       <c r="AC84" t="inlineStr">
@@ -10102,7 +10102,7 @@
       <c r="AE84" t="inlineStr"/>
       <c r="AF84" t="inlineStr">
         <is>
-          <t>2026-05-14T02:33:19+00:00</t>
+          <t>2026-05-14T02:59:23+00:00</t>
         </is>
       </c>
       <c r="AG84" t="inlineStr">
@@ -10205,7 +10205,7 @@
       </c>
       <c r="AB85" t="inlineStr">
         <is>
-          <t>batch_04ef5ec3e6b54457</t>
+          <t>batch_976be391c94a4aae</t>
         </is>
       </c>
       <c r="AC85" t="inlineStr">
@@ -10221,7 +10221,7 @@
       <c r="AE85" t="inlineStr"/>
       <c r="AF85" t="inlineStr">
         <is>
-          <t>2026-05-14T02:33:19+00:00</t>
+          <t>2026-05-14T02:59:23+00:00</t>
         </is>
       </c>
       <c r="AG85" t="inlineStr">
@@ -10324,7 +10324,7 @@
       </c>
       <c r="AB86" t="inlineStr">
         <is>
-          <t>batch_04ef5ec3e6b54457</t>
+          <t>batch_976be391c94a4aae</t>
         </is>
       </c>
       <c r="AC86" t="inlineStr">
@@ -10340,7 +10340,7 @@
       <c r="AE86" t="inlineStr"/>
       <c r="AF86" t="inlineStr">
         <is>
-          <t>2026-05-14T02:33:19+00:00</t>
+          <t>2026-05-14T02:59:23+00:00</t>
         </is>
       </c>
       <c r="AG86" t="inlineStr">
@@ -10443,7 +10443,7 @@
       </c>
       <c r="AB87" t="inlineStr">
         <is>
-          <t>batch_04ef5ec3e6b54457</t>
+          <t>batch_976be391c94a4aae</t>
         </is>
       </c>
       <c r="AC87" t="inlineStr">
@@ -10459,7 +10459,7 @@
       <c r="AE87" t="inlineStr"/>
       <c r="AF87" t="inlineStr">
         <is>
-          <t>2026-05-14T02:33:19+00:00</t>
+          <t>2026-05-14T02:59:23+00:00</t>
         </is>
       </c>
       <c r="AG87" t="inlineStr">
@@ -10562,7 +10562,7 @@
       </c>
       <c r="AB88" t="inlineStr">
         <is>
-          <t>batch_04ef5ec3e6b54457</t>
+          <t>batch_976be391c94a4aae</t>
         </is>
       </c>
       <c r="AC88" t="inlineStr">
@@ -10578,7 +10578,7 @@
       <c r="AE88" t="inlineStr"/>
       <c r="AF88" t="inlineStr">
         <is>
-          <t>2026-05-14T02:33:19+00:00</t>
+          <t>2026-05-14T02:59:23+00:00</t>
         </is>
       </c>
       <c r="AG88" t="inlineStr">
@@ -10681,7 +10681,7 @@
       </c>
       <c r="AB89" t="inlineStr">
         <is>
-          <t>batch_04ef5ec3e6b54457</t>
+          <t>batch_976be391c94a4aae</t>
         </is>
       </c>
       <c r="AC89" t="inlineStr">
@@ -10697,7 +10697,7 @@
       <c r="AE89" t="inlineStr"/>
       <c r="AF89" t="inlineStr">
         <is>
-          <t>2026-05-14T02:33:19+00:00</t>
+          <t>2026-05-14T02:59:23+00:00</t>
         </is>
       </c>
       <c r="AG89" t="inlineStr">
@@ -10800,7 +10800,7 @@
       </c>
       <c r="AB90" t="inlineStr">
         <is>
-          <t>batch_04ef5ec3e6b54457</t>
+          <t>batch_976be391c94a4aae</t>
         </is>
       </c>
       <c r="AC90" t="inlineStr">
@@ -10816,7 +10816,7 @@
       <c r="AE90" t="inlineStr"/>
       <c r="AF90" t="inlineStr">
         <is>
-          <t>2026-05-14T02:33:19+00:00</t>
+          <t>2026-05-14T02:59:23+00:00</t>
         </is>
       </c>
       <c r="AG90" t="inlineStr">
@@ -10919,7 +10919,7 @@
       </c>
       <c r="AB91" t="inlineStr">
         <is>
-          <t>batch_04ef5ec3e6b54457</t>
+          <t>batch_976be391c94a4aae</t>
         </is>
       </c>
       <c r="AC91" t="inlineStr">
@@ -10935,7 +10935,7 @@
       <c r="AE91" t="inlineStr"/>
       <c r="AF91" t="inlineStr">
         <is>
-          <t>2026-05-14T02:33:19+00:00</t>
+          <t>2026-05-14T02:59:23+00:00</t>
         </is>
       </c>
       <c r="AG91" t="inlineStr">
@@ -11038,7 +11038,7 @@
       </c>
       <c r="AB92" t="inlineStr">
         <is>
-          <t>batch_04ef5ec3e6b54457</t>
+          <t>batch_976be391c94a4aae</t>
         </is>
       </c>
       <c r="AC92" t="inlineStr">
@@ -11054,7 +11054,7 @@
       <c r="AE92" t="inlineStr"/>
       <c r="AF92" t="inlineStr">
         <is>
-          <t>2026-05-14T02:33:19+00:00</t>
+          <t>2026-05-14T02:59:23+00:00</t>
         </is>
       </c>
       <c r="AG92" t="inlineStr">
@@ -11157,7 +11157,7 @@
       </c>
       <c r="AB93" t="inlineStr">
         <is>
-          <t>batch_04ef5ec3e6b54457</t>
+          <t>batch_976be391c94a4aae</t>
         </is>
       </c>
       <c r="AC93" t="inlineStr">
@@ -11173,7 +11173,7 @@
       <c r="AE93" t="inlineStr"/>
       <c r="AF93" t="inlineStr">
         <is>
-          <t>2026-05-14T02:33:19+00:00</t>
+          <t>2026-05-14T02:59:23+00:00</t>
         </is>
       </c>
       <c r="AG93" t="inlineStr">
@@ -11276,7 +11276,7 @@
       </c>
       <c r="AB94" t="inlineStr">
         <is>
-          <t>batch_04ef5ec3e6b54457</t>
+          <t>batch_976be391c94a4aae</t>
         </is>
       </c>
       <c r="AC94" t="inlineStr">
@@ -11292,7 +11292,7 @@
       <c r="AE94" t="inlineStr"/>
       <c r="AF94" t="inlineStr">
         <is>
-          <t>2026-05-14T02:33:19+00:00</t>
+          <t>2026-05-14T02:59:23+00:00</t>
         </is>
       </c>
       <c r="AG94" t="inlineStr">
@@ -11395,7 +11395,7 @@
       </c>
       <c r="AB95" t="inlineStr">
         <is>
-          <t>batch_04ef5ec3e6b54457</t>
+          <t>batch_976be391c94a4aae</t>
         </is>
       </c>
       <c r="AC95" t="inlineStr">
@@ -11411,7 +11411,7 @@
       <c r="AE95" t="inlineStr"/>
       <c r="AF95" t="inlineStr">
         <is>
-          <t>2026-05-14T02:33:19+00:00</t>
+          <t>2026-05-14T02:59:23+00:00</t>
         </is>
       </c>
       <c r="AG95" t="inlineStr">
@@ -11514,7 +11514,7 @@
       </c>
       <c r="AB96" t="inlineStr">
         <is>
-          <t>batch_04ef5ec3e6b54457</t>
+          <t>batch_976be391c94a4aae</t>
         </is>
       </c>
       <c r="AC96" t="inlineStr">
@@ -11530,7 +11530,7 @@
       <c r="AE96" t="inlineStr"/>
       <c r="AF96" t="inlineStr">
         <is>
-          <t>2026-05-14T02:33:19+00:00</t>
+          <t>2026-05-14T02:59:23+00:00</t>
         </is>
       </c>
       <c r="AG96" t="inlineStr">
@@ -11633,7 +11633,7 @@
       </c>
       <c r="AB97" t="inlineStr">
         <is>
-          <t>batch_04ef5ec3e6b54457</t>
+          <t>batch_976be391c94a4aae</t>
         </is>
       </c>
       <c r="AC97" t="inlineStr">
@@ -11649,7 +11649,7 @@
       <c r="AE97" t="inlineStr"/>
       <c r="AF97" t="inlineStr">
         <is>
-          <t>2026-05-14T02:33:19+00:00</t>
+          <t>2026-05-14T02:59:23+00:00</t>
         </is>
       </c>
       <c r="AG97" t="inlineStr">
@@ -11752,7 +11752,7 @@
       </c>
       <c r="AB98" t="inlineStr">
         <is>
-          <t>batch_04ef5ec3e6b54457</t>
+          <t>batch_976be391c94a4aae</t>
         </is>
       </c>
       <c r="AC98" t="inlineStr">
@@ -11768,7 +11768,7 @@
       <c r="AE98" t="inlineStr"/>
       <c r="AF98" t="inlineStr">
         <is>
-          <t>2026-05-14T02:33:19+00:00</t>
+          <t>2026-05-14T02:59:23+00:00</t>
         </is>
       </c>
       <c r="AG98" t="inlineStr">
@@ -11868,7 +11868,7 @@
       </c>
       <c r="AB99" t="inlineStr">
         <is>
-          <t>batch_04ef5ec3e6b54457</t>
+          <t>batch_976be391c94a4aae</t>
         </is>
       </c>
       <c r="AC99" t="inlineStr">
@@ -11884,7 +11884,7 @@
       <c r="AE99" t="inlineStr"/>
       <c r="AF99" t="inlineStr">
         <is>
-          <t>2026-05-14T02:33:19+00:00</t>
+          <t>2026-05-14T02:59:23+00:00</t>
         </is>
       </c>
       <c r="AG99" t="inlineStr">
@@ -11984,7 +11984,7 @@
       </c>
       <c r="AB100" t="inlineStr">
         <is>
-          <t>batch_04ef5ec3e6b54457</t>
+          <t>batch_976be391c94a4aae</t>
         </is>
       </c>
       <c r="AC100" t="inlineStr">
@@ -12000,7 +12000,7 @@
       <c r="AE100" t="inlineStr"/>
       <c r="AF100" t="inlineStr">
         <is>
-          <t>2026-05-14T02:33:19+00:00</t>
+          <t>2026-05-14T02:59:23+00:00</t>
         </is>
       </c>
       <c r="AG100" t="inlineStr">
@@ -12100,7 +12100,7 @@
       </c>
       <c r="AB101" t="inlineStr">
         <is>
-          <t>batch_04ef5ec3e6b54457</t>
+          <t>batch_976be391c94a4aae</t>
         </is>
       </c>
       <c r="AC101" t="inlineStr">
@@ -12116,7 +12116,7 @@
       <c r="AE101" t="inlineStr"/>
       <c r="AF101" t="inlineStr">
         <is>
-          <t>2026-05-14T02:33:19+00:00</t>
+          <t>2026-05-14T02:59:23+00:00</t>
         </is>
       </c>
       <c r="AG101" t="inlineStr">
@@ -12216,7 +12216,7 @@
       </c>
       <c r="AB102" t="inlineStr">
         <is>
-          <t>batch_04ef5ec3e6b54457</t>
+          <t>batch_976be391c94a4aae</t>
         </is>
       </c>
       <c r="AC102" t="inlineStr">
@@ -12232,7 +12232,7 @@
       <c r="AE102" t="inlineStr"/>
       <c r="AF102" t="inlineStr">
         <is>
-          <t>2026-05-14T02:33:19+00:00</t>
+          <t>2026-05-14T02:59:23+00:00</t>
         </is>
       </c>
       <c r="AG102" t="inlineStr">
@@ -12332,7 +12332,7 @@
       </c>
       <c r="AB103" t="inlineStr">
         <is>
-          <t>batch_04ef5ec3e6b54457</t>
+          <t>batch_976be391c94a4aae</t>
         </is>
       </c>
       <c r="AC103" t="inlineStr">
@@ -12348,7 +12348,7 @@
       <c r="AE103" t="inlineStr"/>
       <c r="AF103" t="inlineStr">
         <is>
-          <t>2026-05-14T02:33:19+00:00</t>
+          <t>2026-05-14T02:59:23+00:00</t>
         </is>
       </c>
       <c r="AG103" t="inlineStr">
@@ -12448,7 +12448,7 @@
       </c>
       <c r="AB104" t="inlineStr">
         <is>
-          <t>batch_04ef5ec3e6b54457</t>
+          <t>batch_976be391c94a4aae</t>
         </is>
       </c>
       <c r="AC104" t="inlineStr">
@@ -12464,7 +12464,7 @@
       <c r="AE104" t="inlineStr"/>
       <c r="AF104" t="inlineStr">
         <is>
-          <t>2026-05-14T02:33:19+00:00</t>
+          <t>2026-05-14T02:59:23+00:00</t>
         </is>
       </c>
       <c r="AG104" t="inlineStr">
@@ -12567,7 +12567,7 @@
       </c>
       <c r="AB105" t="inlineStr">
         <is>
-          <t>batch_04ef5ec3e6b54457</t>
+          <t>batch_976be391c94a4aae</t>
         </is>
       </c>
       <c r="AC105" t="inlineStr">
@@ -12583,7 +12583,7 @@
       <c r="AE105" t="inlineStr"/>
       <c r="AF105" t="inlineStr">
         <is>
-          <t>2026-05-14T02:33:19+00:00</t>
+          <t>2026-05-14T02:59:23+00:00</t>
         </is>
       </c>
       <c r="AG105" t="inlineStr">
@@ -12683,7 +12683,7 @@
       </c>
       <c r="AB106" t="inlineStr">
         <is>
-          <t>batch_04ef5ec3e6b54457</t>
+          <t>batch_976be391c94a4aae</t>
         </is>
       </c>
       <c r="AC106" t="inlineStr">
@@ -12699,7 +12699,7 @@
       <c r="AE106" t="inlineStr"/>
       <c r="AF106" t="inlineStr">
         <is>
-          <t>2026-05-14T02:33:19+00:00</t>
+          <t>2026-05-14T02:59:23+00:00</t>
         </is>
       </c>
       <c r="AG106" t="inlineStr">
@@ -12799,7 +12799,7 @@
       </c>
       <c r="AB107" t="inlineStr">
         <is>
-          <t>batch_04ef5ec3e6b54457</t>
+          <t>batch_976be391c94a4aae</t>
         </is>
       </c>
       <c r="AC107" t="inlineStr">
@@ -12815,7 +12815,7 @@
       <c r="AE107" t="inlineStr"/>
       <c r="AF107" t="inlineStr">
         <is>
-          <t>2026-05-14T02:33:19+00:00</t>
+          <t>2026-05-14T02:59:23+00:00</t>
         </is>
       </c>
       <c r="AG107" t="inlineStr">
@@ -12915,7 +12915,7 @@
       </c>
       <c r="AB108" t="inlineStr">
         <is>
-          <t>batch_04ef5ec3e6b54457</t>
+          <t>batch_976be391c94a4aae</t>
         </is>
       </c>
       <c r="AC108" t="inlineStr">
@@ -12931,7 +12931,7 @@
       <c r="AE108" t="inlineStr"/>
       <c r="AF108" t="inlineStr">
         <is>
-          <t>2026-05-14T02:33:19+00:00</t>
+          <t>2026-05-14T02:59:23+00:00</t>
         </is>
       </c>
       <c r="AG108" t="inlineStr">
@@ -13031,7 +13031,7 @@
       </c>
       <c r="AB109" t="inlineStr">
         <is>
-          <t>batch_04ef5ec3e6b54457</t>
+          <t>batch_976be391c94a4aae</t>
         </is>
       </c>
       <c r="AC109" t="inlineStr">
@@ -13047,7 +13047,7 @@
       <c r="AE109" t="inlineStr"/>
       <c r="AF109" t="inlineStr">
         <is>
-          <t>2026-05-14T02:33:19+00:00</t>
+          <t>2026-05-14T02:59:23+00:00</t>
         </is>
       </c>
       <c r="AG109" t="inlineStr">
@@ -13147,7 +13147,7 @@
       </c>
       <c r="AB110" t="inlineStr">
         <is>
-          <t>batch_04ef5ec3e6b54457</t>
+          <t>batch_976be391c94a4aae</t>
         </is>
       </c>
       <c r="AC110" t="inlineStr">
@@ -13163,7 +13163,7 @@
       <c r="AE110" t="inlineStr"/>
       <c r="AF110" t="inlineStr">
         <is>
-          <t>2026-05-14T02:33:19+00:00</t>
+          <t>2026-05-14T02:59:23+00:00</t>
         </is>
       </c>
       <c r="AG110" t="inlineStr">
@@ -13263,7 +13263,7 @@
       </c>
       <c r="AB111" t="inlineStr">
         <is>
-          <t>batch_04ef5ec3e6b54457</t>
+          <t>batch_976be391c94a4aae</t>
         </is>
       </c>
       <c r="AC111" t="inlineStr">
@@ -13279,7 +13279,7 @@
       <c r="AE111" t="inlineStr"/>
       <c r="AF111" t="inlineStr">
         <is>
-          <t>2026-05-14T02:33:19+00:00</t>
+          <t>2026-05-14T02:59:23+00:00</t>
         </is>
       </c>
       <c r="AG111" t="inlineStr">
@@ -13379,7 +13379,7 @@
       </c>
       <c r="AB112" t="inlineStr">
         <is>
-          <t>batch_04ef5ec3e6b54457</t>
+          <t>batch_976be391c94a4aae</t>
         </is>
       </c>
       <c r="AC112" t="inlineStr">
@@ -13395,7 +13395,7 @@
       <c r="AE112" t="inlineStr"/>
       <c r="AF112" t="inlineStr">
         <is>
-          <t>2026-05-14T02:33:19+00:00</t>
+          <t>2026-05-14T02:59:23+00:00</t>
         </is>
       </c>
       <c r="AG112" t="inlineStr">
@@ -13495,7 +13495,7 @@
       </c>
       <c r="AB113" t="inlineStr">
         <is>
-          <t>batch_04ef5ec3e6b54457</t>
+          <t>batch_976be391c94a4aae</t>
         </is>
       </c>
       <c r="AC113" t="inlineStr">
@@ -13511,7 +13511,7 @@
       <c r="AE113" t="inlineStr"/>
       <c r="AF113" t="inlineStr">
         <is>
-          <t>2026-05-14T02:33:19+00:00</t>
+          <t>2026-05-14T02:59:23+00:00</t>
         </is>
       </c>
       <c r="AG113" t="inlineStr">
@@ -13611,7 +13611,7 @@
       </c>
       <c r="AB114" t="inlineStr">
         <is>
-          <t>batch_04ef5ec3e6b54457</t>
+          <t>batch_976be391c94a4aae</t>
         </is>
       </c>
       <c r="AC114" t="inlineStr">
@@ -13627,7 +13627,7 @@
       <c r="AE114" t="inlineStr"/>
       <c r="AF114" t="inlineStr">
         <is>
-          <t>2026-05-14T02:33:19+00:00</t>
+          <t>2026-05-14T02:59:23+00:00</t>
         </is>
       </c>
       <c r="AG114" t="inlineStr">
@@ -13727,7 +13727,7 @@
       </c>
       <c r="AB115" t="inlineStr">
         <is>
-          <t>batch_04ef5ec3e6b54457</t>
+          <t>batch_976be391c94a4aae</t>
         </is>
       </c>
       <c r="AC115" t="inlineStr">
@@ -13743,7 +13743,7 @@
       <c r="AE115" t="inlineStr"/>
       <c r="AF115" t="inlineStr">
         <is>
-          <t>2026-05-14T02:33:19+00:00</t>
+          <t>2026-05-14T02:59:23+00:00</t>
         </is>
       </c>
       <c r="AG115" t="inlineStr">
@@ -13843,7 +13843,7 @@
       </c>
       <c r="AB116" t="inlineStr">
         <is>
-          <t>batch_04ef5ec3e6b54457</t>
+          <t>batch_976be391c94a4aae</t>
         </is>
       </c>
       <c r="AC116" t="inlineStr">
@@ -13859,7 +13859,7 @@
       <c r="AE116" t="inlineStr"/>
       <c r="AF116" t="inlineStr">
         <is>
-          <t>2026-05-14T02:33:19+00:00</t>
+          <t>2026-05-14T02:59:23+00:00</t>
         </is>
       </c>
       <c r="AG116" t="inlineStr">
@@ -13959,7 +13959,7 @@
       </c>
       <c r="AB117" t="inlineStr">
         <is>
-          <t>batch_04ef5ec3e6b54457</t>
+          <t>batch_976be391c94a4aae</t>
         </is>
       </c>
       <c r="AC117" t="inlineStr">
@@ -13975,7 +13975,7 @@
       <c r="AE117" t="inlineStr"/>
       <c r="AF117" t="inlineStr">
         <is>
-          <t>2026-05-14T02:33:19+00:00</t>
+          <t>2026-05-14T02:59:23+00:00</t>
         </is>
       </c>
       <c r="AG117" t="inlineStr">
@@ -14075,7 +14075,7 @@
       </c>
       <c r="AB118" t="inlineStr">
         <is>
-          <t>batch_04ef5ec3e6b54457</t>
+          <t>batch_976be391c94a4aae</t>
         </is>
       </c>
       <c r="AC118" t="inlineStr">
@@ -14091,7 +14091,7 @@
       <c r="AE118" t="inlineStr"/>
       <c r="AF118" t="inlineStr">
         <is>
-          <t>2026-05-14T02:33:19+00:00</t>
+          <t>2026-05-14T02:59:23+00:00</t>
         </is>
       </c>
       <c r="AG118" t="inlineStr">
@@ -14191,7 +14191,7 @@
       </c>
       <c r="AB119" t="inlineStr">
         <is>
-          <t>batch_04ef5ec3e6b54457</t>
+          <t>batch_976be391c94a4aae</t>
         </is>
       </c>
       <c r="AC119" t="inlineStr">
@@ -14207,7 +14207,7 @@
       <c r="AE119" t="inlineStr"/>
       <c r="AF119" t="inlineStr">
         <is>
-          <t>2026-05-14T02:33:19+00:00</t>
+          <t>2026-05-14T02:59:23+00:00</t>
         </is>
       </c>
       <c r="AG119" t="inlineStr">
@@ -14307,7 +14307,7 @@
       </c>
       <c r="AB120" t="inlineStr">
         <is>
-          <t>batch_04ef5ec3e6b54457</t>
+          <t>batch_976be391c94a4aae</t>
         </is>
       </c>
       <c r="AC120" t="inlineStr">
@@ -14323,7 +14323,7 @@
       <c r="AE120" t="inlineStr"/>
       <c r="AF120" t="inlineStr">
         <is>
-          <t>2026-05-14T02:33:19+00:00</t>
+          <t>2026-05-14T02:59:23+00:00</t>
         </is>
       </c>
       <c r="AG120" t="inlineStr">
@@ -14423,7 +14423,7 @@
       </c>
       <c r="AB121" t="inlineStr">
         <is>
-          <t>batch_04ef5ec3e6b54457</t>
+          <t>batch_976be391c94a4aae</t>
         </is>
       </c>
       <c r="AC121" t="inlineStr">
@@ -14439,7 +14439,7 @@
       <c r="AE121" t="inlineStr"/>
       <c r="AF121" t="inlineStr">
         <is>
-          <t>2026-05-14T02:33:19+00:00</t>
+          <t>2026-05-14T02:59:23+00:00</t>
         </is>
       </c>
       <c r="AG121" t="inlineStr">
@@ -14539,7 +14539,7 @@
       </c>
       <c r="AB122" t="inlineStr">
         <is>
-          <t>batch_04ef5ec3e6b54457</t>
+          <t>batch_976be391c94a4aae</t>
         </is>
       </c>
       <c r="AC122" t="inlineStr">
@@ -14555,7 +14555,7 @@
       <c r="AE122" t="inlineStr"/>
       <c r="AF122" t="inlineStr">
         <is>
-          <t>2026-05-14T02:33:19+00:00</t>
+          <t>2026-05-14T02:59:23+00:00</t>
         </is>
       </c>
       <c r="AG122" t="inlineStr">
@@ -14655,7 +14655,7 @@
       </c>
       <c r="AB123" t="inlineStr">
         <is>
-          <t>batch_04ef5ec3e6b54457</t>
+          <t>batch_976be391c94a4aae</t>
         </is>
       </c>
       <c r="AC123" t="inlineStr">
@@ -14671,7 +14671,7 @@
       <c r="AE123" t="inlineStr"/>
       <c r="AF123" t="inlineStr">
         <is>
-          <t>2026-05-14T02:33:19+00:00</t>
+          <t>2026-05-14T02:59:23+00:00</t>
         </is>
       </c>
       <c r="AG123" t="inlineStr">
@@ -14771,7 +14771,7 @@
       </c>
       <c r="AB124" t="inlineStr">
         <is>
-          <t>batch_04ef5ec3e6b54457</t>
+          <t>batch_976be391c94a4aae</t>
         </is>
       </c>
       <c r="AC124" t="inlineStr">
@@ -14787,7 +14787,7 @@
       <c r="AE124" t="inlineStr"/>
       <c r="AF124" t="inlineStr">
         <is>
-          <t>2026-05-14T02:33:19+00:00</t>
+          <t>2026-05-14T02:59:23+00:00</t>
         </is>
       </c>
       <c r="AG124" t="inlineStr">
@@ -14887,7 +14887,7 @@
       </c>
       <c r="AB125" t="inlineStr">
         <is>
-          <t>batch_04ef5ec3e6b54457</t>
+          <t>batch_976be391c94a4aae</t>
         </is>
       </c>
       <c r="AC125" t="inlineStr">
@@ -14903,7 +14903,7 @@
       <c r="AE125" t="inlineStr"/>
       <c r="AF125" t="inlineStr">
         <is>
-          <t>2026-05-14T02:33:19+00:00</t>
+          <t>2026-05-14T02:59:23+00:00</t>
         </is>
       </c>
       <c r="AG125" t="inlineStr">
@@ -15003,7 +15003,7 @@
       </c>
       <c r="AB126" t="inlineStr">
         <is>
-          <t>batch_04ef5ec3e6b54457</t>
+          <t>batch_976be391c94a4aae</t>
         </is>
       </c>
       <c r="AC126" t="inlineStr">
@@ -15019,7 +15019,7 @@
       <c r="AE126" t="inlineStr"/>
       <c r="AF126" t="inlineStr">
         <is>
-          <t>2026-05-14T02:33:19+00:00</t>
+          <t>2026-05-14T02:59:23+00:00</t>
         </is>
       </c>
       <c r="AG126" t="inlineStr">
@@ -15119,7 +15119,7 @@
       </c>
       <c r="AB127" t="inlineStr">
         <is>
-          <t>batch_04ef5ec3e6b54457</t>
+          <t>batch_976be391c94a4aae</t>
         </is>
       </c>
       <c r="AC127" t="inlineStr">
@@ -15135,7 +15135,7 @@
       <c r="AE127" t="inlineStr"/>
       <c r="AF127" t="inlineStr">
         <is>
-          <t>2026-05-14T02:33:19+00:00</t>
+          <t>2026-05-14T02:59:23+00:00</t>
         </is>
       </c>
       <c r="AG127" t="inlineStr">
@@ -15235,7 +15235,7 @@
       </c>
       <c r="AB128" t="inlineStr">
         <is>
-          <t>batch_04ef5ec3e6b54457</t>
+          <t>batch_976be391c94a4aae</t>
         </is>
       </c>
       <c r="AC128" t="inlineStr">
@@ -15251,7 +15251,7 @@
       <c r="AE128" t="inlineStr"/>
       <c r="AF128" t="inlineStr">
         <is>
-          <t>2026-05-14T02:33:19+00:00</t>
+          <t>2026-05-14T02:59:23+00:00</t>
         </is>
       </c>
       <c r="AG128" t="inlineStr">
@@ -15351,7 +15351,7 @@
       </c>
       <c r="AB129" t="inlineStr">
         <is>
-          <t>batch_04ef5ec3e6b54457</t>
+          <t>batch_976be391c94a4aae</t>
         </is>
       </c>
       <c r="AC129" t="inlineStr">
@@ -15367,7 +15367,7 @@
       <c r="AE129" t="inlineStr"/>
       <c r="AF129" t="inlineStr">
         <is>
-          <t>2026-05-14T02:33:19+00:00</t>
+          <t>2026-05-14T02:59:23+00:00</t>
         </is>
       </c>
       <c r="AG129" t="inlineStr">
@@ -15467,7 +15467,7 @@
       </c>
       <c r="AB130" t="inlineStr">
         <is>
-          <t>batch_04ef5ec3e6b54457</t>
+          <t>batch_976be391c94a4aae</t>
         </is>
       </c>
       <c r="AC130" t="inlineStr">
@@ -15483,7 +15483,7 @@
       <c r="AE130" t="inlineStr"/>
       <c r="AF130" t="inlineStr">
         <is>
-          <t>2026-05-14T02:33:19+00:00</t>
+          <t>2026-05-14T02:59:23+00:00</t>
         </is>
       </c>
       <c r="AG130" t="inlineStr">
@@ -15583,7 +15583,7 @@
       </c>
       <c r="AB131" t="inlineStr">
         <is>
-          <t>batch_04ef5ec3e6b54457</t>
+          <t>batch_976be391c94a4aae</t>
         </is>
       </c>
       <c r="AC131" t="inlineStr">
@@ -15599,7 +15599,7 @@
       <c r="AE131" t="inlineStr"/>
       <c r="AF131" t="inlineStr">
         <is>
-          <t>2026-05-14T02:33:19+00:00</t>
+          <t>2026-05-14T02:59:23+00:00</t>
         </is>
       </c>
       <c r="AG131" t="inlineStr">
@@ -15699,7 +15699,7 @@
       </c>
       <c r="AB132" t="inlineStr">
         <is>
-          <t>batch_04ef5ec3e6b54457</t>
+          <t>batch_976be391c94a4aae</t>
         </is>
       </c>
       <c r="AC132" t="inlineStr">
@@ -15715,7 +15715,7 @@
       <c r="AE132" t="inlineStr"/>
       <c r="AF132" t="inlineStr">
         <is>
-          <t>2026-05-14T02:33:19+00:00</t>
+          <t>2026-05-14T02:59:23+00:00</t>
         </is>
       </c>
       <c r="AG132" t="inlineStr">
@@ -15815,7 +15815,7 @@
       </c>
       <c r="AB133" t="inlineStr">
         <is>
-          <t>batch_04ef5ec3e6b54457</t>
+          <t>batch_976be391c94a4aae</t>
         </is>
       </c>
       <c r="AC133" t="inlineStr">
@@ -15831,7 +15831,7 @@
       <c r="AE133" t="inlineStr"/>
       <c r="AF133" t="inlineStr">
         <is>
-          <t>2026-05-14T02:33:19+00:00</t>
+          <t>2026-05-14T02:59:23+00:00</t>
         </is>
       </c>
       <c r="AG133" t="inlineStr">
@@ -15931,7 +15931,7 @@
       </c>
       <c r="AB134" t="inlineStr">
         <is>
-          <t>batch_04ef5ec3e6b54457</t>
+          <t>batch_976be391c94a4aae</t>
         </is>
       </c>
       <c r="AC134" t="inlineStr">
@@ -15947,7 +15947,7 @@
       <c r="AE134" t="inlineStr"/>
       <c r="AF134" t="inlineStr">
         <is>
-          <t>2026-05-14T02:33:19+00:00</t>
+          <t>2026-05-14T02:59:23+00:00</t>
         </is>
       </c>
       <c r="AG134" t="inlineStr">
@@ -16047,7 +16047,7 @@
       </c>
       <c r="AB135" t="inlineStr">
         <is>
-          <t>batch_04ef5ec3e6b54457</t>
+          <t>batch_976be391c94a4aae</t>
         </is>
       </c>
       <c r="AC135" t="inlineStr">
@@ -16063,7 +16063,7 @@
       <c r="AE135" t="inlineStr"/>
       <c r="AF135" t="inlineStr">
         <is>
-          <t>2026-05-14T02:33:19+00:00</t>
+          <t>2026-05-14T02:59:23+00:00</t>
         </is>
       </c>
       <c r="AG135" t="inlineStr">
@@ -16163,7 +16163,7 @@
       </c>
       <c r="AB136" t="inlineStr">
         <is>
-          <t>batch_04ef5ec3e6b54457</t>
+          <t>batch_976be391c94a4aae</t>
         </is>
       </c>
       <c r="AC136" t="inlineStr">
@@ -16179,7 +16179,7 @@
       <c r="AE136" t="inlineStr"/>
       <c r="AF136" t="inlineStr">
         <is>
-          <t>2026-05-14T02:33:19+00:00</t>
+          <t>2026-05-14T02:59:23+00:00</t>
         </is>
       </c>
       <c r="AG136" t="inlineStr">
@@ -16279,7 +16279,7 @@
       </c>
       <c r="AB137" t="inlineStr">
         <is>
-          <t>batch_04ef5ec3e6b54457</t>
+          <t>batch_976be391c94a4aae</t>
         </is>
       </c>
       <c r="AC137" t="inlineStr">
@@ -16295,7 +16295,7 @@
       <c r="AE137" t="inlineStr"/>
       <c r="AF137" t="inlineStr">
         <is>
-          <t>2026-05-14T02:33:19+00:00</t>
+          <t>2026-05-14T02:59:23+00:00</t>
         </is>
       </c>
       <c r="AG137" t="inlineStr">
@@ -16395,7 +16395,7 @@
       </c>
       <c r="AB138" t="inlineStr">
         <is>
-          <t>batch_04ef5ec3e6b54457</t>
+          <t>batch_976be391c94a4aae</t>
         </is>
       </c>
       <c r="AC138" t="inlineStr">
@@ -16411,7 +16411,7 @@
       <c r="AE138" t="inlineStr"/>
       <c r="AF138" t="inlineStr">
         <is>
-          <t>2026-05-14T02:33:19+00:00</t>
+          <t>2026-05-14T02:59:23+00:00</t>
         </is>
       </c>
       <c r="AG138" t="inlineStr">
@@ -16511,7 +16511,7 @@
       </c>
       <c r="AB139" t="inlineStr">
         <is>
-          <t>batch_04ef5ec3e6b54457</t>
+          <t>batch_976be391c94a4aae</t>
         </is>
       </c>
       <c r="AC139" t="inlineStr">
@@ -16527,7 +16527,7 @@
       <c r="AE139" t="inlineStr"/>
       <c r="AF139" t="inlineStr">
         <is>
-          <t>2026-05-14T02:33:19+00:00</t>
+          <t>2026-05-14T02:59:23+00:00</t>
         </is>
       </c>
       <c r="AG139" t="inlineStr">
@@ -16627,7 +16627,7 @@
       </c>
       <c r="AB140" t="inlineStr">
         <is>
-          <t>batch_04ef5ec3e6b54457</t>
+          <t>batch_976be391c94a4aae</t>
         </is>
       </c>
       <c r="AC140" t="inlineStr">
@@ -16643,7 +16643,7 @@
       <c r="AE140" t="inlineStr"/>
       <c r="AF140" t="inlineStr">
         <is>
-          <t>2026-05-14T02:33:19+00:00</t>
+          <t>2026-05-14T02:59:23+00:00</t>
         </is>
       </c>
       <c r="AG140" t="inlineStr">
@@ -16743,7 +16743,7 @@
       </c>
       <c r="AB141" t="inlineStr">
         <is>
-          <t>batch_04ef5ec3e6b54457</t>
+          <t>batch_976be391c94a4aae</t>
         </is>
       </c>
       <c r="AC141" t="inlineStr">
@@ -16759,7 +16759,7 @@
       <c r="AE141" t="inlineStr"/>
       <c r="AF141" t="inlineStr">
         <is>
-          <t>2026-05-14T02:33:19+00:00</t>
+          <t>2026-05-14T02:59:23+00:00</t>
         </is>
       </c>
       <c r="AG141" t="inlineStr">
@@ -16859,7 +16859,7 @@
       </c>
       <c r="AB142" t="inlineStr">
         <is>
-          <t>batch_04ef5ec3e6b54457</t>
+          <t>batch_976be391c94a4aae</t>
         </is>
       </c>
       <c r="AC142" t="inlineStr">
@@ -16875,7 +16875,7 @@
       <c r="AE142" t="inlineStr"/>
       <c r="AF142" t="inlineStr">
         <is>
-          <t>2026-05-14T02:33:19+00:00</t>
+          <t>2026-05-14T02:59:23+00:00</t>
         </is>
       </c>
       <c r="AG142" t="inlineStr">
@@ -16975,7 +16975,7 @@
       </c>
       <c r="AB143" t="inlineStr">
         <is>
-          <t>batch_04ef5ec3e6b54457</t>
+          <t>batch_976be391c94a4aae</t>
         </is>
       </c>
       <c r="AC143" t="inlineStr">
@@ -16991,7 +16991,7 @@
       <c r="AE143" t="inlineStr"/>
       <c r="AF143" t="inlineStr">
         <is>
-          <t>2026-05-14T02:33:19+00:00</t>
+          <t>2026-05-14T02:59:23+00:00</t>
         </is>
       </c>
       <c r="AG143" t="inlineStr">
@@ -17091,7 +17091,7 @@
       </c>
       <c r="AB144" t="inlineStr">
         <is>
-          <t>batch_04ef5ec3e6b54457</t>
+          <t>batch_976be391c94a4aae</t>
         </is>
       </c>
       <c r="AC144" t="inlineStr">
@@ -17107,7 +17107,7 @@
       <c r="AE144" t="inlineStr"/>
       <c r="AF144" t="inlineStr">
         <is>
-          <t>2026-05-14T02:33:19+00:00</t>
+          <t>2026-05-14T02:59:23+00:00</t>
         </is>
       </c>
       <c r="AG144" t="inlineStr">
@@ -17207,7 +17207,7 @@
       </c>
       <c r="AB145" t="inlineStr">
         <is>
-          <t>batch_04ef5ec3e6b54457</t>
+          <t>batch_976be391c94a4aae</t>
         </is>
       </c>
       <c r="AC145" t="inlineStr">
@@ -17223,7 +17223,7 @@
       <c r="AE145" t="inlineStr"/>
       <c r="AF145" t="inlineStr">
         <is>
-          <t>2026-05-14T02:33:19+00:00</t>
+          <t>2026-05-14T02:59:23+00:00</t>
         </is>
       </c>
       <c r="AG145" t="inlineStr">
@@ -17323,7 +17323,7 @@
       </c>
       <c r="AB146" t="inlineStr">
         <is>
-          <t>batch_04ef5ec3e6b54457</t>
+          <t>batch_976be391c94a4aae</t>
         </is>
       </c>
       <c r="AC146" t="inlineStr">
@@ -17339,7 +17339,7 @@
       <c r="AE146" t="inlineStr"/>
       <c r="AF146" t="inlineStr">
         <is>
-          <t>2026-05-14T02:33:19+00:00</t>
+          <t>2026-05-14T02:59:23+00:00</t>
         </is>
       </c>
       <c r="AG146" t="inlineStr">
@@ -17439,7 +17439,7 @@
       </c>
       <c r="AB147" t="inlineStr">
         <is>
-          <t>batch_04ef5ec3e6b54457</t>
+          <t>batch_976be391c94a4aae</t>
         </is>
       </c>
       <c r="AC147" t="inlineStr">
@@ -17455,7 +17455,7 @@
       <c r="AE147" t="inlineStr"/>
       <c r="AF147" t="inlineStr">
         <is>
-          <t>2026-05-14T02:33:19+00:00</t>
+          <t>2026-05-14T02:59:23+00:00</t>
         </is>
       </c>
       <c r="AG147" t="inlineStr">
@@ -17555,7 +17555,7 @@
       </c>
       <c r="AB148" t="inlineStr">
         <is>
-          <t>batch_04ef5ec3e6b54457</t>
+          <t>batch_976be391c94a4aae</t>
         </is>
       </c>
       <c r="AC148" t="inlineStr">
@@ -17571,7 +17571,7 @@
       <c r="AE148" t="inlineStr"/>
       <c r="AF148" t="inlineStr">
         <is>
-          <t>2026-05-14T02:33:19+00:00</t>
+          <t>2026-05-14T02:59:23+00:00</t>
         </is>
       </c>
       <c r="AG148" t="inlineStr">
@@ -17671,7 +17671,7 @@
       </c>
       <c r="AB149" t="inlineStr">
         <is>
-          <t>batch_04ef5ec3e6b54457</t>
+          <t>batch_976be391c94a4aae</t>
         </is>
       </c>
       <c r="AC149" t="inlineStr">
@@ -17687,7 +17687,7 @@
       <c r="AE149" t="inlineStr"/>
       <c r="AF149" t="inlineStr">
         <is>
-          <t>2026-05-14T02:33:19+00:00</t>
+          <t>2026-05-14T02:59:23+00:00</t>
         </is>
       </c>
       <c r="AG149" t="inlineStr">
@@ -17787,7 +17787,7 @@
       </c>
       <c r="AB150" t="inlineStr">
         <is>
-          <t>batch_04ef5ec3e6b54457</t>
+          <t>batch_976be391c94a4aae</t>
         </is>
       </c>
       <c r="AC150" t="inlineStr">
@@ -17803,7 +17803,7 @@
       <c r="AE150" t="inlineStr"/>
       <c r="AF150" t="inlineStr">
         <is>
-          <t>2026-05-14T02:33:19+00:00</t>
+          <t>2026-05-14T02:59:23+00:00</t>
         </is>
       </c>
       <c r="AG150" t="inlineStr">
@@ -17903,7 +17903,7 @@
       </c>
       <c r="AB151" t="inlineStr">
         <is>
-          <t>batch_04ef5ec3e6b54457</t>
+          <t>batch_976be391c94a4aae</t>
         </is>
       </c>
       <c r="AC151" t="inlineStr">
@@ -17919,7 +17919,7 @@
       <c r="AE151" t="inlineStr"/>
       <c r="AF151" t="inlineStr">
         <is>
-          <t>2026-05-14T02:33:19+00:00</t>
+          <t>2026-05-14T02:59:23+00:00</t>
         </is>
       </c>
       <c r="AG151" t="inlineStr">
@@ -18019,7 +18019,7 @@
       </c>
       <c r="AB152" t="inlineStr">
         <is>
-          <t>batch_04ef5ec3e6b54457</t>
+          <t>batch_976be391c94a4aae</t>
         </is>
       </c>
       <c r="AC152" t="inlineStr">
@@ -18035,7 +18035,7 @@
       <c r="AE152" t="inlineStr"/>
       <c r="AF152" t="inlineStr">
         <is>
-          <t>2026-05-14T02:33:19+00:00</t>
+          <t>2026-05-14T02:59:23+00:00</t>
         </is>
       </c>
       <c r="AG152" t="inlineStr">
@@ -18135,7 +18135,7 @@
       </c>
       <c r="AB153" t="inlineStr">
         <is>
-          <t>batch_04ef5ec3e6b54457</t>
+          <t>batch_976be391c94a4aae</t>
         </is>
       </c>
       <c r="AC153" t="inlineStr">
@@ -18151,7 +18151,7 @@
       <c r="AE153" t="inlineStr"/>
       <c r="AF153" t="inlineStr">
         <is>
-          <t>2026-05-14T02:33:19+00:00</t>
+          <t>2026-05-14T02:59:23+00:00</t>
         </is>
       </c>
       <c r="AG153" t="inlineStr">
@@ -18251,7 +18251,7 @@
       </c>
       <c r="AB154" t="inlineStr">
         <is>
-          <t>batch_04ef5ec3e6b54457</t>
+          <t>batch_976be391c94a4aae</t>
         </is>
       </c>
       <c r="AC154" t="inlineStr">
@@ -18267,7 +18267,7 @@
       <c r="AE154" t="inlineStr"/>
       <c r="AF154" t="inlineStr">
         <is>
-          <t>2026-05-14T02:33:19+00:00</t>
+          <t>2026-05-14T02:59:23+00:00</t>
         </is>
       </c>
       <c r="AG154" t="inlineStr">
@@ -18367,7 +18367,7 @@
       </c>
       <c r="AB155" t="inlineStr">
         <is>
-          <t>batch_04ef5ec3e6b54457</t>
+          <t>batch_976be391c94a4aae</t>
         </is>
       </c>
       <c r="AC155" t="inlineStr">
@@ -18383,7 +18383,7 @@
       <c r="AE155" t="inlineStr"/>
       <c r="AF155" t="inlineStr">
         <is>
-          <t>2026-05-14T02:33:19+00:00</t>
+          <t>2026-05-14T02:59:23+00:00</t>
         </is>
       </c>
       <c r="AG155" t="inlineStr">
@@ -18483,7 +18483,7 @@
       </c>
       <c r="AB156" t="inlineStr">
         <is>
-          <t>batch_04ef5ec3e6b54457</t>
+          <t>batch_976be391c94a4aae</t>
         </is>
       </c>
       <c r="AC156" t="inlineStr">
@@ -18499,7 +18499,7 @@
       <c r="AE156" t="inlineStr"/>
       <c r="AF156" t="inlineStr">
         <is>
-          <t>2026-05-14T02:33:19+00:00</t>
+          <t>2026-05-14T02:59:23+00:00</t>
         </is>
       </c>
       <c r="AG156" t="inlineStr">
@@ -18599,7 +18599,7 @@
       </c>
       <c r="AB157" t="inlineStr">
         <is>
-          <t>batch_04ef5ec3e6b54457</t>
+          <t>batch_976be391c94a4aae</t>
         </is>
       </c>
       <c r="AC157" t="inlineStr">
@@ -18615,7 +18615,7 @@
       <c r="AE157" t="inlineStr"/>
       <c r="AF157" t="inlineStr">
         <is>
-          <t>2026-05-14T02:33:19+00:00</t>
+          <t>2026-05-14T02:59:23+00:00</t>
         </is>
       </c>
       <c r="AG157" t="inlineStr">
@@ -18715,7 +18715,7 @@
       </c>
       <c r="AB158" t="inlineStr">
         <is>
-          <t>batch_04ef5ec3e6b54457</t>
+          <t>batch_976be391c94a4aae</t>
         </is>
       </c>
       <c r="AC158" t="inlineStr">
@@ -18731,7 +18731,7 @@
       <c r="AE158" t="inlineStr"/>
       <c r="AF158" t="inlineStr">
         <is>
-          <t>2026-05-14T02:33:19+00:00</t>
+          <t>2026-05-14T02:59:23+00:00</t>
         </is>
       </c>
       <c r="AG158" t="inlineStr">
@@ -18831,7 +18831,7 @@
       </c>
       <c r="AB159" t="inlineStr">
         <is>
-          <t>batch_04ef5ec3e6b54457</t>
+          <t>batch_976be391c94a4aae</t>
         </is>
       </c>
       <c r="AC159" t="inlineStr">
@@ -18847,7 +18847,7 @@
       <c r="AE159" t="inlineStr"/>
       <c r="AF159" t="inlineStr">
         <is>
-          <t>2026-05-14T02:33:19+00:00</t>
+          <t>2026-05-14T02:59:23+00:00</t>
         </is>
       </c>
       <c r="AG159" t="inlineStr">
@@ -18947,7 +18947,7 @@
       </c>
       <c r="AB160" t="inlineStr">
         <is>
-          <t>batch_04ef5ec3e6b54457</t>
+          <t>batch_976be391c94a4aae</t>
         </is>
       </c>
       <c r="AC160" t="inlineStr">
@@ -18963,7 +18963,7 @@
       <c r="AE160" t="inlineStr"/>
       <c r="AF160" t="inlineStr">
         <is>
-          <t>2026-05-14T02:33:19+00:00</t>
+          <t>2026-05-14T02:59:23+00:00</t>
         </is>
       </c>
       <c r="AG160" t="inlineStr">
@@ -19063,7 +19063,7 @@
       </c>
       <c r="AB161" t="inlineStr">
         <is>
-          <t>batch_04ef5ec3e6b54457</t>
+          <t>batch_976be391c94a4aae</t>
         </is>
       </c>
       <c r="AC161" t="inlineStr">
@@ -19079,7 +19079,7 @@
       <c r="AE161" t="inlineStr"/>
       <c r="AF161" t="inlineStr">
         <is>
-          <t>2026-05-14T02:33:19+00:00</t>
+          <t>2026-05-14T02:59:23+00:00</t>
         </is>
       </c>
       <c r="AG161" t="inlineStr">
@@ -19179,7 +19179,7 @@
       </c>
       <c r="AB162" t="inlineStr">
         <is>
-          <t>batch_04ef5ec3e6b54457</t>
+          <t>batch_976be391c94a4aae</t>
         </is>
       </c>
       <c r="AC162" t="inlineStr">
@@ -19195,7 +19195,7 @@
       <c r="AE162" t="inlineStr"/>
       <c r="AF162" t="inlineStr">
         <is>
-          <t>2026-05-14T02:33:19+00:00</t>
+          <t>2026-05-14T02:59:23+00:00</t>
         </is>
       </c>
       <c r="AG162" t="inlineStr">
@@ -19295,7 +19295,7 @@
       </c>
       <c r="AB163" t="inlineStr">
         <is>
-          <t>batch_04ef5ec3e6b54457</t>
+          <t>batch_976be391c94a4aae</t>
         </is>
       </c>
       <c r="AC163" t="inlineStr">
@@ -19311,7 +19311,7 @@
       <c r="AE163" t="inlineStr"/>
       <c r="AF163" t="inlineStr">
         <is>
-          <t>2026-05-14T02:33:19+00:00</t>
+          <t>2026-05-14T02:59:23+00:00</t>
         </is>
       </c>
       <c r="AG163" t="inlineStr">
@@ -19411,7 +19411,7 @@
       </c>
       <c r="AB164" t="inlineStr">
         <is>
-          <t>batch_04ef5ec3e6b54457</t>
+          <t>batch_976be391c94a4aae</t>
         </is>
       </c>
       <c r="AC164" t="inlineStr">
@@ -19427,7 +19427,7 @@
       <c r="AE164" t="inlineStr"/>
       <c r="AF164" t="inlineStr">
         <is>
-          <t>2026-05-14T02:33:19+00:00</t>
+          <t>2026-05-14T02:59:23+00:00</t>
         </is>
       </c>
       <c r="AG164" t="inlineStr">
@@ -19527,7 +19527,7 @@
       </c>
       <c r="AB165" t="inlineStr">
         <is>
-          <t>batch_04ef5ec3e6b54457</t>
+          <t>batch_976be391c94a4aae</t>
         </is>
       </c>
       <c r="AC165" t="inlineStr">
@@ -19543,7 +19543,7 @@
       <c r="AE165" t="inlineStr"/>
       <c r="AF165" t="inlineStr">
         <is>
-          <t>2026-05-14T02:33:19+00:00</t>
+          <t>2026-05-14T02:59:23+00:00</t>
         </is>
       </c>
       <c r="AG165" t="inlineStr">
@@ -19643,7 +19643,7 @@
       </c>
       <c r="AB166" t="inlineStr">
         <is>
-          <t>batch_04ef5ec3e6b54457</t>
+          <t>batch_976be391c94a4aae</t>
         </is>
       </c>
       <c r="AC166" t="inlineStr">
@@ -19659,7 +19659,7 @@
       <c r="AE166" t="inlineStr"/>
       <c r="AF166" t="inlineStr">
         <is>
-          <t>2026-05-14T02:33:19+00:00</t>
+          <t>2026-05-14T02:59:23+00:00</t>
         </is>
       </c>
       <c r="AG166" t="inlineStr">
@@ -19759,7 +19759,7 @@
       </c>
       <c r="AB167" t="inlineStr">
         <is>
-          <t>batch_04ef5ec3e6b54457</t>
+          <t>batch_976be391c94a4aae</t>
         </is>
       </c>
       <c r="AC167" t="inlineStr">
@@ -19775,7 +19775,7 @@
       <c r="AE167" t="inlineStr"/>
       <c r="AF167" t="inlineStr">
         <is>
-          <t>2026-05-14T02:33:19+00:00</t>
+          <t>2026-05-14T02:59:23+00:00</t>
         </is>
       </c>
       <c r="AG167" t="inlineStr">
@@ -19875,7 +19875,7 @@
       </c>
       <c r="AB168" t="inlineStr">
         <is>
-          <t>batch_04ef5ec3e6b54457</t>
+          <t>batch_976be391c94a4aae</t>
         </is>
       </c>
       <c r="AC168" t="inlineStr">
@@ -19891,7 +19891,7 @@
       <c r="AE168" t="inlineStr"/>
       <c r="AF168" t="inlineStr">
         <is>
-          <t>2026-05-14T02:33:19+00:00</t>
+          <t>2026-05-14T02:59:23+00:00</t>
         </is>
       </c>
       <c r="AG168" t="inlineStr">
@@ -19991,7 +19991,7 @@
       </c>
       <c r="AB169" t="inlineStr">
         <is>
-          <t>batch_04ef5ec3e6b54457</t>
+          <t>batch_976be391c94a4aae</t>
         </is>
       </c>
       <c r="AC169" t="inlineStr">
@@ -20007,7 +20007,7 @@
       <c r="AE169" t="inlineStr"/>
       <c r="AF169" t="inlineStr">
         <is>
-          <t>2026-05-14T02:33:19+00:00</t>
+          <t>2026-05-14T02:59:23+00:00</t>
         </is>
       </c>
       <c r="AG169" t="inlineStr">
@@ -20107,7 +20107,7 @@
       </c>
       <c r="AB170" t="inlineStr">
         <is>
-          <t>batch_04ef5ec3e6b54457</t>
+          <t>batch_976be391c94a4aae</t>
         </is>
       </c>
       <c r="AC170" t="inlineStr">
@@ -20123,7 +20123,7 @@
       <c r="AE170" t="inlineStr"/>
       <c r="AF170" t="inlineStr">
         <is>
-          <t>2026-05-14T02:33:19+00:00</t>
+          <t>2026-05-14T02:59:23+00:00</t>
         </is>
       </c>
       <c r="AG170" t="inlineStr">
@@ -20223,7 +20223,7 @@
       </c>
       <c r="AB171" t="inlineStr">
         <is>
-          <t>batch_04ef5ec3e6b54457</t>
+          <t>batch_976be391c94a4aae</t>
         </is>
       </c>
       <c r="AC171" t="inlineStr">
@@ -20239,7 +20239,7 @@
       <c r="AE171" t="inlineStr"/>
       <c r="AF171" t="inlineStr">
         <is>
-          <t>2026-05-14T02:33:19+00:00</t>
+          <t>2026-05-14T02:59:23+00:00</t>
         </is>
       </c>
       <c r="AG171" t="inlineStr">
@@ -20339,7 +20339,7 @@
       </c>
       <c r="AB172" t="inlineStr">
         <is>
-          <t>batch_04ef5ec3e6b54457</t>
+          <t>batch_976be391c94a4aae</t>
         </is>
       </c>
       <c r="AC172" t="inlineStr">
@@ -20355,7 +20355,7 @@
       <c r="AE172" t="inlineStr"/>
       <c r="AF172" t="inlineStr">
         <is>
-          <t>2026-05-14T02:33:19+00:00</t>
+          <t>2026-05-14T02:59:23+00:00</t>
         </is>
       </c>
       <c r="AG172" t="inlineStr">
@@ -20455,7 +20455,7 @@
       </c>
       <c r="AB173" t="inlineStr">
         <is>
-          <t>batch_04ef5ec3e6b54457</t>
+          <t>batch_976be391c94a4aae</t>
         </is>
       </c>
       <c r="AC173" t="inlineStr">
@@ -20471,7 +20471,7 @@
       <c r="AE173" t="inlineStr"/>
       <c r="AF173" t="inlineStr">
         <is>
-          <t>2026-05-14T02:33:19+00:00</t>
+          <t>2026-05-14T02:59:23+00:00</t>
         </is>
       </c>
       <c r="AG173" t="inlineStr">
@@ -20571,7 +20571,7 @@
       </c>
       <c r="AB174" t="inlineStr">
         <is>
-          <t>batch_04ef5ec3e6b54457</t>
+          <t>batch_976be391c94a4aae</t>
         </is>
       </c>
       <c r="AC174" t="inlineStr">
@@ -20587,7 +20587,7 @@
       <c r="AE174" t="inlineStr"/>
       <c r="AF174" t="inlineStr">
         <is>
-          <t>2026-05-14T02:33:19+00:00</t>
+          <t>2026-05-14T02:59:23+00:00</t>
         </is>
       </c>
       <c r="AG174" t="inlineStr">
@@ -20687,7 +20687,7 @@
       </c>
       <c r="AB175" t="inlineStr">
         <is>
-          <t>batch_04ef5ec3e6b54457</t>
+          <t>batch_976be391c94a4aae</t>
         </is>
       </c>
       <c r="AC175" t="inlineStr">
@@ -20703,7 +20703,7 @@
       <c r="AE175" t="inlineStr"/>
       <c r="AF175" t="inlineStr">
         <is>
-          <t>2026-05-14T02:33:19+00:00</t>
+          <t>2026-05-14T02:59:23+00:00</t>
         </is>
       </c>
       <c r="AG175" t="inlineStr">
@@ -20803,7 +20803,7 @@
       </c>
       <c r="AB176" t="inlineStr">
         <is>
-          <t>batch_04ef5ec3e6b54457</t>
+          <t>batch_976be391c94a4aae</t>
         </is>
       </c>
       <c r="AC176" t="inlineStr">
@@ -20819,7 +20819,7 @@
       <c r="AE176" t="inlineStr"/>
       <c r="AF176" t="inlineStr">
         <is>
-          <t>2026-05-14T02:33:19+00:00</t>
+          <t>2026-05-14T02:59:23+00:00</t>
         </is>
       </c>
       <c r="AG176" t="inlineStr">
@@ -20919,7 +20919,7 @@
       </c>
       <c r="AB177" t="inlineStr">
         <is>
-          <t>batch_04ef5ec3e6b54457</t>
+          <t>batch_976be391c94a4aae</t>
         </is>
       </c>
       <c r="AC177" t="inlineStr">
@@ -20935,7 +20935,7 @@
       <c r="AE177" t="inlineStr"/>
       <c r="AF177" t="inlineStr">
         <is>
-          <t>2026-05-14T02:33:19+00:00</t>
+          <t>2026-05-14T02:59:23+00:00</t>
         </is>
       </c>
       <c r="AG177" t="inlineStr">
@@ -21035,7 +21035,7 @@
       </c>
       <c r="AB178" t="inlineStr">
         <is>
-          <t>batch_04ef5ec3e6b54457</t>
+          <t>batch_976be391c94a4aae</t>
         </is>
       </c>
       <c r="AC178" t="inlineStr">
@@ -21051,7 +21051,7 @@
       <c r="AE178" t="inlineStr"/>
       <c r="AF178" t="inlineStr">
         <is>
-          <t>2026-05-14T02:33:19+00:00</t>
+          <t>2026-05-14T02:59:23+00:00</t>
         </is>
       </c>
       <c r="AG178" t="inlineStr">
@@ -21151,7 +21151,7 @@
       </c>
       <c r="AB179" t="inlineStr">
         <is>
-          <t>batch_04ef5ec3e6b54457</t>
+          <t>batch_976be391c94a4aae</t>
         </is>
       </c>
       <c r="AC179" t="inlineStr">
@@ -21167,7 +21167,7 @@
       <c r="AE179" t="inlineStr"/>
       <c r="AF179" t="inlineStr">
         <is>
-          <t>2026-05-14T02:33:19+00:00</t>
+          <t>2026-05-14T02:59:23+00:00</t>
         </is>
       </c>
       <c r="AG179" t="inlineStr">
@@ -21267,7 +21267,7 @@
       </c>
       <c r="AB180" t="inlineStr">
         <is>
-          <t>batch_04ef5ec3e6b54457</t>
+          <t>batch_976be391c94a4aae</t>
         </is>
       </c>
       <c r="AC180" t="inlineStr">
@@ -21283,7 +21283,7 @@
       <c r="AE180" t="inlineStr"/>
       <c r="AF180" t="inlineStr">
         <is>
-          <t>2026-05-14T02:33:19+00:00</t>
+          <t>2026-05-14T02:59:23+00:00</t>
         </is>
       </c>
       <c r="AG180" t="inlineStr">
@@ -21383,7 +21383,7 @@
       </c>
       <c r="AB181" t="inlineStr">
         <is>
-          <t>batch_04ef5ec3e6b54457</t>
+          <t>batch_976be391c94a4aae</t>
         </is>
       </c>
       <c r="AC181" t="inlineStr">
@@ -21399,7 +21399,7 @@
       <c r="AE181" t="inlineStr"/>
       <c r="AF181" t="inlineStr">
         <is>
-          <t>2026-05-14T02:33:19+00:00</t>
+          <t>2026-05-14T02:59:23+00:00</t>
         </is>
       </c>
       <c r="AG181" t="inlineStr">
@@ -21499,7 +21499,7 @@
       </c>
       <c r="AB182" t="inlineStr">
         <is>
-          <t>batch_04ef5ec3e6b54457</t>
+          <t>batch_976be391c94a4aae</t>
         </is>
       </c>
       <c r="AC182" t="inlineStr">
@@ -21515,7 +21515,7 @@
       <c r="AE182" t="inlineStr"/>
       <c r="AF182" t="inlineStr">
         <is>
-          <t>2026-05-14T02:33:19+00:00</t>
+          <t>2026-05-14T02:59:23+00:00</t>
         </is>
       </c>
       <c r="AG182" t="inlineStr">
@@ -21615,7 +21615,7 @@
       </c>
       <c r="AB183" t="inlineStr">
         <is>
-          <t>batch_04ef5ec3e6b54457</t>
+          <t>batch_976be391c94a4aae</t>
         </is>
       </c>
       <c r="AC183" t="inlineStr">
@@ -21631,7 +21631,7 @@
       <c r="AE183" t="inlineStr"/>
       <c r="AF183" t="inlineStr">
         <is>
-          <t>2026-05-14T02:33:19+00:00</t>
+          <t>2026-05-14T02:59:23+00:00</t>
         </is>
       </c>
       <c r="AG183" t="inlineStr">
@@ -21731,7 +21731,7 @@
       </c>
       <c r="AB184" t="inlineStr">
         <is>
-          <t>batch_04ef5ec3e6b54457</t>
+          <t>batch_976be391c94a4aae</t>
         </is>
       </c>
       <c r="AC184" t="inlineStr">
@@ -21747,7 +21747,7 @@
       <c r="AE184" t="inlineStr"/>
       <c r="AF184" t="inlineStr">
         <is>
-          <t>2026-05-14T02:33:19+00:00</t>
+          <t>2026-05-14T02:59:23+00:00</t>
         </is>
       </c>
       <c r="AG184" t="inlineStr">
@@ -21847,7 +21847,7 @@
       </c>
       <c r="AB185" t="inlineStr">
         <is>
-          <t>batch_04ef5ec3e6b54457</t>
+          <t>batch_976be391c94a4aae</t>
         </is>
       </c>
       <c r="AC185" t="inlineStr">
@@ -21863,7 +21863,7 @@
       <c r="AE185" t="inlineStr"/>
       <c r="AF185" t="inlineStr">
         <is>
-          <t>2026-05-14T02:33:19+00:00</t>
+          <t>2026-05-14T02:59:23+00:00</t>
         </is>
       </c>
       <c r="AG185" t="inlineStr">
@@ -21963,7 +21963,7 @@
       </c>
       <c r="AB186" t="inlineStr">
         <is>
-          <t>batch_04ef5ec3e6b54457</t>
+          <t>batch_976be391c94a4aae</t>
         </is>
       </c>
       <c r="AC186" t="inlineStr">
@@ -21979,7 +21979,7 @@
       <c r="AE186" t="inlineStr"/>
       <c r="AF186" t="inlineStr">
         <is>
-          <t>2026-05-14T02:33:19+00:00</t>
+          <t>2026-05-14T02:59:23+00:00</t>
         </is>
       </c>
       <c r="AG186" t="inlineStr">
@@ -22079,7 +22079,7 @@
       </c>
       <c r="AB187" t="inlineStr">
         <is>
-          <t>batch_04ef5ec3e6b54457</t>
+          <t>batch_976be391c94a4aae</t>
         </is>
       </c>
       <c r="AC187" t="inlineStr">
@@ -22095,7 +22095,7 @@
       <c r="AE187" t="inlineStr"/>
       <c r="AF187" t="inlineStr">
         <is>
-          <t>2026-05-14T02:33:19+00:00</t>
+          <t>2026-05-14T02:59:23+00:00</t>
         </is>
       </c>
       <c r="AG187" t="inlineStr">
@@ -22195,7 +22195,7 @@
       </c>
       <c r="AB188" t="inlineStr">
         <is>
-          <t>batch_04ef5ec3e6b54457</t>
+          <t>batch_976be391c94a4aae</t>
         </is>
       </c>
       <c r="AC188" t="inlineStr">
@@ -22211,7 +22211,7 @@
       <c r="AE188" t="inlineStr"/>
       <c r="AF188" t="inlineStr">
         <is>
-          <t>2026-05-14T02:33:19+00:00</t>
+          <t>2026-05-14T02:59:23+00:00</t>
         </is>
       </c>
       <c r="AG188" t="inlineStr">
@@ -22311,7 +22311,7 @@
       </c>
       <c r="AB189" t="inlineStr">
         <is>
-          <t>batch_04ef5ec3e6b54457</t>
+          <t>batch_976be391c94a4aae</t>
         </is>
       </c>
       <c r="AC189" t="inlineStr">
@@ -22327,7 +22327,7 @@
       <c r="AE189" t="inlineStr"/>
       <c r="AF189" t="inlineStr">
         <is>
-          <t>2026-05-14T02:33:19+00:00</t>
+          <t>2026-05-14T02:59:23+00:00</t>
         </is>
       </c>
       <c r="AG189" t="inlineStr">
@@ -22427,7 +22427,7 @@
       </c>
       <c r="AB190" t="inlineStr">
         <is>
-          <t>batch_04ef5ec3e6b54457</t>
+          <t>batch_976be391c94a4aae</t>
         </is>
       </c>
       <c r="AC190" t="inlineStr">
@@ -22443,7 +22443,7 @@
       <c r="AE190" t="inlineStr"/>
       <c r="AF190" t="inlineStr">
         <is>
-          <t>2026-05-14T02:33:19+00:00</t>
+          <t>2026-05-14T02:59:23+00:00</t>
         </is>
       </c>
       <c r="AG190" t="inlineStr">
@@ -22543,7 +22543,7 @@
       </c>
       <c r="AB191" t="inlineStr">
         <is>
-          <t>batch_04ef5ec3e6b54457</t>
+          <t>batch_976be391c94a4aae</t>
         </is>
       </c>
       <c r="AC191" t="inlineStr">
@@ -22559,7 +22559,7 @@
       <c r="AE191" t="inlineStr"/>
       <c r="AF191" t="inlineStr">
         <is>
-          <t>2026-05-14T02:33:19+00:00</t>
+          <t>2026-05-14T02:59:23+00:00</t>
         </is>
       </c>
       <c r="AG191" t="inlineStr">
@@ -22659,7 +22659,7 @@
       </c>
       <c r="AB192" t="inlineStr">
         <is>
-          <t>batch_04ef5ec3e6b54457</t>
+          <t>batch_976be391c94a4aae</t>
         </is>
       </c>
       <c r="AC192" t="inlineStr">
@@ -22675,7 +22675,7 @@
       <c r="AE192" t="inlineStr"/>
       <c r="AF192" t="inlineStr">
         <is>
-          <t>2026-05-14T02:33:19+00:00</t>
+          <t>2026-05-14T02:59:23+00:00</t>
         </is>
       </c>
       <c r="AG192" t="inlineStr">
@@ -22775,7 +22775,7 @@
       </c>
       <c r="AB193" t="inlineStr">
         <is>
-          <t>batch_04ef5ec3e6b54457</t>
+          <t>batch_976be391c94a4aae</t>
         </is>
       </c>
       <c r="AC193" t="inlineStr">
@@ -22791,7 +22791,7 @@
       <c r="AE193" t="inlineStr"/>
       <c r="AF193" t="inlineStr">
         <is>
-          <t>2026-05-14T02:33:19+00:00</t>
+          <t>2026-05-14T02:59:23+00:00</t>
         </is>
       </c>
       <c r="AG193" t="inlineStr">
@@ -22891,7 +22891,7 @@
       </c>
       <c r="AB194" t="inlineStr">
         <is>
-          <t>batch_04ef5ec3e6b54457</t>
+          <t>batch_976be391c94a4aae</t>
         </is>
       </c>
       <c r="AC194" t="inlineStr">
@@ -22907,7 +22907,7 @@
       <c r="AE194" t="inlineStr"/>
       <c r="AF194" t="inlineStr">
         <is>
-          <t>2026-05-14T02:33:19+00:00</t>
+          <t>2026-05-14T02:59:23+00:00</t>
         </is>
       </c>
       <c r="AG194" t="inlineStr">
@@ -23007,7 +23007,7 @@
       </c>
       <c r="AB195" t="inlineStr">
         <is>
-          <t>batch_04ef5ec3e6b54457</t>
+          <t>batch_976be391c94a4aae</t>
         </is>
       </c>
       <c r="AC195" t="inlineStr">
@@ -23023,7 +23023,7 @@
       <c r="AE195" t="inlineStr"/>
       <c r="AF195" t="inlineStr">
         <is>
-          <t>2026-05-14T02:33:19+00:00</t>
+          <t>2026-05-14T02:59:23+00:00</t>
         </is>
       </c>
       <c r="AG195" t="inlineStr">
@@ -23123,7 +23123,7 @@
       </c>
       <c r="AB196" t="inlineStr">
         <is>
-          <t>batch_04ef5ec3e6b54457</t>
+          <t>batch_976be391c94a4aae</t>
         </is>
       </c>
       <c r="AC196" t="inlineStr">
@@ -23139,7 +23139,7 @@
       <c r="AE196" t="inlineStr"/>
       <c r="AF196" t="inlineStr">
         <is>
-          <t>2026-05-14T02:33:19+00:00</t>
+          <t>2026-05-14T02:59:23+00:00</t>
         </is>
       </c>
       <c r="AG196" t="inlineStr">
@@ -23239,7 +23239,7 @@
       </c>
       <c r="AB197" t="inlineStr">
         <is>
-          <t>batch_04ef5ec3e6b54457</t>
+          <t>batch_976be391c94a4aae</t>
         </is>
       </c>
       <c r="AC197" t="inlineStr">
@@ -23255,7 +23255,7 @@
       <c r="AE197" t="inlineStr"/>
       <c r="AF197" t="inlineStr">
         <is>
-          <t>2026-05-14T02:33:19+00:00</t>
+          <t>2026-05-14T02:59:23+00:00</t>
         </is>
       </c>
       <c r="AG197" t="inlineStr">
@@ -23355,7 +23355,7 @@
       </c>
       <c r="AB198" t="inlineStr">
         <is>
-          <t>batch_04ef5ec3e6b54457</t>
+          <t>batch_976be391c94a4aae</t>
         </is>
       </c>
       <c r="AC198" t="inlineStr">
@@ -23371,7 +23371,7 @@
       <c r="AE198" t="inlineStr"/>
       <c r="AF198" t="inlineStr">
         <is>
-          <t>2026-05-14T02:33:19+00:00</t>
+          <t>2026-05-14T02:59:23+00:00</t>
         </is>
       </c>
       <c r="AG198" t="inlineStr">
@@ -23471,7 +23471,7 @@
       </c>
       <c r="AB199" t="inlineStr">
         <is>
-          <t>batch_04ef5ec3e6b54457</t>
+          <t>batch_976be391c94a4aae</t>
         </is>
       </c>
       <c r="AC199" t="inlineStr">
@@ -23487,7 +23487,7 @@
       <c r="AE199" t="inlineStr"/>
       <c r="AF199" t="inlineStr">
         <is>
-          <t>2026-05-14T02:33:19+00:00</t>
+          <t>2026-05-14T02:59:23+00:00</t>
         </is>
       </c>
       <c r="AG199" t="inlineStr">
@@ -23587,7 +23587,7 @@
       </c>
       <c r="AB200" t="inlineStr">
         <is>
-          <t>batch_04ef5ec3e6b54457</t>
+          <t>batch_976be391c94a4aae</t>
         </is>
       </c>
       <c r="AC200" t="inlineStr">
@@ -23603,7 +23603,7 @@
       <c r="AE200" t="inlineStr"/>
       <c r="AF200" t="inlineStr">
         <is>
-          <t>2026-05-14T02:33:19+00:00</t>
+          <t>2026-05-14T02:59:23+00:00</t>
         </is>
       </c>
       <c r="AG200" t="inlineStr">
@@ -23706,7 +23706,7 @@
       </c>
       <c r="AB201" t="inlineStr">
         <is>
-          <t>batch_04ef5ec3e6b54457</t>
+          <t>batch_976be391c94a4aae</t>
         </is>
       </c>
       <c r="AC201" t="inlineStr">
@@ -23722,7 +23722,7 @@
       <c r="AE201" t="inlineStr"/>
       <c r="AF201" t="inlineStr">
         <is>
-          <t>2026-05-14T02:33:19+00:00</t>
+          <t>2026-05-14T02:59:23+00:00</t>
         </is>
       </c>
       <c r="AG201" t="inlineStr">
@@ -23825,7 +23825,7 @@
       </c>
       <c r="AB202" t="inlineStr">
         <is>
-          <t>batch_04ef5ec3e6b54457</t>
+          <t>batch_976be391c94a4aae</t>
         </is>
       </c>
       <c r="AC202" t="inlineStr">
@@ -23841,7 +23841,7 @@
       <c r="AE202" t="inlineStr"/>
       <c r="AF202" t="inlineStr">
         <is>
-          <t>2026-05-14T02:33:19+00:00</t>
+          <t>2026-05-14T02:59:23+00:00</t>
         </is>
       </c>
       <c r="AG202" t="inlineStr">
@@ -23941,7 +23941,7 @@
       </c>
       <c r="AB203" t="inlineStr">
         <is>
-          <t>batch_04ef5ec3e6b54457</t>
+          <t>batch_976be391c94a4aae</t>
         </is>
       </c>
       <c r="AC203" t="inlineStr">
@@ -23957,7 +23957,7 @@
       <c r="AE203" t="inlineStr"/>
       <c r="AF203" t="inlineStr">
         <is>
-          <t>2026-05-14T02:33:19+00:00</t>
+          <t>2026-05-14T02:59:23+00:00</t>
         </is>
       </c>
       <c r="AG203" t="inlineStr">
@@ -24057,7 +24057,7 @@
       </c>
       <c r="AB204" t="inlineStr">
         <is>
-          <t>batch_04ef5ec3e6b54457</t>
+          <t>batch_976be391c94a4aae</t>
         </is>
       </c>
       <c r="AC204" t="inlineStr">
@@ -24073,7 +24073,7 @@
       <c r="AE204" t="inlineStr"/>
       <c r="AF204" t="inlineStr">
         <is>
-          <t>2026-05-14T02:33:19+00:00</t>
+          <t>2026-05-14T02:59:23+00:00</t>
         </is>
       </c>
       <c r="AG204" t="inlineStr">
@@ -24173,7 +24173,7 @@
       </c>
       <c r="AB205" t="inlineStr">
         <is>
-          <t>batch_04ef5ec3e6b54457</t>
+          <t>batch_976be391c94a4aae</t>
         </is>
       </c>
       <c r="AC205" t="inlineStr">
@@ -24189,7 +24189,7 @@
       <c r="AE205" t="inlineStr"/>
       <c r="AF205" t="inlineStr">
         <is>
-          <t>2026-05-14T02:33:19+00:00</t>
+          <t>2026-05-14T02:59:23+00:00</t>
         </is>
       </c>
       <c r="AG205" t="inlineStr">
@@ -24289,7 +24289,7 @@
       </c>
       <c r="AB206" t="inlineStr">
         <is>
-          <t>batch_04ef5ec3e6b54457</t>
+          <t>batch_976be391c94a4aae</t>
         </is>
       </c>
       <c r="AC206" t="inlineStr">
@@ -24305,7 +24305,7 @@
       <c r="AE206" t="inlineStr"/>
       <c r="AF206" t="inlineStr">
         <is>
-          <t>2026-05-14T02:33:19+00:00</t>
+          <t>2026-05-14T02:59:23+00:00</t>
         </is>
       </c>
       <c r="AG206" t="inlineStr">
@@ -24405,7 +24405,7 @@
       </c>
       <c r="AB207" t="inlineStr">
         <is>
-          <t>batch_04ef5ec3e6b54457</t>
+          <t>batch_976be391c94a4aae</t>
         </is>
       </c>
       <c r="AC207" t="inlineStr">
@@ -24421,7 +24421,7 @@
       <c r="AE207" t="inlineStr"/>
       <c r="AF207" t="inlineStr">
         <is>
-          <t>2026-05-14T02:33:19+00:00</t>
+          <t>2026-05-14T02:59:23+00:00</t>
         </is>
       </c>
       <c r="AG207" t="inlineStr">
@@ -24521,7 +24521,7 @@
       </c>
       <c r="AB208" t="inlineStr">
         <is>
-          <t>batch_04ef5ec3e6b54457</t>
+          <t>batch_976be391c94a4aae</t>
         </is>
       </c>
       <c r="AC208" t="inlineStr">
@@ -24537,7 +24537,7 @@
       <c r="AE208" t="inlineStr"/>
       <c r="AF208" t="inlineStr">
         <is>
-          <t>2026-05-14T02:33:19+00:00</t>
+          <t>2026-05-14T02:59:23+00:00</t>
         </is>
       </c>
       <c r="AG208" t="inlineStr">
@@ -24637,7 +24637,7 @@
       </c>
       <c r="AB209" t="inlineStr">
         <is>
-          <t>batch_04ef5ec3e6b54457</t>
+          <t>batch_976be391c94a4aae</t>
         </is>
       </c>
       <c r="AC209" t="inlineStr">
@@ -24653,7 +24653,7 @@
       <c r="AE209" t="inlineStr"/>
       <c r="AF209" t="inlineStr">
         <is>
-          <t>2026-05-14T02:33:19+00:00</t>
+          <t>2026-05-14T02:59:23+00:00</t>
         </is>
       </c>
       <c r="AG209" t="inlineStr">
@@ -24753,7 +24753,7 @@
       </c>
       <c r="AB210" t="inlineStr">
         <is>
-          <t>batch_04ef5ec3e6b54457</t>
+          <t>batch_976be391c94a4aae</t>
         </is>
       </c>
       <c r="AC210" t="inlineStr">
@@ -24769,7 +24769,7 @@
       <c r="AE210" t="inlineStr"/>
       <c r="AF210" t="inlineStr">
         <is>
-          <t>2026-05-14T02:33:19+00:00</t>
+          <t>2026-05-14T02:59:23+00:00</t>
         </is>
       </c>
       <c r="AG210" t="inlineStr">
@@ -24869,7 +24869,7 @@
       </c>
       <c r="AB211" t="inlineStr">
         <is>
-          <t>batch_04ef5ec3e6b54457</t>
+          <t>batch_976be391c94a4aae</t>
         </is>
       </c>
       <c r="AC211" t="inlineStr">
@@ -24885,7 +24885,7 @@
       <c r="AE211" t="inlineStr"/>
       <c r="AF211" t="inlineStr">
         <is>
-          <t>2026-05-14T02:33:19+00:00</t>
+          <t>2026-05-14T02:59:23+00:00</t>
         </is>
       </c>
       <c r="AG211" t="inlineStr">
@@ -24985,7 +24985,7 @@
       </c>
       <c r="AB212" t="inlineStr">
         <is>
-          <t>batch_04ef5ec3e6b54457</t>
+          <t>batch_976be391c94a4aae</t>
         </is>
       </c>
       <c r="AC212" t="inlineStr">
@@ -25001,7 +25001,7 @@
       <c r="AE212" t="inlineStr"/>
       <c r="AF212" t="inlineStr">
         <is>
-          <t>2026-05-14T02:33:19+00:00</t>
+          <t>2026-05-14T02:59:23+00:00</t>
         </is>
       </c>
       <c r="AG212" t="inlineStr">
@@ -25101,7 +25101,7 @@
       </c>
       <c r="AB213" t="inlineStr">
         <is>
-          <t>batch_04ef5ec3e6b54457</t>
+          <t>batch_976be391c94a4aae</t>
         </is>
       </c>
       <c r="AC213" t="inlineStr">
@@ -25117,7 +25117,7 @@
       <c r="AE213" t="inlineStr"/>
       <c r="AF213" t="inlineStr">
         <is>
-          <t>2026-05-14T02:33:19+00:00</t>
+          <t>2026-05-14T02:59:23+00:00</t>
         </is>
       </c>
       <c r="AG213" t="inlineStr">
@@ -25217,7 +25217,7 @@
       </c>
       <c r="AB214" t="inlineStr">
         <is>
-          <t>batch_04ef5ec3e6b54457</t>
+          <t>batch_976be391c94a4aae</t>
         </is>
       </c>
       <c r="AC214" t="inlineStr">
@@ -25233,7 +25233,7 @@
       <c r="AE214" t="inlineStr"/>
       <c r="AF214" t="inlineStr">
         <is>
-          <t>2026-05-14T02:33:19+00:00</t>
+          <t>2026-05-14T02:59:23+00:00</t>
         </is>
       </c>
       <c r="AG214" t="inlineStr">
@@ -25333,7 +25333,7 @@
       </c>
       <c r="AB215" t="inlineStr">
         <is>
-          <t>batch_04ef5ec3e6b54457</t>
+          <t>batch_976be391c94a4aae</t>
         </is>
       </c>
       <c r="AC215" t="inlineStr">
@@ -25349,7 +25349,7 @@
       <c r="AE215" t="inlineStr"/>
       <c r="AF215" t="inlineStr">
         <is>
-          <t>2026-05-14T02:33:19+00:00</t>
+          <t>2026-05-14T02:59:23+00:00</t>
         </is>
       </c>
       <c r="AG215" t="inlineStr">
@@ -25449,7 +25449,7 @@
       </c>
       <c r="AB216" t="inlineStr">
         <is>
-          <t>batch_04ef5ec3e6b54457</t>
+          <t>batch_976be391c94a4aae</t>
         </is>
       </c>
       <c r="AC216" t="inlineStr">
@@ -25465,7 +25465,7 @@
       <c r="AE216" t="inlineStr"/>
       <c r="AF216" t="inlineStr">
         <is>
-          <t>2026-05-14T02:33:19+00:00</t>
+          <t>2026-05-14T02:59:23+00:00</t>
         </is>
       </c>
       <c r="AG216" t="inlineStr">
@@ -25565,7 +25565,7 @@
       </c>
       <c r="AB217" t="inlineStr">
         <is>
-          <t>batch_04ef5ec3e6b54457</t>
+          <t>batch_976be391c94a4aae</t>
         </is>
       </c>
       <c r="AC217" t="inlineStr">
@@ -25581,7 +25581,7 @@
       <c r="AE217" t="inlineStr"/>
       <c r="AF217" t="inlineStr">
         <is>
-          <t>2026-05-14T02:33:19+00:00</t>
+          <t>2026-05-14T02:59:23+00:00</t>
         </is>
       </c>
       <c r="AG217" t="inlineStr">
@@ -25681,7 +25681,7 @@
       </c>
       <c r="AB218" t="inlineStr">
         <is>
-          <t>batch_04ef5ec3e6b54457</t>
+          <t>batch_976be391c94a4aae</t>
         </is>
       </c>
       <c r="AC218" t="inlineStr">
@@ -25697,7 +25697,7 @@
       <c r="AE218" t="inlineStr"/>
       <c r="AF218" t="inlineStr">
         <is>
-          <t>2026-05-14T02:33:19+00:00</t>
+          <t>2026-05-14T02:59:23+00:00</t>
         </is>
       </c>
       <c r="AG218" t="inlineStr">
@@ -25797,7 +25797,7 @@
       </c>
       <c r="AB219" t="inlineStr">
         <is>
-          <t>batch_04ef5ec3e6b54457</t>
+          <t>batch_976be391c94a4aae</t>
         </is>
       </c>
       <c r="AC219" t="inlineStr">
@@ -25813,7 +25813,7 @@
       <c r="AE219" t="inlineStr"/>
       <c r="AF219" t="inlineStr">
         <is>
-          <t>2026-05-14T02:33:19+00:00</t>
+          <t>2026-05-14T02:59:23+00:00</t>
         </is>
       </c>
       <c r="AG219" t="inlineStr">
@@ -25913,7 +25913,7 @@
       </c>
       <c r="AB220" t="inlineStr">
         <is>
-          <t>batch_04ef5ec3e6b54457</t>
+          <t>batch_976be391c94a4aae</t>
         </is>
       </c>
       <c r="AC220" t="inlineStr">
@@ -25929,7 +25929,7 @@
       <c r="AE220" t="inlineStr"/>
       <c r="AF220" t="inlineStr">
         <is>
-          <t>2026-05-14T02:33:19+00:00</t>
+          <t>2026-05-14T02:59:23+00:00</t>
         </is>
       </c>
       <c r="AG220" t="inlineStr">
@@ -26029,7 +26029,7 @@
       </c>
       <c r="AB221" t="inlineStr">
         <is>
-          <t>batch_04ef5ec3e6b54457</t>
+          <t>batch_976be391c94a4aae</t>
         </is>
       </c>
       <c r="AC221" t="inlineStr">
@@ -26045,7 +26045,7 @@
       <c r="AE221" t="inlineStr"/>
       <c r="AF221" t="inlineStr">
         <is>
-          <t>2026-05-14T02:33:19+00:00</t>
+          <t>2026-05-14T02:59:23+00:00</t>
         </is>
       </c>
       <c r="AG221" t="inlineStr">
@@ -26145,7 +26145,7 @@
       </c>
       <c r="AB222" t="inlineStr">
         <is>
-          <t>batch_04ef5ec3e6b54457</t>
+          <t>batch_976be391c94a4aae</t>
         </is>
       </c>
       <c r="AC222" t="inlineStr">
@@ -26161,7 +26161,7 @@
       <c r="AE222" t="inlineStr"/>
       <c r="AF222" t="inlineStr">
         <is>
-          <t>2026-05-14T02:33:19+00:00</t>
+          <t>2026-05-14T02:59:23+00:00</t>
         </is>
       </c>
       <c r="AG222" t="inlineStr">
@@ -26261,7 +26261,7 @@
       </c>
       <c r="AB223" t="inlineStr">
         <is>
-          <t>batch_04ef5ec3e6b54457</t>
+          <t>batch_976be391c94a4aae</t>
         </is>
       </c>
       <c r="AC223" t="inlineStr">
@@ -26277,7 +26277,7 @@
       <c r="AE223" t="inlineStr"/>
       <c r="AF223" t="inlineStr">
         <is>
-          <t>2026-05-14T02:33:19+00:00</t>
+          <t>2026-05-14T02:59:23+00:00</t>
         </is>
       </c>
       <c r="AG223" t="inlineStr">
@@ -26377,7 +26377,7 @@
       </c>
       <c r="AB224" t="inlineStr">
         <is>
-          <t>batch_04ef5ec3e6b54457</t>
+          <t>batch_976be391c94a4aae</t>
         </is>
       </c>
       <c r="AC224" t="inlineStr">
@@ -26393,7 +26393,7 @@
       <c r="AE224" t="inlineStr"/>
       <c r="AF224" t="inlineStr">
         <is>
-          <t>2026-05-14T02:33:19+00:00</t>
+          <t>2026-05-14T02:59:23+00:00</t>
         </is>
       </c>
       <c r="AG224" t="inlineStr">
@@ -26493,7 +26493,7 @@
       </c>
       <c r="AB225" t="inlineStr">
         <is>
-          <t>batch_04ef5ec3e6b54457</t>
+          <t>batch_976be391c94a4aae</t>
         </is>
       </c>
       <c r="AC225" t="inlineStr">
@@ -26509,7 +26509,7 @@
       <c r="AE225" t="inlineStr"/>
       <c r="AF225" t="inlineStr">
         <is>
-          <t>2026-05-14T02:33:19+00:00</t>
+          <t>2026-05-14T02:59:23+00:00</t>
         </is>
       </c>
       <c r="AG225" t="inlineStr">
@@ -26609,7 +26609,7 @@
       </c>
       <c r="AB226" t="inlineStr">
         <is>
-          <t>batch_04ef5ec3e6b54457</t>
+          <t>batch_976be391c94a4aae</t>
         </is>
       </c>
       <c r="AC226" t="inlineStr">
@@ -26625,7 +26625,7 @@
       <c r="AE226" t="inlineStr"/>
       <c r="AF226" t="inlineStr">
         <is>
-          <t>2026-05-14T02:33:19+00:00</t>
+          <t>2026-05-14T02:59:23+00:00</t>
         </is>
       </c>
       <c r="AG226" t="inlineStr">
@@ -26725,7 +26725,7 @@
       </c>
       <c r="AB227" t="inlineStr">
         <is>
-          <t>batch_04ef5ec3e6b54457</t>
+          <t>batch_976be391c94a4aae</t>
         </is>
       </c>
       <c r="AC227" t="inlineStr">
@@ -26741,7 +26741,7 @@
       <c r="AE227" t="inlineStr"/>
       <c r="AF227" t="inlineStr">
         <is>
-          <t>2026-05-14T02:33:19+00:00</t>
+          <t>2026-05-14T02:59:23+00:00</t>
         </is>
       </c>
       <c r="AG227" t="inlineStr">
@@ -26841,7 +26841,7 @@
       </c>
       <c r="AB228" t="inlineStr">
         <is>
-          <t>batch_04ef5ec3e6b54457</t>
+          <t>batch_976be391c94a4aae</t>
         </is>
       </c>
       <c r="AC228" t="inlineStr">
@@ -26857,7 +26857,7 @@
       <c r="AE228" t="inlineStr"/>
       <c r="AF228" t="inlineStr">
         <is>
-          <t>2026-05-14T02:33:19+00:00</t>
+          <t>2026-05-14T02:59:23+00:00</t>
         </is>
       </c>
       <c r="AG228" t="inlineStr">
@@ -26957,7 +26957,7 @@
       </c>
       <c r="AB229" t="inlineStr">
         <is>
-          <t>batch_04ef5ec3e6b54457</t>
+          <t>batch_976be391c94a4aae</t>
         </is>
       </c>
       <c r="AC229" t="inlineStr">
@@ -26973,7 +26973,7 @@
       <c r="AE229" t="inlineStr"/>
       <c r="AF229" t="inlineStr">
         <is>
-          <t>2026-05-14T02:33:19+00:00</t>
+          <t>2026-05-14T02:59:23+00:00</t>
         </is>
       </c>
       <c r="AG229" t="inlineStr">
@@ -27073,7 +27073,7 @@
       </c>
       <c r="AB230" t="inlineStr">
         <is>
-          <t>batch_04ef5ec3e6b54457</t>
+          <t>batch_976be391c94a4aae</t>
         </is>
       </c>
       <c r="AC230" t="inlineStr">
@@ -27089,7 +27089,7 @@
       <c r="AE230" t="inlineStr"/>
       <c r="AF230" t="inlineStr">
         <is>
-          <t>2026-05-14T02:33:19+00:00</t>
+          <t>2026-05-14T02:59:23+00:00</t>
         </is>
       </c>
       <c r="AG230" t="inlineStr">
@@ -27189,7 +27189,7 @@
       </c>
       <c r="AB231" t="inlineStr">
         <is>
-          <t>batch_04ef5ec3e6b54457</t>
+          <t>batch_976be391c94a4aae</t>
         </is>
       </c>
       <c r="AC231" t="inlineStr">
@@ -27205,7 +27205,7 @@
       <c r="AE231" t="inlineStr"/>
       <c r="AF231" t="inlineStr">
         <is>
-          <t>2026-05-14T02:33:19+00:00</t>
+          <t>2026-05-14T02:59:23+00:00</t>
         </is>
       </c>
       <c r="AG231" t="inlineStr">
@@ -27305,7 +27305,7 @@
       </c>
       <c r="AB232" t="inlineStr">
         <is>
-          <t>batch_04ef5ec3e6b54457</t>
+          <t>batch_976be391c94a4aae</t>
         </is>
       </c>
       <c r="AC232" t="inlineStr">
@@ -27321,7 +27321,7 @@
       <c r="AE232" t="inlineStr"/>
       <c r="AF232" t="inlineStr">
         <is>
-          <t>2026-05-14T02:33:19+00:00</t>
+          <t>2026-05-14T02:59:23+00:00</t>
         </is>
       </c>
       <c r="AG232" t="inlineStr">
@@ -27421,7 +27421,7 @@
       </c>
       <c r="AB233" t="inlineStr">
         <is>
-          <t>batch_04ef5ec3e6b54457</t>
+          <t>batch_976be391c94a4aae</t>
         </is>
       </c>
       <c r="AC233" t="inlineStr">
@@ -27437,7 +27437,7 @@
       <c r="AE233" t="inlineStr"/>
       <c r="AF233" t="inlineStr">
         <is>
-          <t>2026-05-14T02:33:19+00:00</t>
+          <t>2026-05-14T02:59:23+00:00</t>
         </is>
       </c>
       <c r="AG233" t="inlineStr">
@@ -27537,7 +27537,7 @@
       </c>
       <c r="AB234" t="inlineStr">
         <is>
-          <t>batch_04ef5ec3e6b54457</t>
+          <t>batch_976be391c94a4aae</t>
         </is>
       </c>
       <c r="AC234" t="inlineStr">
@@ -27553,7 +27553,7 @@
       <c r="AE234" t="inlineStr"/>
       <c r="AF234" t="inlineStr">
         <is>
-          <t>2026-05-14T02:33:19+00:00</t>
+          <t>2026-05-14T02:59:23+00:00</t>
         </is>
       </c>
       <c r="AG234" t="inlineStr">
@@ -27653,7 +27653,7 @@
       </c>
       <c r="AB235" t="inlineStr">
         <is>
-          <t>batch_04ef5ec3e6b54457</t>
+          <t>batch_976be391c94a4aae</t>
         </is>
       </c>
       <c r="AC235" t="inlineStr">
@@ -27669,7 +27669,7 @@
       <c r="AE235" t="inlineStr"/>
       <c r="AF235" t="inlineStr">
         <is>
-          <t>2026-05-14T02:33:19+00:00</t>
+          <t>2026-05-14T02:59:23+00:00</t>
         </is>
       </c>
       <c r="AG235" t="inlineStr">
@@ -27769,7 +27769,7 @@
       </c>
       <c r="AB236" t="inlineStr">
         <is>
-          <t>batch_04ef5ec3e6b54457</t>
+          <t>batch_976be391c94a4aae</t>
         </is>
       </c>
       <c r="AC236" t="inlineStr">
@@ -27785,7 +27785,7 @@
       <c r="AE236" t="inlineStr"/>
       <c r="AF236" t="inlineStr">
         <is>
-          <t>2026-05-14T02:33:19+00:00</t>
+          <t>2026-05-14T02:59:23+00:00</t>
         </is>
       </c>
       <c r="AG236" t="inlineStr">
@@ -27885,7 +27885,7 @@
       </c>
       <c r="AB237" t="inlineStr">
         <is>
-          <t>batch_04ef5ec3e6b54457</t>
+          <t>batch_976be391c94a4aae</t>
         </is>
       </c>
       <c r="AC237" t="inlineStr">
@@ -27901,7 +27901,7 @@
       <c r="AE237" t="inlineStr"/>
       <c r="AF237" t="inlineStr">
         <is>
-          <t>2026-05-14T02:33:19+00:00</t>
+          <t>2026-05-14T02:59:23+00:00</t>
         </is>
       </c>
       <c r="AG237" t="inlineStr">
@@ -28001,7 +28001,7 @@
       </c>
       <c r="AB238" t="inlineStr">
         <is>
-          <t>batch_04ef5ec3e6b54457</t>
+          <t>batch_976be391c94a4aae</t>
         </is>
       </c>
       <c r="AC238" t="inlineStr">
@@ -28017,7 +28017,7 @@
       <c r="AE238" t="inlineStr"/>
       <c r="AF238" t="inlineStr">
         <is>
-          <t>2026-05-14T02:33:19+00:00</t>
+          <t>2026-05-14T02:59:23+00:00</t>
         </is>
       </c>
       <c r="AG238" t="inlineStr">
@@ -28117,7 +28117,7 @@
       </c>
       <c r="AB239" t="inlineStr">
         <is>
-          <t>batch_04ef5ec3e6b54457</t>
+          <t>batch_976be391c94a4aae</t>
         </is>
       </c>
       <c r="AC239" t="inlineStr">
@@ -28133,7 +28133,7 @@
       <c r="AE239" t="inlineStr"/>
       <c r="AF239" t="inlineStr">
         <is>
-          <t>2026-05-14T02:33:19+00:00</t>
+          <t>2026-05-14T02:59:23+00:00</t>
         </is>
       </c>
       <c r="AG239" t="inlineStr">
@@ -28233,7 +28233,7 @@
       </c>
       <c r="AB240" t="inlineStr">
         <is>
-          <t>batch_04ef5ec3e6b54457</t>
+          <t>batch_976be391c94a4aae</t>
         </is>
       </c>
       <c r="AC240" t="inlineStr">
@@ -28249,7 +28249,7 @@
       <c r="AE240" t="inlineStr"/>
       <c r="AF240" t="inlineStr">
         <is>
-          <t>2026-05-14T02:33:19+00:00</t>
+          <t>2026-05-14T02:59:23+00:00</t>
         </is>
       </c>
       <c r="AG240" t="inlineStr">
@@ -28349,7 +28349,7 @@
       </c>
       <c r="AB241" t="inlineStr">
         <is>
-          <t>batch_04ef5ec3e6b54457</t>
+          <t>batch_976be391c94a4aae</t>
         </is>
       </c>
       <c r="AC241" t="inlineStr">
@@ -28365,7 +28365,7 @@
       <c r="AE241" t="inlineStr"/>
       <c r="AF241" t="inlineStr">
         <is>
-          <t>2026-05-14T02:33:19+00:00</t>
+          <t>2026-05-14T02:59:23+00:00</t>
         </is>
       </c>
       <c r="AG241" t="inlineStr">
@@ -28465,7 +28465,7 @@
       </c>
       <c r="AB242" t="inlineStr">
         <is>
-          <t>batch_04ef5ec3e6b54457</t>
+          <t>batch_976be391c94a4aae</t>
         </is>
       </c>
       <c r="AC242" t="inlineStr">
@@ -28481,7 +28481,7 @@
       <c r="AE242" t="inlineStr"/>
       <c r="AF242" t="inlineStr">
         <is>
-          <t>2026-05-14T02:33:19+00:00</t>
+          <t>2026-05-14T02:59:23+00:00</t>
         </is>
       </c>
       <c r="AG242" t="inlineStr">
@@ -28581,7 +28581,7 @@
       </c>
       <c r="AB243" t="inlineStr">
         <is>
-          <t>batch_04ef5ec3e6b54457</t>
+          <t>batch_976be391c94a4aae</t>
         </is>
       </c>
       <c r="AC243" t="inlineStr">
@@ -28597,7 +28597,7 @@
       <c r="AE243" t="inlineStr"/>
       <c r="AF243" t="inlineStr">
         <is>
-          <t>2026-05-14T02:33:19+00:00</t>
+          <t>2026-05-14T02:59:23+00:00</t>
         </is>
       </c>
       <c r="AG243" t="inlineStr">
@@ -28697,7 +28697,7 @@
       </c>
       <c r="AB244" t="inlineStr">
         <is>
-          <t>batch_04ef5ec3e6b54457</t>
+          <t>batch_976be391c94a4aae</t>
         </is>
       </c>
       <c r="AC244" t="inlineStr">
@@ -28713,7 +28713,7 @@
       <c r="AE244" t="inlineStr"/>
       <c r="AF244" t="inlineStr">
         <is>
-          <t>2026-05-14T02:33:19+00:00</t>
+          <t>2026-05-14T02:59:23+00:00</t>
         </is>
       </c>
       <c r="AG244" t="inlineStr">
@@ -28813,7 +28813,7 @@
       </c>
       <c r="AB245" t="inlineStr">
         <is>
-          <t>batch_04ef5ec3e6b54457</t>
+          <t>batch_976be391c94a4aae</t>
         </is>
       </c>
       <c r="AC245" t="inlineStr">
@@ -28829,7 +28829,7 @@
       <c r="AE245" t="inlineStr"/>
       <c r="AF245" t="inlineStr">
         <is>
-          <t>2026-05-14T02:33:19+00:00</t>
+          <t>2026-05-14T02:59:23+00:00</t>
         </is>
       </c>
       <c r="AG245" t="inlineStr">
@@ -28929,7 +28929,7 @@
       </c>
       <c r="AB246" t="inlineStr">
         <is>
-          <t>batch_04ef5ec3e6b54457</t>
+          <t>batch_976be391c94a4aae</t>
         </is>
       </c>
       <c r="AC246" t="inlineStr">
@@ -28945,7 +28945,7 @@
       <c r="AE246" t="inlineStr"/>
       <c r="AF246" t="inlineStr">
         <is>
-          <t>2026-05-14T02:33:19+00:00</t>
+          <t>2026-05-14T02:59:23+00:00</t>
         </is>
       </c>
       <c r="AG246" t="inlineStr">
@@ -29045,7 +29045,7 @@
       </c>
       <c r="AB247" t="inlineStr">
         <is>
-          <t>batch_04ef5ec3e6b54457</t>
+          <t>batch_976be391c94a4aae</t>
         </is>
       </c>
       <c r="AC247" t="inlineStr">
@@ -29061,7 +29061,7 @@
       <c r="AE247" t="inlineStr"/>
       <c r="AF247" t="inlineStr">
         <is>
-          <t>2026-05-14T02:33:19+00:00</t>
+          <t>2026-05-14T02:59:23+00:00</t>
         </is>
       </c>
       <c r="AG247" t="inlineStr">
@@ -29161,7 +29161,7 @@
       </c>
       <c r="AB248" t="inlineStr">
         <is>
-          <t>batch_04ef5ec3e6b54457</t>
+          <t>batch_976be391c94a4aae</t>
         </is>
       </c>
       <c r="AC248" t="inlineStr">
@@ -29177,7 +29177,7 @@
       <c r="AE248" t="inlineStr"/>
       <c r="AF248" t="inlineStr">
         <is>
-          <t>2026-05-14T02:33:19+00:00</t>
+          <t>2026-05-14T02:59:23+00:00</t>
         </is>
       </c>
       <c r="AG248" t="inlineStr">
@@ -29277,7 +29277,7 @@
       </c>
       <c r="AB249" t="inlineStr">
         <is>
-          <t>batch_04ef5ec3e6b54457</t>
+          <t>batch_976be391c94a4aae</t>
         </is>
       </c>
       <c r="AC249" t="inlineStr">
@@ -29293,7 +29293,7 @@
       <c r="AE249" t="inlineStr"/>
       <c r="AF249" t="inlineStr">
         <is>
-          <t>2026-05-14T02:33:19+00:00</t>
+          <t>2026-05-14T02:59:23+00:00</t>
         </is>
       </c>
       <c r="AG249" t="inlineStr">
@@ -29393,7 +29393,7 @@
       </c>
       <c r="AB250" t="inlineStr">
         <is>
-          <t>batch_04ef5ec3e6b54457</t>
+          <t>batch_976be391c94a4aae</t>
         </is>
       </c>
       <c r="AC250" t="inlineStr">
@@ -29409,7 +29409,7 @@
       <c r="AE250" t="inlineStr"/>
       <c r="AF250" t="inlineStr">
         <is>
-          <t>2026-05-14T02:33:19+00:00</t>
+          <t>2026-05-14T02:59:23+00:00</t>
         </is>
       </c>
       <c r="AG250" t="inlineStr">
@@ -29509,7 +29509,7 @@
       </c>
       <c r="AB251" t="inlineStr">
         <is>
-          <t>batch_04ef5ec3e6b54457</t>
+          <t>batch_976be391c94a4aae</t>
         </is>
       </c>
       <c r="AC251" t="inlineStr">
@@ -29525,7 +29525,7 @@
       <c r="AE251" t="inlineStr"/>
       <c r="AF251" t="inlineStr">
         <is>
-          <t>2026-05-14T02:33:19+00:00</t>
+          <t>2026-05-14T02:59:23+00:00</t>
         </is>
       </c>
       <c r="AG251" t="inlineStr">
@@ -29625,7 +29625,7 @@
       </c>
       <c r="AB252" t="inlineStr">
         <is>
-          <t>batch_04ef5ec3e6b54457</t>
+          <t>batch_976be391c94a4aae</t>
         </is>
       </c>
       <c r="AC252" t="inlineStr">
@@ -29641,7 +29641,7 @@
       <c r="AE252" t="inlineStr"/>
       <c r="AF252" t="inlineStr">
         <is>
-          <t>2026-05-14T02:33:19+00:00</t>
+          <t>2026-05-14T02:59:23+00:00</t>
         </is>
       </c>
       <c r="AG252" t="inlineStr">
@@ -29741,7 +29741,7 @@
       </c>
       <c r="AB253" t="inlineStr">
         <is>
-          <t>batch_04ef5ec3e6b54457</t>
+          <t>batch_976be391c94a4aae</t>
         </is>
       </c>
       <c r="AC253" t="inlineStr">
@@ -29757,7 +29757,7 @@
       <c r="AE253" t="inlineStr"/>
       <c r="AF253" t="inlineStr">
         <is>
-          <t>2026-05-14T02:33:19+00:00</t>
+          <t>2026-05-14T02:59:23+00:00</t>
         </is>
       </c>
       <c r="AG253" t="inlineStr">
@@ -29857,7 +29857,7 @@
       </c>
       <c r="AB254" t="inlineStr">
         <is>
-          <t>batch_04ef5ec3e6b54457</t>
+          <t>batch_976be391c94a4aae</t>
         </is>
       </c>
       <c r="AC254" t="inlineStr">
@@ -29873,7 +29873,7 @@
       <c r="AE254" t="inlineStr"/>
       <c r="AF254" t="inlineStr">
         <is>
-          <t>2026-05-14T02:33:19+00:00</t>
+          <t>2026-05-14T02:59:23+00:00</t>
         </is>
       </c>
       <c r="AG254" t="inlineStr">
@@ -29973,7 +29973,7 @@
       </c>
       <c r="AB255" t="inlineStr">
         <is>
-          <t>batch_04ef5ec3e6b54457</t>
+          <t>batch_976be391c94a4aae</t>
         </is>
       </c>
       <c r="AC255" t="inlineStr">
@@ -29989,7 +29989,7 @@
       <c r="AE255" t="inlineStr"/>
       <c r="AF255" t="inlineStr">
         <is>
-          <t>2026-05-14T02:33:19+00:00</t>
+          <t>2026-05-14T02:59:23+00:00</t>
         </is>
       </c>
       <c r="AG255" t="inlineStr">
@@ -30089,7 +30089,7 @@
       </c>
       <c r="AB256" t="inlineStr">
         <is>
-          <t>batch_04ef5ec3e6b54457</t>
+          <t>batch_976be391c94a4aae</t>
         </is>
       </c>
       <c r="AC256" t="inlineStr">
@@ -30105,7 +30105,7 @@
       <c r="AE256" t="inlineStr"/>
       <c r="AF256" t="inlineStr">
         <is>
-          <t>2026-05-14T02:33:19+00:00</t>
+          <t>2026-05-14T02:59:23+00:00</t>
         </is>
       </c>
       <c r="AG256" t="inlineStr">
@@ -30205,7 +30205,7 @@
       </c>
       <c r="AB257" t="inlineStr">
         <is>
-          <t>batch_04ef5ec3e6b54457</t>
+          <t>batch_976be391c94a4aae</t>
         </is>
       </c>
       <c r="AC257" t="inlineStr">
@@ -30221,7 +30221,7 @@
       <c r="AE257" t="inlineStr"/>
       <c r="AF257" t="inlineStr">
         <is>
-          <t>2026-05-14T02:33:19+00:00</t>
+          <t>2026-05-14T02:59:23+00:00</t>
         </is>
       </c>
       <c r="AG257" t="inlineStr">
@@ -30321,7 +30321,7 @@
       </c>
       <c r="AB258" t="inlineStr">
         <is>
-          <t>batch_04ef5ec3e6b54457</t>
+          <t>batch_976be391c94a4aae</t>
         </is>
       </c>
       <c r="AC258" t="inlineStr">
@@ -30337,7 +30337,7 @@
       <c r="AE258" t="inlineStr"/>
       <c r="AF258" t="inlineStr">
         <is>
-          <t>2026-05-14T02:33:19+00:00</t>
+          <t>2026-05-14T02:59:23+00:00</t>
         </is>
       </c>
       <c r="AG258" t="inlineStr">
@@ -30437,7 +30437,7 @@
       </c>
       <c r="AB259" t="inlineStr">
         <is>
-          <t>batch_04ef5ec3e6b54457</t>
+          <t>batch_976be391c94a4aae</t>
         </is>
       </c>
       <c r="AC259" t="inlineStr">
@@ -30453,7 +30453,7 @@
       <c r="AE259" t="inlineStr"/>
       <c r="AF259" t="inlineStr">
         <is>
-          <t>2026-05-14T02:33:19+00:00</t>
+          <t>2026-05-14T02:59:23+00:00</t>
         </is>
       </c>
       <c r="AG259" t="inlineStr">
@@ -30553,7 +30553,7 @@
       </c>
       <c r="AB260" t="inlineStr">
         <is>
-          <t>batch_04ef5ec3e6b54457</t>
+          <t>batch_976be391c94a4aae</t>
         </is>
       </c>
       <c r="AC260" t="inlineStr">
@@ -30569,7 +30569,7 @@
       <c r="AE260" t="inlineStr"/>
       <c r="AF260" t="inlineStr">
         <is>
-          <t>2026-05-14T02:33:19+00:00</t>
+          <t>2026-05-14T02:59:23+00:00</t>
         </is>
       </c>
       <c r="AG260" t="inlineStr">
@@ -30669,7 +30669,7 @@
       </c>
       <c r="AB261" t="inlineStr">
         <is>
-          <t>batch_04ef5ec3e6b54457</t>
+          <t>batch_976be391c94a4aae</t>
         </is>
       </c>
       <c r="AC261" t="inlineStr">
@@ -30685,7 +30685,7 @@
       <c r="AE261" t="inlineStr"/>
       <c r="AF261" t="inlineStr">
         <is>
-          <t>2026-05-14T02:33:19+00:00</t>
+          <t>2026-05-14T02:59:23+00:00</t>
         </is>
       </c>
       <c r="AG261" t="inlineStr">
@@ -30785,7 +30785,7 @@
       </c>
       <c r="AB262" t="inlineStr">
         <is>
-          <t>batch_04ef5ec3e6b54457</t>
+          <t>batch_976be391c94a4aae</t>
         </is>
       </c>
       <c r="AC262" t="inlineStr">
@@ -30801,7 +30801,7 @@
       <c r="AE262" t="inlineStr"/>
       <c r="AF262" t="inlineStr">
         <is>
-          <t>2026-05-14T02:33:19+00:00</t>
+          <t>2026-05-14T02:59:23+00:00</t>
         </is>
       </c>
       <c r="AG262" t="inlineStr">
@@ -30901,7 +30901,7 @@
       </c>
       <c r="AB263" t="inlineStr">
         <is>
-          <t>batch_04ef5ec3e6b54457</t>
+          <t>batch_976be391c94a4aae</t>
         </is>
       </c>
       <c r="AC263" t="inlineStr">
@@ -30917,7 +30917,7 @@
       <c r="AE263" t="inlineStr"/>
       <c r="AF263" t="inlineStr">
         <is>
-          <t>2026-05-14T02:33:19+00:00</t>
+          <t>2026-05-14T02:59:23+00:00</t>
         </is>
       </c>
       <c r="AG263" t="inlineStr">
@@ -31017,7 +31017,7 @@
       </c>
       <c r="AB264" t="inlineStr">
         <is>
-          <t>batch_04ef5ec3e6b54457</t>
+          <t>batch_976be391c94a4aae</t>
         </is>
       </c>
       <c r="AC264" t="inlineStr">
@@ -31033,7 +31033,7 @@
       <c r="AE264" t="inlineStr"/>
       <c r="AF264" t="inlineStr">
         <is>
-          <t>2026-05-14T02:33:19+00:00</t>
+          <t>2026-05-14T02:59:23+00:00</t>
         </is>
       </c>
       <c r="AG264" t="inlineStr">
@@ -31133,7 +31133,7 @@
       </c>
       <c r="AB265" t="inlineStr">
         <is>
-          <t>batch_04ef5ec3e6b54457</t>
+          <t>batch_976be391c94a4aae</t>
         </is>
       </c>
       <c r="AC265" t="inlineStr">
@@ -31149,7 +31149,7 @@
       <c r="AE265" t="inlineStr"/>
       <c r="AF265" t="inlineStr">
         <is>
-          <t>2026-05-14T02:33:19+00:00</t>
+          <t>2026-05-14T02:59:23+00:00</t>
         </is>
       </c>
       <c r="AG265" t="inlineStr">
@@ -31249,7 +31249,7 @@
       </c>
       <c r="AB266" t="inlineStr">
         <is>
-          <t>batch_04ef5ec3e6b54457</t>
+          <t>batch_976be391c94a4aae</t>
         </is>
       </c>
       <c r="AC266" t="inlineStr">
@@ -31265,7 +31265,7 @@
       <c r="AE266" t="inlineStr"/>
       <c r="AF266" t="inlineStr">
         <is>
-          <t>2026-05-14T02:33:19+00:00</t>
+          <t>2026-05-14T02:59:23+00:00</t>
         </is>
       </c>
       <c r="AG266" t="inlineStr">
@@ -31365,7 +31365,7 @@
       </c>
       <c r="AB267" t="inlineStr">
         <is>
-          <t>batch_04ef5ec3e6b54457</t>
+          <t>batch_976be391c94a4aae</t>
         </is>
       </c>
       <c r="AC267" t="inlineStr">
@@ -31381,7 +31381,7 @@
       <c r="AE267" t="inlineStr"/>
       <c r="AF267" t="inlineStr">
         <is>
-          <t>2026-05-14T02:33:19+00:00</t>
+          <t>2026-05-14T02:59:23+00:00</t>
         </is>
       </c>
       <c r="AG267" t="inlineStr">
@@ -31481,7 +31481,7 @@
       </c>
       <c r="AB268" t="inlineStr">
         <is>
-          <t>batch_04ef5ec3e6b54457</t>
+          <t>batch_976be391c94a4aae</t>
         </is>
       </c>
       <c r="AC268" t="inlineStr">
@@ -31497,7 +31497,7 @@
       <c r="AE268" t="inlineStr"/>
       <c r="AF268" t="inlineStr">
         <is>
-          <t>2026-05-14T02:33:19+00:00</t>
+          <t>2026-05-14T02:59:23+00:00</t>
         </is>
       </c>
       <c r="AG268" t="inlineStr">
@@ -31597,7 +31597,7 @@
       </c>
       <c r="AB269" t="inlineStr">
         <is>
-          <t>batch_04ef5ec3e6b54457</t>
+          <t>batch_976be391c94a4aae</t>
         </is>
       </c>
       <c r="AC269" t="inlineStr">
@@ -31613,7 +31613,7 @@
       <c r="AE269" t="inlineStr"/>
       <c r="AF269" t="inlineStr">
         <is>
-          <t>2026-05-14T02:33:19+00:00</t>
+          <t>2026-05-14T02:59:23+00:00</t>
         </is>
       </c>
       <c r="AG269" t="inlineStr">
@@ -31713,7 +31713,7 @@
       </c>
       <c r="AB270" t="inlineStr">
         <is>
-          <t>batch_04ef5ec3e6b54457</t>
+          <t>batch_976be391c94a4aae</t>
         </is>
       </c>
       <c r="AC270" t="inlineStr">
@@ -31729,7 +31729,7 @@
       <c r="AE270" t="inlineStr"/>
       <c r="AF270" t="inlineStr">
         <is>
-          <t>2026-05-14T02:33:19+00:00</t>
+          <t>2026-05-14T02:59:23+00:00</t>
         </is>
       </c>
       <c r="AG270" t="inlineStr">
@@ -31829,7 +31829,7 @@
       </c>
       <c r="AB271" t="inlineStr">
         <is>
-          <t>batch_04ef5ec3e6b54457</t>
+          <t>batch_976be391c94a4aae</t>
         </is>
       </c>
       <c r="AC271" t="inlineStr">
@@ -31845,7 +31845,7 @@
       <c r="AE271" t="inlineStr"/>
       <c r="AF271" t="inlineStr">
         <is>
-          <t>2026-05-14T02:33:19+00:00</t>
+          <t>2026-05-14T02:59:23+00:00</t>
         </is>
       </c>
       <c r="AG271" t="inlineStr">
@@ -31945,7 +31945,7 @@
       </c>
       <c r="AB272" t="inlineStr">
         <is>
-          <t>batch_04ef5ec3e6b54457</t>
+          <t>batch_976be391c94a4aae</t>
         </is>
       </c>
       <c r="AC272" t="inlineStr">
@@ -31961,7 +31961,7 @@
       <c r="AE272" t="inlineStr"/>
       <c r="AF272" t="inlineStr">
         <is>
-          <t>2026-05-14T02:33:19+00:00</t>
+          <t>2026-05-14T02:59:23+00:00</t>
         </is>
       </c>
       <c r="AG272" t="inlineStr">
@@ -32061,7 +32061,7 @@
       </c>
       <c r="AB273" t="inlineStr">
         <is>
-          <t>batch_04ef5ec3e6b54457</t>
+          <t>batch_976be391c94a4aae</t>
         </is>
       </c>
       <c r="AC273" t="inlineStr">
@@ -32077,7 +32077,7 @@
       <c r="AE273" t="inlineStr"/>
       <c r="AF273" t="inlineStr">
         <is>
-          <t>2026-05-14T02:33:19+00:00</t>
+          <t>2026-05-14T02:59:23+00:00</t>
         </is>
       </c>
       <c r="AG273" t="inlineStr">
@@ -32177,7 +32177,7 @@
       </c>
       <c r="AB274" t="inlineStr">
         <is>
-          <t>batch_04ef5ec3e6b54457</t>
+          <t>batch_976be391c94a4aae</t>
         </is>
       </c>
       <c r="AC274" t="inlineStr">
@@ -32193,7 +32193,7 @@
       <c r="AE274" t="inlineStr"/>
       <c r="AF274" t="inlineStr">
         <is>
-          <t>2026-05-14T02:33:19+00:00</t>
+          <t>2026-05-14T02:59:23+00:00</t>
         </is>
       </c>
       <c r="AG274" t="inlineStr">
@@ -32293,7 +32293,7 @@
       </c>
       <c r="AB275" t="inlineStr">
         <is>
-          <t>batch_04ef5ec3e6b54457</t>
+          <t>batch_976be391c94a4aae</t>
         </is>
       </c>
       <c r="AC275" t="inlineStr">
@@ -32309,7 +32309,7 @@
       <c r="AE275" t="inlineStr"/>
       <c r="AF275" t="inlineStr">
         <is>
-          <t>2026-05-14T02:33:19+00:00</t>
+          <t>2026-05-14T02:59:23+00:00</t>
         </is>
       </c>
       <c r="AG275" t="inlineStr">
@@ -32409,7 +32409,7 @@
       </c>
       <c r="AB276" t="inlineStr">
         <is>
-          <t>batch_04ef5ec3e6b54457</t>
+          <t>batch_976be391c94a4aae</t>
         </is>
       </c>
       <c r="AC276" t="inlineStr">
@@ -32425,7 +32425,7 @@
       <c r="AE276" t="inlineStr"/>
       <c r="AF276" t="inlineStr">
         <is>
-          <t>2026-05-14T02:33:19+00:00</t>
+          <t>2026-05-14T02:59:23+00:00</t>
         </is>
       </c>
       <c r="AG276" t="inlineStr">
@@ -32525,7 +32525,7 @@
       </c>
       <c r="AB277" t="inlineStr">
         <is>
-          <t>batch_04ef5ec3e6b54457</t>
+          <t>batch_976be391c94a4aae</t>
         </is>
       </c>
       <c r="AC277" t="inlineStr">
@@ -32541,7 +32541,7 @@
       <c r="AE277" t="inlineStr"/>
       <c r="AF277" t="inlineStr">
         <is>
-          <t>2026-05-14T02:33:19+00:00</t>
+          <t>2026-05-14T02:59:23+00:00</t>
         </is>
       </c>
       <c r="AG277" t="inlineStr">
@@ -32641,7 +32641,7 @@
       </c>
       <c r="AB278" t="inlineStr">
         <is>
-          <t>batch_04ef5ec3e6b54457</t>
+          <t>batch_976be391c94a4aae</t>
         </is>
       </c>
       <c r="AC278" t="inlineStr">
@@ -32657,7 +32657,7 @@
       <c r="AE278" t="inlineStr"/>
       <c r="AF278" t="inlineStr">
         <is>
-          <t>2026-05-14T02:33:19+00:00</t>
+          <t>2026-05-14T02:59:23+00:00</t>
         </is>
       </c>
       <c r="AG278" t="inlineStr">
@@ -32757,7 +32757,7 @@
       </c>
       <c r="AB279" t="inlineStr">
         <is>
-          <t>batch_04ef5ec3e6b54457</t>
+          <t>batch_976be391c94a4aae</t>
         </is>
       </c>
       <c r="AC279" t="inlineStr">
@@ -32773,7 +32773,7 @@
       <c r="AE279" t="inlineStr"/>
       <c r="AF279" t="inlineStr">
         <is>
-          <t>2026-05-14T02:33:19+00:00</t>
+          <t>2026-05-14T02:59:23+00:00</t>
         </is>
       </c>
       <c r="AG279" t="inlineStr">
@@ -32873,7 +32873,7 @@
       </c>
       <c r="AB280" t="inlineStr">
         <is>
-          <t>batch_04ef5ec3e6b54457</t>
+          <t>batch_976be391c94a4aae</t>
         </is>
       </c>
       <c r="AC280" t="inlineStr">
@@ -32889,7 +32889,7 @@
       <c r="AE280" t="inlineStr"/>
       <c r="AF280" t="inlineStr">
         <is>
-          <t>2026-05-14T02:33:19+00:00</t>
+          <t>2026-05-14T02:59:23+00:00</t>
         </is>
       </c>
       <c r="AG280" t="inlineStr">
@@ -32989,7 +32989,7 @@
       </c>
       <c r="AB281" t="inlineStr">
         <is>
-          <t>batch_04ef5ec3e6b54457</t>
+          <t>batch_976be391c94a4aae</t>
         </is>
       </c>
       <c r="AC281" t="inlineStr">
@@ -33005,7 +33005,7 @@
       <c r="AE281" t="inlineStr"/>
       <c r="AF281" t="inlineStr">
         <is>
-          <t>2026-05-14T02:33:19+00:00</t>
+          <t>2026-05-14T02:59:23+00:00</t>
         </is>
       </c>
       <c r="AG281" t="inlineStr">
@@ -33105,7 +33105,7 @@
       </c>
       <c r="AB282" t="inlineStr">
         <is>
-          <t>batch_04ef5ec3e6b54457</t>
+          <t>batch_976be391c94a4aae</t>
         </is>
       </c>
       <c r="AC282" t="inlineStr">
@@ -33121,7 +33121,7 @@
       <c r="AE282" t="inlineStr"/>
       <c r="AF282" t="inlineStr">
         <is>
-          <t>2026-05-14T02:33:19+00:00</t>
+          <t>2026-05-14T02:59:23+00:00</t>
         </is>
       </c>
       <c r="AG282" t="inlineStr">
@@ -33221,7 +33221,7 @@
       </c>
       <c r="AB283" t="inlineStr">
         <is>
-          <t>batch_04ef5ec3e6b54457</t>
+          <t>batch_976be391c94a4aae</t>
         </is>
       </c>
       <c r="AC283" t="inlineStr">
@@ -33237,7 +33237,7 @@
       <c r="AE283" t="inlineStr"/>
       <c r="AF283" t="inlineStr">
         <is>
-          <t>2026-05-14T02:33:19+00:00</t>
+          <t>2026-05-14T02:59:23+00:00</t>
         </is>
       </c>
       <c r="AG283" t="inlineStr">
@@ -33337,7 +33337,7 @@
       </c>
       <c r="AB284" t="inlineStr">
         <is>
-          <t>batch_04ef5ec3e6b54457</t>
+          <t>batch_976be391c94a4aae</t>
         </is>
       </c>
       <c r="AC284" t="inlineStr">
@@ -33353,7 +33353,7 @@
       <c r="AE284" t="inlineStr"/>
       <c r="AF284" t="inlineStr">
         <is>
-          <t>2026-05-14T02:33:19+00:00</t>
+          <t>2026-05-14T02:59:23+00:00</t>
         </is>
       </c>
       <c r="AG284" t="inlineStr">
@@ -33453,7 +33453,7 @@
       </c>
       <c r="AB285" t="inlineStr">
         <is>
-          <t>batch_04ef5ec3e6b54457</t>
+          <t>batch_976be391c94a4aae</t>
         </is>
       </c>
       <c r="AC285" t="inlineStr">
@@ -33469,7 +33469,7 @@
       <c r="AE285" t="inlineStr"/>
       <c r="AF285" t="inlineStr">
         <is>
-          <t>2026-05-14T02:33:19+00:00</t>
+          <t>2026-05-14T02:59:23+00:00</t>
         </is>
       </c>
       <c r="AG285" t="inlineStr">
@@ -33569,7 +33569,7 @@
       </c>
       <c r="AB286" t="inlineStr">
         <is>
-          <t>batch_04ef5ec3e6b54457</t>
+          <t>batch_976be391c94a4aae</t>
         </is>
       </c>
       <c r="AC286" t="inlineStr">
@@ -33585,7 +33585,7 @@
       <c r="AE286" t="inlineStr"/>
       <c r="AF286" t="inlineStr">
         <is>
-          <t>2026-05-14T02:33:19+00:00</t>
+          <t>2026-05-14T02:59:23+00:00</t>
         </is>
       </c>
       <c r="AG286" t="inlineStr">
@@ -33685,7 +33685,7 @@
       </c>
       <c r="AB287" t="inlineStr">
         <is>
-          <t>batch_04ef5ec3e6b54457</t>
+          <t>batch_976be391c94a4aae</t>
         </is>
       </c>
       <c r="AC287" t="inlineStr">
@@ -33701,7 +33701,7 @@
       <c r="AE287" t="inlineStr"/>
       <c r="AF287" t="inlineStr">
         <is>
-          <t>2026-05-14T02:33:19+00:00</t>
+          <t>2026-05-14T02:59:23+00:00</t>
         </is>
       </c>
       <c r="AG287" t="inlineStr">
@@ -33801,7 +33801,7 @@
       </c>
       <c r="AB288" t="inlineStr">
         <is>
-          <t>batch_04ef5ec3e6b54457</t>
+          <t>batch_976be391c94a4aae</t>
         </is>
       </c>
       <c r="AC288" t="inlineStr">
@@ -33817,7 +33817,7 @@
       <c r="AE288" t="inlineStr"/>
       <c r="AF288" t="inlineStr">
         <is>
-          <t>2026-05-14T02:33:19+00:00</t>
+          <t>2026-05-14T02:59:23+00:00</t>
         </is>
       </c>
       <c r="AG288" t="inlineStr">
@@ -33917,7 +33917,7 @@
       </c>
       <c r="AB289" t="inlineStr">
         <is>
-          <t>batch_04ef5ec3e6b54457</t>
+          <t>batch_976be391c94a4aae</t>
         </is>
       </c>
       <c r="AC289" t="inlineStr">
@@ -33933,7 +33933,7 @@
       <c r="AE289" t="inlineStr"/>
       <c r="AF289" t="inlineStr">
         <is>
-          <t>2026-05-14T02:33:19+00:00</t>
+          <t>2026-05-14T02:59:23+00:00</t>
         </is>
       </c>
       <c r="AG289" t="inlineStr">
@@ -34033,7 +34033,7 @@
       </c>
       <c r="AB290" t="inlineStr">
         <is>
-          <t>batch_04ef5ec3e6b54457</t>
+          <t>batch_976be391c94a4aae</t>
         </is>
       </c>
       <c r="AC290" t="inlineStr">
@@ -34049,7 +34049,7 @@
       <c r="AE290" t="inlineStr"/>
       <c r="AF290" t="inlineStr">
         <is>
-          <t>2026-05-14T02:33:19+00:00</t>
+          <t>2026-05-14T02:59:23+00:00</t>
         </is>
       </c>
       <c r="AG290" t="inlineStr">
@@ -34149,7 +34149,7 @@
       </c>
       <c r="AB291" t="inlineStr">
         <is>
-          <t>batch_04ef5ec3e6b54457</t>
+          <t>batch_976be391c94a4aae</t>
         </is>
       </c>
       <c r="AC291" t="inlineStr">
@@ -34165,7 +34165,7 @@
       <c r="AE291" t="inlineStr"/>
       <c r="AF291" t="inlineStr">
         <is>
-          <t>2026-05-14T02:33:19+00:00</t>
+          <t>2026-05-14T02:59:23+00:00</t>
         </is>
       </c>
       <c r="AG291" t="inlineStr">
@@ -34265,7 +34265,7 @@
       </c>
       <c r="AB292" t="inlineStr">
         <is>
-          <t>batch_04ef5ec3e6b54457</t>
+          <t>batch_976be391c94a4aae</t>
         </is>
       </c>
       <c r="AC292" t="inlineStr">
@@ -34281,7 +34281,7 @@
       <c r="AE292" t="inlineStr"/>
       <c r="AF292" t="inlineStr">
         <is>
-          <t>2026-05-14T02:33:19+00:00</t>
+          <t>2026-05-14T02:59:23+00:00</t>
         </is>
       </c>
       <c r="AG292" t="inlineStr">
@@ -34381,7 +34381,7 @@
       </c>
       <c r="AB293" t="inlineStr">
         <is>
-          <t>batch_04ef5ec3e6b54457</t>
+          <t>batch_976be391c94a4aae</t>
         </is>
       </c>
       <c r="AC293" t="inlineStr">
@@ -34397,7 +34397,7 @@
       <c r="AE293" t="inlineStr"/>
       <c r="AF293" t="inlineStr">
         <is>
-          <t>2026-05-14T02:33:19+00:00</t>
+          <t>2026-05-14T02:59:23+00:00</t>
         </is>
       </c>
       <c r="AG293" t="inlineStr">
@@ -34497,7 +34497,7 @@
       </c>
       <c r="AB294" t="inlineStr">
         <is>
-          <t>batch_04ef5ec3e6b54457</t>
+          <t>batch_976be391c94a4aae</t>
         </is>
       </c>
       <c r="AC294" t="inlineStr">
@@ -34513,7 +34513,7 @@
       <c r="AE294" t="inlineStr"/>
       <c r="AF294" t="inlineStr">
         <is>
-          <t>2026-05-14T02:33:19+00:00</t>
+          <t>2026-05-14T02:59:23+00:00</t>
         </is>
       </c>
       <c r="AG294" t="inlineStr">
@@ -34613,7 +34613,7 @@
       </c>
       <c r="AB295" t="inlineStr">
         <is>
-          <t>batch_04ef5ec3e6b54457</t>
+          <t>batch_976be391c94a4aae</t>
         </is>
       </c>
       <c r="AC295" t="inlineStr">
@@ -34629,7 +34629,7 @@
       <c r="AE295" t="inlineStr"/>
       <c r="AF295" t="inlineStr">
         <is>
-          <t>2026-05-14T02:33:19+00:00</t>
+          <t>2026-05-14T02:59:23+00:00</t>
         </is>
       </c>
       <c r="AG295" t="inlineStr">
@@ -34729,7 +34729,7 @@
       </c>
       <c r="AB296" t="inlineStr">
         <is>
-          <t>batch_04ef5ec3e6b54457</t>
+          <t>batch_976be391c94a4aae</t>
         </is>
       </c>
       <c r="AC296" t="inlineStr">
@@ -34745,7 +34745,7 @@
       <c r="AE296" t="inlineStr"/>
       <c r="AF296" t="inlineStr">
         <is>
-          <t>2026-05-14T02:33:19+00:00</t>
+          <t>2026-05-14T02:59:23+00:00</t>
         </is>
       </c>
       <c r="AG296" t="inlineStr">
@@ -34845,7 +34845,7 @@
       </c>
       <c r="AB297" t="inlineStr">
         <is>
-          <t>batch_04ef5ec3e6b54457</t>
+          <t>batch_976be391c94a4aae</t>
         </is>
       </c>
       <c r="AC297" t="inlineStr">
@@ -34861,7 +34861,7 @@
       <c r="AE297" t="inlineStr"/>
       <c r="AF297" t="inlineStr">
         <is>
-          <t>2026-05-14T02:33:19+00:00</t>
+          <t>2026-05-14T02:59:23+00:00</t>
         </is>
       </c>
       <c r="AG297" t="inlineStr">
@@ -34961,7 +34961,7 @@
       </c>
       <c r="AB298" t="inlineStr">
         <is>
-          <t>batch_04ef5ec3e6b54457</t>
+          <t>batch_976be391c94a4aae</t>
         </is>
       </c>
       <c r="AC298" t="inlineStr">
@@ -34977,7 +34977,7 @@
       <c r="AE298" t="inlineStr"/>
       <c r="AF298" t="inlineStr">
         <is>
-          <t>2026-05-14T02:33:19+00:00</t>
+          <t>2026-05-14T02:59:23+00:00</t>
         </is>
       </c>
       <c r="AG298" t="inlineStr">
@@ -35077,7 +35077,7 @@
       </c>
       <c r="AB299" t="inlineStr">
         <is>
-          <t>batch_04ef5ec3e6b54457</t>
+          <t>batch_976be391c94a4aae</t>
         </is>
       </c>
       <c r="AC299" t="inlineStr">
@@ -35093,7 +35093,7 @@
       <c r="AE299" t="inlineStr"/>
       <c r="AF299" t="inlineStr">
         <is>
-          <t>2026-05-14T02:33:19+00:00</t>
+          <t>2026-05-14T02:59:23+00:00</t>
         </is>
       </c>
       <c r="AG299" t="inlineStr">
@@ -35193,7 +35193,7 @@
       </c>
       <c r="AB300" t="inlineStr">
         <is>
-          <t>batch_04ef5ec3e6b54457</t>
+          <t>batch_976be391c94a4aae</t>
         </is>
       </c>
       <c r="AC300" t="inlineStr">
@@ -35209,7 +35209,7 @@
       <c r="AE300" t="inlineStr"/>
       <c r="AF300" t="inlineStr">
         <is>
-          <t>2026-05-14T02:33:19+00:00</t>
+          <t>2026-05-14T02:59:23+00:00</t>
         </is>
       </c>
       <c r="AG300" t="inlineStr">
@@ -35309,7 +35309,7 @@
       </c>
       <c r="AB301" t="inlineStr">
         <is>
-          <t>batch_04ef5ec3e6b54457</t>
+          <t>batch_976be391c94a4aae</t>
         </is>
       </c>
       <c r="AC301" t="inlineStr">
@@ -35325,7 +35325,7 @@
       <c r="AE301" t="inlineStr"/>
       <c r="AF301" t="inlineStr">
         <is>
-          <t>2026-05-14T02:33:19+00:00</t>
+          <t>2026-05-14T02:59:23+00:00</t>
         </is>
       </c>
       <c r="AG301" t="inlineStr">
@@ -35425,7 +35425,7 @@
       </c>
       <c r="AB302" t="inlineStr">
         <is>
-          <t>batch_04ef5ec3e6b54457</t>
+          <t>batch_976be391c94a4aae</t>
         </is>
       </c>
       <c r="AC302" t="inlineStr">
@@ -35441,7 +35441,7 @@
       <c r="AE302" t="inlineStr"/>
       <c r="AF302" t="inlineStr">
         <is>
-          <t>2026-05-14T02:33:19+00:00</t>
+          <t>2026-05-14T02:59:23+00:00</t>
         </is>
       </c>
       <c r="AG302" t="inlineStr">
@@ -35541,7 +35541,7 @@
       </c>
       <c r="AB303" t="inlineStr">
         <is>
-          <t>batch_04ef5ec3e6b54457</t>
+          <t>batch_976be391c94a4aae</t>
         </is>
       </c>
       <c r="AC303" t="inlineStr">
@@ -35557,7 +35557,7 @@
       <c r="AE303" t="inlineStr"/>
       <c r="AF303" t="inlineStr">
         <is>
-          <t>2026-05-14T02:33:19+00:00</t>
+          <t>2026-05-14T02:59:23+00:00</t>
         </is>
       </c>
       <c r="AG303" t="inlineStr">
@@ -35657,7 +35657,7 @@
       </c>
       <c r="AB304" t="inlineStr">
         <is>
-          <t>batch_04ef5ec3e6b54457</t>
+          <t>batch_976be391c94a4aae</t>
         </is>
       </c>
       <c r="AC304" t="inlineStr">
@@ -35673,7 +35673,7 @@
       <c r="AE304" t="inlineStr"/>
       <c r="AF304" t="inlineStr">
         <is>
-          <t>2026-05-14T02:33:19+00:00</t>
+          <t>2026-05-14T02:59:23+00:00</t>
         </is>
       </c>
       <c r="AG304" t="inlineStr">
@@ -35773,7 +35773,7 @@
       </c>
       <c r="AB305" t="inlineStr">
         <is>
-          <t>batch_04ef5ec3e6b54457</t>
+          <t>batch_976be391c94a4aae</t>
         </is>
       </c>
       <c r="AC305" t="inlineStr">
@@ -35789,7 +35789,7 @@
       <c r="AE305" t="inlineStr"/>
       <c r="AF305" t="inlineStr">
         <is>
-          <t>2026-05-14T02:33:19+00:00</t>
+          <t>2026-05-14T02:59:23+00:00</t>
         </is>
       </c>
       <c r="AG305" t="inlineStr">
@@ -35889,7 +35889,7 @@
       </c>
       <c r="AB306" t="inlineStr">
         <is>
-          <t>batch_04ef5ec3e6b54457</t>
+          <t>batch_976be391c94a4aae</t>
         </is>
       </c>
       <c r="AC306" t="inlineStr">
@@ -35905,7 +35905,7 @@
       <c r="AE306" t="inlineStr"/>
       <c r="AF306" t="inlineStr">
         <is>
-          <t>2026-05-14T02:33:19+00:00</t>
+          <t>2026-05-14T02:59:23+00:00</t>
         </is>
       </c>
       <c r="AG306" t="inlineStr">
@@ -36005,7 +36005,7 @@
       </c>
       <c r="AB307" t="inlineStr">
         <is>
-          <t>batch_04ef5ec3e6b54457</t>
+          <t>batch_976be391c94a4aae</t>
         </is>
       </c>
       <c r="AC307" t="inlineStr">
@@ -36021,7 +36021,7 @@
       <c r="AE307" t="inlineStr"/>
       <c r="AF307" t="inlineStr">
         <is>
-          <t>2026-05-14T02:33:19+00:00</t>
+          <t>2026-05-14T02:59:23+00:00</t>
         </is>
       </c>
       <c r="AG307" t="inlineStr">
@@ -36121,7 +36121,7 @@
       </c>
       <c r="AB308" t="inlineStr">
         <is>
-          <t>batch_04ef5ec3e6b54457</t>
+          <t>batch_976be391c94a4aae</t>
         </is>
       </c>
       <c r="AC308" t="inlineStr">
@@ -36137,7 +36137,7 @@
       <c r="AE308" t="inlineStr"/>
       <c r="AF308" t="inlineStr">
         <is>
-          <t>2026-05-14T02:33:19+00:00</t>
+          <t>2026-05-14T02:59:23+00:00</t>
         </is>
       </c>
       <c r="AG308" t="inlineStr">
@@ -36237,7 +36237,7 @@
       </c>
       <c r="AB309" t="inlineStr">
         <is>
-          <t>batch_04ef5ec3e6b54457</t>
+          <t>batch_976be391c94a4aae</t>
         </is>
       </c>
       <c r="AC309" t="inlineStr">
@@ -36253,7 +36253,7 @@
       <c r="AE309" t="inlineStr"/>
       <c r="AF309" t="inlineStr">
         <is>
-          <t>2026-05-14T02:33:19+00:00</t>
+          <t>2026-05-14T02:59:23+00:00</t>
         </is>
       </c>
       <c r="AG309" t="inlineStr">
@@ -36353,7 +36353,7 @@
       </c>
       <c r="AB310" t="inlineStr">
         <is>
-          <t>batch_04ef5ec3e6b54457</t>
+          <t>batch_976be391c94a4aae</t>
         </is>
       </c>
       <c r="AC310" t="inlineStr">
@@ -36369,7 +36369,7 @@
       <c r="AE310" t="inlineStr"/>
       <c r="AF310" t="inlineStr">
         <is>
-          <t>2026-05-14T02:33:19+00:00</t>
+          <t>2026-05-14T02:59:23+00:00</t>
         </is>
       </c>
       <c r="AG310" t="inlineStr">
@@ -36469,7 +36469,7 @@
       </c>
       <c r="AB311" t="inlineStr">
         <is>
-          <t>batch_04ef5ec3e6b54457</t>
+          <t>batch_976be391c94a4aae</t>
         </is>
       </c>
       <c r="AC311" t="inlineStr">
@@ -36485,7 +36485,7 @@
       <c r="AE311" t="inlineStr"/>
       <c r="AF311" t="inlineStr">
         <is>
-          <t>2026-05-14T02:33:19+00:00</t>
+          <t>2026-05-14T02:59:23+00:00</t>
         </is>
       </c>
       <c r="AG311" t="inlineStr">
@@ -36585,7 +36585,7 @@
       </c>
       <c r="AB312" t="inlineStr">
         <is>
-          <t>batch_04ef5ec3e6b54457</t>
+          <t>batch_976be391c94a4aae</t>
         </is>
       </c>
       <c r="AC312" t="inlineStr">
@@ -36601,7 +36601,7 @@
       <c r="AE312" t="inlineStr"/>
       <c r="AF312" t="inlineStr">
         <is>
-          <t>2026-05-14T02:33:19+00:00</t>
+          <t>2026-05-14T02:59:23+00:00</t>
         </is>
       </c>
       <c r="AG312" t="inlineStr">
@@ -36701,7 +36701,7 @@
       </c>
       <c r="AB313" t="inlineStr">
         <is>
-          <t>batch_04ef5ec3e6b54457</t>
+          <t>batch_976be391c94a4aae</t>
         </is>
       </c>
       <c r="AC313" t="inlineStr">
@@ -36717,7 +36717,7 @@
       <c r="AE313" t="inlineStr"/>
       <c r="AF313" t="inlineStr">
         <is>
-          <t>2026-05-14T02:33:19+00:00</t>
+          <t>2026-05-14T02:59:23+00:00</t>
         </is>
       </c>
       <c r="AG313" t="inlineStr">
@@ -36817,7 +36817,7 @@
       </c>
       <c r="AB314" t="inlineStr">
         <is>
-          <t>batch_04ef5ec3e6b54457</t>
+          <t>batch_976be391c94a4aae</t>
         </is>
       </c>
       <c r="AC314" t="inlineStr">
@@ -36833,7 +36833,7 @@
       <c r="AE314" t="inlineStr"/>
       <c r="AF314" t="inlineStr">
         <is>
-          <t>2026-05-14T02:33:19+00:00</t>
+          <t>2026-05-14T02:59:23+00:00</t>
         </is>
       </c>
       <c r="AG314" t="inlineStr">
@@ -36933,7 +36933,7 @@
       </c>
       <c r="AB315" t="inlineStr">
         <is>
-          <t>batch_04ef5ec3e6b54457</t>
+          <t>batch_976be391c94a4aae</t>
         </is>
       </c>
       <c r="AC315" t="inlineStr">
@@ -36949,7 +36949,7 @@
       <c r="AE315" t="inlineStr"/>
       <c r="AF315" t="inlineStr">
         <is>
-          <t>2026-05-14T02:33:19+00:00</t>
+          <t>2026-05-14T02:59:23+00:00</t>
         </is>
       </c>
       <c r="AG315" t="inlineStr">
@@ -37049,7 +37049,7 @@
       </c>
       <c r="AB316" t="inlineStr">
         <is>
-          <t>batch_04ef5ec3e6b54457</t>
+          <t>batch_976be391c94a4aae</t>
         </is>
       </c>
       <c r="AC316" t="inlineStr">
@@ -37065,7 +37065,7 @@
       <c r="AE316" t="inlineStr"/>
       <c r="AF316" t="inlineStr">
         <is>
-          <t>2026-05-14T02:33:19+00:00</t>
+          <t>2026-05-14T02:59:23+00:00</t>
         </is>
       </c>
       <c r="AG316" t="inlineStr">
@@ -37165,7 +37165,7 @@
       </c>
       <c r="AB317" t="inlineStr">
         <is>
-          <t>batch_04ef5ec3e6b54457</t>
+          <t>batch_976be391c94a4aae</t>
         </is>
       </c>
       <c r="AC317" t="inlineStr">
@@ -37181,7 +37181,7 @@
       <c r="AE317" t="inlineStr"/>
       <c r="AF317" t="inlineStr">
         <is>
-          <t>2026-05-14T02:33:19+00:00</t>
+          <t>2026-05-14T02:59:23+00:00</t>
         </is>
       </c>
       <c r="AG317" t="inlineStr">
@@ -37281,7 +37281,7 @@
       </c>
       <c r="AB318" t="inlineStr">
         <is>
-          <t>batch_04ef5ec3e6b54457</t>
+          <t>batch_976be391c94a4aae</t>
         </is>
       </c>
       <c r="AC318" t="inlineStr">
@@ -37297,7 +37297,7 @@
       <c r="AE318" t="inlineStr"/>
       <c r="AF318" t="inlineStr">
         <is>
-          <t>2026-05-14T02:33:19+00:00</t>
+          <t>2026-05-14T02:59:23+00:00</t>
         </is>
       </c>
       <c r="AG318" t="inlineStr">
@@ -37397,7 +37397,7 @@
       </c>
       <c r="AB319" t="inlineStr">
         <is>
-          <t>batch_04ef5ec3e6b54457</t>
+          <t>batch_976be391c94a4aae</t>
         </is>
       </c>
       <c r="AC319" t="inlineStr">
@@ -37413,7 +37413,7 @@
       <c r="AE319" t="inlineStr"/>
       <c r="AF319" t="inlineStr">
         <is>
-          <t>2026-05-14T02:33:19+00:00</t>
+          <t>2026-05-14T02:59:23+00:00</t>
         </is>
       </c>
       <c r="AG319" t="inlineStr">
@@ -37513,7 +37513,7 @@
       </c>
       <c r="AB320" t="inlineStr">
         <is>
-          <t>batch_04ef5ec3e6b54457</t>
+          <t>batch_976be391c94a4aae</t>
         </is>
       </c>
       <c r="AC320" t="inlineStr">
@@ -37529,7 +37529,7 @@
       <c r="AE320" t="inlineStr"/>
       <c r="AF320" t="inlineStr">
         <is>
-          <t>2026-05-14T02:33:19+00:00</t>
+          <t>2026-05-14T02:59:23+00:00</t>
         </is>
       </c>
       <c r="AG320" t="inlineStr">
@@ -37629,7 +37629,7 @@
       </c>
       <c r="AB321" t="inlineStr">
         <is>
-          <t>batch_04ef5ec3e6b54457</t>
+          <t>batch_976be391c94a4aae</t>
         </is>
       </c>
       <c r="AC321" t="inlineStr">
@@ -37645,7 +37645,7 @@
       <c r="AE321" t="inlineStr"/>
       <c r="AF321" t="inlineStr">
         <is>
-          <t>2026-05-14T02:33:19+00:00</t>
+          <t>2026-05-14T02:59:23+00:00</t>
         </is>
       </c>
       <c r="AG321" t="inlineStr">
@@ -37745,7 +37745,7 @@
       </c>
       <c r="AB322" t="inlineStr">
         <is>
-          <t>batch_04ef5ec3e6b54457</t>
+          <t>batch_976be391c94a4aae</t>
         </is>
       </c>
       <c r="AC322" t="inlineStr">
@@ -37761,7 +37761,7 @@
       <c r="AE322" t="inlineStr"/>
       <c r="AF322" t="inlineStr">
         <is>
-          <t>2026-05-14T02:33:19+00:00</t>
+          <t>2026-05-14T02:59:23+00:00</t>
         </is>
       </c>
       <c r="AG322" t="inlineStr">
@@ -37861,7 +37861,7 @@
       </c>
       <c r="AB323" t="inlineStr">
         <is>
-          <t>batch_04ef5ec3e6b54457</t>
+          <t>batch_976be391c94a4aae</t>
         </is>
       </c>
       <c r="AC323" t="inlineStr">
@@ -37877,7 +37877,7 @@
       <c r="AE323" t="inlineStr"/>
       <c r="AF323" t="inlineStr">
         <is>
-          <t>2026-05-14T02:33:19+00:00</t>
+          <t>2026-05-14T02:59:23+00:00</t>
         </is>
       </c>
       <c r="AG323" t="inlineStr">
@@ -37977,7 +37977,7 @@
       </c>
       <c r="AB324" t="inlineStr">
         <is>
-          <t>batch_04ef5ec3e6b54457</t>
+          <t>batch_976be391c94a4aae</t>
         </is>
       </c>
       <c r="AC324" t="inlineStr">
@@ -37993,7 +37993,7 @@
       <c r="AE324" t="inlineStr"/>
       <c r="AF324" t="inlineStr">
         <is>
-          <t>2026-05-14T02:33:19+00:00</t>
+          <t>2026-05-14T02:59:23+00:00</t>
         </is>
       </c>
       <c r="AG324" t="inlineStr">
@@ -38093,7 +38093,7 @@
       </c>
       <c r="AB325" t="inlineStr">
         <is>
-          <t>batch_04ef5ec3e6b54457</t>
+          <t>batch_976be391c94a4aae</t>
         </is>
       </c>
       <c r="AC325" t="inlineStr">
@@ -38109,7 +38109,7 @@
       <c r="AE325" t="inlineStr"/>
       <c r="AF325" t="inlineStr">
         <is>
-          <t>2026-05-14T02:33:19+00:00</t>
+          <t>2026-05-14T02:59:23+00:00</t>
         </is>
       </c>
       <c r="AG325" t="inlineStr">
@@ -38209,7 +38209,7 @@
       </c>
       <c r="AB326" t="inlineStr">
         <is>
-          <t>batch_04ef5ec3e6b54457</t>
+          <t>batch_976be391c94a4aae</t>
         </is>
       </c>
       <c r="AC326" t="inlineStr">
@@ -38225,7 +38225,7 @@
       <c r="AE326" t="inlineStr"/>
       <c r="AF326" t="inlineStr">
         <is>
-          <t>2026-05-14T02:33:19+00:00</t>
+          <t>2026-05-14T02:59:23+00:00</t>
         </is>
       </c>
       <c r="AG326" t="inlineStr">
@@ -38325,7 +38325,7 @@
       </c>
       <c r="AB327" t="inlineStr">
         <is>
-          <t>batch_04ef5ec3e6b54457</t>
+          <t>batch_976be391c94a4aae</t>
         </is>
       </c>
       <c r="AC327" t="inlineStr">
@@ -38341,7 +38341,7 @@
       <c r="AE327" t="inlineStr"/>
       <c r="AF327" t="inlineStr">
         <is>
-          <t>2026-05-14T02:33:19+00:00</t>
+          <t>2026-05-14T02:59:23+00:00</t>
         </is>
       </c>
       <c r="AG327" t="inlineStr">
@@ -38441,7 +38441,7 @@
       </c>
       <c r="AB328" t="inlineStr">
         <is>
-          <t>batch_04ef5ec3e6b54457</t>
+          <t>batch_976be391c94a4aae</t>
         </is>
       </c>
       <c r="AC328" t="inlineStr">
@@ -38457,7 +38457,7 @@
       <c r="AE328" t="inlineStr"/>
       <c r="AF328" t="inlineStr">
         <is>
-          <t>2026-05-14T02:33:19+00:00</t>
+          <t>2026-05-14T02:59:23+00:00</t>
         </is>
       </c>
       <c r="AG328" t="inlineStr">
@@ -38557,7 +38557,7 @@
       </c>
       <c r="AB329" t="inlineStr">
         <is>
-          <t>batch_04ef5ec3e6b54457</t>
+          <t>batch_976be391c94a4aae</t>
         </is>
       </c>
       <c r="AC329" t="inlineStr">
@@ -38573,7 +38573,7 @@
       <c r="AE329" t="inlineStr"/>
       <c r="AF329" t="inlineStr">
         <is>
-          <t>2026-05-14T02:33:19+00:00</t>
+          <t>2026-05-14T02:59:23+00:00</t>
         </is>
       </c>
       <c r="AG329" t="inlineStr">
@@ -38673,7 +38673,7 @@
       </c>
       <c r="AB330" t="inlineStr">
         <is>
-          <t>batch_04ef5ec3e6b54457</t>
+          <t>batch_976be391c94a4aae</t>
         </is>
       </c>
       <c r="AC330" t="inlineStr">
@@ -38689,7 +38689,7 @@
       <c r="AE330" t="inlineStr"/>
       <c r="AF330" t="inlineStr">
         <is>
-          <t>2026-05-14T02:33:19+00:00</t>
+          <t>2026-05-14T02:59:23+00:00</t>
         </is>
       </c>
       <c r="AG330" t="inlineStr">
@@ -38789,7 +38789,7 @@
       </c>
       <c r="AB331" t="inlineStr">
         <is>
-          <t>batch_04ef5ec3e6b54457</t>
+          <t>batch_976be391c94a4aae</t>
         </is>
       </c>
       <c r="AC331" t="inlineStr">
@@ -38805,7 +38805,7 @@
       <c r="AE331" t="inlineStr"/>
       <c r="AF331" t="inlineStr">
         <is>
-          <t>2026-05-14T02:33:19+00:00</t>
+          <t>2026-05-14T02:59:23+00:00</t>
         </is>
       </c>
       <c r="AG331" t="inlineStr">
@@ -38905,7 +38905,7 @@
       </c>
       <c r="AB332" t="inlineStr">
         <is>
-          <t>batch_04ef5ec3e6b54457</t>
+          <t>batch_976be391c94a4aae</t>
         </is>
       </c>
       <c r="AC332" t="inlineStr">
@@ -38921,7 +38921,7 @@
       <c r="AE332" t="inlineStr"/>
       <c r="AF332" t="inlineStr">
         <is>
-          <t>2026-05-14T02:33:19+00:00</t>
+          <t>2026-05-14T02:59:23+00:00</t>
         </is>
       </c>
       <c r="AG332" t="inlineStr">
@@ -39021,7 +39021,7 @@
       </c>
       <c r="AB333" t="inlineStr">
         <is>
-          <t>batch_04ef5ec3e6b54457</t>
+          <t>batch_976be391c94a4aae</t>
         </is>
       </c>
       <c r="AC333" t="inlineStr">
@@ -39037,7 +39037,7 @@
       <c r="AE333" t="inlineStr"/>
       <c r="AF333" t="inlineStr">
         <is>
-          <t>2026-05-14T02:33:19+00:00</t>
+          <t>2026-05-14T02:59:23+00:00</t>
         </is>
       </c>
       <c r="AG333" t="inlineStr">
@@ -39137,7 +39137,7 @@
       </c>
       <c r="AB334" t="inlineStr">
         <is>
-          <t>batch_04ef5ec3e6b54457</t>
+          <t>batch_976be391c94a4aae</t>
         </is>
       </c>
       <c r="AC334" t="inlineStr">
@@ -39153,7 +39153,7 @@
       <c r="AE334" t="inlineStr"/>
       <c r="AF334" t="inlineStr">
         <is>
-          <t>2026-05-14T02:33:19+00:00</t>
+          <t>2026-05-14T02:59:23+00:00</t>
         </is>
       </c>
       <c r="AG334" t="inlineStr">
@@ -39253,7 +39253,7 @@
       </c>
       <c r="AB335" t="inlineStr">
         <is>
-          <t>batch_04ef5ec3e6b54457</t>
+          <t>batch_976be391c94a4aae</t>
         </is>
       </c>
       <c r="AC335" t="inlineStr">
@@ -39269,7 +39269,7 @@
       <c r="AE335" t="inlineStr"/>
       <c r="AF335" t="inlineStr">
         <is>
-          <t>2026-05-14T02:33:19+00:00</t>
+          <t>2026-05-14T02:59:23+00:00</t>
         </is>
       </c>
       <c r="AG335" t="inlineStr">
@@ -39369,7 +39369,7 @@
       </c>
       <c r="AB336" t="inlineStr">
         <is>
-          <t>batch_04ef5ec3e6b54457</t>
+          <t>batch_976be391c94a4aae</t>
         </is>
       </c>
       <c r="AC336" t="inlineStr">
@@ -39385,7 +39385,7 @@
       <c r="AE336" t="inlineStr"/>
       <c r="AF336" t="inlineStr">
         <is>
-          <t>2026-05-14T02:33:19+00:00</t>
+          <t>2026-05-14T02:59:23+00:00</t>
         </is>
       </c>
       <c r="AG336" t="inlineStr">
@@ -39485,7 +39485,7 @@
       </c>
       <c r="AB337" t="inlineStr">
         <is>
-          <t>batch_04ef5ec3e6b54457</t>
+          <t>batch_976be391c94a4aae</t>
         </is>
       </c>
       <c r="AC337" t="inlineStr">
@@ -39501,7 +39501,7 @@
       <c r="AE337" t="inlineStr"/>
       <c r="AF337" t="inlineStr">
         <is>
-          <t>2026-05-14T02:33:19+00:00</t>
+          <t>2026-05-14T02:59:23+00:00</t>
         </is>
       </c>
       <c r="AG337" t="inlineStr">
@@ -39601,7 +39601,7 @@
       </c>
       <c r="AB338" t="inlineStr">
         <is>
-          <t>batch_04ef5ec3e6b54457</t>
+          <t>batch_976be391c94a4aae</t>
         </is>
       </c>
       <c r="AC338" t="inlineStr">
@@ -39617,7 +39617,7 @@
       <c r="AE338" t="inlineStr"/>
       <c r="AF338" t="inlineStr">
         <is>
-          <t>2026-05-14T02:33:19+00:00</t>
+          <t>2026-05-14T02:59:23+00:00</t>
         </is>
       </c>
       <c r="AG338" t="inlineStr">
@@ -39717,7 +39717,7 @@
       </c>
       <c r="AB339" t="inlineStr">
         <is>
-          <t>batch_04ef5ec3e6b54457</t>
+          <t>batch_976be391c94a4aae</t>
         </is>
       </c>
       <c r="AC339" t="inlineStr">
@@ -39733,7 +39733,7 @@
       <c r="AE339" t="inlineStr"/>
       <c r="AF339" t="inlineStr">
         <is>
-          <t>2026-05-14T02:33:19+00:00</t>
+          <t>2026-05-14T02:59:23+00:00</t>
         </is>
       </c>
       <c r="AG339" t="inlineStr">
@@ -39833,7 +39833,7 @@
       </c>
       <c r="AB340" t="inlineStr">
         <is>
-          <t>batch_04ef5ec3e6b54457</t>
+          <t>batch_976be391c94a4aae</t>
         </is>
       </c>
       <c r="AC340" t="inlineStr">
@@ -39849,7 +39849,7 @@
       <c r="AE340" t="inlineStr"/>
       <c r="AF340" t="inlineStr">
         <is>
-          <t>2026-05-14T02:33:19+00:00</t>
+          <t>2026-05-14T02:59:23+00:00</t>
         </is>
       </c>
       <c r="AG340" t="inlineStr">
@@ -39949,7 +39949,7 @@
       </c>
       <c r="AB341" t="inlineStr">
         <is>
-          <t>batch_04ef5ec3e6b54457</t>
+          <t>batch_976be391c94a4aae</t>
         </is>
       </c>
       <c r="AC341" t="inlineStr">
@@ -39965,7 +39965,7 @@
       <c r="AE341" t="inlineStr"/>
       <c r="AF341" t="inlineStr">
         <is>
-          <t>2026-05-14T02:33:19+00:00</t>
+          <t>2026-05-14T02:59:23+00:00</t>
         </is>
       </c>
       <c r="AG341" t="inlineStr">
@@ -40065,7 +40065,7 @@
       </c>
       <c r="AB342" t="inlineStr">
         <is>
-          <t>batch_04ef5ec3e6b54457</t>
+          <t>batch_976be391c94a4aae</t>
         </is>
       </c>
       <c r="AC342" t="inlineStr">
@@ -40081,7 +40081,7 @@
       <c r="AE342" t="inlineStr"/>
       <c r="AF342" t="inlineStr">
         <is>
-          <t>2026-05-14T02:33:19+00:00</t>
+          <t>2026-05-14T02:59:23+00:00</t>
         </is>
       </c>
       <c r="AG342" t="inlineStr">
@@ -40181,7 +40181,7 @@
       </c>
       <c r="AB343" t="inlineStr">
         <is>
-          <t>batch_04ef5ec3e6b54457</t>
+          <t>batch_976be391c94a4aae</t>
         </is>
       </c>
       <c r="AC343" t="inlineStr">
@@ -40197,7 +40197,7 @@
       <c r="AE343" t="inlineStr"/>
       <c r="AF343" t="inlineStr">
         <is>
-          <t>2026-05-14T02:33:19+00:00</t>
+          <t>2026-05-14T02:59:23+00:00</t>
         </is>
       </c>
       <c r="AG343" t="inlineStr">
@@ -40297,7 +40297,7 @@
       </c>
       <c r="AB344" t="inlineStr">
         <is>
-          <t>batch_04ef5ec3e6b54457</t>
+          <t>batch_976be391c94a4aae</t>
         </is>
       </c>
       <c r="AC344" t="inlineStr">
@@ -40313,7 +40313,7 @@
       <c r="AE344" t="inlineStr"/>
       <c r="AF344" t="inlineStr">
         <is>
-          <t>2026-05-14T02:33:19+00:00</t>
+          <t>2026-05-14T02:59:23+00:00</t>
         </is>
       </c>
       <c r="AG344" t="inlineStr">
@@ -40413,7 +40413,7 @@
       </c>
       <c r="AB345" t="inlineStr">
         <is>
-          <t>batch_04ef5ec3e6b54457</t>
+          <t>batch_976be391c94a4aae</t>
         </is>
       </c>
       <c r="AC345" t="inlineStr">
@@ -40429,7 +40429,7 @@
       <c r="AE345" t="inlineStr"/>
       <c r="AF345" t="inlineStr">
         <is>
-          <t>2026-05-14T02:33:19+00:00</t>
+          <t>2026-05-14T02:59:23+00:00</t>
         </is>
       </c>
       <c r="AG345" t="inlineStr">
@@ -40529,7 +40529,7 @@
       </c>
       <c r="AB346" t="inlineStr">
         <is>
-          <t>batch_04ef5ec3e6b54457</t>
+          <t>batch_976be391c94a4aae</t>
         </is>
       </c>
       <c r="AC346" t="inlineStr">
@@ -40545,7 +40545,7 @@
       <c r="AE346" t="inlineStr"/>
       <c r="AF346" t="inlineStr">
         <is>
-          <t>2026-05-14T02:33:19+00:00</t>
+          <t>2026-05-14T02:59:23+00:00</t>
         </is>
       </c>
       <c r="AG346" t="inlineStr">
@@ -40645,7 +40645,7 @@
       </c>
       <c r="AB347" t="inlineStr">
         <is>
-          <t>batch_04ef5ec3e6b54457</t>
+          <t>batch_976be391c94a4aae</t>
         </is>
       </c>
       <c r="AC347" t="inlineStr">
@@ -40661,7 +40661,7 @@
       <c r="AE347" t="inlineStr"/>
       <c r="AF347" t="inlineStr">
         <is>
-          <t>2026-05-14T02:33:19+00:00</t>
+          <t>2026-05-14T02:59:23+00:00</t>
         </is>
       </c>
       <c r="AG347" t="inlineStr">
@@ -40761,7 +40761,7 @@
       </c>
       <c r="AB348" t="inlineStr">
         <is>
-          <t>batch_04ef5ec3e6b54457</t>
+          <t>batch_976be391c94a4aae</t>
         </is>
       </c>
       <c r="AC348" t="inlineStr">
@@ -40777,7 +40777,7 @@
       <c r="AE348" t="inlineStr"/>
       <c r="AF348" t="inlineStr">
         <is>
-          <t>2026-05-14T02:33:19+00:00</t>
+          <t>2026-05-14T02:59:23+00:00</t>
         </is>
       </c>
       <c r="AG348" t="inlineStr">
@@ -40877,7 +40877,7 @@
       </c>
       <c r="AB349" t="inlineStr">
         <is>
-          <t>batch_04ef5ec3e6b54457</t>
+          <t>batch_976be391c94a4aae</t>
         </is>
       </c>
       <c r="AC349" t="inlineStr">
@@ -40893,7 +40893,7 @@
       <c r="AE349" t="inlineStr"/>
       <c r="AF349" t="inlineStr">
         <is>
-          <t>2026-05-14T02:33:19+00:00</t>
+          <t>2026-05-14T02:59:23+00:00</t>
         </is>
       </c>
       <c r="AG349" t="inlineStr">
@@ -40978,7 +40978,7 @@
       </c>
       <c r="AB350" t="inlineStr">
         <is>
-          <t>batch_04ef5ec3e6b54457</t>
+          <t>batch_976be391c94a4aae</t>
         </is>
       </c>
       <c r="AC350" t="inlineStr">
@@ -40994,7 +40994,7 @@
       <c r="AE350" t="inlineStr"/>
       <c r="AF350" t="inlineStr">
         <is>
-          <t>2026-05-14T02:33:19+00:00</t>
+          <t>2026-05-14T02:59:23+00:00</t>
         </is>
       </c>
       <c r="AG350" t="inlineStr">
@@ -41079,7 +41079,7 @@
       </c>
       <c r="AB351" t="inlineStr">
         <is>
-          <t>batch_04ef5ec3e6b54457</t>
+          <t>batch_976be391c94a4aae</t>
         </is>
       </c>
       <c r="AC351" t="inlineStr">
@@ -41095,7 +41095,7 @@
       <c r="AE351" t="inlineStr"/>
       <c r="AF351" t="inlineStr">
         <is>
-          <t>2026-05-14T02:33:19+00:00</t>
+          <t>2026-05-14T02:59:23+00:00</t>
         </is>
       </c>
       <c r="AG351" t="inlineStr">
@@ -41180,7 +41180,7 @@
       </c>
       <c r="AB352" t="inlineStr">
         <is>
-          <t>batch_04ef5ec3e6b54457</t>
+          <t>batch_976be391c94a4aae</t>
         </is>
       </c>
       <c r="AC352" t="inlineStr">
@@ -41196,7 +41196,7 @@
       <c r="AE352" t="inlineStr"/>
       <c r="AF352" t="inlineStr">
         <is>
-          <t>2026-05-14T02:33:19+00:00</t>
+          <t>2026-05-14T02:59:23+00:00</t>
         </is>
       </c>
       <c r="AG352" t="inlineStr">
@@ -41281,7 +41281,7 @@
       </c>
       <c r="AB353" t="inlineStr">
         <is>
-          <t>batch_04ef5ec3e6b54457</t>
+          <t>batch_976be391c94a4aae</t>
         </is>
       </c>
       <c r="AC353" t="inlineStr">
@@ -41297,7 +41297,7 @@
       <c r="AE353" t="inlineStr"/>
       <c r="AF353" t="inlineStr">
         <is>
-          <t>2026-05-14T02:33:19+00:00</t>
+          <t>2026-05-14T02:59:23+00:00</t>
         </is>
       </c>
       <c r="AG353" t="inlineStr">
@@ -41382,7 +41382,7 @@
       </c>
       <c r="AB354" t="inlineStr">
         <is>
-          <t>batch_04ef5ec3e6b54457</t>
+          <t>batch_976be391c94a4aae</t>
         </is>
       </c>
       <c r="AC354" t="inlineStr">
@@ -41398,7 +41398,7 @@
       <c r="AE354" t="inlineStr"/>
       <c r="AF354" t="inlineStr">
         <is>
-          <t>2026-05-14T02:33:19+00:00</t>
+          <t>2026-05-14T02:59:23+00:00</t>
         </is>
       </c>
       <c r="AG354" t="inlineStr">
@@ -41483,7 +41483,7 @@
       </c>
       <c r="AB355" t="inlineStr">
         <is>
-          <t>batch_04ef5ec3e6b54457</t>
+          <t>batch_976be391c94a4aae</t>
         </is>
       </c>
       <c r="AC355" t="inlineStr">
@@ -41499,7 +41499,7 @@
       <c r="AE355" t="inlineStr"/>
       <c r="AF355" t="inlineStr">
         <is>
-          <t>2026-05-14T02:33:19+00:00</t>
+          <t>2026-05-14T02:59:23+00:00</t>
         </is>
       </c>
       <c r="AG355" t="inlineStr">
@@ -41584,7 +41584,7 @@
       </c>
       <c r="AB356" t="inlineStr">
         <is>
-          <t>batch_04ef5ec3e6b54457</t>
+          <t>batch_976be391c94a4aae</t>
         </is>
       </c>
       <c r="AC356" t="inlineStr">
@@ -41600,7 +41600,7 @@
       <c r="AE356" t="inlineStr"/>
       <c r="AF356" t="inlineStr">
         <is>
-          <t>2026-05-14T02:33:19+00:00</t>
+          <t>2026-05-14T02:59:23+00:00</t>
         </is>
       </c>
       <c r="AG356" t="inlineStr">
@@ -41685,7 +41685,7 @@
       </c>
       <c r="AB357" t="inlineStr">
         <is>
-          <t>batch_04ef5ec3e6b54457</t>
+          <t>batch_976be391c94a4aae</t>
         </is>
       </c>
       <c r="AC357" t="inlineStr">
@@ -41701,7 +41701,7 @@
       <c r="AE357" t="inlineStr"/>
       <c r="AF357" t="inlineStr">
         <is>
-          <t>2026-05-14T02:33:19+00:00</t>
+          <t>2026-05-14T02:59:23+00:00</t>
         </is>
       </c>
       <c r="AG357" t="inlineStr">
@@ -41786,7 +41786,7 @@
       </c>
       <c r="AB358" t="inlineStr">
         <is>
-          <t>batch_04ef5ec3e6b54457</t>
+          <t>batch_976be391c94a4aae</t>
         </is>
       </c>
       <c r="AC358" t="inlineStr">
@@ -41802,7 +41802,7 @@
       <c r="AE358" t="inlineStr"/>
       <c r="AF358" t="inlineStr">
         <is>
-          <t>2026-05-14T02:33:19+00:00</t>
+          <t>2026-05-14T02:59:23+00:00</t>
         </is>
       </c>
       <c r="AG358" t="inlineStr">
@@ -41887,7 +41887,7 @@
       </c>
       <c r="AB359" t="inlineStr">
         <is>
-          <t>batch_04ef5ec3e6b54457</t>
+          <t>batch_976be391c94a4aae</t>
         </is>
       </c>
       <c r="AC359" t="inlineStr">
@@ -41903,7 +41903,7 @@
       <c r="AE359" t="inlineStr"/>
       <c r="AF359" t="inlineStr">
         <is>
-          <t>2026-05-14T02:33:19+00:00</t>
+          <t>2026-05-14T02:59:23+00:00</t>
         </is>
       </c>
       <c r="AG359" t="inlineStr">
@@ -41988,7 +41988,7 @@
       </c>
       <c r="AB360" t="inlineStr">
         <is>
-          <t>batch_04ef5ec3e6b54457</t>
+          <t>batch_976be391c94a4aae</t>
         </is>
       </c>
       <c r="AC360" t="inlineStr">
@@ -42004,7 +42004,7 @@
       <c r="AE360" t="inlineStr"/>
       <c r="AF360" t="inlineStr">
         <is>
-          <t>2026-05-14T02:33:19+00:00</t>
+          <t>2026-05-14T02:59:23+00:00</t>
         </is>
       </c>
       <c r="AG360" t="inlineStr">
@@ -42089,7 +42089,7 @@
       </c>
       <c r="AB361" t="inlineStr">
         <is>
-          <t>batch_04ef5ec3e6b54457</t>
+          <t>batch_976be391c94a4aae</t>
         </is>
       </c>
       <c r="AC361" t="inlineStr">
@@ -42105,7 +42105,7 @@
       <c r="AE361" t="inlineStr"/>
       <c r="AF361" t="inlineStr">
         <is>
-          <t>2026-05-14T02:33:19+00:00</t>
+          <t>2026-05-14T02:59:23+00:00</t>
         </is>
       </c>
       <c r="AG361" t="inlineStr">
@@ -42181,7 +42181,7 @@
       </c>
       <c r="AB362" t="inlineStr">
         <is>
-          <t>batch_04ef5ec3e6b54457</t>
+          <t>batch_976be391c94a4aae</t>
         </is>
       </c>
       <c r="AC362" t="inlineStr">
@@ -42197,7 +42197,7 @@
       <c r="AE362" t="inlineStr"/>
       <c r="AF362" t="inlineStr">
         <is>
-          <t>2026-05-14T02:33:19+00:00</t>
+          <t>2026-05-14T02:59:23+00:00</t>
         </is>
       </c>
       <c r="AG362" t="inlineStr">
@@ -42273,7 +42273,7 @@
       </c>
       <c r="AB363" t="inlineStr">
         <is>
-          <t>batch_04ef5ec3e6b54457</t>
+          <t>batch_976be391c94a4aae</t>
         </is>
       </c>
       <c r="AC363" t="inlineStr">
@@ -42289,7 +42289,7 @@
       <c r="AE363" t="inlineStr"/>
       <c r="AF363" t="inlineStr">
         <is>
-          <t>2026-05-14T02:33:19+00:00</t>
+          <t>2026-05-14T02:59:23+00:00</t>
         </is>
       </c>
       <c r="AG363" t="inlineStr">
@@ -42365,7 +42365,7 @@
       </c>
       <c r="AB364" t="inlineStr">
         <is>
-          <t>batch_04ef5ec3e6b54457</t>
+          <t>batch_976be391c94a4aae</t>
         </is>
       </c>
       <c r="AC364" t="inlineStr">
@@ -42381,7 +42381,7 @@
       <c r="AE364" t="inlineStr"/>
       <c r="AF364" t="inlineStr">
         <is>
-          <t>2026-05-14T02:33:19+00:00</t>
+          <t>2026-05-14T02:59:23+00:00</t>
         </is>
       </c>
       <c r="AG364" t="inlineStr">
@@ -42457,7 +42457,7 @@
       </c>
       <c r="AB365" t="inlineStr">
         <is>
-          <t>batch_04ef5ec3e6b54457</t>
+          <t>batch_976be391c94a4aae</t>
         </is>
       </c>
       <c r="AC365" t="inlineStr">
@@ -42473,7 +42473,7 @@
       <c r="AE365" t="inlineStr"/>
       <c r="AF365" t="inlineStr">
         <is>
-          <t>2026-05-14T02:33:19+00:00</t>
+          <t>2026-05-14T02:59:23+00:00</t>
         </is>
       </c>
       <c r="AG365" t="inlineStr">
@@ -42549,7 +42549,7 @@
       </c>
       <c r="AB366" t="inlineStr">
         <is>
-          <t>batch_04ef5ec3e6b54457</t>
+          <t>batch_976be391c94a4aae</t>
         </is>
       </c>
       <c r="AC366" t="inlineStr">
@@ -42565,7 +42565,7 @@
       <c r="AE366" t="inlineStr"/>
       <c r="AF366" t="inlineStr">
         <is>
-          <t>2026-05-14T02:33:19+00:00</t>
+          <t>2026-05-14T02:59:23+00:00</t>
         </is>
       </c>
       <c r="AG366" t="inlineStr">
@@ -42641,7 +42641,7 @@
       </c>
       <c r="AB367" t="inlineStr">
         <is>
-          <t>batch_04ef5ec3e6b54457</t>
+          <t>batch_976be391c94a4aae</t>
         </is>
       </c>
       <c r="AC367" t="inlineStr">
@@ -42657,7 +42657,7 @@
       <c r="AE367" t="inlineStr"/>
       <c r="AF367" t="inlineStr">
         <is>
-          <t>2026-05-14T02:33:19+00:00</t>
+          <t>2026-05-14T02:59:23+00:00</t>
         </is>
       </c>
       <c r="AG367" t="inlineStr">
@@ -42733,7 +42733,7 @@
       </c>
       <c r="AB368" t="inlineStr">
         <is>
-          <t>batch_04ef5ec3e6b54457</t>
+          <t>batch_976be391c94a4aae</t>
         </is>
       </c>
       <c r="AC368" t="inlineStr">
@@ -42749,7 +42749,7 @@
       <c r="AE368" t="inlineStr"/>
       <c r="AF368" t="inlineStr">
         <is>
-          <t>2026-05-14T02:33:19+00:00</t>
+          <t>2026-05-14T02:59:23+00:00</t>
         </is>
       </c>
       <c r="AG368" t="inlineStr">
@@ -42825,7 +42825,7 @@
       </c>
       <c r="AB369" t="inlineStr">
         <is>
-          <t>batch_04ef5ec3e6b54457</t>
+          <t>batch_976be391c94a4aae</t>
         </is>
       </c>
       <c r="AC369" t="inlineStr">
@@ -42841,7 +42841,7 @@
       <c r="AE369" t="inlineStr"/>
       <c r="AF369" t="inlineStr">
         <is>
-          <t>2026-05-14T02:33:19+00:00</t>
+          <t>2026-05-14T02:59:23+00:00</t>
         </is>
       </c>
       <c r="AG369" t="inlineStr">
@@ -42917,7 +42917,7 @@
       </c>
       <c r="AB370" t="inlineStr">
         <is>
-          <t>batch_04ef5ec3e6b54457</t>
+          <t>batch_976be391c94a4aae</t>
         </is>
       </c>
       <c r="AC370" t="inlineStr">
@@ -42933,7 +42933,7 @@
       <c r="AE370" t="inlineStr"/>
       <c r="AF370" t="inlineStr">
         <is>
-          <t>2026-05-14T02:33:19+00:00</t>
+          <t>2026-05-14T02:59:23+00:00</t>
         </is>
       </c>
       <c r="AG370" t="inlineStr">
@@ -43009,7 +43009,7 @@
       </c>
       <c r="AB371" t="inlineStr">
         <is>
-          <t>batch_04ef5ec3e6b54457</t>
+          <t>batch_976be391c94a4aae</t>
         </is>
       </c>
       <c r="AC371" t="inlineStr">
@@ -43025,7 +43025,7 @@
       <c r="AE371" t="inlineStr"/>
       <c r="AF371" t="inlineStr">
         <is>
-          <t>2026-05-14T02:33:19+00:00</t>
+          <t>2026-05-14T02:59:23+00:00</t>
         </is>
       </c>
       <c r="AG371" t="inlineStr">
@@ -43101,7 +43101,7 @@
       </c>
       <c r="AB372" t="inlineStr">
         <is>
-          <t>batch_04ef5ec3e6b54457</t>
+          <t>batch_976be391c94a4aae</t>
         </is>
       </c>
       <c r="AC372" t="inlineStr">
@@ -43117,7 +43117,7 @@
       <c r="AE372" t="inlineStr"/>
       <c r="AF372" t="inlineStr">
         <is>
-          <t>2026-05-14T02:33:19+00:00</t>
+          <t>2026-05-14T02:59:23+00:00</t>
         </is>
       </c>
       <c r="AG372" t="inlineStr">
@@ -44570,7 +44570,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Built 2026-05-14T02:47:34+00:00. Normalization version: v1.2.</t>
+          <t>Built 2026-05-14T02:59:23+00:00. Normalization version: v1.2.</t>
         </is>
       </c>
     </row>

--- a/services/costar/MASTER/COSTAR_MASTER_MERCADOS.xlsx
+++ b/services/costar/MASTER/COSTAR_MASTER_MERCADOS.xlsx
@@ -898,7 +898,7 @@
       </c>
       <c r="AT2" t="inlineStr">
         <is>
-          <t>batch_43847c5c0d554445</t>
+          <t>batch_0c2ed97284e04906</t>
         </is>
       </c>
       <c r="AU2" t="inlineStr">
@@ -914,7 +914,7 @@
       <c r="AW2" t="inlineStr"/>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>2026-05-14T03:06:34+00:00</t>
+          <t>2026-05-14T03:16:15+00:00</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
@@ -1044,7 +1044,7 @@
       </c>
       <c r="AT3" t="inlineStr">
         <is>
-          <t>batch_43847c5c0d554445</t>
+          <t>batch_0c2ed97284e04906</t>
         </is>
       </c>
       <c r="AU3" t="inlineStr">
@@ -1060,7 +1060,7 @@
       <c r="AW3" t="inlineStr"/>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>2026-05-14T03:06:34+00:00</t>
+          <t>2026-05-14T03:16:15+00:00</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">
@@ -1190,7 +1190,7 @@
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>batch_43847c5c0d554445</t>
+          <t>batch_0c2ed97284e04906</t>
         </is>
       </c>
       <c r="AU4" t="inlineStr">
@@ -1206,7 +1206,7 @@
       <c r="AW4" t="inlineStr"/>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>2026-05-14T03:06:34+00:00</t>
+          <t>2026-05-14T03:16:15+00:00</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">
@@ -1336,7 +1336,7 @@
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>batch_43847c5c0d554445</t>
+          <t>batch_0c2ed97284e04906</t>
         </is>
       </c>
       <c r="AU5" t="inlineStr">
@@ -1352,7 +1352,7 @@
       <c r="AW5" t="inlineStr"/>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>2026-05-14T03:06:34+00:00</t>
+          <t>2026-05-14T03:16:15+00:00</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr">
@@ -1482,7 +1482,7 @@
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>batch_43847c5c0d554445</t>
+          <t>batch_0c2ed97284e04906</t>
         </is>
       </c>
       <c r="AU6" t="inlineStr">
@@ -1498,7 +1498,7 @@
       <c r="AW6" t="inlineStr"/>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>2026-05-14T03:06:34+00:00</t>
+          <t>2026-05-14T03:16:15+00:00</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr">
@@ -1628,7 +1628,7 @@
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>batch_43847c5c0d554445</t>
+          <t>batch_0c2ed97284e04906</t>
         </is>
       </c>
       <c r="AU7" t="inlineStr">
@@ -1644,7 +1644,7 @@
       <c r="AW7" t="inlineStr"/>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>2026-05-14T03:06:34+00:00</t>
+          <t>2026-05-14T03:16:15+00:00</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr">
@@ -1720,7 +1720,7 @@
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>batch_43847c5c0d554445</t>
+          <t>batch_0c2ed97284e04906</t>
         </is>
       </c>
       <c r="AU8" t="inlineStr">
@@ -1736,7 +1736,7 @@
       <c r="AW8" t="inlineStr"/>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>2026-05-14T03:06:34+00:00</t>
+          <t>2026-05-14T03:16:15+00:00</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr">
@@ -1827,7 +1827,7 @@
       </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>batch_43847c5c0d554445</t>
+          <t>batch_0c2ed97284e04906</t>
         </is>
       </c>
       <c r="AU9" t="inlineStr">
@@ -1843,7 +1843,7 @@
       <c r="AW9" t="inlineStr"/>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>2026-05-14T03:06:34+00:00</t>
+          <t>2026-05-14T03:16:15+00:00</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr">
@@ -1934,7 +1934,7 @@
       </c>
       <c r="AT10" t="inlineStr">
         <is>
-          <t>batch_43847c5c0d554445</t>
+          <t>batch_0c2ed97284e04906</t>
         </is>
       </c>
       <c r="AU10" t="inlineStr">
@@ -1950,7 +1950,7 @@
       <c r="AW10" t="inlineStr"/>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>2026-05-14T03:06:34+00:00</t>
+          <t>2026-05-14T03:16:15+00:00</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr">
@@ -2041,7 +2041,7 @@
       </c>
       <c r="AT11" t="inlineStr">
         <is>
-          <t>batch_43847c5c0d554445</t>
+          <t>batch_0c2ed97284e04906</t>
         </is>
       </c>
       <c r="AU11" t="inlineStr">
@@ -2057,7 +2057,7 @@
       <c r="AW11" t="inlineStr"/>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>2026-05-14T03:06:34+00:00</t>
+          <t>2026-05-14T03:16:15+00:00</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr">
@@ -2148,7 +2148,7 @@
       </c>
       <c r="AT12" t="inlineStr">
         <is>
-          <t>batch_43847c5c0d554445</t>
+          <t>batch_0c2ed97284e04906</t>
         </is>
       </c>
       <c r="AU12" t="inlineStr">
@@ -2164,7 +2164,7 @@
       <c r="AW12" t="inlineStr"/>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>2026-05-14T03:06:34+00:00</t>
+          <t>2026-05-14T03:16:15+00:00</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr">
@@ -2255,7 +2255,7 @@
       </c>
       <c r="AT13" t="inlineStr">
         <is>
-          <t>batch_43847c5c0d554445</t>
+          <t>batch_0c2ed97284e04906</t>
         </is>
       </c>
       <c r="AU13" t="inlineStr">
@@ -2271,7 +2271,7 @@
       <c r="AW13" t="inlineStr"/>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>2026-05-14T03:06:34+00:00</t>
+          <t>2026-05-14T03:16:15+00:00</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr">
@@ -2362,7 +2362,7 @@
       </c>
       <c r="AT14" t="inlineStr">
         <is>
-          <t>batch_43847c5c0d554445</t>
+          <t>batch_0c2ed97284e04906</t>
         </is>
       </c>
       <c r="AU14" t="inlineStr">
@@ -2378,7 +2378,7 @@
       <c r="AW14" t="inlineStr"/>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>2026-05-14T03:06:34+00:00</t>
+          <t>2026-05-14T03:16:15+00:00</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr">
@@ -2469,7 +2469,7 @@
       </c>
       <c r="AT15" t="inlineStr">
         <is>
-          <t>batch_43847c5c0d554445</t>
+          <t>batch_0c2ed97284e04906</t>
         </is>
       </c>
       <c r="AU15" t="inlineStr">
@@ -2485,7 +2485,7 @@
       <c r="AW15" t="inlineStr"/>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>2026-05-14T03:06:34+00:00</t>
+          <t>2026-05-14T03:16:15+00:00</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr">
@@ -2576,7 +2576,7 @@
       </c>
       <c r="AT16" t="inlineStr">
         <is>
-          <t>batch_43847c5c0d554445</t>
+          <t>batch_0c2ed97284e04906</t>
         </is>
       </c>
       <c r="AU16" t="inlineStr">
@@ -2592,7 +2592,7 @@
       <c r="AW16" t="inlineStr"/>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>2026-05-14T03:06:34+00:00</t>
+          <t>2026-05-14T03:16:15+00:00</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr">
@@ -2745,7 +2745,7 @@
       </c>
       <c r="AT17" t="inlineStr">
         <is>
-          <t>batch_43847c5c0d554445</t>
+          <t>batch_0c2ed97284e04906</t>
         </is>
       </c>
       <c r="AU17" t="inlineStr">
@@ -2761,7 +2761,7 @@
       <c r="AW17" t="inlineStr"/>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>2026-05-14T03:06:34+00:00</t>
+          <t>2026-05-14T03:16:15+00:00</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr">
@@ -2914,7 +2914,7 @@
       </c>
       <c r="AT18" t="inlineStr">
         <is>
-          <t>batch_43847c5c0d554445</t>
+          <t>batch_0c2ed97284e04906</t>
         </is>
       </c>
       <c r="AU18" t="inlineStr">
@@ -2930,7 +2930,7 @@
       <c r="AW18" t="inlineStr"/>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>2026-05-14T03:06:34+00:00</t>
+          <t>2026-05-14T03:16:15+00:00</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr">
@@ -3083,7 +3083,7 @@
       </c>
       <c r="AT19" t="inlineStr">
         <is>
-          <t>batch_43847c5c0d554445</t>
+          <t>batch_0c2ed97284e04906</t>
         </is>
       </c>
       <c r="AU19" t="inlineStr">
@@ -3099,7 +3099,7 @@
       <c r="AW19" t="inlineStr"/>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>2026-05-14T03:06:34+00:00</t>
+          <t>2026-05-14T03:16:15+00:00</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr">
@@ -3252,7 +3252,7 @@
       </c>
       <c r="AT20" t="inlineStr">
         <is>
-          <t>batch_43847c5c0d554445</t>
+          <t>batch_0c2ed97284e04906</t>
         </is>
       </c>
       <c r="AU20" t="inlineStr">
@@ -3268,7 +3268,7 @@
       <c r="AW20" t="inlineStr"/>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>2026-05-14T03:06:34+00:00</t>
+          <t>2026-05-14T03:16:15+00:00</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr">
@@ -3421,7 +3421,7 @@
       </c>
       <c r="AT21" t="inlineStr">
         <is>
-          <t>batch_43847c5c0d554445</t>
+          <t>batch_0c2ed97284e04906</t>
         </is>
       </c>
       <c r="AU21" t="inlineStr">
@@ -3437,7 +3437,7 @@
       <c r="AW21" t="inlineStr"/>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>2026-05-14T03:06:34+00:00</t>
+          <t>2026-05-14T03:16:15+00:00</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr">
@@ -3590,7 +3590,7 @@
       </c>
       <c r="AT22" t="inlineStr">
         <is>
-          <t>batch_43847c5c0d554445</t>
+          <t>batch_0c2ed97284e04906</t>
         </is>
       </c>
       <c r="AU22" t="inlineStr">
@@ -3606,7 +3606,7 @@
       <c r="AW22" t="inlineStr"/>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>2026-05-14T03:06:34+00:00</t>
+          <t>2026-05-14T03:16:15+00:00</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr">
@@ -3759,7 +3759,7 @@
       </c>
       <c r="AT23" t="inlineStr">
         <is>
-          <t>batch_43847c5c0d554445</t>
+          <t>batch_0c2ed97284e04906</t>
         </is>
       </c>
       <c r="AU23" t="inlineStr">
@@ -3775,7 +3775,7 @@
       <c r="AW23" t="inlineStr"/>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>2026-05-14T03:06:34+00:00</t>
+          <t>2026-05-14T03:16:15+00:00</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr">
@@ -3928,7 +3928,7 @@
       </c>
       <c r="AT24" t="inlineStr">
         <is>
-          <t>batch_43847c5c0d554445</t>
+          <t>batch_0c2ed97284e04906</t>
         </is>
       </c>
       <c r="AU24" t="inlineStr">
@@ -3944,7 +3944,7 @@
       <c r="AW24" t="inlineStr"/>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>2026-05-14T03:06:34+00:00</t>
+          <t>2026-05-14T03:16:15+00:00</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr">
@@ -4097,7 +4097,7 @@
       </c>
       <c r="AT25" t="inlineStr">
         <is>
-          <t>batch_43847c5c0d554445</t>
+          <t>batch_0c2ed97284e04906</t>
         </is>
       </c>
       <c r="AU25" t="inlineStr">
@@ -4113,7 +4113,7 @@
       <c r="AW25" t="inlineStr"/>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>2026-05-14T03:06:34+00:00</t>
+          <t>2026-05-14T03:16:15+00:00</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr">
@@ -4266,7 +4266,7 @@
       </c>
       <c r="AT26" t="inlineStr">
         <is>
-          <t>batch_43847c5c0d554445</t>
+          <t>batch_0c2ed97284e04906</t>
         </is>
       </c>
       <c r="AU26" t="inlineStr">
@@ -4282,7 +4282,7 @@
       <c r="AW26" t="inlineStr"/>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>2026-05-14T03:06:34+00:00</t>
+          <t>2026-05-14T03:16:15+00:00</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr">
@@ -4435,7 +4435,7 @@
       </c>
       <c r="AT27" t="inlineStr">
         <is>
-          <t>batch_43847c5c0d554445</t>
+          <t>batch_0c2ed97284e04906</t>
         </is>
       </c>
       <c r="AU27" t="inlineStr">
@@ -4451,7 +4451,7 @@
       <c r="AW27" t="inlineStr"/>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>2026-05-14T03:06:34+00:00</t>
+          <t>2026-05-14T03:16:15+00:00</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr">
@@ -4604,7 +4604,7 @@
       </c>
       <c r="AT28" t="inlineStr">
         <is>
-          <t>batch_43847c5c0d554445</t>
+          <t>batch_0c2ed97284e04906</t>
         </is>
       </c>
       <c r="AU28" t="inlineStr">
@@ -4620,7 +4620,7 @@
       <c r="AW28" t="inlineStr"/>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>2026-05-14T03:06:34+00:00</t>
+          <t>2026-05-14T03:16:15+00:00</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr">
@@ -4773,7 +4773,7 @@
       </c>
       <c r="AT29" t="inlineStr">
         <is>
-          <t>batch_43847c5c0d554445</t>
+          <t>batch_0c2ed97284e04906</t>
         </is>
       </c>
       <c r="AU29" t="inlineStr">
@@ -4789,7 +4789,7 @@
       <c r="AW29" t="inlineStr"/>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>2026-05-14T03:06:34+00:00</t>
+          <t>2026-05-14T03:16:15+00:00</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr">
@@ -4942,7 +4942,7 @@
       </c>
       <c r="AT30" t="inlineStr">
         <is>
-          <t>batch_43847c5c0d554445</t>
+          <t>batch_0c2ed97284e04906</t>
         </is>
       </c>
       <c r="AU30" t="inlineStr">
@@ -4958,7 +4958,7 @@
       <c r="AW30" t="inlineStr"/>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>2026-05-14T03:06:34+00:00</t>
+          <t>2026-05-14T03:16:15+00:00</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr">
@@ -5111,7 +5111,7 @@
       </c>
       <c r="AT31" t="inlineStr">
         <is>
-          <t>batch_43847c5c0d554445</t>
+          <t>batch_0c2ed97284e04906</t>
         </is>
       </c>
       <c r="AU31" t="inlineStr">
@@ -5127,7 +5127,7 @@
       <c r="AW31" t="inlineStr"/>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>2026-05-14T03:06:34+00:00</t>
+          <t>2026-05-14T03:16:15+00:00</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr">
@@ -5280,7 +5280,7 @@
       </c>
       <c r="AT32" t="inlineStr">
         <is>
-          <t>batch_43847c5c0d554445</t>
+          <t>batch_0c2ed97284e04906</t>
         </is>
       </c>
       <c r="AU32" t="inlineStr">
@@ -5296,7 +5296,7 @@
       <c r="AW32" t="inlineStr"/>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>2026-05-14T03:06:34+00:00</t>
+          <t>2026-05-14T03:16:15+00:00</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr">
@@ -5449,7 +5449,7 @@
       </c>
       <c r="AT33" t="inlineStr">
         <is>
-          <t>batch_43847c5c0d554445</t>
+          <t>batch_0c2ed97284e04906</t>
         </is>
       </c>
       <c r="AU33" t="inlineStr">
@@ -5465,7 +5465,7 @@
       <c r="AW33" t="inlineStr"/>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>2026-05-14T03:06:34+00:00</t>
+          <t>2026-05-14T03:16:15+00:00</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr">
@@ -5618,7 +5618,7 @@
       </c>
       <c r="AT34" t="inlineStr">
         <is>
-          <t>batch_43847c5c0d554445</t>
+          <t>batch_0c2ed97284e04906</t>
         </is>
       </c>
       <c r="AU34" t="inlineStr">
@@ -5634,7 +5634,7 @@
       <c r="AW34" t="inlineStr"/>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>2026-05-14T03:06:34+00:00</t>
+          <t>2026-05-14T03:16:15+00:00</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr">
@@ -5787,7 +5787,7 @@
       </c>
       <c r="AT35" t="inlineStr">
         <is>
-          <t>batch_43847c5c0d554445</t>
+          <t>batch_0c2ed97284e04906</t>
         </is>
       </c>
       <c r="AU35" t="inlineStr">
@@ -5803,7 +5803,7 @@
       <c r="AW35" t="inlineStr"/>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>2026-05-14T03:06:34+00:00</t>
+          <t>2026-05-14T03:16:15+00:00</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr">
@@ -5956,7 +5956,7 @@
       </c>
       <c r="AT36" t="inlineStr">
         <is>
-          <t>batch_43847c5c0d554445</t>
+          <t>batch_0c2ed97284e04906</t>
         </is>
       </c>
       <c r="AU36" t="inlineStr">
@@ -5972,7 +5972,7 @@
       <c r="AW36" t="inlineStr"/>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>2026-05-14T03:06:34+00:00</t>
+          <t>2026-05-14T03:16:15+00:00</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr">
@@ -6125,7 +6125,7 @@
       </c>
       <c r="AT37" t="inlineStr">
         <is>
-          <t>batch_43847c5c0d554445</t>
+          <t>batch_0c2ed97284e04906</t>
         </is>
       </c>
       <c r="AU37" t="inlineStr">
@@ -6141,7 +6141,7 @@
       <c r="AW37" t="inlineStr"/>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>2026-05-14T03:06:34+00:00</t>
+          <t>2026-05-14T03:16:15+00:00</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr">
@@ -6294,7 +6294,7 @@
       </c>
       <c r="AT38" t="inlineStr">
         <is>
-          <t>batch_43847c5c0d554445</t>
+          <t>batch_0c2ed97284e04906</t>
         </is>
       </c>
       <c r="AU38" t="inlineStr">
@@ -6310,7 +6310,7 @@
       <c r="AW38" t="inlineStr"/>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>2026-05-14T03:06:34+00:00</t>
+          <t>2026-05-14T03:16:15+00:00</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr">
@@ -6463,7 +6463,7 @@
       </c>
       <c r="AT39" t="inlineStr">
         <is>
-          <t>batch_43847c5c0d554445</t>
+          <t>batch_0c2ed97284e04906</t>
         </is>
       </c>
       <c r="AU39" t="inlineStr">
@@ -6479,7 +6479,7 @@
       <c r="AW39" t="inlineStr"/>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>2026-05-14T03:06:34+00:00</t>
+          <t>2026-05-14T03:16:15+00:00</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr">
@@ -6632,7 +6632,7 @@
       </c>
       <c r="AT40" t="inlineStr">
         <is>
-          <t>batch_43847c5c0d554445</t>
+          <t>batch_0c2ed97284e04906</t>
         </is>
       </c>
       <c r="AU40" t="inlineStr">
@@ -6648,7 +6648,7 @@
       <c r="AW40" t="inlineStr"/>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>2026-05-14T03:06:34+00:00</t>
+          <t>2026-05-14T03:16:15+00:00</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr">
@@ -6801,7 +6801,7 @@
       </c>
       <c r="AT41" t="inlineStr">
         <is>
-          <t>batch_43847c5c0d554445</t>
+          <t>batch_0c2ed97284e04906</t>
         </is>
       </c>
       <c r="AU41" t="inlineStr">
@@ -6817,7 +6817,7 @@
       <c r="AW41" t="inlineStr"/>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>2026-05-14T03:06:34+00:00</t>
+          <t>2026-05-14T03:16:15+00:00</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr">
@@ -6970,7 +6970,7 @@
       </c>
       <c r="AT42" t="inlineStr">
         <is>
-          <t>batch_43847c5c0d554445</t>
+          <t>batch_0c2ed97284e04906</t>
         </is>
       </c>
       <c r="AU42" t="inlineStr">
@@ -6986,7 +6986,7 @@
       <c r="AW42" t="inlineStr"/>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>2026-05-14T03:06:34+00:00</t>
+          <t>2026-05-14T03:16:15+00:00</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr">
@@ -7139,7 +7139,7 @@
       </c>
       <c r="AT43" t="inlineStr">
         <is>
-          <t>batch_43847c5c0d554445</t>
+          <t>batch_0c2ed97284e04906</t>
         </is>
       </c>
       <c r="AU43" t="inlineStr">
@@ -7155,7 +7155,7 @@
       <c r="AW43" t="inlineStr"/>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>2026-05-14T03:06:34+00:00</t>
+          <t>2026-05-14T03:16:15+00:00</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr">
@@ -7308,7 +7308,7 @@
       </c>
       <c r="AT44" t="inlineStr">
         <is>
-          <t>batch_43847c5c0d554445</t>
+          <t>batch_0c2ed97284e04906</t>
         </is>
       </c>
       <c r="AU44" t="inlineStr">
@@ -7324,7 +7324,7 @@
       <c r="AW44" t="inlineStr"/>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>2026-05-14T03:06:34+00:00</t>
+          <t>2026-05-14T03:16:15+00:00</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr">
@@ -7477,7 +7477,7 @@
       </c>
       <c r="AT45" t="inlineStr">
         <is>
-          <t>batch_43847c5c0d554445</t>
+          <t>batch_0c2ed97284e04906</t>
         </is>
       </c>
       <c r="AU45" t="inlineStr">
@@ -7493,7 +7493,7 @@
       <c r="AW45" t="inlineStr"/>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>2026-05-14T03:06:34+00:00</t>
+          <t>2026-05-14T03:16:15+00:00</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr">
@@ -7646,7 +7646,7 @@
       </c>
       <c r="AT46" t="inlineStr">
         <is>
-          <t>batch_43847c5c0d554445</t>
+          <t>batch_0c2ed97284e04906</t>
         </is>
       </c>
       <c r="AU46" t="inlineStr">
@@ -7662,7 +7662,7 @@
       <c r="AW46" t="inlineStr"/>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>2026-05-14T03:06:34+00:00</t>
+          <t>2026-05-14T03:16:15+00:00</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr">
@@ -7815,7 +7815,7 @@
       </c>
       <c r="AT47" t="inlineStr">
         <is>
-          <t>batch_43847c5c0d554445</t>
+          <t>batch_0c2ed97284e04906</t>
         </is>
       </c>
       <c r="AU47" t="inlineStr">
@@ -7831,7 +7831,7 @@
       <c r="AW47" t="inlineStr"/>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>2026-05-14T03:06:34+00:00</t>
+          <t>2026-05-14T03:16:15+00:00</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr">
@@ -7984,7 +7984,7 @@
       </c>
       <c r="AT48" t="inlineStr">
         <is>
-          <t>batch_43847c5c0d554445</t>
+          <t>batch_0c2ed97284e04906</t>
         </is>
       </c>
       <c r="AU48" t="inlineStr">
@@ -8000,7 +8000,7 @@
       <c r="AW48" t="inlineStr"/>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>2026-05-14T03:06:34+00:00</t>
+          <t>2026-05-14T03:16:15+00:00</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr">
@@ -8153,7 +8153,7 @@
       </c>
       <c r="AT49" t="inlineStr">
         <is>
-          <t>batch_43847c5c0d554445</t>
+          <t>batch_0c2ed97284e04906</t>
         </is>
       </c>
       <c r="AU49" t="inlineStr">
@@ -8169,7 +8169,7 @@
       <c r="AW49" t="inlineStr"/>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>2026-05-14T03:06:34+00:00</t>
+          <t>2026-05-14T03:16:15+00:00</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr">
@@ -8322,7 +8322,7 @@
       </c>
       <c r="AT50" t="inlineStr">
         <is>
-          <t>batch_43847c5c0d554445</t>
+          <t>batch_0c2ed97284e04906</t>
         </is>
       </c>
       <c r="AU50" t="inlineStr">
@@ -8338,7 +8338,7 @@
       <c r="AW50" t="inlineStr"/>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>2026-05-14T03:06:34+00:00</t>
+          <t>2026-05-14T03:16:15+00:00</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr">
@@ -8491,7 +8491,7 @@
       </c>
       <c r="AT51" t="inlineStr">
         <is>
-          <t>batch_43847c5c0d554445</t>
+          <t>batch_0c2ed97284e04906</t>
         </is>
       </c>
       <c r="AU51" t="inlineStr">
@@ -8507,7 +8507,7 @@
       <c r="AW51" t="inlineStr"/>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>2026-05-14T03:06:34+00:00</t>
+          <t>2026-05-14T03:16:15+00:00</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr">
@@ -8660,7 +8660,7 @@
       </c>
       <c r="AT52" t="inlineStr">
         <is>
-          <t>batch_43847c5c0d554445</t>
+          <t>batch_0c2ed97284e04906</t>
         </is>
       </c>
       <c r="AU52" t="inlineStr">
@@ -8676,7 +8676,7 @@
       <c r="AW52" t="inlineStr"/>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>2026-05-14T03:06:34+00:00</t>
+          <t>2026-05-14T03:16:15+00:00</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr">
@@ -8829,7 +8829,7 @@
       </c>
       <c r="AT53" t="inlineStr">
         <is>
-          <t>batch_43847c5c0d554445</t>
+          <t>batch_0c2ed97284e04906</t>
         </is>
       </c>
       <c r="AU53" t="inlineStr">
@@ -8845,7 +8845,7 @@
       <c r="AW53" t="inlineStr"/>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>2026-05-14T03:06:34+00:00</t>
+          <t>2026-05-14T03:16:15+00:00</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr">
@@ -8998,7 +8998,7 @@
       </c>
       <c r="AT54" t="inlineStr">
         <is>
-          <t>batch_43847c5c0d554445</t>
+          <t>batch_0c2ed97284e04906</t>
         </is>
       </c>
       <c r="AU54" t="inlineStr">
@@ -9014,7 +9014,7 @@
       <c r="AW54" t="inlineStr"/>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>2026-05-14T03:06:34+00:00</t>
+          <t>2026-05-14T03:16:15+00:00</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr">
@@ -9167,7 +9167,7 @@
       </c>
       <c r="AT55" t="inlineStr">
         <is>
-          <t>batch_43847c5c0d554445</t>
+          <t>batch_0c2ed97284e04906</t>
         </is>
       </c>
       <c r="AU55" t="inlineStr">
@@ -9183,7 +9183,7 @@
       <c r="AW55" t="inlineStr"/>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>2026-05-14T03:06:34+00:00</t>
+          <t>2026-05-14T03:16:15+00:00</t>
         </is>
       </c>
       <c r="AY55" t="inlineStr">
@@ -9336,7 +9336,7 @@
       </c>
       <c r="AT56" t="inlineStr">
         <is>
-          <t>batch_43847c5c0d554445</t>
+          <t>batch_0c2ed97284e04906</t>
         </is>
       </c>
       <c r="AU56" t="inlineStr">
@@ -9352,7 +9352,7 @@
       <c r="AW56" t="inlineStr"/>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>2026-05-14T03:06:34+00:00</t>
+          <t>2026-05-14T03:16:15+00:00</t>
         </is>
       </c>
       <c r="AY56" t="inlineStr">
@@ -9505,7 +9505,7 @@
       </c>
       <c r="AT57" t="inlineStr">
         <is>
-          <t>batch_43847c5c0d554445</t>
+          <t>batch_0c2ed97284e04906</t>
         </is>
       </c>
       <c r="AU57" t="inlineStr">
@@ -9521,7 +9521,7 @@
       <c r="AW57" t="inlineStr"/>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>2026-05-14T03:06:34+00:00</t>
+          <t>2026-05-14T03:16:15+00:00</t>
         </is>
       </c>
       <c r="AY57" t="inlineStr">
@@ -9674,7 +9674,7 @@
       </c>
       <c r="AT58" t="inlineStr">
         <is>
-          <t>batch_43847c5c0d554445</t>
+          <t>batch_0c2ed97284e04906</t>
         </is>
       </c>
       <c r="AU58" t="inlineStr">
@@ -9690,7 +9690,7 @@
       <c r="AW58" t="inlineStr"/>
       <c r="AX58" t="inlineStr">
         <is>
-          <t>2026-05-14T03:06:34+00:00</t>
+          <t>2026-05-14T03:16:15+00:00</t>
         </is>
       </c>
       <c r="AY58" t="inlineStr">
@@ -9843,7 +9843,7 @@
       </c>
       <c r="AT59" t="inlineStr">
         <is>
-          <t>batch_43847c5c0d554445</t>
+          <t>batch_0c2ed97284e04906</t>
         </is>
       </c>
       <c r="AU59" t="inlineStr">
@@ -9859,7 +9859,7 @@
       <c r="AW59" t="inlineStr"/>
       <c r="AX59" t="inlineStr">
         <is>
-          <t>2026-05-14T03:06:34+00:00</t>
+          <t>2026-05-14T03:16:15+00:00</t>
         </is>
       </c>
       <c r="AY59" t="inlineStr">
@@ -10012,7 +10012,7 @@
       </c>
       <c r="AT60" t="inlineStr">
         <is>
-          <t>batch_43847c5c0d554445</t>
+          <t>batch_0c2ed97284e04906</t>
         </is>
       </c>
       <c r="AU60" t="inlineStr">
@@ -10028,7 +10028,7 @@
       <c r="AW60" t="inlineStr"/>
       <c r="AX60" t="inlineStr">
         <is>
-          <t>2026-05-14T03:06:34+00:00</t>
+          <t>2026-05-14T03:16:15+00:00</t>
         </is>
       </c>
       <c r="AY60" t="inlineStr">
@@ -10181,7 +10181,7 @@
       </c>
       <c r="AT61" t="inlineStr">
         <is>
-          <t>batch_43847c5c0d554445</t>
+          <t>batch_0c2ed97284e04906</t>
         </is>
       </c>
       <c r="AU61" t="inlineStr">
@@ -10197,7 +10197,7 @@
       <c r="AW61" t="inlineStr"/>
       <c r="AX61" t="inlineStr">
         <is>
-          <t>2026-05-14T03:06:34+00:00</t>
+          <t>2026-05-14T03:16:15+00:00</t>
         </is>
       </c>
       <c r="AY61" t="inlineStr">
@@ -10350,7 +10350,7 @@
       </c>
       <c r="AT62" t="inlineStr">
         <is>
-          <t>batch_43847c5c0d554445</t>
+          <t>batch_0c2ed97284e04906</t>
         </is>
       </c>
       <c r="AU62" t="inlineStr">
@@ -10366,7 +10366,7 @@
       <c r="AW62" t="inlineStr"/>
       <c r="AX62" t="inlineStr">
         <is>
-          <t>2026-05-14T03:06:34+00:00</t>
+          <t>2026-05-14T03:16:15+00:00</t>
         </is>
       </c>
       <c r="AY62" t="inlineStr">
@@ -10519,7 +10519,7 @@
       </c>
       <c r="AT63" t="inlineStr">
         <is>
-          <t>batch_43847c5c0d554445</t>
+          <t>batch_0c2ed97284e04906</t>
         </is>
       </c>
       <c r="AU63" t="inlineStr">
@@ -10535,7 +10535,7 @@
       <c r="AW63" t="inlineStr"/>
       <c r="AX63" t="inlineStr">
         <is>
-          <t>2026-05-14T03:06:34+00:00</t>
+          <t>2026-05-14T03:16:15+00:00</t>
         </is>
       </c>
       <c r="AY63" t="inlineStr">
@@ -10688,7 +10688,7 @@
       </c>
       <c r="AT64" t="inlineStr">
         <is>
-          <t>batch_43847c5c0d554445</t>
+          <t>batch_0c2ed97284e04906</t>
         </is>
       </c>
       <c r="AU64" t="inlineStr">
@@ -10704,7 +10704,7 @@
       <c r="AW64" t="inlineStr"/>
       <c r="AX64" t="inlineStr">
         <is>
-          <t>2026-05-14T03:06:34+00:00</t>
+          <t>2026-05-14T03:16:15+00:00</t>
         </is>
       </c>
       <c r="AY64" t="inlineStr">
@@ -10857,7 +10857,7 @@
       </c>
       <c r="AT65" t="inlineStr">
         <is>
-          <t>batch_43847c5c0d554445</t>
+          <t>batch_0c2ed97284e04906</t>
         </is>
       </c>
       <c r="AU65" t="inlineStr">
@@ -10873,7 +10873,7 @@
       <c r="AW65" t="inlineStr"/>
       <c r="AX65" t="inlineStr">
         <is>
-          <t>2026-05-14T03:06:34+00:00</t>
+          <t>2026-05-14T03:16:15+00:00</t>
         </is>
       </c>
       <c r="AY65" t="inlineStr">
@@ -11026,7 +11026,7 @@
       </c>
       <c r="AT66" t="inlineStr">
         <is>
-          <t>batch_43847c5c0d554445</t>
+          <t>batch_0c2ed97284e04906</t>
         </is>
       </c>
       <c r="AU66" t="inlineStr">
@@ -11042,7 +11042,7 @@
       <c r="AW66" t="inlineStr"/>
       <c r="AX66" t="inlineStr">
         <is>
-          <t>2026-05-14T03:06:34+00:00</t>
+          <t>2026-05-14T03:16:15+00:00</t>
         </is>
       </c>
       <c r="AY66" t="inlineStr">
@@ -11195,7 +11195,7 @@
       </c>
       <c r="AT67" t="inlineStr">
         <is>
-          <t>batch_43847c5c0d554445</t>
+          <t>batch_0c2ed97284e04906</t>
         </is>
       </c>
       <c r="AU67" t="inlineStr">
@@ -11211,7 +11211,7 @@
       <c r="AW67" t="inlineStr"/>
       <c r="AX67" t="inlineStr">
         <is>
-          <t>2026-05-14T03:06:34+00:00</t>
+          <t>2026-05-14T03:16:15+00:00</t>
         </is>
       </c>
       <c r="AY67" t="inlineStr">
@@ -11364,7 +11364,7 @@
       </c>
       <c r="AT68" t="inlineStr">
         <is>
-          <t>batch_43847c5c0d554445</t>
+          <t>batch_0c2ed97284e04906</t>
         </is>
       </c>
       <c r="AU68" t="inlineStr">
@@ -11380,7 +11380,7 @@
       <c r="AW68" t="inlineStr"/>
       <c r="AX68" t="inlineStr">
         <is>
-          <t>2026-05-14T03:06:34+00:00</t>
+          <t>2026-05-14T03:16:15+00:00</t>
         </is>
       </c>
       <c r="AY68" t="inlineStr">
@@ -11533,7 +11533,7 @@
       </c>
       <c r="AT69" t="inlineStr">
         <is>
-          <t>batch_43847c5c0d554445</t>
+          <t>batch_0c2ed97284e04906</t>
         </is>
       </c>
       <c r="AU69" t="inlineStr">
@@ -11549,7 +11549,7 @@
       <c r="AW69" t="inlineStr"/>
       <c r="AX69" t="inlineStr">
         <is>
-          <t>2026-05-14T03:06:34+00:00</t>
+          <t>2026-05-14T03:16:15+00:00</t>
         </is>
       </c>
       <c r="AY69" t="inlineStr">
@@ -11702,7 +11702,7 @@
       </c>
       <c r="AT70" t="inlineStr">
         <is>
-          <t>batch_43847c5c0d554445</t>
+          <t>batch_0c2ed97284e04906</t>
         </is>
       </c>
       <c r="AU70" t="inlineStr">
@@ -11718,7 +11718,7 @@
       <c r="AW70" t="inlineStr"/>
       <c r="AX70" t="inlineStr">
         <is>
-          <t>2026-05-14T03:06:34+00:00</t>
+          <t>2026-05-14T03:16:15+00:00</t>
         </is>
       </c>
       <c r="AY70" t="inlineStr">
@@ -11871,7 +11871,7 @@
       </c>
       <c r="AT71" t="inlineStr">
         <is>
-          <t>batch_43847c5c0d554445</t>
+          <t>batch_0c2ed97284e04906</t>
         </is>
       </c>
       <c r="AU71" t="inlineStr">
@@ -11887,7 +11887,7 @@
       <c r="AW71" t="inlineStr"/>
       <c r="AX71" t="inlineStr">
         <is>
-          <t>2026-05-14T03:06:34+00:00</t>
+          <t>2026-05-14T03:16:15+00:00</t>
         </is>
       </c>
       <c r="AY71" t="inlineStr">
@@ -12040,7 +12040,7 @@
       </c>
       <c r="AT72" t="inlineStr">
         <is>
-          <t>batch_43847c5c0d554445</t>
+          <t>batch_0c2ed97284e04906</t>
         </is>
       </c>
       <c r="AU72" t="inlineStr">
@@ -12056,7 +12056,7 @@
       <c r="AW72" t="inlineStr"/>
       <c r="AX72" t="inlineStr">
         <is>
-          <t>2026-05-14T03:06:34+00:00</t>
+          <t>2026-05-14T03:16:15+00:00</t>
         </is>
       </c>
       <c r="AY72" t="inlineStr">
@@ -12209,7 +12209,7 @@
       </c>
       <c r="AT73" t="inlineStr">
         <is>
-          <t>batch_43847c5c0d554445</t>
+          <t>batch_0c2ed97284e04906</t>
         </is>
       </c>
       <c r="AU73" t="inlineStr">
@@ -12225,7 +12225,7 @@
       <c r="AW73" t="inlineStr"/>
       <c r="AX73" t="inlineStr">
         <is>
-          <t>2026-05-14T03:06:34+00:00</t>
+          <t>2026-05-14T03:16:15+00:00</t>
         </is>
       </c>
       <c r="AY73" t="inlineStr">
@@ -12378,7 +12378,7 @@
       </c>
       <c r="AT74" t="inlineStr">
         <is>
-          <t>batch_43847c5c0d554445</t>
+          <t>batch_0c2ed97284e04906</t>
         </is>
       </c>
       <c r="AU74" t="inlineStr">
@@ -12394,7 +12394,7 @@
       <c r="AW74" t="inlineStr"/>
       <c r="AX74" t="inlineStr">
         <is>
-          <t>2026-05-14T03:06:34+00:00</t>
+          <t>2026-05-14T03:16:15+00:00</t>
         </is>
       </c>
       <c r="AY74" t="inlineStr">
@@ -12547,7 +12547,7 @@
       </c>
       <c r="AT75" t="inlineStr">
         <is>
-          <t>batch_43847c5c0d554445</t>
+          <t>batch_0c2ed97284e04906</t>
         </is>
       </c>
       <c r="AU75" t="inlineStr">
@@ -12563,7 +12563,7 @@
       <c r="AW75" t="inlineStr"/>
       <c r="AX75" t="inlineStr">
         <is>
-          <t>2026-05-14T03:06:34+00:00</t>
+          <t>2026-05-14T03:16:15+00:00</t>
         </is>
       </c>
       <c r="AY75" t="inlineStr">
@@ -12716,7 +12716,7 @@
       </c>
       <c r="AT76" t="inlineStr">
         <is>
-          <t>batch_43847c5c0d554445</t>
+          <t>batch_0c2ed97284e04906</t>
         </is>
       </c>
       <c r="AU76" t="inlineStr">
@@ -12732,7 +12732,7 @@
       <c r="AW76" t="inlineStr"/>
       <c r="AX76" t="inlineStr">
         <is>
-          <t>2026-05-14T03:06:34+00:00</t>
+          <t>2026-05-14T03:16:15+00:00</t>
         </is>
       </c>
       <c r="AY76" t="inlineStr">
@@ -12885,7 +12885,7 @@
       </c>
       <c r="AT77" t="inlineStr">
         <is>
-          <t>batch_43847c5c0d554445</t>
+          <t>batch_0c2ed97284e04906</t>
         </is>
       </c>
       <c r="AU77" t="inlineStr">
@@ -12901,7 +12901,7 @@
       <c r="AW77" t="inlineStr"/>
       <c r="AX77" t="inlineStr">
         <is>
-          <t>2026-05-14T03:06:34+00:00</t>
+          <t>2026-05-14T03:16:15+00:00</t>
         </is>
       </c>
       <c r="AY77" t="inlineStr">
@@ -13054,7 +13054,7 @@
       </c>
       <c r="AT78" t="inlineStr">
         <is>
-          <t>batch_43847c5c0d554445</t>
+          <t>batch_0c2ed97284e04906</t>
         </is>
       </c>
       <c r="AU78" t="inlineStr">
@@ -13070,7 +13070,7 @@
       <c r="AW78" t="inlineStr"/>
       <c r="AX78" t="inlineStr">
         <is>
-          <t>2026-05-14T03:06:34+00:00</t>
+          <t>2026-05-14T03:16:15+00:00</t>
         </is>
       </c>
       <c r="AY78" t="inlineStr">
@@ -13223,7 +13223,7 @@
       </c>
       <c r="AT79" t="inlineStr">
         <is>
-          <t>batch_43847c5c0d554445</t>
+          <t>batch_0c2ed97284e04906</t>
         </is>
       </c>
       <c r="AU79" t="inlineStr">
@@ -13239,7 +13239,7 @@
       <c r="AW79" t="inlineStr"/>
       <c r="AX79" t="inlineStr">
         <is>
-          <t>2026-05-14T03:06:34+00:00</t>
+          <t>2026-05-14T03:16:15+00:00</t>
         </is>
       </c>
       <c r="AY79" t="inlineStr">
@@ -13392,7 +13392,7 @@
       </c>
       <c r="AT80" t="inlineStr">
         <is>
-          <t>batch_43847c5c0d554445</t>
+          <t>batch_0c2ed97284e04906</t>
         </is>
       </c>
       <c r="AU80" t="inlineStr">
@@ -13408,7 +13408,7 @@
       <c r="AW80" t="inlineStr"/>
       <c r="AX80" t="inlineStr">
         <is>
-          <t>2026-05-14T03:06:34+00:00</t>
+          <t>2026-05-14T03:16:15+00:00</t>
         </is>
       </c>
       <c r="AY80" t="inlineStr">
@@ -13561,7 +13561,7 @@
       </c>
       <c r="AT81" t="inlineStr">
         <is>
-          <t>batch_43847c5c0d554445</t>
+          <t>batch_0c2ed97284e04906</t>
         </is>
       </c>
       <c r="AU81" t="inlineStr">
@@ -13577,7 +13577,7 @@
       <c r="AW81" t="inlineStr"/>
       <c r="AX81" t="inlineStr">
         <is>
-          <t>2026-05-14T03:06:34+00:00</t>
+          <t>2026-05-14T03:16:15+00:00</t>
         </is>
       </c>
       <c r="AY81" t="inlineStr">
@@ -13730,7 +13730,7 @@
       </c>
       <c r="AT82" t="inlineStr">
         <is>
-          <t>batch_43847c5c0d554445</t>
+          <t>batch_0c2ed97284e04906</t>
         </is>
       </c>
       <c r="AU82" t="inlineStr">
@@ -13746,7 +13746,7 @@
       <c r="AW82" t="inlineStr"/>
       <c r="AX82" t="inlineStr">
         <is>
-          <t>2026-05-14T03:06:34+00:00</t>
+          <t>2026-05-14T03:16:15+00:00</t>
         </is>
       </c>
       <c r="AY82" t="inlineStr">
@@ -13899,7 +13899,7 @@
       </c>
       <c r="AT83" t="inlineStr">
         <is>
-          <t>batch_43847c5c0d554445</t>
+          <t>batch_0c2ed97284e04906</t>
         </is>
       </c>
       <c r="AU83" t="inlineStr">
@@ -13915,7 +13915,7 @@
       <c r="AW83" t="inlineStr"/>
       <c r="AX83" t="inlineStr">
         <is>
-          <t>2026-05-14T03:06:34+00:00</t>
+          <t>2026-05-14T03:16:15+00:00</t>
         </is>
       </c>
       <c r="AY83" t="inlineStr">
@@ -14068,7 +14068,7 @@
       </c>
       <c r="AT84" t="inlineStr">
         <is>
-          <t>batch_43847c5c0d554445</t>
+          <t>batch_0c2ed97284e04906</t>
         </is>
       </c>
       <c r="AU84" t="inlineStr">
@@ -14084,7 +14084,7 @@
       <c r="AW84" t="inlineStr"/>
       <c r="AX84" t="inlineStr">
         <is>
-          <t>2026-05-14T03:06:34+00:00</t>
+          <t>2026-05-14T03:16:15+00:00</t>
         </is>
       </c>
       <c r="AY84" t="inlineStr">
@@ -14237,7 +14237,7 @@
       </c>
       <c r="AT85" t="inlineStr">
         <is>
-          <t>batch_43847c5c0d554445</t>
+          <t>batch_0c2ed97284e04906</t>
         </is>
       </c>
       <c r="AU85" t="inlineStr">
@@ -14253,7 +14253,7 @@
       <c r="AW85" t="inlineStr"/>
       <c r="AX85" t="inlineStr">
         <is>
-          <t>2026-05-14T03:06:34+00:00</t>
+          <t>2026-05-14T03:16:15+00:00</t>
         </is>
       </c>
       <c r="AY85" t="inlineStr">
@@ -14406,7 +14406,7 @@
       </c>
       <c r="AT86" t="inlineStr">
         <is>
-          <t>batch_43847c5c0d554445</t>
+          <t>batch_0c2ed97284e04906</t>
         </is>
       </c>
       <c r="AU86" t="inlineStr">
@@ -14422,7 +14422,7 @@
       <c r="AW86" t="inlineStr"/>
       <c r="AX86" t="inlineStr">
         <is>
-          <t>2026-05-14T03:06:34+00:00</t>
+          <t>2026-05-14T03:16:15+00:00</t>
         </is>
       </c>
       <c r="AY86" t="inlineStr">
@@ -14575,7 +14575,7 @@
       </c>
       <c r="AT87" t="inlineStr">
         <is>
-          <t>batch_43847c5c0d554445</t>
+          <t>batch_0c2ed97284e04906</t>
         </is>
       </c>
       <c r="AU87" t="inlineStr">
@@ -14591,7 +14591,7 @@
       <c r="AW87" t="inlineStr"/>
       <c r="AX87" t="inlineStr">
         <is>
-          <t>2026-05-14T03:06:34+00:00</t>
+          <t>2026-05-14T03:16:15+00:00</t>
         </is>
       </c>
       <c r="AY87" t="inlineStr">
@@ -14744,7 +14744,7 @@
       </c>
       <c r="AT88" t="inlineStr">
         <is>
-          <t>batch_43847c5c0d554445</t>
+          <t>batch_0c2ed97284e04906</t>
         </is>
       </c>
       <c r="AU88" t="inlineStr">
@@ -14760,7 +14760,7 @@
       <c r="AW88" t="inlineStr"/>
       <c r="AX88" t="inlineStr">
         <is>
-          <t>2026-05-14T03:06:34+00:00</t>
+          <t>2026-05-14T03:16:15+00:00</t>
         </is>
       </c>
       <c r="AY88" t="inlineStr">
@@ -14913,7 +14913,7 @@
       </c>
       <c r="AT89" t="inlineStr">
         <is>
-          <t>batch_43847c5c0d554445</t>
+          <t>batch_0c2ed97284e04906</t>
         </is>
       </c>
       <c r="AU89" t="inlineStr">
@@ -14929,7 +14929,7 @@
       <c r="AW89" t="inlineStr"/>
       <c r="AX89" t="inlineStr">
         <is>
-          <t>2026-05-14T03:06:34+00:00</t>
+          <t>2026-05-14T03:16:15+00:00</t>
         </is>
       </c>
       <c r="AY89" t="inlineStr">
@@ -15082,7 +15082,7 @@
       </c>
       <c r="AT90" t="inlineStr">
         <is>
-          <t>batch_43847c5c0d554445</t>
+          <t>batch_0c2ed97284e04906</t>
         </is>
       </c>
       <c r="AU90" t="inlineStr">
@@ -15098,7 +15098,7 @@
       <c r="AW90" t="inlineStr"/>
       <c r="AX90" t="inlineStr">
         <is>
-          <t>2026-05-14T03:06:34+00:00</t>
+          <t>2026-05-14T03:16:15+00:00</t>
         </is>
       </c>
       <c r="AY90" t="inlineStr">
@@ -15251,7 +15251,7 @@
       </c>
       <c r="AT91" t="inlineStr">
         <is>
-          <t>batch_43847c5c0d554445</t>
+          <t>batch_0c2ed97284e04906</t>
         </is>
       </c>
       <c r="AU91" t="inlineStr">
@@ -15267,7 +15267,7 @@
       <c r="AW91" t="inlineStr"/>
       <c r="AX91" t="inlineStr">
         <is>
-          <t>2026-05-14T03:06:34+00:00</t>
+          <t>2026-05-14T03:16:15+00:00</t>
         </is>
       </c>
       <c r="AY91" t="inlineStr">
@@ -15420,7 +15420,7 @@
       </c>
       <c r="AT92" t="inlineStr">
         <is>
-          <t>batch_43847c5c0d554445</t>
+          <t>batch_0c2ed97284e04906</t>
         </is>
       </c>
       <c r="AU92" t="inlineStr">
@@ -15436,7 +15436,7 @@
       <c r="AW92" t="inlineStr"/>
       <c r="AX92" t="inlineStr">
         <is>
-          <t>2026-05-14T03:06:34+00:00</t>
+          <t>2026-05-14T03:16:15+00:00</t>
         </is>
       </c>
       <c r="AY92" t="inlineStr">
@@ -15589,7 +15589,7 @@
       </c>
       <c r="AT93" t="inlineStr">
         <is>
-          <t>batch_43847c5c0d554445</t>
+          <t>batch_0c2ed97284e04906</t>
         </is>
       </c>
       <c r="AU93" t="inlineStr">
@@ -15605,7 +15605,7 @@
       <c r="AW93" t="inlineStr"/>
       <c r="AX93" t="inlineStr">
         <is>
-          <t>2026-05-14T03:06:34+00:00</t>
+          <t>2026-05-14T03:16:15+00:00</t>
         </is>
       </c>
       <c r="AY93" t="inlineStr">
@@ -15758,7 +15758,7 @@
       </c>
       <c r="AT94" t="inlineStr">
         <is>
-          <t>batch_43847c5c0d554445</t>
+          <t>batch_0c2ed97284e04906</t>
         </is>
       </c>
       <c r="AU94" t="inlineStr">
@@ -15774,7 +15774,7 @@
       <c r="AW94" t="inlineStr"/>
       <c r="AX94" t="inlineStr">
         <is>
-          <t>2026-05-14T03:06:34+00:00</t>
+          <t>2026-05-14T03:16:15+00:00</t>
         </is>
       </c>
       <c r="AY94" t="inlineStr">
@@ -15927,7 +15927,7 @@
       </c>
       <c r="AT95" t="inlineStr">
         <is>
-          <t>batch_43847c5c0d554445</t>
+          <t>batch_0c2ed97284e04906</t>
         </is>
       </c>
       <c r="AU95" t="inlineStr">
@@ -15943,7 +15943,7 @@
       <c r="AW95" t="inlineStr"/>
       <c r="AX95" t="inlineStr">
         <is>
-          <t>2026-05-14T03:06:34+00:00</t>
+          <t>2026-05-14T03:16:15+00:00</t>
         </is>
       </c>
       <c r="AY95" t="inlineStr">
@@ -16096,7 +16096,7 @@
       </c>
       <c r="AT96" t="inlineStr">
         <is>
-          <t>batch_43847c5c0d554445</t>
+          <t>batch_0c2ed97284e04906</t>
         </is>
       </c>
       <c r="AU96" t="inlineStr">
@@ -16112,7 +16112,7 @@
       <c r="AW96" t="inlineStr"/>
       <c r="AX96" t="inlineStr">
         <is>
-          <t>2026-05-14T03:06:34+00:00</t>
+          <t>2026-05-14T03:16:15+00:00</t>
         </is>
       </c>
       <c r="AY96" t="inlineStr">
@@ -16265,7 +16265,7 @@
       </c>
       <c r="AT97" t="inlineStr">
         <is>
-          <t>batch_43847c5c0d554445</t>
+          <t>batch_0c2ed97284e04906</t>
         </is>
       </c>
       <c r="AU97" t="inlineStr">
@@ -16281,7 +16281,7 @@
       <c r="AW97" t="inlineStr"/>
       <c r="AX97" t="inlineStr">
         <is>
-          <t>2026-05-14T03:06:34+00:00</t>
+          <t>2026-05-14T03:16:15+00:00</t>
         </is>
       </c>
       <c r="AY97" t="inlineStr">
@@ -16434,7 +16434,7 @@
       </c>
       <c r="AT98" t="inlineStr">
         <is>
-          <t>batch_43847c5c0d554445</t>
+          <t>batch_0c2ed97284e04906</t>
         </is>
       </c>
       <c r="AU98" t="inlineStr">
@@ -16450,7 +16450,7 @@
       <c r="AW98" t="inlineStr"/>
       <c r="AX98" t="inlineStr">
         <is>
-          <t>2026-05-14T03:06:34+00:00</t>
+          <t>2026-05-14T03:16:15+00:00</t>
         </is>
       </c>
       <c r="AY98" t="inlineStr">
@@ -16594,7 +16594,7 @@
       </c>
       <c r="AT99" t="inlineStr">
         <is>
-          <t>batch_43847c5c0d554445</t>
+          <t>batch_0c2ed97284e04906</t>
         </is>
       </c>
       <c r="AU99" t="inlineStr">
@@ -16610,7 +16610,7 @@
       <c r="AW99" t="inlineStr"/>
       <c r="AX99" t="inlineStr">
         <is>
-          <t>2026-05-14T03:06:34+00:00</t>
+          <t>2026-05-14T03:16:15+00:00</t>
         </is>
       </c>
       <c r="AY99" t="inlineStr">
@@ -16754,7 +16754,7 @@
       </c>
       <c r="AT100" t="inlineStr">
         <is>
-          <t>batch_43847c5c0d554445</t>
+          <t>batch_0c2ed97284e04906</t>
         </is>
       </c>
       <c r="AU100" t="inlineStr">
@@ -16770,7 +16770,7 @@
       <c r="AW100" t="inlineStr"/>
       <c r="AX100" t="inlineStr">
         <is>
-          <t>2026-05-14T03:06:34+00:00</t>
+          <t>2026-05-14T03:16:15+00:00</t>
         </is>
       </c>
       <c r="AY100" t="inlineStr">
@@ -16914,7 +16914,7 @@
       </c>
       <c r="AT101" t="inlineStr">
         <is>
-          <t>batch_43847c5c0d554445</t>
+          <t>batch_0c2ed97284e04906</t>
         </is>
       </c>
       <c r="AU101" t="inlineStr">
@@ -16930,7 +16930,7 @@
       <c r="AW101" t="inlineStr"/>
       <c r="AX101" t="inlineStr">
         <is>
-          <t>2026-05-14T03:06:34+00:00</t>
+          <t>2026-05-14T03:16:15+00:00</t>
         </is>
       </c>
       <c r="AY101" t="inlineStr">
@@ -17074,7 +17074,7 @@
       </c>
       <c r="AT102" t="inlineStr">
         <is>
-          <t>batch_43847c5c0d554445</t>
+          <t>batch_0c2ed97284e04906</t>
         </is>
       </c>
       <c r="AU102" t="inlineStr">
@@ -17090,7 +17090,7 @@
       <c r="AW102" t="inlineStr"/>
       <c r="AX102" t="inlineStr">
         <is>
-          <t>2026-05-14T03:06:34+00:00</t>
+          <t>2026-05-14T03:16:15+00:00</t>
         </is>
       </c>
       <c r="AY102" t="inlineStr">
@@ -17234,7 +17234,7 @@
       </c>
       <c r="AT103" t="inlineStr">
         <is>
-          <t>batch_43847c5c0d554445</t>
+          <t>batch_0c2ed97284e04906</t>
         </is>
       </c>
       <c r="AU103" t="inlineStr">
@@ -17250,7 +17250,7 @@
       <c r="AW103" t="inlineStr"/>
       <c r="AX103" t="inlineStr">
         <is>
-          <t>2026-05-14T03:06:34+00:00</t>
+          <t>2026-05-14T03:16:15+00:00</t>
         </is>
       </c>
       <c r="AY103" t="inlineStr">
@@ -17394,7 +17394,7 @@
       </c>
       <c r="AT104" t="inlineStr">
         <is>
-          <t>batch_43847c5c0d554445</t>
+          <t>batch_0c2ed97284e04906</t>
         </is>
       </c>
       <c r="AU104" t="inlineStr">
@@ -17410,7 +17410,7 @@
       <c r="AW104" t="inlineStr"/>
       <c r="AX104" t="inlineStr">
         <is>
-          <t>2026-05-14T03:06:34+00:00</t>
+          <t>2026-05-14T03:16:15+00:00</t>
         </is>
       </c>
       <c r="AY104" t="inlineStr">
@@ -17563,7 +17563,7 @@
       </c>
       <c r="AT105" t="inlineStr">
         <is>
-          <t>batch_43847c5c0d554445</t>
+          <t>batch_0c2ed97284e04906</t>
         </is>
       </c>
       <c r="AU105" t="inlineStr">
@@ -17579,7 +17579,7 @@
       <c r="AW105" t="inlineStr"/>
       <c r="AX105" t="inlineStr">
         <is>
-          <t>2026-05-14T03:06:34+00:00</t>
+          <t>2026-05-14T03:16:15+00:00</t>
         </is>
       </c>
       <c r="AY105" t="inlineStr">
@@ -17720,7 +17720,7 @@
       </c>
       <c r="AT106" t="inlineStr">
         <is>
-          <t>batch_43847c5c0d554445</t>
+          <t>batch_0c2ed97284e04906</t>
         </is>
       </c>
       <c r="AU106" t="inlineStr">
@@ -17736,7 +17736,7 @@
       <c r="AW106" t="inlineStr"/>
       <c r="AX106" t="inlineStr">
         <is>
-          <t>2026-05-14T03:06:34+00:00</t>
+          <t>2026-05-14T03:16:15+00:00</t>
         </is>
       </c>
       <c r="AY106" t="inlineStr">
@@ -17877,7 +17877,7 @@
       </c>
       <c r="AT107" t="inlineStr">
         <is>
-          <t>batch_43847c5c0d554445</t>
+          <t>batch_0c2ed97284e04906</t>
         </is>
       </c>
       <c r="AU107" t="inlineStr">
@@ -17893,7 +17893,7 @@
       <c r="AW107" t="inlineStr"/>
       <c r="AX107" t="inlineStr">
         <is>
-          <t>2026-05-14T03:06:34+00:00</t>
+          <t>2026-05-14T03:16:15+00:00</t>
         </is>
       </c>
       <c r="AY107" t="inlineStr">
@@ -18034,7 +18034,7 @@
       </c>
       <c r="AT108" t="inlineStr">
         <is>
-          <t>batch_43847c5c0d554445</t>
+          <t>batch_0c2ed97284e04906</t>
         </is>
       </c>
       <c r="AU108" t="inlineStr">
@@ -18050,7 +18050,7 @@
       <c r="AW108" t="inlineStr"/>
       <c r="AX108" t="inlineStr">
         <is>
-          <t>2026-05-14T03:06:34+00:00</t>
+          <t>2026-05-14T03:16:15+00:00</t>
         </is>
       </c>
       <c r="AY108" t="inlineStr">
@@ -18194,7 +18194,7 @@
       </c>
       <c r="AT109" t="inlineStr">
         <is>
-          <t>batch_43847c5c0d554445</t>
+          <t>batch_0c2ed97284e04906</t>
         </is>
       </c>
       <c r="AU109" t="inlineStr">
@@ -18210,7 +18210,7 @@
       <c r="AW109" t="inlineStr"/>
       <c r="AX109" t="inlineStr">
         <is>
-          <t>2026-05-14T03:06:34+00:00</t>
+          <t>2026-05-14T03:16:15+00:00</t>
         </is>
       </c>
       <c r="AY109" t="inlineStr">
@@ -18354,7 +18354,7 @@
       </c>
       <c r="AT110" t="inlineStr">
         <is>
-          <t>batch_43847c5c0d554445</t>
+          <t>batch_0c2ed97284e04906</t>
         </is>
       </c>
       <c r="AU110" t="inlineStr">
@@ -18370,7 +18370,7 @@
       <c r="AW110" t="inlineStr"/>
       <c r="AX110" t="inlineStr">
         <is>
-          <t>2026-05-14T03:06:34+00:00</t>
+          <t>2026-05-14T03:16:15+00:00</t>
         </is>
       </c>
       <c r="AY110" t="inlineStr">
@@ -18514,7 +18514,7 @@
       </c>
       <c r="AT111" t="inlineStr">
         <is>
-          <t>batch_43847c5c0d554445</t>
+          <t>batch_0c2ed97284e04906</t>
         </is>
       </c>
       <c r="AU111" t="inlineStr">
@@ -18530,7 +18530,7 @@
       <c r="AW111" t="inlineStr"/>
       <c r="AX111" t="inlineStr">
         <is>
-          <t>2026-05-14T03:06:34+00:00</t>
+          <t>2026-05-14T03:16:15+00:00</t>
         </is>
       </c>
       <c r="AY111" t="inlineStr">
@@ -18674,7 +18674,7 @@
       </c>
       <c r="AT112" t="inlineStr">
         <is>
-          <t>batch_43847c5c0d554445</t>
+          <t>batch_0c2ed97284e04906</t>
         </is>
       </c>
       <c r="AU112" t="inlineStr">
@@ -18690,7 +18690,7 @@
       <c r="AW112" t="inlineStr"/>
       <c r="AX112" t="inlineStr">
         <is>
-          <t>2026-05-14T03:06:34+00:00</t>
+          <t>2026-05-14T03:16:15+00:00</t>
         </is>
       </c>
       <c r="AY112" t="inlineStr">
@@ -18834,7 +18834,7 @@
       </c>
       <c r="AT113" t="inlineStr">
         <is>
-          <t>batch_43847c5c0d554445</t>
+          <t>batch_0c2ed97284e04906</t>
         </is>
       </c>
       <c r="AU113" t="inlineStr">
@@ -18850,7 +18850,7 @@
       <c r="AW113" t="inlineStr"/>
       <c r="AX113" t="inlineStr">
         <is>
-          <t>2026-05-14T03:06:34+00:00</t>
+          <t>2026-05-14T03:16:15+00:00</t>
         </is>
       </c>
       <c r="AY113" t="inlineStr">
@@ -18994,7 +18994,7 @@
       </c>
       <c r="AT114" t="inlineStr">
         <is>
-          <t>batch_43847c5c0d554445</t>
+          <t>batch_0c2ed97284e04906</t>
         </is>
       </c>
       <c r="AU114" t="inlineStr">
@@ -19010,7 +19010,7 @@
       <c r="AW114" t="inlineStr"/>
       <c r="AX114" t="inlineStr">
         <is>
-          <t>2026-05-14T03:06:34+00:00</t>
+          <t>2026-05-14T03:16:15+00:00</t>
         </is>
       </c>
       <c r="AY114" t="inlineStr">
@@ -19154,7 +19154,7 @@
       </c>
       <c r="AT115" t="inlineStr">
         <is>
-          <t>batch_43847c5c0d554445</t>
+          <t>batch_0c2ed97284e04906</t>
         </is>
       </c>
       <c r="AU115" t="inlineStr">
@@ -19170,7 +19170,7 @@
       <c r="AW115" t="inlineStr"/>
       <c r="AX115" t="inlineStr">
         <is>
-          <t>2026-05-14T03:06:34+00:00</t>
+          <t>2026-05-14T03:16:15+00:00</t>
         </is>
       </c>
       <c r="AY115" t="inlineStr">
@@ -19314,7 +19314,7 @@
       </c>
       <c r="AT116" t="inlineStr">
         <is>
-          <t>batch_43847c5c0d554445</t>
+          <t>batch_0c2ed97284e04906</t>
         </is>
       </c>
       <c r="AU116" t="inlineStr">
@@ -19330,7 +19330,7 @@
       <c r="AW116" t="inlineStr"/>
       <c r="AX116" t="inlineStr">
         <is>
-          <t>2026-05-14T03:06:34+00:00</t>
+          <t>2026-05-14T03:16:15+00:00</t>
         </is>
       </c>
       <c r="AY116" t="inlineStr">
@@ -19474,7 +19474,7 @@
       </c>
       <c r="AT117" t="inlineStr">
         <is>
-          <t>batch_43847c5c0d554445</t>
+          <t>batch_0c2ed97284e04906</t>
         </is>
       </c>
       <c r="AU117" t="inlineStr">
@@ -19490,7 +19490,7 @@
       <c r="AW117" t="inlineStr"/>
       <c r="AX117" t="inlineStr">
         <is>
-          <t>2026-05-14T03:06:34+00:00</t>
+          <t>2026-05-14T03:16:15+00:00</t>
         </is>
       </c>
       <c r="AY117" t="inlineStr">
@@ -19634,7 +19634,7 @@
       </c>
       <c r="AT118" t="inlineStr">
         <is>
-          <t>batch_43847c5c0d554445</t>
+          <t>batch_0c2ed97284e04906</t>
         </is>
       </c>
       <c r="AU118" t="inlineStr">
@@ -19650,7 +19650,7 @@
       <c r="AW118" t="inlineStr"/>
       <c r="AX118" t="inlineStr">
         <is>
-          <t>2026-05-14T03:06:34+00:00</t>
+          <t>2026-05-14T03:16:15+00:00</t>
         </is>
       </c>
       <c r="AY118" t="inlineStr">
@@ -19794,7 +19794,7 @@
       </c>
       <c r="AT119" t="inlineStr">
         <is>
-          <t>batch_43847c5c0d554445</t>
+          <t>batch_0c2ed97284e04906</t>
         </is>
       </c>
       <c r="AU119" t="inlineStr">
@@ -19810,7 +19810,7 @@
       <c r="AW119" t="inlineStr"/>
       <c r="AX119" t="inlineStr">
         <is>
-          <t>2026-05-14T03:06:34+00:00</t>
+          <t>2026-05-14T03:16:15+00:00</t>
         </is>
       </c>
       <c r="AY119" t="inlineStr">
@@ -19954,7 +19954,7 @@
       </c>
       <c r="AT120" t="inlineStr">
         <is>
-          <t>batch_43847c5c0d554445</t>
+          <t>batch_0c2ed97284e04906</t>
         </is>
       </c>
       <c r="AU120" t="inlineStr">
@@ -19970,7 +19970,7 @@
       <c r="AW120" t="inlineStr"/>
       <c r="AX120" t="inlineStr">
         <is>
-          <t>2026-05-14T03:06:34+00:00</t>
+          <t>2026-05-14T03:16:15+00:00</t>
         </is>
       </c>
       <c r="AY120" t="inlineStr">
@@ -20114,7 +20114,7 @@
       </c>
       <c r="AT121" t="inlineStr">
         <is>
-          <t>batch_43847c5c0d554445</t>
+          <t>batch_0c2ed97284e04906</t>
         </is>
       </c>
       <c r="AU121" t="inlineStr">
@@ -20130,7 +20130,7 @@
       <c r="AW121" t="inlineStr"/>
       <c r="AX121" t="inlineStr">
         <is>
-          <t>2026-05-14T03:06:34+00:00</t>
+          <t>2026-05-14T03:16:15+00:00</t>
         </is>
       </c>
       <c r="AY121" t="inlineStr">
@@ -20274,7 +20274,7 @@
       </c>
       <c r="AT122" t="inlineStr">
         <is>
-          <t>batch_43847c5c0d554445</t>
+          <t>batch_0c2ed97284e04906</t>
         </is>
       </c>
       <c r="AU122" t="inlineStr">
@@ -20290,7 +20290,7 @@
       <c r="AW122" t="inlineStr"/>
       <c r="AX122" t="inlineStr">
         <is>
-          <t>2026-05-14T03:06:34+00:00</t>
+          <t>2026-05-14T03:16:15+00:00</t>
         </is>
       </c>
       <c r="AY122" t="inlineStr">
@@ -20434,7 +20434,7 @@
       </c>
       <c r="AT123" t="inlineStr">
         <is>
-          <t>batch_43847c5c0d554445</t>
+          <t>batch_0c2ed97284e04906</t>
         </is>
       </c>
       <c r="AU123" t="inlineStr">
@@ -20450,7 +20450,7 @@
       <c r="AW123" t="inlineStr"/>
       <c r="AX123" t="inlineStr">
         <is>
-          <t>2026-05-14T03:06:34+00:00</t>
+          <t>2026-05-14T03:16:15+00:00</t>
         </is>
       </c>
       <c r="AY123" t="inlineStr">
@@ -20594,7 +20594,7 @@
       </c>
       <c r="AT124" t="inlineStr">
         <is>
-          <t>batch_43847c5c0d554445</t>
+          <t>batch_0c2ed97284e04906</t>
         </is>
       </c>
       <c r="AU124" t="inlineStr">
@@ -20610,7 +20610,7 @@
       <c r="AW124" t="inlineStr"/>
       <c r="AX124" t="inlineStr">
         <is>
-          <t>2026-05-14T03:06:34+00:00</t>
+          <t>2026-05-14T03:16:15+00:00</t>
         </is>
       </c>
       <c r="AY124" t="inlineStr">
@@ -20754,7 +20754,7 @@
       </c>
       <c r="AT125" t="inlineStr">
         <is>
-          <t>batch_43847c5c0d554445</t>
+          <t>batch_0c2ed97284e04906</t>
         </is>
       </c>
       <c r="AU125" t="inlineStr">
@@ -20770,7 +20770,7 @@
       <c r="AW125" t="inlineStr"/>
       <c r="AX125" t="inlineStr">
         <is>
-          <t>2026-05-14T03:06:34+00:00</t>
+          <t>2026-05-14T03:16:15+00:00</t>
         </is>
       </c>
       <c r="AY125" t="inlineStr">
@@ -20914,7 +20914,7 @@
       </c>
       <c r="AT126" t="inlineStr">
         <is>
-          <t>batch_43847c5c0d554445</t>
+          <t>batch_0c2ed97284e04906</t>
         </is>
       </c>
       <c r="AU126" t="inlineStr">
@@ -20930,7 +20930,7 @@
       <c r="AW126" t="inlineStr"/>
       <c r="AX126" t="inlineStr">
         <is>
-          <t>2026-05-14T03:06:34+00:00</t>
+          <t>2026-05-14T03:16:15+00:00</t>
         </is>
       </c>
       <c r="AY126" t="inlineStr">
@@ -21074,7 +21074,7 @@
       </c>
       <c r="AT127" t="inlineStr">
         <is>
-          <t>batch_43847c5c0d554445</t>
+          <t>batch_0c2ed97284e04906</t>
         </is>
       </c>
       <c r="AU127" t="inlineStr">
@@ -21090,7 +21090,7 @@
       <c r="AW127" t="inlineStr"/>
       <c r="AX127" t="inlineStr">
         <is>
-          <t>2026-05-14T03:06:34+00:00</t>
+          <t>2026-05-14T03:16:15+00:00</t>
         </is>
       </c>
       <c r="AY127" t="inlineStr">
@@ -21234,7 +21234,7 @@
       </c>
       <c r="AT128" t="inlineStr">
         <is>
-          <t>batch_43847c5c0d554445</t>
+          <t>batch_0c2ed97284e04906</t>
         </is>
       </c>
       <c r="AU128" t="inlineStr">
@@ -21250,7 +21250,7 @@
       <c r="AW128" t="inlineStr"/>
       <c r="AX128" t="inlineStr">
         <is>
-          <t>2026-05-14T03:06:34+00:00</t>
+          <t>2026-05-14T03:16:15+00:00</t>
         </is>
       </c>
       <c r="AY128" t="inlineStr">
@@ -21394,7 +21394,7 @@
       </c>
       <c r="AT129" t="inlineStr">
         <is>
-          <t>batch_43847c5c0d554445</t>
+          <t>batch_0c2ed97284e04906</t>
         </is>
       </c>
       <c r="AU129" t="inlineStr">
@@ -21410,7 +21410,7 @@
       <c r="AW129" t="inlineStr"/>
       <c r="AX129" t="inlineStr">
         <is>
-          <t>2026-05-14T03:06:34+00:00</t>
+          <t>2026-05-14T03:16:15+00:00</t>
         </is>
       </c>
       <c r="AY129" t="inlineStr">
@@ -21554,7 +21554,7 @@
       </c>
       <c r="AT130" t="inlineStr">
         <is>
-          <t>batch_43847c5c0d554445</t>
+          <t>batch_0c2ed97284e04906</t>
         </is>
       </c>
       <c r="AU130" t="inlineStr">
@@ -21570,7 +21570,7 @@
       <c r="AW130" t="inlineStr"/>
       <c r="AX130" t="inlineStr">
         <is>
-          <t>2026-05-14T03:06:34+00:00</t>
+          <t>2026-05-14T03:16:15+00:00</t>
         </is>
       </c>
       <c r="AY130" t="inlineStr">
@@ -21714,7 +21714,7 @@
       </c>
       <c r="AT131" t="inlineStr">
         <is>
-          <t>batch_43847c5c0d554445</t>
+          <t>batch_0c2ed97284e04906</t>
         </is>
       </c>
       <c r="AU131" t="inlineStr">
@@ -21730,7 +21730,7 @@
       <c r="AW131" t="inlineStr"/>
       <c r="AX131" t="inlineStr">
         <is>
-          <t>2026-05-14T03:06:34+00:00</t>
+          <t>2026-05-14T03:16:15+00:00</t>
         </is>
       </c>
       <c r="AY131" t="inlineStr">
@@ -21874,7 +21874,7 @@
       </c>
       <c r="AT132" t="inlineStr">
         <is>
-          <t>batch_43847c5c0d554445</t>
+          <t>batch_0c2ed97284e04906</t>
         </is>
       </c>
       <c r="AU132" t="inlineStr">
@@ -21890,7 +21890,7 @@
       <c r="AW132" t="inlineStr"/>
       <c r="AX132" t="inlineStr">
         <is>
-          <t>2026-05-14T03:06:34+00:00</t>
+          <t>2026-05-14T03:16:15+00:00</t>
         </is>
       </c>
       <c r="AY132" t="inlineStr">
@@ -22034,7 +22034,7 @@
       </c>
       <c r="AT133" t="inlineStr">
         <is>
-          <t>batch_43847c5c0d554445</t>
+          <t>batch_0c2ed97284e04906</t>
         </is>
       </c>
       <c r="AU133" t="inlineStr">
@@ -22050,7 +22050,7 @@
       <c r="AW133" t="inlineStr"/>
       <c r="AX133" t="inlineStr">
         <is>
-          <t>2026-05-14T03:06:34+00:00</t>
+          <t>2026-05-14T03:16:15+00:00</t>
         </is>
       </c>
       <c r="AY133" t="inlineStr">
@@ -22194,7 +22194,7 @@
       </c>
       <c r="AT134" t="inlineStr">
         <is>
-          <t>batch_43847c5c0d554445</t>
+          <t>batch_0c2ed97284e04906</t>
         </is>
       </c>
       <c r="AU134" t="inlineStr">
@@ -22210,7 +22210,7 @@
       <c r="AW134" t="inlineStr"/>
       <c r="AX134" t="inlineStr">
         <is>
-          <t>2026-05-14T03:06:34+00:00</t>
+          <t>2026-05-14T03:16:15+00:00</t>
         </is>
       </c>
       <c r="AY134" t="inlineStr">
@@ -22354,7 +22354,7 @@
       </c>
       <c r="AT135" t="inlineStr">
         <is>
-          <t>batch_43847c5c0d554445</t>
+          <t>batch_0c2ed97284e04906</t>
         </is>
       </c>
       <c r="AU135" t="inlineStr">
@@ -22370,7 +22370,7 @@
       <c r="AW135" t="inlineStr"/>
       <c r="AX135" t="inlineStr">
         <is>
-          <t>2026-05-14T03:06:34+00:00</t>
+          <t>2026-05-14T03:16:15+00:00</t>
         </is>
       </c>
       <c r="AY135" t="inlineStr">
@@ -22514,7 +22514,7 @@
       </c>
       <c r="AT136" t="inlineStr">
         <is>
-          <t>batch_43847c5c0d554445</t>
+          <t>batch_0c2ed97284e04906</t>
         </is>
       </c>
       <c r="AU136" t="inlineStr">
@@ -22530,7 +22530,7 @@
       <c r="AW136" t="inlineStr"/>
       <c r="AX136" t="inlineStr">
         <is>
-          <t>2026-05-14T03:06:34+00:00</t>
+          <t>2026-05-14T03:16:15+00:00</t>
         </is>
       </c>
       <c r="AY136" t="inlineStr">
@@ -22674,7 +22674,7 @@
       </c>
       <c r="AT137" t="inlineStr">
         <is>
-          <t>batch_43847c5c0d554445</t>
+          <t>batch_0c2ed97284e04906</t>
         </is>
       </c>
       <c r="AU137" t="inlineStr">
@@ -22690,7 +22690,7 @@
       <c r="AW137" t="inlineStr"/>
       <c r="AX137" t="inlineStr">
         <is>
-          <t>2026-05-14T03:06:34+00:00</t>
+          <t>2026-05-14T03:16:15+00:00</t>
         </is>
       </c>
       <c r="AY137" t="inlineStr">
@@ -22834,7 +22834,7 @@
       </c>
       <c r="AT138" t="inlineStr">
         <is>
-          <t>batch_43847c5c0d554445</t>
+          <t>batch_0c2ed97284e04906</t>
         </is>
       </c>
       <c r="AU138" t="inlineStr">
@@ -22850,7 +22850,7 @@
       <c r="AW138" t="inlineStr"/>
       <c r="AX138" t="inlineStr">
         <is>
-          <t>2026-05-14T03:06:34+00:00</t>
+          <t>2026-05-14T03:16:15+00:00</t>
         </is>
       </c>
       <c r="AY138" t="inlineStr">
@@ -22994,7 +22994,7 @@
       </c>
       <c r="AT139" t="inlineStr">
         <is>
-          <t>batch_43847c5c0d554445</t>
+          <t>batch_0c2ed97284e04906</t>
         </is>
       </c>
       <c r="AU139" t="inlineStr">
@@ -23010,7 +23010,7 @@
       <c r="AW139" t="inlineStr"/>
       <c r="AX139" t="inlineStr">
         <is>
-          <t>2026-05-14T03:06:34+00:00</t>
+          <t>2026-05-14T03:16:15+00:00</t>
         </is>
       </c>
       <c r="AY139" t="inlineStr">
@@ -23154,7 +23154,7 @@
       </c>
       <c r="AT140" t="inlineStr">
         <is>
-          <t>batch_43847c5c0d554445</t>
+          <t>batch_0c2ed97284e04906</t>
         </is>
       </c>
       <c r="AU140" t="inlineStr">
@@ -23170,7 +23170,7 @@
       <c r="AW140" t="inlineStr"/>
       <c r="AX140" t="inlineStr">
         <is>
-          <t>2026-05-14T03:06:34+00:00</t>
+          <t>2026-05-14T03:16:15+00:00</t>
         </is>
       </c>
       <c r="AY140" t="inlineStr">
@@ -23314,7 +23314,7 @@
       </c>
       <c r="AT141" t="inlineStr">
         <is>
-          <t>batch_43847c5c0d554445</t>
+          <t>batch_0c2ed97284e04906</t>
         </is>
       </c>
       <c r="AU141" t="inlineStr">
@@ -23330,7 +23330,7 @@
       <c r="AW141" t="inlineStr"/>
       <c r="AX141" t="inlineStr">
         <is>
-          <t>2026-05-14T03:06:34+00:00</t>
+          <t>2026-05-14T03:16:15+00:00</t>
         </is>
       </c>
       <c r="AY141" t="inlineStr">
@@ -23474,7 +23474,7 @@
       </c>
       <c r="AT142" t="inlineStr">
         <is>
-          <t>batch_43847c5c0d554445</t>
+          <t>batch_0c2ed97284e04906</t>
         </is>
       </c>
       <c r="AU142" t="inlineStr">
@@ -23490,7 +23490,7 @@
       <c r="AW142" t="inlineStr"/>
       <c r="AX142" t="inlineStr">
         <is>
-          <t>2026-05-14T03:06:34+00:00</t>
+          <t>2026-05-14T03:16:15+00:00</t>
         </is>
       </c>
       <c r="AY142" t="inlineStr">
@@ -23634,7 +23634,7 @@
       </c>
       <c r="AT143" t="inlineStr">
         <is>
-          <t>batch_43847c5c0d554445</t>
+          <t>batch_0c2ed97284e04906</t>
         </is>
       </c>
       <c r="AU143" t="inlineStr">
@@ -23650,7 +23650,7 @@
       <c r="AW143" t="inlineStr"/>
       <c r="AX143" t="inlineStr">
         <is>
-          <t>2026-05-14T03:06:34+00:00</t>
+          <t>2026-05-14T03:16:15+00:00</t>
         </is>
       </c>
       <c r="AY143" t="inlineStr">
@@ -23794,7 +23794,7 @@
       </c>
       <c r="AT144" t="inlineStr">
         <is>
-          <t>batch_43847c5c0d554445</t>
+          <t>batch_0c2ed97284e04906</t>
         </is>
       </c>
       <c r="AU144" t="inlineStr">
@@ -23810,7 +23810,7 @@
       <c r="AW144" t="inlineStr"/>
       <c r="AX144" t="inlineStr">
         <is>
-          <t>2026-05-14T03:06:34+00:00</t>
+          <t>2026-05-14T03:16:15+00:00</t>
         </is>
       </c>
       <c r="AY144" t="inlineStr">
@@ -23954,7 +23954,7 @@
       </c>
       <c r="AT145" t="inlineStr">
         <is>
-          <t>batch_43847c5c0d554445</t>
+          <t>batch_0c2ed97284e04906</t>
         </is>
       </c>
       <c r="AU145" t="inlineStr">
@@ -23970,7 +23970,7 @@
       <c r="AW145" t="inlineStr"/>
       <c r="AX145" t="inlineStr">
         <is>
-          <t>2026-05-14T03:06:34+00:00</t>
+          <t>2026-05-14T03:16:15+00:00</t>
         </is>
       </c>
       <c r="AY145" t="inlineStr">
@@ -24114,7 +24114,7 @@
       </c>
       <c r="AT146" t="inlineStr">
         <is>
-          <t>batch_43847c5c0d554445</t>
+          <t>batch_0c2ed97284e04906</t>
         </is>
       </c>
       <c r="AU146" t="inlineStr">
@@ -24130,7 +24130,7 @@
       <c r="AW146" t="inlineStr"/>
       <c r="AX146" t="inlineStr">
         <is>
-          <t>2026-05-14T03:06:34+00:00</t>
+          <t>2026-05-14T03:16:15+00:00</t>
         </is>
       </c>
       <c r="AY146" t="inlineStr">
@@ -24274,7 +24274,7 @@
       </c>
       <c r="AT147" t="inlineStr">
         <is>
-          <t>batch_43847c5c0d554445</t>
+          <t>batch_0c2ed97284e04906</t>
         </is>
       </c>
       <c r="AU147" t="inlineStr">
@@ -24290,7 +24290,7 @@
       <c r="AW147" t="inlineStr"/>
       <c r="AX147" t="inlineStr">
         <is>
-          <t>2026-05-14T03:06:34+00:00</t>
+          <t>2026-05-14T03:16:15+00:00</t>
         </is>
       </c>
       <c r="AY147" t="inlineStr">
@@ -24434,7 +24434,7 @@
       </c>
       <c r="AT148" t="inlineStr">
         <is>
-          <t>batch_43847c5c0d554445</t>
+          <t>batch_0c2ed97284e04906</t>
         </is>
       </c>
       <c r="AU148" t="inlineStr">
@@ -24450,7 +24450,7 @@
       <c r="AW148" t="inlineStr"/>
       <c r="AX148" t="inlineStr">
         <is>
-          <t>2026-05-14T03:06:34+00:00</t>
+          <t>2026-05-14T03:16:15+00:00</t>
         </is>
       </c>
       <c r="AY148" t="inlineStr">
@@ -24594,7 +24594,7 @@
       </c>
       <c r="AT149" t="inlineStr">
         <is>
-          <t>batch_43847c5c0d554445</t>
+          <t>batch_0c2ed97284e04906</t>
         </is>
       </c>
       <c r="AU149" t="inlineStr">
@@ -24610,7 +24610,7 @@
       <c r="AW149" t="inlineStr"/>
       <c r="AX149" t="inlineStr">
         <is>
-          <t>2026-05-14T03:06:34+00:00</t>
+          <t>2026-05-14T03:16:15+00:00</t>
         </is>
       </c>
       <c r="AY149" t="inlineStr">
@@ -24754,7 +24754,7 @@
       </c>
       <c r="AT150" t="inlineStr">
         <is>
-          <t>batch_43847c5c0d554445</t>
+          <t>batch_0c2ed97284e04906</t>
         </is>
       </c>
       <c r="AU150" t="inlineStr">
@@ -24770,7 +24770,7 @@
       <c r="AW150" t="inlineStr"/>
       <c r="AX150" t="inlineStr">
         <is>
-          <t>2026-05-14T03:06:34+00:00</t>
+          <t>2026-05-14T03:16:15+00:00</t>
         </is>
       </c>
       <c r="AY150" t="inlineStr">
@@ -24914,7 +24914,7 @@
       </c>
       <c r="AT151" t="inlineStr">
         <is>
-          <t>batch_43847c5c0d554445</t>
+          <t>batch_0c2ed97284e04906</t>
         </is>
       </c>
       <c r="AU151" t="inlineStr">
@@ -24930,7 +24930,7 @@
       <c r="AW151" t="inlineStr"/>
       <c r="AX151" t="inlineStr">
         <is>
-          <t>2026-05-14T03:06:34+00:00</t>
+          <t>2026-05-14T03:16:15+00:00</t>
         </is>
       </c>
       <c r="AY151" t="inlineStr">
@@ -25074,7 +25074,7 @@
       </c>
       <c r="AT152" t="inlineStr">
         <is>
-          <t>batch_43847c5c0d554445</t>
+          <t>batch_0c2ed97284e04906</t>
         </is>
       </c>
       <c r="AU152" t="inlineStr">
@@ -25090,7 +25090,7 @@
       <c r="AW152" t="inlineStr"/>
       <c r="AX152" t="inlineStr">
         <is>
-          <t>2026-05-14T03:06:34+00:00</t>
+          <t>2026-05-14T03:16:15+00:00</t>
         </is>
       </c>
       <c r="AY152" t="inlineStr">
@@ -25234,7 +25234,7 @@
       </c>
       <c r="AT153" t="inlineStr">
         <is>
-          <t>batch_43847c5c0d554445</t>
+          <t>batch_0c2ed97284e04906</t>
         </is>
       </c>
       <c r="AU153" t="inlineStr">
@@ -25250,7 +25250,7 @@
       <c r="AW153" t="inlineStr"/>
       <c r="AX153" t="inlineStr">
         <is>
-          <t>2026-05-14T03:06:34+00:00</t>
+          <t>2026-05-14T03:16:15+00:00</t>
         </is>
       </c>
       <c r="AY153" t="inlineStr">
@@ -25394,7 +25394,7 @@
       </c>
       <c r="AT154" t="inlineStr">
         <is>
-          <t>batch_43847c5c0d554445</t>
+          <t>batch_0c2ed97284e04906</t>
         </is>
       </c>
       <c r="AU154" t="inlineStr">
@@ -25410,7 +25410,7 @@
       <c r="AW154" t="inlineStr"/>
       <c r="AX154" t="inlineStr">
         <is>
-          <t>2026-05-14T03:06:34+00:00</t>
+          <t>2026-05-14T03:16:15+00:00</t>
         </is>
       </c>
       <c r="AY154" t="inlineStr">
@@ -25554,7 +25554,7 @@
       </c>
       <c r="AT155" t="inlineStr">
         <is>
-          <t>batch_43847c5c0d554445</t>
+          <t>batch_0c2ed97284e04906</t>
         </is>
       </c>
       <c r="AU155" t="inlineStr">
@@ -25570,7 +25570,7 @@
       <c r="AW155" t="inlineStr"/>
       <c r="AX155" t="inlineStr">
         <is>
-          <t>2026-05-14T03:06:34+00:00</t>
+          <t>2026-05-14T03:16:15+00:00</t>
         </is>
       </c>
       <c r="AY155" t="inlineStr">
@@ -25714,7 +25714,7 @@
       </c>
       <c r="AT156" t="inlineStr">
         <is>
-          <t>batch_43847c5c0d554445</t>
+          <t>batch_0c2ed97284e04906</t>
         </is>
       </c>
       <c r="AU156" t="inlineStr">
@@ -25730,7 +25730,7 @@
       <c r="AW156" t="inlineStr"/>
       <c r="AX156" t="inlineStr">
         <is>
-          <t>2026-05-14T03:06:34+00:00</t>
+          <t>2026-05-14T03:16:15+00:00</t>
         </is>
       </c>
       <c r="AY156" t="inlineStr">
@@ -25874,7 +25874,7 @@
       </c>
       <c r="AT157" t="inlineStr">
         <is>
-          <t>batch_43847c5c0d554445</t>
+          <t>batch_0c2ed97284e04906</t>
         </is>
       </c>
       <c r="AU157" t="inlineStr">
@@ -25890,7 +25890,7 @@
       <c r="AW157" t="inlineStr"/>
       <c r="AX157" t="inlineStr">
         <is>
-          <t>2026-05-14T03:06:34+00:00</t>
+          <t>2026-05-14T03:16:15+00:00</t>
         </is>
       </c>
       <c r="AY157" t="inlineStr">
@@ -26034,7 +26034,7 @@
       </c>
       <c r="AT158" t="inlineStr">
         <is>
-          <t>batch_43847c5c0d554445</t>
+          <t>batch_0c2ed97284e04906</t>
         </is>
       </c>
       <c r="AU158" t="inlineStr">
@@ -26050,7 +26050,7 @@
       <c r="AW158" t="inlineStr"/>
       <c r="AX158" t="inlineStr">
         <is>
-          <t>2026-05-14T03:06:34+00:00</t>
+          <t>2026-05-14T03:16:15+00:00</t>
         </is>
       </c>
       <c r="AY158" t="inlineStr">
@@ -26194,7 +26194,7 @@
       </c>
       <c r="AT159" t="inlineStr">
         <is>
-          <t>batch_43847c5c0d554445</t>
+          <t>batch_0c2ed97284e04906</t>
         </is>
       </c>
       <c r="AU159" t="inlineStr">
@@ -26210,7 +26210,7 @@
       <c r="AW159" t="inlineStr"/>
       <c r="AX159" t="inlineStr">
         <is>
-          <t>2026-05-14T03:06:34+00:00</t>
+          <t>2026-05-14T03:16:15+00:00</t>
         </is>
       </c>
       <c r="AY159" t="inlineStr">
@@ -26354,7 +26354,7 @@
       </c>
       <c r="AT160" t="inlineStr">
         <is>
-          <t>batch_43847c5c0d554445</t>
+          <t>batch_0c2ed97284e04906</t>
         </is>
       </c>
       <c r="AU160" t="inlineStr">
@@ -26370,7 +26370,7 @@
       <c r="AW160" t="inlineStr"/>
       <c r="AX160" t="inlineStr">
         <is>
-          <t>2026-05-14T03:06:34+00:00</t>
+          <t>2026-05-14T03:16:15+00:00</t>
         </is>
       </c>
       <c r="AY160" t="inlineStr">
@@ -26514,7 +26514,7 @@
       </c>
       <c r="AT161" t="inlineStr">
         <is>
-          <t>batch_43847c5c0d554445</t>
+          <t>batch_0c2ed97284e04906</t>
         </is>
       </c>
       <c r="AU161" t="inlineStr">
@@ -26530,7 +26530,7 @@
       <c r="AW161" t="inlineStr"/>
       <c r="AX161" t="inlineStr">
         <is>
-          <t>2026-05-14T03:06:34+00:00</t>
+          <t>2026-05-14T03:16:15+00:00</t>
         </is>
       </c>
       <c r="AY161" t="inlineStr">
@@ -26674,7 +26674,7 @@
       </c>
       <c r="AT162" t="inlineStr">
         <is>
-          <t>batch_43847c5c0d554445</t>
+          <t>batch_0c2ed97284e04906</t>
         </is>
       </c>
       <c r="AU162" t="inlineStr">
@@ -26690,7 +26690,7 @@
       <c r="AW162" t="inlineStr"/>
       <c r="AX162" t="inlineStr">
         <is>
-          <t>2026-05-14T03:06:34+00:00</t>
+          <t>2026-05-14T03:16:15+00:00</t>
         </is>
       </c>
       <c r="AY162" t="inlineStr">
@@ -26834,7 +26834,7 @@
       </c>
       <c r="AT163" t="inlineStr">
         <is>
-          <t>batch_43847c5c0d554445</t>
+          <t>batch_0c2ed97284e04906</t>
         </is>
       </c>
       <c r="AU163" t="inlineStr">
@@ -26850,7 +26850,7 @@
       <c r="AW163" t="inlineStr"/>
       <c r="AX163" t="inlineStr">
         <is>
-          <t>2026-05-14T03:06:34+00:00</t>
+          <t>2026-05-14T03:16:15+00:00</t>
         </is>
       </c>
       <c r="AY163" t="inlineStr">
@@ -26994,7 +26994,7 @@
       </c>
       <c r="AT164" t="inlineStr">
         <is>
-          <t>batch_43847c5c0d554445</t>
+          <t>batch_0c2ed97284e04906</t>
         </is>
       </c>
       <c r="AU164" t="inlineStr">
@@ -27010,7 +27010,7 @@
       <c r="AW164" t="inlineStr"/>
       <c r="AX164" t="inlineStr">
         <is>
-          <t>2026-05-14T03:06:34+00:00</t>
+          <t>2026-05-14T03:16:15+00:00</t>
         </is>
       </c>
       <c r="AY164" t="inlineStr">
@@ -27154,7 +27154,7 @@
       </c>
       <c r="AT165" t="inlineStr">
         <is>
-          <t>batch_43847c5c0d554445</t>
+          <t>batch_0c2ed97284e04906</t>
         </is>
       </c>
       <c r="AU165" t="inlineStr">
@@ -27170,7 +27170,7 @@
       <c r="AW165" t="inlineStr"/>
       <c r="AX165" t="inlineStr">
         <is>
-          <t>2026-05-14T03:06:34+00:00</t>
+          <t>2026-05-14T03:16:15+00:00</t>
         </is>
       </c>
       <c r="AY165" t="inlineStr">
@@ -27314,7 +27314,7 @@
       </c>
       <c r="AT166" t="inlineStr">
         <is>
-          <t>batch_43847c5c0d554445</t>
+          <t>batch_0c2ed97284e04906</t>
         </is>
       </c>
       <c r="AU166" t="inlineStr">
@@ -27330,7 +27330,7 @@
       <c r="AW166" t="inlineStr"/>
       <c r="AX166" t="inlineStr">
         <is>
-          <t>2026-05-14T03:06:34+00:00</t>
+          <t>2026-05-14T03:16:15+00:00</t>
         </is>
       </c>
       <c r="AY166" t="inlineStr">
@@ -27474,7 +27474,7 @@
       </c>
       <c r="AT167" t="inlineStr">
         <is>
-          <t>batch_43847c5c0d554445</t>
+          <t>batch_0c2ed97284e04906</t>
         </is>
       </c>
       <c r="AU167" t="inlineStr">
@@ -27490,7 +27490,7 @@
       <c r="AW167" t="inlineStr"/>
       <c r="AX167" t="inlineStr">
         <is>
-          <t>2026-05-14T03:06:34+00:00</t>
+          <t>2026-05-14T03:16:15+00:00</t>
         </is>
       </c>
       <c r="AY167" t="inlineStr">
@@ -27634,7 +27634,7 @@
       </c>
       <c r="AT168" t="inlineStr">
         <is>
-          <t>batch_43847c5c0d554445</t>
+          <t>batch_0c2ed97284e04906</t>
         </is>
       </c>
       <c r="AU168" t="inlineStr">
@@ -27650,7 +27650,7 @@
       <c r="AW168" t="inlineStr"/>
       <c r="AX168" t="inlineStr">
         <is>
-          <t>2026-05-14T03:06:34+00:00</t>
+          <t>2026-05-14T03:16:15+00:00</t>
         </is>
       </c>
       <c r="AY168" t="inlineStr">
@@ -27794,7 +27794,7 @@
       </c>
       <c r="AT169" t="inlineStr">
         <is>
-          <t>batch_43847c5c0d554445</t>
+          <t>batch_0c2ed97284e04906</t>
         </is>
       </c>
       <c r="AU169" t="inlineStr">
@@ -27810,7 +27810,7 @@
       <c r="AW169" t="inlineStr"/>
       <c r="AX169" t="inlineStr">
         <is>
-          <t>2026-05-14T03:06:34+00:00</t>
+          <t>2026-05-14T03:16:15+00:00</t>
         </is>
       </c>
       <c r="AY169" t="inlineStr">
@@ -27954,7 +27954,7 @@
       </c>
       <c r="AT170" t="inlineStr">
         <is>
-          <t>batch_43847c5c0d554445</t>
+          <t>batch_0c2ed97284e04906</t>
         </is>
       </c>
       <c r="AU170" t="inlineStr">
@@ -27970,7 +27970,7 @@
       <c r="AW170" t="inlineStr"/>
       <c r="AX170" t="inlineStr">
         <is>
-          <t>2026-05-14T03:06:34+00:00</t>
+          <t>2026-05-14T03:16:15+00:00</t>
         </is>
       </c>
       <c r="AY170" t="inlineStr">
@@ -28114,7 +28114,7 @@
       </c>
       <c r="AT171" t="inlineStr">
         <is>
-          <t>batch_43847c5c0d554445</t>
+          <t>batch_0c2ed97284e04906</t>
         </is>
       </c>
       <c r="AU171" t="inlineStr">
@@ -28130,7 +28130,7 @@
       <c r="AW171" t="inlineStr"/>
       <c r="AX171" t="inlineStr">
         <is>
-          <t>2026-05-14T03:06:34+00:00</t>
+          <t>2026-05-14T03:16:15+00:00</t>
         </is>
       </c>
       <c r="AY171" t="inlineStr">
@@ -28274,7 +28274,7 @@
       </c>
       <c r="AT172" t="inlineStr">
         <is>
-          <t>batch_43847c5c0d554445</t>
+          <t>batch_0c2ed97284e04906</t>
         </is>
       </c>
       <c r="AU172" t="inlineStr">
@@ -28290,7 +28290,7 @@
       <c r="AW172" t="inlineStr"/>
       <c r="AX172" t="inlineStr">
         <is>
-          <t>2026-05-14T03:06:34+00:00</t>
+          <t>2026-05-14T03:16:15+00:00</t>
         </is>
       </c>
       <c r="AY172" t="inlineStr">
@@ -28434,7 +28434,7 @@
       </c>
       <c r="AT173" t="inlineStr">
         <is>
-          <t>batch_43847c5c0d554445</t>
+          <t>batch_0c2ed97284e04906</t>
         </is>
       </c>
       <c r="AU173" t="inlineStr">
@@ -28450,7 +28450,7 @@
       <c r="AW173" t="inlineStr"/>
       <c r="AX173" t="inlineStr">
         <is>
-          <t>2026-05-14T03:06:34+00:00</t>
+          <t>2026-05-14T03:16:15+00:00</t>
         </is>
       </c>
       <c r="AY173" t="inlineStr">
@@ -28594,7 +28594,7 @@
       </c>
       <c r="AT174" t="inlineStr">
         <is>
-          <t>batch_43847c5c0d554445</t>
+          <t>batch_0c2ed97284e04906</t>
         </is>
       </c>
       <c r="AU174" t="inlineStr">
@@ -28610,7 +28610,7 @@
       <c r="AW174" t="inlineStr"/>
       <c r="AX174" t="inlineStr">
         <is>
-          <t>2026-05-14T03:06:34+00:00</t>
+          <t>2026-05-14T03:16:15+00:00</t>
         </is>
       </c>
       <c r="AY174" t="inlineStr">
@@ -28754,7 +28754,7 @@
       </c>
       <c r="AT175" t="inlineStr">
         <is>
-          <t>batch_43847c5c0d554445</t>
+          <t>batch_0c2ed97284e04906</t>
         </is>
       </c>
       <c r="AU175" t="inlineStr">
@@ -28770,7 +28770,7 @@
       <c r="AW175" t="inlineStr"/>
       <c r="AX175" t="inlineStr">
         <is>
-          <t>2026-05-14T03:06:34+00:00</t>
+          <t>2026-05-14T03:16:15+00:00</t>
         </is>
       </c>
       <c r="AY175" t="inlineStr">
@@ -28914,7 +28914,7 @@
       </c>
       <c r="AT176" t="inlineStr">
         <is>
-          <t>batch_43847c5c0d554445</t>
+          <t>batch_0c2ed97284e04906</t>
         </is>
       </c>
       <c r="AU176" t="inlineStr">
@@ -28930,7 +28930,7 @@
       <c r="AW176" t="inlineStr"/>
       <c r="AX176" t="inlineStr">
         <is>
-          <t>2026-05-14T03:06:34+00:00</t>
+          <t>2026-05-14T03:16:15+00:00</t>
         </is>
       </c>
       <c r="AY176" t="inlineStr">
@@ -29074,7 +29074,7 @@
       </c>
       <c r="AT177" t="inlineStr">
         <is>
-          <t>batch_43847c5c0d554445</t>
+          <t>batch_0c2ed97284e04906</t>
         </is>
       </c>
       <c r="AU177" t="inlineStr">
@@ -29090,7 +29090,7 @@
       <c r="AW177" t="inlineStr"/>
       <c r="AX177" t="inlineStr">
         <is>
-          <t>2026-05-14T03:06:34+00:00</t>
+          <t>2026-05-14T03:16:15+00:00</t>
         </is>
       </c>
       <c r="AY177" t="inlineStr">
@@ -29234,7 +29234,7 @@
       </c>
       <c r="AT178" t="inlineStr">
         <is>
-          <t>batch_43847c5c0d554445</t>
+          <t>batch_0c2ed97284e04906</t>
         </is>
       </c>
       <c r="AU178" t="inlineStr">
@@ -29250,7 +29250,7 @@
       <c r="AW178" t="inlineStr"/>
       <c r="AX178" t="inlineStr">
         <is>
-          <t>2026-05-14T03:06:34+00:00</t>
+          <t>2026-05-14T03:16:15+00:00</t>
         </is>
       </c>
       <c r="AY178" t="inlineStr">
@@ -29394,7 +29394,7 @@
       </c>
       <c r="AT179" t="inlineStr">
         <is>
-          <t>batch_43847c5c0d554445</t>
+          <t>batch_0c2ed97284e04906</t>
         </is>
       </c>
       <c r="AU179" t="inlineStr">
@@ -29410,7 +29410,7 @@
       <c r="AW179" t="inlineStr"/>
       <c r="AX179" t="inlineStr">
         <is>
-          <t>2026-05-14T03:06:34+00:00</t>
+          <t>2026-05-14T03:16:15+00:00</t>
         </is>
       </c>
       <c r="AY179" t="inlineStr">
@@ -29554,7 +29554,7 @@
       </c>
       <c r="AT180" t="inlineStr">
         <is>
-          <t>batch_43847c5c0d554445</t>
+          <t>batch_0c2ed97284e04906</t>
         </is>
       </c>
       <c r="AU180" t="inlineStr">
@@ -29570,7 +29570,7 @@
       <c r="AW180" t="inlineStr"/>
       <c r="AX180" t="inlineStr">
         <is>
-          <t>2026-05-14T03:06:34+00:00</t>
+          <t>2026-05-14T03:16:15+00:00</t>
         </is>
       </c>
       <c r="AY180" t="inlineStr">
@@ -29714,7 +29714,7 @@
       </c>
       <c r="AT181" t="inlineStr">
         <is>
-          <t>batch_43847c5c0d554445</t>
+          <t>batch_0c2ed97284e04906</t>
         </is>
       </c>
       <c r="AU181" t="inlineStr">
@@ -29730,7 +29730,7 @@
       <c r="AW181" t="inlineStr"/>
       <c r="AX181" t="inlineStr">
         <is>
-          <t>2026-05-14T03:06:34+00:00</t>
+          <t>2026-05-14T03:16:15+00:00</t>
         </is>
       </c>
       <c r="AY181" t="inlineStr">
@@ -29874,7 +29874,7 @@
       </c>
       <c r="AT182" t="inlineStr">
         <is>
-          <t>batch_43847c5c0d554445</t>
+          <t>batch_0c2ed97284e04906</t>
         </is>
       </c>
       <c r="AU182" t="inlineStr">
@@ -29890,7 +29890,7 @@
       <c r="AW182" t="inlineStr"/>
       <c r="AX182" t="inlineStr">
         <is>
-          <t>2026-05-14T03:06:34+00:00</t>
+          <t>2026-05-14T03:16:15+00:00</t>
         </is>
       </c>
       <c r="AY182" t="inlineStr">
@@ -30031,7 +30031,7 @@
       </c>
       <c r="AT183" t="inlineStr">
         <is>
-          <t>batch_43847c5c0d554445</t>
+          <t>batch_0c2ed97284e04906</t>
         </is>
       </c>
       <c r="AU183" t="inlineStr">
@@ -30047,7 +30047,7 @@
       <c r="AW183" t="inlineStr"/>
       <c r="AX183" t="inlineStr">
         <is>
-          <t>2026-05-14T03:06:34+00:00</t>
+          <t>2026-05-14T03:16:15+00:00</t>
         </is>
       </c>
       <c r="AY183" t="inlineStr">
@@ -30191,7 +30191,7 @@
       </c>
       <c r="AT184" t="inlineStr">
         <is>
-          <t>batch_43847c5c0d554445</t>
+          <t>batch_0c2ed97284e04906</t>
         </is>
       </c>
       <c r="AU184" t="inlineStr">
@@ -30207,7 +30207,7 @@
       <c r="AW184" t="inlineStr"/>
       <c r="AX184" t="inlineStr">
         <is>
-          <t>2026-05-14T03:06:34+00:00</t>
+          <t>2026-05-14T03:16:15+00:00</t>
         </is>
       </c>
       <c r="AY184" t="inlineStr">
@@ -30351,7 +30351,7 @@
       </c>
       <c r="AT185" t="inlineStr">
         <is>
-          <t>batch_43847c5c0d554445</t>
+          <t>batch_0c2ed97284e04906</t>
         </is>
       </c>
       <c r="AU185" t="inlineStr">
@@ -30367,7 +30367,7 @@
       <c r="AW185" t="inlineStr"/>
       <c r="AX185" t="inlineStr">
         <is>
-          <t>2026-05-14T03:06:34+00:00</t>
+          <t>2026-05-14T03:16:15+00:00</t>
         </is>
       </c>
       <c r="AY185" t="inlineStr">
@@ -30511,7 +30511,7 @@
       </c>
       <c r="AT186" t="inlineStr">
         <is>
-          <t>batch_43847c5c0d554445</t>
+          <t>batch_0c2ed97284e04906</t>
         </is>
       </c>
       <c r="AU186" t="inlineStr">
@@ -30527,7 +30527,7 @@
       <c r="AW186" t="inlineStr"/>
       <c r="AX186" t="inlineStr">
         <is>
-          <t>2026-05-14T03:06:34+00:00</t>
+          <t>2026-05-14T03:16:15+00:00</t>
         </is>
       </c>
       <c r="AY186" t="inlineStr">
@@ -30671,7 +30671,7 @@
       </c>
       <c r="AT187" t="inlineStr">
         <is>
-          <t>batch_43847c5c0d554445</t>
+          <t>batch_0c2ed97284e04906</t>
         </is>
       </c>
       <c r="AU187" t="inlineStr">
@@ -30687,7 +30687,7 @@
       <c r="AW187" t="inlineStr"/>
       <c r="AX187" t="inlineStr">
         <is>
-          <t>2026-05-14T03:06:34+00:00</t>
+          <t>2026-05-14T03:16:15+00:00</t>
         </is>
       </c>
       <c r="AY187" t="inlineStr">
@@ -30831,7 +30831,7 @@
       </c>
       <c r="AT188" t="inlineStr">
         <is>
-          <t>batch_43847c5c0d554445</t>
+          <t>batch_0c2ed97284e04906</t>
         </is>
       </c>
       <c r="AU188" t="inlineStr">
@@ -30847,7 +30847,7 @@
       <c r="AW188" t="inlineStr"/>
       <c r="AX188" t="inlineStr">
         <is>
-          <t>2026-05-14T03:06:34+00:00</t>
+          <t>2026-05-14T03:16:15+00:00</t>
         </is>
       </c>
       <c r="AY188" t="inlineStr">
@@ -30991,7 +30991,7 @@
       </c>
       <c r="AT189" t="inlineStr">
         <is>
-          <t>batch_43847c5c0d554445</t>
+          <t>batch_0c2ed97284e04906</t>
         </is>
       </c>
       <c r="AU189" t="inlineStr">
@@ -31007,7 +31007,7 @@
       <c r="AW189" t="inlineStr"/>
       <c r="AX189" t="inlineStr">
         <is>
-          <t>2026-05-14T03:06:34+00:00</t>
+          <t>2026-05-14T03:16:15+00:00</t>
         </is>
       </c>
       <c r="AY189" t="inlineStr">
@@ -31151,7 +31151,7 @@
       </c>
       <c r="AT190" t="inlineStr">
         <is>
-          <t>batch_43847c5c0d554445</t>
+          <t>batch_0c2ed97284e04906</t>
         </is>
       </c>
       <c r="AU190" t="inlineStr">
@@ -31167,7 +31167,7 @@
       <c r="AW190" t="inlineStr"/>
       <c r="AX190" t="inlineStr">
         <is>
-          <t>2026-05-14T03:06:34+00:00</t>
+          <t>2026-05-14T03:16:15+00:00</t>
         </is>
       </c>
       <c r="AY190" t="inlineStr">
@@ -31311,7 +31311,7 @@
       </c>
       <c r="AT191" t="inlineStr">
         <is>
-          <t>batch_43847c5c0d554445</t>
+          <t>batch_0c2ed97284e04906</t>
         </is>
       </c>
       <c r="AU191" t="inlineStr">
@@ -31327,7 +31327,7 @@
       <c r="AW191" t="inlineStr"/>
       <c r="AX191" t="inlineStr">
         <is>
-          <t>2026-05-14T03:06:34+00:00</t>
+          <t>2026-05-14T03:16:15+00:00</t>
         </is>
       </c>
       <c r="AY191" t="inlineStr">
@@ -31471,7 +31471,7 @@
       </c>
       <c r="AT192" t="inlineStr">
         <is>
-          <t>batch_43847c5c0d554445</t>
+          <t>batch_0c2ed97284e04906</t>
         </is>
       </c>
       <c r="AU192" t="inlineStr">
@@ -31487,7 +31487,7 @@
       <c r="AW192" t="inlineStr"/>
       <c r="AX192" t="inlineStr">
         <is>
-          <t>2026-05-14T03:06:34+00:00</t>
+          <t>2026-05-14T03:16:15+00:00</t>
         </is>
       </c>
       <c r="AY192" t="inlineStr">
@@ -31631,7 +31631,7 @@
       </c>
       <c r="AT193" t="inlineStr">
         <is>
-          <t>batch_43847c5c0d554445</t>
+          <t>batch_0c2ed97284e04906</t>
         </is>
       </c>
       <c r="AU193" t="inlineStr">
@@ -31647,7 +31647,7 @@
       <c r="AW193" t="inlineStr"/>
       <c r="AX193" t="inlineStr">
         <is>
-          <t>2026-05-14T03:06:34+00:00</t>
+          <t>2026-05-14T03:16:15+00:00</t>
         </is>
       </c>
       <c r="AY193" t="inlineStr">
@@ -31791,7 +31791,7 @@
       </c>
       <c r="AT194" t="inlineStr">
         <is>
-          <t>batch_43847c5c0d554445</t>
+          <t>batch_0c2ed97284e04906</t>
         </is>
       </c>
       <c r="AU194" t="inlineStr">
@@ -31807,7 +31807,7 @@
       <c r="AW194" t="inlineStr"/>
       <c r="AX194" t="inlineStr">
         <is>
-          <t>2026-05-14T03:06:34+00:00</t>
+          <t>2026-05-14T03:16:15+00:00</t>
         </is>
       </c>
       <c r="AY194" t="inlineStr">
@@ -31951,7 +31951,7 @@
       </c>
       <c r="AT195" t="inlineStr">
         <is>
-          <t>batch_43847c5c0d554445</t>
+          <t>batch_0c2ed97284e04906</t>
         </is>
       </c>
       <c r="AU195" t="inlineStr">
@@ -31967,7 +31967,7 @@
       <c r="AW195" t="inlineStr"/>
       <c r="AX195" t="inlineStr">
         <is>
-          <t>2026-05-14T03:06:34+00:00</t>
+          <t>2026-05-14T03:16:15+00:00</t>
         </is>
       </c>
       <c r="AY195" t="inlineStr">
@@ -32111,7 +32111,7 @@
       </c>
       <c r="AT196" t="inlineStr">
         <is>
-          <t>batch_43847c5c0d554445</t>
+          <t>batch_0c2ed97284e04906</t>
         </is>
       </c>
       <c r="AU196" t="inlineStr">
@@ -32127,7 +32127,7 @@
       <c r="AW196" t="inlineStr"/>
       <c r="AX196" t="inlineStr">
         <is>
-          <t>2026-05-14T03:06:34+00:00</t>
+          <t>2026-05-14T03:16:15+00:00</t>
         </is>
       </c>
       <c r="AY196" t="inlineStr">
@@ -32271,7 +32271,7 @@
       </c>
       <c r="AT197" t="inlineStr">
         <is>
-          <t>batch_43847c5c0d554445</t>
+          <t>batch_0c2ed97284e04906</t>
         </is>
       </c>
       <c r="AU197" t="inlineStr">
@@ -32287,7 +32287,7 @@
       <c r="AW197" t="inlineStr"/>
       <c r="AX197" t="inlineStr">
         <is>
-          <t>2026-05-14T03:06:34+00:00</t>
+          <t>2026-05-14T03:16:15+00:00</t>
         </is>
       </c>
       <c r="AY197" t="inlineStr">
@@ -32431,7 +32431,7 @@
       </c>
       <c r="AT198" t="inlineStr">
         <is>
-          <t>batch_43847c5c0d554445</t>
+          <t>batch_0c2ed97284e04906</t>
         </is>
       </c>
       <c r="AU198" t="inlineStr">
@@ -32447,7 +32447,7 @@
       <c r="AW198" t="inlineStr"/>
       <c r="AX198" t="inlineStr">
         <is>
-          <t>2026-05-14T03:06:34+00:00</t>
+          <t>2026-05-14T03:16:15+00:00</t>
         </is>
       </c>
       <c r="AY198" t="inlineStr">
@@ -32591,7 +32591,7 @@
       </c>
       <c r="AT199" t="inlineStr">
         <is>
-          <t>batch_43847c5c0d554445</t>
+          <t>batch_0c2ed97284e04906</t>
         </is>
       </c>
       <c r="AU199" t="inlineStr">
@@ -32607,7 +32607,7 @@
       <c r="AW199" t="inlineStr"/>
       <c r="AX199" t="inlineStr">
         <is>
-          <t>2026-05-14T03:06:34+00:00</t>
+          <t>2026-05-14T03:16:15+00:00</t>
         </is>
       </c>
       <c r="AY199" t="inlineStr">
@@ -32751,7 +32751,7 @@
       </c>
       <c r="AT200" t="inlineStr">
         <is>
-          <t>batch_43847c5c0d554445</t>
+          <t>batch_0c2ed97284e04906</t>
         </is>
       </c>
       <c r="AU200" t="inlineStr">
@@ -32767,7 +32767,7 @@
       <c r="AW200" t="inlineStr"/>
       <c r="AX200" t="inlineStr">
         <is>
-          <t>2026-05-14T03:06:34+00:00</t>
+          <t>2026-05-14T03:16:15+00:00</t>
         </is>
       </c>
       <c r="AY200" t="inlineStr">
@@ -32920,7 +32920,7 @@
       </c>
       <c r="AT201" t="inlineStr">
         <is>
-          <t>batch_43847c5c0d554445</t>
+          <t>batch_0c2ed97284e04906</t>
         </is>
       </c>
       <c r="AU201" t="inlineStr">
@@ -32936,7 +32936,7 @@
       <c r="AW201" t="inlineStr"/>
       <c r="AX201" t="inlineStr">
         <is>
-          <t>2026-05-14T03:06:34+00:00</t>
+          <t>2026-05-14T03:16:15+00:00</t>
         </is>
       </c>
       <c r="AY201" t="inlineStr">
@@ -33089,7 +33089,7 @@
       </c>
       <c r="AT202" t="inlineStr">
         <is>
-          <t>batch_43847c5c0d554445</t>
+          <t>batch_0c2ed97284e04906</t>
         </is>
       </c>
       <c r="AU202" t="inlineStr">
@@ -33105,7 +33105,7 @@
       <c r="AW202" t="inlineStr"/>
       <c r="AX202" t="inlineStr">
         <is>
-          <t>2026-05-14T03:06:34+00:00</t>
+          <t>2026-05-14T03:16:15+00:00</t>
         </is>
       </c>
       <c r="AY202" t="inlineStr">
@@ -33249,7 +33249,7 @@
       </c>
       <c r="AT203" t="inlineStr">
         <is>
-          <t>batch_43847c5c0d554445</t>
+          <t>batch_0c2ed97284e04906</t>
         </is>
       </c>
       <c r="AU203" t="inlineStr">
@@ -33265,7 +33265,7 @@
       <c r="AW203" t="inlineStr"/>
       <c r="AX203" t="inlineStr">
         <is>
-          <t>2026-05-14T03:06:34+00:00</t>
+          <t>2026-05-14T03:16:15+00:00</t>
         </is>
       </c>
       <c r="AY203" t="inlineStr">
@@ -33409,7 +33409,7 @@
       </c>
       <c r="AT204" t="inlineStr">
         <is>
-          <t>batch_43847c5c0d554445</t>
+          <t>batch_0c2ed97284e04906</t>
         </is>
       </c>
       <c r="AU204" t="inlineStr">
@@ -33425,7 +33425,7 @@
       <c r="AW204" t="inlineStr"/>
       <c r="AX204" t="inlineStr">
         <is>
-          <t>2026-05-14T03:06:34+00:00</t>
+          <t>2026-05-14T03:16:15+00:00</t>
         </is>
       </c>
       <c r="AY204" t="inlineStr">
@@ -33569,7 +33569,7 @@
       </c>
       <c r="AT205" t="inlineStr">
         <is>
-          <t>batch_43847c5c0d554445</t>
+          <t>batch_0c2ed97284e04906</t>
         </is>
       </c>
       <c r="AU205" t="inlineStr">
@@ -33585,7 +33585,7 @@
       <c r="AW205" t="inlineStr"/>
       <c r="AX205" t="inlineStr">
         <is>
-          <t>2026-05-14T03:06:34+00:00</t>
+          <t>2026-05-14T03:16:15+00:00</t>
         </is>
       </c>
       <c r="AY205" t="inlineStr">
@@ -33729,7 +33729,7 @@
       </c>
       <c r="AT206" t="inlineStr">
         <is>
-          <t>batch_43847c5c0d554445</t>
+          <t>batch_0c2ed97284e04906</t>
         </is>
       </c>
       <c r="AU206" t="inlineStr">
@@ -33745,7 +33745,7 @@
       <c r="AW206" t="inlineStr"/>
       <c r="AX206" t="inlineStr">
         <is>
-          <t>2026-05-14T03:06:34+00:00</t>
+          <t>2026-05-14T03:16:15+00:00</t>
         </is>
       </c>
       <c r="AY206" t="inlineStr">
@@ -33889,7 +33889,7 @@
       </c>
       <c r="AT207" t="inlineStr">
         <is>
-          <t>batch_43847c5c0d554445</t>
+          <t>batch_0c2ed97284e04906</t>
         </is>
       </c>
       <c r="AU207" t="inlineStr">
@@ -33905,7 +33905,7 @@
       <c r="AW207" t="inlineStr"/>
       <c r="AX207" t="inlineStr">
         <is>
-          <t>2026-05-14T03:06:34+00:00</t>
+          <t>2026-05-14T03:16:15+00:00</t>
         </is>
       </c>
       <c r="AY207" t="inlineStr">
@@ -34049,7 +34049,7 @@
       </c>
       <c r="AT208" t="inlineStr">
         <is>
-          <t>batch_43847c5c0d554445</t>
+          <t>batch_0c2ed97284e04906</t>
         </is>
       </c>
       <c r="AU208" t="inlineStr">
@@ -34065,7 +34065,7 @@
       <c r="AW208" t="inlineStr"/>
       <c r="AX208" t="inlineStr">
         <is>
-          <t>2026-05-14T03:06:34+00:00</t>
+          <t>2026-05-14T03:16:15+00:00</t>
         </is>
       </c>
       <c r="AY208" t="inlineStr">
@@ -34209,7 +34209,7 @@
       </c>
       <c r="AT209" t="inlineStr">
         <is>
-          <t>batch_43847c5c0d554445</t>
+          <t>batch_0c2ed97284e04906</t>
         </is>
       </c>
       <c r="AU209" t="inlineStr">
@@ -34225,7 +34225,7 @@
       <c r="AW209" t="inlineStr"/>
       <c r="AX209" t="inlineStr">
         <is>
-          <t>2026-05-14T03:06:34+00:00</t>
+          <t>2026-05-14T03:16:15+00:00</t>
         </is>
       </c>
       <c r="AY209" t="inlineStr">
@@ -34369,7 +34369,7 @@
       </c>
       <c r="AT210" t="inlineStr">
         <is>
-          <t>batch_43847c5c0d554445</t>
+          <t>batch_0c2ed97284e04906</t>
         </is>
       </c>
       <c r="AU210" t="inlineStr">
@@ -34385,7 +34385,7 @@
       <c r="AW210" t="inlineStr"/>
       <c r="AX210" t="inlineStr">
         <is>
-          <t>2026-05-14T03:06:34+00:00</t>
+          <t>2026-05-14T03:16:15+00:00</t>
         </is>
       </c>
       <c r="AY210" t="inlineStr">
@@ -34529,7 +34529,7 @@
       </c>
       <c r="AT211" t="inlineStr">
         <is>
-          <t>batch_43847c5c0d554445</t>
+          <t>batch_0c2ed97284e04906</t>
         </is>
       </c>
       <c r="AU211" t="inlineStr">
@@ -34545,7 +34545,7 @@
       <c r="AW211" t="inlineStr"/>
       <c r="AX211" t="inlineStr">
         <is>
-          <t>2026-05-14T03:06:34+00:00</t>
+          <t>2026-05-14T03:16:15+00:00</t>
         </is>
       </c>
       <c r="AY211" t="inlineStr">
@@ -34689,7 +34689,7 @@
       </c>
       <c r="AT212" t="inlineStr">
         <is>
-          <t>batch_43847c5c0d554445</t>
+          <t>batch_0c2ed97284e04906</t>
         </is>
       </c>
       <c r="AU212" t="inlineStr">
@@ -34705,7 +34705,7 @@
       <c r="AW212" t="inlineStr"/>
       <c r="AX212" t="inlineStr">
         <is>
-          <t>2026-05-14T03:06:34+00:00</t>
+          <t>2026-05-14T03:16:15+00:00</t>
         </is>
       </c>
       <c r="AY212" t="inlineStr">
@@ -34849,7 +34849,7 @@
       </c>
       <c r="AT213" t="inlineStr">
         <is>
-          <t>batch_43847c5c0d554445</t>
+          <t>batch_0c2ed97284e04906</t>
         </is>
       </c>
       <c r="AU213" t="inlineStr">
@@ -34865,7 +34865,7 @@
       <c r="AW213" t="inlineStr"/>
       <c r="AX213" t="inlineStr">
         <is>
-          <t>2026-05-14T03:06:34+00:00</t>
+          <t>2026-05-14T03:16:15+00:00</t>
         </is>
       </c>
       <c r="AY213" t="inlineStr">
@@ -35009,7 +35009,7 @@
       </c>
       <c r="AT214" t="inlineStr">
         <is>
-          <t>batch_43847c5c0d554445</t>
+          <t>batch_0c2ed97284e04906</t>
         </is>
       </c>
       <c r="AU214" t="inlineStr">
@@ -35025,7 +35025,7 @@
       <c r="AW214" t="inlineStr"/>
       <c r="AX214" t="inlineStr">
         <is>
-          <t>2026-05-14T03:06:34+00:00</t>
+          <t>2026-05-14T03:16:15+00:00</t>
         </is>
       </c>
       <c r="AY214" t="inlineStr">
@@ -35169,7 +35169,7 @@
       </c>
       <c r="AT215" t="inlineStr">
         <is>
-          <t>batch_43847c5c0d554445</t>
+          <t>batch_0c2ed97284e04906</t>
         </is>
       </c>
       <c r="AU215" t="inlineStr">
@@ -35185,7 +35185,7 @@
       <c r="AW215" t="inlineStr"/>
       <c r="AX215" t="inlineStr">
         <is>
-          <t>2026-05-14T03:06:34+00:00</t>
+          <t>2026-05-14T03:16:15+00:00</t>
         </is>
       </c>
       <c r="AY215" t="inlineStr">
@@ -35329,7 +35329,7 @@
       </c>
       <c r="AT216" t="inlineStr">
         <is>
-          <t>batch_43847c5c0d554445</t>
+          <t>batch_0c2ed97284e04906</t>
         </is>
       </c>
       <c r="AU216" t="inlineStr">
@@ -35345,7 +35345,7 @@
       <c r="AW216" t="inlineStr"/>
       <c r="AX216" t="inlineStr">
         <is>
-          <t>2026-05-14T03:06:34+00:00</t>
+          <t>2026-05-14T03:16:15+00:00</t>
         </is>
       </c>
       <c r="AY216" t="inlineStr">
@@ -35489,7 +35489,7 @@
       </c>
       <c r="AT217" t="inlineStr">
         <is>
-          <t>batch_43847c5c0d554445</t>
+          <t>batch_0c2ed97284e04906</t>
         </is>
       </c>
       <c r="AU217" t="inlineStr">
@@ -35505,7 +35505,7 @@
       <c r="AW217" t="inlineStr"/>
       <c r="AX217" t="inlineStr">
         <is>
-          <t>2026-05-14T03:06:34+00:00</t>
+          <t>2026-05-14T03:16:15+00:00</t>
         </is>
       </c>
       <c r="AY217" t="inlineStr">
@@ -35649,7 +35649,7 @@
       </c>
       <c r="AT218" t="inlineStr">
         <is>
-          <t>batch_43847c5c0d554445</t>
+          <t>batch_0c2ed97284e04906</t>
         </is>
       </c>
       <c r="AU218" t="inlineStr">
@@ -35665,7 +35665,7 @@
       <c r="AW218" t="inlineStr"/>
       <c r="AX218" t="inlineStr">
         <is>
-          <t>2026-05-14T03:06:34+00:00</t>
+          <t>2026-05-14T03:16:15+00:00</t>
         </is>
       </c>
       <c r="AY218" t="inlineStr">
@@ -35809,7 +35809,7 @@
       </c>
       <c r="AT219" t="inlineStr">
         <is>
-          <t>batch_43847c5c0d554445</t>
+          <t>batch_0c2ed97284e04906</t>
         </is>
       </c>
       <c r="AU219" t="inlineStr">
@@ -35825,7 +35825,7 @@
       <c r="AW219" t="inlineStr"/>
       <c r="AX219" t="inlineStr">
         <is>
-          <t>2026-05-14T03:06:34+00:00</t>
+          <t>2026-05-14T03:16:15+00:00</t>
         </is>
       </c>
       <c r="AY219" t="inlineStr">
@@ -35969,7 +35969,7 @@
       </c>
       <c r="AT220" t="inlineStr">
         <is>
-          <t>batch_43847c5c0d554445</t>
+          <t>batch_0c2ed97284e04906</t>
         </is>
       </c>
       <c r="AU220" t="inlineStr">
@@ -35985,7 +35985,7 @@
       <c r="AW220" t="inlineStr"/>
       <c r="AX220" t="inlineStr">
         <is>
-          <t>2026-05-14T03:06:34+00:00</t>
+          <t>2026-05-14T03:16:15+00:00</t>
         </is>
       </c>
       <c r="AY220" t="inlineStr">
@@ -36129,7 +36129,7 @@
       </c>
       <c r="AT221" t="inlineStr">
         <is>
-          <t>batch_43847c5c0d554445</t>
+          <t>batch_0c2ed97284e04906</t>
         </is>
       </c>
       <c r="AU221" t="inlineStr">
@@ -36145,7 +36145,7 @@
       <c r="AW221" t="inlineStr"/>
       <c r="AX221" t="inlineStr">
         <is>
-          <t>2026-05-14T03:06:34+00:00</t>
+          <t>2026-05-14T03:16:15+00:00</t>
         </is>
       </c>
       <c r="AY221" t="inlineStr">
@@ -36289,7 +36289,7 @@
       </c>
       <c r="AT222" t="inlineStr">
         <is>
-          <t>batch_43847c5c0d554445</t>
+          <t>batch_0c2ed97284e04906</t>
         </is>
       </c>
       <c r="AU222" t="inlineStr">
@@ -36305,7 +36305,7 @@
       <c r="AW222" t="inlineStr"/>
       <c r="AX222" t="inlineStr">
         <is>
-          <t>2026-05-14T03:06:34+00:00</t>
+          <t>2026-05-14T03:16:15+00:00</t>
         </is>
       </c>
       <c r="AY222" t="inlineStr">
@@ -36449,7 +36449,7 @@
       </c>
       <c r="AT223" t="inlineStr">
         <is>
-          <t>batch_43847c5c0d554445</t>
+          <t>batch_0c2ed97284e04906</t>
         </is>
       </c>
       <c r="AU223" t="inlineStr">
@@ -36465,7 +36465,7 @@
       <c r="AW223" t="inlineStr"/>
       <c r="AX223" t="inlineStr">
         <is>
-          <t>2026-05-14T03:06:34+00:00</t>
+          <t>2026-05-14T03:16:15+00:00</t>
         </is>
       </c>
       <c r="AY223" t="inlineStr">
@@ -36609,7 +36609,7 @@
       </c>
       <c r="AT224" t="inlineStr">
         <is>
-          <t>batch_43847c5c0d554445</t>
+          <t>batch_0c2ed97284e04906</t>
         </is>
       </c>
       <c r="AU224" t="inlineStr">
@@ -36625,7 +36625,7 @@
       <c r="AW224" t="inlineStr"/>
       <c r="AX224" t="inlineStr">
         <is>
-          <t>2026-05-14T03:06:34+00:00</t>
+          <t>2026-05-14T03:16:15+00:00</t>
         </is>
       </c>
       <c r="AY224" t="inlineStr">
@@ -36769,7 +36769,7 @@
       </c>
       <c r="AT225" t="inlineStr">
         <is>
-          <t>batch_43847c5c0d554445</t>
+          <t>batch_0c2ed97284e04906</t>
         </is>
       </c>
       <c r="AU225" t="inlineStr">
@@ -36785,7 +36785,7 @@
       <c r="AW225" t="inlineStr"/>
       <c r="AX225" t="inlineStr">
         <is>
-          <t>2026-05-14T03:06:34+00:00</t>
+          <t>2026-05-14T03:16:15+00:00</t>
         </is>
       </c>
       <c r="AY225" t="inlineStr">
@@ -36929,7 +36929,7 @@
       </c>
       <c r="AT226" t="inlineStr">
         <is>
-          <t>batch_43847c5c0d554445</t>
+          <t>batch_0c2ed97284e04906</t>
         </is>
       </c>
       <c r="AU226" t="inlineStr">
@@ -36945,7 +36945,7 @@
       <c r="AW226" t="inlineStr"/>
       <c r="AX226" t="inlineStr">
         <is>
-          <t>2026-05-14T03:06:34+00:00</t>
+          <t>2026-05-14T03:16:15+00:00</t>
         </is>
       </c>
       <c r="AY226" t="inlineStr">
@@ -37089,7 +37089,7 @@
       </c>
       <c r="AT227" t="inlineStr">
         <is>
-          <t>batch_43847c5c0d554445</t>
+          <t>batch_0c2ed97284e04906</t>
         </is>
       </c>
       <c r="AU227" t="inlineStr">
@@ -37105,7 +37105,7 @@
       <c r="AW227" t="inlineStr"/>
       <c r="AX227" t="inlineStr">
         <is>
-          <t>2026-05-14T03:06:34+00:00</t>
+          <t>2026-05-14T03:16:15+00:00</t>
         </is>
       </c>
       <c r="AY227" t="inlineStr">
@@ -37249,7 +37249,7 @@
       </c>
       <c r="AT228" t="inlineStr">
         <is>
-          <t>batch_43847c5c0d554445</t>
+          <t>batch_0c2ed97284e04906</t>
         </is>
       </c>
       <c r="AU228" t="inlineStr">
@@ -37265,7 +37265,7 @@
       <c r="AW228" t="inlineStr"/>
       <c r="AX228" t="inlineStr">
         <is>
-          <t>2026-05-14T03:06:34+00:00</t>
+          <t>2026-05-14T03:16:15+00:00</t>
         </is>
       </c>
       <c r="AY228" t="inlineStr">
@@ -37409,7 +37409,7 @@
       </c>
       <c r="AT229" t="inlineStr">
         <is>
-          <t>batch_43847c5c0d554445</t>
+          <t>batch_0c2ed97284e04906</t>
         </is>
       </c>
       <c r="AU229" t="inlineStr">
@@ -37425,7 +37425,7 @@
       <c r="AW229" t="inlineStr"/>
       <c r="AX229" t="inlineStr">
         <is>
-          <t>2026-05-14T03:06:34+00:00</t>
+          <t>2026-05-14T03:16:15+00:00</t>
         </is>
       </c>
       <c r="AY229" t="inlineStr">
@@ -37569,7 +37569,7 @@
       </c>
       <c r="AT230" t="inlineStr">
         <is>
-          <t>batch_43847c5c0d554445</t>
+          <t>batch_0c2ed97284e04906</t>
         </is>
       </c>
       <c r="AU230" t="inlineStr">
@@ -37585,7 +37585,7 @@
       <c r="AW230" t="inlineStr"/>
       <c r="AX230" t="inlineStr">
         <is>
-          <t>2026-05-14T03:06:34+00:00</t>
+          <t>2026-05-14T03:16:15+00:00</t>
         </is>
       </c>
       <c r="AY230" t="inlineStr">
@@ -37729,7 +37729,7 @@
       </c>
       <c r="AT231" t="inlineStr">
         <is>
-          <t>batch_43847c5c0d554445</t>
+          <t>batch_0c2ed97284e04906</t>
         </is>
       </c>
       <c r="AU231" t="inlineStr">
@@ -37745,7 +37745,7 @@
       <c r="AW231" t="inlineStr"/>
       <c r="AX231" t="inlineStr">
         <is>
-          <t>2026-05-14T03:06:34+00:00</t>
+          <t>2026-05-14T03:16:15+00:00</t>
         </is>
       </c>
       <c r="AY231" t="inlineStr">
@@ -37889,7 +37889,7 @@
       </c>
       <c r="AT232" t="inlineStr">
         <is>
-          <t>batch_43847c5c0d554445</t>
+          <t>batch_0c2ed97284e04906</t>
         </is>
       </c>
       <c r="AU232" t="inlineStr">
@@ -37905,7 +37905,7 @@
       <c r="AW232" t="inlineStr"/>
       <c r="AX232" t="inlineStr">
         <is>
-          <t>2026-05-14T03:06:34+00:00</t>
+          <t>2026-05-14T03:16:15+00:00</t>
         </is>
       </c>
       <c r="AY232" t="inlineStr">
@@ -38049,7 +38049,7 @@
       </c>
       <c r="AT233" t="inlineStr">
         <is>
-          <t>batch_43847c5c0d554445</t>
+          <t>batch_0c2ed97284e04906</t>
         </is>
       </c>
       <c r="AU233" t="inlineStr">
@@ -38065,7 +38065,7 @@
       <c r="AW233" t="inlineStr"/>
       <c r="AX233" t="inlineStr">
         <is>
-          <t>2026-05-14T03:06:34+00:00</t>
+          <t>2026-05-14T03:16:15+00:00</t>
         </is>
       </c>
       <c r="AY233" t="inlineStr">
@@ -38209,7 +38209,7 @@
       </c>
       <c r="AT234" t="inlineStr">
         <is>
-          <t>batch_43847c5c0d554445</t>
+          <t>batch_0c2ed97284e04906</t>
         </is>
       </c>
       <c r="AU234" t="inlineStr">
@@ -38225,7 +38225,7 @@
       <c r="AW234" t="inlineStr"/>
       <c r="AX234" t="inlineStr">
         <is>
-          <t>2026-05-14T03:06:34+00:00</t>
+          <t>2026-05-14T03:16:15+00:00</t>
         </is>
       </c>
       <c r="AY234" t="inlineStr">
@@ -38369,7 +38369,7 @@
       </c>
       <c r="AT235" t="inlineStr">
         <is>
-          <t>batch_43847c5c0d554445</t>
+          <t>batch_0c2ed97284e04906</t>
         </is>
       </c>
       <c r="AU235" t="inlineStr">
@@ -38385,7 +38385,7 @@
       <c r="AW235" t="inlineStr"/>
       <c r="AX235" t="inlineStr">
         <is>
-          <t>2026-05-14T03:06:34+00:00</t>
+          <t>2026-05-14T03:16:15+00:00</t>
         </is>
       </c>
       <c r="AY235" t="inlineStr">
@@ -38529,7 +38529,7 @@
       </c>
       <c r="AT236" t="inlineStr">
         <is>
-          <t>batch_43847c5c0d554445</t>
+          <t>batch_0c2ed97284e04906</t>
         </is>
       </c>
       <c r="AU236" t="inlineStr">
@@ -38545,7 +38545,7 @@
       <c r="AW236" t="inlineStr"/>
       <c r="AX236" t="inlineStr">
         <is>
-          <t>2026-05-14T03:06:34+00:00</t>
+          <t>2026-05-14T03:16:15+00:00</t>
         </is>
       </c>
       <c r="AY236" t="inlineStr">
@@ -38689,7 +38689,7 @@
       </c>
       <c r="AT237" t="inlineStr">
         <is>
-          <t>batch_43847c5c0d554445</t>
+          <t>batch_0c2ed97284e04906</t>
         </is>
       </c>
       <c r="AU237" t="inlineStr">
@@ -38705,7 +38705,7 @@
       <c r="AW237" t="inlineStr"/>
       <c r="AX237" t="inlineStr">
         <is>
-          <t>2026-05-14T03:06:34+00:00</t>
+          <t>2026-05-14T03:16:15+00:00</t>
         </is>
       </c>
       <c r="AY237" t="inlineStr">
@@ -38849,7 +38849,7 @@
       </c>
       <c r="AT238" t="inlineStr">
         <is>
-          <t>batch_43847c5c0d554445</t>
+          <t>batch_0c2ed97284e04906</t>
         </is>
       </c>
       <c r="AU238" t="inlineStr">
@@ -38865,7 +38865,7 @@
       <c r="AW238" t="inlineStr"/>
       <c r="AX238" t="inlineStr">
         <is>
-          <t>2026-05-14T03:06:34+00:00</t>
+          <t>2026-05-14T03:16:15+00:00</t>
         </is>
       </c>
       <c r="AY238" t="inlineStr">
@@ -39009,7 +39009,7 @@
       </c>
       <c r="AT239" t="inlineStr">
         <is>
-          <t>batch_43847c5c0d554445</t>
+          <t>batch_0c2ed97284e04906</t>
         </is>
       </c>
       <c r="AU239" t="inlineStr">
@@ -39025,7 +39025,7 @@
       <c r="AW239" t="inlineStr"/>
       <c r="AX239" t="inlineStr">
         <is>
-          <t>2026-05-14T03:06:34+00:00</t>
+          <t>2026-05-14T03:16:15+00:00</t>
         </is>
       </c>
       <c r="AY239" t="inlineStr">
@@ -39169,7 +39169,7 @@
       </c>
       <c r="AT240" t="inlineStr">
         <is>
-          <t>batch_43847c5c0d554445</t>
+          <t>batch_0c2ed97284e04906</t>
         </is>
       </c>
       <c r="AU240" t="inlineStr">
@@ -39185,7 +39185,7 @@
       <c r="AW240" t="inlineStr"/>
       <c r="AX240" t="inlineStr">
         <is>
-          <t>2026-05-14T03:06:34+00:00</t>
+          <t>2026-05-14T03:16:15+00:00</t>
         </is>
       </c>
       <c r="AY240" t="inlineStr">
@@ -39329,7 +39329,7 @@
       </c>
       <c r="AT241" t="inlineStr">
         <is>
-          <t>batch_43847c5c0d554445</t>
+          <t>batch_0c2ed97284e04906</t>
         </is>
       </c>
       <c r="AU241" t="inlineStr">
@@ -39345,7 +39345,7 @@
       <c r="AW241" t="inlineStr"/>
       <c r="AX241" t="inlineStr">
         <is>
-          <t>2026-05-14T03:06:34+00:00</t>
+          <t>2026-05-14T03:16:15+00:00</t>
         </is>
       </c>
       <c r="AY241" t="inlineStr">
@@ -39489,7 +39489,7 @@
       </c>
       <c r="AT242" t="inlineStr">
         <is>
-          <t>batch_43847c5c0d554445</t>
+          <t>batch_0c2ed97284e04906</t>
         </is>
       </c>
       <c r="AU242" t="inlineStr">
@@ -39505,7 +39505,7 @@
       <c r="AW242" t="inlineStr"/>
       <c r="AX242" t="inlineStr">
         <is>
-          <t>2026-05-14T03:06:34+00:00</t>
+          <t>2026-05-14T03:16:15+00:00</t>
         </is>
       </c>
       <c r="AY242" t="inlineStr">
@@ -39649,7 +39649,7 @@
       </c>
       <c r="AT243" t="inlineStr">
         <is>
-          <t>batch_43847c5c0d554445</t>
+          <t>batch_0c2ed97284e04906</t>
         </is>
       </c>
       <c r="AU243" t="inlineStr">
@@ -39665,7 +39665,7 @@
       <c r="AW243" t="inlineStr"/>
       <c r="AX243" t="inlineStr">
         <is>
-          <t>2026-05-14T03:06:34+00:00</t>
+          <t>2026-05-14T03:16:15+00:00</t>
         </is>
       </c>
       <c r="AY243" t="inlineStr">
@@ -39809,7 +39809,7 @@
       </c>
       <c r="AT244" t="inlineStr">
         <is>
-          <t>batch_43847c5c0d554445</t>
+          <t>batch_0c2ed97284e04906</t>
         </is>
       </c>
       <c r="AU244" t="inlineStr">
@@ -39825,7 +39825,7 @@
       <c r="AW244" t="inlineStr"/>
       <c r="AX244" t="inlineStr">
         <is>
-          <t>2026-05-14T03:06:34+00:00</t>
+          <t>2026-05-14T03:16:15+00:00</t>
         </is>
       </c>
       <c r="AY244" t="inlineStr">
@@ -39969,7 +39969,7 @@
       </c>
       <c r="AT245" t="inlineStr">
         <is>
-          <t>batch_43847c5c0d554445</t>
+          <t>batch_0c2ed97284e04906</t>
         </is>
       </c>
       <c r="AU245" t="inlineStr">
@@ -39985,7 +39985,7 @@
       <c r="AW245" t="inlineStr"/>
       <c r="AX245" t="inlineStr">
         <is>
-          <t>2026-05-14T03:06:34+00:00</t>
+          <t>2026-05-14T03:16:15+00:00</t>
         </is>
       </c>
       <c r="AY245" t="inlineStr">
@@ -40129,7 +40129,7 @@
       </c>
       <c r="AT246" t="inlineStr">
         <is>
-          <t>batch_43847c5c0d554445</t>
+          <t>batch_0c2ed97284e04906</t>
         </is>
       </c>
       <c r="AU246" t="inlineStr">
@@ -40145,7 +40145,7 @@
       <c r="AW246" t="inlineStr"/>
       <c r="AX246" t="inlineStr">
         <is>
-          <t>2026-05-14T03:06:34+00:00</t>
+          <t>2026-05-14T03:16:15+00:00</t>
         </is>
       </c>
       <c r="AY246" t="inlineStr">
@@ -40289,7 +40289,7 @@
       </c>
       <c r="AT247" t="inlineStr">
         <is>
-          <t>batch_43847c5c0d554445</t>
+          <t>batch_0c2ed97284e04906</t>
         </is>
       </c>
       <c r="AU247" t="inlineStr">
@@ -40305,7 +40305,7 @@
       <c r="AW247" t="inlineStr"/>
       <c r="AX247" t="inlineStr">
         <is>
-          <t>2026-05-14T03:06:34+00:00</t>
+          <t>2026-05-14T03:16:15+00:00</t>
         </is>
       </c>
       <c r="AY247" t="inlineStr">
@@ -40449,7 +40449,7 @@
       </c>
       <c r="AT248" t="inlineStr">
         <is>
-          <t>batch_43847c5c0d554445</t>
+          <t>batch_0c2ed97284e04906</t>
         </is>
       </c>
       <c r="AU248" t="inlineStr">
@@ -40465,7 +40465,7 @@
       <c r="AW248" t="inlineStr"/>
       <c r="AX248" t="inlineStr">
         <is>
-          <t>2026-05-14T03:06:34+00:00</t>
+          <t>2026-05-14T03:16:15+00:00</t>
         </is>
       </c>
       <c r="AY248" t="inlineStr">
@@ -40609,7 +40609,7 @@
       </c>
       <c r="AT249" t="inlineStr">
         <is>
-          <t>batch_43847c5c0d554445</t>
+          <t>batch_0c2ed97284e04906</t>
         </is>
       </c>
       <c r="AU249" t="inlineStr">
@@ -40625,7 +40625,7 @@
       <c r="AW249" t="inlineStr"/>
       <c r="AX249" t="inlineStr">
         <is>
-          <t>2026-05-14T03:06:34+00:00</t>
+          <t>2026-05-14T03:16:15+00:00</t>
         </is>
       </c>
       <c r="AY249" t="inlineStr">
@@ -40769,7 +40769,7 @@
       </c>
       <c r="AT250" t="inlineStr">
         <is>
-          <t>batch_43847c5c0d554445</t>
+          <t>batch_0c2ed97284e04906</t>
         </is>
       </c>
       <c r="AU250" t="inlineStr">
@@ -40785,7 +40785,7 @@
       <c r="AW250" t="inlineStr"/>
       <c r="AX250" t="inlineStr">
         <is>
-          <t>2026-05-14T03:06:34+00:00</t>
+          <t>2026-05-14T03:16:15+00:00</t>
         </is>
       </c>
       <c r="AY250" t="inlineStr">
@@ -40929,7 +40929,7 @@
       </c>
       <c r="AT251" t="inlineStr">
         <is>
-          <t>batch_43847c5c0d554445</t>
+          <t>batch_0c2ed97284e04906</t>
         </is>
       </c>
       <c r="AU251" t="inlineStr">
@@ -40945,7 +40945,7 @@
       <c r="AW251" t="inlineStr"/>
       <c r="AX251" t="inlineStr">
         <is>
-          <t>2026-05-14T03:06:34+00:00</t>
+          <t>2026-05-14T03:16:15+00:00</t>
         </is>
       </c>
       <c r="AY251" t="inlineStr">
@@ -41089,7 +41089,7 @@
       </c>
       <c r="AT252" t="inlineStr">
         <is>
-          <t>batch_43847c5c0d554445</t>
+          <t>batch_0c2ed97284e04906</t>
         </is>
       </c>
       <c r="AU252" t="inlineStr">
@@ -41105,7 +41105,7 @@
       <c r="AW252" t="inlineStr"/>
       <c r="AX252" t="inlineStr">
         <is>
-          <t>2026-05-14T03:06:34+00:00</t>
+          <t>2026-05-14T03:16:15+00:00</t>
         </is>
       </c>
       <c r="AY252" t="inlineStr">
@@ -41249,7 +41249,7 @@
       </c>
       <c r="AT253" t="inlineStr">
         <is>
-          <t>batch_43847c5c0d554445</t>
+          <t>batch_0c2ed97284e04906</t>
         </is>
       </c>
       <c r="AU253" t="inlineStr">
@@ -41265,7 +41265,7 @@
       <c r="AW253" t="inlineStr"/>
       <c r="AX253" t="inlineStr">
         <is>
-          <t>2026-05-14T03:06:34+00:00</t>
+          <t>2026-05-14T03:16:15+00:00</t>
         </is>
       </c>
       <c r="AY253" t="inlineStr">
@@ -41409,7 +41409,7 @@
       </c>
       <c r="AT254" t="inlineStr">
         <is>
-          <t>batch_43847c5c0d554445</t>
+          <t>batch_0c2ed97284e04906</t>
         </is>
       </c>
       <c r="AU254" t="inlineStr">
@@ -41425,7 +41425,7 @@
       <c r="AW254" t="inlineStr"/>
       <c r="AX254" t="inlineStr">
         <is>
-          <t>2026-05-14T03:06:34+00:00</t>
+          <t>2026-05-14T03:16:15+00:00</t>
         </is>
       </c>
       <c r="AY254" t="inlineStr">
@@ -41569,7 +41569,7 @@
       </c>
       <c r="AT255" t="inlineStr">
         <is>
-          <t>batch_43847c5c0d554445</t>
+          <t>batch_0c2ed97284e04906</t>
         </is>
       </c>
       <c r="AU255" t="inlineStr">
@@ -41585,7 +41585,7 @@
       <c r="AW255" t="inlineStr"/>
       <c r="AX255" t="inlineStr">
         <is>
-          <t>2026-05-14T03:06:34+00:00</t>
+          <t>2026-05-14T03:16:15+00:00</t>
         </is>
       </c>
       <c r="AY255" t="inlineStr">
@@ -41729,7 +41729,7 @@
       </c>
       <c r="AT256" t="inlineStr">
         <is>
-          <t>batch_43847c5c0d554445</t>
+          <t>batch_0c2ed97284e04906</t>
         </is>
       </c>
       <c r="AU256" t="inlineStr">
@@ -41745,7 +41745,7 @@
       <c r="AW256" t="inlineStr"/>
       <c r="AX256" t="inlineStr">
         <is>
-          <t>2026-05-14T03:06:34+00:00</t>
+          <t>2026-05-14T03:16:15+00:00</t>
         </is>
       </c>
       <c r="AY256" t="inlineStr">
@@ -41889,7 +41889,7 @@
       </c>
       <c r="AT257" t="inlineStr">
         <is>
-          <t>batch_43847c5c0d554445</t>
+          <t>batch_0c2ed97284e04906</t>
         </is>
       </c>
       <c r="AU257" t="inlineStr">
@@ -41905,7 +41905,7 @@
       <c r="AW257" t="inlineStr"/>
       <c r="AX257" t="inlineStr">
         <is>
-          <t>2026-05-14T03:06:34+00:00</t>
+          <t>2026-05-14T03:16:15+00:00</t>
         </is>
       </c>
       <c r="AY257" t="inlineStr">
@@ -42049,7 +42049,7 @@
       </c>
       <c r="AT258" t="inlineStr">
         <is>
-          <t>batch_43847c5c0d554445</t>
+          <t>batch_0c2ed97284e04906</t>
         </is>
       </c>
       <c r="AU258" t="inlineStr">
@@ -42065,7 +42065,7 @@
       <c r="AW258" t="inlineStr"/>
       <c r="AX258" t="inlineStr">
         <is>
-          <t>2026-05-14T03:06:34+00:00</t>
+          <t>2026-05-14T03:16:15+00:00</t>
         </is>
       </c>
       <c r="AY258" t="inlineStr">
@@ -42209,7 +42209,7 @@
       </c>
       <c r="AT259" t="inlineStr">
         <is>
-          <t>batch_43847c5c0d554445</t>
+          <t>batch_0c2ed97284e04906</t>
         </is>
       </c>
       <c r="AU259" t="inlineStr">
@@ -42225,7 +42225,7 @@
       <c r="AW259" t="inlineStr"/>
       <c r="AX259" t="inlineStr">
         <is>
-          <t>2026-05-14T03:06:34+00:00</t>
+          <t>2026-05-14T03:16:15+00:00</t>
         </is>
       </c>
       <c r="AY259" t="inlineStr">
@@ -42369,7 +42369,7 @@
       </c>
       <c r="AT260" t="inlineStr">
         <is>
-          <t>batch_43847c5c0d554445</t>
+          <t>batch_0c2ed97284e04906</t>
         </is>
       </c>
       <c r="AU260" t="inlineStr">
@@ -42385,7 +42385,7 @@
       <c r="AW260" t="inlineStr"/>
       <c r="AX260" t="inlineStr">
         <is>
-          <t>2026-05-14T03:06:34+00:00</t>
+          <t>2026-05-14T03:16:15+00:00</t>
         </is>
       </c>
       <c r="AY260" t="inlineStr">
@@ -42529,7 +42529,7 @@
       </c>
       <c r="AT261" t="inlineStr">
         <is>
-          <t>batch_43847c5c0d554445</t>
+          <t>batch_0c2ed97284e04906</t>
         </is>
       </c>
       <c r="AU261" t="inlineStr">
@@ -42545,7 +42545,7 @@
       <c r="AW261" t="inlineStr"/>
       <c r="AX261" t="inlineStr">
         <is>
-          <t>2026-05-14T03:06:34+00:00</t>
+          <t>2026-05-14T03:16:15+00:00</t>
         </is>
       </c>
       <c r="AY261" t="inlineStr">
@@ -42689,7 +42689,7 @@
       </c>
       <c r="AT262" t="inlineStr">
         <is>
-          <t>batch_43847c5c0d554445</t>
+          <t>batch_0c2ed97284e04906</t>
         </is>
       </c>
       <c r="AU262" t="inlineStr">
@@ -42705,7 +42705,7 @@
       <c r="AW262" t="inlineStr"/>
       <c r="AX262" t="inlineStr">
         <is>
-          <t>2026-05-14T03:06:34+00:00</t>
+          <t>2026-05-14T03:16:15+00:00</t>
         </is>
       </c>
       <c r="AY262" t="inlineStr">
@@ -42849,7 +42849,7 @@
       </c>
       <c r="AT263" t="inlineStr">
         <is>
-          <t>batch_43847c5c0d554445</t>
+          <t>batch_0c2ed97284e04906</t>
         </is>
       </c>
       <c r="AU263" t="inlineStr">
@@ -42865,7 +42865,7 @@
       <c r="AW263" t="inlineStr"/>
       <c r="AX263" t="inlineStr">
         <is>
-          <t>2026-05-14T03:06:34+00:00</t>
+          <t>2026-05-14T03:16:15+00:00</t>
         </is>
       </c>
       <c r="AY263" t="inlineStr">
@@ -43009,7 +43009,7 @@
       </c>
       <c r="AT264" t="inlineStr">
         <is>
-          <t>batch_43847c5c0d554445</t>
+          <t>batch_0c2ed97284e04906</t>
         </is>
       </c>
       <c r="AU264" t="inlineStr">
@@ -43025,7 +43025,7 @@
       <c r="AW264" t="inlineStr"/>
       <c r="AX264" t="inlineStr">
         <is>
-          <t>2026-05-14T03:06:34+00:00</t>
+          <t>2026-05-14T03:16:15+00:00</t>
         </is>
       </c>
       <c r="AY264" t="inlineStr">
@@ -43169,7 +43169,7 @@
       </c>
       <c r="AT265" t="inlineStr">
         <is>
-          <t>batch_43847c5c0d554445</t>
+          <t>batch_0c2ed97284e04906</t>
         </is>
       </c>
       <c r="AU265" t="inlineStr">
@@ -43185,7 +43185,7 @@
       <c r="AW265" t="inlineStr"/>
       <c r="AX265" t="inlineStr">
         <is>
-          <t>2026-05-14T03:06:34+00:00</t>
+          <t>2026-05-14T03:16:15+00:00</t>
         </is>
       </c>
       <c r="AY265" t="inlineStr">
@@ -43329,7 +43329,7 @@
       </c>
       <c r="AT266" t="inlineStr">
         <is>
-          <t>batch_43847c5c0d554445</t>
+          <t>batch_0c2ed97284e04906</t>
         </is>
       </c>
       <c r="AU266" t="inlineStr">
@@ -43345,7 +43345,7 @@
       <c r="AW266" t="inlineStr"/>
       <c r="AX266" t="inlineStr">
         <is>
-          <t>2026-05-14T03:06:34+00:00</t>
+          <t>2026-05-14T03:16:15+00:00</t>
         </is>
       </c>
       <c r="AY266" t="inlineStr">
@@ -43489,7 +43489,7 @@
       </c>
       <c r="AT267" t="inlineStr">
         <is>
-          <t>batch_43847c5c0d554445</t>
+          <t>batch_0c2ed97284e04906</t>
         </is>
       </c>
       <c r="AU267" t="inlineStr">
@@ -43505,7 +43505,7 @@
       <c r="AW267" t="inlineStr"/>
       <c r="AX267" t="inlineStr">
         <is>
-          <t>2026-05-14T03:06:34+00:00</t>
+          <t>2026-05-14T03:16:15+00:00</t>
         </is>
       </c>
       <c r="AY267" t="inlineStr">
@@ -43649,7 +43649,7 @@
       </c>
       <c r="AT268" t="inlineStr">
         <is>
-          <t>batch_43847c5c0d554445</t>
+          <t>batch_0c2ed97284e04906</t>
         </is>
       </c>
       <c r="AU268" t="inlineStr">
@@ -43665,7 +43665,7 @@
       <c r="AW268" t="inlineStr"/>
       <c r="AX268" t="inlineStr">
         <is>
-          <t>2026-05-14T03:06:34+00:00</t>
+          <t>2026-05-14T03:16:15+00:00</t>
         </is>
       </c>
       <c r="AY268" t="inlineStr">
@@ -43809,7 +43809,7 @@
       </c>
       <c r="AT269" t="inlineStr">
         <is>
-          <t>batch_43847c5c0d554445</t>
+          <t>batch_0c2ed97284e04906</t>
         </is>
       </c>
       <c r="AU269" t="inlineStr">
@@ -43825,7 +43825,7 @@
       <c r="AW269" t="inlineStr"/>
       <c r="AX269" t="inlineStr">
         <is>
-          <t>2026-05-14T03:06:34+00:00</t>
+          <t>2026-05-14T03:16:15+00:00</t>
         </is>
       </c>
       <c r="AY269" t="inlineStr">
@@ -43969,7 +43969,7 @@
       </c>
       <c r="AT270" t="inlineStr">
         <is>
-          <t>batch_43847c5c0d554445</t>
+          <t>batch_0c2ed97284e04906</t>
         </is>
       </c>
       <c r="AU270" t="inlineStr">
@@ -43985,7 +43985,7 @@
       <c r="AW270" t="inlineStr"/>
       <c r="AX270" t="inlineStr">
         <is>
-          <t>2026-05-14T03:06:34+00:00</t>
+          <t>2026-05-14T03:16:15+00:00</t>
         </is>
       </c>
       <c r="AY270" t="inlineStr">
@@ -44129,7 +44129,7 @@
       </c>
       <c r="AT271" t="inlineStr">
         <is>
-          <t>batch_43847c5c0d554445</t>
+          <t>batch_0c2ed97284e04906</t>
         </is>
       </c>
       <c r="AU271" t="inlineStr">
@@ -44145,7 +44145,7 @@
       <c r="AW271" t="inlineStr"/>
       <c r="AX271" t="inlineStr">
         <is>
-          <t>2026-05-14T03:06:34+00:00</t>
+          <t>2026-05-14T03:16:15+00:00</t>
         </is>
       </c>
       <c r="AY271" t="inlineStr">
@@ -44289,7 +44289,7 @@
       </c>
       <c r="AT272" t="inlineStr">
         <is>
-          <t>batch_43847c5c0d554445</t>
+          <t>batch_0c2ed97284e04906</t>
         </is>
       </c>
       <c r="AU272" t="inlineStr">
@@ -44305,7 +44305,7 @@
       <c r="AW272" t="inlineStr"/>
       <c r="AX272" t="inlineStr">
         <is>
-          <t>2026-05-14T03:06:34+00:00</t>
+          <t>2026-05-14T03:16:15+00:00</t>
         </is>
       </c>
       <c r="AY272" t="inlineStr">
@@ -44449,7 +44449,7 @@
       </c>
       <c r="AT273" t="inlineStr">
         <is>
-          <t>batch_43847c5c0d554445</t>
+          <t>batch_0c2ed97284e04906</t>
         </is>
       </c>
       <c r="AU273" t="inlineStr">
@@ -44465,7 +44465,7 @@
       <c r="AW273" t="inlineStr"/>
       <c r="AX273" t="inlineStr">
         <is>
-          <t>2026-05-14T03:06:34+00:00</t>
+          <t>2026-05-14T03:16:15+00:00</t>
         </is>
       </c>
       <c r="AY273" t="inlineStr">
@@ -44609,7 +44609,7 @@
       </c>
       <c r="AT274" t="inlineStr">
         <is>
-          <t>batch_43847c5c0d554445</t>
+          <t>batch_0c2ed97284e04906</t>
         </is>
       </c>
       <c r="AU274" t="inlineStr">
@@ -44625,7 +44625,7 @@
       <c r="AW274" t="inlineStr"/>
       <c r="AX274" t="inlineStr">
         <is>
-          <t>2026-05-14T03:06:34+00:00</t>
+          <t>2026-05-14T03:16:15+00:00</t>
         </is>
       </c>
       <c r="AY274" t="inlineStr">
@@ -44769,7 +44769,7 @@
       </c>
       <c r="AT275" t="inlineStr">
         <is>
-          <t>batch_43847c5c0d554445</t>
+          <t>batch_0c2ed97284e04906</t>
         </is>
       </c>
       <c r="AU275" t="inlineStr">
@@ -44785,7 +44785,7 @@
       <c r="AW275" t="inlineStr"/>
       <c r="AX275" t="inlineStr">
         <is>
-          <t>2026-05-14T03:06:34+00:00</t>
+          <t>2026-05-14T03:16:15+00:00</t>
         </is>
       </c>
       <c r="AY275" t="inlineStr">
@@ -44929,7 +44929,7 @@
       </c>
       <c r="AT276" t="inlineStr">
         <is>
-          <t>batch_43847c5c0d554445</t>
+          <t>batch_0c2ed97284e04906</t>
         </is>
       </c>
       <c r="AU276" t="inlineStr">
@@ -44945,7 +44945,7 @@
       <c r="AW276" t="inlineStr"/>
       <c r="AX276" t="inlineStr">
         <is>
-          <t>2026-05-14T03:06:34+00:00</t>
+          <t>2026-05-14T03:16:15+00:00</t>
         </is>
       </c>
       <c r="AY276" t="inlineStr">
@@ -45089,7 +45089,7 @@
       </c>
       <c r="AT277" t="inlineStr">
         <is>
-          <t>batch_43847c5c0d554445</t>
+          <t>batch_0c2ed97284e04906</t>
         </is>
       </c>
       <c r="AU277" t="inlineStr">
@@ -45105,7 +45105,7 @@
       <c r="AW277" t="inlineStr"/>
       <c r="AX277" t="inlineStr">
         <is>
-          <t>2026-05-14T03:06:34+00:00</t>
+          <t>2026-05-14T03:16:15+00:00</t>
         </is>
       </c>
       <c r="AY277" t="inlineStr">
@@ -45249,7 +45249,7 @@
       </c>
       <c r="AT278" t="inlineStr">
         <is>
-          <t>batch_43847c5c0d554445</t>
+          <t>batch_0c2ed97284e04906</t>
         </is>
       </c>
       <c r="AU278" t="inlineStr">
@@ -45265,7 +45265,7 @@
       <c r="AW278" t="inlineStr"/>
       <c r="AX278" t="inlineStr">
         <is>
-          <t>2026-05-14T03:06:34+00:00</t>
+          <t>2026-05-14T03:16:15+00:00</t>
         </is>
       </c>
       <c r="AY278" t="inlineStr">
@@ -45409,7 +45409,7 @@
       </c>
       <c r="AT279" t="inlineStr">
         <is>
-          <t>batch_43847c5c0d554445</t>
+          <t>batch_0c2ed97284e04906</t>
         </is>
       </c>
       <c r="AU279" t="inlineStr">
@@ -45425,7 +45425,7 @@
       <c r="AW279" t="inlineStr"/>
       <c r="AX279" t="inlineStr">
         <is>
-          <t>2026-05-14T03:06:34+00:00</t>
+          <t>2026-05-14T03:16:15+00:00</t>
         </is>
       </c>
       <c r="AY279" t="inlineStr">
@@ -45569,7 +45569,7 @@
       </c>
       <c r="AT280" t="inlineStr">
         <is>
-          <t>batch_43847c5c0d554445</t>
+          <t>batch_0c2ed97284e04906</t>
         </is>
       </c>
       <c r="AU280" t="inlineStr">
@@ -45585,7 +45585,7 @@
       <c r="AW280" t="inlineStr"/>
       <c r="AX280" t="inlineStr">
         <is>
-          <t>2026-05-14T03:06:34+00:00</t>
+          <t>2026-05-14T03:16:15+00:00</t>
         </is>
       </c>
       <c r="AY280" t="inlineStr">
@@ -45729,7 +45729,7 @@
       </c>
       <c r="AT281" t="inlineStr">
         <is>
-          <t>batch_43847c5c0d554445</t>
+          <t>batch_0c2ed97284e04906</t>
         </is>
       </c>
       <c r="AU281" t="inlineStr">
@@ -45745,7 +45745,7 @@
       <c r="AW281" t="inlineStr"/>
       <c r="AX281" t="inlineStr">
         <is>
-          <t>2026-05-14T03:06:34+00:00</t>
+          <t>2026-05-14T03:16:15+00:00</t>
         </is>
       </c>
       <c r="AY281" t="inlineStr">
@@ -45889,7 +45889,7 @@
       </c>
       <c r="AT282" t="inlineStr">
         <is>
-          <t>batch_43847c5c0d554445</t>
+          <t>batch_0c2ed97284e04906</t>
         </is>
       </c>
       <c r="AU282" t="inlineStr">
@@ -45905,7 +45905,7 @@
       <c r="AW282" t="inlineStr"/>
       <c r="AX282" t="inlineStr">
         <is>
-          <t>2026-05-14T03:06:34+00:00</t>
+          <t>2026-05-14T03:16:15+00:00</t>
         </is>
       </c>
       <c r="AY282" t="inlineStr">
@@ -46049,7 +46049,7 @@
       </c>
       <c r="AT283" t="inlineStr">
         <is>
-          <t>batch_43847c5c0d554445</t>
+          <t>batch_0c2ed97284e04906</t>
         </is>
       </c>
       <c r="AU283" t="inlineStr">
@@ -46065,7 +46065,7 @@
       <c r="AW283" t="inlineStr"/>
       <c r="AX283" t="inlineStr">
         <is>
-          <t>2026-05-14T03:06:34+00:00</t>
+          <t>2026-05-14T03:16:15+00:00</t>
         </is>
       </c>
       <c r="AY283" t="inlineStr">
@@ -46209,7 +46209,7 @@
       </c>
       <c r="AT284" t="inlineStr">
         <is>
-          <t>batch_43847c5c0d554445</t>
+          <t>batch_0c2ed97284e04906</t>
         </is>
       </c>
       <c r="AU284" t="inlineStr">
@@ -46225,7 +46225,7 @@
       <c r="AW284" t="inlineStr"/>
       <c r="AX284" t="inlineStr">
         <is>
-          <t>2026-05-14T03:06:34+00:00</t>
+          <t>2026-05-14T03:16:15+00:00</t>
         </is>
       </c>
       <c r="AY284" t="inlineStr">
@@ -46369,7 +46369,7 @@
       </c>
       <c r="AT285" t="inlineStr">
         <is>
-          <t>batch_43847c5c0d554445</t>
+          <t>batch_0c2ed97284e04906</t>
         </is>
       </c>
       <c r="AU285" t="inlineStr">
@@ -46385,7 +46385,7 @@
       <c r="AW285" t="inlineStr"/>
       <c r="AX285" t="inlineStr">
         <is>
-          <t>2026-05-14T03:06:34+00:00</t>
+          <t>2026-05-14T03:16:15+00:00</t>
         </is>
       </c>
       <c r="AY285" t="inlineStr">
@@ -46529,7 +46529,7 @@
       </c>
       <c r="AT286" t="inlineStr">
         <is>
-          <t>batch_43847c5c0d554445</t>
+          <t>batch_0c2ed97284e04906</t>
         </is>
       </c>
       <c r="AU286" t="inlineStr">
@@ -46545,7 +46545,7 @@
       <c r="AW286" t="inlineStr"/>
       <c r="AX286" t="inlineStr">
         <is>
-          <t>2026-05-14T03:06:34+00:00</t>
+          <t>2026-05-14T03:16:15+00:00</t>
         </is>
       </c>
       <c r="AY286" t="inlineStr">
@@ -46689,7 +46689,7 @@
       </c>
       <c r="AT287" t="inlineStr">
         <is>
-          <t>batch_43847c5c0d554445</t>
+          <t>batch_0c2ed97284e04906</t>
         </is>
       </c>
       <c r="AU287" t="inlineStr">
@@ -46705,7 +46705,7 @@
       <c r="AW287" t="inlineStr"/>
       <c r="AX287" t="inlineStr">
         <is>
-          <t>2026-05-14T03:06:34+00:00</t>
+          <t>2026-05-14T03:16:15+00:00</t>
         </is>
       </c>
       <c r="AY287" t="inlineStr">
@@ -46849,7 +46849,7 @@
       </c>
       <c r="AT288" t="inlineStr">
         <is>
-          <t>batch_43847c5c0d554445</t>
+          <t>batch_0c2ed97284e04906</t>
         </is>
       </c>
       <c r="AU288" t="inlineStr">
@@ -46865,7 +46865,7 @@
       <c r="AW288" t="inlineStr"/>
       <c r="AX288" t="inlineStr">
         <is>
-          <t>2026-05-14T03:06:34+00:00</t>
+          <t>2026-05-14T03:16:15+00:00</t>
         </is>
       </c>
       <c r="AY288" t="inlineStr">
@@ -47009,7 +47009,7 @@
       </c>
       <c r="AT289" t="inlineStr">
         <is>
-          <t>batch_43847c5c0d554445</t>
+          <t>batch_0c2ed97284e04906</t>
         </is>
       </c>
       <c r="AU289" t="inlineStr">
@@ -47025,7 +47025,7 @@
       <c r="AW289" t="inlineStr"/>
       <c r="AX289" t="inlineStr">
         <is>
-          <t>2026-05-14T03:06:34+00:00</t>
+          <t>2026-05-14T03:16:15+00:00</t>
         </is>
       </c>
       <c r="AY289" t="inlineStr">
@@ -47169,7 +47169,7 @@
       </c>
       <c r="AT290" t="inlineStr">
         <is>
-          <t>batch_43847c5c0d554445</t>
+          <t>batch_0c2ed97284e04906</t>
         </is>
       </c>
       <c r="AU290" t="inlineStr">
@@ -47185,7 +47185,7 @@
       <c r="AW290" t="inlineStr"/>
       <c r="AX290" t="inlineStr">
         <is>
-          <t>2026-05-14T03:06:34+00:00</t>
+          <t>2026-05-14T03:16:15+00:00</t>
         </is>
       </c>
       <c r="AY290" t="inlineStr">
@@ -47329,7 +47329,7 @@
       </c>
       <c r="AT291" t="inlineStr">
         <is>
-          <t>batch_43847c5c0d554445</t>
+          <t>batch_0c2ed97284e04906</t>
         </is>
       </c>
       <c r="AU291" t="inlineStr">
@@ -47345,7 +47345,7 @@
       <c r="AW291" t="inlineStr"/>
       <c r="AX291" t="inlineStr">
         <is>
-          <t>2026-05-14T03:06:34+00:00</t>
+          <t>2026-05-14T03:16:15+00:00</t>
         </is>
       </c>
       <c r="AY291" t="inlineStr">
@@ -47489,7 +47489,7 @@
       </c>
       <c r="AT292" t="inlineStr">
         <is>
-          <t>batch_43847c5c0d554445</t>
+          <t>batch_0c2ed97284e04906</t>
         </is>
       </c>
       <c r="AU292" t="inlineStr">
@@ -47505,7 +47505,7 @@
       <c r="AW292" t="inlineStr"/>
       <c r="AX292" t="inlineStr">
         <is>
-          <t>2026-05-14T03:06:34+00:00</t>
+          <t>2026-05-14T03:16:15+00:00</t>
         </is>
       </c>
       <c r="AY292" t="inlineStr">
@@ -47649,7 +47649,7 @@
       </c>
       <c r="AT293" t="inlineStr">
         <is>
-          <t>batch_43847c5c0d554445</t>
+          <t>batch_0c2ed97284e04906</t>
         </is>
       </c>
       <c r="AU293" t="inlineStr">
@@ -47665,7 +47665,7 @@
       <c r="AW293" t="inlineStr"/>
       <c r="AX293" t="inlineStr">
         <is>
-          <t>2026-05-14T03:06:34+00:00</t>
+          <t>2026-05-14T03:16:15+00:00</t>
         </is>
       </c>
       <c r="AY293" t="inlineStr">
@@ -47809,7 +47809,7 @@
       </c>
       <c r="AT294" t="inlineStr">
         <is>
-          <t>batch_43847c5c0d554445</t>
+          <t>batch_0c2ed97284e04906</t>
         </is>
       </c>
       <c r="AU294" t="inlineStr">
@@ -47825,7 +47825,7 @@
       <c r="AW294" t="inlineStr"/>
       <c r="AX294" t="inlineStr">
         <is>
-          <t>2026-05-14T03:06:34+00:00</t>
+          <t>2026-05-14T03:16:15+00:00</t>
         </is>
       </c>
       <c r="AY294" t="inlineStr">
@@ -47969,7 +47969,7 @@
       </c>
       <c r="AT295" t="inlineStr">
         <is>
-          <t>batch_43847c5c0d554445</t>
+          <t>batch_0c2ed97284e04906</t>
         </is>
       </c>
       <c r="AU295" t="inlineStr">
@@ -47985,7 +47985,7 @@
       <c r="AW295" t="inlineStr"/>
       <c r="AX295" t="inlineStr">
         <is>
-          <t>2026-05-14T03:06:34+00:00</t>
+          <t>2026-05-14T03:16:15+00:00</t>
         </is>
       </c>
       <c r="AY295" t="inlineStr">
@@ -48129,7 +48129,7 @@
       </c>
       <c r="AT296" t="inlineStr">
         <is>
-          <t>batch_43847c5c0d554445</t>
+          <t>batch_0c2ed97284e04906</t>
         </is>
       </c>
       <c r="AU296" t="inlineStr">
@@ -48145,7 +48145,7 @@
       <c r="AW296" t="inlineStr"/>
       <c r="AX296" t="inlineStr">
         <is>
-          <t>2026-05-14T03:06:34+00:00</t>
+          <t>2026-05-14T03:16:15+00:00</t>
         </is>
       </c>
       <c r="AY296" t="inlineStr">
@@ -48289,7 +48289,7 @@
       </c>
       <c r="AT297" t="inlineStr">
         <is>
-          <t>batch_43847c5c0d554445</t>
+          <t>batch_0c2ed97284e04906</t>
         </is>
       </c>
       <c r="AU297" t="inlineStr">
@@ -48305,7 +48305,7 @@
       <c r="AW297" t="inlineStr"/>
       <c r="AX297" t="inlineStr">
         <is>
-          <t>2026-05-14T03:06:34+00:00</t>
+          <t>2026-05-14T03:16:15+00:00</t>
         </is>
       </c>
       <c r="AY297" t="inlineStr">
@@ -48449,7 +48449,7 @@
       </c>
       <c r="AT298" t="inlineStr">
         <is>
-          <t>batch_43847c5c0d554445</t>
+          <t>batch_0c2ed97284e04906</t>
         </is>
       </c>
       <c r="AU298" t="inlineStr">
@@ -48465,7 +48465,7 @@
       <c r="AW298" t="inlineStr"/>
       <c r="AX298" t="inlineStr">
         <is>
-          <t>2026-05-14T03:06:34+00:00</t>
+          <t>2026-05-14T03:16:15+00:00</t>
         </is>
       </c>
       <c r="AY298" t="inlineStr">
@@ -48609,7 +48609,7 @@
       </c>
       <c r="AT299" t="inlineStr">
         <is>
-          <t>batch_43847c5c0d554445</t>
+          <t>batch_0c2ed97284e04906</t>
         </is>
       </c>
       <c r="AU299" t="inlineStr">
@@ -48625,7 +48625,7 @@
       <c r="AW299" t="inlineStr"/>
       <c r="AX299" t="inlineStr">
         <is>
-          <t>2026-05-14T03:06:34+00:00</t>
+          <t>2026-05-14T03:16:15+00:00</t>
         </is>
       </c>
       <c r="AY299" t="inlineStr">
@@ -48769,7 +48769,7 @@
       </c>
       <c r="AT300" t="inlineStr">
         <is>
-          <t>batch_43847c5c0d554445</t>
+          <t>batch_0c2ed97284e04906</t>
         </is>
       </c>
       <c r="AU300" t="inlineStr">
@@ -48785,7 +48785,7 @@
       <c r="AW300" t="inlineStr"/>
       <c r="AX300" t="inlineStr">
         <is>
-          <t>2026-05-14T03:06:34+00:00</t>
+          <t>2026-05-14T03:16:15+00:00</t>
         </is>
       </c>
       <c r="AY300" t="inlineStr">
@@ -48929,7 +48929,7 @@
       </c>
       <c r="AT301" t="inlineStr">
         <is>
-          <t>batch_43847c5c0d554445</t>
+          <t>batch_0c2ed97284e04906</t>
         </is>
       </c>
       <c r="AU301" t="inlineStr">
@@ -48945,7 +48945,7 @@
       <c r="AW301" t="inlineStr"/>
       <c r="AX301" t="inlineStr">
         <is>
-          <t>2026-05-14T03:06:34+00:00</t>
+          <t>2026-05-14T03:16:15+00:00</t>
         </is>
       </c>
       <c r="AY301" t="inlineStr">
@@ -49089,7 +49089,7 @@
       </c>
       <c r="AT302" t="inlineStr">
         <is>
-          <t>batch_43847c5c0d554445</t>
+          <t>batch_0c2ed97284e04906</t>
         </is>
       </c>
       <c r="AU302" t="inlineStr">
@@ -49105,7 +49105,7 @@
       <c r="AW302" t="inlineStr"/>
       <c r="AX302" t="inlineStr">
         <is>
-          <t>2026-05-14T03:06:34+00:00</t>
+          <t>2026-05-14T03:16:15+00:00</t>
         </is>
       </c>
       <c r="AY302" t="inlineStr">
@@ -49249,7 +49249,7 @@
       </c>
       <c r="AT303" t="inlineStr">
         <is>
-          <t>batch_43847c5c0d554445</t>
+          <t>batch_0c2ed97284e04906</t>
         </is>
       </c>
       <c r="AU303" t="inlineStr">
@@ -49265,7 +49265,7 @@
       <c r="AW303" t="inlineStr"/>
       <c r="AX303" t="inlineStr">
         <is>
-          <t>2026-05-14T03:06:34+00:00</t>
+          <t>2026-05-14T03:16:15+00:00</t>
         </is>
       </c>
       <c r="AY303" t="inlineStr">
@@ -49409,7 +49409,7 @@
       </c>
       <c r="AT304" t="inlineStr">
         <is>
-          <t>batch_43847c5c0d554445</t>
+          <t>batch_0c2ed97284e04906</t>
         </is>
       </c>
       <c r="AU304" t="inlineStr">
@@ -49425,7 +49425,7 @@
       <c r="AW304" t="inlineStr"/>
       <c r="AX304" t="inlineStr">
         <is>
-          <t>2026-05-14T03:06:34+00:00</t>
+          <t>2026-05-14T03:16:15+00:00</t>
         </is>
       </c>
       <c r="AY304" t="inlineStr">
@@ -49569,7 +49569,7 @@
       </c>
       <c r="AT305" t="inlineStr">
         <is>
-          <t>batch_43847c5c0d554445</t>
+          <t>batch_0c2ed97284e04906</t>
         </is>
       </c>
       <c r="AU305" t="inlineStr">
@@ -49585,7 +49585,7 @@
       <c r="AW305" t="inlineStr"/>
       <c r="AX305" t="inlineStr">
         <is>
-          <t>2026-05-14T03:06:34+00:00</t>
+          <t>2026-05-14T03:16:15+00:00</t>
         </is>
       </c>
       <c r="AY305" t="inlineStr">
@@ -49729,7 +49729,7 @@
       </c>
       <c r="AT306" t="inlineStr">
         <is>
-          <t>batch_43847c5c0d554445</t>
+          <t>batch_0c2ed97284e04906</t>
         </is>
       </c>
       <c r="AU306" t="inlineStr">
@@ -49745,7 +49745,7 @@
       <c r="AW306" t="inlineStr"/>
       <c r="AX306" t="inlineStr">
         <is>
-          <t>2026-05-14T03:06:34+00:00</t>
+          <t>2026-05-14T03:16:15+00:00</t>
         </is>
       </c>
       <c r="AY306" t="inlineStr">
@@ -49889,7 +49889,7 @@
       </c>
       <c r="AT307" t="inlineStr">
         <is>
-          <t>batch_43847c5c0d554445</t>
+          <t>batch_0c2ed97284e04906</t>
         </is>
       </c>
       <c r="AU307" t="inlineStr">
@@ -49905,7 +49905,7 @@
       <c r="AW307" t="inlineStr"/>
       <c r="AX307" t="inlineStr">
         <is>
-          <t>2026-05-14T03:06:34+00:00</t>
+          <t>2026-05-14T03:16:15+00:00</t>
         </is>
       </c>
       <c r="AY307" t="inlineStr">
@@ -50049,7 +50049,7 @@
       </c>
       <c r="AT308" t="inlineStr">
         <is>
-          <t>batch_43847c5c0d554445</t>
+          <t>batch_0c2ed97284e04906</t>
         </is>
       </c>
       <c r="AU308" t="inlineStr">
@@ -50065,7 +50065,7 @@
       <c r="AW308" t="inlineStr"/>
       <c r="AX308" t="inlineStr">
         <is>
-          <t>2026-05-14T03:06:34+00:00</t>
+          <t>2026-05-14T03:16:15+00:00</t>
         </is>
       </c>
       <c r="AY308" t="inlineStr">
@@ -50209,7 +50209,7 @@
       </c>
       <c r="AT309" t="inlineStr">
         <is>
-          <t>batch_43847c5c0d554445</t>
+          <t>batch_0c2ed97284e04906</t>
         </is>
       </c>
       <c r="AU309" t="inlineStr">
@@ -50225,7 +50225,7 @@
       <c r="AW309" t="inlineStr"/>
       <c r="AX309" t="inlineStr">
         <is>
-          <t>2026-05-14T03:06:34+00:00</t>
+          <t>2026-05-14T03:16:15+00:00</t>
         </is>
       </c>
       <c r="AY309" t="inlineStr">
@@ -50369,7 +50369,7 @@
       </c>
       <c r="AT310" t="inlineStr">
         <is>
-          <t>batch_43847c5c0d554445</t>
+          <t>batch_0c2ed97284e04906</t>
         </is>
       </c>
       <c r="AU310" t="inlineStr">
@@ -50385,7 +50385,7 @@
       <c r="AW310" t="inlineStr"/>
       <c r="AX310" t="inlineStr">
         <is>
-          <t>2026-05-14T03:06:34+00:00</t>
+          <t>2026-05-14T03:16:15+00:00</t>
         </is>
       </c>
       <c r="AY310" t="inlineStr">
@@ -50529,7 +50529,7 @@
       </c>
       <c r="AT311" t="inlineStr">
         <is>
-          <t>batch_43847c5c0d554445</t>
+          <t>batch_0c2ed97284e04906</t>
         </is>
       </c>
       <c r="AU311" t="inlineStr">
@@ -50545,7 +50545,7 @@
       <c r="AW311" t="inlineStr"/>
       <c r="AX311" t="inlineStr">
         <is>
-          <t>2026-05-14T03:06:34+00:00</t>
+          <t>2026-05-14T03:16:15+00:00</t>
         </is>
       </c>
       <c r="AY311" t="inlineStr">
@@ -50689,7 +50689,7 @@
       </c>
       <c r="AT312" t="inlineStr">
         <is>
-          <t>batch_43847c5c0d554445</t>
+          <t>batch_0c2ed97284e04906</t>
         </is>
       </c>
       <c r="AU312" t="inlineStr">
@@ -50705,7 +50705,7 @@
       <c r="AW312" t="inlineStr"/>
       <c r="AX312" t="inlineStr">
         <is>
-          <t>2026-05-14T03:06:34+00:00</t>
+          <t>2026-05-14T03:16:15+00:00</t>
         </is>
       </c>
       <c r="AY312" t="inlineStr">
@@ -50849,7 +50849,7 @@
       </c>
       <c r="AT313" t="inlineStr">
         <is>
-          <t>batch_43847c5c0d554445</t>
+          <t>batch_0c2ed97284e04906</t>
         </is>
       </c>
       <c r="AU313" t="inlineStr">
@@ -50865,7 +50865,7 @@
       <c r="AW313" t="inlineStr"/>
       <c r="AX313" t="inlineStr">
         <is>
-          <t>2026-05-14T03:06:34+00:00</t>
+          <t>2026-05-14T03:16:15+00:00</t>
         </is>
       </c>
       <c r="AY313" t="inlineStr">
@@ -51009,7 +51009,7 @@
       </c>
       <c r="AT314" t="inlineStr">
         <is>
-          <t>batch_43847c5c0d554445</t>
+          <t>batch_0c2ed97284e04906</t>
         </is>
       </c>
       <c r="AU314" t="inlineStr">
@@ -51025,7 +51025,7 @@
       <c r="AW314" t="inlineStr"/>
       <c r="AX314" t="inlineStr">
         <is>
-          <t>2026-05-14T03:06:34+00:00</t>
+          <t>2026-05-14T03:16:15+00:00</t>
         </is>
       </c>
       <c r="AY314" t="inlineStr">
@@ -51169,7 +51169,7 @@
       </c>
       <c r="AT315" t="inlineStr">
         <is>
-          <t>batch_43847c5c0d554445</t>
+          <t>batch_0c2ed97284e04906</t>
         </is>
       </c>
       <c r="AU315" t="inlineStr">
@@ -51185,7 +51185,7 @@
       <c r="AW315" t="inlineStr"/>
       <c r="AX315" t="inlineStr">
         <is>
-          <t>2026-05-14T03:06:34+00:00</t>
+          <t>2026-05-14T03:16:15+00:00</t>
         </is>
       </c>
       <c r="AY315" t="inlineStr">
@@ -51329,7 +51329,7 @@
       </c>
       <c r="AT316" t="inlineStr">
         <is>
-          <t>batch_43847c5c0d554445</t>
+          <t>batch_0c2ed97284e04906</t>
         </is>
       </c>
       <c r="AU316" t="inlineStr">
@@ -51345,7 +51345,7 @@
       <c r="AW316" t="inlineStr"/>
       <c r="AX316" t="inlineStr">
         <is>
-          <t>2026-05-14T03:06:34+00:00</t>
+          <t>2026-05-14T03:16:15+00:00</t>
         </is>
       </c>
       <c r="AY316" t="inlineStr">
@@ -51489,7 +51489,7 @@
       </c>
       <c r="AT317" t="inlineStr">
         <is>
-          <t>batch_43847c5c0d554445</t>
+          <t>batch_0c2ed97284e04906</t>
         </is>
       </c>
       <c r="AU317" t="inlineStr">
@@ -51505,7 +51505,7 @@
       <c r="AW317" t="inlineStr"/>
       <c r="AX317" t="inlineStr">
         <is>
-          <t>2026-05-14T03:06:34+00:00</t>
+          <t>2026-05-14T03:16:15+00:00</t>
         </is>
       </c>
       <c r="AY317" t="inlineStr">
@@ -51649,7 +51649,7 @@
       </c>
       <c r="AT318" t="inlineStr">
         <is>
-          <t>batch_43847c5c0d554445</t>
+          <t>batch_0c2ed97284e04906</t>
         </is>
       </c>
       <c r="AU318" t="inlineStr">
@@ -51665,7 +51665,7 @@
       <c r="AW318" t="inlineStr"/>
       <c r="AX318" t="inlineStr">
         <is>
-          <t>2026-05-14T03:06:34+00:00</t>
+          <t>2026-05-14T03:16:15+00:00</t>
         </is>
       </c>
       <c r="AY318" t="inlineStr">
@@ -51809,7 +51809,7 @@
       </c>
       <c r="AT319" t="inlineStr">
         <is>
-          <t>batch_43847c5c0d554445</t>
+          <t>batch_0c2ed97284e04906</t>
         </is>
       </c>
       <c r="AU319" t="inlineStr">
@@ -51825,7 +51825,7 @@
       <c r="AW319" t="inlineStr"/>
       <c r="AX319" t="inlineStr">
         <is>
-          <t>2026-05-14T03:06:34+00:00</t>
+          <t>2026-05-14T03:16:15+00:00</t>
         </is>
       </c>
       <c r="AY319" t="inlineStr">
@@ -51969,7 +51969,7 @@
       </c>
       <c r="AT320" t="inlineStr">
         <is>
-          <t>batch_43847c5c0d554445</t>
+          <t>batch_0c2ed97284e04906</t>
         </is>
       </c>
       <c r="AU320" t="inlineStr">
@@ -51985,7 +51985,7 @@
       <c r="AW320" t="inlineStr"/>
       <c r="AX320" t="inlineStr">
         <is>
-          <t>2026-05-14T03:06:34+00:00</t>
+          <t>2026-05-14T03:16:15+00:00</t>
         </is>
       </c>
       <c r="AY320" t="inlineStr">
@@ -52129,7 +52129,7 @@
       </c>
       <c r="AT321" t="inlineStr">
         <is>
-          <t>batch_43847c5c0d554445</t>
+          <t>batch_0c2ed97284e04906</t>
         </is>
       </c>
       <c r="AU321" t="inlineStr">
@@ -52145,7 +52145,7 @@
       <c r="AW321" t="inlineStr"/>
       <c r="AX321" t="inlineStr">
         <is>
-          <t>2026-05-14T03:06:34+00:00</t>
+          <t>2026-05-14T03:16:15+00:00</t>
         </is>
       </c>
       <c r="AY321" t="inlineStr">
@@ -52289,7 +52289,7 @@
       </c>
       <c r="AT322" t="inlineStr">
         <is>
-          <t>batch_43847c5c0d554445</t>
+          <t>batch_0c2ed97284e04906</t>
         </is>
       </c>
       <c r="AU322" t="inlineStr">
@@ -52305,7 +52305,7 @@
       <c r="AW322" t="inlineStr"/>
       <c r="AX322" t="inlineStr">
         <is>
-          <t>2026-05-14T03:06:34+00:00</t>
+          <t>2026-05-14T03:16:15+00:00</t>
         </is>
       </c>
       <c r="AY322" t="inlineStr">
@@ -52449,7 +52449,7 @@
       </c>
       <c r="AT323" t="inlineStr">
         <is>
-          <t>batch_43847c5c0d554445</t>
+          <t>batch_0c2ed97284e04906</t>
         </is>
       </c>
       <c r="AU323" t="inlineStr">
@@ -52465,7 +52465,7 @@
       <c r="AW323" t="inlineStr"/>
       <c r="AX323" t="inlineStr">
         <is>
-          <t>2026-05-14T03:06:34+00:00</t>
+          <t>2026-05-14T03:16:15+00:00</t>
         </is>
       </c>
       <c r="AY323" t="inlineStr">
@@ -52609,7 +52609,7 @@
       </c>
       <c r="AT324" t="inlineStr">
         <is>
-          <t>batch_43847c5c0d554445</t>
+          <t>batch_0c2ed97284e04906</t>
         </is>
       </c>
       <c r="AU324" t="inlineStr">
@@ -52625,7 +52625,7 @@
       <c r="AW324" t="inlineStr"/>
       <c r="AX324" t="inlineStr">
         <is>
-          <t>2026-05-14T03:06:34+00:00</t>
+          <t>2026-05-14T03:16:15+00:00</t>
         </is>
       </c>
       <c r="AY324" t="inlineStr">
@@ -52769,7 +52769,7 @@
       </c>
       <c r="AT325" t="inlineStr">
         <is>
-          <t>batch_43847c5c0d554445</t>
+          <t>batch_0c2ed97284e04906</t>
         </is>
       </c>
       <c r="AU325" t="inlineStr">
@@ -52785,7 +52785,7 @@
       <c r="AW325" t="inlineStr"/>
       <c r="AX325" t="inlineStr">
         <is>
-          <t>2026-05-14T03:06:34+00:00</t>
+          <t>2026-05-14T03:16:15+00:00</t>
         </is>
       </c>
       <c r="AY325" t="inlineStr">
@@ -52929,7 +52929,7 @@
       </c>
       <c r="AT326" t="inlineStr">
         <is>
-          <t>batch_43847c5c0d554445</t>
+          <t>batch_0c2ed97284e04906</t>
         </is>
       </c>
       <c r="AU326" t="inlineStr">
@@ -52945,7 +52945,7 @@
       <c r="AW326" t="inlineStr"/>
       <c r="AX326" t="inlineStr">
         <is>
-          <t>2026-05-14T03:06:34+00:00</t>
+          <t>2026-05-14T03:16:15+00:00</t>
         </is>
       </c>
       <c r="AY326" t="inlineStr">
@@ -53089,7 +53089,7 @@
       </c>
       <c r="AT327" t="inlineStr">
         <is>
-          <t>batch_43847c5c0d554445</t>
+          <t>batch_0c2ed97284e04906</t>
         </is>
       </c>
       <c r="AU327" t="inlineStr">
@@ -53105,7 +53105,7 @@
       <c r="AW327" t="inlineStr"/>
       <c r="AX327" t="inlineStr">
         <is>
-          <t>2026-05-14T03:06:34+00:00</t>
+          <t>2026-05-14T03:16:15+00:00</t>
         </is>
       </c>
       <c r="AY327" t="inlineStr">
@@ -53249,7 +53249,7 @@
       </c>
       <c r="AT328" t="inlineStr">
         <is>
-          <t>batch_43847c5c0d554445</t>
+          <t>batch_0c2ed97284e04906</t>
         </is>
       </c>
       <c r="AU328" t="inlineStr">
@@ -53265,7 +53265,7 @@
       <c r="AW328" t="inlineStr"/>
       <c r="AX328" t="inlineStr">
         <is>
-          <t>2026-05-14T03:06:34+00:00</t>
+          <t>2026-05-14T03:16:15+00:00</t>
         </is>
       </c>
       <c r="AY328" t="inlineStr">
@@ -53409,7 +53409,7 @@
       </c>
       <c r="AT329" t="inlineStr">
         <is>
-          <t>batch_43847c5c0d554445</t>
+          <t>batch_0c2ed97284e04906</t>
         </is>
       </c>
       <c r="AU329" t="inlineStr">
@@ -53425,7 +53425,7 @@
       <c r="AW329" t="inlineStr"/>
       <c r="AX329" t="inlineStr">
         <is>
-          <t>2026-05-14T03:06:34+00:00</t>
+          <t>2026-05-14T03:16:15+00:00</t>
         </is>
       </c>
       <c r="AY329" t="inlineStr">
@@ -53569,7 +53569,7 @@
       </c>
       <c r="AT330" t="inlineStr">
         <is>
-          <t>batch_43847c5c0d554445</t>
+          <t>batch_0c2ed97284e04906</t>
         </is>
       </c>
       <c r="AU330" t="inlineStr">
@@ -53585,7 +53585,7 @@
       <c r="AW330" t="inlineStr"/>
       <c r="AX330" t="inlineStr">
         <is>
-          <t>2026-05-14T03:06:34+00:00</t>
+          <t>2026-05-14T03:16:15+00:00</t>
         </is>
       </c>
       <c r="AY330" t="inlineStr">
@@ -53729,7 +53729,7 @@
       </c>
       <c r="AT331" t="inlineStr">
         <is>
-          <t>batch_43847c5c0d554445</t>
+          <t>batch_0c2ed97284e04906</t>
         </is>
       </c>
       <c r="AU331" t="inlineStr">
@@ -53745,7 +53745,7 @@
       <c r="AW331" t="inlineStr"/>
       <c r="AX331" t="inlineStr">
         <is>
-          <t>2026-05-14T03:06:34+00:00</t>
+          <t>2026-05-14T03:16:15+00:00</t>
         </is>
       </c>
       <c r="AY331" t="inlineStr">
@@ -53889,7 +53889,7 @@
       </c>
       <c r="AT332" t="inlineStr">
         <is>
-          <t>batch_43847c5c0d554445</t>
+          <t>batch_0c2ed97284e04906</t>
         </is>
       </c>
       <c r="AU332" t="inlineStr">
@@ -53905,7 +53905,7 @@
       <c r="AW332" t="inlineStr"/>
       <c r="AX332" t="inlineStr">
         <is>
-          <t>2026-05-14T03:06:34+00:00</t>
+          <t>2026-05-14T03:16:15+00:00</t>
         </is>
       </c>
       <c r="AY332" t="inlineStr">
@@ -54049,7 +54049,7 @@
       </c>
       <c r="AT333" t="inlineStr">
         <is>
-          <t>batch_43847c5c0d554445</t>
+          <t>batch_0c2ed97284e04906</t>
         </is>
       </c>
       <c r="AU333" t="inlineStr">
@@ -54065,7 +54065,7 @@
       <c r="AW333" t="inlineStr"/>
       <c r="AX333" t="inlineStr">
         <is>
-          <t>2026-05-14T03:06:34+00:00</t>
+          <t>2026-05-14T03:16:15+00:00</t>
         </is>
       </c>
       <c r="AY333" t="inlineStr">
@@ -54209,7 +54209,7 @@
       </c>
       <c r="AT334" t="inlineStr">
         <is>
-          <t>batch_43847c5c0d554445</t>
+          <t>batch_0c2ed97284e04906</t>
         </is>
       </c>
       <c r="AU334" t="inlineStr">
@@ -54225,7 +54225,7 @@
       <c r="AW334" t="inlineStr"/>
       <c r="AX334" t="inlineStr">
         <is>
-          <t>2026-05-14T03:06:34+00:00</t>
+          <t>2026-05-14T03:16:15+00:00</t>
         </is>
       </c>
       <c r="AY334" t="inlineStr">
@@ -54369,7 +54369,7 @@
       </c>
       <c r="AT335" t="inlineStr">
         <is>
-          <t>batch_43847c5c0d554445</t>
+          <t>batch_0c2ed97284e04906</t>
         </is>
       </c>
       <c r="AU335" t="inlineStr">
@@ -54385,7 +54385,7 @@
       <c r="AW335" t="inlineStr"/>
       <c r="AX335" t="inlineStr">
         <is>
-          <t>2026-05-14T03:06:34+00:00</t>
+          <t>2026-05-14T03:16:15+00:00</t>
         </is>
       </c>
       <c r="AY335" t="inlineStr">
@@ -54529,7 +54529,7 @@
       </c>
       <c r="AT336" t="inlineStr">
         <is>
-          <t>batch_43847c5c0d554445</t>
+          <t>batch_0c2ed97284e04906</t>
         </is>
       </c>
       <c r="AU336" t="inlineStr">
@@ -54545,7 +54545,7 @@
       <c r="AW336" t="inlineStr"/>
       <c r="AX336" t="inlineStr">
         <is>
-          <t>2026-05-14T03:06:34+00:00</t>
+          <t>2026-05-14T03:16:15+00:00</t>
         </is>
       </c>
       <c r="AY336" t="inlineStr">
@@ -54689,7 +54689,7 @@
       </c>
       <c r="AT337" t="inlineStr">
         <is>
-          <t>batch_43847c5c0d554445</t>
+          <t>batch_0c2ed97284e04906</t>
         </is>
       </c>
       <c r="AU337" t="inlineStr">
@@ -54705,7 +54705,7 @@
       <c r="AW337" t="inlineStr"/>
       <c r="AX337" t="inlineStr">
         <is>
-          <t>2026-05-14T03:06:34+00:00</t>
+          <t>2026-05-14T03:16:15+00:00</t>
         </is>
       </c>
       <c r="AY337" t="inlineStr">
@@ -54849,7 +54849,7 @@
       </c>
       <c r="AT338" t="inlineStr">
         <is>
-          <t>batch_43847c5c0d554445</t>
+          <t>batch_0c2ed97284e04906</t>
         </is>
       </c>
       <c r="AU338" t="inlineStr">
@@ -54865,7 +54865,7 @@
       <c r="AW338" t="inlineStr"/>
       <c r="AX338" t="inlineStr">
         <is>
-          <t>2026-05-14T03:06:34+00:00</t>
+          <t>2026-05-14T03:16:15+00:00</t>
         </is>
       </c>
       <c r="AY338" t="inlineStr">
@@ -55009,7 +55009,7 @@
       </c>
       <c r="AT339" t="inlineStr">
         <is>
-          <t>batch_43847c5c0d554445</t>
+          <t>batch_0c2ed97284e04906</t>
         </is>
       </c>
       <c r="AU339" t="inlineStr">
@@ -55025,7 +55025,7 @@
       <c r="AW339" t="inlineStr"/>
       <c r="AX339" t="inlineStr">
         <is>
-          <t>2026-05-14T03:06:34+00:00</t>
+          <t>2026-05-14T03:16:15+00:00</t>
         </is>
       </c>
       <c r="AY339" t="inlineStr">
@@ -55169,7 +55169,7 @@
       </c>
       <c r="AT340" t="inlineStr">
         <is>
-          <t>batch_43847c5c0d554445</t>
+          <t>batch_0c2ed97284e04906</t>
         </is>
       </c>
       <c r="AU340" t="inlineStr">
@@ -55185,7 +55185,7 @@
       <c r="AW340" t="inlineStr"/>
       <c r="AX340" t="inlineStr">
         <is>
-          <t>2026-05-14T03:06:34+00:00</t>
+          <t>2026-05-14T03:16:15+00:00</t>
         </is>
       </c>
       <c r="AY340" t="inlineStr">
@@ -55329,7 +55329,7 @@
       </c>
       <c r="AT341" t="inlineStr">
         <is>
-          <t>batch_43847c5c0d554445</t>
+          <t>batch_0c2ed97284e04906</t>
         </is>
       </c>
       <c r="AU341" t="inlineStr">
@@ -55345,7 +55345,7 @@
       <c r="AW341" t="inlineStr"/>
       <c r="AX341" t="inlineStr">
         <is>
-          <t>2026-05-14T03:06:34+00:00</t>
+          <t>2026-05-14T03:16:15+00:00</t>
         </is>
       </c>
       <c r="AY341" t="inlineStr">
@@ -55489,7 +55489,7 @@
       </c>
       <c r="AT342" t="inlineStr">
         <is>
-          <t>batch_43847c5c0d554445</t>
+          <t>batch_0c2ed97284e04906</t>
         </is>
       </c>
       <c r="AU342" t="inlineStr">
@@ -55505,7 +55505,7 @@
       <c r="AW342" t="inlineStr"/>
       <c r="AX342" t="inlineStr">
         <is>
-          <t>2026-05-14T03:06:34+00:00</t>
+          <t>2026-05-14T03:16:15+00:00</t>
         </is>
       </c>
       <c r="AY342" t="inlineStr">
@@ -55649,7 +55649,7 @@
       </c>
       <c r="AT343" t="inlineStr">
         <is>
-          <t>batch_43847c5c0d554445</t>
+          <t>batch_0c2ed97284e04906</t>
         </is>
       </c>
       <c r="AU343" t="inlineStr">
@@ -55665,7 +55665,7 @@
       <c r="AW343" t="inlineStr"/>
       <c r="AX343" t="inlineStr">
         <is>
-          <t>2026-05-14T03:06:34+00:00</t>
+          <t>2026-05-14T03:16:15+00:00</t>
         </is>
       </c>
       <c r="AY343" t="inlineStr">
@@ -55809,7 +55809,7 @@
       </c>
       <c r="AT344" t="inlineStr">
         <is>
-          <t>batch_43847c5c0d554445</t>
+          <t>batch_0c2ed97284e04906</t>
         </is>
       </c>
       <c r="AU344" t="inlineStr">
@@ -55825,7 +55825,7 @@
       <c r="AW344" t="inlineStr"/>
       <c r="AX344" t="inlineStr">
         <is>
-          <t>2026-05-14T03:06:34+00:00</t>
+          <t>2026-05-14T03:16:15+00:00</t>
         </is>
       </c>
       <c r="AY344" t="inlineStr">
@@ -55969,7 +55969,7 @@
       </c>
       <c r="AT345" t="inlineStr">
         <is>
-          <t>batch_43847c5c0d554445</t>
+          <t>batch_0c2ed97284e04906</t>
         </is>
       </c>
       <c r="AU345" t="inlineStr">
@@ -55985,7 +55985,7 @@
       <c r="AW345" t="inlineStr"/>
       <c r="AX345" t="inlineStr">
         <is>
-          <t>2026-05-14T03:06:34+00:00</t>
+          <t>2026-05-14T03:16:15+00:00</t>
         </is>
       </c>
       <c r="AY345" t="inlineStr">
@@ -56129,7 +56129,7 @@
       </c>
       <c r="AT346" t="inlineStr">
         <is>
-          <t>batch_43847c5c0d554445</t>
+          <t>batch_0c2ed97284e04906</t>
         </is>
       </c>
       <c r="AU346" t="inlineStr">
@@ -56145,7 +56145,7 @@
       <c r="AW346" t="inlineStr"/>
       <c r="AX346" t="inlineStr">
         <is>
-          <t>2026-05-14T03:06:34+00:00</t>
+          <t>2026-05-14T03:16:15+00:00</t>
         </is>
       </c>
       <c r="AY346" t="inlineStr">
@@ -56289,7 +56289,7 @@
       </c>
       <c r="AT347" t="inlineStr">
         <is>
-          <t>batch_43847c5c0d554445</t>
+          <t>batch_0c2ed97284e04906</t>
         </is>
       </c>
       <c r="AU347" t="inlineStr">
@@ -56305,7 +56305,7 @@
       <c r="AW347" t="inlineStr"/>
       <c r="AX347" t="inlineStr">
         <is>
-          <t>2026-05-14T03:06:34+00:00</t>
+          <t>2026-05-14T03:16:15+00:00</t>
         </is>
       </c>
       <c r="AY347" t="inlineStr">
@@ -56449,7 +56449,7 @@
       </c>
       <c r="AT348" t="inlineStr">
         <is>
-          <t>batch_43847c5c0d554445</t>
+          <t>batch_0c2ed97284e04906</t>
         </is>
       </c>
       <c r="AU348" t="inlineStr">
@@ -56465,7 +56465,7 @@
       <c r="AW348" t="inlineStr"/>
       <c r="AX348" t="inlineStr">
         <is>
-          <t>2026-05-14T03:06:34+00:00</t>
+          <t>2026-05-14T03:16:15+00:00</t>
         </is>
       </c>
       <c r="AY348" t="inlineStr">
@@ -56609,7 +56609,7 @@
       </c>
       <c r="AT349" t="inlineStr">
         <is>
-          <t>batch_43847c5c0d554445</t>
+          <t>batch_0c2ed97284e04906</t>
         </is>
       </c>
       <c r="AU349" t="inlineStr">
@@ -56625,7 +56625,7 @@
       <c r="AW349" t="inlineStr"/>
       <c r="AX349" t="inlineStr">
         <is>
-          <t>2026-05-14T03:06:34+00:00</t>
+          <t>2026-05-14T03:16:15+00:00</t>
         </is>
       </c>
       <c r="AY349" t="inlineStr">
@@ -56754,7 +56754,7 @@
       </c>
       <c r="AT350" t="inlineStr">
         <is>
-          <t>batch_43847c5c0d554445</t>
+          <t>batch_0c2ed97284e04906</t>
         </is>
       </c>
       <c r="AU350" t="inlineStr">
@@ -56770,7 +56770,7 @@
       <c r="AW350" t="inlineStr"/>
       <c r="AX350" t="inlineStr">
         <is>
-          <t>2026-05-14T03:06:34+00:00</t>
+          <t>2026-05-14T03:16:15+00:00</t>
         </is>
       </c>
       <c r="AY350" t="inlineStr">
@@ -56899,7 +56899,7 @@
       </c>
       <c r="AT351" t="inlineStr">
         <is>
-          <t>batch_43847c5c0d554445</t>
+          <t>batch_0c2ed97284e04906</t>
         </is>
       </c>
       <c r="AU351" t="inlineStr">
@@ -56915,7 +56915,7 @@
       <c r="AW351" t="inlineStr"/>
       <c r="AX351" t="inlineStr">
         <is>
-          <t>2026-05-14T03:06:34+00:00</t>
+          <t>2026-05-14T03:16:15+00:00</t>
         </is>
       </c>
       <c r="AY351" t="inlineStr">
@@ -57044,7 +57044,7 @@
       </c>
       <c r="AT352" t="inlineStr">
         <is>
-          <t>batch_43847c5c0d554445</t>
+          <t>batch_0c2ed97284e04906</t>
         </is>
       </c>
       <c r="AU352" t="inlineStr">
@@ -57060,7 +57060,7 @@
       <c r="AW352" t="inlineStr"/>
       <c r="AX352" t="inlineStr">
         <is>
-          <t>2026-05-14T03:06:34+00:00</t>
+          <t>2026-05-14T03:16:15+00:00</t>
         </is>
       </c>
       <c r="AY352" t="inlineStr">
@@ -57189,7 +57189,7 @@
       </c>
       <c r="AT353" t="inlineStr">
         <is>
-          <t>batch_43847c5c0d554445</t>
+          <t>batch_0c2ed97284e04906</t>
         </is>
       </c>
       <c r="AU353" t="inlineStr">
@@ -57205,7 +57205,7 @@
       <c r="AW353" t="inlineStr"/>
       <c r="AX353" t="inlineStr">
         <is>
-          <t>2026-05-14T03:06:34+00:00</t>
+          <t>2026-05-14T03:16:15+00:00</t>
         </is>
       </c>
       <c r="AY353" t="inlineStr">
@@ -57334,7 +57334,7 @@
       </c>
       <c r="AT354" t="inlineStr">
         <is>
-          <t>batch_43847c5c0d554445</t>
+          <t>batch_0c2ed97284e04906</t>
         </is>
       </c>
       <c r="AU354" t="inlineStr">
@@ -57350,7 +57350,7 @@
       <c r="AW354" t="inlineStr"/>
       <c r="AX354" t="inlineStr">
         <is>
-          <t>2026-05-14T03:06:34+00:00</t>
+          <t>2026-05-14T03:16:15+00:00</t>
         </is>
       </c>
       <c r="AY354" t="inlineStr">
@@ -57479,7 +57479,7 @@
       </c>
       <c r="AT355" t="inlineStr">
         <is>
-          <t>batch_43847c5c0d554445</t>
+          <t>batch_0c2ed97284e04906</t>
         </is>
       </c>
       <c r="AU355" t="inlineStr">
@@ -57495,7 +57495,7 @@
       <c r="AW355" t="inlineStr"/>
       <c r="AX355" t="inlineStr">
         <is>
-          <t>2026-05-14T03:06:34+00:00</t>
+          <t>2026-05-14T03:16:15+00:00</t>
         </is>
       </c>
       <c r="AY355" t="inlineStr">
@@ -57624,7 +57624,7 @@
       </c>
       <c r="AT356" t="inlineStr">
         <is>
-          <t>batch_43847c5c0d554445</t>
+          <t>batch_0c2ed97284e04906</t>
         </is>
       </c>
       <c r="AU356" t="inlineStr">
@@ -57640,7 +57640,7 @@
       <c r="AW356" t="inlineStr"/>
       <c r="AX356" t="inlineStr">
         <is>
-          <t>2026-05-14T03:06:34+00:00</t>
+          <t>2026-05-14T03:16:15+00:00</t>
         </is>
       </c>
       <c r="AY356" t="inlineStr">
@@ -57769,7 +57769,7 @@
       </c>
       <c r="AT357" t="inlineStr">
         <is>
-          <t>batch_43847c5c0d554445</t>
+          <t>batch_0c2ed97284e04906</t>
         </is>
       </c>
       <c r="AU357" t="inlineStr">
@@ -57785,7 +57785,7 @@
       <c r="AW357" t="inlineStr"/>
       <c r="AX357" t="inlineStr">
         <is>
-          <t>2026-05-14T03:06:34+00:00</t>
+          <t>2026-05-14T03:16:15+00:00</t>
         </is>
       </c>
       <c r="AY357" t="inlineStr">
@@ -57914,7 +57914,7 @@
       </c>
       <c r="AT358" t="inlineStr">
         <is>
-          <t>batch_43847c5c0d554445</t>
+          <t>batch_0c2ed97284e04906</t>
         </is>
       </c>
       <c r="AU358" t="inlineStr">
@@ -57930,7 +57930,7 @@
       <c r="AW358" t="inlineStr"/>
       <c r="AX358" t="inlineStr">
         <is>
-          <t>2026-05-14T03:06:34+00:00</t>
+          <t>2026-05-14T03:16:15+00:00</t>
         </is>
       </c>
       <c r="AY358" t="inlineStr">
@@ -58059,7 +58059,7 @@
       </c>
       <c r="AT359" t="inlineStr">
         <is>
-          <t>batch_43847c5c0d554445</t>
+          <t>batch_0c2ed97284e04906</t>
         </is>
       </c>
       <c r="AU359" t="inlineStr">
@@ -58075,7 +58075,7 @@
       <c r="AW359" t="inlineStr"/>
       <c r="AX359" t="inlineStr">
         <is>
-          <t>2026-05-14T03:06:34+00:00</t>
+          <t>2026-05-14T03:16:15+00:00</t>
         </is>
       </c>
       <c r="AY359" t="inlineStr">
@@ -58204,7 +58204,7 @@
       </c>
       <c r="AT360" t="inlineStr">
         <is>
-          <t>batch_43847c5c0d554445</t>
+          <t>batch_0c2ed97284e04906</t>
         </is>
       </c>
       <c r="AU360" t="inlineStr">
@@ -58220,7 +58220,7 @@
       <c r="AW360" t="inlineStr"/>
       <c r="AX360" t="inlineStr">
         <is>
-          <t>2026-05-14T03:06:34+00:00</t>
+          <t>2026-05-14T03:16:15+00:00</t>
         </is>
       </c>
       <c r="AY360" t="inlineStr">
@@ -58340,7 +58340,7 @@
       </c>
       <c r="AT361" t="inlineStr">
         <is>
-          <t>batch_43847c5c0d554445</t>
+          <t>batch_0c2ed97284e04906</t>
         </is>
       </c>
       <c r="AU361" t="inlineStr">
@@ -58356,7 +58356,7 @@
       <c r="AW361" t="inlineStr"/>
       <c r="AX361" t="inlineStr">
         <is>
-          <t>2026-05-14T03:06:34+00:00</t>
+          <t>2026-05-14T03:16:15+00:00</t>
         </is>
       </c>
       <c r="AY361" t="inlineStr">
@@ -58458,7 +58458,7 @@
       </c>
       <c r="AT362" t="inlineStr">
         <is>
-          <t>batch_43847c5c0d554445</t>
+          <t>batch_0c2ed97284e04906</t>
         </is>
       </c>
       <c r="AU362" t="inlineStr">
@@ -58474,7 +58474,7 @@
       <c r="AW362" t="inlineStr"/>
       <c r="AX362" t="inlineStr">
         <is>
-          <t>2026-05-14T03:06:34+00:00</t>
+          <t>2026-05-14T03:16:15+00:00</t>
         </is>
       </c>
       <c r="AY362" t="inlineStr">
@@ -58576,7 +58576,7 @@
       </c>
       <c r="AT363" t="inlineStr">
         <is>
-          <t>batch_43847c5c0d554445</t>
+          <t>batch_0c2ed97284e04906</t>
         </is>
       </c>
       <c r="AU363" t="inlineStr">
@@ -58592,7 +58592,7 @@
       <c r="AW363" t="inlineStr"/>
       <c r="AX363" t="inlineStr">
         <is>
-          <t>2026-05-14T03:06:34+00:00</t>
+          <t>2026-05-14T03:16:15+00:00</t>
         </is>
       </c>
       <c r="AY363" t="inlineStr">
@@ -58694,7 +58694,7 @@
       </c>
       <c r="AT364" t="inlineStr">
         <is>
-          <t>batch_43847c5c0d554445</t>
+          <t>batch_0c2ed97284e04906</t>
         </is>
       </c>
       <c r="AU364" t="inlineStr">
@@ -58710,7 +58710,7 @@
       <c r="AW364" t="inlineStr"/>
       <c r="AX364" t="inlineStr">
         <is>
-          <t>2026-05-14T03:06:34+00:00</t>
+          <t>2026-05-14T03:16:15+00:00</t>
         </is>
       </c>
       <c r="AY364" t="inlineStr">
@@ -58812,7 +58812,7 @@
       </c>
       <c r="AT365" t="inlineStr">
         <is>
-          <t>batch_43847c5c0d554445</t>
+          <t>batch_0c2ed97284e04906</t>
         </is>
       </c>
       <c r="AU365" t="inlineStr">
@@ -58828,7 +58828,7 @@
       <c r="AW365" t="inlineStr"/>
       <c r="AX365" t="inlineStr">
         <is>
-          <t>2026-05-14T03:06:34+00:00</t>
+          <t>2026-05-14T03:16:15+00:00</t>
         </is>
       </c>
       <c r="AY365" t="inlineStr">
@@ -58930,7 +58930,7 @@
       </c>
       <c r="AT366" t="inlineStr">
         <is>
-          <t>batch_43847c5c0d554445</t>
+          <t>batch_0c2ed97284e04906</t>
         </is>
       </c>
       <c r="AU366" t="inlineStr">
@@ -58946,7 +58946,7 @@
       <c r="AW366" t="inlineStr"/>
       <c r="AX366" t="inlineStr">
         <is>
-          <t>2026-05-14T03:06:34+00:00</t>
+          <t>2026-05-14T03:16:15+00:00</t>
         </is>
       </c>
       <c r="AY366" t="inlineStr">
@@ -59048,7 +59048,7 @@
       </c>
       <c r="AT367" t="inlineStr">
         <is>
-          <t>batch_43847c5c0d554445</t>
+          <t>batch_0c2ed97284e04906</t>
         </is>
       </c>
       <c r="AU367" t="inlineStr">
@@ -59064,7 +59064,7 @@
       <c r="AW367" t="inlineStr"/>
       <c r="AX367" t="inlineStr">
         <is>
-          <t>2026-05-14T03:06:34+00:00</t>
+          <t>2026-05-14T03:16:15+00:00</t>
         </is>
       </c>
       <c r="AY367" t="inlineStr">
@@ -59166,7 +59166,7 @@
       </c>
       <c r="AT368" t="inlineStr">
         <is>
-          <t>batch_43847c5c0d554445</t>
+          <t>batch_0c2ed97284e04906</t>
         </is>
       </c>
       <c r="AU368" t="inlineStr">
@@ -59182,7 +59182,7 @@
       <c r="AW368" t="inlineStr"/>
       <c r="AX368" t="inlineStr">
         <is>
-          <t>2026-05-14T03:06:34+00:00</t>
+          <t>2026-05-14T03:16:15+00:00</t>
         </is>
       </c>
       <c r="AY368" t="inlineStr">
@@ -59284,7 +59284,7 @@
       </c>
       <c r="AT369" t="inlineStr">
         <is>
-          <t>batch_43847c5c0d554445</t>
+          <t>batch_0c2ed97284e04906</t>
         </is>
       </c>
       <c r="AU369" t="inlineStr">
@@ -59300,7 +59300,7 @@
       <c r="AW369" t="inlineStr"/>
       <c r="AX369" t="inlineStr">
         <is>
-          <t>2026-05-14T03:06:34+00:00</t>
+          <t>2026-05-14T03:16:15+00:00</t>
         </is>
       </c>
       <c r="AY369" t="inlineStr">
@@ -59402,7 +59402,7 @@
       </c>
       <c r="AT370" t="inlineStr">
         <is>
-          <t>batch_43847c5c0d554445</t>
+          <t>batch_0c2ed97284e04906</t>
         </is>
       </c>
       <c r="AU370" t="inlineStr">
@@ -59418,7 +59418,7 @@
       <c r="AW370" t="inlineStr"/>
       <c r="AX370" t="inlineStr">
         <is>
-          <t>2026-05-14T03:06:34+00:00</t>
+          <t>2026-05-14T03:16:15+00:00</t>
         </is>
       </c>
       <c r="AY370" t="inlineStr">
@@ -59520,7 +59520,7 @@
       </c>
       <c r="AT371" t="inlineStr">
         <is>
-          <t>batch_43847c5c0d554445</t>
+          <t>batch_0c2ed97284e04906</t>
         </is>
       </c>
       <c r="AU371" t="inlineStr">
@@ -59536,7 +59536,7 @@
       <c r="AW371" t="inlineStr"/>
       <c r="AX371" t="inlineStr">
         <is>
-          <t>2026-05-14T03:06:34+00:00</t>
+          <t>2026-05-14T03:16:15+00:00</t>
         </is>
       </c>
       <c r="AY371" t="inlineStr">
@@ -59638,7 +59638,7 @@
       </c>
       <c r="AT372" t="inlineStr">
         <is>
-          <t>batch_43847c5c0d554445</t>
+          <t>batch_0c2ed97284e04906</t>
         </is>
       </c>
       <c r="AU372" t="inlineStr">
@@ -59654,7 +59654,7 @@
       <c r="AW372" t="inlineStr"/>
       <c r="AX372" t="inlineStr">
         <is>
-          <t>2026-05-14T03:06:34+00:00</t>
+          <t>2026-05-14T03:16:15+00:00</t>
         </is>
       </c>
       <c r="AY372" t="inlineStr">
@@ -61593,7 +61593,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Built 2026-05-14T03:06:58+00:00. Normalization version: v1.2.</t>
+          <t>Built 2026-05-14T03:16:15+00:00. Normalization version: v1.2.</t>
         </is>
       </c>
     </row>

--- a/services/costar/MASTER/COSTAR_MASTER_MERCADOS.xlsx
+++ b/services/costar/MASTER/COSTAR_MASTER_MERCADOS.xlsx
@@ -898,7 +898,7 @@
       </c>
       <c r="AT2" t="inlineStr">
         <is>
-          <t>batch_2e8f5425de7c49e5</t>
+          <t>batch_164c8f2ccaa64eaf</t>
         </is>
       </c>
       <c r="AU2" t="inlineStr">
@@ -914,7 +914,7 @@
       <c r="AW2" t="inlineStr"/>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>2026-05-14T03:50:20+00:00</t>
+          <t>2026-05-20T00:13:57+00:00</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
@@ -1044,7 +1044,7 @@
       </c>
       <c r="AT3" t="inlineStr">
         <is>
-          <t>batch_2e8f5425de7c49e5</t>
+          <t>batch_164c8f2ccaa64eaf</t>
         </is>
       </c>
       <c r="AU3" t="inlineStr">
@@ -1060,7 +1060,7 @@
       <c r="AW3" t="inlineStr"/>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>2026-05-14T03:50:20+00:00</t>
+          <t>2026-05-20T00:13:57+00:00</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">
@@ -1190,7 +1190,7 @@
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>batch_2e8f5425de7c49e5</t>
+          <t>batch_164c8f2ccaa64eaf</t>
         </is>
       </c>
       <c r="AU4" t="inlineStr">
@@ -1206,7 +1206,7 @@
       <c r="AW4" t="inlineStr"/>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>2026-05-14T03:50:20+00:00</t>
+          <t>2026-05-20T00:13:57+00:00</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">
@@ -1336,7 +1336,7 @@
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>batch_2e8f5425de7c49e5</t>
+          <t>batch_164c8f2ccaa64eaf</t>
         </is>
       </c>
       <c r="AU5" t="inlineStr">
@@ -1352,7 +1352,7 @@
       <c r="AW5" t="inlineStr"/>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>2026-05-14T03:50:20+00:00</t>
+          <t>2026-05-20T00:13:57+00:00</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr">
@@ -1482,7 +1482,7 @@
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>batch_2e8f5425de7c49e5</t>
+          <t>batch_164c8f2ccaa64eaf</t>
         </is>
       </c>
       <c r="AU6" t="inlineStr">
@@ -1498,7 +1498,7 @@
       <c r="AW6" t="inlineStr"/>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>2026-05-14T03:50:20+00:00</t>
+          <t>2026-05-20T00:13:57+00:00</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr">
@@ -1628,7 +1628,7 @@
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>batch_2e8f5425de7c49e5</t>
+          <t>batch_164c8f2ccaa64eaf</t>
         </is>
       </c>
       <c r="AU7" t="inlineStr">
@@ -1644,7 +1644,7 @@
       <c r="AW7" t="inlineStr"/>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>2026-05-14T03:50:20+00:00</t>
+          <t>2026-05-20T00:13:57+00:00</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr">
@@ -1720,7 +1720,7 @@
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>batch_2e8f5425de7c49e5</t>
+          <t>batch_164c8f2ccaa64eaf</t>
         </is>
       </c>
       <c r="AU8" t="inlineStr">
@@ -1736,7 +1736,7 @@
       <c r="AW8" t="inlineStr"/>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>2026-05-14T03:50:20+00:00</t>
+          <t>2026-05-20T00:13:57+00:00</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr">
@@ -1827,7 +1827,7 @@
       </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>batch_2e8f5425de7c49e5</t>
+          <t>batch_164c8f2ccaa64eaf</t>
         </is>
       </c>
       <c r="AU9" t="inlineStr">
@@ -1843,7 +1843,7 @@
       <c r="AW9" t="inlineStr"/>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>2026-05-14T03:50:20+00:00</t>
+          <t>2026-05-20T00:13:57+00:00</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr">
@@ -1934,7 +1934,7 @@
       </c>
       <c r="AT10" t="inlineStr">
         <is>
-          <t>batch_2e8f5425de7c49e5</t>
+          <t>batch_164c8f2ccaa64eaf</t>
         </is>
       </c>
       <c r="AU10" t="inlineStr">
@@ -1950,7 +1950,7 @@
       <c r="AW10" t="inlineStr"/>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>2026-05-14T03:50:20+00:00</t>
+          <t>2026-05-20T00:13:57+00:00</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr">
@@ -2041,7 +2041,7 @@
       </c>
       <c r="AT11" t="inlineStr">
         <is>
-          <t>batch_2e8f5425de7c49e5</t>
+          <t>batch_164c8f2ccaa64eaf</t>
         </is>
       </c>
       <c r="AU11" t="inlineStr">
@@ -2057,7 +2057,7 @@
       <c r="AW11" t="inlineStr"/>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>2026-05-14T03:50:20+00:00</t>
+          <t>2026-05-20T00:13:57+00:00</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr">
@@ -2148,7 +2148,7 @@
       </c>
       <c r="AT12" t="inlineStr">
         <is>
-          <t>batch_2e8f5425de7c49e5</t>
+          <t>batch_164c8f2ccaa64eaf</t>
         </is>
       </c>
       <c r="AU12" t="inlineStr">
@@ -2164,7 +2164,7 @@
       <c r="AW12" t="inlineStr"/>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>2026-05-14T03:50:20+00:00</t>
+          <t>2026-05-20T00:13:57+00:00</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr">
@@ -2255,7 +2255,7 @@
       </c>
       <c r="AT13" t="inlineStr">
         <is>
-          <t>batch_2e8f5425de7c49e5</t>
+          <t>batch_164c8f2ccaa64eaf</t>
         </is>
       </c>
       <c r="AU13" t="inlineStr">
@@ -2271,7 +2271,7 @@
       <c r="AW13" t="inlineStr"/>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>2026-05-14T03:50:20+00:00</t>
+          <t>2026-05-20T00:13:57+00:00</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr">
@@ -2362,7 +2362,7 @@
       </c>
       <c r="AT14" t="inlineStr">
         <is>
-          <t>batch_2e8f5425de7c49e5</t>
+          <t>batch_164c8f2ccaa64eaf</t>
         </is>
       </c>
       <c r="AU14" t="inlineStr">
@@ -2378,7 +2378,7 @@
       <c r="AW14" t="inlineStr"/>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>2026-05-14T03:50:20+00:00</t>
+          <t>2026-05-20T00:13:57+00:00</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr">
@@ -2469,7 +2469,7 @@
       </c>
       <c r="AT15" t="inlineStr">
         <is>
-          <t>batch_2e8f5425de7c49e5</t>
+          <t>batch_164c8f2ccaa64eaf</t>
         </is>
       </c>
       <c r="AU15" t="inlineStr">
@@ -2485,7 +2485,7 @@
       <c r="AW15" t="inlineStr"/>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>2026-05-14T03:50:20+00:00</t>
+          <t>2026-05-20T00:13:57+00:00</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr">
@@ -2576,7 +2576,7 @@
       </c>
       <c r="AT16" t="inlineStr">
         <is>
-          <t>batch_2e8f5425de7c49e5</t>
+          <t>batch_164c8f2ccaa64eaf</t>
         </is>
       </c>
       <c r="AU16" t="inlineStr">
@@ -2592,7 +2592,7 @@
       <c r="AW16" t="inlineStr"/>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>2026-05-14T03:50:20+00:00</t>
+          <t>2026-05-20T00:13:57+00:00</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr">
@@ -2745,7 +2745,7 @@
       </c>
       <c r="AT17" t="inlineStr">
         <is>
-          <t>batch_2e8f5425de7c49e5</t>
+          <t>batch_164c8f2ccaa64eaf</t>
         </is>
       </c>
       <c r="AU17" t="inlineStr">
@@ -2761,7 +2761,7 @@
       <c r="AW17" t="inlineStr"/>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>2026-05-14T03:50:20+00:00</t>
+          <t>2026-05-20T00:13:57+00:00</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr">
@@ -2914,7 +2914,7 @@
       </c>
       <c r="AT18" t="inlineStr">
         <is>
-          <t>batch_2e8f5425de7c49e5</t>
+          <t>batch_164c8f2ccaa64eaf</t>
         </is>
       </c>
       <c r="AU18" t="inlineStr">
@@ -2930,7 +2930,7 @@
       <c r="AW18" t="inlineStr"/>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>2026-05-14T03:50:20+00:00</t>
+          <t>2026-05-20T00:13:57+00:00</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr">
@@ -3083,7 +3083,7 @@
       </c>
       <c r="AT19" t="inlineStr">
         <is>
-          <t>batch_2e8f5425de7c49e5</t>
+          <t>batch_164c8f2ccaa64eaf</t>
         </is>
       </c>
       <c r="AU19" t="inlineStr">
@@ -3099,7 +3099,7 @@
       <c r="AW19" t="inlineStr"/>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>2026-05-14T03:50:20+00:00</t>
+          <t>2026-05-20T00:13:57+00:00</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr">
@@ -3252,7 +3252,7 @@
       </c>
       <c r="AT20" t="inlineStr">
         <is>
-          <t>batch_2e8f5425de7c49e5</t>
+          <t>batch_164c8f2ccaa64eaf</t>
         </is>
       </c>
       <c r="AU20" t="inlineStr">
@@ -3268,7 +3268,7 @@
       <c r="AW20" t="inlineStr"/>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>2026-05-14T03:50:20+00:00</t>
+          <t>2026-05-20T00:13:57+00:00</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr">
@@ -3421,7 +3421,7 @@
       </c>
       <c r="AT21" t="inlineStr">
         <is>
-          <t>batch_2e8f5425de7c49e5</t>
+          <t>batch_164c8f2ccaa64eaf</t>
         </is>
       </c>
       <c r="AU21" t="inlineStr">
@@ -3437,7 +3437,7 @@
       <c r="AW21" t="inlineStr"/>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>2026-05-14T03:50:20+00:00</t>
+          <t>2026-05-20T00:13:57+00:00</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr">
@@ -3590,7 +3590,7 @@
       </c>
       <c r="AT22" t="inlineStr">
         <is>
-          <t>batch_2e8f5425de7c49e5</t>
+          <t>batch_164c8f2ccaa64eaf</t>
         </is>
       </c>
       <c r="AU22" t="inlineStr">
@@ -3606,7 +3606,7 @@
       <c r="AW22" t="inlineStr"/>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>2026-05-14T03:50:20+00:00</t>
+          <t>2026-05-20T00:13:57+00:00</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr">
@@ -3759,7 +3759,7 @@
       </c>
       <c r="AT23" t="inlineStr">
         <is>
-          <t>batch_2e8f5425de7c49e5</t>
+          <t>batch_164c8f2ccaa64eaf</t>
         </is>
       </c>
       <c r="AU23" t="inlineStr">
@@ -3775,7 +3775,7 @@
       <c r="AW23" t="inlineStr"/>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>2026-05-14T03:50:20+00:00</t>
+          <t>2026-05-20T00:13:57+00:00</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr">
@@ -3928,7 +3928,7 @@
       </c>
       <c r="AT24" t="inlineStr">
         <is>
-          <t>batch_2e8f5425de7c49e5</t>
+          <t>batch_164c8f2ccaa64eaf</t>
         </is>
       </c>
       <c r="AU24" t="inlineStr">
@@ -3944,7 +3944,7 @@
       <c r="AW24" t="inlineStr"/>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>2026-05-14T03:50:20+00:00</t>
+          <t>2026-05-20T00:13:57+00:00</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr">
@@ -4097,7 +4097,7 @@
       </c>
       <c r="AT25" t="inlineStr">
         <is>
-          <t>batch_2e8f5425de7c49e5</t>
+          <t>batch_164c8f2ccaa64eaf</t>
         </is>
       </c>
       <c r="AU25" t="inlineStr">
@@ -4113,7 +4113,7 @@
       <c r="AW25" t="inlineStr"/>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>2026-05-14T03:50:20+00:00</t>
+          <t>2026-05-20T00:13:57+00:00</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr">
@@ -4266,7 +4266,7 @@
       </c>
       <c r="AT26" t="inlineStr">
         <is>
-          <t>batch_2e8f5425de7c49e5</t>
+          <t>batch_164c8f2ccaa64eaf</t>
         </is>
       </c>
       <c r="AU26" t="inlineStr">
@@ -4282,7 +4282,7 @@
       <c r="AW26" t="inlineStr"/>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>2026-05-14T03:50:20+00:00</t>
+          <t>2026-05-20T00:13:57+00:00</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr">
@@ -4435,7 +4435,7 @@
       </c>
       <c r="AT27" t="inlineStr">
         <is>
-          <t>batch_2e8f5425de7c49e5</t>
+          <t>batch_164c8f2ccaa64eaf</t>
         </is>
       </c>
       <c r="AU27" t="inlineStr">
@@ -4451,7 +4451,7 @@
       <c r="AW27" t="inlineStr"/>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>2026-05-14T03:50:20+00:00</t>
+          <t>2026-05-20T00:13:57+00:00</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr">
@@ -4604,7 +4604,7 @@
       </c>
       <c r="AT28" t="inlineStr">
         <is>
-          <t>batch_2e8f5425de7c49e5</t>
+          <t>batch_164c8f2ccaa64eaf</t>
         </is>
       </c>
       <c r="AU28" t="inlineStr">
@@ -4620,7 +4620,7 @@
       <c r="AW28" t="inlineStr"/>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>2026-05-14T03:50:20+00:00</t>
+          <t>2026-05-20T00:13:57+00:00</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr">
@@ -4773,7 +4773,7 @@
       </c>
       <c r="AT29" t="inlineStr">
         <is>
-          <t>batch_2e8f5425de7c49e5</t>
+          <t>batch_164c8f2ccaa64eaf</t>
         </is>
       </c>
       <c r="AU29" t="inlineStr">
@@ -4789,7 +4789,7 @@
       <c r="AW29" t="inlineStr"/>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>2026-05-14T03:50:20+00:00</t>
+          <t>2026-05-20T00:13:57+00:00</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr">
@@ -4942,7 +4942,7 @@
       </c>
       <c r="AT30" t="inlineStr">
         <is>
-          <t>batch_2e8f5425de7c49e5</t>
+          <t>batch_164c8f2ccaa64eaf</t>
         </is>
       </c>
       <c r="AU30" t="inlineStr">
@@ -4958,7 +4958,7 @@
       <c r="AW30" t="inlineStr"/>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>2026-05-14T03:50:20+00:00</t>
+          <t>2026-05-20T00:13:57+00:00</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr">
@@ -5111,7 +5111,7 @@
       </c>
       <c r="AT31" t="inlineStr">
         <is>
-          <t>batch_2e8f5425de7c49e5</t>
+          <t>batch_164c8f2ccaa64eaf</t>
         </is>
       </c>
       <c r="AU31" t="inlineStr">
@@ -5127,7 +5127,7 @@
       <c r="AW31" t="inlineStr"/>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>2026-05-14T03:50:20+00:00</t>
+          <t>2026-05-20T00:13:57+00:00</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr">
@@ -5280,7 +5280,7 @@
       </c>
       <c r="AT32" t="inlineStr">
         <is>
-          <t>batch_2e8f5425de7c49e5</t>
+          <t>batch_164c8f2ccaa64eaf</t>
         </is>
       </c>
       <c r="AU32" t="inlineStr">
@@ -5296,7 +5296,7 @@
       <c r="AW32" t="inlineStr"/>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>2026-05-14T03:50:20+00:00</t>
+          <t>2026-05-20T00:13:57+00:00</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr">
@@ -5449,7 +5449,7 @@
       </c>
       <c r="AT33" t="inlineStr">
         <is>
-          <t>batch_2e8f5425de7c49e5</t>
+          <t>batch_164c8f2ccaa64eaf</t>
         </is>
       </c>
       <c r="AU33" t="inlineStr">
@@ -5465,7 +5465,7 @@
       <c r="AW33" t="inlineStr"/>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>2026-05-14T03:50:20+00:00</t>
+          <t>2026-05-20T00:13:57+00:00</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr">
@@ -5618,7 +5618,7 @@
       </c>
       <c r="AT34" t="inlineStr">
         <is>
-          <t>batch_2e8f5425de7c49e5</t>
+          <t>batch_164c8f2ccaa64eaf</t>
         </is>
       </c>
       <c r="AU34" t="inlineStr">
@@ -5634,7 +5634,7 @@
       <c r="AW34" t="inlineStr"/>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>2026-05-14T03:50:20+00:00</t>
+          <t>2026-05-20T00:13:57+00:00</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr">
@@ -5787,7 +5787,7 @@
       </c>
       <c r="AT35" t="inlineStr">
         <is>
-          <t>batch_2e8f5425de7c49e5</t>
+          <t>batch_164c8f2ccaa64eaf</t>
         </is>
       </c>
       <c r="AU35" t="inlineStr">
@@ -5803,7 +5803,7 @@
       <c r="AW35" t="inlineStr"/>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>2026-05-14T03:50:20+00:00</t>
+          <t>2026-05-20T00:13:57+00:00</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr">
@@ -5956,7 +5956,7 @@
       </c>
       <c r="AT36" t="inlineStr">
         <is>
-          <t>batch_2e8f5425de7c49e5</t>
+          <t>batch_164c8f2ccaa64eaf</t>
         </is>
       </c>
       <c r="AU36" t="inlineStr">
@@ -5972,7 +5972,7 @@
       <c r="AW36" t="inlineStr"/>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>2026-05-14T03:50:20+00:00</t>
+          <t>2026-05-20T00:13:57+00:00</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr">
@@ -6125,7 +6125,7 @@
       </c>
       <c r="AT37" t="inlineStr">
         <is>
-          <t>batch_2e8f5425de7c49e5</t>
+          <t>batch_164c8f2ccaa64eaf</t>
         </is>
       </c>
       <c r="AU37" t="inlineStr">
@@ -6141,7 +6141,7 @@
       <c r="AW37" t="inlineStr"/>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>2026-05-14T03:50:20+00:00</t>
+          <t>2026-05-20T00:13:57+00:00</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr">
@@ -6294,7 +6294,7 @@
       </c>
       <c r="AT38" t="inlineStr">
         <is>
-          <t>batch_2e8f5425de7c49e5</t>
+          <t>batch_164c8f2ccaa64eaf</t>
         </is>
       </c>
       <c r="AU38" t="inlineStr">
@@ -6310,7 +6310,7 @@
       <c r="AW38" t="inlineStr"/>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>2026-05-14T03:50:20+00:00</t>
+          <t>2026-05-20T00:13:57+00:00</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr">
@@ -6463,7 +6463,7 @@
       </c>
       <c r="AT39" t="inlineStr">
         <is>
-          <t>batch_2e8f5425de7c49e5</t>
+          <t>batch_164c8f2ccaa64eaf</t>
         </is>
       </c>
       <c r="AU39" t="inlineStr">
@@ -6479,7 +6479,7 @@
       <c r="AW39" t="inlineStr"/>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>2026-05-14T03:50:20+00:00</t>
+          <t>2026-05-20T00:13:57+00:00</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr">
@@ -6632,7 +6632,7 @@
       </c>
       <c r="AT40" t="inlineStr">
         <is>
-          <t>batch_2e8f5425de7c49e5</t>
+          <t>batch_164c8f2ccaa64eaf</t>
         </is>
       </c>
       <c r="AU40" t="inlineStr">
@@ -6648,7 +6648,7 @@
       <c r="AW40" t="inlineStr"/>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>2026-05-14T03:50:20+00:00</t>
+          <t>2026-05-20T00:13:57+00:00</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr">
@@ -6801,7 +6801,7 @@
       </c>
       <c r="AT41" t="inlineStr">
         <is>
-          <t>batch_2e8f5425de7c49e5</t>
+          <t>batch_164c8f2ccaa64eaf</t>
         </is>
       </c>
       <c r="AU41" t="inlineStr">
@@ -6817,7 +6817,7 @@
       <c r="AW41" t="inlineStr"/>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>2026-05-14T03:50:20+00:00</t>
+          <t>2026-05-20T00:13:57+00:00</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr">
@@ -6970,7 +6970,7 @@
       </c>
       <c r="AT42" t="inlineStr">
         <is>
-          <t>batch_2e8f5425de7c49e5</t>
+          <t>batch_164c8f2ccaa64eaf</t>
         </is>
       </c>
       <c r="AU42" t="inlineStr">
@@ -6986,7 +6986,7 @@
       <c r="AW42" t="inlineStr"/>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>2026-05-14T03:50:20+00:00</t>
+          <t>2026-05-20T00:13:57+00:00</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr">
@@ -7139,7 +7139,7 @@
       </c>
       <c r="AT43" t="inlineStr">
         <is>
-          <t>batch_2e8f5425de7c49e5</t>
+          <t>batch_164c8f2ccaa64eaf</t>
         </is>
       </c>
       <c r="AU43" t="inlineStr">
@@ -7155,7 +7155,7 @@
       <c r="AW43" t="inlineStr"/>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>2026-05-14T03:50:20+00:00</t>
+          <t>2026-05-20T00:13:57+00:00</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr">
@@ -7308,7 +7308,7 @@
       </c>
       <c r="AT44" t="inlineStr">
         <is>
-          <t>batch_2e8f5425de7c49e5</t>
+          <t>batch_164c8f2ccaa64eaf</t>
         </is>
       </c>
       <c r="AU44" t="inlineStr">
@@ -7324,7 +7324,7 @@
       <c r="AW44" t="inlineStr"/>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>2026-05-14T03:50:20+00:00</t>
+          <t>2026-05-20T00:13:57+00:00</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr">
@@ -7477,7 +7477,7 @@
       </c>
       <c r="AT45" t="inlineStr">
         <is>
-          <t>batch_2e8f5425de7c49e5</t>
+          <t>batch_164c8f2ccaa64eaf</t>
         </is>
       </c>
       <c r="AU45" t="inlineStr">
@@ -7493,7 +7493,7 @@
       <c r="AW45" t="inlineStr"/>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>2026-05-14T03:50:20+00:00</t>
+          <t>2026-05-20T00:13:57+00:00</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr">
@@ -7646,7 +7646,7 @@
       </c>
       <c r="AT46" t="inlineStr">
         <is>
-          <t>batch_2e8f5425de7c49e5</t>
+          <t>batch_164c8f2ccaa64eaf</t>
         </is>
       </c>
       <c r="AU46" t="inlineStr">
@@ -7662,7 +7662,7 @@
       <c r="AW46" t="inlineStr"/>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>2026-05-14T03:50:20+00:00</t>
+          <t>2026-05-20T00:13:57+00:00</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr">
@@ -7815,7 +7815,7 @@
       </c>
       <c r="AT47" t="inlineStr">
         <is>
-          <t>batch_2e8f5425de7c49e5</t>
+          <t>batch_164c8f2ccaa64eaf</t>
         </is>
       </c>
       <c r="AU47" t="inlineStr">
@@ -7831,7 +7831,7 @@
       <c r="AW47" t="inlineStr"/>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>2026-05-14T03:50:20+00:00</t>
+          <t>2026-05-20T00:13:57+00:00</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr">
@@ -7984,7 +7984,7 @@
       </c>
       <c r="AT48" t="inlineStr">
         <is>
-          <t>batch_2e8f5425de7c49e5</t>
+          <t>batch_164c8f2ccaa64eaf</t>
         </is>
       </c>
       <c r="AU48" t="inlineStr">
@@ -8000,7 +8000,7 @@
       <c r="AW48" t="inlineStr"/>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>2026-05-14T03:50:20+00:00</t>
+          <t>2026-05-20T00:13:57+00:00</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr">
@@ -8153,7 +8153,7 @@
       </c>
       <c r="AT49" t="inlineStr">
         <is>
-          <t>batch_2e8f5425de7c49e5</t>
+          <t>batch_164c8f2ccaa64eaf</t>
         </is>
       </c>
       <c r="AU49" t="inlineStr">
@@ -8169,7 +8169,7 @@
       <c r="AW49" t="inlineStr"/>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>2026-05-14T03:50:20+00:00</t>
+          <t>2026-05-20T00:13:57+00:00</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr">
@@ -8322,7 +8322,7 @@
       </c>
       <c r="AT50" t="inlineStr">
         <is>
-          <t>batch_2e8f5425de7c49e5</t>
+          <t>batch_164c8f2ccaa64eaf</t>
         </is>
       </c>
       <c r="AU50" t="inlineStr">
@@ -8338,7 +8338,7 @@
       <c r="AW50" t="inlineStr"/>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>2026-05-14T03:50:20+00:00</t>
+          <t>2026-05-20T00:13:57+00:00</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr">
@@ -8491,7 +8491,7 @@
       </c>
       <c r="AT51" t="inlineStr">
         <is>
-          <t>batch_2e8f5425de7c49e5</t>
+          <t>batch_164c8f2ccaa64eaf</t>
         </is>
       </c>
       <c r="AU51" t="inlineStr">
@@ -8507,7 +8507,7 @@
       <c r="AW51" t="inlineStr"/>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>2026-05-14T03:50:20+00:00</t>
+          <t>2026-05-20T00:13:57+00:00</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr">
@@ -8660,7 +8660,7 @@
       </c>
       <c r="AT52" t="inlineStr">
         <is>
-          <t>batch_2e8f5425de7c49e5</t>
+          <t>batch_164c8f2ccaa64eaf</t>
         </is>
       </c>
       <c r="AU52" t="inlineStr">
@@ -8676,7 +8676,7 @@
       <c r="AW52" t="inlineStr"/>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>2026-05-14T03:50:20+00:00</t>
+          <t>2026-05-20T00:13:57+00:00</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr">
@@ -8829,7 +8829,7 @@
       </c>
       <c r="AT53" t="inlineStr">
         <is>
-          <t>batch_2e8f5425de7c49e5</t>
+          <t>batch_164c8f2ccaa64eaf</t>
         </is>
       </c>
       <c r="AU53" t="inlineStr">
@@ -8845,7 +8845,7 @@
       <c r="AW53" t="inlineStr"/>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>2026-05-14T03:50:20+00:00</t>
+          <t>2026-05-20T00:13:57+00:00</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr">
@@ -8998,7 +8998,7 @@
       </c>
       <c r="AT54" t="inlineStr">
         <is>
-          <t>batch_2e8f5425de7c49e5</t>
+          <t>batch_164c8f2ccaa64eaf</t>
         </is>
       </c>
       <c r="AU54" t="inlineStr">
@@ -9014,7 +9014,7 @@
       <c r="AW54" t="inlineStr"/>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>2026-05-14T03:50:20+00:00</t>
+          <t>2026-05-20T00:13:57+00:00</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr">
@@ -9167,7 +9167,7 @@
       </c>
       <c r="AT55" t="inlineStr">
         <is>
-          <t>batch_2e8f5425de7c49e5</t>
+          <t>batch_164c8f2ccaa64eaf</t>
         </is>
       </c>
       <c r="AU55" t="inlineStr">
@@ -9183,7 +9183,7 @@
       <c r="AW55" t="inlineStr"/>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>2026-05-14T03:50:20+00:00</t>
+          <t>2026-05-20T00:13:57+00:00</t>
         </is>
       </c>
       <c r="AY55" t="inlineStr">
@@ -9336,7 +9336,7 @@
       </c>
       <c r="AT56" t="inlineStr">
         <is>
-          <t>batch_2e8f5425de7c49e5</t>
+          <t>batch_164c8f2ccaa64eaf</t>
         </is>
       </c>
       <c r="AU56" t="inlineStr">
@@ -9352,7 +9352,7 @@
       <c r="AW56" t="inlineStr"/>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>2026-05-14T03:50:20+00:00</t>
+          <t>2026-05-20T00:13:57+00:00</t>
         </is>
       </c>
       <c r="AY56" t="inlineStr">
@@ -9505,7 +9505,7 @@
       </c>
       <c r="AT57" t="inlineStr">
         <is>
-          <t>batch_2e8f5425de7c49e5</t>
+          <t>batch_164c8f2ccaa64eaf</t>
         </is>
       </c>
       <c r="AU57" t="inlineStr">
@@ -9521,7 +9521,7 @@
       <c r="AW57" t="inlineStr"/>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>2026-05-14T03:50:20+00:00</t>
+          <t>2026-05-20T00:13:57+00:00</t>
         </is>
       </c>
       <c r="AY57" t="inlineStr">
@@ -9674,7 +9674,7 @@
       </c>
       <c r="AT58" t="inlineStr">
         <is>
-          <t>batch_2e8f5425de7c49e5</t>
+          <t>batch_164c8f2ccaa64eaf</t>
         </is>
       </c>
       <c r="AU58" t="inlineStr">
@@ -9690,7 +9690,7 @@
       <c r="AW58" t="inlineStr"/>
       <c r="AX58" t="inlineStr">
         <is>
-          <t>2026-05-14T03:50:20+00:00</t>
+          <t>2026-05-20T00:13:57+00:00</t>
         </is>
       </c>
       <c r="AY58" t="inlineStr">
@@ -9843,7 +9843,7 @@
       </c>
       <c r="AT59" t="inlineStr">
         <is>
-          <t>batch_2e8f5425de7c49e5</t>
+          <t>batch_164c8f2ccaa64eaf</t>
         </is>
       </c>
       <c r="AU59" t="inlineStr">
@@ -9859,7 +9859,7 @@
       <c r="AW59" t="inlineStr"/>
       <c r="AX59" t="inlineStr">
         <is>
-          <t>2026-05-14T03:50:20+00:00</t>
+          <t>2026-05-20T00:13:57+00:00</t>
         </is>
       </c>
       <c r="AY59" t="inlineStr">
@@ -10012,7 +10012,7 @@
       </c>
       <c r="AT60" t="inlineStr">
         <is>
-          <t>batch_2e8f5425de7c49e5</t>
+          <t>batch_164c8f2ccaa64eaf</t>
         </is>
       </c>
       <c r="AU60" t="inlineStr">
@@ -10028,7 +10028,7 @@
       <c r="AW60" t="inlineStr"/>
       <c r="AX60" t="inlineStr">
         <is>
-          <t>2026-05-14T03:50:20+00:00</t>
+          <t>2026-05-20T00:13:57+00:00</t>
         </is>
       </c>
       <c r="AY60" t="inlineStr">
@@ -10181,7 +10181,7 @@
       </c>
       <c r="AT61" t="inlineStr">
         <is>
-          <t>batch_2e8f5425de7c49e5</t>
+          <t>batch_164c8f2ccaa64eaf</t>
         </is>
       </c>
       <c r="AU61" t="inlineStr">
@@ -10197,7 +10197,7 @@
       <c r="AW61" t="inlineStr"/>
       <c r="AX61" t="inlineStr">
         <is>
-          <t>2026-05-14T03:50:20+00:00</t>
+          <t>2026-05-20T00:13:57+00:00</t>
         </is>
       </c>
       <c r="AY61" t="inlineStr">
@@ -10350,7 +10350,7 @@
       </c>
       <c r="AT62" t="inlineStr">
         <is>
-          <t>batch_2e8f5425de7c49e5</t>
+          <t>batch_164c8f2ccaa64eaf</t>
         </is>
       </c>
       <c r="AU62" t="inlineStr">
@@ -10366,7 +10366,7 @@
       <c r="AW62" t="inlineStr"/>
       <c r="AX62" t="inlineStr">
         <is>
-          <t>2026-05-14T03:50:20+00:00</t>
+          <t>2026-05-20T00:13:57+00:00</t>
         </is>
       </c>
       <c r="AY62" t="inlineStr">
@@ -10519,7 +10519,7 @@
       </c>
       <c r="AT63" t="inlineStr">
         <is>
-          <t>batch_2e8f5425de7c49e5</t>
+          <t>batch_164c8f2ccaa64eaf</t>
         </is>
       </c>
       <c r="AU63" t="inlineStr">
@@ -10535,7 +10535,7 @@
       <c r="AW63" t="inlineStr"/>
       <c r="AX63" t="inlineStr">
         <is>
-          <t>2026-05-14T03:50:20+00:00</t>
+          <t>2026-05-20T00:13:57+00:00</t>
         </is>
       </c>
       <c r="AY63" t="inlineStr">
@@ -10688,7 +10688,7 @@
       </c>
       <c r="AT64" t="inlineStr">
         <is>
-          <t>batch_2e8f5425de7c49e5</t>
+          <t>batch_164c8f2ccaa64eaf</t>
         </is>
       </c>
       <c r="AU64" t="inlineStr">
@@ -10704,7 +10704,7 @@
       <c r="AW64" t="inlineStr"/>
       <c r="AX64" t="inlineStr">
         <is>
-          <t>2026-05-14T03:50:20+00:00</t>
+          <t>2026-05-20T00:13:57+00:00</t>
         </is>
       </c>
       <c r="AY64" t="inlineStr">
@@ -10857,7 +10857,7 @@
       </c>
       <c r="AT65" t="inlineStr">
         <is>
-          <t>batch_2e8f5425de7c49e5</t>
+          <t>batch_164c8f2ccaa64eaf</t>
         </is>
       </c>
       <c r="AU65" t="inlineStr">
@@ -10873,7 +10873,7 @@
       <c r="AW65" t="inlineStr"/>
       <c r="AX65" t="inlineStr">
         <is>
-          <t>2026-05-14T03:50:20+00:00</t>
+          <t>2026-05-20T00:13:57+00:00</t>
         </is>
       </c>
       <c r="AY65" t="inlineStr">
@@ -11026,7 +11026,7 @@
       </c>
       <c r="AT66" t="inlineStr">
         <is>
-          <t>batch_2e8f5425de7c49e5</t>
+          <t>batch_164c8f2ccaa64eaf</t>
         </is>
       </c>
       <c r="AU66" t="inlineStr">
@@ -11042,7 +11042,7 @@
       <c r="AW66" t="inlineStr"/>
       <c r="AX66" t="inlineStr">
         <is>
-          <t>2026-05-14T03:50:20+00:00</t>
+          <t>2026-05-20T00:13:57+00:00</t>
         </is>
       </c>
       <c r="AY66" t="inlineStr">
@@ -11195,7 +11195,7 @@
       </c>
       <c r="AT67" t="inlineStr">
         <is>
-          <t>batch_2e8f5425de7c49e5</t>
+          <t>batch_164c8f2ccaa64eaf</t>
         </is>
       </c>
       <c r="AU67" t="inlineStr">
@@ -11211,7 +11211,7 @@
       <c r="AW67" t="inlineStr"/>
       <c r="AX67" t="inlineStr">
         <is>
-          <t>2026-05-14T03:50:20+00:00</t>
+          <t>2026-05-20T00:13:57+00:00</t>
         </is>
       </c>
       <c r="AY67" t="inlineStr">
@@ -11364,7 +11364,7 @@
       </c>
       <c r="AT68" t="inlineStr">
         <is>
-          <t>batch_2e8f5425de7c49e5</t>
+          <t>batch_164c8f2ccaa64eaf</t>
         </is>
       </c>
       <c r="AU68" t="inlineStr">
@@ -11380,7 +11380,7 @@
       <c r="AW68" t="inlineStr"/>
       <c r="AX68" t="inlineStr">
         <is>
-          <t>2026-05-14T03:50:20+00:00</t>
+          <t>2026-05-20T00:13:57+00:00</t>
         </is>
       </c>
       <c r="AY68" t="inlineStr">
@@ -11533,7 +11533,7 @@
       </c>
       <c r="AT69" t="inlineStr">
         <is>
-          <t>batch_2e8f5425de7c49e5</t>
+          <t>batch_164c8f2ccaa64eaf</t>
         </is>
       </c>
       <c r="AU69" t="inlineStr">
@@ -11549,7 +11549,7 @@
       <c r="AW69" t="inlineStr"/>
       <c r="AX69" t="inlineStr">
         <is>
-          <t>2026-05-14T03:50:20+00:00</t>
+          <t>2026-05-20T00:13:57+00:00</t>
         </is>
       </c>
       <c r="AY69" t="inlineStr">
@@ -11702,7 +11702,7 @@
       </c>
       <c r="AT70" t="inlineStr">
         <is>
-          <t>batch_2e8f5425de7c49e5</t>
+          <t>batch_164c8f2ccaa64eaf</t>
         </is>
       </c>
       <c r="AU70" t="inlineStr">
@@ -11718,7 +11718,7 @@
       <c r="AW70" t="inlineStr"/>
       <c r="AX70" t="inlineStr">
         <is>
-          <t>2026-05-14T03:50:20+00:00</t>
+          <t>2026-05-20T00:13:57+00:00</t>
         </is>
       </c>
       <c r="AY70" t="inlineStr">
@@ -11871,7 +11871,7 @@
       </c>
       <c r="AT71" t="inlineStr">
         <is>
-          <t>batch_2e8f5425de7c49e5</t>
+          <t>batch_164c8f2ccaa64eaf</t>
         </is>
       </c>
       <c r="AU71" t="inlineStr">
@@ -11887,7 +11887,7 @@
       <c r="AW71" t="inlineStr"/>
       <c r="AX71" t="inlineStr">
         <is>
-          <t>2026-05-14T03:50:20+00:00</t>
+          <t>2026-05-20T00:13:57+00:00</t>
         </is>
       </c>
       <c r="AY71" t="inlineStr">
@@ -12040,7 +12040,7 @@
       </c>
       <c r="AT72" t="inlineStr">
         <is>
-          <t>batch_2e8f5425de7c49e5</t>
+          <t>batch_164c8f2ccaa64eaf</t>
         </is>
       </c>
       <c r="AU72" t="inlineStr">
@@ -12056,7 +12056,7 @@
       <c r="AW72" t="inlineStr"/>
       <c r="AX72" t="inlineStr">
         <is>
-          <t>2026-05-14T03:50:20+00:00</t>
+          <t>2026-05-20T00:13:57+00:00</t>
         </is>
       </c>
       <c r="AY72" t="inlineStr">
@@ -12209,7 +12209,7 @@
       </c>
       <c r="AT73" t="inlineStr">
         <is>
-          <t>batch_2e8f5425de7c49e5</t>
+          <t>batch_164c8f2ccaa64eaf</t>
         </is>
       </c>
       <c r="AU73" t="inlineStr">
@@ -12225,7 +12225,7 @@
       <c r="AW73" t="inlineStr"/>
       <c r="AX73" t="inlineStr">
         <is>
-          <t>2026-05-14T03:50:20+00:00</t>
+          <t>2026-05-20T00:13:57+00:00</t>
         </is>
       </c>
       <c r="AY73" t="inlineStr">
@@ -12378,7 +12378,7 @@
       </c>
       <c r="AT74" t="inlineStr">
         <is>
-          <t>batch_2e8f5425de7c49e5</t>
+          <t>batch_164c8f2ccaa64eaf</t>
         </is>
       </c>
       <c r="AU74" t="inlineStr">
@@ -12394,7 +12394,7 @@
       <c r="AW74" t="inlineStr"/>
       <c r="AX74" t="inlineStr">
         <is>
-          <t>2026-05-14T03:50:20+00:00</t>
+          <t>2026-05-20T00:13:57+00:00</t>
         </is>
       </c>
       <c r="AY74" t="inlineStr">
@@ -12547,7 +12547,7 @@
       </c>
       <c r="AT75" t="inlineStr">
         <is>
-          <t>batch_2e8f5425de7c49e5</t>
+          <t>batch_164c8f2ccaa64eaf</t>
         </is>
       </c>
       <c r="AU75" t="inlineStr">
@@ -12563,7 +12563,7 @@
       <c r="AW75" t="inlineStr"/>
       <c r="AX75" t="inlineStr">
         <is>
-          <t>2026-05-14T03:50:20+00:00</t>
+          <t>2026-05-20T00:13:57+00:00</t>
         </is>
       </c>
       <c r="AY75" t="inlineStr">
@@ -12716,7 +12716,7 @@
       </c>
       <c r="AT76" t="inlineStr">
         <is>
-          <t>batch_2e8f5425de7c49e5</t>
+          <t>batch_164c8f2ccaa64eaf</t>
         </is>
       </c>
       <c r="AU76" t="inlineStr">
@@ -12732,7 +12732,7 @@
       <c r="AW76" t="inlineStr"/>
       <c r="AX76" t="inlineStr">
         <is>
-          <t>2026-05-14T03:50:20+00:00</t>
+          <t>2026-05-20T00:13:57+00:00</t>
         </is>
       </c>
       <c r="AY76" t="inlineStr">
@@ -12885,7 +12885,7 @@
       </c>
       <c r="AT77" t="inlineStr">
         <is>
-          <t>batch_2e8f5425de7c49e5</t>
+          <t>batch_164c8f2ccaa64eaf</t>
         </is>
       </c>
       <c r="AU77" t="inlineStr">
@@ -12901,7 +12901,7 @@
       <c r="AW77" t="inlineStr"/>
       <c r="AX77" t="inlineStr">
         <is>
-          <t>2026-05-14T03:50:20+00:00</t>
+          <t>2026-05-20T00:13:57+00:00</t>
         </is>
       </c>
       <c r="AY77" t="inlineStr">
@@ -13054,7 +13054,7 @@
       </c>
       <c r="AT78" t="inlineStr">
         <is>
-          <t>batch_2e8f5425de7c49e5</t>
+          <t>batch_164c8f2ccaa64eaf</t>
         </is>
       </c>
       <c r="AU78" t="inlineStr">
@@ -13070,7 +13070,7 @@
       <c r="AW78" t="inlineStr"/>
       <c r="AX78" t="inlineStr">
         <is>
-          <t>2026-05-14T03:50:20+00:00</t>
+          <t>2026-05-20T00:13:57+00:00</t>
         </is>
       </c>
       <c r="AY78" t="inlineStr">
@@ -13223,7 +13223,7 @@
       </c>
       <c r="AT79" t="inlineStr">
         <is>
-          <t>batch_2e8f5425de7c49e5</t>
+          <t>batch_164c8f2ccaa64eaf</t>
         </is>
       </c>
       <c r="AU79" t="inlineStr">
@@ -13239,7 +13239,7 @@
       <c r="AW79" t="inlineStr"/>
       <c r="AX79" t="inlineStr">
         <is>
-          <t>2026-05-14T03:50:20+00:00</t>
+          <t>2026-05-20T00:13:57+00:00</t>
         </is>
       </c>
       <c r="AY79" t="inlineStr">
@@ -13392,7 +13392,7 @@
       </c>
       <c r="AT80" t="inlineStr">
         <is>
-          <t>batch_2e8f5425de7c49e5</t>
+          <t>batch_164c8f2ccaa64eaf</t>
         </is>
       </c>
       <c r="AU80" t="inlineStr">
@@ -13408,7 +13408,7 @@
       <c r="AW80" t="inlineStr"/>
       <c r="AX80" t="inlineStr">
         <is>
-          <t>2026-05-14T03:50:20+00:00</t>
+          <t>2026-05-20T00:13:57+00:00</t>
         </is>
       </c>
       <c r="AY80" t="inlineStr">
@@ -13561,7 +13561,7 @@
       </c>
       <c r="AT81" t="inlineStr">
         <is>
-          <t>batch_2e8f5425de7c49e5</t>
+          <t>batch_164c8f2ccaa64eaf</t>
         </is>
       </c>
       <c r="AU81" t="inlineStr">
@@ -13577,7 +13577,7 @@
       <c r="AW81" t="inlineStr"/>
       <c r="AX81" t="inlineStr">
         <is>
-          <t>2026-05-14T03:50:20+00:00</t>
+          <t>2026-05-20T00:13:57+00:00</t>
         </is>
       </c>
       <c r="AY81" t="inlineStr">
@@ -13730,7 +13730,7 @@
       </c>
       <c r="AT82" t="inlineStr">
         <is>
-          <t>batch_2e8f5425de7c49e5</t>
+          <t>batch_164c8f2ccaa64eaf</t>
         </is>
       </c>
       <c r="AU82" t="inlineStr">
@@ -13746,7 +13746,7 @@
       <c r="AW82" t="inlineStr"/>
       <c r="AX82" t="inlineStr">
         <is>
-          <t>2026-05-14T03:50:20+00:00</t>
+          <t>2026-05-20T00:13:57+00:00</t>
         </is>
       </c>
       <c r="AY82" t="inlineStr">
@@ -13899,7 +13899,7 @@
       </c>
       <c r="AT83" t="inlineStr">
         <is>
-          <t>batch_2e8f5425de7c49e5</t>
+          <t>batch_164c8f2ccaa64eaf</t>
         </is>
       </c>
       <c r="AU83" t="inlineStr">
@@ -13915,7 +13915,7 @@
       <c r="AW83" t="inlineStr"/>
       <c r="AX83" t="inlineStr">
         <is>
-          <t>2026-05-14T03:50:20+00:00</t>
+          <t>2026-05-20T00:13:57+00:00</t>
         </is>
       </c>
       <c r="AY83" t="inlineStr">
@@ -14068,7 +14068,7 @@
       </c>
       <c r="AT84" t="inlineStr">
         <is>
-          <t>batch_2e8f5425de7c49e5</t>
+          <t>batch_164c8f2ccaa64eaf</t>
         </is>
       </c>
       <c r="AU84" t="inlineStr">
@@ -14084,7 +14084,7 @@
       <c r="AW84" t="inlineStr"/>
       <c r="AX84" t="inlineStr">
         <is>
-          <t>2026-05-14T03:50:20+00:00</t>
+          <t>2026-05-20T00:13:57+00:00</t>
         </is>
       </c>
       <c r="AY84" t="inlineStr">
@@ -14237,7 +14237,7 @@
       </c>
       <c r="AT85" t="inlineStr">
         <is>
-          <t>batch_2e8f5425de7c49e5</t>
+          <t>batch_164c8f2ccaa64eaf</t>
         </is>
       </c>
       <c r="AU85" t="inlineStr">
@@ -14253,7 +14253,7 @@
       <c r="AW85" t="inlineStr"/>
       <c r="AX85" t="inlineStr">
         <is>
-          <t>2026-05-14T03:50:20+00:00</t>
+          <t>2026-05-20T00:13:57+00:00</t>
         </is>
       </c>
       <c r="AY85" t="inlineStr">
@@ -14406,7 +14406,7 @@
       </c>
       <c r="AT86" t="inlineStr">
         <is>
-          <t>batch_2e8f5425de7c49e5</t>
+          <t>batch_164c8f2ccaa64eaf</t>
         </is>
       </c>
       <c r="AU86" t="inlineStr">
@@ -14422,7 +14422,7 @@
       <c r="AW86" t="inlineStr"/>
       <c r="AX86" t="inlineStr">
         <is>
-          <t>2026-05-14T03:50:20+00:00</t>
+          <t>2026-05-20T00:13:57+00:00</t>
         </is>
       </c>
       <c r="AY86" t="inlineStr">
@@ -14575,7 +14575,7 @@
       </c>
       <c r="AT87" t="inlineStr">
         <is>
-          <t>batch_2e8f5425de7c49e5</t>
+          <t>batch_164c8f2ccaa64eaf</t>
         </is>
       </c>
       <c r="AU87" t="inlineStr">
@@ -14591,7 +14591,7 @@
       <c r="AW87" t="inlineStr"/>
       <c r="AX87" t="inlineStr">
         <is>
-          <t>2026-05-14T03:50:20+00:00</t>
+          <t>2026-05-20T00:13:57+00:00</t>
         </is>
       </c>
       <c r="AY87" t="inlineStr">
@@ -14744,7 +14744,7 @@
       </c>
       <c r="AT88" t="inlineStr">
         <is>
-          <t>batch_2e8f5425de7c49e5</t>
+          <t>batch_164c8f2ccaa64eaf</t>
         </is>
       </c>
       <c r="AU88" t="inlineStr">
@@ -14760,7 +14760,7 @@
       <c r="AW88" t="inlineStr"/>
       <c r="AX88" t="inlineStr">
         <is>
-          <t>2026-05-14T03:50:20+00:00</t>
+          <t>2026-05-20T00:13:57+00:00</t>
         </is>
       </c>
       <c r="AY88" t="inlineStr">
@@ -14913,7 +14913,7 @@
       </c>
       <c r="AT89" t="inlineStr">
         <is>
-          <t>batch_2e8f5425de7c49e5</t>
+          <t>batch_164c8f2ccaa64eaf</t>
         </is>
       </c>
       <c r="AU89" t="inlineStr">
@@ -14929,7 +14929,7 @@
       <c r="AW89" t="inlineStr"/>
       <c r="AX89" t="inlineStr">
         <is>
-          <t>2026-05-14T03:50:20+00:00</t>
+          <t>2026-05-20T00:13:57+00:00</t>
         </is>
       </c>
       <c r="AY89" t="inlineStr">
@@ -15082,7 +15082,7 @@
       </c>
       <c r="AT90" t="inlineStr">
         <is>
-          <t>batch_2e8f5425de7c49e5</t>
+          <t>batch_164c8f2ccaa64eaf</t>
         </is>
       </c>
       <c r="AU90" t="inlineStr">
@@ -15098,7 +15098,7 @@
       <c r="AW90" t="inlineStr"/>
       <c r="AX90" t="inlineStr">
         <is>
-          <t>2026-05-14T03:50:20+00:00</t>
+          <t>2026-05-20T00:13:57+00:00</t>
         </is>
       </c>
       <c r="AY90" t="inlineStr">
@@ -15251,7 +15251,7 @@
       </c>
       <c r="AT91" t="inlineStr">
         <is>
-          <t>batch_2e8f5425de7c49e5</t>
+          <t>batch_164c8f2ccaa64eaf</t>
         </is>
       </c>
       <c r="AU91" t="inlineStr">
@@ -15267,7 +15267,7 @@
       <c r="AW91" t="inlineStr"/>
       <c r="AX91" t="inlineStr">
         <is>
-          <t>2026-05-14T03:50:20+00:00</t>
+          <t>2026-05-20T00:13:57+00:00</t>
         </is>
       </c>
       <c r="AY91" t="inlineStr">
@@ -15420,7 +15420,7 @@
       </c>
       <c r="AT92" t="inlineStr">
         <is>
-          <t>batch_2e8f5425de7c49e5</t>
+          <t>batch_164c8f2ccaa64eaf</t>
         </is>
       </c>
       <c r="AU92" t="inlineStr">
@@ -15436,7 +15436,7 @@
       <c r="AW92" t="inlineStr"/>
       <c r="AX92" t="inlineStr">
         <is>
-          <t>2026-05-14T03:50:20+00:00</t>
+          <t>2026-05-20T00:13:57+00:00</t>
         </is>
       </c>
       <c r="AY92" t="inlineStr">
@@ -15589,7 +15589,7 @@
       </c>
       <c r="AT93" t="inlineStr">
         <is>
-          <t>batch_2e8f5425de7c49e5</t>
+          <t>batch_164c8f2ccaa64eaf</t>
         </is>
       </c>
       <c r="AU93" t="inlineStr">
@@ -15605,7 +15605,7 @@
       <c r="AW93" t="inlineStr"/>
       <c r="AX93" t="inlineStr">
         <is>
-          <t>2026-05-14T03:50:20+00:00</t>
+          <t>2026-05-20T00:13:57+00:00</t>
         </is>
       </c>
       <c r="AY93" t="inlineStr">
@@ -15758,7 +15758,7 @@
       </c>
       <c r="AT94" t="inlineStr">
         <is>
-          <t>batch_2e8f5425de7c49e5</t>
+          <t>batch_164c8f2ccaa64eaf</t>
         </is>
       </c>
       <c r="AU94" t="inlineStr">
@@ -15774,7 +15774,7 @@
       <c r="AW94" t="inlineStr"/>
       <c r="AX94" t="inlineStr">
         <is>
-          <t>2026-05-14T03:50:20+00:00</t>
+          <t>2026-05-20T00:13:57+00:00</t>
         </is>
       </c>
       <c r="AY94" t="inlineStr">
@@ -15927,7 +15927,7 @@
       </c>
       <c r="AT95" t="inlineStr">
         <is>
-          <t>batch_2e8f5425de7c49e5</t>
+          <t>batch_164c8f2ccaa64eaf</t>
         </is>
       </c>
       <c r="AU95" t="inlineStr">
@@ -15943,7 +15943,7 @@
       <c r="AW95" t="inlineStr"/>
       <c r="AX95" t="inlineStr">
         <is>
-          <t>2026-05-14T03:50:20+00:00</t>
+          <t>2026-05-20T00:13:57+00:00</t>
         </is>
       </c>
       <c r="AY95" t="inlineStr">
@@ -16096,7 +16096,7 @@
       </c>
       <c r="AT96" t="inlineStr">
         <is>
-          <t>batch_2e8f5425de7c49e5</t>
+          <t>batch_164c8f2ccaa64eaf</t>
         </is>
       </c>
       <c r="AU96" t="inlineStr">
@@ -16112,7 +16112,7 @@
       <c r="AW96" t="inlineStr"/>
       <c r="AX96" t="inlineStr">
         <is>
-          <t>2026-05-14T03:50:20+00:00</t>
+          <t>2026-05-20T00:13:57+00:00</t>
         </is>
       </c>
       <c r="AY96" t="inlineStr">
@@ -16265,7 +16265,7 @@
       </c>
       <c r="AT97" t="inlineStr">
         <is>
-          <t>batch_2e8f5425de7c49e5</t>
+          <t>batch_164c8f2ccaa64eaf</t>
         </is>
       </c>
       <c r="AU97" t="inlineStr">
@@ -16281,7 +16281,7 @@
       <c r="AW97" t="inlineStr"/>
       <c r="AX97" t="inlineStr">
         <is>
-          <t>2026-05-14T03:50:20+00:00</t>
+          <t>2026-05-20T00:13:57+00:00</t>
         </is>
       </c>
       <c r="AY97" t="inlineStr">
@@ -16434,7 +16434,7 @@
       </c>
       <c r="AT98" t="inlineStr">
         <is>
-          <t>batch_2e8f5425de7c49e5</t>
+          <t>batch_164c8f2ccaa64eaf</t>
         </is>
       </c>
       <c r="AU98" t="inlineStr">
@@ -16450,7 +16450,7 @@
       <c r="AW98" t="inlineStr"/>
       <c r="AX98" t="inlineStr">
         <is>
-          <t>2026-05-14T03:50:20+00:00</t>
+          <t>2026-05-20T00:13:57+00:00</t>
         </is>
       </c>
       <c r="AY98" t="inlineStr">
@@ -16594,7 +16594,7 @@
       </c>
       <c r="AT99" t="inlineStr">
         <is>
-          <t>batch_2e8f5425de7c49e5</t>
+          <t>batch_164c8f2ccaa64eaf</t>
         </is>
       </c>
       <c r="AU99" t="inlineStr">
@@ -16610,7 +16610,7 @@
       <c r="AW99" t="inlineStr"/>
       <c r="AX99" t="inlineStr">
         <is>
-          <t>2026-05-14T03:50:20+00:00</t>
+          <t>2026-05-20T00:13:57+00:00</t>
         </is>
       </c>
       <c r="AY99" t="inlineStr">
@@ -16754,7 +16754,7 @@
       </c>
       <c r="AT100" t="inlineStr">
         <is>
-          <t>batch_2e8f5425de7c49e5</t>
+          <t>batch_164c8f2ccaa64eaf</t>
         </is>
       </c>
       <c r="AU100" t="inlineStr">
@@ -16770,7 +16770,7 @@
       <c r="AW100" t="inlineStr"/>
       <c r="AX100" t="inlineStr">
         <is>
-          <t>2026-05-14T03:50:20+00:00</t>
+          <t>2026-05-20T00:13:57+00:00</t>
         </is>
       </c>
       <c r="AY100" t="inlineStr">
@@ -16914,7 +16914,7 @@
       </c>
       <c r="AT101" t="inlineStr">
         <is>
-          <t>batch_2e8f5425de7c49e5</t>
+          <t>batch_164c8f2ccaa64eaf</t>
         </is>
       </c>
       <c r="AU101" t="inlineStr">
@@ -16930,7 +16930,7 @@
       <c r="AW101" t="inlineStr"/>
       <c r="AX101" t="inlineStr">
         <is>
-          <t>2026-05-14T03:50:20+00:00</t>
+          <t>2026-05-20T00:13:57+00:00</t>
         </is>
       </c>
       <c r="AY101" t="inlineStr">
@@ -17074,7 +17074,7 @@
       </c>
       <c r="AT102" t="inlineStr">
         <is>
-          <t>batch_2e8f5425de7c49e5</t>
+          <t>batch_164c8f2ccaa64eaf</t>
         </is>
       </c>
       <c r="AU102" t="inlineStr">
@@ -17090,7 +17090,7 @@
       <c r="AW102" t="inlineStr"/>
       <c r="AX102" t="inlineStr">
         <is>
-          <t>2026-05-14T03:50:20+00:00</t>
+          <t>2026-05-20T00:13:57+00:00</t>
         </is>
       </c>
       <c r="AY102" t="inlineStr">
@@ -17234,7 +17234,7 @@
       </c>
       <c r="AT103" t="inlineStr">
         <is>
-          <t>batch_2e8f5425de7c49e5</t>
+          <t>batch_164c8f2ccaa64eaf</t>
         </is>
       </c>
       <c r="AU103" t="inlineStr">
@@ -17250,7 +17250,7 @@
       <c r="AW103" t="inlineStr"/>
       <c r="AX103" t="inlineStr">
         <is>
-          <t>2026-05-14T03:50:20+00:00</t>
+          <t>2026-05-20T00:13:57+00:00</t>
         </is>
       </c>
       <c r="AY103" t="inlineStr">
@@ -17394,7 +17394,7 @@
       </c>
       <c r="AT104" t="inlineStr">
         <is>
-          <t>batch_2e8f5425de7c49e5</t>
+          <t>batch_164c8f2ccaa64eaf</t>
         </is>
       </c>
       <c r="AU104" t="inlineStr">
@@ -17410,7 +17410,7 @@
       <c r="AW104" t="inlineStr"/>
       <c r="AX104" t="inlineStr">
         <is>
-          <t>2026-05-14T03:50:20+00:00</t>
+          <t>2026-05-20T00:13:57+00:00</t>
         </is>
       </c>
       <c r="AY104" t="inlineStr">
@@ -17563,7 +17563,7 @@
       </c>
       <c r="AT105" t="inlineStr">
         <is>
-          <t>batch_2e8f5425de7c49e5</t>
+          <t>batch_164c8f2ccaa64eaf</t>
         </is>
       </c>
       <c r="AU105" t="inlineStr">
@@ -17579,7 +17579,7 @@
       <c r="AW105" t="inlineStr"/>
       <c r="AX105" t="inlineStr">
         <is>
-          <t>2026-05-14T03:50:20+00:00</t>
+          <t>2026-05-20T00:13:57+00:00</t>
         </is>
       </c>
       <c r="AY105" t="inlineStr">
@@ -17720,7 +17720,7 @@
       </c>
       <c r="AT106" t="inlineStr">
         <is>
-          <t>batch_2e8f5425de7c49e5</t>
+          <t>batch_164c8f2ccaa64eaf</t>
         </is>
       </c>
       <c r="AU106" t="inlineStr">
@@ -17736,7 +17736,7 @@
       <c r="AW106" t="inlineStr"/>
       <c r="AX106" t="inlineStr">
         <is>
-          <t>2026-05-14T03:50:20+00:00</t>
+          <t>2026-05-20T00:13:57+00:00</t>
         </is>
       </c>
       <c r="AY106" t="inlineStr">
@@ -17877,7 +17877,7 @@
       </c>
       <c r="AT107" t="inlineStr">
         <is>
-          <t>batch_2e8f5425de7c49e5</t>
+          <t>batch_164c8f2ccaa64eaf</t>
         </is>
       </c>
       <c r="AU107" t="inlineStr">
@@ -17893,7 +17893,7 @@
       <c r="AW107" t="inlineStr"/>
       <c r="AX107" t="inlineStr">
         <is>
-          <t>2026-05-14T03:50:20+00:00</t>
+          <t>2026-05-20T00:13:57+00:00</t>
         </is>
       </c>
       <c r="AY107" t="inlineStr">
@@ -18034,7 +18034,7 @@
       </c>
       <c r="AT108" t="inlineStr">
         <is>
-          <t>batch_2e8f5425de7c49e5</t>
+          <t>batch_164c8f2ccaa64eaf</t>
         </is>
       </c>
       <c r="AU108" t="inlineStr">
@@ -18050,7 +18050,7 @@
       <c r="AW108" t="inlineStr"/>
       <c r="AX108" t="inlineStr">
         <is>
-          <t>2026-05-14T03:50:20+00:00</t>
+          <t>2026-05-20T00:13:57+00:00</t>
         </is>
       </c>
       <c r="AY108" t="inlineStr">
@@ -18194,7 +18194,7 @@
       </c>
       <c r="AT109" t="inlineStr">
         <is>
-          <t>batch_2e8f5425de7c49e5</t>
+          <t>batch_164c8f2ccaa64eaf</t>
         </is>
       </c>
       <c r="AU109" t="inlineStr">
@@ -18210,7 +18210,7 @@
       <c r="AW109" t="inlineStr"/>
       <c r="AX109" t="inlineStr">
         <is>
-          <t>2026-05-14T03:50:20+00:00</t>
+          <t>2026-05-20T00:13:57+00:00</t>
         </is>
       </c>
       <c r="AY109" t="inlineStr">
@@ -18354,7 +18354,7 @@
       </c>
       <c r="AT110" t="inlineStr">
         <is>
-          <t>batch_2e8f5425de7c49e5</t>
+          <t>batch_164c8f2ccaa64eaf</t>
         </is>
       </c>
       <c r="AU110" t="inlineStr">
@@ -18370,7 +18370,7 @@
       <c r="AW110" t="inlineStr"/>
       <c r="AX110" t="inlineStr">
         <is>
-          <t>2026-05-14T03:50:20+00:00</t>
+          <t>2026-05-20T00:13:57+00:00</t>
         </is>
       </c>
       <c r="AY110" t="inlineStr">
@@ -18514,7 +18514,7 @@
       </c>
       <c r="AT111" t="inlineStr">
         <is>
-          <t>batch_2e8f5425de7c49e5</t>
+          <t>batch_164c8f2ccaa64eaf</t>
         </is>
       </c>
       <c r="AU111" t="inlineStr">
@@ -18530,7 +18530,7 @@
       <c r="AW111" t="inlineStr"/>
       <c r="AX111" t="inlineStr">
         <is>
-          <t>2026-05-14T03:50:20+00:00</t>
+          <t>2026-05-20T00:13:57+00:00</t>
         </is>
       </c>
       <c r="AY111" t="inlineStr">
@@ -18674,7 +18674,7 @@
       </c>
       <c r="AT112" t="inlineStr">
         <is>
-          <t>batch_2e8f5425de7c49e5</t>
+          <t>batch_164c8f2ccaa64eaf</t>
         </is>
       </c>
       <c r="AU112" t="inlineStr">
@@ -18690,7 +18690,7 @@
       <c r="AW112" t="inlineStr"/>
       <c r="AX112" t="inlineStr">
         <is>
-          <t>2026-05-14T03:50:20+00:00</t>
+          <t>2026-05-20T00:13:57+00:00</t>
         </is>
       </c>
       <c r="AY112" t="inlineStr">
@@ -18834,7 +18834,7 @@
       </c>
       <c r="AT113" t="inlineStr">
         <is>
-          <t>batch_2e8f5425de7c49e5</t>
+          <t>batch_164c8f2ccaa64eaf</t>
         </is>
       </c>
       <c r="AU113" t="inlineStr">
@@ -18850,7 +18850,7 @@
       <c r="AW113" t="inlineStr"/>
       <c r="AX113" t="inlineStr">
         <is>
-          <t>2026-05-14T03:50:20+00:00</t>
+          <t>2026-05-20T00:13:57+00:00</t>
         </is>
       </c>
       <c r="AY113" t="inlineStr">
@@ -18994,7 +18994,7 @@
       </c>
       <c r="AT114" t="inlineStr">
         <is>
-          <t>batch_2e8f5425de7c49e5</t>
+          <t>batch_164c8f2ccaa64eaf</t>
         </is>
       </c>
       <c r="AU114" t="inlineStr">
@@ -19010,7 +19010,7 @@
       <c r="AW114" t="inlineStr"/>
       <c r="AX114" t="inlineStr">
         <is>
-          <t>2026-05-14T03:50:20+00:00</t>
+          <t>2026-05-20T00:13:57+00:00</t>
         </is>
       </c>
       <c r="AY114" t="inlineStr">
@@ -19154,7 +19154,7 @@
       </c>
       <c r="AT115" t="inlineStr">
         <is>
-          <t>batch_2e8f5425de7c49e5</t>
+          <t>batch_164c8f2ccaa64eaf</t>
         </is>
       </c>
       <c r="AU115" t="inlineStr">
@@ -19170,7 +19170,7 @@
       <c r="AW115" t="inlineStr"/>
       <c r="AX115" t="inlineStr">
         <is>
-          <t>2026-05-14T03:50:20+00:00</t>
+          <t>2026-05-20T00:13:57+00:00</t>
         </is>
       </c>
       <c r="AY115" t="inlineStr">
@@ -19314,7 +19314,7 @@
       </c>
       <c r="AT116" t="inlineStr">
         <is>
-          <t>batch_2e8f5425de7c49e5</t>
+          <t>batch_164c8f2ccaa64eaf</t>
         </is>
       </c>
       <c r="AU116" t="inlineStr">
@@ -19330,7 +19330,7 @@
       <c r="AW116" t="inlineStr"/>
       <c r="AX116" t="inlineStr">
         <is>
-          <t>2026-05-14T03:50:20+00:00</t>
+          <t>2026-05-20T00:13:57+00:00</t>
         </is>
       </c>
       <c r="AY116" t="inlineStr">
@@ -19474,7 +19474,7 @@
       </c>
       <c r="AT117" t="inlineStr">
         <is>
-          <t>batch_2e8f5425de7c49e5</t>
+          <t>batch_164c8f2ccaa64eaf</t>
         </is>
       </c>
       <c r="AU117" t="inlineStr">
@@ -19490,7 +19490,7 @@
       <c r="AW117" t="inlineStr"/>
       <c r="AX117" t="inlineStr">
         <is>
-          <t>2026-05-14T03:50:20+00:00</t>
+          <t>2026-05-20T00:13:57+00:00</t>
         </is>
       </c>
       <c r="AY117" t="inlineStr">
@@ -19634,7 +19634,7 @@
       </c>
       <c r="AT118" t="inlineStr">
         <is>
-          <t>batch_2e8f5425de7c49e5</t>
+          <t>batch_164c8f2ccaa64eaf</t>
         </is>
       </c>
       <c r="AU118" t="inlineStr">
@@ -19650,7 +19650,7 @@
       <c r="AW118" t="inlineStr"/>
       <c r="AX118" t="inlineStr">
         <is>
-          <t>2026-05-14T03:50:20+00:00</t>
+          <t>2026-05-20T00:13:57+00:00</t>
         </is>
       </c>
       <c r="AY118" t="inlineStr">
@@ -19794,7 +19794,7 @@
       </c>
       <c r="AT119" t="inlineStr">
         <is>
-          <t>batch_2e8f5425de7c49e5</t>
+          <t>batch_164c8f2ccaa64eaf</t>
         </is>
       </c>
       <c r="AU119" t="inlineStr">
@@ -19810,7 +19810,7 @@
       <c r="AW119" t="inlineStr"/>
       <c r="AX119" t="inlineStr">
         <is>
-          <t>2026-05-14T03:50:20+00:00</t>
+          <t>2026-05-20T00:13:57+00:00</t>
         </is>
       </c>
       <c r="AY119" t="inlineStr">
@@ -19954,7 +19954,7 @@
       </c>
       <c r="AT120" t="inlineStr">
         <is>
-          <t>batch_2e8f5425de7c49e5</t>
+          <t>batch_164c8f2ccaa64eaf</t>
         </is>
       </c>
       <c r="AU120" t="inlineStr">
@@ -19970,7 +19970,7 @@
       <c r="AW120" t="inlineStr"/>
       <c r="AX120" t="inlineStr">
         <is>
-          <t>2026-05-14T03:50:20+00:00</t>
+          <t>2026-05-20T00:13:57+00:00</t>
         </is>
       </c>
       <c r="AY120" t="inlineStr">
@@ -20114,7 +20114,7 @@
       </c>
       <c r="AT121" t="inlineStr">
         <is>
-          <t>batch_2e8f5425de7c49e5</t>
+          <t>batch_164c8f2ccaa64eaf</t>
         </is>
       </c>
       <c r="AU121" t="inlineStr">
@@ -20130,7 +20130,7 @@
       <c r="AW121" t="inlineStr"/>
       <c r="AX121" t="inlineStr">
         <is>
-          <t>2026-05-14T03:50:20+00:00</t>
+          <t>2026-05-20T00:13:57+00:00</t>
         </is>
       </c>
       <c r="AY121" t="inlineStr">
@@ -20274,7 +20274,7 @@
       </c>
       <c r="AT122" t="inlineStr">
         <is>
-          <t>batch_2e8f5425de7c49e5</t>
+          <t>batch_164c8f2ccaa64eaf</t>
         </is>
       </c>
       <c r="AU122" t="inlineStr">
@@ -20290,7 +20290,7 @@
       <c r="AW122" t="inlineStr"/>
       <c r="AX122" t="inlineStr">
         <is>
-          <t>2026-05-14T03:50:20+00:00</t>
+          <t>2026-05-20T00:13:57+00:00</t>
         </is>
       </c>
       <c r="AY122" t="inlineStr">
@@ -20434,7 +20434,7 @@
       </c>
       <c r="AT123" t="inlineStr">
         <is>
-          <t>batch_2e8f5425de7c49e5</t>
+          <t>batch_164c8f2ccaa64eaf</t>
         </is>
       </c>
       <c r="AU123" t="inlineStr">
@@ -20450,7 +20450,7 @@
       <c r="AW123" t="inlineStr"/>
       <c r="AX123" t="inlineStr">
         <is>
-          <t>2026-05-14T03:50:20+00:00</t>
+          <t>2026-05-20T00:13:57+00:00</t>
         </is>
       </c>
       <c r="AY123" t="inlineStr">
@@ -20594,7 +20594,7 @@
       </c>
       <c r="AT124" t="inlineStr">
         <is>
-          <t>batch_2e8f5425de7c49e5</t>
+          <t>batch_164c8f2ccaa64eaf</t>
         </is>
       </c>
       <c r="AU124" t="inlineStr">
@@ -20610,7 +20610,7 @@
       <c r="AW124" t="inlineStr"/>
       <c r="AX124" t="inlineStr">
         <is>
-          <t>2026-05-14T03:50:20+00:00</t>
+          <t>2026-05-20T00:13:57+00:00</t>
         </is>
       </c>
       <c r="AY124" t="inlineStr">
@@ -20754,7 +20754,7 @@
       </c>
       <c r="AT125" t="inlineStr">
         <is>
-          <t>batch_2e8f5425de7c49e5</t>
+          <t>batch_164c8f2ccaa64eaf</t>
         </is>
       </c>
       <c r="AU125" t="inlineStr">
@@ -20770,7 +20770,7 @@
       <c r="AW125" t="inlineStr"/>
       <c r="AX125" t="inlineStr">
         <is>
-          <t>2026-05-14T03:50:20+00:00</t>
+          <t>2026-05-20T00:13:57+00:00</t>
         </is>
       </c>
       <c r="AY125" t="inlineStr">
@@ -20914,7 +20914,7 @@
       </c>
       <c r="AT126" t="inlineStr">
         <is>
-          <t>batch_2e8f5425de7c49e5</t>
+          <t>batch_164c8f2ccaa64eaf</t>
         </is>
       </c>
       <c r="AU126" t="inlineStr">
@@ -20930,7 +20930,7 @@
       <c r="AW126" t="inlineStr"/>
       <c r="AX126" t="inlineStr">
         <is>
-          <t>2026-05-14T03:50:20+00:00</t>
+          <t>2026-05-20T00:13:57+00:00</t>
         </is>
       </c>
       <c r="AY126" t="inlineStr">
@@ -21074,7 +21074,7 @@
       </c>
       <c r="AT127" t="inlineStr">
         <is>
-          <t>batch_2e8f5425de7c49e5</t>
+          <t>batch_164c8f2ccaa64eaf</t>
         </is>
       </c>
       <c r="AU127" t="inlineStr">
@@ -21090,7 +21090,7 @@
       <c r="AW127" t="inlineStr"/>
       <c r="AX127" t="inlineStr">
         <is>
-          <t>2026-05-14T03:50:20+00:00</t>
+          <t>2026-05-20T00:13:57+00:00</t>
         </is>
       </c>
       <c r="AY127" t="inlineStr">
@@ -21234,7 +21234,7 @@
       </c>
       <c r="AT128" t="inlineStr">
         <is>
-          <t>batch_2e8f5425de7c49e5</t>
+          <t>batch_164c8f2ccaa64eaf</t>
         </is>
       </c>
       <c r="AU128" t="inlineStr">
@@ -21250,7 +21250,7 @@
       <c r="AW128" t="inlineStr"/>
       <c r="AX128" t="inlineStr">
         <is>
-          <t>2026-05-14T03:50:20+00:00</t>
+          <t>2026-05-20T00:13:57+00:00</t>
         </is>
       </c>
       <c r="AY128" t="inlineStr">
@@ -21394,7 +21394,7 @@
       </c>
       <c r="AT129" t="inlineStr">
         <is>
-          <t>batch_2e8f5425de7c49e5</t>
+          <t>batch_164c8f2ccaa64eaf</t>
         </is>
       </c>
       <c r="AU129" t="inlineStr">
@@ -21410,7 +21410,7 @@
       <c r="AW129" t="inlineStr"/>
       <c r="AX129" t="inlineStr">
         <is>
-          <t>2026-05-14T03:50:20+00:00</t>
+          <t>2026-05-20T00:13:57+00:00</t>
         </is>
       </c>
       <c r="AY129" t="inlineStr">
@@ -21554,7 +21554,7 @@
       </c>
       <c r="AT130" t="inlineStr">
         <is>
-          <t>batch_2e8f5425de7c49e5</t>
+          <t>batch_164c8f2ccaa64eaf</t>
         </is>
       </c>
       <c r="AU130" t="inlineStr">
@@ -21570,7 +21570,7 @@
       <c r="AW130" t="inlineStr"/>
       <c r="AX130" t="inlineStr">
         <is>
-          <t>2026-05-14T03:50:20+00:00</t>
+          <t>2026-05-20T00:13:57+00:00</t>
         </is>
       </c>
       <c r="AY130" t="inlineStr">
@@ -21714,7 +21714,7 @@
       </c>
       <c r="AT131" t="inlineStr">
         <is>
-          <t>batch_2e8f5425de7c49e5</t>
+          <t>batch_164c8f2ccaa64eaf</t>
         </is>
       </c>
       <c r="AU131" t="inlineStr">
@@ -21730,7 +21730,7 @@
       <c r="AW131" t="inlineStr"/>
       <c r="AX131" t="inlineStr">
         <is>
-          <t>2026-05-14T03:50:20+00:00</t>
+          <t>2026-05-20T00:13:57+00:00</t>
         </is>
       </c>
       <c r="AY131" t="inlineStr">
@@ -21874,7 +21874,7 @@
       </c>
       <c r="AT132" t="inlineStr">
         <is>
-          <t>batch_2e8f5425de7c49e5</t>
+          <t>batch_164c8f2ccaa64eaf</t>
         </is>
       </c>
       <c r="AU132" t="inlineStr">
@@ -21890,7 +21890,7 @@
       <c r="AW132" t="inlineStr"/>
       <c r="AX132" t="inlineStr">
         <is>
-          <t>2026-05-14T03:50:20+00:00</t>
+          <t>2026-05-20T00:13:57+00:00</t>
         </is>
       </c>
       <c r="AY132" t="inlineStr">
@@ -22034,7 +22034,7 @@
       </c>
       <c r="AT133" t="inlineStr">
         <is>
-          <t>batch_2e8f5425de7c49e5</t>
+          <t>batch_164c8f2ccaa64eaf</t>
         </is>
       </c>
       <c r="AU133" t="inlineStr">
@@ -22050,7 +22050,7 @@
       <c r="AW133" t="inlineStr"/>
       <c r="AX133" t="inlineStr">
         <is>
-          <t>2026-05-14T03:50:20+00:00</t>
+          <t>2026-05-20T00:13:57+00:00</t>
         </is>
       </c>
       <c r="AY133" t="inlineStr">
@@ -22194,7 +22194,7 @@
       </c>
       <c r="AT134" t="inlineStr">
         <is>
-          <t>batch_2e8f5425de7c49e5</t>
+          <t>batch_164c8f2ccaa64eaf</t>
         </is>
       </c>
       <c r="AU134" t="inlineStr">
@@ -22210,7 +22210,7 @@
       <c r="AW134" t="inlineStr"/>
       <c r="AX134" t="inlineStr">
         <is>
-          <t>2026-05-14T03:50:20+00:00</t>
+          <t>2026-05-20T00:13:57+00:00</t>
         </is>
       </c>
       <c r="AY134" t="inlineStr">
@@ -22354,7 +22354,7 @@
       </c>
       <c r="AT135" t="inlineStr">
         <is>
-          <t>batch_2e8f5425de7c49e5</t>
+          <t>batch_164c8f2ccaa64eaf</t>
         </is>
       </c>
       <c r="AU135" t="inlineStr">
@@ -22370,7 +22370,7 @@
       <c r="AW135" t="inlineStr"/>
       <c r="AX135" t="inlineStr">
         <is>
-          <t>2026-05-14T03:50:20+00:00</t>
+          <t>2026-05-20T00:13:57+00:00</t>
         </is>
       </c>
       <c r="AY135" t="inlineStr">
@@ -22514,7 +22514,7 @@
       </c>
       <c r="AT136" t="inlineStr">
         <is>
-          <t>batch_2e8f5425de7c49e5</t>
+          <t>batch_164c8f2ccaa64eaf</t>
         </is>
       </c>
       <c r="AU136" t="inlineStr">
@@ -22530,7 +22530,7 @@
       <c r="AW136" t="inlineStr"/>
       <c r="AX136" t="inlineStr">
         <is>
-          <t>2026-05-14T03:50:20+00:00</t>
+          <t>2026-05-20T00:13:57+00:00</t>
         </is>
       </c>
       <c r="AY136" t="inlineStr">
@@ -22674,7 +22674,7 @@
       </c>
       <c r="AT137" t="inlineStr">
         <is>
-          <t>batch_2e8f5425de7c49e5</t>
+          <t>batch_164c8f2ccaa64eaf</t>
         </is>
       </c>
       <c r="AU137" t="inlineStr">
@@ -22690,7 +22690,7 @@
       <c r="AW137" t="inlineStr"/>
       <c r="AX137" t="inlineStr">
         <is>
-          <t>2026-05-14T03:50:20+00:00</t>
+          <t>2026-05-20T00:13:57+00:00</t>
         </is>
       </c>
       <c r="AY137" t="inlineStr">
@@ -22834,7 +22834,7 @@
       </c>
       <c r="AT138" t="inlineStr">
         <is>
-          <t>batch_2e8f5425de7c49e5</t>
+          <t>batch_164c8f2ccaa64eaf</t>
         </is>
       </c>
       <c r="AU138" t="inlineStr">
@@ -22850,7 +22850,7 @@
       <c r="AW138" t="inlineStr"/>
       <c r="AX138" t="inlineStr">
         <is>
-          <t>2026-05-14T03:50:20+00:00</t>
+          <t>2026-05-20T00:13:57+00:00</t>
         </is>
       </c>
       <c r="AY138" t="inlineStr">
@@ -22994,7 +22994,7 @@
       </c>
       <c r="AT139" t="inlineStr">
         <is>
-          <t>batch_2e8f5425de7c49e5</t>
+          <t>batch_164c8f2ccaa64eaf</t>
         </is>
       </c>
       <c r="AU139" t="inlineStr">
@@ -23010,7 +23010,7 @@
       <c r="AW139" t="inlineStr"/>
       <c r="AX139" t="inlineStr">
         <is>
-          <t>2026-05-14T03:50:20+00:00</t>
+          <t>2026-05-20T00:13:57+00:00</t>
         </is>
       </c>
       <c r="AY139" t="inlineStr">
@@ -23154,7 +23154,7 @@
       </c>
       <c r="AT140" t="inlineStr">
         <is>
-          <t>batch_2e8f5425de7c49e5</t>
+          <t>batch_164c8f2ccaa64eaf</t>
         </is>
       </c>
       <c r="AU140" t="inlineStr">
@@ -23170,7 +23170,7 @@
       <c r="AW140" t="inlineStr"/>
       <c r="AX140" t="inlineStr">
         <is>
-          <t>2026-05-14T03:50:20+00:00</t>
+          <t>2026-05-20T00:13:57+00:00</t>
         </is>
       </c>
       <c r="AY140" t="inlineStr">
@@ -23314,7 +23314,7 @@
       </c>
       <c r="AT141" t="inlineStr">
         <is>
-          <t>batch_2e8f5425de7c49e5</t>
+          <t>batch_164c8f2ccaa64eaf</t>
         </is>
       </c>
       <c r="AU141" t="inlineStr">
@@ -23330,7 +23330,7 @@
       <c r="AW141" t="inlineStr"/>
       <c r="AX141" t="inlineStr">
         <is>
-          <t>2026-05-14T03:50:20+00:00</t>
+          <t>2026-05-20T00:13:57+00:00</t>
         </is>
       </c>
       <c r="AY141" t="inlineStr">
@@ -23474,7 +23474,7 @@
       </c>
       <c r="AT142" t="inlineStr">
         <is>
-          <t>batch_2e8f5425de7c49e5</t>
+          <t>batch_164c8f2ccaa64eaf</t>
         </is>
       </c>
       <c r="AU142" t="inlineStr">
@@ -23490,7 +23490,7 @@
       <c r="AW142" t="inlineStr"/>
       <c r="AX142" t="inlineStr">
         <is>
-          <t>2026-05-14T03:50:20+00:00</t>
+          <t>2026-05-20T00:13:57+00:00</t>
         </is>
       </c>
       <c r="AY142" t="inlineStr">
@@ -23634,7 +23634,7 @@
       </c>
       <c r="AT143" t="inlineStr">
         <is>
-          <t>batch_2e8f5425de7c49e5</t>
+          <t>batch_164c8f2ccaa64eaf</t>
         </is>
       </c>
       <c r="AU143" t="inlineStr">
@@ -23650,7 +23650,7 @@
       <c r="AW143" t="inlineStr"/>
       <c r="AX143" t="inlineStr">
         <is>
-          <t>2026-05-14T03:50:20+00:00</t>
+          <t>2026-05-20T00:13:57+00:00</t>
         </is>
       </c>
       <c r="AY143" t="inlineStr">
@@ -23794,7 +23794,7 @@
       </c>
       <c r="AT144" t="inlineStr">
         <is>
-          <t>batch_2e8f5425de7c49e5</t>
+          <t>batch_164c8f2ccaa64eaf</t>
         </is>
       </c>
       <c r="AU144" t="inlineStr">
@@ -23810,7 +23810,7 @@
       <c r="AW144" t="inlineStr"/>
       <c r="AX144" t="inlineStr">
         <is>
-          <t>2026-05-14T03:50:20+00:00</t>
+          <t>2026-05-20T00:13:57+00:00</t>
         </is>
       </c>
       <c r="AY144" t="inlineStr">
@@ -23954,7 +23954,7 @@
       </c>
       <c r="AT145" t="inlineStr">
         <is>
-          <t>batch_2e8f5425de7c49e5</t>
+          <t>batch_164c8f2ccaa64eaf</t>
         </is>
       </c>
       <c r="AU145" t="inlineStr">
@@ -23970,7 +23970,7 @@
       <c r="AW145" t="inlineStr"/>
       <c r="AX145" t="inlineStr">
         <is>
-          <t>2026-05-14T03:50:20+00:00</t>
+          <t>2026-05-20T00:13:57+00:00</t>
         </is>
       </c>
       <c r="AY145" t="inlineStr">
@@ -24114,7 +24114,7 @@
       </c>
       <c r="AT146" t="inlineStr">
         <is>
-          <t>batch_2e8f5425de7c49e5</t>
+          <t>batch_164c8f2ccaa64eaf</t>
         </is>
       </c>
       <c r="AU146" t="inlineStr">
@@ -24130,7 +24130,7 @@
       <c r="AW146" t="inlineStr"/>
       <c r="AX146" t="inlineStr">
         <is>
-          <t>2026-05-14T03:50:20+00:00</t>
+          <t>2026-05-20T00:13:57+00:00</t>
         </is>
       </c>
       <c r="AY146" t="inlineStr">
@@ -24274,7 +24274,7 @@
       </c>
       <c r="AT147" t="inlineStr">
         <is>
-          <t>batch_2e8f5425de7c49e5</t>
+          <t>batch_164c8f2ccaa64eaf</t>
         </is>
       </c>
       <c r="AU147" t="inlineStr">
@@ -24290,7 +24290,7 @@
       <c r="AW147" t="inlineStr"/>
       <c r="AX147" t="inlineStr">
         <is>
-          <t>2026-05-14T03:50:20+00:00</t>
+          <t>2026-05-20T00:13:57+00:00</t>
         </is>
       </c>
       <c r="AY147" t="inlineStr">
@@ -24434,7 +24434,7 @@
       </c>
       <c r="AT148" t="inlineStr">
         <is>
-          <t>batch_2e8f5425de7c49e5</t>
+          <t>batch_164c8f2ccaa64eaf</t>
         </is>
       </c>
       <c r="AU148" t="inlineStr">
@@ -24450,7 +24450,7 @@
       <c r="AW148" t="inlineStr"/>
       <c r="AX148" t="inlineStr">
         <is>
-          <t>2026-05-14T03:50:20+00:00</t>
+          <t>2026-05-20T00:13:57+00:00</t>
         </is>
       </c>
       <c r="AY148" t="inlineStr">
@@ -24594,7 +24594,7 @@
       </c>
       <c r="AT149" t="inlineStr">
         <is>
-          <t>batch_2e8f5425de7c49e5</t>
+          <t>batch_164c8f2ccaa64eaf</t>
         </is>
       </c>
       <c r="AU149" t="inlineStr">
@@ -24610,7 +24610,7 @@
       <c r="AW149" t="inlineStr"/>
       <c r="AX149" t="inlineStr">
         <is>
-          <t>2026-05-14T03:50:20+00:00</t>
+          <t>2026-05-20T00:13:57+00:00</t>
         </is>
       </c>
       <c r="AY149" t="inlineStr">
@@ -24754,7 +24754,7 @@
       </c>
       <c r="AT150" t="inlineStr">
         <is>
-          <t>batch_2e8f5425de7c49e5</t>
+          <t>batch_164c8f2ccaa64eaf</t>
         </is>
       </c>
       <c r="AU150" t="inlineStr">
@@ -24770,7 +24770,7 @@
       <c r="AW150" t="inlineStr"/>
       <c r="AX150" t="inlineStr">
         <is>
-          <t>2026-05-14T03:50:20+00:00</t>
+          <t>2026-05-20T00:13:57+00:00</t>
         </is>
       </c>
       <c r="AY150" t="inlineStr">
@@ -24914,7 +24914,7 @@
       </c>
       <c r="AT151" t="inlineStr">
         <is>
-          <t>batch_2e8f5425de7c49e5</t>
+          <t>batch_164c8f2ccaa64eaf</t>
         </is>
       </c>
       <c r="AU151" t="inlineStr">
@@ -24930,7 +24930,7 @@
       <c r="AW151" t="inlineStr"/>
       <c r="AX151" t="inlineStr">
         <is>
-          <t>2026-05-14T03:50:20+00:00</t>
+          <t>2026-05-20T00:13:57+00:00</t>
         </is>
       </c>
       <c r="AY151" t="inlineStr">
@@ -25074,7 +25074,7 @@
       </c>
       <c r="AT152" t="inlineStr">
         <is>
-          <t>batch_2e8f5425de7c49e5</t>
+          <t>batch_164c8f2ccaa64eaf</t>
         </is>
       </c>
       <c r="AU152" t="inlineStr">
@@ -25090,7 +25090,7 @@
       <c r="AW152" t="inlineStr"/>
       <c r="AX152" t="inlineStr">
         <is>
-          <t>2026-05-14T03:50:20+00:00</t>
+          <t>2026-05-20T00:13:57+00:00</t>
         </is>
       </c>
       <c r="AY152" t="inlineStr">
@@ -25234,7 +25234,7 @@
       </c>
       <c r="AT153" t="inlineStr">
         <is>
-          <t>batch_2e8f5425de7c49e5</t>
+          <t>batch_164c8f2ccaa64eaf</t>
         </is>
       </c>
       <c r="AU153" t="inlineStr">
@@ -25250,7 +25250,7 @@
       <c r="AW153" t="inlineStr"/>
       <c r="AX153" t="inlineStr">
         <is>
-          <t>2026-05-14T03:50:20+00:00</t>
+          <t>2026-05-20T00:13:57+00:00</t>
         </is>
       </c>
       <c r="AY153" t="inlineStr">
@@ -25394,7 +25394,7 @@
       </c>
       <c r="AT154" t="inlineStr">
         <is>
-          <t>batch_2e8f5425de7c49e5</t>
+          <t>batch_164c8f2ccaa64eaf</t>
         </is>
       </c>
       <c r="AU154" t="inlineStr">
@@ -25410,7 +25410,7 @@
       <c r="AW154" t="inlineStr"/>
       <c r="AX154" t="inlineStr">
         <is>
-          <t>2026-05-14T03:50:20+00:00</t>
+          <t>2026-05-20T00:13:57+00:00</t>
         </is>
       </c>
       <c r="AY154" t="inlineStr">
@@ -25554,7 +25554,7 @@
       </c>
       <c r="AT155" t="inlineStr">
         <is>
-          <t>batch_2e8f5425de7c49e5</t>
+          <t>batch_164c8f2ccaa64eaf</t>
         </is>
       </c>
       <c r="AU155" t="inlineStr">
@@ -25570,7 +25570,7 @@
       <c r="AW155" t="inlineStr"/>
       <c r="AX155" t="inlineStr">
         <is>
-          <t>2026-05-14T03:50:20+00:00</t>
+          <t>2026-05-20T00:13:57+00:00</t>
         </is>
       </c>
       <c r="AY155" t="inlineStr">
@@ -25714,7 +25714,7 @@
       </c>
       <c r="AT156" t="inlineStr">
         <is>
-          <t>batch_2e8f5425de7c49e5</t>
+          <t>batch_164c8f2ccaa64eaf</t>
         </is>
       </c>
       <c r="AU156" t="inlineStr">
@@ -25730,7 +25730,7 @@
       <c r="AW156" t="inlineStr"/>
       <c r="AX156" t="inlineStr">
         <is>
-          <t>2026-05-14T03:50:20+00:00</t>
+          <t>2026-05-20T00:13:57+00:00</t>
         </is>
       </c>
       <c r="AY156" t="inlineStr">
@@ -25874,7 +25874,7 @@
       </c>
       <c r="AT157" t="inlineStr">
         <is>
-          <t>batch_2e8f5425de7c49e5</t>
+          <t>batch_164c8f2ccaa64eaf</t>
         </is>
       </c>
       <c r="AU157" t="inlineStr">
@@ -25890,7 +25890,7 @@
       <c r="AW157" t="inlineStr"/>
       <c r="AX157" t="inlineStr">
         <is>
-          <t>2026-05-14T03:50:20+00:00</t>
+          <t>2026-05-20T00:13:57+00:00</t>
         </is>
       </c>
       <c r="AY157" t="inlineStr">
@@ -26034,7 +26034,7 @@
       </c>
       <c r="AT158" t="inlineStr">
         <is>
-          <t>batch_2e8f5425de7c49e5</t>
+          <t>batch_164c8f2ccaa64eaf</t>
         </is>
       </c>
       <c r="AU158" t="inlineStr">
@@ -26050,7 +26050,7 @@
       <c r="AW158" t="inlineStr"/>
       <c r="AX158" t="inlineStr">
         <is>
-          <t>2026-05-14T03:50:20+00:00</t>
+          <t>2026-05-20T00:13:57+00:00</t>
         </is>
       </c>
       <c r="AY158" t="inlineStr">
@@ -26194,7 +26194,7 @@
       </c>
       <c r="AT159" t="inlineStr">
         <is>
-          <t>batch_2e8f5425de7c49e5</t>
+          <t>batch_164c8f2ccaa64eaf</t>
         </is>
       </c>
       <c r="AU159" t="inlineStr">
@@ -26210,7 +26210,7 @@
       <c r="AW159" t="inlineStr"/>
       <c r="AX159" t="inlineStr">
         <is>
-          <t>2026-05-14T03:50:20+00:00</t>
+          <t>2026-05-20T00:13:57+00:00</t>
         </is>
       </c>
       <c r="AY159" t="inlineStr">
@@ -26354,7 +26354,7 @@
       </c>
       <c r="AT160" t="inlineStr">
         <is>
-          <t>batch_2e8f5425de7c49e5</t>
+          <t>batch_164c8f2ccaa64eaf</t>
         </is>
       </c>
       <c r="AU160" t="inlineStr">
@@ -26370,7 +26370,7 @@
       <c r="AW160" t="inlineStr"/>
       <c r="AX160" t="inlineStr">
         <is>
-          <t>2026-05-14T03:50:20+00:00</t>
+          <t>2026-05-20T00:13:57+00:00</t>
         </is>
       </c>
       <c r="AY160" t="inlineStr">
@@ -26514,7 +26514,7 @@
       </c>
       <c r="AT161" t="inlineStr">
         <is>
-          <t>batch_2e8f5425de7c49e5</t>
+          <t>batch_164c8f2ccaa64eaf</t>
         </is>
       </c>
       <c r="AU161" t="inlineStr">
@@ -26530,7 +26530,7 @@
       <c r="AW161" t="inlineStr"/>
       <c r="AX161" t="inlineStr">
         <is>
-          <t>2026-05-14T03:50:20+00:00</t>
+          <t>2026-05-20T00:13:57+00:00</t>
         </is>
       </c>
       <c r="AY161" t="inlineStr">
@@ -26674,7 +26674,7 @@
       </c>
       <c r="AT162" t="inlineStr">
         <is>
-          <t>batch_2e8f5425de7c49e5</t>
+          <t>batch_164c8f2ccaa64eaf</t>
         </is>
       </c>
       <c r="AU162" t="inlineStr">
@@ -26690,7 +26690,7 @@
       <c r="AW162" t="inlineStr"/>
       <c r="AX162" t="inlineStr">
         <is>
-          <t>2026-05-14T03:50:20+00:00</t>
+          <t>2026-05-20T00:13:57+00:00</t>
         </is>
       </c>
       <c r="AY162" t="inlineStr">
@@ -26834,7 +26834,7 @@
       </c>
       <c r="AT163" t="inlineStr">
         <is>
-          <t>batch_2e8f5425de7c49e5</t>
+          <t>batch_164c8f2ccaa64eaf</t>
         </is>
       </c>
       <c r="AU163" t="inlineStr">
@@ -26850,7 +26850,7 @@
       <c r="AW163" t="inlineStr"/>
       <c r="AX163" t="inlineStr">
         <is>
-          <t>2026-05-14T03:50:20+00:00</t>
+          <t>2026-05-20T00:13:57+00:00</t>
         </is>
       </c>
       <c r="AY163" t="inlineStr">
@@ -26994,7 +26994,7 @@
       </c>
       <c r="AT164" t="inlineStr">
         <is>
-          <t>batch_2e8f5425de7c49e5</t>
+          <t>batch_164c8f2ccaa64eaf</t>
         </is>
       </c>
       <c r="AU164" t="inlineStr">
@@ -27010,7 +27010,7 @@
       <c r="AW164" t="inlineStr"/>
       <c r="AX164" t="inlineStr">
         <is>
-          <t>2026-05-14T03:50:20+00:00</t>
+          <t>2026-05-20T00:13:57+00:00</t>
         </is>
       </c>
       <c r="AY164" t="inlineStr">
@@ -27154,7 +27154,7 @@
       </c>
       <c r="AT165" t="inlineStr">
         <is>
-          <t>batch_2e8f5425de7c49e5</t>
+          <t>batch_164c8f2ccaa64eaf</t>
         </is>
       </c>
       <c r="AU165" t="inlineStr">
@@ -27170,7 +27170,7 @@
       <c r="AW165" t="inlineStr"/>
       <c r="AX165" t="inlineStr">
         <is>
-          <t>2026-05-14T03:50:20+00:00</t>
+          <t>2026-05-20T00:13:57+00:00</t>
         </is>
       </c>
       <c r="AY165" t="inlineStr">
@@ -27314,7 +27314,7 @@
       </c>
       <c r="AT166" t="inlineStr">
         <is>
-          <t>batch_2e8f5425de7c49e5</t>
+          <t>batch_164c8f2ccaa64eaf</t>
         </is>
       </c>
       <c r="AU166" t="inlineStr">
@@ -27330,7 +27330,7 @@
       <c r="AW166" t="inlineStr"/>
       <c r="AX166" t="inlineStr">
         <is>
-          <t>2026-05-14T03:50:20+00:00</t>
+          <t>2026-05-20T00:13:57+00:00</t>
         </is>
       </c>
       <c r="AY166" t="inlineStr">
@@ -27474,7 +27474,7 @@
       </c>
       <c r="AT167" t="inlineStr">
         <is>
-          <t>batch_2e8f5425de7c49e5</t>
+          <t>batch_164c8f2ccaa64eaf</t>
         </is>
       </c>
       <c r="AU167" t="inlineStr">
@@ -27490,7 +27490,7 @@
       <c r="AW167" t="inlineStr"/>
       <c r="AX167" t="inlineStr">
         <is>
-          <t>2026-05-14T03:50:20+00:00</t>
+          <t>2026-05-20T00:13:57+00:00</t>
         </is>
       </c>
       <c r="AY167" t="inlineStr">
@@ -27634,7 +27634,7 @@
       </c>
       <c r="AT168" t="inlineStr">
         <is>
-          <t>batch_2e8f5425de7c49e5</t>
+          <t>batch_164c8f2ccaa64eaf</t>
         </is>
       </c>
       <c r="AU168" t="inlineStr">
@@ -27650,7 +27650,7 @@
       <c r="AW168" t="inlineStr"/>
       <c r="AX168" t="inlineStr">
         <is>
-          <t>2026-05-14T03:50:20+00:00</t>
+          <t>2026-05-20T00:13:57+00:00</t>
         </is>
       </c>
       <c r="AY168" t="inlineStr">
@@ -27794,7 +27794,7 @@
       </c>
       <c r="AT169" t="inlineStr">
         <is>
-          <t>batch_2e8f5425de7c49e5</t>
+          <t>batch_164c8f2ccaa64eaf</t>
         </is>
       </c>
       <c r="AU169" t="inlineStr">
@@ -27810,7 +27810,7 @@
       <c r="AW169" t="inlineStr"/>
       <c r="AX169" t="inlineStr">
         <is>
-          <t>2026-05-14T03:50:20+00:00</t>
+          <t>2026-05-20T00:13:57+00:00</t>
         </is>
       </c>
       <c r="AY169" t="inlineStr">
@@ -27954,7 +27954,7 @@
       </c>
       <c r="AT170" t="inlineStr">
         <is>
-          <t>batch_2e8f5425de7c49e5</t>
+          <t>batch_164c8f2ccaa64eaf</t>
         </is>
       </c>
       <c r="AU170" t="inlineStr">
@@ -27970,7 +27970,7 @@
       <c r="AW170" t="inlineStr"/>
       <c r="AX170" t="inlineStr">
         <is>
-          <t>2026-05-14T03:50:20+00:00</t>
+          <t>2026-05-20T00:13:57+00:00</t>
         </is>
       </c>
       <c r="AY170" t="inlineStr">
@@ -28114,7 +28114,7 @@
       </c>
       <c r="AT171" t="inlineStr">
         <is>
-          <t>batch_2e8f5425de7c49e5</t>
+          <t>batch_164c8f2ccaa64eaf</t>
         </is>
       </c>
       <c r="AU171" t="inlineStr">
@@ -28130,7 +28130,7 @@
       <c r="AW171" t="inlineStr"/>
       <c r="AX171" t="inlineStr">
         <is>
-          <t>2026-05-14T03:50:20+00:00</t>
+          <t>2026-05-20T00:13:57+00:00</t>
         </is>
       </c>
       <c r="AY171" t="inlineStr">
@@ -28274,7 +28274,7 @@
       </c>
       <c r="AT172" t="inlineStr">
         <is>
-          <t>batch_2e8f5425de7c49e5</t>
+          <t>batch_164c8f2ccaa64eaf</t>
         </is>
       </c>
       <c r="AU172" t="inlineStr">
@@ -28290,7 +28290,7 @@
       <c r="AW172" t="inlineStr"/>
       <c r="AX172" t="inlineStr">
         <is>
-          <t>2026-05-14T03:50:20+00:00</t>
+          <t>2026-05-20T00:13:57+00:00</t>
         </is>
       </c>
       <c r="AY172" t="inlineStr">
@@ -28434,7 +28434,7 @@
       </c>
       <c r="AT173" t="inlineStr">
         <is>
-          <t>batch_2e8f5425de7c49e5</t>
+          <t>batch_164c8f2ccaa64eaf</t>
         </is>
       </c>
       <c r="AU173" t="inlineStr">
@@ -28450,7 +28450,7 @@
       <c r="AW173" t="inlineStr"/>
       <c r="AX173" t="inlineStr">
         <is>
-          <t>2026-05-14T03:50:20+00:00</t>
+          <t>2026-05-20T00:13:57+00:00</t>
         </is>
       </c>
       <c r="AY173" t="inlineStr">
@@ -28594,7 +28594,7 @@
       </c>
       <c r="AT174" t="inlineStr">
         <is>
-          <t>batch_2e8f5425de7c49e5</t>
+          <t>batch_164c8f2ccaa64eaf</t>
         </is>
       </c>
       <c r="AU174" t="inlineStr">
@@ -28610,7 +28610,7 @@
       <c r="AW174" t="inlineStr"/>
       <c r="AX174" t="inlineStr">
         <is>
-          <t>2026-05-14T03:50:20+00:00</t>
+          <t>2026-05-20T00:13:57+00:00</t>
         </is>
       </c>
       <c r="AY174" t="inlineStr">
@@ -28754,7 +28754,7 @@
       </c>
       <c r="AT175" t="inlineStr">
         <is>
-          <t>batch_2e8f5425de7c49e5</t>
+          <t>batch_164c8f2ccaa64eaf</t>
         </is>
       </c>
       <c r="AU175" t="inlineStr">
@@ -28770,7 +28770,7 @@
       <c r="AW175" t="inlineStr"/>
       <c r="AX175" t="inlineStr">
         <is>
-          <t>2026-05-14T03:50:20+00:00</t>
+          <t>2026-05-20T00:13:57+00:00</t>
         </is>
       </c>
       <c r="AY175" t="inlineStr">
@@ -28914,7 +28914,7 @@
       </c>
       <c r="AT176" t="inlineStr">
         <is>
-          <t>batch_2e8f5425de7c49e5</t>
+          <t>batch_164c8f2ccaa64eaf</t>
         </is>
       </c>
       <c r="AU176" t="inlineStr">
@@ -28930,7 +28930,7 @@
       <c r="AW176" t="inlineStr"/>
       <c r="AX176" t="inlineStr">
         <is>
-          <t>2026-05-14T03:50:20+00:00</t>
+          <t>2026-05-20T00:13:57+00:00</t>
         </is>
       </c>
       <c r="AY176" t="inlineStr">
@@ -29074,7 +29074,7 @@
       </c>
       <c r="AT177" t="inlineStr">
         <is>
-          <t>batch_2e8f5425de7c49e5</t>
+          <t>batch_164c8f2ccaa64eaf</t>
         </is>
       </c>
       <c r="AU177" t="inlineStr">
@@ -29090,7 +29090,7 @@
       <c r="AW177" t="inlineStr"/>
       <c r="AX177" t="inlineStr">
         <is>
-          <t>2026-05-14T03:50:20+00:00</t>
+          <t>2026-05-20T00:13:57+00:00</t>
         </is>
       </c>
       <c r="AY177" t="inlineStr">
@@ -29234,7 +29234,7 @@
       </c>
       <c r="AT178" t="inlineStr">
         <is>
-          <t>batch_2e8f5425de7c49e5</t>
+          <t>batch_164c8f2ccaa64eaf</t>
         </is>
       </c>
       <c r="AU178" t="inlineStr">
@@ -29250,7 +29250,7 @@
       <c r="AW178" t="inlineStr"/>
       <c r="AX178" t="inlineStr">
         <is>
-          <t>2026-05-14T03:50:20+00:00</t>
+          <t>2026-05-20T00:13:57+00:00</t>
         </is>
       </c>
       <c r="AY178" t="inlineStr">
@@ -29394,7 +29394,7 @@
       </c>
       <c r="AT179" t="inlineStr">
         <is>
-          <t>batch_2e8f5425de7c49e5</t>
+          <t>batch_164c8f2ccaa64eaf</t>
         </is>
       </c>
       <c r="AU179" t="inlineStr">
@@ -29410,7 +29410,7 @@
       <c r="AW179" t="inlineStr"/>
       <c r="AX179" t="inlineStr">
         <is>
-          <t>2026-05-14T03:50:20+00:00</t>
+          <t>2026-05-20T00:13:57+00:00</t>
         </is>
       </c>
       <c r="AY179" t="inlineStr">
@@ -29554,7 +29554,7 @@
       </c>
       <c r="AT180" t="inlineStr">
         <is>
-          <t>batch_2e8f5425de7c49e5</t>
+          <t>batch_164c8f2ccaa64eaf</t>
         </is>
       </c>
       <c r="AU180" t="inlineStr">
@@ -29570,7 +29570,7 @@
       <c r="AW180" t="inlineStr"/>
       <c r="AX180" t="inlineStr">
         <is>
-          <t>2026-05-14T03:50:20+00:00</t>
+          <t>2026-05-20T00:13:57+00:00</t>
         </is>
       </c>
       <c r="AY180" t="inlineStr">
@@ -29714,7 +29714,7 @@
       </c>
       <c r="AT181" t="inlineStr">
         <is>
-          <t>batch_2e8f5425de7c49e5</t>
+          <t>batch_164c8f2ccaa64eaf</t>
         </is>
       </c>
       <c r="AU181" t="inlineStr">
@@ -29730,7 +29730,7 @@
       <c r="AW181" t="inlineStr"/>
       <c r="AX181" t="inlineStr">
         <is>
-          <t>2026-05-14T03:50:20+00:00</t>
+          <t>2026-05-20T00:13:57+00:00</t>
         </is>
       </c>
       <c r="AY181" t="inlineStr">
@@ -29874,7 +29874,7 @@
       </c>
       <c r="AT182" t="inlineStr">
         <is>
-          <t>batch_2e8f5425de7c49e5</t>
+          <t>batch_164c8f2ccaa64eaf</t>
         </is>
       </c>
       <c r="AU182" t="inlineStr">
@@ -29890,7 +29890,7 @@
       <c r="AW182" t="inlineStr"/>
       <c r="AX182" t="inlineStr">
         <is>
-          <t>2026-05-14T03:50:20+00:00</t>
+          <t>2026-05-20T00:13:57+00:00</t>
         </is>
       </c>
       <c r="AY182" t="inlineStr">
@@ -30031,7 +30031,7 @@
       </c>
       <c r="AT183" t="inlineStr">
         <is>
-          <t>batch_2e8f5425de7c49e5</t>
+          <t>batch_164c8f2ccaa64eaf</t>
         </is>
       </c>
       <c r="AU183" t="inlineStr">
@@ -30047,7 +30047,7 @@
       <c r="AW183" t="inlineStr"/>
       <c r="AX183" t="inlineStr">
         <is>
-          <t>2026-05-14T03:50:20+00:00</t>
+          <t>2026-05-20T00:13:57+00:00</t>
         </is>
       </c>
       <c r="AY183" t="inlineStr">
@@ -30191,7 +30191,7 @@
       </c>
       <c r="AT184" t="inlineStr">
         <is>
-          <t>batch_2e8f5425de7c49e5</t>
+          <t>batch_164c8f2ccaa64eaf</t>
         </is>
       </c>
       <c r="AU184" t="inlineStr">
@@ -30207,7 +30207,7 @@
       <c r="AW184" t="inlineStr"/>
       <c r="AX184" t="inlineStr">
         <is>
-          <t>2026-05-14T03:50:20+00:00</t>
+          <t>2026-05-20T00:13:57+00:00</t>
         </is>
       </c>
       <c r="AY184" t="inlineStr">
@@ -30351,7 +30351,7 @@
       </c>
       <c r="AT185" t="inlineStr">
         <is>
-          <t>batch_2e8f5425de7c49e5</t>
+          <t>batch_164c8f2ccaa64eaf</t>
         </is>
       </c>
       <c r="AU185" t="inlineStr">
@@ -30367,7 +30367,7 @@
       <c r="AW185" t="inlineStr"/>
       <c r="AX185" t="inlineStr">
         <is>
-          <t>2026-05-14T03:50:20+00:00</t>
+          <t>2026-05-20T00:13:57+00:00</t>
         </is>
       </c>
       <c r="AY185" t="inlineStr">
@@ -30511,7 +30511,7 @@
       </c>
       <c r="AT186" t="inlineStr">
         <is>
-          <t>batch_2e8f5425de7c49e5</t>
+          <t>batch_164c8f2ccaa64eaf</t>
         </is>
       </c>
       <c r="AU186" t="inlineStr">
@@ -30527,7 +30527,7 @@
       <c r="AW186" t="inlineStr"/>
       <c r="AX186" t="inlineStr">
         <is>
-          <t>2026-05-14T03:50:20+00:00</t>
+          <t>2026-05-20T00:13:57+00:00</t>
         </is>
       </c>
       <c r="AY186" t="inlineStr">
@@ -30671,7 +30671,7 @@
       </c>
       <c r="AT187" t="inlineStr">
         <is>
-          <t>batch_2e8f5425de7c49e5</t>
+          <t>batch_164c8f2ccaa64eaf</t>
         </is>
       </c>
       <c r="AU187" t="inlineStr">
@@ -30687,7 +30687,7 @@
       <c r="AW187" t="inlineStr"/>
       <c r="AX187" t="inlineStr">
         <is>
-          <t>2026-05-14T03:50:20+00:00</t>
+          <t>2026-05-20T00:13:57+00:00</t>
         </is>
       </c>
       <c r="AY187" t="inlineStr">
@@ -30831,7 +30831,7 @@
       </c>
       <c r="AT188" t="inlineStr">
         <is>
-          <t>batch_2e8f5425de7c49e5</t>
+          <t>batch_164c8f2ccaa64eaf</t>
         </is>
       </c>
       <c r="AU188" t="inlineStr">
@@ -30847,7 +30847,7 @@
       <c r="AW188" t="inlineStr"/>
       <c r="AX188" t="inlineStr">
         <is>
-          <t>2026-05-14T03:50:20+00:00</t>
+          <t>2026-05-20T00:13:57+00:00</t>
         </is>
       </c>
       <c r="AY188" t="inlineStr">
@@ -30991,7 +30991,7 @@
       </c>
       <c r="AT189" t="inlineStr">
         <is>
-          <t>batch_2e8f5425de7c49e5</t>
+          <t>batch_164c8f2ccaa64eaf</t>
         </is>
       </c>
       <c r="AU189" t="inlineStr">
@@ -31007,7 +31007,7 @@
       <c r="AW189" t="inlineStr"/>
       <c r="AX189" t="inlineStr">
         <is>
-          <t>2026-05-14T03:50:20+00:00</t>
+          <t>2026-05-20T00:13:57+00:00</t>
         </is>
       </c>
       <c r="AY189" t="inlineStr">
@@ -31151,7 +31151,7 @@
       </c>
       <c r="AT190" t="inlineStr">
         <is>
-          <t>batch_2e8f5425de7c49e5</t>
+          <t>batch_164c8f2ccaa64eaf</t>
         </is>
       </c>
       <c r="AU190" t="inlineStr">
@@ -31167,7 +31167,7 @@
       <c r="AW190" t="inlineStr"/>
       <c r="AX190" t="inlineStr">
         <is>
-          <t>2026-05-14T03:50:20+00:00</t>
+          <t>2026-05-20T00:13:57+00:00</t>
         </is>
       </c>
       <c r="AY190" t="inlineStr">
@@ -31311,7 +31311,7 @@
       </c>
       <c r="AT191" t="inlineStr">
         <is>
-          <t>batch_2e8f5425de7c49e5</t>
+          <t>batch_164c8f2ccaa64eaf</t>
         </is>
       </c>
       <c r="AU191" t="inlineStr">
@@ -31327,7 +31327,7 @@
       <c r="AW191" t="inlineStr"/>
       <c r="AX191" t="inlineStr">
         <is>
-          <t>2026-05-14T03:50:20+00:00</t>
+          <t>2026-05-20T00:13:57+00:00</t>
         </is>
       </c>
       <c r="AY191" t="inlineStr">
@@ -31471,7 +31471,7 @@
       </c>
       <c r="AT192" t="inlineStr">
         <is>
-          <t>batch_2e8f5425de7c49e5</t>
+          <t>batch_164c8f2ccaa64eaf</t>
         </is>
       </c>
       <c r="AU192" t="inlineStr">
@@ -31487,7 +31487,7 @@
       <c r="AW192" t="inlineStr"/>
       <c r="AX192" t="inlineStr">
         <is>
-          <t>2026-05-14T03:50:20+00:00</t>
+          <t>2026-05-20T00:13:57+00:00</t>
         </is>
       </c>
       <c r="AY192" t="inlineStr">
@@ -31631,7 +31631,7 @@
       </c>
       <c r="AT193" t="inlineStr">
         <is>
-          <t>batch_2e8f5425de7c49e5</t>
+          <t>batch_164c8f2ccaa64eaf</t>
         </is>
       </c>
       <c r="AU193" t="inlineStr">
@@ -31647,7 +31647,7 @@
       <c r="AW193" t="inlineStr"/>
       <c r="AX193" t="inlineStr">
         <is>
-          <t>2026-05-14T03:50:20+00:00</t>
+          <t>2026-05-20T00:13:57+00:00</t>
         </is>
       </c>
       <c r="AY193" t="inlineStr">
@@ -31791,7 +31791,7 @@
       </c>
       <c r="AT194" t="inlineStr">
         <is>
-          <t>batch_2e8f5425de7c49e5</t>
+          <t>batch_164c8f2ccaa64eaf</t>
         </is>
       </c>
       <c r="AU194" t="inlineStr">
@@ -31807,7 +31807,7 @@
       <c r="AW194" t="inlineStr"/>
       <c r="AX194" t="inlineStr">
         <is>
-          <t>2026-05-14T03:50:20+00:00</t>
+          <t>2026-05-20T00:13:57+00:00</t>
         </is>
       </c>
       <c r="AY194" t="inlineStr">
@@ -31951,7 +31951,7 @@
       </c>
       <c r="AT195" t="inlineStr">
         <is>
-          <t>batch_2e8f5425de7c49e5</t>
+          <t>batch_164c8f2ccaa64eaf</t>
         </is>
       </c>
       <c r="AU195" t="inlineStr">
@@ -31967,7 +31967,7 @@
       <c r="AW195" t="inlineStr"/>
       <c r="AX195" t="inlineStr">
         <is>
-          <t>2026-05-14T03:50:20+00:00</t>
+          <t>2026-05-20T00:13:57+00:00</t>
         </is>
       </c>
       <c r="AY195" t="inlineStr">
@@ -32111,7 +32111,7 @@
       </c>
       <c r="AT196" t="inlineStr">
         <is>
-          <t>batch_2e8f5425de7c49e5</t>
+          <t>batch_164c8f2ccaa64eaf</t>
         </is>
       </c>
       <c r="AU196" t="inlineStr">
@@ -32127,7 +32127,7 @@
       <c r="AW196" t="inlineStr"/>
       <c r="AX196" t="inlineStr">
         <is>
-          <t>2026-05-14T03:50:20+00:00</t>
+          <t>2026-05-20T00:13:57+00:00</t>
         </is>
       </c>
       <c r="AY196" t="inlineStr">
@@ -32271,7 +32271,7 @@
       </c>
       <c r="AT197" t="inlineStr">
         <is>
-          <t>batch_2e8f5425de7c49e5</t>
+          <t>batch_164c8f2ccaa64eaf</t>
         </is>
       </c>
       <c r="AU197" t="inlineStr">
@@ -32287,7 +32287,7 @@
       <c r="AW197" t="inlineStr"/>
       <c r="AX197" t="inlineStr">
         <is>
-          <t>2026-05-14T03:50:20+00:00</t>
+          <t>2026-05-20T00:13:57+00:00</t>
         </is>
       </c>
       <c r="AY197" t="inlineStr">
@@ -32431,7 +32431,7 @@
       </c>
       <c r="AT198" t="inlineStr">
         <is>
-          <t>batch_2e8f5425de7c49e5</t>
+          <t>batch_164c8f2ccaa64eaf</t>
         </is>
       </c>
       <c r="AU198" t="inlineStr">
@@ -32447,7 +32447,7 @@
       <c r="AW198" t="inlineStr"/>
       <c r="AX198" t="inlineStr">
         <is>
-          <t>2026-05-14T03:50:20+00:00</t>
+          <t>2026-05-20T00:13:57+00:00</t>
         </is>
       </c>
       <c r="AY198" t="inlineStr">
@@ -32591,7 +32591,7 @@
       </c>
       <c r="AT199" t="inlineStr">
         <is>
-          <t>batch_2e8f5425de7c49e5</t>
+          <t>batch_164c8f2ccaa64eaf</t>
         </is>
       </c>
       <c r="AU199" t="inlineStr">
@@ -32607,7 +32607,7 @@
       <c r="AW199" t="inlineStr"/>
       <c r="AX199" t="inlineStr">
         <is>
-          <t>2026-05-14T03:50:20+00:00</t>
+          <t>2026-05-20T00:13:57+00:00</t>
         </is>
       </c>
       <c r="AY199" t="inlineStr">
@@ -32751,7 +32751,7 @@
       </c>
       <c r="AT200" t="inlineStr">
         <is>
-          <t>batch_2e8f5425de7c49e5</t>
+          <t>batch_164c8f2ccaa64eaf</t>
         </is>
       </c>
       <c r="AU200" t="inlineStr">
@@ -32767,7 +32767,7 @@
       <c r="AW200" t="inlineStr"/>
       <c r="AX200" t="inlineStr">
         <is>
-          <t>2026-05-14T03:50:20+00:00</t>
+          <t>2026-05-20T00:13:57+00:00</t>
         </is>
       </c>
       <c r="AY200" t="inlineStr">
@@ -32920,7 +32920,7 @@
       </c>
       <c r="AT201" t="inlineStr">
         <is>
-          <t>batch_2e8f5425de7c49e5</t>
+          <t>batch_164c8f2ccaa64eaf</t>
         </is>
       </c>
       <c r="AU201" t="inlineStr">
@@ -32936,7 +32936,7 @@
       <c r="AW201" t="inlineStr"/>
       <c r="AX201" t="inlineStr">
         <is>
-          <t>2026-05-14T03:50:20+00:00</t>
+          <t>2026-05-20T00:13:57+00:00</t>
         </is>
       </c>
       <c r="AY201" t="inlineStr">
@@ -33089,7 +33089,7 @@
       </c>
       <c r="AT202" t="inlineStr">
         <is>
-          <t>batch_2e8f5425de7c49e5</t>
+          <t>batch_164c8f2ccaa64eaf</t>
         </is>
       </c>
       <c r="AU202" t="inlineStr">
@@ -33105,7 +33105,7 @@
       <c r="AW202" t="inlineStr"/>
       <c r="AX202" t="inlineStr">
         <is>
-          <t>2026-05-14T03:50:20+00:00</t>
+          <t>2026-05-20T00:13:57+00:00</t>
         </is>
       </c>
       <c r="AY202" t="inlineStr">
@@ -33249,7 +33249,7 @@
       </c>
       <c r="AT203" t="inlineStr">
         <is>
-          <t>batch_2e8f5425de7c49e5</t>
+          <t>batch_164c8f2ccaa64eaf</t>
         </is>
       </c>
       <c r="AU203" t="inlineStr">
@@ -33265,7 +33265,7 @@
       <c r="AW203" t="inlineStr"/>
       <c r="AX203" t="inlineStr">
         <is>
-          <t>2026-05-14T03:50:20+00:00</t>
+          <t>2026-05-20T00:13:57+00:00</t>
         </is>
       </c>
       <c r="AY203" t="inlineStr">
@@ -33409,7 +33409,7 @@
       </c>
       <c r="AT204" t="inlineStr">
         <is>
-          <t>batch_2e8f5425de7c49e5</t>
+          <t>batch_164c8f2ccaa64eaf</t>
         </is>
       </c>
       <c r="AU204" t="inlineStr">
@@ -33425,7 +33425,7 @@
       <c r="AW204" t="inlineStr"/>
       <c r="AX204" t="inlineStr">
         <is>
-          <t>2026-05-14T03:50:20+00:00</t>
+          <t>2026-05-20T00:13:57+00:00</t>
         </is>
       </c>
       <c r="AY204" t="inlineStr">
@@ -33569,7 +33569,7 @@
       </c>
       <c r="AT205" t="inlineStr">
         <is>
-          <t>batch_2e8f5425de7c49e5</t>
+          <t>batch_164c8f2ccaa64eaf</t>
         </is>
       </c>
       <c r="AU205" t="inlineStr">
@@ -33585,7 +33585,7 @@
       <c r="AW205" t="inlineStr"/>
       <c r="AX205" t="inlineStr">
         <is>
-          <t>2026-05-14T03:50:20+00:00</t>
+          <t>2026-05-20T00:13:57+00:00</t>
         </is>
       </c>
       <c r="AY205" t="inlineStr">
@@ -33729,7 +33729,7 @@
       </c>
       <c r="AT206" t="inlineStr">
         <is>
-          <t>batch_2e8f5425de7c49e5</t>
+          <t>batch_164c8f2ccaa64eaf</t>
         </is>
       </c>
       <c r="AU206" t="inlineStr">
@@ -33745,7 +33745,7 @@
       <c r="AW206" t="inlineStr"/>
       <c r="AX206" t="inlineStr">
         <is>
-          <t>2026-05-14T03:50:20+00:00</t>
+          <t>2026-05-20T00:13:57+00:00</t>
         </is>
       </c>
       <c r="AY206" t="inlineStr">
@@ -33889,7 +33889,7 @@
       </c>
       <c r="AT207" t="inlineStr">
         <is>
-          <t>batch_2e8f5425de7c49e5</t>
+          <t>batch_164c8f2ccaa64eaf</t>
         </is>
       </c>
       <c r="AU207" t="inlineStr">
@@ -33905,7 +33905,7 @@
       <c r="AW207" t="inlineStr"/>
       <c r="AX207" t="inlineStr">
         <is>
-          <t>2026-05-14T03:50:20+00:00</t>
+          <t>2026-05-20T00:13:57+00:00</t>
         </is>
       </c>
       <c r="AY207" t="inlineStr">
@@ -34049,7 +34049,7 @@
       </c>
       <c r="AT208" t="inlineStr">
         <is>
-          <t>batch_2e8f5425de7c49e5</t>
+          <t>batch_164c8f2ccaa64eaf</t>
         </is>
       </c>
       <c r="AU208" t="inlineStr">
@@ -34065,7 +34065,7 @@
       <c r="AW208" t="inlineStr"/>
       <c r="AX208" t="inlineStr">
         <is>
-          <t>2026-05-14T03:50:20+00:00</t>
+          <t>2026-05-20T00:13:57+00:00</t>
         </is>
       </c>
       <c r="AY208" t="inlineStr">
@@ -34209,7 +34209,7 @@
       </c>
       <c r="AT209" t="inlineStr">
         <is>
-          <t>batch_2e8f5425de7c49e5</t>
+          <t>batch_164c8f2ccaa64eaf</t>
         </is>
       </c>
       <c r="AU209" t="inlineStr">
@@ -34225,7 +34225,7 @@
       <c r="AW209" t="inlineStr"/>
       <c r="AX209" t="inlineStr">
         <is>
-          <t>2026-05-14T03:50:20+00:00</t>
+          <t>2026-05-20T00:13:57+00:00</t>
         </is>
       </c>
       <c r="AY209" t="inlineStr">
@@ -34369,7 +34369,7 @@
       </c>
       <c r="AT210" t="inlineStr">
         <is>
-          <t>batch_2e8f5425de7c49e5</t>
+          <t>batch_164c8f2ccaa64eaf</t>
         </is>
       </c>
       <c r="AU210" t="inlineStr">
@@ -34385,7 +34385,7 @@
       <c r="AW210" t="inlineStr"/>
       <c r="AX210" t="inlineStr">
         <is>
-          <t>2026-05-14T03:50:20+00:00</t>
+          <t>2026-05-20T00:13:57+00:00</t>
         </is>
       </c>
       <c r="AY210" t="inlineStr">
@@ -34529,7 +34529,7 @@
       </c>
       <c r="AT211" t="inlineStr">
         <is>
-          <t>batch_2e8f5425de7c49e5</t>
+          <t>batch_164c8f2ccaa64eaf</t>
         </is>
       </c>
       <c r="AU211" t="inlineStr">
@@ -34545,7 +34545,7 @@
       <c r="AW211" t="inlineStr"/>
       <c r="AX211" t="inlineStr">
         <is>
-          <t>2026-05-14T03:50:20+00:00</t>
+          <t>2026-05-20T00:13:57+00:00</t>
         </is>
       </c>
       <c r="AY211" t="inlineStr">
@@ -34689,7 +34689,7 @@
       </c>
       <c r="AT212" t="inlineStr">
         <is>
-          <t>batch_2e8f5425de7c49e5</t>
+          <t>batch_164c8f2ccaa64eaf</t>
         </is>
       </c>
       <c r="AU212" t="inlineStr">
@@ -34705,7 +34705,7 @@
       <c r="AW212" t="inlineStr"/>
       <c r="AX212" t="inlineStr">
         <is>
-          <t>2026-05-14T03:50:20+00:00</t>
+          <t>2026-05-20T00:13:57+00:00</t>
         </is>
       </c>
       <c r="AY212" t="inlineStr">
@@ -34849,7 +34849,7 @@
       </c>
       <c r="AT213" t="inlineStr">
         <is>
-          <t>batch_2e8f5425de7c49e5</t>
+          <t>batch_164c8f2ccaa64eaf</t>
         </is>
       </c>
       <c r="AU213" t="inlineStr">
@@ -34865,7 +34865,7 @@
       <c r="AW213" t="inlineStr"/>
       <c r="AX213" t="inlineStr">
         <is>
-          <t>2026-05-14T03:50:20+00:00</t>
+          <t>2026-05-20T00:13:57+00:00</t>
         </is>
       </c>
       <c r="AY213" t="inlineStr">
@@ -35009,7 +35009,7 @@
       </c>
       <c r="AT214" t="inlineStr">
         <is>
-          <t>batch_2e8f5425de7c49e5</t>
+          <t>batch_164c8f2ccaa64eaf</t>
         </is>
       </c>
       <c r="AU214" t="inlineStr">
@@ -35025,7 +35025,7 @@
       <c r="AW214" t="inlineStr"/>
       <c r="AX214" t="inlineStr">
         <is>
-          <t>2026-05-14T03:50:20+00:00</t>
+          <t>2026-05-20T00:13:57+00:00</t>
         </is>
       </c>
       <c r="AY214" t="inlineStr">
@@ -35169,7 +35169,7 @@
       </c>
       <c r="AT215" t="inlineStr">
         <is>
-          <t>batch_2e8f5425de7c49e5</t>
+          <t>batch_164c8f2ccaa64eaf</t>
         </is>
       </c>
       <c r="AU215" t="inlineStr">
@@ -35185,7 +35185,7 @@
       <c r="AW215" t="inlineStr"/>
       <c r="AX215" t="inlineStr">
         <is>
-          <t>2026-05-14T03:50:20+00:00</t>
+          <t>2026-05-20T00:13:57+00:00</t>
         </is>
       </c>
       <c r="AY215" t="inlineStr">
@@ -35329,7 +35329,7 @@
       </c>
       <c r="AT216" t="inlineStr">
         <is>
-          <t>batch_2e8f5425de7c49e5</t>
+          <t>batch_164c8f2ccaa64eaf</t>
         </is>
       </c>
       <c r="AU216" t="inlineStr">
@@ -35345,7 +35345,7 @@
       <c r="AW216" t="inlineStr"/>
       <c r="AX216" t="inlineStr">
         <is>
-          <t>2026-05-14T03:50:20+00:00</t>
+          <t>2026-05-20T00:13:57+00:00</t>
         </is>
       </c>
       <c r="AY216" t="inlineStr">
@@ -35489,7 +35489,7 @@
       </c>
       <c r="AT217" t="inlineStr">
         <is>
-          <t>batch_2e8f5425de7c49e5</t>
+          <t>batch_164c8f2ccaa64eaf</t>
         </is>
       </c>
       <c r="AU217" t="inlineStr">
@@ -35505,7 +35505,7 @@
       <c r="AW217" t="inlineStr"/>
       <c r="AX217" t="inlineStr">
         <is>
-          <t>2026-05-14T03:50:20+00:00</t>
+          <t>2026-05-20T00:13:57+00:00</t>
         </is>
       </c>
       <c r="AY217" t="inlineStr">
@@ -35649,7 +35649,7 @@
       </c>
       <c r="AT218" t="inlineStr">
         <is>
-          <t>batch_2e8f5425de7c49e5</t>
+          <t>batch_164c8f2ccaa64eaf</t>
         </is>
       </c>
       <c r="AU218" t="inlineStr">
@@ -35665,7 +35665,7 @@
       <c r="AW218" t="inlineStr"/>
       <c r="AX218" t="inlineStr">
         <is>
-          <t>2026-05-14T03:50:20+00:00</t>
+          <t>2026-05-20T00:13:57+00:00</t>
         </is>
       </c>
       <c r="AY218" t="inlineStr">
@@ -35809,7 +35809,7 @@
       </c>
       <c r="AT219" t="inlineStr">
         <is>
-          <t>batch_2e8f5425de7c49e5</t>
+          <t>batch_164c8f2ccaa64eaf</t>
         </is>
       </c>
       <c r="AU219" t="inlineStr">
@@ -35825,7 +35825,7 @@
       <c r="AW219" t="inlineStr"/>
       <c r="AX219" t="inlineStr">
         <is>
-          <t>2026-05-14T03:50:20+00:00</t>
+          <t>2026-05-20T00:13:57+00:00</t>
         </is>
       </c>
       <c r="AY219" t="inlineStr">
@@ -35969,7 +35969,7 @@
       </c>
       <c r="AT220" t="inlineStr">
         <is>
-          <t>batch_2e8f5425de7c49e5</t>
+          <t>batch_164c8f2ccaa64eaf</t>
         </is>
       </c>
       <c r="AU220" t="inlineStr">
@@ -35985,7 +35985,7 @@
       <c r="AW220" t="inlineStr"/>
       <c r="AX220" t="inlineStr">
         <is>
-          <t>2026-05-14T03:50:20+00:00</t>
+          <t>2026-05-20T00:13:57+00:00</t>
         </is>
       </c>
       <c r="AY220" t="inlineStr">
@@ -36129,7 +36129,7 @@
       </c>
       <c r="AT221" t="inlineStr">
         <is>
-          <t>batch_2e8f5425de7c49e5</t>
+          <t>batch_164c8f2ccaa64eaf</t>
         </is>
       </c>
       <c r="AU221" t="inlineStr">
@@ -36145,7 +36145,7 @@
       <c r="AW221" t="inlineStr"/>
       <c r="AX221" t="inlineStr">
         <is>
-          <t>2026-05-14T03:50:20+00:00</t>
+          <t>2026-05-20T00:13:57+00:00</t>
         </is>
       </c>
       <c r="AY221" t="inlineStr">
@@ -36289,7 +36289,7 @@
       </c>
       <c r="AT222" t="inlineStr">
         <is>
-          <t>batch_2e8f5425de7c49e5</t>
+          <t>batch_164c8f2ccaa64eaf</t>
         </is>
       </c>
       <c r="AU222" t="inlineStr">
@@ -36305,7 +36305,7 @@
       <c r="AW222" t="inlineStr"/>
       <c r="AX222" t="inlineStr">
         <is>
-          <t>2026-05-14T03:50:20+00:00</t>
+          <t>2026-05-20T00:13:57+00:00</t>
         </is>
       </c>
       <c r="AY222" t="inlineStr">
@@ -36449,7 +36449,7 @@
       </c>
       <c r="AT223" t="inlineStr">
         <is>
-          <t>batch_2e8f5425de7c49e5</t>
+          <t>batch_164c8f2ccaa64eaf</t>
         </is>
       </c>
       <c r="AU223" t="inlineStr">
@@ -36465,7 +36465,7 @@
       <c r="AW223" t="inlineStr"/>
       <c r="AX223" t="inlineStr">
         <is>
-          <t>2026-05-14T03:50:20+00:00</t>
+          <t>2026-05-20T00:13:57+00:00</t>
         </is>
       </c>
       <c r="AY223" t="inlineStr">
@@ -36609,7 +36609,7 @@
       </c>
       <c r="AT224" t="inlineStr">
         <is>
-          <t>batch_2e8f5425de7c49e5</t>
+          <t>batch_164c8f2ccaa64eaf</t>
         </is>
       </c>
       <c r="AU224" t="inlineStr">
@@ -36625,7 +36625,7 @@
       <c r="AW224" t="inlineStr"/>
       <c r="AX224" t="inlineStr">
         <is>
-          <t>2026-05-14T03:50:20+00:00</t>
+          <t>2026-05-20T00:13:57+00:00</t>
         </is>
       </c>
       <c r="AY224" t="inlineStr">
@@ -36769,7 +36769,7 @@
       </c>
       <c r="AT225" t="inlineStr">
         <is>
-          <t>batch_2e8f5425de7c49e5</t>
+          <t>batch_164c8f2ccaa64eaf</t>
         </is>
       </c>
       <c r="AU225" t="inlineStr">
@@ -36785,7 +36785,7 @@
       <c r="AW225" t="inlineStr"/>
       <c r="AX225" t="inlineStr">
         <is>
-          <t>2026-05-14T03:50:20+00:00</t>
+          <t>2026-05-20T00:13:57+00:00</t>
         </is>
       </c>
       <c r="AY225" t="inlineStr">
@@ -36929,7 +36929,7 @@
       </c>
       <c r="AT226" t="inlineStr">
         <is>
-          <t>batch_2e8f5425de7c49e5</t>
+          <t>batch_164c8f2ccaa64eaf</t>
         </is>
       </c>
       <c r="AU226" t="inlineStr">
@@ -36945,7 +36945,7 @@
       <c r="AW226" t="inlineStr"/>
       <c r="AX226" t="inlineStr">
         <is>
-          <t>2026-05-14T03:50:20+00:00</t>
+          <t>2026-05-20T00:13:57+00:00</t>
         </is>
       </c>
       <c r="AY226" t="inlineStr">
@@ -37089,7 +37089,7 @@
       </c>
       <c r="AT227" t="inlineStr">
         <is>
-          <t>batch_2e8f5425de7c49e5</t>
+          <t>batch_164c8f2ccaa64eaf</t>
         </is>
       </c>
       <c r="AU227" t="inlineStr">
@@ -37105,7 +37105,7 @@
       <c r="AW227" t="inlineStr"/>
       <c r="AX227" t="inlineStr">
         <is>
-          <t>2026-05-14T03:50:20+00:00</t>
+          <t>2026-05-20T00:13:57+00:00</t>
         </is>
       </c>
       <c r="AY227" t="inlineStr">
@@ -37249,7 +37249,7 @@
       </c>
       <c r="AT228" t="inlineStr">
         <is>
-          <t>batch_2e8f5425de7c49e5</t>
+          <t>batch_164c8f2ccaa64eaf</t>
         </is>
       </c>
       <c r="AU228" t="inlineStr">
@@ -37265,7 +37265,7 @@
       <c r="AW228" t="inlineStr"/>
       <c r="AX228" t="inlineStr">
         <is>
-          <t>2026-05-14T03:50:20+00:00</t>
+          <t>2026-05-20T00:13:57+00:00</t>
         </is>
       </c>
       <c r="AY228" t="inlineStr">
@@ -37409,7 +37409,7 @@
       </c>
       <c r="AT229" t="inlineStr">
         <is>
-          <t>batch_2e8f5425de7c49e5</t>
+          <t>batch_164c8f2ccaa64eaf</t>
         </is>
       </c>
       <c r="AU229" t="inlineStr">
@@ -37425,7 +37425,7 @@
       <c r="AW229" t="inlineStr"/>
       <c r="AX229" t="inlineStr">
         <is>
-          <t>2026-05-14T03:50:20+00:00</t>
+          <t>2026-05-20T00:13:57+00:00</t>
         </is>
       </c>
       <c r="AY229" t="inlineStr">
@@ -37569,7 +37569,7 @@
       </c>
       <c r="AT230" t="inlineStr">
         <is>
-          <t>batch_2e8f5425de7c49e5</t>
+          <t>batch_164c8f2ccaa64eaf</t>
         </is>
       </c>
       <c r="AU230" t="inlineStr">
@@ -37585,7 +37585,7 @@
       <c r="AW230" t="inlineStr"/>
       <c r="AX230" t="inlineStr">
         <is>
-          <t>2026-05-14T03:50:20+00:00</t>
+          <t>2026-05-20T00:13:57+00:00</t>
         </is>
       </c>
       <c r="AY230" t="inlineStr">
@@ -37729,7 +37729,7 @@
       </c>
       <c r="AT231" t="inlineStr">
         <is>
-          <t>batch_2e8f5425de7c49e5</t>
+          <t>batch_164c8f2ccaa64eaf</t>
         </is>
       </c>
       <c r="AU231" t="inlineStr">
@@ -37745,7 +37745,7 @@
       <c r="AW231" t="inlineStr"/>
       <c r="AX231" t="inlineStr">
         <is>
-          <t>2026-05-14T03:50:20+00:00</t>
+          <t>2026-05-20T00:13:57+00:00</t>
         </is>
       </c>
       <c r="AY231" t="inlineStr">
@@ -37889,7 +37889,7 @@
       </c>
       <c r="AT232" t="inlineStr">
         <is>
-          <t>batch_2e8f5425de7c49e5</t>
+          <t>batch_164c8f2ccaa64eaf</t>
         </is>
       </c>
       <c r="AU232" t="inlineStr">
@@ -37905,7 +37905,7 @@
       <c r="AW232" t="inlineStr"/>
       <c r="AX232" t="inlineStr">
         <is>
-          <t>2026-05-14T03:50:20+00:00</t>
+          <t>2026-05-20T00:13:57+00:00</t>
         </is>
       </c>
       <c r="AY232" t="inlineStr">
@@ -38049,7 +38049,7 @@
       </c>
       <c r="AT233" t="inlineStr">
         <is>
-          <t>batch_2e8f5425de7c49e5</t>
+          <t>batch_164c8f2ccaa64eaf</t>
         </is>
       </c>
       <c r="AU233" t="inlineStr">
@@ -38065,7 +38065,7 @@
       <c r="AW233" t="inlineStr"/>
       <c r="AX233" t="inlineStr">
         <is>
-          <t>2026-05-14T03:50:20+00:00</t>
+          <t>2026-05-20T00:13:57+00:00</t>
         </is>
       </c>
       <c r="AY233" t="inlineStr">
@@ -38209,7 +38209,7 @@
       </c>
       <c r="AT234" t="inlineStr">
         <is>
-          <t>batch_2e8f5425de7c49e5</t>
+          <t>batch_164c8f2ccaa64eaf</t>
         </is>
       </c>
       <c r="AU234" t="inlineStr">
@@ -38225,7 +38225,7 @@
       <c r="AW234" t="inlineStr"/>
       <c r="AX234" t="inlineStr">
         <is>
-          <t>2026-05-14T03:50:20+00:00</t>
+          <t>2026-05-20T00:13:57+00:00</t>
         </is>
       </c>
       <c r="AY234" t="inlineStr">
@@ -38369,7 +38369,7 @@
       </c>
       <c r="AT235" t="inlineStr">
         <is>
-          <t>batch_2e8f5425de7c49e5</t>
+          <t>batch_164c8f2ccaa64eaf</t>
         </is>
       </c>
       <c r="AU235" t="inlineStr">
@@ -38385,7 +38385,7 @@
       <c r="AW235" t="inlineStr"/>
       <c r="AX235" t="inlineStr">
         <is>
-          <t>2026-05-14T03:50:20+00:00</t>
+          <t>2026-05-20T00:13:57+00:00</t>
         </is>
       </c>
       <c r="AY235" t="inlineStr">
@@ -38529,7 +38529,7 @@
       </c>
       <c r="AT236" t="inlineStr">
         <is>
-          <t>batch_2e8f5425de7c49e5</t>
+          <t>batch_164c8f2ccaa64eaf</t>
         </is>
       </c>
       <c r="AU236" t="inlineStr">
@@ -38545,7 +38545,7 @@
       <c r="AW236" t="inlineStr"/>
       <c r="AX236" t="inlineStr">
         <is>
-          <t>2026-05-14T03:50:20+00:00</t>
+          <t>2026-05-20T00:13:57+00:00</t>
         </is>
       </c>
       <c r="AY236" t="inlineStr">
@@ -38689,7 +38689,7 @@
       </c>
       <c r="AT237" t="inlineStr">
         <is>
-          <t>batch_2e8f5425de7c49e5</t>
+          <t>batch_164c8f2ccaa64eaf</t>
         </is>
       </c>
       <c r="AU237" t="inlineStr">
@@ -38705,7 +38705,7 @@
       <c r="AW237" t="inlineStr"/>
       <c r="AX237" t="inlineStr">
         <is>
-          <t>2026-05-14T03:50:20+00:00</t>
+          <t>2026-05-20T00:13:57+00:00</t>
         </is>
       </c>
       <c r="AY237" t="inlineStr">
@@ -38849,7 +38849,7 @@
       </c>
       <c r="AT238" t="inlineStr">
         <is>
-          <t>batch_2e8f5425de7c49e5</t>
+          <t>batch_164c8f2ccaa64eaf</t>
         </is>
       </c>
       <c r="AU238" t="inlineStr">
@@ -38865,7 +38865,7 @@
       <c r="AW238" t="inlineStr"/>
       <c r="AX238" t="inlineStr">
         <is>
-          <t>2026-05-14T03:50:20+00:00</t>
+          <t>2026-05-20T00:13:57+00:00</t>
         </is>
       </c>
       <c r="AY238" t="inlineStr">
@@ -39009,7 +39009,7 @@
       </c>
       <c r="AT239" t="inlineStr">
         <is>
-          <t>batch_2e8f5425de7c49e5</t>
+          <t>batch_164c8f2ccaa64eaf</t>
         </is>
       </c>
       <c r="AU239" t="inlineStr">
@@ -39025,7 +39025,7 @@
       <c r="AW239" t="inlineStr"/>
       <c r="AX239" t="inlineStr">
         <is>
-          <t>2026-05-14T03:50:20+00:00</t>
+          <t>2026-05-20T00:13:57+00:00</t>
         </is>
       </c>
       <c r="AY239" t="inlineStr">
@@ -39169,7 +39169,7 @@
       </c>
       <c r="AT240" t="inlineStr">
         <is>
-          <t>batch_2e8f5425de7c49e5</t>
+          <t>batch_164c8f2ccaa64eaf</t>
         </is>
       </c>
       <c r="AU240" t="inlineStr">
@@ -39185,7 +39185,7 @@
       <c r="AW240" t="inlineStr"/>
       <c r="AX240" t="inlineStr">
         <is>
-          <t>2026-05-14T03:50:20+00:00</t>
+          <t>2026-05-20T00:13:57+00:00</t>
         </is>
       </c>
       <c r="AY240" t="inlineStr">
@@ -39329,7 +39329,7 @@
       </c>
       <c r="AT241" t="inlineStr">
         <is>
-          <t>batch_2e8f5425de7c49e5</t>
+          <t>batch_164c8f2ccaa64eaf</t>
         </is>
       </c>
       <c r="AU241" t="inlineStr">
@@ -39345,7 +39345,7 @@
       <c r="AW241" t="inlineStr"/>
       <c r="AX241" t="inlineStr">
         <is>
-          <t>2026-05-14T03:50:20+00:00</t>
+          <t>2026-05-20T00:13:57+00:00</t>
         </is>
       </c>
       <c r="AY241" t="inlineStr">
@@ -39489,7 +39489,7 @@
       </c>
       <c r="AT242" t="inlineStr">
         <is>
-          <t>batch_2e8f5425de7c49e5</t>
+          <t>batch_164c8f2ccaa64eaf</t>
         </is>
       </c>
       <c r="AU242" t="inlineStr">
@@ -39505,7 +39505,7 @@
       <c r="AW242" t="inlineStr"/>
       <c r="AX242" t="inlineStr">
         <is>
-          <t>2026-05-14T03:50:20+00:00</t>
+          <t>2026-05-20T00:13:57+00:00</t>
         </is>
       </c>
       <c r="AY242" t="inlineStr">
@@ -39649,7 +39649,7 @@
       </c>
       <c r="AT243" t="inlineStr">
         <is>
-          <t>batch_2e8f5425de7c49e5</t>
+          <t>batch_164c8f2ccaa64eaf</t>
         </is>
       </c>
       <c r="AU243" t="inlineStr">
@@ -39665,7 +39665,7 @@
       <c r="AW243" t="inlineStr"/>
       <c r="AX243" t="inlineStr">
         <is>
-          <t>2026-05-14T03:50:20+00:00</t>
+          <t>2026-05-20T00:13:57+00:00</t>
         </is>
       </c>
       <c r="AY243" t="inlineStr">
@@ -39809,7 +39809,7 @@
       </c>
       <c r="AT244" t="inlineStr">
         <is>
-          <t>batch_2e8f5425de7c49e5</t>
+          <t>batch_164c8f2ccaa64eaf</t>
         </is>
       </c>
       <c r="AU244" t="inlineStr">
@@ -39825,7 +39825,7 @@
       <c r="AW244" t="inlineStr"/>
       <c r="AX244" t="inlineStr">
         <is>
-          <t>2026-05-14T03:50:20+00:00</t>
+          <t>2026-05-20T00:13:57+00:00</t>
         </is>
       </c>
       <c r="AY244" t="inlineStr">
@@ -39969,7 +39969,7 @@
       </c>
       <c r="AT245" t="inlineStr">
         <is>
-          <t>batch_2e8f5425de7c49e5</t>
+          <t>batch_164c8f2ccaa64eaf</t>
         </is>
       </c>
       <c r="AU245" t="inlineStr">
@@ -39985,7 +39985,7 @@
       <c r="AW245" t="inlineStr"/>
       <c r="AX245" t="inlineStr">
         <is>
-          <t>2026-05-14T03:50:20+00:00</t>
+          <t>2026-05-20T00:13:57+00:00</t>
         </is>
       </c>
       <c r="AY245" t="inlineStr">
@@ -40129,7 +40129,7 @@
       </c>
       <c r="AT246" t="inlineStr">
         <is>
-          <t>batch_2e8f5425de7c49e5</t>
+          <t>batch_164c8f2ccaa64eaf</t>
         </is>
       </c>
       <c r="AU246" t="inlineStr">
@@ -40145,7 +40145,7 @@
       <c r="AW246" t="inlineStr"/>
       <c r="AX246" t="inlineStr">
         <is>
-          <t>2026-05-14T03:50:20+00:00</t>
+          <t>2026-05-20T00:13:57+00:00</t>
         </is>
       </c>
       <c r="AY246" t="inlineStr">
@@ -40289,7 +40289,7 @@
       </c>
       <c r="AT247" t="inlineStr">
         <is>
-          <t>batch_2e8f5425de7c49e5</t>
+          <t>batch_164c8f2ccaa64eaf</t>
         </is>
       </c>
       <c r="AU247" t="inlineStr">
@@ -40305,7 +40305,7 @@
       <c r="AW247" t="inlineStr"/>
       <c r="AX247" t="inlineStr">
         <is>
-          <t>2026-05-14T03:50:20+00:00</t>
+          <t>2026-05-20T00:13:57+00:00</t>
         </is>
       </c>
       <c r="AY247" t="inlineStr">
@@ -40449,7 +40449,7 @@
       </c>
       <c r="AT248" t="inlineStr">
         <is>
-          <t>batch_2e8f5425de7c49e5</t>
+          <t>batch_164c8f2ccaa64eaf</t>
         </is>
       </c>
       <c r="AU248" t="inlineStr">
@@ -40465,7 +40465,7 @@
       <c r="AW248" t="inlineStr"/>
       <c r="AX248" t="inlineStr">
         <is>
-          <t>2026-05-14T03:50:20+00:00</t>
+          <t>2026-05-20T00:13:57+00:00</t>
         </is>
       </c>
       <c r="AY248" t="inlineStr">
@@ -40609,7 +40609,7 @@
       </c>
       <c r="AT249" t="inlineStr">
         <is>
-          <t>batch_2e8f5425de7c49e5</t>
+          <t>batch_164c8f2ccaa64eaf</t>
         </is>
       </c>
       <c r="AU249" t="inlineStr">
@@ -40625,7 +40625,7 @@
       <c r="AW249" t="inlineStr"/>
       <c r="AX249" t="inlineStr">
         <is>
-          <t>2026-05-14T03:50:20+00:00</t>
+          <t>2026-05-20T00:13:57+00:00</t>
         </is>
       </c>
       <c r="AY249" t="inlineStr">
@@ -40769,7 +40769,7 @@
       </c>
       <c r="AT250" t="inlineStr">
         <is>
-          <t>batch_2e8f5425de7c49e5</t>
+          <t>batch_164c8f2ccaa64eaf</t>
         </is>
       </c>
       <c r="AU250" t="inlineStr">
@@ -40785,7 +40785,7 @@
       <c r="AW250" t="inlineStr"/>
       <c r="AX250" t="inlineStr">
         <is>
-          <t>2026-05-14T03:50:20+00:00</t>
+          <t>2026-05-20T00:13:57+00:00</t>
         </is>
       </c>
       <c r="AY250" t="inlineStr">
@@ -40929,7 +40929,7 @@
       </c>
       <c r="AT251" t="inlineStr">
         <is>
-          <t>batch_2e8f5425de7c49e5</t>
+          <t>batch_164c8f2ccaa64eaf</t>
         </is>
       </c>
       <c r="AU251" t="inlineStr">
@@ -40945,7 +40945,7 @@
       <c r="AW251" t="inlineStr"/>
       <c r="AX251" t="inlineStr">
         <is>
-          <t>2026-05-14T03:50:20+00:00</t>
+          <t>2026-05-20T00:13:57+00:00</t>
         </is>
       </c>
       <c r="AY251" t="inlineStr">
@@ -41089,7 +41089,7 @@
       </c>
       <c r="AT252" t="inlineStr">
         <is>
-          <t>batch_2e8f5425de7c49e5</t>
+          <t>batch_164c8f2ccaa64eaf</t>
         </is>
       </c>
       <c r="AU252" t="inlineStr">
@@ -41105,7 +41105,7 @@
       <c r="AW252" t="inlineStr"/>
       <c r="AX252" t="inlineStr">
         <is>
-          <t>2026-05-14T03:50:20+00:00</t>
+          <t>2026-05-20T00:13:57+00:00</t>
         </is>
       </c>
       <c r="AY252" t="inlineStr">
@@ -41249,7 +41249,7 @@
       </c>
       <c r="AT253" t="inlineStr">
         <is>
-          <t>batch_2e8f5425de7c49e5</t>
+          <t>batch_164c8f2ccaa64eaf</t>
         </is>
       </c>
       <c r="AU253" t="inlineStr">
@@ -41265,7 +41265,7 @@
       <c r="AW253" t="inlineStr"/>
       <c r="AX253" t="inlineStr">
         <is>
-          <t>2026-05-14T03:50:20+00:00</t>
+          <t>2026-05-20T00:13:57+00:00</t>
         </is>
       </c>
       <c r="AY253" t="inlineStr">
@@ -41409,7 +41409,7 @@
       </c>
       <c r="AT254" t="inlineStr">
         <is>
-          <t>batch_2e8f5425de7c49e5</t>
+          <t>batch_164c8f2ccaa64eaf</t>
         </is>
       </c>
       <c r="AU254" t="inlineStr">
@@ -41425,7 +41425,7 @@
       <c r="AW254" t="inlineStr"/>
       <c r="AX254" t="inlineStr">
         <is>
-          <t>2026-05-14T03:50:20+00:00</t>
+          <t>2026-05-20T00:13:57+00:00</t>
         </is>
       </c>
       <c r="AY254" t="inlineStr">
@@ -41569,7 +41569,7 @@
       </c>
       <c r="AT255" t="inlineStr">
         <is>
-          <t>batch_2e8f5425de7c49e5</t>
+          <t>batch_164c8f2ccaa64eaf</t>
         </is>
       </c>
       <c r="AU255" t="inlineStr">
@@ -41585,7 +41585,7 @@
       <c r="AW255" t="inlineStr"/>
       <c r="AX255" t="inlineStr">
         <is>
-          <t>2026-05-14T03:50:20+00:00</t>
+          <t>2026-05-20T00:13:57+00:00</t>
         </is>
       </c>
       <c r="AY255" t="inlineStr">
@@ -41729,7 +41729,7 @@
       </c>
       <c r="AT256" t="inlineStr">
         <is>
-          <t>batch_2e8f5425de7c49e5</t>
+          <t>batch_164c8f2ccaa64eaf</t>
         </is>
       </c>
       <c r="AU256" t="inlineStr">
@@ -41745,7 +41745,7 @@
       <c r="AW256" t="inlineStr"/>
       <c r="AX256" t="inlineStr">
         <is>
-          <t>2026-05-14T03:50:20+00:00</t>
+          <t>2026-05-20T00:13:57+00:00</t>
         </is>
       </c>
       <c r="AY256" t="inlineStr">
@@ -41889,7 +41889,7 @@
       </c>
       <c r="AT257" t="inlineStr">
         <is>
-          <t>batch_2e8f5425de7c49e5</t>
+          <t>batch_164c8f2ccaa64eaf</t>
         </is>
       </c>
       <c r="AU257" t="inlineStr">
@@ -41905,7 +41905,7 @@
       <c r="AW257" t="inlineStr"/>
       <c r="AX257" t="inlineStr">
         <is>
-          <t>2026-05-14T03:50:20+00:00</t>
+          <t>2026-05-20T00:13:57+00:00</t>
         </is>
       </c>
       <c r="AY257" t="inlineStr">
@@ -42049,7 +42049,7 @@
       </c>
       <c r="AT258" t="inlineStr">
         <is>
-          <t>batch_2e8f5425de7c49e5</t>
+          <t>batch_164c8f2ccaa64eaf</t>
         </is>
       </c>
       <c r="AU258" t="inlineStr">
@@ -42065,7 +42065,7 @@
       <c r="AW258" t="inlineStr"/>
       <c r="AX258" t="inlineStr">
         <is>
-          <t>2026-05-14T03:50:20+00:00</t>
+          <t>2026-05-20T00:13:57+00:00</t>
         </is>
       </c>
       <c r="AY258" t="inlineStr">
@@ -42209,7 +42209,7 @@
       </c>
       <c r="AT259" t="inlineStr">
         <is>
-          <t>batch_2e8f5425de7c49e5</t>
+          <t>batch_164c8f2ccaa64eaf</t>
         </is>
       </c>
       <c r="AU259" t="inlineStr">
@@ -42225,7 +42225,7 @@
       <c r="AW259" t="inlineStr"/>
       <c r="AX259" t="inlineStr">
         <is>
-          <t>2026-05-14T03:50:20+00:00</t>
+          <t>2026-05-20T00:13:57+00:00</t>
         </is>
       </c>
       <c r="AY259" t="inlineStr">
@@ -42369,7 +42369,7 @@
       </c>
       <c r="AT260" t="inlineStr">
         <is>
-          <t>batch_2e8f5425de7c49e5</t>
+          <t>batch_164c8f2ccaa64eaf</t>
         </is>
       </c>
       <c r="AU260" t="inlineStr">
@@ -42385,7 +42385,7 @@
       <c r="AW260" t="inlineStr"/>
       <c r="AX260" t="inlineStr">
         <is>
-          <t>2026-05-14T03:50:20+00:00</t>
+          <t>2026-05-20T00:13:57+00:00</t>
         </is>
       </c>
       <c r="AY260" t="inlineStr">
@@ -42529,7 +42529,7 @@
       </c>
       <c r="AT261" t="inlineStr">
         <is>
-          <t>batch_2e8f5425de7c49e5</t>
+          <t>batch_164c8f2ccaa64eaf</t>
         </is>
       </c>
       <c r="AU261" t="inlineStr">
@@ -42545,7 +42545,7 @@
       <c r="AW261" t="inlineStr"/>
       <c r="AX261" t="inlineStr">
         <is>
-          <t>2026-05-14T03:50:20+00:00</t>
+          <t>2026-05-20T00:13:57+00:00</t>
         </is>
       </c>
       <c r="AY261" t="inlineStr">
@@ -42689,7 +42689,7 @@
       </c>
       <c r="AT262" t="inlineStr">
         <is>
-          <t>batch_2e8f5425de7c49e5</t>
+          <t>batch_164c8f2ccaa64eaf</t>
         </is>
       </c>
       <c r="AU262" t="inlineStr">
@@ -42705,7 +42705,7 @@
       <c r="AW262" t="inlineStr"/>
       <c r="AX262" t="inlineStr">
         <is>
-          <t>2026-05-14T03:50:20+00:00</t>
+          <t>2026-05-20T00:13:57+00:00</t>
         </is>
       </c>
       <c r="AY262" t="inlineStr">
@@ -42849,7 +42849,7 @@
       </c>
       <c r="AT263" t="inlineStr">
         <is>
-          <t>batch_2e8f5425de7c49e5</t>
+          <t>batch_164c8f2ccaa64eaf</t>
         </is>
       </c>
       <c r="AU263" t="inlineStr">
@@ -42865,7 +42865,7 @@
       <c r="AW263" t="inlineStr"/>
       <c r="AX263" t="inlineStr">
         <is>
-          <t>2026-05-14T03:50:20+00:00</t>
+          <t>2026-05-20T00:13:57+00:00</t>
         </is>
       </c>
       <c r="AY263" t="inlineStr">
@@ -43009,7 +43009,7 @@
       </c>
       <c r="AT264" t="inlineStr">
         <is>
-          <t>batch_2e8f5425de7c49e5</t>
+          <t>batch_164c8f2ccaa64eaf</t>
         </is>
       </c>
       <c r="AU264" t="inlineStr">
@@ -43025,7 +43025,7 @@
       <c r="AW264" t="inlineStr"/>
       <c r="AX264" t="inlineStr">
         <is>
-          <t>2026-05-14T03:50:20+00:00</t>
+          <t>2026-05-20T00:13:57+00:00</t>
         </is>
       </c>
       <c r="AY264" t="inlineStr">
@@ -43169,7 +43169,7 @@
       </c>
       <c r="AT265" t="inlineStr">
         <is>
-          <t>batch_2e8f5425de7c49e5</t>
+          <t>batch_164c8f2ccaa64eaf</t>
         </is>
       </c>
       <c r="AU265" t="inlineStr">
@@ -43185,7 +43185,7 @@
       <c r="AW265" t="inlineStr"/>
       <c r="AX265" t="inlineStr">
         <is>
-          <t>2026-05-14T03:50:20+00:00</t>
+          <t>2026-05-20T00:13:57+00:00</t>
         </is>
       </c>
       <c r="AY265" t="inlineStr">
@@ -43329,7 +43329,7 @@
       </c>
       <c r="AT266" t="inlineStr">
         <is>
-          <t>batch_2e8f5425de7c49e5</t>
+          <t>batch_164c8f2ccaa64eaf</t>
         </is>
       </c>
       <c r="AU266" t="inlineStr">
@@ -43345,7 +43345,7 @@
       <c r="AW266" t="inlineStr"/>
       <c r="AX266" t="inlineStr">
         <is>
-          <t>2026-05-14T03:50:20+00:00</t>
+          <t>2026-05-20T00:13:57+00:00</t>
         </is>
       </c>
       <c r="AY266" t="inlineStr">
@@ -43489,7 +43489,7 @@
       </c>
       <c r="AT267" t="inlineStr">
         <is>
-          <t>batch_2e8f5425de7c49e5</t>
+          <t>batch_164c8f2ccaa64eaf</t>
         </is>
       </c>
       <c r="AU267" t="inlineStr">
@@ -43505,7 +43505,7 @@
       <c r="AW267" t="inlineStr"/>
       <c r="AX267" t="inlineStr">
         <is>
-          <t>2026-05-14T03:50:20+00:00</t>
+          <t>2026-05-20T00:13:57+00:00</t>
         </is>
       </c>
       <c r="AY267" t="inlineStr">
@@ -43649,7 +43649,7 @@
       </c>
       <c r="AT268" t="inlineStr">
         <is>
-          <t>batch_2e8f5425de7c49e5</t>
+          <t>batch_164c8f2ccaa64eaf</t>
         </is>
       </c>
       <c r="AU268" t="inlineStr">
@@ -43665,7 +43665,7 @@
       <c r="AW268" t="inlineStr"/>
       <c r="AX268" t="inlineStr">
         <is>
-          <t>2026-05-14T03:50:20+00:00</t>
+          <t>2026-05-20T00:13:57+00:00</t>
         </is>
       </c>
       <c r="AY268" t="inlineStr">
@@ -43809,7 +43809,7 @@
       </c>
       <c r="AT269" t="inlineStr">
         <is>
-          <t>batch_2e8f5425de7c49e5</t>
+          <t>batch_164c8f2ccaa64eaf</t>
         </is>
       </c>
       <c r="AU269" t="inlineStr">
@@ -43825,7 +43825,7 @@
       <c r="AW269" t="inlineStr"/>
       <c r="AX269" t="inlineStr">
         <is>
-          <t>2026-05-14T03:50:20+00:00</t>
+          <t>2026-05-20T00:13:57+00:00</t>
         </is>
       </c>
       <c r="AY269" t="inlineStr">
@@ -43969,7 +43969,7 @@
       </c>
       <c r="AT270" t="inlineStr">
         <is>
-          <t>batch_2e8f5425de7c49e5</t>
+          <t>batch_164c8f2ccaa64eaf</t>
         </is>
       </c>
       <c r="AU270" t="inlineStr">
@@ -43985,7 +43985,7 @@
       <c r="AW270" t="inlineStr"/>
       <c r="AX270" t="inlineStr">
         <is>
-          <t>2026-05-14T03:50:20+00:00</t>
+          <t>2026-05-20T00:13:57+00:00</t>
         </is>
       </c>
       <c r="AY270" t="inlineStr">
@@ -44129,7 +44129,7 @@
       </c>
       <c r="AT271" t="inlineStr">
         <is>
-          <t>batch_2e8f5425de7c49e5</t>
+          <t>batch_164c8f2ccaa64eaf</t>
         </is>
       </c>
       <c r="AU271" t="inlineStr">
@@ -44145,7 +44145,7 @@
       <c r="AW271" t="inlineStr"/>
       <c r="AX271" t="inlineStr">
         <is>
-          <t>2026-05-14T03:50:20+00:00</t>
+          <t>2026-05-20T00:13:57+00:00</t>
         </is>
       </c>
       <c r="AY271" t="inlineStr">
@@ -44289,7 +44289,7 @@
       </c>
       <c r="AT272" t="inlineStr">
         <is>
-          <t>batch_2e8f5425de7c49e5</t>
+          <t>batch_164c8f2ccaa64eaf</t>
         </is>
       </c>
       <c r="AU272" t="inlineStr">
@@ -44305,7 +44305,7 @@
       <c r="AW272" t="inlineStr"/>
       <c r="AX272" t="inlineStr">
         <is>
-          <t>2026-05-14T03:50:20+00:00</t>
+          <t>2026-05-20T00:13:57+00:00</t>
         </is>
       </c>
       <c r="AY272" t="inlineStr">
@@ -44449,7 +44449,7 @@
       </c>
       <c r="AT273" t="inlineStr">
         <is>
-          <t>batch_2e8f5425de7c49e5</t>
+          <t>batch_164c8f2ccaa64eaf</t>
         </is>
       </c>
       <c r="AU273" t="inlineStr">
@@ -44465,7 +44465,7 @@
       <c r="AW273" t="inlineStr"/>
       <c r="AX273" t="inlineStr">
         <is>
-          <t>2026-05-14T03:50:20+00:00</t>
+          <t>2026-05-20T00:13:57+00:00</t>
         </is>
       </c>
       <c r="AY273" t="inlineStr">
@@ -44609,7 +44609,7 @@
       </c>
       <c r="AT274" t="inlineStr">
         <is>
-          <t>batch_2e8f5425de7c49e5</t>
+          <t>batch_164c8f2ccaa64eaf</t>
         </is>
       </c>
       <c r="AU274" t="inlineStr">
@@ -44625,7 +44625,7 @@
       <c r="AW274" t="inlineStr"/>
       <c r="AX274" t="inlineStr">
         <is>
-          <t>2026-05-14T03:50:20+00:00</t>
+          <t>2026-05-20T00:13:57+00:00</t>
         </is>
       </c>
       <c r="AY274" t="inlineStr">
@@ -44769,7 +44769,7 @@
       </c>
       <c r="AT275" t="inlineStr">
         <is>
-          <t>batch_2e8f5425de7c49e5</t>
+          <t>batch_164c8f2ccaa64eaf</t>
         </is>
       </c>
       <c r="AU275" t="inlineStr">
@@ -44785,7 +44785,7 @@
       <c r="AW275" t="inlineStr"/>
       <c r="AX275" t="inlineStr">
         <is>
-          <t>2026-05-14T03:50:20+00:00</t>
+          <t>2026-05-20T00:13:57+00:00</t>
         </is>
       </c>
       <c r="AY275" t="inlineStr">
@@ -44929,7 +44929,7 @@
       </c>
       <c r="AT276" t="inlineStr">
         <is>
-          <t>batch_2e8f5425de7c49e5</t>
+          <t>batch_164c8f2ccaa64eaf</t>
         </is>
       </c>
       <c r="AU276" t="inlineStr">
@@ -44945,7 +44945,7 @@
       <c r="AW276" t="inlineStr"/>
       <c r="AX276" t="inlineStr">
         <is>
-          <t>2026-05-14T03:50:20+00:00</t>
+          <t>2026-05-20T00:13:57+00:00</t>
         </is>
       </c>
       <c r="AY276" t="inlineStr">
@@ -45089,7 +45089,7 @@
       </c>
       <c r="AT277" t="inlineStr">
         <is>
-          <t>batch_2e8f5425de7c49e5</t>
+          <t>batch_164c8f2ccaa64eaf</t>
         </is>
       </c>
       <c r="AU277" t="inlineStr">
@@ -45105,7 +45105,7 @@
       <c r="AW277" t="inlineStr"/>
       <c r="AX277" t="inlineStr">
         <is>
-          <t>2026-05-14T03:50:20+00:00</t>
+          <t>2026-05-20T00:13:57+00:00</t>
         </is>
       </c>
       <c r="AY277" t="inlineStr">
@@ -45249,7 +45249,7 @@
       </c>
       <c r="AT278" t="inlineStr">
         <is>
-          <t>batch_2e8f5425de7c49e5</t>
+          <t>batch_164c8f2ccaa64eaf</t>
         </is>
       </c>
       <c r="AU278" t="inlineStr">
@@ -45265,7 +45265,7 @@
       <c r="AW278" t="inlineStr"/>
       <c r="AX278" t="inlineStr">
         <is>
-          <t>2026-05-14T03:50:20+00:00</t>
+          <t>2026-05-20T00:13:57+00:00</t>
         </is>
       </c>
       <c r="AY278" t="inlineStr">
@@ -45409,7 +45409,7 @@
       </c>
       <c r="AT279" t="inlineStr">
         <is>
-          <t>batch_2e8f5425de7c49e5</t>
+          <t>batch_164c8f2ccaa64eaf</t>
         </is>
       </c>
       <c r="AU279" t="inlineStr">
@@ -45425,7 +45425,7 @@
       <c r="AW279" t="inlineStr"/>
       <c r="AX279" t="inlineStr">
         <is>
-          <t>2026-05-14T03:50:20+00:00</t>
+          <t>2026-05-20T00:13:57+00:00</t>
         </is>
       </c>
       <c r="AY279" t="inlineStr">
@@ -45569,7 +45569,7 @@
       </c>
       <c r="AT280" t="inlineStr">
         <is>
-          <t>batch_2e8f5425de7c49e5</t>
+          <t>batch_164c8f2ccaa64eaf</t>
         </is>
       </c>
       <c r="AU280" t="inlineStr">
@@ -45585,7 +45585,7 @@
       <c r="AW280" t="inlineStr"/>
       <c r="AX280" t="inlineStr">
         <is>
-          <t>2026-05-14T03:50:20+00:00</t>
+          <t>2026-05-20T00:13:57+00:00</t>
         </is>
       </c>
       <c r="AY280" t="inlineStr">
@@ -45729,7 +45729,7 @@
       </c>
       <c r="AT281" t="inlineStr">
         <is>
-          <t>batch_2e8f5425de7c49e5</t>
+          <t>batch_164c8f2ccaa64eaf</t>
         </is>
       </c>
       <c r="AU281" t="inlineStr">
@@ -45745,7 +45745,7 @@
       <c r="AW281" t="inlineStr"/>
       <c r="AX281" t="inlineStr">
         <is>
-          <t>2026-05-14T03:50:20+00:00</t>
+          <t>2026-05-20T00:13:57+00:00</t>
         </is>
       </c>
       <c r="AY281" t="inlineStr">
@@ -45889,7 +45889,7 @@
       </c>
       <c r="AT282" t="inlineStr">
         <is>
-          <t>batch_2e8f5425de7c49e5</t>
+          <t>batch_164c8f2ccaa64eaf</t>
         </is>
       </c>
       <c r="AU282" t="inlineStr">
@@ -45905,7 +45905,7 @@
       <c r="AW282" t="inlineStr"/>
       <c r="AX282" t="inlineStr">
         <is>
-          <t>2026-05-14T03:50:20+00:00</t>
+          <t>2026-05-20T00:13:57+00:00</t>
         </is>
       </c>
       <c r="AY282" t="inlineStr">
@@ -46049,7 +46049,7 @@
       </c>
       <c r="AT283" t="inlineStr">
         <is>
-          <t>batch_2e8f5425de7c49e5</t>
+          <t>batch_164c8f2ccaa64eaf</t>
         </is>
       </c>
       <c r="AU283" t="inlineStr">
@@ -46065,7 +46065,7 @@
       <c r="AW283" t="inlineStr"/>
       <c r="AX283" t="inlineStr">
         <is>
-          <t>2026-05-14T03:50:20+00:00</t>
+          <t>2026-05-20T00:13:57+00:00</t>
         </is>
       </c>
       <c r="AY283" t="inlineStr">
@@ -46209,7 +46209,7 @@
       </c>
       <c r="AT284" t="inlineStr">
         <is>
-          <t>batch_2e8f5425de7c49e5</t>
+          <t>batch_164c8f2ccaa64eaf</t>
         </is>
       </c>
       <c r="AU284" t="inlineStr">
@@ -46225,7 +46225,7 @@
       <c r="AW284" t="inlineStr"/>
       <c r="AX284" t="inlineStr">
         <is>
-          <t>2026-05-14T03:50:20+00:00</t>
+          <t>2026-05-20T00:13:57+00:00</t>
         </is>
       </c>
       <c r="AY284" t="inlineStr">
@@ -46369,7 +46369,7 @@
       </c>
       <c r="AT285" t="inlineStr">
         <is>
-          <t>batch_2e8f5425de7c49e5</t>
+          <t>batch_164c8f2ccaa64eaf</t>
         </is>
       </c>
       <c r="AU285" t="inlineStr">
@@ -46385,7 +46385,7 @@
       <c r="AW285" t="inlineStr"/>
       <c r="AX285" t="inlineStr">
         <is>
-          <t>2026-05-14T03:50:20+00:00</t>
+          <t>2026-05-20T00:13:57+00:00</t>
         </is>
       </c>
       <c r="AY285" t="inlineStr">
@@ -46529,7 +46529,7 @@
       </c>
       <c r="AT286" t="inlineStr">
         <is>
-          <t>batch_2e8f5425de7c49e5</t>
+          <t>batch_164c8f2ccaa64eaf</t>
         </is>
       </c>
       <c r="AU286" t="inlineStr">
@@ -46545,7 +46545,7 @@
       <c r="AW286" t="inlineStr"/>
       <c r="AX286" t="inlineStr">
         <is>
-          <t>2026-05-14T03:50:20+00:00</t>
+          <t>2026-05-20T00:13:57+00:00</t>
         </is>
       </c>
       <c r="AY286" t="inlineStr">
@@ -46689,7 +46689,7 @@
       </c>
       <c r="AT287" t="inlineStr">
         <is>
-          <t>batch_2e8f5425de7c49e5</t>
+          <t>batch_164c8f2ccaa64eaf</t>
         </is>
       </c>
       <c r="AU287" t="inlineStr">
@@ -46705,7 +46705,7 @@
       <c r="AW287" t="inlineStr"/>
       <c r="AX287" t="inlineStr">
         <is>
-          <t>2026-05-14T03:50:20+00:00</t>
+          <t>2026-05-20T00:13:57+00:00</t>
         </is>
       </c>
       <c r="AY287" t="inlineStr">
@@ -46849,7 +46849,7 @@
       </c>
       <c r="AT288" t="inlineStr">
         <is>
-          <t>batch_2e8f5425de7c49e5</t>
+          <t>batch_164c8f2ccaa64eaf</t>
         </is>
       </c>
       <c r="AU288" t="inlineStr">
@@ -46865,7 +46865,7 @@
       <c r="AW288" t="inlineStr"/>
       <c r="AX288" t="inlineStr">
         <is>
-          <t>2026-05-14T03:50:20+00:00</t>
+          <t>2026-05-20T00:13:57+00:00</t>
         </is>
       </c>
       <c r="AY288" t="inlineStr">
@@ -47009,7 +47009,7 @@
       </c>
       <c r="AT289" t="inlineStr">
         <is>
-          <t>batch_2e8f5425de7c49e5</t>
+          <t>batch_164c8f2ccaa64eaf</t>
         </is>
       </c>
       <c r="AU289" t="inlineStr">
@@ -47025,7 +47025,7 @@
       <c r="AW289" t="inlineStr"/>
       <c r="AX289" t="inlineStr">
         <is>
-          <t>2026-05-14T03:50:20+00:00</t>
+          <t>2026-05-20T00:13:57+00:00</t>
         </is>
       </c>
       <c r="AY289" t="inlineStr">
@@ -47169,7 +47169,7 @@
       </c>
       <c r="AT290" t="inlineStr">
         <is>
-          <t>batch_2e8f5425de7c49e5</t>
+          <t>batch_164c8f2ccaa64eaf</t>
         </is>
       </c>
       <c r="AU290" t="inlineStr">
@@ -47185,7 +47185,7 @@
       <c r="AW290" t="inlineStr"/>
       <c r="AX290" t="inlineStr">
         <is>
-          <t>2026-05-14T03:50:20+00:00</t>
+          <t>2026-05-20T00:13:57+00:00</t>
         </is>
       </c>
       <c r="AY290" t="inlineStr">
@@ -47329,7 +47329,7 @@
       </c>
       <c r="AT291" t="inlineStr">
         <is>
-          <t>batch_2e8f5425de7c49e5</t>
+          <t>batch_164c8f2ccaa64eaf</t>
         </is>
       </c>
       <c r="AU291" t="inlineStr">
@@ -47345,7 +47345,7 @@
       <c r="AW291" t="inlineStr"/>
       <c r="AX291" t="inlineStr">
         <is>
-          <t>2026-05-14T03:50:20+00:00</t>
+          <t>2026-05-20T00:13:57+00:00</t>
         </is>
       </c>
       <c r="AY291" t="inlineStr">
@@ -47489,7 +47489,7 @@
       </c>
       <c r="AT292" t="inlineStr">
         <is>
-          <t>batch_2e8f5425de7c49e5</t>
+          <t>batch_164c8f2ccaa64eaf</t>
         </is>
       </c>
       <c r="AU292" t="inlineStr">
@@ -47505,7 +47505,7 @@
       <c r="AW292" t="inlineStr"/>
       <c r="AX292" t="inlineStr">
         <is>
-          <t>2026-05-14T03:50:20+00:00</t>
+          <t>2026-05-20T00:13:57+00:00</t>
         </is>
       </c>
       <c r="AY292" t="inlineStr">
@@ -47649,7 +47649,7 @@
       </c>
       <c r="AT293" t="inlineStr">
         <is>
-          <t>batch_2e8f5425de7c49e5</t>
+          <t>batch_164c8f2ccaa64eaf</t>
         </is>
       </c>
       <c r="AU293" t="inlineStr">
@@ -47665,7 +47665,7 @@
       <c r="AW293" t="inlineStr"/>
       <c r="AX293" t="inlineStr">
         <is>
-          <t>2026-05-14T03:50:20+00:00</t>
+          <t>2026-05-20T00:13:57+00:00</t>
         </is>
       </c>
       <c r="AY293" t="inlineStr">
@@ -47809,7 +47809,7 @@
       </c>
       <c r="AT294" t="inlineStr">
         <is>
-          <t>batch_2e8f5425de7c49e5</t>
+          <t>batch_164c8f2ccaa64eaf</t>
         </is>
       </c>
       <c r="AU294" t="inlineStr">
@@ -47825,7 +47825,7 @@
       <c r="AW294" t="inlineStr"/>
       <c r="AX294" t="inlineStr">
         <is>
-          <t>2026-05-14T03:50:20+00:00</t>
+          <t>2026-05-20T00:13:57+00:00</t>
         </is>
       </c>
       <c r="AY294" t="inlineStr">
@@ -47969,7 +47969,7 @@
       </c>
       <c r="AT295" t="inlineStr">
         <is>
-          <t>batch_2e8f5425de7c49e5</t>
+          <t>batch_164c8f2ccaa64eaf</t>
         </is>
       </c>
       <c r="AU295" t="inlineStr">
@@ -47985,7 +47985,7 @@
       <c r="AW295" t="inlineStr"/>
       <c r="AX295" t="inlineStr">
         <is>
-          <t>2026-05-14T03:50:20+00:00</t>
+          <t>2026-05-20T00:13:57+00:00</t>
         </is>
       </c>
       <c r="AY295" t="inlineStr">
@@ -48129,7 +48129,7 @@
       </c>
       <c r="AT296" t="inlineStr">
         <is>
-          <t>batch_2e8f5425de7c49e5</t>
+          <t>batch_164c8f2ccaa64eaf</t>
         </is>
       </c>
       <c r="AU296" t="inlineStr">
@@ -48145,7 +48145,7 @@
       <c r="AW296" t="inlineStr"/>
       <c r="AX296" t="inlineStr">
         <is>
-          <t>2026-05-14T03:50:20+00:00</t>
+          <t>2026-05-20T00:13:57+00:00</t>
         </is>
       </c>
       <c r="AY296" t="inlineStr">
@@ -48289,7 +48289,7 @@
       </c>
       <c r="AT297" t="inlineStr">
         <is>
-          <t>batch_2e8f5425de7c49e5</t>
+          <t>batch_164c8f2ccaa64eaf</t>
         </is>
       </c>
       <c r="AU297" t="inlineStr">
@@ -48305,7 +48305,7 @@
       <c r="AW297" t="inlineStr"/>
       <c r="AX297" t="inlineStr">
         <is>
-          <t>2026-05-14T03:50:20+00:00</t>
+          <t>2026-05-20T00:13:57+00:00</t>
         </is>
       </c>
       <c r="AY297" t="inlineStr">
@@ -48449,7 +48449,7 @@
       </c>
       <c r="AT298" t="inlineStr">
         <is>
-          <t>batch_2e8f5425de7c49e5</t>
+          <t>batch_164c8f2ccaa64eaf</t>
         </is>
       </c>
       <c r="AU298" t="inlineStr">
@@ -48465,7 +48465,7 @@
       <c r="AW298" t="inlineStr"/>
       <c r="AX298" t="inlineStr">
         <is>
-          <t>2026-05-14T03:50:20+00:00</t>
+          <t>2026-05-20T00:13:57+00:00</t>
         </is>
       </c>
       <c r="AY298" t="inlineStr">
@@ -48609,7 +48609,7 @@
       </c>
       <c r="AT299" t="inlineStr">
         <is>
-          <t>batch_2e8f5425de7c49e5</t>
+          <t>batch_164c8f2ccaa64eaf</t>
         </is>
       </c>
       <c r="AU299" t="inlineStr">
@@ -48625,7 +48625,7 @@
       <c r="AW299" t="inlineStr"/>
       <c r="AX299" t="inlineStr">
         <is>
-          <t>2026-05-14T03:50:20+00:00</t>
+          <t>2026-05-20T00:13:57+00:00</t>
         </is>
       </c>
       <c r="AY299" t="inlineStr">
@@ -48769,7 +48769,7 @@
       </c>
       <c r="AT300" t="inlineStr">
         <is>
-          <t>batch_2e8f5425de7c49e5</t>
+          <t>batch_164c8f2ccaa64eaf</t>
         </is>
       </c>
       <c r="AU300" t="inlineStr">
@@ -48785,7 +48785,7 @@
       <c r="AW300" t="inlineStr"/>
       <c r="AX300" t="inlineStr">
         <is>
-          <t>2026-05-14T03:50:20+00:00</t>
+          <t>2026-05-20T00:13:57+00:00</t>
         </is>
       </c>
       <c r="AY300" t="inlineStr">
@@ -48929,7 +48929,7 @@
       </c>
       <c r="AT301" t="inlineStr">
         <is>
-          <t>batch_2e8f5425de7c49e5</t>
+          <t>batch_164c8f2ccaa64eaf</t>
         </is>
       </c>
       <c r="AU301" t="inlineStr">
@@ -48945,7 +48945,7 @@
       <c r="AW301" t="inlineStr"/>
       <c r="AX301" t="inlineStr">
         <is>
-          <t>2026-05-14T03:50:20+00:00</t>
+          <t>2026-05-20T00:13:57+00:00</t>
         </is>
       </c>
       <c r="AY301" t="inlineStr">
@@ -49089,7 +49089,7 @@
       </c>
       <c r="AT302" t="inlineStr">
         <is>
-          <t>batch_2e8f5425de7c49e5</t>
+          <t>batch_164c8f2ccaa64eaf</t>
         </is>
       </c>
       <c r="AU302" t="inlineStr">
@@ -49105,7 +49105,7 @@
       <c r="AW302" t="inlineStr"/>
       <c r="AX302" t="inlineStr">
         <is>
-          <t>2026-05-14T03:50:20+00:00</t>
+          <t>2026-05-20T00:13:57+00:00</t>
         </is>
       </c>
       <c r="AY302" t="inlineStr">
@@ -49249,7 +49249,7 @@
       </c>
       <c r="AT303" t="inlineStr">
         <is>
-          <t>batch_2e8f5425de7c49e5</t>
+          <t>batch_164c8f2ccaa64eaf</t>
         </is>
       </c>
       <c r="AU303" t="inlineStr">
@@ -49265,7 +49265,7 @@
       <c r="AW303" t="inlineStr"/>
       <c r="AX303" t="inlineStr">
         <is>
-          <t>2026-05-14T03:50:20+00:00</t>
+          <t>2026-05-20T00:13:57+00:00</t>
         </is>
       </c>
       <c r="AY303" t="inlineStr">
@@ -49409,7 +49409,7 @@
       </c>
       <c r="AT304" t="inlineStr">
         <is>
-          <t>batch_2e8f5425de7c49e5</t>
+          <t>batch_164c8f2ccaa64eaf</t>
         </is>
       </c>
       <c r="AU304" t="inlineStr">
@@ -49425,7 +49425,7 @@
       <c r="AW304" t="inlineStr"/>
       <c r="AX304" t="inlineStr">
         <is>
-          <t>2026-05-14T03:50:20+00:00</t>
+          <t>2026-05-20T00:13:57+00:00</t>
         </is>
       </c>
       <c r="AY304" t="inlineStr">
@@ -49569,7 +49569,7 @@
       </c>
       <c r="AT305" t="inlineStr">
         <is>
-          <t>batch_2e8f5425de7c49e5</t>
+          <t>batch_164c8f2ccaa64eaf</t>
         </is>
       </c>
       <c r="AU305" t="inlineStr">
@@ -49585,7 +49585,7 @@
       <c r="AW305" t="inlineStr"/>
       <c r="AX305" t="inlineStr">
         <is>
-          <t>2026-05-14T03:50:20+00:00</t>
+          <t>2026-05-20T00:13:57+00:00</t>
         </is>
       </c>
       <c r="AY305" t="inlineStr">
@@ -49729,7 +49729,7 @@
       </c>
       <c r="AT306" t="inlineStr">
         <is>
-          <t>batch_2e8f5425de7c49e5</t>
+          <t>batch_164c8f2ccaa64eaf</t>
         </is>
       </c>
       <c r="AU306" t="inlineStr">
@@ -49745,7 +49745,7 @@
       <c r="AW306" t="inlineStr"/>
       <c r="AX306" t="inlineStr">
         <is>
-          <t>2026-05-14T03:50:20+00:00</t>
+          <t>2026-05-20T00:13:57+00:00</t>
         </is>
       </c>
       <c r="AY306" t="inlineStr">
@@ -49889,7 +49889,7 @@
       </c>
       <c r="AT307" t="inlineStr">
         <is>
-          <t>batch_2e8f5425de7c49e5</t>
+          <t>batch_164c8f2ccaa64eaf</t>
         </is>
       </c>
       <c r="AU307" t="inlineStr">
@@ -49905,7 +49905,7 @@
       <c r="AW307" t="inlineStr"/>
       <c r="AX307" t="inlineStr">
         <is>
-          <t>2026-05-14T03:50:20+00:00</t>
+          <t>2026-05-20T00:13:57+00:00</t>
         </is>
       </c>
       <c r="AY307" t="inlineStr">
@@ -50049,7 +50049,7 @@
       </c>
       <c r="AT308" t="inlineStr">
         <is>
-          <t>batch_2e8f5425de7c49e5</t>
+          <t>batch_164c8f2ccaa64eaf</t>
         </is>
       </c>
       <c r="AU308" t="inlineStr">
@@ -50065,7 +50065,7 @@
       <c r="AW308" t="inlineStr"/>
       <c r="AX308" t="inlineStr">
         <is>
-          <t>2026-05-14T03:50:20+00:00</t>
+          <t>2026-05-20T00:13:57+00:00</t>
         </is>
       </c>
       <c r="AY308" t="inlineStr">
@@ -50209,7 +50209,7 @@
       </c>
       <c r="AT309" t="inlineStr">
         <is>
-          <t>batch_2e8f5425de7c49e5</t>
+          <t>batch_164c8f2ccaa64eaf</t>
         </is>
       </c>
       <c r="AU309" t="inlineStr">
@@ -50225,7 +50225,7 @@
       <c r="AW309" t="inlineStr"/>
       <c r="AX309" t="inlineStr">
         <is>
-          <t>2026-05-14T03:50:20+00:00</t>
+          <t>2026-05-20T00:13:57+00:00</t>
         </is>
       </c>
       <c r="AY309" t="inlineStr">
@@ -50369,7 +50369,7 @@
       </c>
       <c r="AT310" t="inlineStr">
         <is>
-          <t>batch_2e8f5425de7c49e5</t>
+          <t>batch_164c8f2ccaa64eaf</t>
         </is>
       </c>
       <c r="AU310" t="inlineStr">
@@ -50385,7 +50385,7 @@
       <c r="AW310" t="inlineStr"/>
       <c r="AX310" t="inlineStr">
         <is>
-          <t>2026-05-14T03:50:20+00:00</t>
+          <t>2026-05-20T00:13:57+00:00</t>
         </is>
       </c>
       <c r="AY310" t="inlineStr">
@@ -50529,7 +50529,7 @@
       </c>
       <c r="AT311" t="inlineStr">
         <is>
-          <t>batch_2e8f5425de7c49e5</t>
+          <t>batch_164c8f2ccaa64eaf</t>
         </is>
       </c>
       <c r="AU311" t="inlineStr">
@@ -50545,7 +50545,7 @@
       <c r="AW311" t="inlineStr"/>
       <c r="AX311" t="inlineStr">
         <is>
-          <t>2026-05-14T03:50:20+00:00</t>
+          <t>2026-05-20T00:13:57+00:00</t>
         </is>
       </c>
       <c r="AY311" t="inlineStr">
@@ -50689,7 +50689,7 @@
       </c>
       <c r="AT312" t="inlineStr">
         <is>
-          <t>batch_2e8f5425de7c49e5</t>
+          <t>batch_164c8f2ccaa64eaf</t>
         </is>
       </c>
       <c r="AU312" t="inlineStr">
@@ -50705,7 +50705,7 @@
       <c r="AW312" t="inlineStr"/>
       <c r="AX312" t="inlineStr">
         <is>
-          <t>2026-05-14T03:50:20+00:00</t>
+          <t>2026-05-20T00:13:57+00:00</t>
         </is>
       </c>
       <c r="AY312" t="inlineStr">
@@ -50849,7 +50849,7 @@
       </c>
       <c r="AT313" t="inlineStr">
         <is>
-          <t>batch_2e8f5425de7c49e5</t>
+          <t>batch_164c8f2ccaa64eaf</t>
         </is>
       </c>
       <c r="AU313" t="inlineStr">
@@ -50865,7 +50865,7 @@
       <c r="AW313" t="inlineStr"/>
       <c r="AX313" t="inlineStr">
         <is>
-          <t>2026-05-14T03:50:20+00:00</t>
+          <t>2026-05-20T00:13:57+00:00</t>
         </is>
       </c>
       <c r="AY313" t="inlineStr">
@@ -51009,7 +51009,7 @@
       </c>
       <c r="AT314" t="inlineStr">
         <is>
-          <t>batch_2e8f5425de7c49e5</t>
+          <t>batch_164c8f2ccaa64eaf</t>
         </is>
       </c>
       <c r="AU314" t="inlineStr">
@@ -51025,7 +51025,7 @@
       <c r="AW314" t="inlineStr"/>
       <c r="AX314" t="inlineStr">
         <is>
-          <t>2026-05-14T03:50:20+00:00</t>
+          <t>2026-05-20T00:13:57+00:00</t>
         </is>
       </c>
       <c r="AY314" t="inlineStr">
@@ -51169,7 +51169,7 @@
       </c>
       <c r="AT315" t="inlineStr">
         <is>
-          <t>batch_2e8f5425de7c49e5</t>
+          <t>batch_164c8f2ccaa64eaf</t>
         </is>
       </c>
       <c r="AU315" t="inlineStr">
@@ -51185,7 +51185,7 @@
       <c r="AW315" t="inlineStr"/>
       <c r="AX315" t="inlineStr">
         <is>
-          <t>2026-05-14T03:50:20+00:00</t>
+          <t>2026-05-20T00:13:57+00:00</t>
         </is>
       </c>
       <c r="AY315" t="inlineStr">
@@ -51329,7 +51329,7 @@
       </c>
       <c r="AT316" t="inlineStr">
         <is>
-          <t>batch_2e8f5425de7c49e5</t>
+          <t>batch_164c8f2ccaa64eaf</t>
         </is>
       </c>
       <c r="AU316" t="inlineStr">
@@ -51345,7 +51345,7 @@
       <c r="AW316" t="inlineStr"/>
       <c r="AX316" t="inlineStr">
         <is>
-          <t>2026-05-14T03:50:20+00:00</t>
+          <t>2026-05-20T00:13:57+00:00</t>
         </is>
       </c>
       <c r="AY316" t="inlineStr">
@@ -51489,7 +51489,7 @@
       </c>
       <c r="AT317" t="inlineStr">
         <is>
-          <t>batch_2e8f5425de7c49e5</t>
+          <t>batch_164c8f2ccaa64eaf</t>
         </is>
       </c>
       <c r="AU317" t="inlineStr">
@@ -51505,7 +51505,7 @@
       <c r="AW317" t="inlineStr"/>
       <c r="AX317" t="inlineStr">
         <is>
-          <t>2026-05-14T03:50:20+00:00</t>
+          <t>2026-05-20T00:13:57+00:00</t>
         </is>
       </c>
       <c r="AY317" t="inlineStr">
@@ -51649,7 +51649,7 @@
       </c>
       <c r="AT318" t="inlineStr">
         <is>
-          <t>batch_2e8f5425de7c49e5</t>
+          <t>batch_164c8f2ccaa64eaf</t>
         </is>
       </c>
       <c r="AU318" t="inlineStr">
@@ -51665,7 +51665,7 @@
       <c r="AW318" t="inlineStr"/>
       <c r="AX318" t="inlineStr">
         <is>
-          <t>2026-05-14T03:50:20+00:00</t>
+          <t>2026-05-20T00:13:57+00:00</t>
         </is>
       </c>
       <c r="AY318" t="inlineStr">
@@ -51809,7 +51809,7 @@
       </c>
       <c r="AT319" t="inlineStr">
         <is>
-          <t>batch_2e8f5425de7c49e5</t>
+          <t>batch_164c8f2ccaa64eaf</t>
         </is>
       </c>
       <c r="AU319" t="inlineStr">
@@ -51825,7 +51825,7 @@
       <c r="AW319" t="inlineStr"/>
       <c r="AX319" t="inlineStr">
         <is>
-          <t>2026-05-14T03:50:20+00:00</t>
+          <t>2026-05-20T00:13:57+00:00</t>
         </is>
       </c>
       <c r="AY319" t="inlineStr">
@@ -51969,7 +51969,7 @@
       </c>
       <c r="AT320" t="inlineStr">
         <is>
-          <t>batch_2e8f5425de7c49e5</t>
+          <t>batch_164c8f2ccaa64eaf</t>
         </is>
       </c>
       <c r="AU320" t="inlineStr">
@@ -51985,7 +51985,7 @@
       <c r="AW320" t="inlineStr"/>
       <c r="AX320" t="inlineStr">
         <is>
-          <t>2026-05-14T03:50:20+00:00</t>
+          <t>2026-05-20T00:13:57+00:00</t>
         </is>
       </c>
       <c r="AY320" t="inlineStr">
@@ -52129,7 +52129,7 @@
       </c>
       <c r="AT321" t="inlineStr">
         <is>
-          <t>batch_2e8f5425de7c49e5</t>
+          <t>batch_164c8f2ccaa64eaf</t>
         </is>
       </c>
       <c r="AU321" t="inlineStr">
@@ -52145,7 +52145,7 @@
       <c r="AW321" t="inlineStr"/>
       <c r="AX321" t="inlineStr">
         <is>
-          <t>2026-05-14T03:50:20+00:00</t>
+          <t>2026-05-20T00:13:57+00:00</t>
         </is>
       </c>
       <c r="AY321" t="inlineStr">
@@ -52289,7 +52289,7 @@
       </c>
       <c r="AT322" t="inlineStr">
         <is>
-          <t>batch_2e8f5425de7c49e5</t>
+          <t>batch_164c8f2ccaa64eaf</t>
         </is>
       </c>
       <c r="AU322" t="inlineStr">
@@ -52305,7 +52305,7 @@
       <c r="AW322" t="inlineStr"/>
       <c r="AX322" t="inlineStr">
         <is>
-          <t>2026-05-14T03:50:20+00:00</t>
+          <t>2026-05-20T00:13:57+00:00</t>
         </is>
       </c>
       <c r="AY322" t="inlineStr">
@@ -52449,7 +52449,7 @@
       </c>
       <c r="AT323" t="inlineStr">
         <is>
-          <t>batch_2e8f5425de7c49e5</t>
+          <t>batch_164c8f2ccaa64eaf</t>
         </is>
       </c>
       <c r="AU323" t="inlineStr">
@@ -52465,7 +52465,7 @@
       <c r="AW323" t="inlineStr"/>
       <c r="AX323" t="inlineStr">
         <is>
-          <t>2026-05-14T03:50:20+00:00</t>
+          <t>2026-05-20T00:13:57+00:00</t>
         </is>
       </c>
       <c r="AY323" t="inlineStr">
@@ -52609,7 +52609,7 @@
       </c>
       <c r="AT324" t="inlineStr">
         <is>
-          <t>batch_2e8f5425de7c49e5</t>
+          <t>batch_164c8f2ccaa64eaf</t>
         </is>
       </c>
       <c r="AU324" t="inlineStr">
@@ -52625,7 +52625,7 @@
       <c r="AW324" t="inlineStr"/>
       <c r="AX324" t="inlineStr">
         <is>
-          <t>2026-05-14T03:50:20+00:00</t>
+          <t>2026-05-20T00:13:57+00:00</t>
         </is>
       </c>
       <c r="AY324" t="inlineStr">
@@ -52769,7 +52769,7 @@
       </c>
       <c r="AT325" t="inlineStr">
         <is>
-          <t>batch_2e8f5425de7c49e5</t>
+          <t>batch_164c8f2ccaa64eaf</t>
         </is>
       </c>
       <c r="AU325" t="inlineStr">
@@ -52785,7 +52785,7 @@
       <c r="AW325" t="inlineStr"/>
       <c r="AX325" t="inlineStr">
         <is>
-          <t>2026-05-14T03:50:20+00:00</t>
+          <t>2026-05-20T00:13:57+00:00</t>
         </is>
       </c>
       <c r="AY325" t="inlineStr">
@@ -52929,7 +52929,7 @@
       </c>
       <c r="AT326" t="inlineStr">
         <is>
-          <t>batch_2e8f5425de7c49e5</t>
+          <t>batch_164c8f2ccaa64eaf</t>
         </is>
       </c>
       <c r="AU326" t="inlineStr">
@@ -52945,7 +52945,7 @@
       <c r="AW326" t="inlineStr"/>
       <c r="AX326" t="inlineStr">
         <is>
-          <t>2026-05-14T03:50:20+00:00</t>
+          <t>2026-05-20T00:13:57+00:00</t>
         </is>
       </c>
       <c r="AY326" t="inlineStr">
@@ -53089,7 +53089,7 @@
       </c>
       <c r="AT327" t="inlineStr">
         <is>
-          <t>batch_2e8f5425de7c49e5</t>
+          <t>batch_164c8f2ccaa64eaf</t>
         </is>
       </c>
       <c r="AU327" t="inlineStr">
@@ -53105,7 +53105,7 @@
       <c r="AW327" t="inlineStr"/>
       <c r="AX327" t="inlineStr">
         <is>
-          <t>2026-05-14T03:50:20+00:00</t>
+          <t>2026-05-20T00:13:57+00:00</t>
         </is>
       </c>
       <c r="AY327" t="inlineStr">
@@ -53249,7 +53249,7 @@
       </c>
       <c r="AT328" t="inlineStr">
         <is>
-          <t>batch_2e8f5425de7c49e5</t>
+          <t>batch_164c8f2ccaa64eaf</t>
         </is>
       </c>
       <c r="AU328" t="inlineStr">
@@ -53265,7 +53265,7 @@
       <c r="AW328" t="inlineStr"/>
       <c r="AX328" t="inlineStr">
         <is>
-          <t>2026-05-14T03:50:20+00:00</t>
+          <t>2026-05-20T00:13:57+00:00</t>
         </is>
       </c>
       <c r="AY328" t="inlineStr">
@@ -53409,7 +53409,7 @@
       </c>
       <c r="AT329" t="inlineStr">
         <is>
-          <t>batch_2e8f5425de7c49e5</t>
+          <t>batch_164c8f2ccaa64eaf</t>
         </is>
       </c>
       <c r="AU329" t="inlineStr">
@@ -53425,7 +53425,7 @@
       <c r="AW329" t="inlineStr"/>
       <c r="AX329" t="inlineStr">
         <is>
-          <t>2026-05-14T03:50:20+00:00</t>
+          <t>2026-05-20T00:13:57+00:00</t>
         </is>
       </c>
       <c r="AY329" t="inlineStr">
@@ -53569,7 +53569,7 @@
       </c>
       <c r="AT330" t="inlineStr">
         <is>
-          <t>batch_2e8f5425de7c49e5</t>
+          <t>batch_164c8f2ccaa64eaf</t>
         </is>
       </c>
       <c r="AU330" t="inlineStr">
@@ -53585,7 +53585,7 @@
       <c r="AW330" t="inlineStr"/>
       <c r="AX330" t="inlineStr">
         <is>
-          <t>2026-05-14T03:50:20+00:00</t>
+          <t>2026-05-20T00:13:57+00:00</t>
         </is>
       </c>
       <c r="AY330" t="inlineStr">
@@ -53729,7 +53729,7 @@
       </c>
       <c r="AT331" t="inlineStr">
         <is>
-          <t>batch_2e8f5425de7c49e5</t>
+          <t>batch_164c8f2ccaa64eaf</t>
         </is>
       </c>
       <c r="AU331" t="inlineStr">
@@ -53745,7 +53745,7 @@
       <c r="AW331" t="inlineStr"/>
       <c r="AX331" t="inlineStr">
         <is>
-          <t>2026-05-14T03:50:20+00:00</t>
+          <t>2026-05-20T00:13:57+00:00</t>
         </is>
       </c>
       <c r="AY331" t="inlineStr">
@@ -53889,7 +53889,7 @@
       </c>
       <c r="AT332" t="inlineStr">
         <is>
-          <t>batch_2e8f5425de7c49e5</t>
+          <t>batch_164c8f2ccaa64eaf</t>
         </is>
       </c>
       <c r="AU332" t="inlineStr">
@@ -53905,7 +53905,7 @@
       <c r="AW332" t="inlineStr"/>
       <c r="AX332" t="inlineStr">
         <is>
-          <t>2026-05-14T03:50:20+00:00</t>
+          <t>2026-05-20T00:13:57+00:00</t>
         </is>
       </c>
       <c r="AY332" t="inlineStr">
@@ -54049,7 +54049,7 @@
       </c>
       <c r="AT333" t="inlineStr">
         <is>
-          <t>batch_2e8f5425de7c49e5</t>
+          <t>batch_164c8f2ccaa64eaf</t>
         </is>
       </c>
       <c r="AU333" t="inlineStr">
@@ -54065,7 +54065,7 @@
       <c r="AW333" t="inlineStr"/>
       <c r="AX333" t="inlineStr">
         <is>
-          <t>2026-05-14T03:50:20+00:00</t>
+          <t>2026-05-20T00:13:57+00:00</t>
         </is>
       </c>
       <c r="AY333" t="inlineStr">
@@ -54209,7 +54209,7 @@
       </c>
       <c r="AT334" t="inlineStr">
         <is>
-          <t>batch_2e8f5425de7c49e5</t>
+          <t>batch_164c8f2ccaa64eaf</t>
         </is>
       </c>
       <c r="AU334" t="inlineStr">
@@ -54225,7 +54225,7 @@
       <c r="AW334" t="inlineStr"/>
       <c r="AX334" t="inlineStr">
         <is>
-          <t>2026-05-14T03:50:20+00:00</t>
+          <t>2026-05-20T00:13:57+00:00</t>
         </is>
       </c>
       <c r="AY334" t="inlineStr">
@@ -54369,7 +54369,7 @@
       </c>
       <c r="AT335" t="inlineStr">
         <is>
-          <t>batch_2e8f5425de7c49e5</t>
+          <t>batch_164c8f2ccaa64eaf</t>
         </is>
       </c>
       <c r="AU335" t="inlineStr">
@@ -54385,7 +54385,7 @@
       <c r="AW335" t="inlineStr"/>
       <c r="AX335" t="inlineStr">
         <is>
-          <t>2026-05-14T03:50:20+00:00</t>
+          <t>2026-05-20T00:13:57+00:00</t>
         </is>
       </c>
       <c r="AY335" t="inlineStr">
@@ -54529,7 +54529,7 @@
       </c>
       <c r="AT336" t="inlineStr">
         <is>
-          <t>batch_2e8f5425de7c49e5</t>
+          <t>batch_164c8f2ccaa64eaf</t>
         </is>
       </c>
       <c r="AU336" t="inlineStr">
@@ -54545,7 +54545,7 @@
       <c r="AW336" t="inlineStr"/>
       <c r="AX336" t="inlineStr">
         <is>
-          <t>2026-05-14T03:50:20+00:00</t>
+          <t>2026-05-20T00:13:57+00:00</t>
         </is>
       </c>
       <c r="AY336" t="inlineStr">
@@ -54689,7 +54689,7 @@
       </c>
       <c r="AT337" t="inlineStr">
         <is>
-          <t>batch_2e8f5425de7c49e5</t>
+          <t>batch_164c8f2ccaa64eaf</t>
         </is>
       </c>
       <c r="AU337" t="inlineStr">
@@ -54705,7 +54705,7 @@
       <c r="AW337" t="inlineStr"/>
       <c r="AX337" t="inlineStr">
         <is>
-          <t>2026-05-14T03:50:20+00:00</t>
+          <t>2026-05-20T00:13:57+00:00</t>
         </is>
       </c>
       <c r="AY337" t="inlineStr">
@@ -54849,7 +54849,7 @@
       </c>
       <c r="AT338" t="inlineStr">
         <is>
-          <t>batch_2e8f5425de7c49e5</t>
+          <t>batch_164c8f2ccaa64eaf</t>
         </is>
       </c>
       <c r="AU338" t="inlineStr">
@@ -54865,7 +54865,7 @@
       <c r="AW338" t="inlineStr"/>
       <c r="AX338" t="inlineStr">
         <is>
-          <t>2026-05-14T03:50:20+00:00</t>
+          <t>2026-05-20T00:13:57+00:00</t>
         </is>
       </c>
       <c r="AY338" t="inlineStr">
@@ -55009,7 +55009,7 @@
       </c>
       <c r="AT339" t="inlineStr">
         <is>
-          <t>batch_2e8f5425de7c49e5</t>
+          <t>batch_164c8f2ccaa64eaf</t>
         </is>
       </c>
       <c r="AU339" t="inlineStr">
@@ -55025,7 +55025,7 @@
       <c r="AW339" t="inlineStr"/>
       <c r="AX339" t="inlineStr">
         <is>
-          <t>2026-05-14T03:50:20+00:00</t>
+          <t>2026-05-20T00:13:57+00:00</t>
         </is>
       </c>
       <c r="AY339" t="inlineStr">
@@ -55169,7 +55169,7 @@
       </c>
       <c r="AT340" t="inlineStr">
         <is>
-          <t>batch_2e8f5425de7c49e5</t>
+          <t>batch_164c8f2ccaa64eaf</t>
         </is>
       </c>
       <c r="AU340" t="inlineStr">
@@ -55185,7 +55185,7 @@
       <c r="AW340" t="inlineStr"/>
       <c r="AX340" t="inlineStr">
         <is>
-          <t>2026-05-14T03:50:20+00:00</t>
+          <t>2026-05-20T00:13:57+00:00</t>
         </is>
       </c>
       <c r="AY340" t="inlineStr">
@@ -55329,7 +55329,7 @@
       </c>
       <c r="AT341" t="inlineStr">
         <is>
-          <t>batch_2e8f5425de7c49e5</t>
+          <t>batch_164c8f2ccaa64eaf</t>
         </is>
       </c>
       <c r="AU341" t="inlineStr">
@@ -55345,7 +55345,7 @@
       <c r="AW341" t="inlineStr"/>
       <c r="AX341" t="inlineStr">
         <is>
-          <t>2026-05-14T03:50:20+00:00</t>
+          <t>2026-05-20T00:13:57+00:00</t>
         </is>
       </c>
       <c r="AY341" t="inlineStr">
@@ -55489,7 +55489,7 @@
       </c>
       <c r="AT342" t="inlineStr">
         <is>
-          <t>batch_2e8f5425de7c49e5</t>
+          <t>batch_164c8f2ccaa64eaf</t>
         </is>
       </c>
       <c r="AU342" t="inlineStr">
@@ -55505,7 +55505,7 @@
       <c r="AW342" t="inlineStr"/>
       <c r="AX342" t="inlineStr">
         <is>
-          <t>2026-05-14T03:50:20+00:00</t>
+          <t>2026-05-20T00:13:57+00:00</t>
         </is>
       </c>
       <c r="AY342" t="inlineStr">
@@ -55649,7 +55649,7 @@
       </c>
       <c r="AT343" t="inlineStr">
         <is>
-          <t>batch_2e8f5425de7c49e5</t>
+          <t>batch_164c8f2ccaa64eaf</t>
         </is>
       </c>
       <c r="AU343" t="inlineStr">
@@ -55665,7 +55665,7 @@
       <c r="AW343" t="inlineStr"/>
       <c r="AX343" t="inlineStr">
         <is>
-          <t>2026-05-14T03:50:20+00:00</t>
+          <t>2026-05-20T00:13:57+00:00</t>
         </is>
       </c>
       <c r="AY343" t="inlineStr">
@@ -55809,7 +55809,7 @@
       </c>
       <c r="AT344" t="inlineStr">
         <is>
-          <t>batch_2e8f5425de7c49e5</t>
+          <t>batch_164c8f2ccaa64eaf</t>
         </is>
       </c>
       <c r="AU344" t="inlineStr">
@@ -55825,7 +55825,7 @@
       <c r="AW344" t="inlineStr"/>
       <c r="AX344" t="inlineStr">
         <is>
-          <t>2026-05-14T03:50:20+00:00</t>
+          <t>2026-05-20T00:13:57+00:00</t>
         </is>
       </c>
       <c r="AY344" t="inlineStr">
@@ -55969,7 +55969,7 @@
       </c>
       <c r="AT345" t="inlineStr">
         <is>
-          <t>batch_2e8f5425de7c49e5</t>
+          <t>batch_164c8f2ccaa64eaf</t>
         </is>
       </c>
       <c r="AU345" t="inlineStr">
@@ -55985,7 +55985,7 @@
       <c r="AW345" t="inlineStr"/>
       <c r="AX345" t="inlineStr">
         <is>
-          <t>2026-05-14T03:50:20+00:00</t>
+          <t>2026-05-20T00:13:57+00:00</t>
         </is>
       </c>
       <c r="AY345" t="inlineStr">
@@ -56129,7 +56129,7 @@
       </c>
       <c r="AT346" t="inlineStr">
         <is>
-          <t>batch_2e8f5425de7c49e5</t>
+          <t>batch_164c8f2ccaa64eaf</t>
         </is>
       </c>
       <c r="AU346" t="inlineStr">
@@ -56145,7 +56145,7 @@
       <c r="AW346" t="inlineStr"/>
       <c r="AX346" t="inlineStr">
         <is>
-          <t>2026-05-14T03:50:20+00:00</t>
+          <t>2026-05-20T00:13:57+00:00</t>
         </is>
       </c>
       <c r="AY346" t="inlineStr">
@@ -56289,7 +56289,7 @@
       </c>
       <c r="AT347" t="inlineStr">
         <is>
-          <t>batch_2e8f5425de7c49e5</t>
+          <t>batch_164c8f2ccaa64eaf</t>
         </is>
       </c>
       <c r="AU347" t="inlineStr">
@@ -56305,7 +56305,7 @@
       <c r="AW347" t="inlineStr"/>
       <c r="AX347" t="inlineStr">
         <is>
-          <t>2026-05-14T03:50:20+00:00</t>
+          <t>2026-05-20T00:13:57+00:00</t>
         </is>
       </c>
       <c r="AY347" t="inlineStr">
@@ -56449,7 +56449,7 @@
       </c>
       <c r="AT348" t="inlineStr">
         <is>
-          <t>batch_2e8f5425de7c49e5</t>
+          <t>batch_164c8f2ccaa64eaf</t>
         </is>
       </c>
       <c r="AU348" t="inlineStr">
@@ -56465,7 +56465,7 @@
       <c r="AW348" t="inlineStr"/>
       <c r="AX348" t="inlineStr">
         <is>
-          <t>2026-05-14T03:50:20+00:00</t>
+          <t>2026-05-20T00:13:57+00:00</t>
         </is>
       </c>
       <c r="AY348" t="inlineStr">
@@ -56609,7 +56609,7 @@
       </c>
       <c r="AT349" t="inlineStr">
         <is>
-          <t>batch_2e8f5425de7c49e5</t>
+          <t>batch_164c8f2ccaa64eaf</t>
         </is>
       </c>
       <c r="AU349" t="inlineStr">
@@ -56625,7 +56625,7 @@
       <c r="AW349" t="inlineStr"/>
       <c r="AX349" t="inlineStr">
         <is>
-          <t>2026-05-14T03:50:20+00:00</t>
+          <t>2026-05-20T00:13:57+00:00</t>
         </is>
       </c>
       <c r="AY349" t="inlineStr">
@@ -56754,7 +56754,7 @@
       </c>
       <c r="AT350" t="inlineStr">
         <is>
-          <t>batch_2e8f5425de7c49e5</t>
+          <t>batch_164c8f2ccaa64eaf</t>
         </is>
       </c>
       <c r="AU350" t="inlineStr">
@@ -56770,7 +56770,7 @@
       <c r="AW350" t="inlineStr"/>
       <c r="AX350" t="inlineStr">
         <is>
-          <t>2026-05-14T03:50:20+00:00</t>
+          <t>2026-05-20T00:13:57+00:00</t>
         </is>
       </c>
       <c r="AY350" t="inlineStr">
@@ -56899,7 +56899,7 @@
       </c>
       <c r="AT351" t="inlineStr">
         <is>
-          <t>batch_2e8f5425de7c49e5</t>
+          <t>batch_164c8f2ccaa64eaf</t>
         </is>
       </c>
       <c r="AU351" t="inlineStr">
@@ -56915,7 +56915,7 @@
       <c r="AW351" t="inlineStr"/>
       <c r="AX351" t="inlineStr">
         <is>
-          <t>2026-05-14T03:50:20+00:00</t>
+          <t>2026-05-20T00:13:57+00:00</t>
         </is>
       </c>
       <c r="AY351" t="inlineStr">
@@ -57044,7 +57044,7 @@
       </c>
       <c r="AT352" t="inlineStr">
         <is>
-          <t>batch_2e8f5425de7c49e5</t>
+          <t>batch_164c8f2ccaa64eaf</t>
         </is>
       </c>
       <c r="AU352" t="inlineStr">
@@ -57060,7 +57060,7 @@
       <c r="AW352" t="inlineStr"/>
       <c r="AX352" t="inlineStr">
         <is>
-          <t>2026-05-14T03:50:20+00:00</t>
+          <t>2026-05-20T00:13:57+00:00</t>
         </is>
       </c>
       <c r="AY352" t="inlineStr">
@@ -57189,7 +57189,7 @@
       </c>
       <c r="AT353" t="inlineStr">
         <is>
-          <t>batch_2e8f5425de7c49e5</t>
+          <t>batch_164c8f2ccaa64eaf</t>
         </is>
       </c>
       <c r="AU353" t="inlineStr">
@@ -57205,7 +57205,7 @@
       <c r="AW353" t="inlineStr"/>
       <c r="AX353" t="inlineStr">
         <is>
-          <t>2026-05-14T03:50:20+00:00</t>
+          <t>2026-05-20T00:13:57+00:00</t>
         </is>
       </c>
       <c r="AY353" t="inlineStr">
@@ -57334,7 +57334,7 @@
       </c>
       <c r="AT354" t="inlineStr">
         <is>
-          <t>batch_2e8f5425de7c49e5</t>
+          <t>batch_164c8f2ccaa64eaf</t>
         </is>
       </c>
       <c r="AU354" t="inlineStr">
@@ -57350,7 +57350,7 @@
       <c r="AW354" t="inlineStr"/>
       <c r="AX354" t="inlineStr">
         <is>
-          <t>2026-05-14T03:50:20+00:00</t>
+          <t>2026-05-20T00:13:57+00:00</t>
         </is>
       </c>
       <c r="AY354" t="inlineStr">
@@ -57479,7 +57479,7 @@
       </c>
       <c r="AT355" t="inlineStr">
         <is>
-          <t>batch_2e8f5425de7c49e5</t>
+          <t>batch_164c8f2ccaa64eaf</t>
         </is>
       </c>
       <c r="AU355" t="inlineStr">
@@ -57495,7 +57495,7 @@
       <c r="AW355" t="inlineStr"/>
       <c r="AX355" t="inlineStr">
         <is>
-          <t>2026-05-14T03:50:20+00:00</t>
+          <t>2026-05-20T00:13:57+00:00</t>
         </is>
       </c>
       <c r="AY355" t="inlineStr">
@@ -57624,7 +57624,7 @@
       </c>
       <c r="AT356" t="inlineStr">
         <is>
-          <t>batch_2e8f5425de7c49e5</t>
+          <t>batch_164c8f2ccaa64eaf</t>
         </is>
       </c>
       <c r="AU356" t="inlineStr">
@@ -57640,7 +57640,7 @@
       <c r="AW356" t="inlineStr"/>
       <c r="AX356" t="inlineStr">
         <is>
-          <t>2026-05-14T03:50:20+00:00</t>
+          <t>2026-05-20T00:13:57+00:00</t>
         </is>
       </c>
       <c r="AY356" t="inlineStr">
@@ -57769,7 +57769,7 @@
       </c>
       <c r="AT357" t="inlineStr">
         <is>
-          <t>batch_2e8f5425de7c49e5</t>
+          <t>batch_164c8f2ccaa64eaf</t>
         </is>
       </c>
       <c r="AU357" t="inlineStr">
@@ -57785,7 +57785,7 @@
       <c r="AW357" t="inlineStr"/>
       <c r="AX357" t="inlineStr">
         <is>
-          <t>2026-05-14T03:50:20+00:00</t>
+          <t>2026-05-20T00:13:57+00:00</t>
         </is>
       </c>
       <c r="AY357" t="inlineStr">
@@ -57914,7 +57914,7 @@
       </c>
       <c r="AT358" t="inlineStr">
         <is>
-          <t>batch_2e8f5425de7c49e5</t>
+          <t>batch_164c8f2ccaa64eaf</t>
         </is>
       </c>
       <c r="AU358" t="inlineStr">
@@ -57930,7 +57930,7 @@
       <c r="AW358" t="inlineStr"/>
       <c r="AX358" t="inlineStr">
         <is>
-          <t>2026-05-14T03:50:20+00:00</t>
+          <t>2026-05-20T00:13:57+00:00</t>
         </is>
       </c>
       <c r="AY358" t="inlineStr">
@@ -58059,7 +58059,7 @@
       </c>
       <c r="AT359" t="inlineStr">
         <is>
-          <t>batch_2e8f5425de7c49e5</t>
+          <t>batch_164c8f2ccaa64eaf</t>
         </is>
       </c>
       <c r="AU359" t="inlineStr">
@@ -58075,7 +58075,7 @@
       <c r="AW359" t="inlineStr"/>
       <c r="AX359" t="inlineStr">
         <is>
-          <t>2026-05-14T03:50:20+00:00</t>
+          <t>2026-05-20T00:13:57+00:00</t>
         </is>
       </c>
       <c r="AY359" t="inlineStr">
@@ -58204,7 +58204,7 @@
       </c>
       <c r="AT360" t="inlineStr">
         <is>
-          <t>batch_2e8f5425de7c49e5</t>
+          <t>batch_164c8f2ccaa64eaf</t>
         </is>
       </c>
       <c r="AU360" t="inlineStr">
@@ -58220,7 +58220,7 @@
       <c r="AW360" t="inlineStr"/>
       <c r="AX360" t="inlineStr">
         <is>
-          <t>2026-05-14T03:50:20+00:00</t>
+          <t>2026-05-20T00:13:57+00:00</t>
         </is>
       </c>
       <c r="AY360" t="inlineStr">
@@ -58340,7 +58340,7 @@
       </c>
       <c r="AT361" t="inlineStr">
         <is>
-          <t>batch_2e8f5425de7c49e5</t>
+          <t>batch_164c8f2ccaa64eaf</t>
         </is>
       </c>
       <c r="AU361" t="inlineStr">
@@ -58356,7 +58356,7 @@
       <c r="AW361" t="inlineStr"/>
       <c r="AX361" t="inlineStr">
         <is>
-          <t>2026-05-14T03:50:20+00:00</t>
+          <t>2026-05-20T00:13:57+00:00</t>
         </is>
       </c>
       <c r="AY361" t="inlineStr">
@@ -58458,7 +58458,7 @@
       </c>
       <c r="AT362" t="inlineStr">
         <is>
-          <t>batch_2e8f5425de7c49e5</t>
+          <t>batch_164c8f2ccaa64eaf</t>
         </is>
       </c>
       <c r="AU362" t="inlineStr">
@@ -58474,7 +58474,7 @@
       <c r="AW362" t="inlineStr"/>
       <c r="AX362" t="inlineStr">
         <is>
-          <t>2026-05-14T03:50:20+00:00</t>
+          <t>2026-05-20T00:13:57+00:00</t>
         </is>
       </c>
       <c r="AY362" t="inlineStr">
@@ -58576,7 +58576,7 @@
       </c>
       <c r="AT363" t="inlineStr">
         <is>
-          <t>batch_2e8f5425de7c49e5</t>
+          <t>batch_164c8f2ccaa64eaf</t>
         </is>
       </c>
       <c r="AU363" t="inlineStr">
@@ -58592,7 +58592,7 @@
       <c r="AW363" t="inlineStr"/>
       <c r="AX363" t="inlineStr">
         <is>
-          <t>2026-05-14T03:50:20+00:00</t>
+          <t>2026-05-20T00:13:57+00:00</t>
         </is>
       </c>
       <c r="AY363" t="inlineStr">
@@ -58694,7 +58694,7 @@
       </c>
       <c r="AT364" t="inlineStr">
         <is>
-          <t>batch_2e8f5425de7c49e5</t>
+          <t>batch_164c8f2ccaa64eaf</t>
         </is>
       </c>
       <c r="AU364" t="inlineStr">
@@ -58710,7 +58710,7 @@
       <c r="AW364" t="inlineStr"/>
       <c r="AX364" t="inlineStr">
         <is>
-          <t>2026-05-14T03:50:20+00:00</t>
+          <t>2026-05-20T00:13:57+00:00</t>
         </is>
       </c>
       <c r="AY364" t="inlineStr">
@@ -58812,7 +58812,7 @@
       </c>
       <c r="AT365" t="inlineStr">
         <is>
-          <t>batch_2e8f5425de7c49e5</t>
+          <t>batch_164c8f2ccaa64eaf</t>
         </is>
       </c>
       <c r="AU365" t="inlineStr">
@@ -58828,7 +58828,7 @@
       <c r="AW365" t="inlineStr"/>
       <c r="AX365" t="inlineStr">
         <is>
-          <t>2026-05-14T03:50:20+00:00</t>
+          <t>2026-05-20T00:13:57+00:00</t>
         </is>
       </c>
       <c r="AY365" t="inlineStr">
@@ -58930,7 +58930,7 @@
       </c>
       <c r="AT366" t="inlineStr">
         <is>
-          <t>batch_2e8f5425de7c49e5</t>
+          <t>batch_164c8f2ccaa64eaf</t>
         </is>
       </c>
       <c r="AU366" t="inlineStr">
@@ -58946,7 +58946,7 @@
       <c r="AW366" t="inlineStr"/>
       <c r="AX366" t="inlineStr">
         <is>
-          <t>2026-05-14T03:50:20+00:00</t>
+          <t>2026-05-20T00:13:57+00:00</t>
         </is>
       </c>
       <c r="AY366" t="inlineStr">
@@ -59048,7 +59048,7 @@
       </c>
       <c r="AT367" t="inlineStr">
         <is>
-          <t>batch_2e8f5425de7c49e5</t>
+          <t>batch_164c8f2ccaa64eaf</t>
         </is>
       </c>
       <c r="AU367" t="inlineStr">
@@ -59064,7 +59064,7 @@
       <c r="AW367" t="inlineStr"/>
       <c r="AX367" t="inlineStr">
         <is>
-          <t>2026-05-14T03:50:20+00:00</t>
+          <t>2026-05-20T00:13:57+00:00</t>
         </is>
       </c>
       <c r="AY367" t="inlineStr">
@@ -59166,7 +59166,7 @@
       </c>
       <c r="AT368" t="inlineStr">
         <is>
-          <t>batch_2e8f5425de7c49e5</t>
+          <t>batch_164c8f2ccaa64eaf</t>
         </is>
       </c>
       <c r="AU368" t="inlineStr">
@@ -59182,7 +59182,7 @@
       <c r="AW368" t="inlineStr"/>
       <c r="AX368" t="inlineStr">
         <is>
-          <t>2026-05-14T03:50:20+00:00</t>
+          <t>2026-05-20T00:13:57+00:00</t>
         </is>
       </c>
       <c r="AY368" t="inlineStr">
@@ -59284,7 +59284,7 @@
       </c>
       <c r="AT369" t="inlineStr">
         <is>
-          <t>batch_2e8f5425de7c49e5</t>
+          <t>batch_164c8f2ccaa64eaf</t>
         </is>
       </c>
       <c r="AU369" t="inlineStr">
@@ -59300,7 +59300,7 @@
       <c r="AW369" t="inlineStr"/>
       <c r="AX369" t="inlineStr">
         <is>
-          <t>2026-05-14T03:50:20+00:00</t>
+          <t>2026-05-20T00:13:57+00:00</t>
         </is>
       </c>
       <c r="AY369" t="inlineStr">
@@ -59402,7 +59402,7 @@
       </c>
       <c r="AT370" t="inlineStr">
         <is>
-          <t>batch_2e8f5425de7c49e5</t>
+          <t>batch_164c8f2ccaa64eaf</t>
         </is>
       </c>
       <c r="AU370" t="inlineStr">
@@ -59418,7 +59418,7 @@
       <c r="AW370" t="inlineStr"/>
       <c r="AX370" t="inlineStr">
         <is>
-          <t>2026-05-14T03:50:20+00:00</t>
+          <t>2026-05-20T00:13:57+00:00</t>
         </is>
       </c>
       <c r="AY370" t="inlineStr">
@@ -59520,7 +59520,7 @@
       </c>
       <c r="AT371" t="inlineStr">
         <is>
-          <t>batch_2e8f5425de7c49e5</t>
+          <t>batch_164c8f2ccaa64eaf</t>
         </is>
       </c>
       <c r="AU371" t="inlineStr">
@@ -59536,7 +59536,7 @@
       <c r="AW371" t="inlineStr"/>
       <c r="AX371" t="inlineStr">
         <is>
-          <t>2026-05-14T03:50:20+00:00</t>
+          <t>2026-05-20T00:13:57+00:00</t>
         </is>
       </c>
       <c r="AY371" t="inlineStr">
@@ -59638,7 +59638,7 @@
       </c>
       <c r="AT372" t="inlineStr">
         <is>
-          <t>batch_2e8f5425de7c49e5</t>
+          <t>batch_164c8f2ccaa64eaf</t>
         </is>
       </c>
       <c r="AU372" t="inlineStr">
@@ -59654,7 +59654,7 @@
       <c r="AW372" t="inlineStr"/>
       <c r="AX372" t="inlineStr">
         <is>
-          <t>2026-05-14T03:50:20+00:00</t>
+          <t>2026-05-20T00:13:57+00:00</t>
         </is>
       </c>
       <c r="AY372" t="inlineStr">
@@ -61593,7 +61593,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Built 2026-05-14T03:50:20+00:00. Normalization version: v1.2.</t>
+          <t>Built 2026-05-20T00:13:57+00:00. Normalization version: v1.2.</t>
         </is>
       </c>
     </row>

--- a/services/costar/MASTER/COSTAR_MASTER_MERCADOS.xlsx
+++ b/services/costar/MASTER/COSTAR_MASTER_MERCADOS.xlsx
@@ -898,7 +898,7 @@
       </c>
       <c r="AT2" t="inlineStr">
         <is>
-          <t>batch_164c8f2ccaa64eaf</t>
+          <t>batch_4e3853438a5d4f9c</t>
         </is>
       </c>
       <c r="AU2" t="inlineStr">
@@ -914,7 +914,7 @@
       <c r="AW2" t="inlineStr"/>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>2026-05-20T00:13:57+00:00</t>
+          <t>2026-05-20T00:48:39+00:00</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
@@ -1044,7 +1044,7 @@
       </c>
       <c r="AT3" t="inlineStr">
         <is>
-          <t>batch_164c8f2ccaa64eaf</t>
+          <t>batch_4e3853438a5d4f9c</t>
         </is>
       </c>
       <c r="AU3" t="inlineStr">
@@ -1060,7 +1060,7 @@
       <c r="AW3" t="inlineStr"/>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>2026-05-20T00:13:57+00:00</t>
+          <t>2026-05-20T00:48:39+00:00</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">
@@ -1190,7 +1190,7 @@
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>batch_164c8f2ccaa64eaf</t>
+          <t>batch_4e3853438a5d4f9c</t>
         </is>
       </c>
       <c r="AU4" t="inlineStr">
@@ -1206,7 +1206,7 @@
       <c r="AW4" t="inlineStr"/>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>2026-05-20T00:13:57+00:00</t>
+          <t>2026-05-20T00:48:39+00:00</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">
@@ -1336,7 +1336,7 @@
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>batch_164c8f2ccaa64eaf</t>
+          <t>batch_4e3853438a5d4f9c</t>
         </is>
       </c>
       <c r="AU5" t="inlineStr">
@@ -1352,7 +1352,7 @@
       <c r="AW5" t="inlineStr"/>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>2026-05-20T00:13:57+00:00</t>
+          <t>2026-05-20T00:48:39+00:00</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr">
@@ -1482,7 +1482,7 @@
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>batch_164c8f2ccaa64eaf</t>
+          <t>batch_4e3853438a5d4f9c</t>
         </is>
       </c>
       <c r="AU6" t="inlineStr">
@@ -1498,7 +1498,7 @@
       <c r="AW6" t="inlineStr"/>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>2026-05-20T00:13:57+00:00</t>
+          <t>2026-05-20T00:48:39+00:00</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr">
@@ -1628,7 +1628,7 @@
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>batch_164c8f2ccaa64eaf</t>
+          <t>batch_4e3853438a5d4f9c</t>
         </is>
       </c>
       <c r="AU7" t="inlineStr">
@@ -1644,7 +1644,7 @@
       <c r="AW7" t="inlineStr"/>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>2026-05-20T00:13:57+00:00</t>
+          <t>2026-05-20T00:48:39+00:00</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr">
@@ -1720,7 +1720,7 @@
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>batch_164c8f2ccaa64eaf</t>
+          <t>batch_4e3853438a5d4f9c</t>
         </is>
       </c>
       <c r="AU8" t="inlineStr">
@@ -1736,7 +1736,7 @@
       <c r="AW8" t="inlineStr"/>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>2026-05-20T00:13:57+00:00</t>
+          <t>2026-05-20T00:48:39+00:00</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr">
@@ -1827,7 +1827,7 @@
       </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>batch_164c8f2ccaa64eaf</t>
+          <t>batch_4e3853438a5d4f9c</t>
         </is>
       </c>
       <c r="AU9" t="inlineStr">
@@ -1843,7 +1843,7 @@
       <c r="AW9" t="inlineStr"/>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>2026-05-20T00:13:57+00:00</t>
+          <t>2026-05-20T00:48:39+00:00</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr">
@@ -1934,7 +1934,7 @@
       </c>
       <c r="AT10" t="inlineStr">
         <is>
-          <t>batch_164c8f2ccaa64eaf</t>
+          <t>batch_4e3853438a5d4f9c</t>
         </is>
       </c>
       <c r="AU10" t="inlineStr">
@@ -1950,7 +1950,7 @@
       <c r="AW10" t="inlineStr"/>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>2026-05-20T00:13:57+00:00</t>
+          <t>2026-05-20T00:48:39+00:00</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr">
@@ -2041,7 +2041,7 @@
       </c>
       <c r="AT11" t="inlineStr">
         <is>
-          <t>batch_164c8f2ccaa64eaf</t>
+          <t>batch_4e3853438a5d4f9c</t>
         </is>
       </c>
       <c r="AU11" t="inlineStr">
@@ -2057,7 +2057,7 @@
       <c r="AW11" t="inlineStr"/>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>2026-05-20T00:13:57+00:00</t>
+          <t>2026-05-20T00:48:39+00:00</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr">
@@ -2148,7 +2148,7 @@
       </c>
       <c r="AT12" t="inlineStr">
         <is>
-          <t>batch_164c8f2ccaa64eaf</t>
+          <t>batch_4e3853438a5d4f9c</t>
         </is>
       </c>
       <c r="AU12" t="inlineStr">
@@ -2164,7 +2164,7 @@
       <c r="AW12" t="inlineStr"/>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>2026-05-20T00:13:57+00:00</t>
+          <t>2026-05-20T00:48:39+00:00</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr">
@@ -2255,7 +2255,7 @@
       </c>
       <c r="AT13" t="inlineStr">
         <is>
-          <t>batch_164c8f2ccaa64eaf</t>
+          <t>batch_4e3853438a5d4f9c</t>
         </is>
       </c>
       <c r="AU13" t="inlineStr">
@@ -2271,7 +2271,7 @@
       <c r="AW13" t="inlineStr"/>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>2026-05-20T00:13:57+00:00</t>
+          <t>2026-05-20T00:48:39+00:00</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr">
@@ -2362,7 +2362,7 @@
       </c>
       <c r="AT14" t="inlineStr">
         <is>
-          <t>batch_164c8f2ccaa64eaf</t>
+          <t>batch_4e3853438a5d4f9c</t>
         </is>
       </c>
       <c r="AU14" t="inlineStr">
@@ -2378,7 +2378,7 @@
       <c r="AW14" t="inlineStr"/>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>2026-05-20T00:13:57+00:00</t>
+          <t>2026-05-20T00:48:39+00:00</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr">
@@ -2469,7 +2469,7 @@
       </c>
       <c r="AT15" t="inlineStr">
         <is>
-          <t>batch_164c8f2ccaa64eaf</t>
+          <t>batch_4e3853438a5d4f9c</t>
         </is>
       </c>
       <c r="AU15" t="inlineStr">
@@ -2485,7 +2485,7 @@
       <c r="AW15" t="inlineStr"/>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>2026-05-20T00:13:57+00:00</t>
+          <t>2026-05-20T00:48:39+00:00</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr">
@@ -2576,7 +2576,7 @@
       </c>
       <c r="AT16" t="inlineStr">
         <is>
-          <t>batch_164c8f2ccaa64eaf</t>
+          <t>batch_4e3853438a5d4f9c</t>
         </is>
       </c>
       <c r="AU16" t="inlineStr">
@@ -2592,7 +2592,7 @@
       <c r="AW16" t="inlineStr"/>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>2026-05-20T00:13:57+00:00</t>
+          <t>2026-05-20T00:48:39+00:00</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr">
@@ -2745,7 +2745,7 @@
       </c>
       <c r="AT17" t="inlineStr">
         <is>
-          <t>batch_164c8f2ccaa64eaf</t>
+          <t>batch_4e3853438a5d4f9c</t>
         </is>
       </c>
       <c r="AU17" t="inlineStr">
@@ -2761,7 +2761,7 @@
       <c r="AW17" t="inlineStr"/>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>2026-05-20T00:13:57+00:00</t>
+          <t>2026-05-20T00:48:39+00:00</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr">
@@ -2914,7 +2914,7 @@
       </c>
       <c r="AT18" t="inlineStr">
         <is>
-          <t>batch_164c8f2ccaa64eaf</t>
+          <t>batch_4e3853438a5d4f9c</t>
         </is>
       </c>
       <c r="AU18" t="inlineStr">
@@ -2930,7 +2930,7 @@
       <c r="AW18" t="inlineStr"/>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>2026-05-20T00:13:57+00:00</t>
+          <t>2026-05-20T00:48:39+00:00</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr">
@@ -3083,7 +3083,7 @@
       </c>
       <c r="AT19" t="inlineStr">
         <is>
-          <t>batch_164c8f2ccaa64eaf</t>
+          <t>batch_4e3853438a5d4f9c</t>
         </is>
       </c>
       <c r="AU19" t="inlineStr">
@@ -3099,7 +3099,7 @@
       <c r="AW19" t="inlineStr"/>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>2026-05-20T00:13:57+00:00</t>
+          <t>2026-05-20T00:48:39+00:00</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr">
@@ -3252,7 +3252,7 @@
       </c>
       <c r="AT20" t="inlineStr">
         <is>
-          <t>batch_164c8f2ccaa64eaf</t>
+          <t>batch_4e3853438a5d4f9c</t>
         </is>
       </c>
       <c r="AU20" t="inlineStr">
@@ -3268,7 +3268,7 @@
       <c r="AW20" t="inlineStr"/>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>2026-05-20T00:13:57+00:00</t>
+          <t>2026-05-20T00:48:39+00:00</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr">
@@ -3421,7 +3421,7 @@
       </c>
       <c r="AT21" t="inlineStr">
         <is>
-          <t>batch_164c8f2ccaa64eaf</t>
+          <t>batch_4e3853438a5d4f9c</t>
         </is>
       </c>
       <c r="AU21" t="inlineStr">
@@ -3437,7 +3437,7 @@
       <c r="AW21" t="inlineStr"/>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>2026-05-20T00:13:57+00:00</t>
+          <t>2026-05-20T00:48:39+00:00</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr">
@@ -3590,7 +3590,7 @@
       </c>
       <c r="AT22" t="inlineStr">
         <is>
-          <t>batch_164c8f2ccaa64eaf</t>
+          <t>batch_4e3853438a5d4f9c</t>
         </is>
       </c>
       <c r="AU22" t="inlineStr">
@@ -3606,7 +3606,7 @@
       <c r="AW22" t="inlineStr"/>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>2026-05-20T00:13:57+00:00</t>
+          <t>2026-05-20T00:48:39+00:00</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr">
@@ -3759,7 +3759,7 @@
       </c>
       <c r="AT23" t="inlineStr">
         <is>
-          <t>batch_164c8f2ccaa64eaf</t>
+          <t>batch_4e3853438a5d4f9c</t>
         </is>
       </c>
       <c r="AU23" t="inlineStr">
@@ -3775,7 +3775,7 @@
       <c r="AW23" t="inlineStr"/>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>2026-05-20T00:13:57+00:00</t>
+          <t>2026-05-20T00:48:39+00:00</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr">
@@ -3928,7 +3928,7 @@
       </c>
       <c r="AT24" t="inlineStr">
         <is>
-          <t>batch_164c8f2ccaa64eaf</t>
+          <t>batch_4e3853438a5d4f9c</t>
         </is>
       </c>
       <c r="AU24" t="inlineStr">
@@ -3944,7 +3944,7 @@
       <c r="AW24" t="inlineStr"/>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>2026-05-20T00:13:57+00:00</t>
+          <t>2026-05-20T00:48:39+00:00</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr">
@@ -4097,7 +4097,7 @@
       </c>
       <c r="AT25" t="inlineStr">
         <is>
-          <t>batch_164c8f2ccaa64eaf</t>
+          <t>batch_4e3853438a5d4f9c</t>
         </is>
       </c>
       <c r="AU25" t="inlineStr">
@@ -4113,7 +4113,7 @@
       <c r="AW25" t="inlineStr"/>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>2026-05-20T00:13:57+00:00</t>
+          <t>2026-05-20T00:48:39+00:00</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr">
@@ -4266,7 +4266,7 @@
       </c>
       <c r="AT26" t="inlineStr">
         <is>
-          <t>batch_164c8f2ccaa64eaf</t>
+          <t>batch_4e3853438a5d4f9c</t>
         </is>
       </c>
       <c r="AU26" t="inlineStr">
@@ -4282,7 +4282,7 @@
       <c r="AW26" t="inlineStr"/>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>2026-05-20T00:13:57+00:00</t>
+          <t>2026-05-20T00:48:39+00:00</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr">
@@ -4435,7 +4435,7 @@
       </c>
       <c r="AT27" t="inlineStr">
         <is>
-          <t>batch_164c8f2ccaa64eaf</t>
+          <t>batch_4e3853438a5d4f9c</t>
         </is>
       </c>
       <c r="AU27" t="inlineStr">
@@ -4451,7 +4451,7 @@
       <c r="AW27" t="inlineStr"/>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>2026-05-20T00:13:57+00:00</t>
+          <t>2026-05-20T00:48:39+00:00</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr">
@@ -4604,7 +4604,7 @@
       </c>
       <c r="AT28" t="inlineStr">
         <is>
-          <t>batch_164c8f2ccaa64eaf</t>
+          <t>batch_4e3853438a5d4f9c</t>
         </is>
       </c>
       <c r="AU28" t="inlineStr">
@@ -4620,7 +4620,7 @@
       <c r="AW28" t="inlineStr"/>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>2026-05-20T00:13:57+00:00</t>
+          <t>2026-05-20T00:48:39+00:00</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr">
@@ -4773,7 +4773,7 @@
       </c>
       <c r="AT29" t="inlineStr">
         <is>
-          <t>batch_164c8f2ccaa64eaf</t>
+          <t>batch_4e3853438a5d4f9c</t>
         </is>
       </c>
       <c r="AU29" t="inlineStr">
@@ -4789,7 +4789,7 @@
       <c r="AW29" t="inlineStr"/>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>2026-05-20T00:13:57+00:00</t>
+          <t>2026-05-20T00:48:39+00:00</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr">
@@ -4942,7 +4942,7 @@
       </c>
       <c r="AT30" t="inlineStr">
         <is>
-          <t>batch_164c8f2ccaa64eaf</t>
+          <t>batch_4e3853438a5d4f9c</t>
         </is>
       </c>
       <c r="AU30" t="inlineStr">
@@ -4958,7 +4958,7 @@
       <c r="AW30" t="inlineStr"/>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>2026-05-20T00:13:57+00:00</t>
+          <t>2026-05-20T00:48:39+00:00</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr">
@@ -5111,7 +5111,7 @@
       </c>
       <c r="AT31" t="inlineStr">
         <is>
-          <t>batch_164c8f2ccaa64eaf</t>
+          <t>batch_4e3853438a5d4f9c</t>
         </is>
       </c>
       <c r="AU31" t="inlineStr">
@@ -5127,7 +5127,7 @@
       <c r="AW31" t="inlineStr"/>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>2026-05-20T00:13:57+00:00</t>
+          <t>2026-05-20T00:48:39+00:00</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr">
@@ -5280,7 +5280,7 @@
       </c>
       <c r="AT32" t="inlineStr">
         <is>
-          <t>batch_164c8f2ccaa64eaf</t>
+          <t>batch_4e3853438a5d4f9c</t>
         </is>
       </c>
       <c r="AU32" t="inlineStr">
@@ -5296,7 +5296,7 @@
       <c r="AW32" t="inlineStr"/>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>2026-05-20T00:13:57+00:00</t>
+          <t>2026-05-20T00:48:39+00:00</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr">
@@ -5449,7 +5449,7 @@
       </c>
       <c r="AT33" t="inlineStr">
         <is>
-          <t>batch_164c8f2ccaa64eaf</t>
+          <t>batch_4e3853438a5d4f9c</t>
         </is>
       </c>
       <c r="AU33" t="inlineStr">
@@ -5465,7 +5465,7 @@
       <c r="AW33" t="inlineStr"/>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>2026-05-20T00:13:57+00:00</t>
+          <t>2026-05-20T00:48:39+00:00</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr">
@@ -5618,7 +5618,7 @@
       </c>
       <c r="AT34" t="inlineStr">
         <is>
-          <t>batch_164c8f2ccaa64eaf</t>
+          <t>batch_4e3853438a5d4f9c</t>
         </is>
       </c>
       <c r="AU34" t="inlineStr">
@@ -5634,7 +5634,7 @@
       <c r="AW34" t="inlineStr"/>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>2026-05-20T00:13:57+00:00</t>
+          <t>2026-05-20T00:48:39+00:00</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr">
@@ -5787,7 +5787,7 @@
       </c>
       <c r="AT35" t="inlineStr">
         <is>
-          <t>batch_164c8f2ccaa64eaf</t>
+          <t>batch_4e3853438a5d4f9c</t>
         </is>
       </c>
       <c r="AU35" t="inlineStr">
@@ -5803,7 +5803,7 @@
       <c r="AW35" t="inlineStr"/>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>2026-05-20T00:13:57+00:00</t>
+          <t>2026-05-20T00:48:39+00:00</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr">
@@ -5956,7 +5956,7 @@
       </c>
       <c r="AT36" t="inlineStr">
         <is>
-          <t>batch_164c8f2ccaa64eaf</t>
+          <t>batch_4e3853438a5d4f9c</t>
         </is>
       </c>
       <c r="AU36" t="inlineStr">
@@ -5972,7 +5972,7 @@
       <c r="AW36" t="inlineStr"/>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>2026-05-20T00:13:57+00:00</t>
+          <t>2026-05-20T00:48:39+00:00</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr">
@@ -6125,7 +6125,7 @@
       </c>
       <c r="AT37" t="inlineStr">
         <is>
-          <t>batch_164c8f2ccaa64eaf</t>
+          <t>batch_4e3853438a5d4f9c</t>
         </is>
       </c>
       <c r="AU37" t="inlineStr">
@@ -6141,7 +6141,7 @@
       <c r="AW37" t="inlineStr"/>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>2026-05-20T00:13:57+00:00</t>
+          <t>2026-05-20T00:48:39+00:00</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr">
@@ -6294,7 +6294,7 @@
       </c>
       <c r="AT38" t="inlineStr">
         <is>
-          <t>batch_164c8f2ccaa64eaf</t>
+          <t>batch_4e3853438a5d4f9c</t>
         </is>
       </c>
       <c r="AU38" t="inlineStr">
@@ -6310,7 +6310,7 @@
       <c r="AW38" t="inlineStr"/>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>2026-05-20T00:13:57+00:00</t>
+          <t>2026-05-20T00:48:39+00:00</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr">
@@ -6463,7 +6463,7 @@
       </c>
       <c r="AT39" t="inlineStr">
         <is>
-          <t>batch_164c8f2ccaa64eaf</t>
+          <t>batch_4e3853438a5d4f9c</t>
         </is>
       </c>
       <c r="AU39" t="inlineStr">
@@ -6479,7 +6479,7 @@
       <c r="AW39" t="inlineStr"/>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>2026-05-20T00:13:57+00:00</t>
+          <t>2026-05-20T00:48:39+00:00</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr">
@@ -6632,7 +6632,7 @@
       </c>
       <c r="AT40" t="inlineStr">
         <is>
-          <t>batch_164c8f2ccaa64eaf</t>
+          <t>batch_4e3853438a5d4f9c</t>
         </is>
       </c>
       <c r="AU40" t="inlineStr">
@@ -6648,7 +6648,7 @@
       <c r="AW40" t="inlineStr"/>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>2026-05-20T00:13:57+00:00</t>
+          <t>2026-05-20T00:48:39+00:00</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr">
@@ -6801,7 +6801,7 @@
       </c>
       <c r="AT41" t="inlineStr">
         <is>
-          <t>batch_164c8f2ccaa64eaf</t>
+          <t>batch_4e3853438a5d4f9c</t>
         </is>
       </c>
       <c r="AU41" t="inlineStr">
@@ -6817,7 +6817,7 @@
       <c r="AW41" t="inlineStr"/>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>2026-05-20T00:13:57+00:00</t>
+          <t>2026-05-20T00:48:39+00:00</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr">
@@ -6970,7 +6970,7 @@
       </c>
       <c r="AT42" t="inlineStr">
         <is>
-          <t>batch_164c8f2ccaa64eaf</t>
+          <t>batch_4e3853438a5d4f9c</t>
         </is>
       </c>
       <c r="AU42" t="inlineStr">
@@ -6986,7 +6986,7 @@
       <c r="AW42" t="inlineStr"/>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>2026-05-20T00:13:57+00:00</t>
+          <t>2026-05-20T00:48:39+00:00</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr">
@@ -7139,7 +7139,7 @@
       </c>
       <c r="AT43" t="inlineStr">
         <is>
-          <t>batch_164c8f2ccaa64eaf</t>
+          <t>batch_4e3853438a5d4f9c</t>
         </is>
       </c>
       <c r="AU43" t="inlineStr">
@@ -7155,7 +7155,7 @@
       <c r="AW43" t="inlineStr"/>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>2026-05-20T00:13:57+00:00</t>
+          <t>2026-05-20T00:48:39+00:00</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr">
@@ -7308,7 +7308,7 @@
       </c>
       <c r="AT44" t="inlineStr">
         <is>
-          <t>batch_164c8f2ccaa64eaf</t>
+          <t>batch_4e3853438a5d4f9c</t>
         </is>
       </c>
       <c r="AU44" t="inlineStr">
@@ -7324,7 +7324,7 @@
       <c r="AW44" t="inlineStr"/>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>2026-05-20T00:13:57+00:00</t>
+          <t>2026-05-20T00:48:39+00:00</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr">
@@ -7477,7 +7477,7 @@
       </c>
       <c r="AT45" t="inlineStr">
         <is>
-          <t>batch_164c8f2ccaa64eaf</t>
+          <t>batch_4e3853438a5d4f9c</t>
         </is>
       </c>
       <c r="AU45" t="inlineStr">
@@ -7493,7 +7493,7 @@
       <c r="AW45" t="inlineStr"/>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>2026-05-20T00:13:57+00:00</t>
+          <t>2026-05-20T00:48:39+00:00</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr">
@@ -7646,7 +7646,7 @@
       </c>
       <c r="AT46" t="inlineStr">
         <is>
-          <t>batch_164c8f2ccaa64eaf</t>
+          <t>batch_4e3853438a5d4f9c</t>
         </is>
       </c>
       <c r="AU46" t="inlineStr">
@@ -7662,7 +7662,7 @@
       <c r="AW46" t="inlineStr"/>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>2026-05-20T00:13:57+00:00</t>
+          <t>2026-05-20T00:48:39+00:00</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr">
@@ -7815,7 +7815,7 @@
       </c>
       <c r="AT47" t="inlineStr">
         <is>
-          <t>batch_164c8f2ccaa64eaf</t>
+          <t>batch_4e3853438a5d4f9c</t>
         </is>
       </c>
       <c r="AU47" t="inlineStr">
@@ -7831,7 +7831,7 @@
       <c r="AW47" t="inlineStr"/>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>2026-05-20T00:13:57+00:00</t>
+          <t>2026-05-20T00:48:39+00:00</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr">
@@ -7984,7 +7984,7 @@
       </c>
       <c r="AT48" t="inlineStr">
         <is>
-          <t>batch_164c8f2ccaa64eaf</t>
+          <t>batch_4e3853438a5d4f9c</t>
         </is>
       </c>
       <c r="AU48" t="inlineStr">
@@ -8000,7 +8000,7 @@
       <c r="AW48" t="inlineStr"/>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>2026-05-20T00:13:57+00:00</t>
+          <t>2026-05-20T00:48:39+00:00</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr">
@@ -8153,7 +8153,7 @@
       </c>
       <c r="AT49" t="inlineStr">
         <is>
-          <t>batch_164c8f2ccaa64eaf</t>
+          <t>batch_4e3853438a5d4f9c</t>
         </is>
       </c>
       <c r="AU49" t="inlineStr">
@@ -8169,7 +8169,7 @@
       <c r="AW49" t="inlineStr"/>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>2026-05-20T00:13:57+00:00</t>
+          <t>2026-05-20T00:48:39+00:00</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr">
@@ -8322,7 +8322,7 @@
       </c>
       <c r="AT50" t="inlineStr">
         <is>
-          <t>batch_164c8f2ccaa64eaf</t>
+          <t>batch_4e3853438a5d4f9c</t>
         </is>
       </c>
       <c r="AU50" t="inlineStr">
@@ -8338,7 +8338,7 @@
       <c r="AW50" t="inlineStr"/>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>2026-05-20T00:13:57+00:00</t>
+          <t>2026-05-20T00:48:39+00:00</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr">
@@ -8491,7 +8491,7 @@
       </c>
       <c r="AT51" t="inlineStr">
         <is>
-          <t>batch_164c8f2ccaa64eaf</t>
+          <t>batch_4e3853438a5d4f9c</t>
         </is>
       </c>
       <c r="AU51" t="inlineStr">
@@ -8507,7 +8507,7 @@
       <c r="AW51" t="inlineStr"/>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>2026-05-20T00:13:57+00:00</t>
+          <t>2026-05-20T00:48:39+00:00</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr">
@@ -8660,7 +8660,7 @@
       </c>
       <c r="AT52" t="inlineStr">
         <is>
-          <t>batch_164c8f2ccaa64eaf</t>
+          <t>batch_4e3853438a5d4f9c</t>
         </is>
       </c>
       <c r="AU52" t="inlineStr">
@@ -8676,7 +8676,7 @@
       <c r="AW52" t="inlineStr"/>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>2026-05-20T00:13:57+00:00</t>
+          <t>2026-05-20T00:48:39+00:00</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr">
@@ -8829,7 +8829,7 @@
       </c>
       <c r="AT53" t="inlineStr">
         <is>
-          <t>batch_164c8f2ccaa64eaf</t>
+          <t>batch_4e3853438a5d4f9c</t>
         </is>
       </c>
       <c r="AU53" t="inlineStr">
@@ -8845,7 +8845,7 @@
       <c r="AW53" t="inlineStr"/>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>2026-05-20T00:13:57+00:00</t>
+          <t>2026-05-20T00:48:39+00:00</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr">
@@ -8998,7 +8998,7 @@
       </c>
       <c r="AT54" t="inlineStr">
         <is>
-          <t>batch_164c8f2ccaa64eaf</t>
+          <t>batch_4e3853438a5d4f9c</t>
         </is>
       </c>
       <c r="AU54" t="inlineStr">
@@ -9014,7 +9014,7 @@
       <c r="AW54" t="inlineStr"/>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>2026-05-20T00:13:57+00:00</t>
+          <t>2026-05-20T00:48:39+00:00</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr">
@@ -9167,7 +9167,7 @@
       </c>
       <c r="AT55" t="inlineStr">
         <is>
-          <t>batch_164c8f2ccaa64eaf</t>
+          <t>batch_4e3853438a5d4f9c</t>
         </is>
       </c>
       <c r="AU55" t="inlineStr">
@@ -9183,7 +9183,7 @@
       <c r="AW55" t="inlineStr"/>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>2026-05-20T00:13:57+00:00</t>
+          <t>2026-05-20T00:48:39+00:00</t>
         </is>
       </c>
       <c r="AY55" t="inlineStr">
@@ -9336,7 +9336,7 @@
       </c>
       <c r="AT56" t="inlineStr">
         <is>
-          <t>batch_164c8f2ccaa64eaf</t>
+          <t>batch_4e3853438a5d4f9c</t>
         </is>
       </c>
       <c r="AU56" t="inlineStr">
@@ -9352,7 +9352,7 @@
       <c r="AW56" t="inlineStr"/>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>2026-05-20T00:13:57+00:00</t>
+          <t>2026-05-20T00:48:39+00:00</t>
         </is>
       </c>
       <c r="AY56" t="inlineStr">
@@ -9505,7 +9505,7 @@
       </c>
       <c r="AT57" t="inlineStr">
         <is>
-          <t>batch_164c8f2ccaa64eaf</t>
+          <t>batch_4e3853438a5d4f9c</t>
         </is>
       </c>
       <c r="AU57" t="inlineStr">
@@ -9521,7 +9521,7 @@
       <c r="AW57" t="inlineStr"/>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>2026-05-20T00:13:57+00:00</t>
+          <t>2026-05-20T00:48:39+00:00</t>
         </is>
       </c>
       <c r="AY57" t="inlineStr">
@@ -9674,7 +9674,7 @@
       </c>
       <c r="AT58" t="inlineStr">
         <is>
-          <t>batch_164c8f2ccaa64eaf</t>
+          <t>batch_4e3853438a5d4f9c</t>
         </is>
       </c>
       <c r="AU58" t="inlineStr">
@@ -9690,7 +9690,7 @@
       <c r="AW58" t="inlineStr"/>
       <c r="AX58" t="inlineStr">
         <is>
-          <t>2026-05-20T00:13:57+00:00</t>
+          <t>2026-05-20T00:48:39+00:00</t>
         </is>
       </c>
       <c r="AY58" t="inlineStr">
@@ -9843,7 +9843,7 @@
       </c>
       <c r="AT59" t="inlineStr">
         <is>
-          <t>batch_164c8f2ccaa64eaf</t>
+          <t>batch_4e3853438a5d4f9c</t>
         </is>
       </c>
       <c r="AU59" t="inlineStr">
@@ -9859,7 +9859,7 @@
       <c r="AW59" t="inlineStr"/>
       <c r="AX59" t="inlineStr">
         <is>
-          <t>2026-05-20T00:13:57+00:00</t>
+          <t>2026-05-20T00:48:39+00:00</t>
         </is>
       </c>
       <c r="AY59" t="inlineStr">
@@ -10012,7 +10012,7 @@
       </c>
       <c r="AT60" t="inlineStr">
         <is>
-          <t>batch_164c8f2ccaa64eaf</t>
+          <t>batch_4e3853438a5d4f9c</t>
         </is>
       </c>
       <c r="AU60" t="inlineStr">
@@ -10028,7 +10028,7 @@
       <c r="AW60" t="inlineStr"/>
       <c r="AX60" t="inlineStr">
         <is>
-          <t>2026-05-20T00:13:57+00:00</t>
+          <t>2026-05-20T00:48:39+00:00</t>
         </is>
       </c>
       <c r="AY60" t="inlineStr">
@@ -10181,7 +10181,7 @@
       </c>
       <c r="AT61" t="inlineStr">
         <is>
-          <t>batch_164c8f2ccaa64eaf</t>
+          <t>batch_4e3853438a5d4f9c</t>
         </is>
       </c>
       <c r="AU61" t="inlineStr">
@@ -10197,7 +10197,7 @@
       <c r="AW61" t="inlineStr"/>
       <c r="AX61" t="inlineStr">
         <is>
-          <t>2026-05-20T00:13:57+00:00</t>
+          <t>2026-05-20T00:48:39+00:00</t>
         </is>
       </c>
       <c r="AY61" t="inlineStr">
@@ -10350,7 +10350,7 @@
       </c>
       <c r="AT62" t="inlineStr">
         <is>
-          <t>batch_164c8f2ccaa64eaf</t>
+          <t>batch_4e3853438a5d4f9c</t>
         </is>
       </c>
       <c r="AU62" t="inlineStr">
@@ -10366,7 +10366,7 @@
       <c r="AW62" t="inlineStr"/>
       <c r="AX62" t="inlineStr">
         <is>
-          <t>2026-05-20T00:13:57+00:00</t>
+          <t>2026-05-20T00:48:39+00:00</t>
         </is>
       </c>
       <c r="AY62" t="inlineStr">
@@ -10519,7 +10519,7 @@
       </c>
       <c r="AT63" t="inlineStr">
         <is>
-          <t>batch_164c8f2ccaa64eaf</t>
+          <t>batch_4e3853438a5d4f9c</t>
         </is>
       </c>
       <c r="AU63" t="inlineStr">
@@ -10535,7 +10535,7 @@
       <c r="AW63" t="inlineStr"/>
       <c r="AX63" t="inlineStr">
         <is>
-          <t>2026-05-20T00:13:57+00:00</t>
+          <t>2026-05-20T00:48:39+00:00</t>
         </is>
       </c>
       <c r="AY63" t="inlineStr">
@@ -10688,7 +10688,7 @@
       </c>
       <c r="AT64" t="inlineStr">
         <is>
-          <t>batch_164c8f2ccaa64eaf</t>
+          <t>batch_4e3853438a5d4f9c</t>
         </is>
       </c>
       <c r="AU64" t="inlineStr">
@@ -10704,7 +10704,7 @@
       <c r="AW64" t="inlineStr"/>
       <c r="AX64" t="inlineStr">
         <is>
-          <t>2026-05-20T00:13:57+00:00</t>
+          <t>2026-05-20T00:48:39+00:00</t>
         </is>
       </c>
       <c r="AY64" t="inlineStr">
@@ -10857,7 +10857,7 @@
       </c>
       <c r="AT65" t="inlineStr">
         <is>
-          <t>batch_164c8f2ccaa64eaf</t>
+          <t>batch_4e3853438a5d4f9c</t>
         </is>
       </c>
       <c r="AU65" t="inlineStr">
@@ -10873,7 +10873,7 @@
       <c r="AW65" t="inlineStr"/>
       <c r="AX65" t="inlineStr">
         <is>
-          <t>2026-05-20T00:13:57+00:00</t>
+          <t>2026-05-20T00:48:39+00:00</t>
         </is>
       </c>
       <c r="AY65" t="inlineStr">
@@ -11026,7 +11026,7 @@
       </c>
       <c r="AT66" t="inlineStr">
         <is>
-          <t>batch_164c8f2ccaa64eaf</t>
+          <t>batch_4e3853438a5d4f9c</t>
         </is>
       </c>
       <c r="AU66" t="inlineStr">
@@ -11042,7 +11042,7 @@
       <c r="AW66" t="inlineStr"/>
       <c r="AX66" t="inlineStr">
         <is>
-          <t>2026-05-20T00:13:57+00:00</t>
+          <t>2026-05-20T00:48:39+00:00</t>
         </is>
       </c>
       <c r="AY66" t="inlineStr">
@@ -11195,7 +11195,7 @@
       </c>
       <c r="AT67" t="inlineStr">
         <is>
-          <t>batch_164c8f2ccaa64eaf</t>
+          <t>batch_4e3853438a5d4f9c</t>
         </is>
       </c>
       <c r="AU67" t="inlineStr">
@@ -11211,7 +11211,7 @@
       <c r="AW67" t="inlineStr"/>
       <c r="AX67" t="inlineStr">
         <is>
-          <t>2026-05-20T00:13:57+00:00</t>
+          <t>2026-05-20T00:48:39+00:00</t>
         </is>
       </c>
       <c r="AY67" t="inlineStr">
@@ -11364,7 +11364,7 @@
       </c>
       <c r="AT68" t="inlineStr">
         <is>
-          <t>batch_164c8f2ccaa64eaf</t>
+          <t>batch_4e3853438a5d4f9c</t>
         </is>
       </c>
       <c r="AU68" t="inlineStr">
@@ -11380,7 +11380,7 @@
       <c r="AW68" t="inlineStr"/>
       <c r="AX68" t="inlineStr">
         <is>
-          <t>2026-05-20T00:13:57+00:00</t>
+          <t>2026-05-20T00:48:39+00:00</t>
         </is>
       </c>
       <c r="AY68" t="inlineStr">
@@ -11533,7 +11533,7 @@
       </c>
       <c r="AT69" t="inlineStr">
         <is>
-          <t>batch_164c8f2ccaa64eaf</t>
+          <t>batch_4e3853438a5d4f9c</t>
         </is>
       </c>
       <c r="AU69" t="inlineStr">
@@ -11549,7 +11549,7 @@
       <c r="AW69" t="inlineStr"/>
       <c r="AX69" t="inlineStr">
         <is>
-          <t>2026-05-20T00:13:57+00:00</t>
+          <t>2026-05-20T00:48:39+00:00</t>
         </is>
       </c>
       <c r="AY69" t="inlineStr">
@@ -11702,7 +11702,7 @@
       </c>
       <c r="AT70" t="inlineStr">
         <is>
-          <t>batch_164c8f2ccaa64eaf</t>
+          <t>batch_4e3853438a5d4f9c</t>
         </is>
       </c>
       <c r="AU70" t="inlineStr">
@@ -11718,7 +11718,7 @@
       <c r="AW70" t="inlineStr"/>
       <c r="AX70" t="inlineStr">
         <is>
-          <t>2026-05-20T00:13:57+00:00</t>
+          <t>2026-05-20T00:48:39+00:00</t>
         </is>
       </c>
       <c r="AY70" t="inlineStr">
@@ -11871,7 +11871,7 @@
       </c>
       <c r="AT71" t="inlineStr">
         <is>
-          <t>batch_164c8f2ccaa64eaf</t>
+          <t>batch_4e3853438a5d4f9c</t>
         </is>
       </c>
       <c r="AU71" t="inlineStr">
@@ -11887,7 +11887,7 @@
       <c r="AW71" t="inlineStr"/>
       <c r="AX71" t="inlineStr">
         <is>
-          <t>2026-05-20T00:13:57+00:00</t>
+          <t>2026-05-20T00:48:39+00:00</t>
         </is>
       </c>
       <c r="AY71" t="inlineStr">
@@ -12040,7 +12040,7 @@
       </c>
       <c r="AT72" t="inlineStr">
         <is>
-          <t>batch_164c8f2ccaa64eaf</t>
+          <t>batch_4e3853438a5d4f9c</t>
         </is>
       </c>
       <c r="AU72" t="inlineStr">
@@ -12056,7 +12056,7 @@
       <c r="AW72" t="inlineStr"/>
       <c r="AX72" t="inlineStr">
         <is>
-          <t>2026-05-20T00:13:57+00:00</t>
+          <t>2026-05-20T00:48:39+00:00</t>
         </is>
       </c>
       <c r="AY72" t="inlineStr">
@@ -12209,7 +12209,7 @@
       </c>
       <c r="AT73" t="inlineStr">
         <is>
-          <t>batch_164c8f2ccaa64eaf</t>
+          <t>batch_4e3853438a5d4f9c</t>
         </is>
       </c>
       <c r="AU73" t="inlineStr">
@@ -12225,7 +12225,7 @@
       <c r="AW73" t="inlineStr"/>
       <c r="AX73" t="inlineStr">
         <is>
-          <t>2026-05-20T00:13:57+00:00</t>
+          <t>2026-05-20T00:48:39+00:00</t>
         </is>
       </c>
       <c r="AY73" t="inlineStr">
@@ -12378,7 +12378,7 @@
       </c>
       <c r="AT74" t="inlineStr">
         <is>
-          <t>batch_164c8f2ccaa64eaf</t>
+          <t>batch_4e3853438a5d4f9c</t>
         </is>
       </c>
       <c r="AU74" t="inlineStr">
@@ -12394,7 +12394,7 @@
       <c r="AW74" t="inlineStr"/>
       <c r="AX74" t="inlineStr">
         <is>
-          <t>2026-05-20T00:13:57+00:00</t>
+          <t>2026-05-20T00:48:39+00:00</t>
         </is>
       </c>
       <c r="AY74" t="inlineStr">
@@ -12547,7 +12547,7 @@
       </c>
       <c r="AT75" t="inlineStr">
         <is>
-          <t>batch_164c8f2ccaa64eaf</t>
+          <t>batch_4e3853438a5d4f9c</t>
         </is>
       </c>
       <c r="AU75" t="inlineStr">
@@ -12563,7 +12563,7 @@
       <c r="AW75" t="inlineStr"/>
       <c r="AX75" t="inlineStr">
         <is>
-          <t>2026-05-20T00:13:57+00:00</t>
+          <t>2026-05-20T00:48:39+00:00</t>
         </is>
       </c>
       <c r="AY75" t="inlineStr">
@@ -12716,7 +12716,7 @@
       </c>
       <c r="AT76" t="inlineStr">
         <is>
-          <t>batch_164c8f2ccaa64eaf</t>
+          <t>batch_4e3853438a5d4f9c</t>
         </is>
       </c>
       <c r="AU76" t="inlineStr">
@@ -12732,7 +12732,7 @@
       <c r="AW76" t="inlineStr"/>
       <c r="AX76" t="inlineStr">
         <is>
-          <t>2026-05-20T00:13:57+00:00</t>
+          <t>2026-05-20T00:48:39+00:00</t>
         </is>
       </c>
       <c r="AY76" t="inlineStr">
@@ -12885,7 +12885,7 @@
       </c>
       <c r="AT77" t="inlineStr">
         <is>
-          <t>batch_164c8f2ccaa64eaf</t>
+          <t>batch_4e3853438a5d4f9c</t>
         </is>
       </c>
       <c r="AU77" t="inlineStr">
@@ -12901,7 +12901,7 @@
       <c r="AW77" t="inlineStr"/>
       <c r="AX77" t="inlineStr">
         <is>
-          <t>2026-05-20T00:13:57+00:00</t>
+          <t>2026-05-20T00:48:39+00:00</t>
         </is>
       </c>
       <c r="AY77" t="inlineStr">
@@ -13054,7 +13054,7 @@
       </c>
       <c r="AT78" t="inlineStr">
         <is>
-          <t>batch_164c8f2ccaa64eaf</t>
+          <t>batch_4e3853438a5d4f9c</t>
         </is>
       </c>
       <c r="AU78" t="inlineStr">
@@ -13070,7 +13070,7 @@
       <c r="AW78" t="inlineStr"/>
       <c r="AX78" t="inlineStr">
         <is>
-          <t>2026-05-20T00:13:57+00:00</t>
+          <t>2026-05-20T00:48:39+00:00</t>
         </is>
       </c>
       <c r="AY78" t="inlineStr">
@@ -13223,7 +13223,7 @@
       </c>
       <c r="AT79" t="inlineStr">
         <is>
-          <t>batch_164c8f2ccaa64eaf</t>
+          <t>batch_4e3853438a5d4f9c</t>
         </is>
       </c>
       <c r="AU79" t="inlineStr">
@@ -13239,7 +13239,7 @@
       <c r="AW79" t="inlineStr"/>
       <c r="AX79" t="inlineStr">
         <is>
-          <t>2026-05-20T00:13:57+00:00</t>
+          <t>2026-05-20T00:48:39+00:00</t>
         </is>
       </c>
       <c r="AY79" t="inlineStr">
@@ -13392,7 +13392,7 @@
       </c>
       <c r="AT80" t="inlineStr">
         <is>
-          <t>batch_164c8f2ccaa64eaf</t>
+          <t>batch_4e3853438a5d4f9c</t>
         </is>
       </c>
       <c r="AU80" t="inlineStr">
@@ -13408,7 +13408,7 @@
       <c r="AW80" t="inlineStr"/>
       <c r="AX80" t="inlineStr">
         <is>
-          <t>2026-05-20T00:13:57+00:00</t>
+          <t>2026-05-20T00:48:39+00:00</t>
         </is>
       </c>
       <c r="AY80" t="inlineStr">
@@ -13561,7 +13561,7 @@
       </c>
       <c r="AT81" t="inlineStr">
         <is>
-          <t>batch_164c8f2ccaa64eaf</t>
+          <t>batch_4e3853438a5d4f9c</t>
         </is>
       </c>
       <c r="AU81" t="inlineStr">
@@ -13577,7 +13577,7 @@
       <c r="AW81" t="inlineStr"/>
       <c r="AX81" t="inlineStr">
         <is>
-          <t>2026-05-20T00:13:57+00:00</t>
+          <t>2026-05-20T00:48:39+00:00</t>
         </is>
       </c>
       <c r="AY81" t="inlineStr">
@@ -13730,7 +13730,7 @@
       </c>
       <c r="AT82" t="inlineStr">
         <is>
-          <t>batch_164c8f2ccaa64eaf</t>
+          <t>batch_4e3853438a5d4f9c</t>
         </is>
       </c>
       <c r="AU82" t="inlineStr">
@@ -13746,7 +13746,7 @@
       <c r="AW82" t="inlineStr"/>
       <c r="AX82" t="inlineStr">
         <is>
-          <t>2026-05-20T00:13:57+00:00</t>
+          <t>2026-05-20T00:48:39+00:00</t>
         </is>
       </c>
       <c r="AY82" t="inlineStr">
@@ -13899,7 +13899,7 @@
       </c>
       <c r="AT83" t="inlineStr">
         <is>
-          <t>batch_164c8f2ccaa64eaf</t>
+          <t>batch_4e3853438a5d4f9c</t>
         </is>
       </c>
       <c r="AU83" t="inlineStr">
@@ -13915,7 +13915,7 @@
       <c r="AW83" t="inlineStr"/>
       <c r="AX83" t="inlineStr">
         <is>
-          <t>2026-05-20T00:13:57+00:00</t>
+          <t>2026-05-20T00:48:39+00:00</t>
         </is>
       </c>
       <c r="AY83" t="inlineStr">
@@ -14068,7 +14068,7 @@
       </c>
       <c r="AT84" t="inlineStr">
         <is>
-          <t>batch_164c8f2ccaa64eaf</t>
+          <t>batch_4e3853438a5d4f9c</t>
         </is>
       </c>
       <c r="AU84" t="inlineStr">
@@ -14084,7 +14084,7 @@
       <c r="AW84" t="inlineStr"/>
       <c r="AX84" t="inlineStr">
         <is>
-          <t>2026-05-20T00:13:57+00:00</t>
+          <t>2026-05-20T00:48:39+00:00</t>
         </is>
       </c>
       <c r="AY84" t="inlineStr">
@@ -14237,7 +14237,7 @@
       </c>
       <c r="AT85" t="inlineStr">
         <is>
-          <t>batch_164c8f2ccaa64eaf</t>
+          <t>batch_4e3853438a5d4f9c</t>
         </is>
       </c>
       <c r="AU85" t="inlineStr">
@@ -14253,7 +14253,7 @@
       <c r="AW85" t="inlineStr"/>
       <c r="AX85" t="inlineStr">
         <is>
-          <t>2026-05-20T00:13:57+00:00</t>
+          <t>2026-05-20T00:48:39+00:00</t>
         </is>
       </c>
       <c r="AY85" t="inlineStr">
@@ -14406,7 +14406,7 @@
       </c>
       <c r="AT86" t="inlineStr">
         <is>
-          <t>batch_164c8f2ccaa64eaf</t>
+          <t>batch_4e3853438a5d4f9c</t>
         </is>
       </c>
       <c r="AU86" t="inlineStr">
@@ -14422,7 +14422,7 @@
       <c r="AW86" t="inlineStr"/>
       <c r="AX86" t="inlineStr">
         <is>
-          <t>2026-05-20T00:13:57+00:00</t>
+          <t>2026-05-20T00:48:39+00:00</t>
         </is>
       </c>
       <c r="AY86" t="inlineStr">
@@ -14575,7 +14575,7 @@
       </c>
       <c r="AT87" t="inlineStr">
         <is>
-          <t>batch_164c8f2ccaa64eaf</t>
+          <t>batch_4e3853438a5d4f9c</t>
         </is>
       </c>
       <c r="AU87" t="inlineStr">
@@ -14591,7 +14591,7 @@
       <c r="AW87" t="inlineStr"/>
       <c r="AX87" t="inlineStr">
         <is>
-          <t>2026-05-20T00:13:57+00:00</t>
+          <t>2026-05-20T00:48:39+00:00</t>
         </is>
       </c>
       <c r="AY87" t="inlineStr">
@@ -14744,7 +14744,7 @@
       </c>
       <c r="AT88" t="inlineStr">
         <is>
-          <t>batch_164c8f2ccaa64eaf</t>
+          <t>batch_4e3853438a5d4f9c</t>
         </is>
       </c>
       <c r="AU88" t="inlineStr">
@@ -14760,7 +14760,7 @@
       <c r="AW88" t="inlineStr"/>
       <c r="AX88" t="inlineStr">
         <is>
-          <t>2026-05-20T00:13:57+00:00</t>
+          <t>2026-05-20T00:48:39+00:00</t>
         </is>
       </c>
       <c r="AY88" t="inlineStr">
@@ -14913,7 +14913,7 @@
       </c>
       <c r="AT89" t="inlineStr">
         <is>
-          <t>batch_164c8f2ccaa64eaf</t>
+          <t>batch_4e3853438a5d4f9c</t>
         </is>
       </c>
       <c r="AU89" t="inlineStr">
@@ -14929,7 +14929,7 @@
       <c r="AW89" t="inlineStr"/>
       <c r="AX89" t="inlineStr">
         <is>
-          <t>2026-05-20T00:13:57+00:00</t>
+          <t>2026-05-20T00:48:39+00:00</t>
         </is>
       </c>
       <c r="AY89" t="inlineStr">
@@ -15082,7 +15082,7 @@
       </c>
       <c r="AT90" t="inlineStr">
         <is>
-          <t>batch_164c8f2ccaa64eaf</t>
+          <t>batch_4e3853438a5d4f9c</t>
         </is>
       </c>
       <c r="AU90" t="inlineStr">
@@ -15098,7 +15098,7 @@
       <c r="AW90" t="inlineStr"/>
       <c r="AX90" t="inlineStr">
         <is>
-          <t>2026-05-20T00:13:57+00:00</t>
+          <t>2026-05-20T00:48:39+00:00</t>
         </is>
       </c>
       <c r="AY90" t="inlineStr">
@@ -15251,7 +15251,7 @@
       </c>
       <c r="AT91" t="inlineStr">
         <is>
-          <t>batch_164c8f2ccaa64eaf</t>
+          <t>batch_4e3853438a5d4f9c</t>
         </is>
       </c>
       <c r="AU91" t="inlineStr">
@@ -15267,7 +15267,7 @@
       <c r="AW91" t="inlineStr"/>
       <c r="AX91" t="inlineStr">
         <is>
-          <t>2026-05-20T00:13:57+00:00</t>
+          <t>2026-05-20T00:48:39+00:00</t>
         </is>
       </c>
       <c r="AY91" t="inlineStr">
@@ -15420,7 +15420,7 @@
       </c>
       <c r="AT92" t="inlineStr">
         <is>
-          <t>batch_164c8f2ccaa64eaf</t>
+          <t>batch_4e3853438a5d4f9c</t>
         </is>
       </c>
       <c r="AU92" t="inlineStr">
@@ -15436,7 +15436,7 @@
       <c r="AW92" t="inlineStr"/>
       <c r="AX92" t="inlineStr">
         <is>
-          <t>2026-05-20T00:13:57+00:00</t>
+          <t>2026-05-20T00:48:39+00:00</t>
         </is>
       </c>
       <c r="AY92" t="inlineStr">
@@ -15589,7 +15589,7 @@
       </c>
       <c r="AT93" t="inlineStr">
         <is>
-          <t>batch_164c8f2ccaa64eaf</t>
+          <t>batch_4e3853438a5d4f9c</t>
         </is>
       </c>
       <c r="AU93" t="inlineStr">
@@ -15605,7 +15605,7 @@
       <c r="AW93" t="inlineStr"/>
       <c r="AX93" t="inlineStr">
         <is>
-          <t>2026-05-20T00:13:57+00:00</t>
+          <t>2026-05-20T00:48:39+00:00</t>
         </is>
       </c>
       <c r="AY93" t="inlineStr">
@@ -15758,7 +15758,7 @@
       </c>
       <c r="AT94" t="inlineStr">
         <is>
-          <t>batch_164c8f2ccaa64eaf</t>
+          <t>batch_4e3853438a5d4f9c</t>
         </is>
       </c>
       <c r="AU94" t="inlineStr">
@@ -15774,7 +15774,7 @@
       <c r="AW94" t="inlineStr"/>
       <c r="AX94" t="inlineStr">
         <is>
-          <t>2026-05-20T00:13:57+00:00</t>
+          <t>2026-05-20T00:48:39+00:00</t>
         </is>
       </c>
       <c r="AY94" t="inlineStr">
@@ -15927,7 +15927,7 @@
       </c>
       <c r="AT95" t="inlineStr">
         <is>
-          <t>batch_164c8f2ccaa64eaf</t>
+          <t>batch_4e3853438a5d4f9c</t>
         </is>
       </c>
       <c r="AU95" t="inlineStr">
@@ -15943,7 +15943,7 @@
       <c r="AW95" t="inlineStr"/>
       <c r="AX95" t="inlineStr">
         <is>
-          <t>2026-05-20T00:13:57+00:00</t>
+          <t>2026-05-20T00:48:39+00:00</t>
         </is>
       </c>
       <c r="AY95" t="inlineStr">
@@ -16096,7 +16096,7 @@
       </c>
       <c r="AT96" t="inlineStr">
         <is>
-          <t>batch_164c8f2ccaa64eaf</t>
+          <t>batch_4e3853438a5d4f9c</t>
         </is>
       </c>
       <c r="AU96" t="inlineStr">
@@ -16112,7 +16112,7 @@
       <c r="AW96" t="inlineStr"/>
       <c r="AX96" t="inlineStr">
         <is>
-          <t>2026-05-20T00:13:57+00:00</t>
+          <t>2026-05-20T00:48:39+00:00</t>
         </is>
       </c>
       <c r="AY96" t="inlineStr">
@@ -16265,7 +16265,7 @@
       </c>
       <c r="AT97" t="inlineStr">
         <is>
-          <t>batch_164c8f2ccaa64eaf</t>
+          <t>batch_4e3853438a5d4f9c</t>
         </is>
       </c>
       <c r="AU97" t="inlineStr">
@@ -16281,7 +16281,7 @@
       <c r="AW97" t="inlineStr"/>
       <c r="AX97" t="inlineStr">
         <is>
-          <t>2026-05-20T00:13:57+00:00</t>
+          <t>2026-05-20T00:48:39+00:00</t>
         </is>
       </c>
       <c r="AY97" t="inlineStr">
@@ -16434,7 +16434,7 @@
       </c>
       <c r="AT98" t="inlineStr">
         <is>
-          <t>batch_164c8f2ccaa64eaf</t>
+          <t>batch_4e3853438a5d4f9c</t>
         </is>
       </c>
       <c r="AU98" t="inlineStr">
@@ -16450,7 +16450,7 @@
       <c r="AW98" t="inlineStr"/>
       <c r="AX98" t="inlineStr">
         <is>
-          <t>2026-05-20T00:13:57+00:00</t>
+          <t>2026-05-20T00:48:39+00:00</t>
         </is>
       </c>
       <c r="AY98" t="inlineStr">
@@ -16594,7 +16594,7 @@
       </c>
       <c r="AT99" t="inlineStr">
         <is>
-          <t>batch_164c8f2ccaa64eaf</t>
+          <t>batch_4e3853438a5d4f9c</t>
         </is>
       </c>
       <c r="AU99" t="inlineStr">
@@ -16610,7 +16610,7 @@
       <c r="AW99" t="inlineStr"/>
       <c r="AX99" t="inlineStr">
         <is>
-          <t>2026-05-20T00:13:57+00:00</t>
+          <t>2026-05-20T00:48:39+00:00</t>
         </is>
       </c>
       <c r="AY99" t="inlineStr">
@@ -16754,7 +16754,7 @@
       </c>
       <c r="AT100" t="inlineStr">
         <is>
-          <t>batch_164c8f2ccaa64eaf</t>
+          <t>batch_4e3853438a5d4f9c</t>
         </is>
       </c>
       <c r="AU100" t="inlineStr">
@@ -16770,7 +16770,7 @@
       <c r="AW100" t="inlineStr"/>
       <c r="AX100" t="inlineStr">
         <is>
-          <t>2026-05-20T00:13:57+00:00</t>
+          <t>2026-05-20T00:48:39+00:00</t>
         </is>
       </c>
       <c r="AY100" t="inlineStr">
@@ -16914,7 +16914,7 @@
       </c>
       <c r="AT101" t="inlineStr">
         <is>
-          <t>batch_164c8f2ccaa64eaf</t>
+          <t>batch_4e3853438a5d4f9c</t>
         </is>
       </c>
       <c r="AU101" t="inlineStr">
@@ -16930,7 +16930,7 @@
       <c r="AW101" t="inlineStr"/>
       <c r="AX101" t="inlineStr">
         <is>
-          <t>2026-05-20T00:13:57+00:00</t>
+          <t>2026-05-20T00:48:39+00:00</t>
         </is>
       </c>
       <c r="AY101" t="inlineStr">
@@ -17074,7 +17074,7 @@
       </c>
       <c r="AT102" t="inlineStr">
         <is>
-          <t>batch_164c8f2ccaa64eaf</t>
+          <t>batch_4e3853438a5d4f9c</t>
         </is>
       </c>
       <c r="AU102" t="inlineStr">
@@ -17090,7 +17090,7 @@
       <c r="AW102" t="inlineStr"/>
       <c r="AX102" t="inlineStr">
         <is>
-          <t>2026-05-20T00:13:57+00:00</t>
+          <t>2026-05-20T00:48:39+00:00</t>
         </is>
       </c>
       <c r="AY102" t="inlineStr">
@@ -17234,7 +17234,7 @@
       </c>
       <c r="AT103" t="inlineStr">
         <is>
-          <t>batch_164c8f2ccaa64eaf</t>
+          <t>batch_4e3853438a5d4f9c</t>
         </is>
       </c>
       <c r="AU103" t="inlineStr">
@@ -17250,7 +17250,7 @@
       <c r="AW103" t="inlineStr"/>
       <c r="AX103" t="inlineStr">
         <is>
-          <t>2026-05-20T00:13:57+00:00</t>
+          <t>2026-05-20T00:48:39+00:00</t>
         </is>
       </c>
       <c r="AY103" t="inlineStr">
@@ -17394,7 +17394,7 @@
       </c>
       <c r="AT104" t="inlineStr">
         <is>
-          <t>batch_164c8f2ccaa64eaf</t>
+          <t>batch_4e3853438a5d4f9c</t>
         </is>
       </c>
       <c r="AU104" t="inlineStr">
@@ -17410,7 +17410,7 @@
       <c r="AW104" t="inlineStr"/>
       <c r="AX104" t="inlineStr">
         <is>
-          <t>2026-05-20T00:13:57+00:00</t>
+          <t>2026-05-20T00:48:39+00:00</t>
         </is>
       </c>
       <c r="AY104" t="inlineStr">
@@ -17563,7 +17563,7 @@
       </c>
       <c r="AT105" t="inlineStr">
         <is>
-          <t>batch_164c8f2ccaa64eaf</t>
+          <t>batch_4e3853438a5d4f9c</t>
         </is>
       </c>
       <c r="AU105" t="inlineStr">
@@ -17579,7 +17579,7 @@
       <c r="AW105" t="inlineStr"/>
       <c r="AX105" t="inlineStr">
         <is>
-          <t>2026-05-20T00:13:57+00:00</t>
+          <t>2026-05-20T00:48:39+00:00</t>
         </is>
       </c>
       <c r="AY105" t="inlineStr">
@@ -17720,7 +17720,7 @@
       </c>
       <c r="AT106" t="inlineStr">
         <is>
-          <t>batch_164c8f2ccaa64eaf</t>
+          <t>batch_4e3853438a5d4f9c</t>
         </is>
       </c>
       <c r="AU106" t="inlineStr">
@@ -17736,7 +17736,7 @@
       <c r="AW106" t="inlineStr"/>
       <c r="AX106" t="inlineStr">
         <is>
-          <t>2026-05-20T00:13:57+00:00</t>
+          <t>2026-05-20T00:48:39+00:00</t>
         </is>
       </c>
       <c r="AY106" t="inlineStr">
@@ -17877,7 +17877,7 @@
       </c>
       <c r="AT107" t="inlineStr">
         <is>
-          <t>batch_164c8f2ccaa64eaf</t>
+          <t>batch_4e3853438a5d4f9c</t>
         </is>
       </c>
       <c r="AU107" t="inlineStr">
@@ -17893,7 +17893,7 @@
       <c r="AW107" t="inlineStr"/>
       <c r="AX107" t="inlineStr">
         <is>
-          <t>2026-05-20T00:13:57+00:00</t>
+          <t>2026-05-20T00:48:39+00:00</t>
         </is>
       </c>
       <c r="AY107" t="inlineStr">
@@ -18034,7 +18034,7 @@
       </c>
       <c r="AT108" t="inlineStr">
         <is>
-          <t>batch_164c8f2ccaa64eaf</t>
+          <t>batch_4e3853438a5d4f9c</t>
         </is>
       </c>
       <c r="AU108" t="inlineStr">
@@ -18050,7 +18050,7 @@
       <c r="AW108" t="inlineStr"/>
       <c r="AX108" t="inlineStr">
         <is>
-          <t>2026-05-20T00:13:57+00:00</t>
+          <t>2026-05-20T00:48:39+00:00</t>
         </is>
       </c>
       <c r="AY108" t="inlineStr">
@@ -18194,7 +18194,7 @@
       </c>
       <c r="AT109" t="inlineStr">
         <is>
-          <t>batch_164c8f2ccaa64eaf</t>
+          <t>batch_4e3853438a5d4f9c</t>
         </is>
       </c>
       <c r="AU109" t="inlineStr">
@@ -18210,7 +18210,7 @@
       <c r="AW109" t="inlineStr"/>
       <c r="AX109" t="inlineStr">
         <is>
-          <t>2026-05-20T00:13:57+00:00</t>
+          <t>2026-05-20T00:48:39+00:00</t>
         </is>
       </c>
       <c r="AY109" t="inlineStr">
@@ -18354,7 +18354,7 @@
       </c>
       <c r="AT110" t="inlineStr">
         <is>
-          <t>batch_164c8f2ccaa64eaf</t>
+          <t>batch_4e3853438a5d4f9c</t>
         </is>
       </c>
       <c r="AU110" t="inlineStr">
@@ -18370,7 +18370,7 @@
       <c r="AW110" t="inlineStr"/>
       <c r="AX110" t="inlineStr">
         <is>
-          <t>2026-05-20T00:13:57+00:00</t>
+          <t>2026-05-20T00:48:39+00:00</t>
         </is>
       </c>
       <c r="AY110" t="inlineStr">
@@ -18514,7 +18514,7 @@
       </c>
       <c r="AT111" t="inlineStr">
         <is>
-          <t>batch_164c8f2ccaa64eaf</t>
+          <t>batch_4e3853438a5d4f9c</t>
         </is>
       </c>
       <c r="AU111" t="inlineStr">
@@ -18530,7 +18530,7 @@
       <c r="AW111" t="inlineStr"/>
       <c r="AX111" t="inlineStr">
         <is>
-          <t>2026-05-20T00:13:57+00:00</t>
+          <t>2026-05-20T00:48:39+00:00</t>
         </is>
       </c>
       <c r="AY111" t="inlineStr">
@@ -18674,7 +18674,7 @@
       </c>
       <c r="AT112" t="inlineStr">
         <is>
-          <t>batch_164c8f2ccaa64eaf</t>
+          <t>batch_4e3853438a5d4f9c</t>
         </is>
       </c>
       <c r="AU112" t="inlineStr">
@@ -18690,7 +18690,7 @@
       <c r="AW112" t="inlineStr"/>
       <c r="AX112" t="inlineStr">
         <is>
-          <t>2026-05-20T00:13:57+00:00</t>
+          <t>2026-05-20T00:48:39+00:00</t>
         </is>
       </c>
       <c r="AY112" t="inlineStr">
@@ -18834,7 +18834,7 @@
       </c>
       <c r="AT113" t="inlineStr">
         <is>
-          <t>batch_164c8f2ccaa64eaf</t>
+          <t>batch_4e3853438a5d4f9c</t>
         </is>
       </c>
       <c r="AU113" t="inlineStr">
@@ -18850,7 +18850,7 @@
       <c r="AW113" t="inlineStr"/>
       <c r="AX113" t="inlineStr">
         <is>
-          <t>2026-05-20T00:13:57+00:00</t>
+          <t>2026-05-20T00:48:39+00:00</t>
         </is>
       </c>
       <c r="AY113" t="inlineStr">
@@ -18994,7 +18994,7 @@
       </c>
       <c r="AT114" t="inlineStr">
         <is>
-          <t>batch_164c8f2ccaa64eaf</t>
+          <t>batch_4e3853438a5d4f9c</t>
         </is>
       </c>
       <c r="AU114" t="inlineStr">
@@ -19010,7 +19010,7 @@
       <c r="AW114" t="inlineStr"/>
       <c r="AX114" t="inlineStr">
         <is>
-          <t>2026-05-20T00:13:57+00:00</t>
+          <t>2026-05-20T00:48:39+00:00</t>
         </is>
       </c>
       <c r="AY114" t="inlineStr">
@@ -19154,7 +19154,7 @@
       </c>
       <c r="AT115" t="inlineStr">
         <is>
-          <t>batch_164c8f2ccaa64eaf</t>
+          <t>batch_4e3853438a5d4f9c</t>
         </is>
       </c>
       <c r="AU115" t="inlineStr">
@@ -19170,7 +19170,7 @@
       <c r="AW115" t="inlineStr"/>
       <c r="AX115" t="inlineStr">
         <is>
-          <t>2026-05-20T00:13:57+00:00</t>
+          <t>2026-05-20T00:48:39+00:00</t>
         </is>
       </c>
       <c r="AY115" t="inlineStr">
@@ -19314,7 +19314,7 @@
       </c>
       <c r="AT116" t="inlineStr">
         <is>
-          <t>batch_164c8f2ccaa64eaf</t>
+          <t>batch_4e3853438a5d4f9c</t>
         </is>
       </c>
       <c r="AU116" t="inlineStr">
@@ -19330,7 +19330,7 @@
       <c r="AW116" t="inlineStr"/>
       <c r="AX116" t="inlineStr">
         <is>
-          <t>2026-05-20T00:13:57+00:00</t>
+          <t>2026-05-20T00:48:39+00:00</t>
         </is>
       </c>
       <c r="AY116" t="inlineStr">
@@ -19474,7 +19474,7 @@
       </c>
       <c r="AT117" t="inlineStr">
         <is>
-          <t>batch_164c8f2ccaa64eaf</t>
+          <t>batch_4e3853438a5d4f9c</t>
         </is>
       </c>
       <c r="AU117" t="inlineStr">
@@ -19490,7 +19490,7 @@
       <c r="AW117" t="inlineStr"/>
       <c r="AX117" t="inlineStr">
         <is>
-          <t>2026-05-20T00:13:57+00:00</t>
+          <t>2026-05-20T00:48:39+00:00</t>
         </is>
       </c>
       <c r="AY117" t="inlineStr">
@@ -19634,7 +19634,7 @@
       </c>
       <c r="AT118" t="inlineStr">
         <is>
-          <t>batch_164c8f2ccaa64eaf</t>
+          <t>batch_4e3853438a5d4f9c</t>
         </is>
       </c>
       <c r="AU118" t="inlineStr">
@@ -19650,7 +19650,7 @@
       <c r="AW118" t="inlineStr"/>
       <c r="AX118" t="inlineStr">
         <is>
-          <t>2026-05-20T00:13:57+00:00</t>
+          <t>2026-05-20T00:48:39+00:00</t>
         </is>
       </c>
       <c r="AY118" t="inlineStr">
@@ -19794,7 +19794,7 @@
       </c>
       <c r="AT119" t="inlineStr">
         <is>
-          <t>batch_164c8f2ccaa64eaf</t>
+          <t>batch_4e3853438a5d4f9c</t>
         </is>
       </c>
       <c r="AU119" t="inlineStr">
@@ -19810,7 +19810,7 @@
       <c r="AW119" t="inlineStr"/>
       <c r="AX119" t="inlineStr">
         <is>
-          <t>2026-05-20T00:13:57+00:00</t>
+          <t>2026-05-20T00:48:39+00:00</t>
         </is>
       </c>
       <c r="AY119" t="inlineStr">
@@ -19954,7 +19954,7 @@
       </c>
       <c r="AT120" t="inlineStr">
         <is>
-          <t>batch_164c8f2ccaa64eaf</t>
+          <t>batch_4e3853438a5d4f9c</t>
         </is>
       </c>
       <c r="AU120" t="inlineStr">
@@ -19970,7 +19970,7 @@
       <c r="AW120" t="inlineStr"/>
       <c r="AX120" t="inlineStr">
         <is>
-          <t>2026-05-20T00:13:57+00:00</t>
+          <t>2026-05-20T00:48:39+00:00</t>
         </is>
       </c>
       <c r="AY120" t="inlineStr">
@@ -20114,7 +20114,7 @@
       </c>
       <c r="AT121" t="inlineStr">
         <is>
-          <t>batch_164c8f2ccaa64eaf</t>
+          <t>batch_4e3853438a5d4f9c</t>
         </is>
       </c>
       <c r="AU121" t="inlineStr">
@@ -20130,7 +20130,7 @@
       <c r="AW121" t="inlineStr"/>
       <c r="AX121" t="inlineStr">
         <is>
-          <t>2026-05-20T00:13:57+00:00</t>
+          <t>2026-05-20T00:48:39+00:00</t>
         </is>
       </c>
       <c r="AY121" t="inlineStr">
@@ -20274,7 +20274,7 @@
       </c>
       <c r="AT122" t="inlineStr">
         <is>
-          <t>batch_164c8f2ccaa64eaf</t>
+          <t>batch_4e3853438a5d4f9c</t>
         </is>
       </c>
       <c r="AU122" t="inlineStr">
@@ -20290,7 +20290,7 @@
       <c r="AW122" t="inlineStr"/>
       <c r="AX122" t="inlineStr">
         <is>
-          <t>2026-05-20T00:13:57+00:00</t>
+          <t>2026-05-20T00:48:39+00:00</t>
         </is>
       </c>
       <c r="AY122" t="inlineStr">
@@ -20434,7 +20434,7 @@
       </c>
       <c r="AT123" t="inlineStr">
         <is>
-          <t>batch_164c8f2ccaa64eaf</t>
+          <t>batch_4e3853438a5d4f9c</t>
         </is>
       </c>
       <c r="AU123" t="inlineStr">
@@ -20450,7 +20450,7 @@
       <c r="AW123" t="inlineStr"/>
       <c r="AX123" t="inlineStr">
         <is>
-          <t>2026-05-20T00:13:57+00:00</t>
+          <t>2026-05-20T00:48:39+00:00</t>
         </is>
       </c>
       <c r="AY123" t="inlineStr">
@@ -20594,7 +20594,7 @@
       </c>
       <c r="AT124" t="inlineStr">
         <is>
-          <t>batch_164c8f2ccaa64eaf</t>
+          <t>batch_4e3853438a5d4f9c</t>
         </is>
       </c>
       <c r="AU124" t="inlineStr">
@@ -20610,7 +20610,7 @@
       <c r="AW124" t="inlineStr"/>
       <c r="AX124" t="inlineStr">
         <is>
-          <t>2026-05-20T00:13:57+00:00</t>
+          <t>2026-05-20T00:48:39+00:00</t>
         </is>
       </c>
       <c r="AY124" t="inlineStr">
@@ -20754,7 +20754,7 @@
       </c>
       <c r="AT125" t="inlineStr">
         <is>
-          <t>batch_164c8f2ccaa64eaf</t>
+          <t>batch_4e3853438a5d4f9c</t>
         </is>
       </c>
       <c r="AU125" t="inlineStr">
@@ -20770,7 +20770,7 @@
       <c r="AW125" t="inlineStr"/>
       <c r="AX125" t="inlineStr">
         <is>
-          <t>2026-05-20T00:13:57+00:00</t>
+          <t>2026-05-20T00:48:39+00:00</t>
         </is>
       </c>
       <c r="AY125" t="inlineStr">
@@ -20914,7 +20914,7 @@
       </c>
       <c r="AT126" t="inlineStr">
         <is>
-          <t>batch_164c8f2ccaa64eaf</t>
+          <t>batch_4e3853438a5d4f9c</t>
         </is>
       </c>
       <c r="AU126" t="inlineStr">
@@ -20930,7 +20930,7 @@
       <c r="AW126" t="inlineStr"/>
       <c r="AX126" t="inlineStr">
         <is>
-          <t>2026-05-20T00:13:57+00:00</t>
+          <t>2026-05-20T00:48:39+00:00</t>
         </is>
       </c>
       <c r="AY126" t="inlineStr">
@@ -21074,7 +21074,7 @@
       </c>
       <c r="AT127" t="inlineStr">
         <is>
-          <t>batch_164c8f2ccaa64eaf</t>
+          <t>batch_4e3853438a5d4f9c</t>
         </is>
       </c>
       <c r="AU127" t="inlineStr">
@@ -21090,7 +21090,7 @@
       <c r="AW127" t="inlineStr"/>
       <c r="AX127" t="inlineStr">
         <is>
-          <t>2026-05-20T00:13:57+00:00</t>
+          <t>2026-05-20T00:48:39+00:00</t>
         </is>
       </c>
       <c r="AY127" t="inlineStr">
@@ -21234,7 +21234,7 @@
       </c>
       <c r="AT128" t="inlineStr">
         <is>
-          <t>batch_164c8f2ccaa64eaf</t>
+          <t>batch_4e3853438a5d4f9c</t>
         </is>
       </c>
       <c r="AU128" t="inlineStr">
@@ -21250,7 +21250,7 @@
       <c r="AW128" t="inlineStr"/>
       <c r="AX128" t="inlineStr">
         <is>
-          <t>2026-05-20T00:13:57+00:00</t>
+          <t>2026-05-20T00:48:39+00:00</t>
         </is>
       </c>
       <c r="AY128" t="inlineStr">
@@ -21394,7 +21394,7 @@
       </c>
       <c r="AT129" t="inlineStr">
         <is>
-          <t>batch_164c8f2ccaa64eaf</t>
+          <t>batch_4e3853438a5d4f9c</t>
         </is>
       </c>
       <c r="AU129" t="inlineStr">
@@ -21410,7 +21410,7 @@
       <c r="AW129" t="inlineStr"/>
       <c r="AX129" t="inlineStr">
         <is>
-          <t>2026-05-20T00:13:57+00:00</t>
+          <t>2026-05-20T00:48:39+00:00</t>
         </is>
       </c>
       <c r="AY129" t="inlineStr">
@@ -21554,7 +21554,7 @@
       </c>
       <c r="AT130" t="inlineStr">
         <is>
-          <t>batch_164c8f2ccaa64eaf</t>
+          <t>batch_4e3853438a5d4f9c</t>
         </is>
       </c>
       <c r="AU130" t="inlineStr">
@@ -21570,7 +21570,7 @@
       <c r="AW130" t="inlineStr"/>
       <c r="AX130" t="inlineStr">
         <is>
-          <t>2026-05-20T00:13:57+00:00</t>
+          <t>2026-05-20T00:48:39+00:00</t>
         </is>
       </c>
       <c r="AY130" t="inlineStr">
@@ -21714,7 +21714,7 @@
       </c>
       <c r="AT131" t="inlineStr">
         <is>
-          <t>batch_164c8f2ccaa64eaf</t>
+          <t>batch_4e3853438a5d4f9c</t>
         </is>
       </c>
       <c r="AU131" t="inlineStr">
@@ -21730,7 +21730,7 @@
       <c r="AW131" t="inlineStr"/>
       <c r="AX131" t="inlineStr">
         <is>
-          <t>2026-05-20T00:13:57+00:00</t>
+          <t>2026-05-20T00:48:39+00:00</t>
         </is>
       </c>
       <c r="AY131" t="inlineStr">
@@ -21874,7 +21874,7 @@
       </c>
       <c r="AT132" t="inlineStr">
         <is>
-          <t>batch_164c8f2ccaa64eaf</t>
+          <t>batch_4e3853438a5d4f9c</t>
         </is>
       </c>
       <c r="AU132" t="inlineStr">
@@ -21890,7 +21890,7 @@
       <c r="AW132" t="inlineStr"/>
       <c r="AX132" t="inlineStr">
         <is>
-          <t>2026-05-20T00:13:57+00:00</t>
+          <t>2026-05-20T00:48:39+00:00</t>
         </is>
       </c>
       <c r="AY132" t="inlineStr">
@@ -22034,7 +22034,7 @@
       </c>
       <c r="AT133" t="inlineStr">
         <is>
-          <t>batch_164c8f2ccaa64eaf</t>
+          <t>batch_4e3853438a5d4f9c</t>
         </is>
       </c>
       <c r="AU133" t="inlineStr">
@@ -22050,7 +22050,7 @@
       <c r="AW133" t="inlineStr"/>
       <c r="AX133" t="inlineStr">
         <is>
-          <t>2026-05-20T00:13:57+00:00</t>
+          <t>2026-05-20T00:48:39+00:00</t>
         </is>
       </c>
       <c r="AY133" t="inlineStr">
@@ -22194,7 +22194,7 @@
       </c>
       <c r="AT134" t="inlineStr">
         <is>
-          <t>batch_164c8f2ccaa64eaf</t>
+          <t>batch_4e3853438a5d4f9c</t>
         </is>
       </c>
       <c r="AU134" t="inlineStr">
@@ -22210,7 +22210,7 @@
       <c r="AW134" t="inlineStr"/>
       <c r="AX134" t="inlineStr">
         <is>
-          <t>2026-05-20T00:13:57+00:00</t>
+          <t>2026-05-20T00:48:39+00:00</t>
         </is>
       </c>
       <c r="AY134" t="inlineStr">
@@ -22354,7 +22354,7 @@
       </c>
       <c r="AT135" t="inlineStr">
         <is>
-          <t>batch_164c8f2ccaa64eaf</t>
+          <t>batch_4e3853438a5d4f9c</t>
         </is>
       </c>
       <c r="AU135" t="inlineStr">
@@ -22370,7 +22370,7 @@
       <c r="AW135" t="inlineStr"/>
       <c r="AX135" t="inlineStr">
         <is>
-          <t>2026-05-20T00:13:57+00:00</t>
+          <t>2026-05-20T00:48:39+00:00</t>
         </is>
       </c>
       <c r="AY135" t="inlineStr">
@@ -22514,7 +22514,7 @@
       </c>
       <c r="AT136" t="inlineStr">
         <is>
-          <t>batch_164c8f2ccaa64eaf</t>
+          <t>batch_4e3853438a5d4f9c</t>
         </is>
       </c>
       <c r="AU136" t="inlineStr">
@@ -22530,7 +22530,7 @@
       <c r="AW136" t="inlineStr"/>
       <c r="AX136" t="inlineStr">
         <is>
-          <t>2026-05-20T00:13:57+00:00</t>
+          <t>2026-05-20T00:48:39+00:00</t>
         </is>
       </c>
       <c r="AY136" t="inlineStr">
@@ -22674,7 +22674,7 @@
       </c>
       <c r="AT137" t="inlineStr">
         <is>
-          <t>batch_164c8f2ccaa64eaf</t>
+          <t>batch_4e3853438a5d4f9c</t>
         </is>
       </c>
       <c r="AU137" t="inlineStr">
@@ -22690,7 +22690,7 @@
       <c r="AW137" t="inlineStr"/>
       <c r="AX137" t="inlineStr">
         <is>
-          <t>2026-05-20T00:13:57+00:00</t>
+          <t>2026-05-20T00:48:39+00:00</t>
         </is>
       </c>
       <c r="AY137" t="inlineStr">
@@ -22834,7 +22834,7 @@
       </c>
       <c r="AT138" t="inlineStr">
         <is>
-          <t>batch_164c8f2ccaa64eaf</t>
+          <t>batch_4e3853438a5d4f9c</t>
         </is>
       </c>
       <c r="AU138" t="inlineStr">
@@ -22850,7 +22850,7 @@
       <c r="AW138" t="inlineStr"/>
       <c r="AX138" t="inlineStr">
         <is>
-          <t>2026-05-20T00:13:57+00:00</t>
+          <t>2026-05-20T00:48:39+00:00</t>
         </is>
       </c>
       <c r="AY138" t="inlineStr">
@@ -22994,7 +22994,7 @@
       </c>
       <c r="AT139" t="inlineStr">
         <is>
-          <t>batch_164c8f2ccaa64eaf</t>
+          <t>batch_4e3853438a5d4f9c</t>
         </is>
       </c>
       <c r="AU139" t="inlineStr">
@@ -23010,7 +23010,7 @@
       <c r="AW139" t="inlineStr"/>
       <c r="AX139" t="inlineStr">
         <is>
-          <t>2026-05-20T00:13:57+00:00</t>
+          <t>2026-05-20T00:48:39+00:00</t>
         </is>
       </c>
       <c r="AY139" t="inlineStr">
@@ -23154,7 +23154,7 @@
       </c>
       <c r="AT140" t="inlineStr">
         <is>
-          <t>batch_164c8f2ccaa64eaf</t>
+          <t>batch_4e3853438a5d4f9c</t>
         </is>
       </c>
       <c r="AU140" t="inlineStr">
@@ -23170,7 +23170,7 @@
       <c r="AW140" t="inlineStr"/>
       <c r="AX140" t="inlineStr">
         <is>
-          <t>2026-05-20T00:13:57+00:00</t>
+          <t>2026-05-20T00:48:39+00:00</t>
         </is>
       </c>
       <c r="AY140" t="inlineStr">
@@ -23314,7 +23314,7 @@
       </c>
       <c r="AT141" t="inlineStr">
         <is>
-          <t>batch_164c8f2ccaa64eaf</t>
+          <t>batch_4e3853438a5d4f9c</t>
         </is>
       </c>
       <c r="AU141" t="inlineStr">
@@ -23330,7 +23330,7 @@
       <c r="AW141" t="inlineStr"/>
       <c r="AX141" t="inlineStr">
         <is>
-          <t>2026-05-20T00:13:57+00:00</t>
+          <t>2026-05-20T00:48:39+00:00</t>
         </is>
       </c>
       <c r="AY141" t="inlineStr">
@@ -23474,7 +23474,7 @@
       </c>
       <c r="AT142" t="inlineStr">
         <is>
-          <t>batch_164c8f2ccaa64eaf</t>
+          <t>batch_4e3853438a5d4f9c</t>
         </is>
       </c>
       <c r="AU142" t="inlineStr">
@@ -23490,7 +23490,7 @@
       <c r="AW142" t="inlineStr"/>
       <c r="AX142" t="inlineStr">
         <is>
-          <t>2026-05-20T00:13:57+00:00</t>
+          <t>2026-05-20T00:48:39+00:00</t>
         </is>
       </c>
       <c r="AY142" t="inlineStr">
@@ -23634,7 +23634,7 @@
       </c>
       <c r="AT143" t="inlineStr">
         <is>
-          <t>batch_164c8f2ccaa64eaf</t>
+          <t>batch_4e3853438a5d4f9c</t>
         </is>
       </c>
       <c r="AU143" t="inlineStr">
@@ -23650,7 +23650,7 @@
       <c r="AW143" t="inlineStr"/>
       <c r="AX143" t="inlineStr">
         <is>
-          <t>2026-05-20T00:13:57+00:00</t>
+          <t>2026-05-20T00:48:39+00:00</t>
         </is>
       </c>
       <c r="AY143" t="inlineStr">
@@ -23794,7 +23794,7 @@
       </c>
       <c r="AT144" t="inlineStr">
         <is>
-          <t>batch_164c8f2ccaa64eaf</t>
+          <t>batch_4e3853438a5d4f9c</t>
         </is>
       </c>
       <c r="AU144" t="inlineStr">
@@ -23810,7 +23810,7 @@
       <c r="AW144" t="inlineStr"/>
       <c r="AX144" t="inlineStr">
         <is>
-          <t>2026-05-20T00:13:57+00:00</t>
+          <t>2026-05-20T00:48:39+00:00</t>
         </is>
       </c>
       <c r="AY144" t="inlineStr">
@@ -23954,7 +23954,7 @@
       </c>
       <c r="AT145" t="inlineStr">
         <is>
-          <t>batch_164c8f2ccaa64eaf</t>
+          <t>batch_4e3853438a5d4f9c</t>
         </is>
       </c>
       <c r="AU145" t="inlineStr">
@@ -23970,7 +23970,7 @@
       <c r="AW145" t="inlineStr"/>
       <c r="AX145" t="inlineStr">
         <is>
-          <t>2026-05-20T00:13:57+00:00</t>
+          <t>2026-05-20T00:48:39+00:00</t>
         </is>
       </c>
       <c r="AY145" t="inlineStr">
@@ -24114,7 +24114,7 @@
       </c>
       <c r="AT146" t="inlineStr">
         <is>
-          <t>batch_164c8f2ccaa64eaf</t>
+          <t>batch_4e3853438a5d4f9c</t>
         </is>
       </c>
       <c r="AU146" t="inlineStr">
@@ -24130,7 +24130,7 @@
       <c r="AW146" t="inlineStr"/>
       <c r="AX146" t="inlineStr">
         <is>
-          <t>2026-05-20T00:13:57+00:00</t>
+          <t>2026-05-20T00:48:39+00:00</t>
         </is>
       </c>
       <c r="AY146" t="inlineStr">
@@ -24274,7 +24274,7 @@
       </c>
       <c r="AT147" t="inlineStr">
         <is>
-          <t>batch_164c8f2ccaa64eaf</t>
+          <t>batch_4e3853438a5d4f9c</t>
         </is>
       </c>
       <c r="AU147" t="inlineStr">
@@ -24290,7 +24290,7 @@
       <c r="AW147" t="inlineStr"/>
       <c r="AX147" t="inlineStr">
         <is>
-          <t>2026-05-20T00:13:57+00:00</t>
+          <t>2026-05-20T00:48:39+00:00</t>
         </is>
       </c>
       <c r="AY147" t="inlineStr">
@@ -24434,7 +24434,7 @@
       </c>
       <c r="AT148" t="inlineStr">
         <is>
-          <t>batch_164c8f2ccaa64eaf</t>
+          <t>batch_4e3853438a5d4f9c</t>
         </is>
       </c>
       <c r="AU148" t="inlineStr">
@@ -24450,7 +24450,7 @@
       <c r="AW148" t="inlineStr"/>
       <c r="AX148" t="inlineStr">
         <is>
-          <t>2026-05-20T00:13:57+00:00</t>
+          <t>2026-05-20T00:48:39+00:00</t>
         </is>
       </c>
       <c r="AY148" t="inlineStr">
@@ -24594,7 +24594,7 @@
       </c>
       <c r="AT149" t="inlineStr">
         <is>
-          <t>batch_164c8f2ccaa64eaf</t>
+          <t>batch_4e3853438a5d4f9c</t>
         </is>
       </c>
       <c r="AU149" t="inlineStr">
@@ -24610,7 +24610,7 @@
       <c r="AW149" t="inlineStr"/>
       <c r="AX149" t="inlineStr">
         <is>
-          <t>2026-05-20T00:13:57+00:00</t>
+          <t>2026-05-20T00:48:39+00:00</t>
         </is>
       </c>
       <c r="AY149" t="inlineStr">
@@ -24754,7 +24754,7 @@
       </c>
       <c r="AT150" t="inlineStr">
         <is>
-          <t>batch_164c8f2ccaa64eaf</t>
+          <t>batch_4e3853438a5d4f9c</t>
         </is>
       </c>
       <c r="AU150" t="inlineStr">
@@ -24770,7 +24770,7 @@
       <c r="AW150" t="inlineStr"/>
       <c r="AX150" t="inlineStr">
         <is>
-          <t>2026-05-20T00:13:57+00:00</t>
+          <t>2026-05-20T00:48:39+00:00</t>
         </is>
       </c>
       <c r="AY150" t="inlineStr">
@@ -24914,7 +24914,7 @@
       </c>
       <c r="AT151" t="inlineStr">
         <is>
-          <t>batch_164c8f2ccaa64eaf</t>
+          <t>batch_4e3853438a5d4f9c</t>
         </is>
       </c>
       <c r="AU151" t="inlineStr">
@@ -24930,7 +24930,7 @@
       <c r="AW151" t="inlineStr"/>
       <c r="AX151" t="inlineStr">
         <is>
-          <t>2026-05-20T00:13:57+00:00</t>
+          <t>2026-05-20T00:48:39+00:00</t>
         </is>
       </c>
       <c r="AY151" t="inlineStr">
@@ -25074,7 +25074,7 @@
       </c>
       <c r="AT152" t="inlineStr">
         <is>
-          <t>batch_164c8f2ccaa64eaf</t>
+          <t>batch_4e3853438a5d4f9c</t>
         </is>
       </c>
       <c r="AU152" t="inlineStr">
@@ -25090,7 +25090,7 @@
       <c r="AW152" t="inlineStr"/>
       <c r="AX152" t="inlineStr">
         <is>
-          <t>2026-05-20T00:13:57+00:00</t>
+          <t>2026-05-20T00:48:39+00:00</t>
         </is>
       </c>
       <c r="AY152" t="inlineStr">
@@ -25234,7 +25234,7 @@
       </c>
       <c r="AT153" t="inlineStr">
         <is>
-          <t>batch_164c8f2ccaa64eaf</t>
+          <t>batch_4e3853438a5d4f9c</t>
         </is>
       </c>
       <c r="AU153" t="inlineStr">
@@ -25250,7 +25250,7 @@
       <c r="AW153" t="inlineStr"/>
       <c r="AX153" t="inlineStr">
         <is>
-          <t>2026-05-20T00:13:57+00:00</t>
+          <t>2026-05-20T00:48:39+00:00</t>
         </is>
       </c>
       <c r="AY153" t="inlineStr">
@@ -25394,7 +25394,7 @@
       </c>
       <c r="AT154" t="inlineStr">
         <is>
-          <t>batch_164c8f2ccaa64eaf</t>
+          <t>batch_4e3853438a5d4f9c</t>
         </is>
       </c>
       <c r="AU154" t="inlineStr">
@@ -25410,7 +25410,7 @@
       <c r="AW154" t="inlineStr"/>
       <c r="AX154" t="inlineStr">
         <is>
-          <t>2026-05-20T00:13:57+00:00</t>
+          <t>2026-05-20T00:48:39+00:00</t>
         </is>
       </c>
       <c r="AY154" t="inlineStr">
@@ -25554,7 +25554,7 @@
       </c>
       <c r="AT155" t="inlineStr">
         <is>
-          <t>batch_164c8f2ccaa64eaf</t>
+          <t>batch_4e3853438a5d4f9c</t>
         </is>
       </c>
       <c r="AU155" t="inlineStr">
@@ -25570,7 +25570,7 @@
       <c r="AW155" t="inlineStr"/>
       <c r="AX155" t="inlineStr">
         <is>
-          <t>2026-05-20T00:13:57+00:00</t>
+          <t>2026-05-20T00:48:39+00:00</t>
         </is>
       </c>
       <c r="AY155" t="inlineStr">
@@ -25714,7 +25714,7 @@
       </c>
       <c r="AT156" t="inlineStr">
         <is>
-          <t>batch_164c8f2ccaa64eaf</t>
+          <t>batch_4e3853438a5d4f9c</t>
         </is>
       </c>
       <c r="AU156" t="inlineStr">
@@ -25730,7 +25730,7 @@
       <c r="AW156" t="inlineStr"/>
       <c r="AX156" t="inlineStr">
         <is>
-          <t>2026-05-20T00:13:57+00:00</t>
+          <t>2026-05-20T00:48:39+00:00</t>
         </is>
       </c>
       <c r="AY156" t="inlineStr">
@@ -25874,7 +25874,7 @@
       </c>
       <c r="AT157" t="inlineStr">
         <is>
-          <t>batch_164c8f2ccaa64eaf</t>
+          <t>batch_4e3853438a5d4f9c</t>
         </is>
       </c>
       <c r="AU157" t="inlineStr">
@@ -25890,7 +25890,7 @@
       <c r="AW157" t="inlineStr"/>
       <c r="AX157" t="inlineStr">
         <is>
-          <t>2026-05-20T00:13:57+00:00</t>
+          <t>2026-05-20T00:48:39+00:00</t>
         </is>
       </c>
       <c r="AY157" t="inlineStr">
@@ -26034,7 +26034,7 @@
       </c>
       <c r="AT158" t="inlineStr">
         <is>
-          <t>batch_164c8f2ccaa64eaf</t>
+          <t>batch_4e3853438a5d4f9c</t>
         </is>
       </c>
       <c r="AU158" t="inlineStr">
@@ -26050,7 +26050,7 @@
       <c r="AW158" t="inlineStr"/>
       <c r="AX158" t="inlineStr">
         <is>
-          <t>2026-05-20T00:13:57+00:00</t>
+          <t>2026-05-20T00:48:39+00:00</t>
         </is>
       </c>
       <c r="AY158" t="inlineStr">
@@ -26194,7 +26194,7 @@
       </c>
       <c r="AT159" t="inlineStr">
         <is>
-          <t>batch_164c8f2ccaa64eaf</t>
+          <t>batch_4e3853438a5d4f9c</t>
         </is>
       </c>
       <c r="AU159" t="inlineStr">
@@ -26210,7 +26210,7 @@
       <c r="AW159" t="inlineStr"/>
       <c r="AX159" t="inlineStr">
         <is>
-          <t>2026-05-20T00:13:57+00:00</t>
+          <t>2026-05-20T00:48:39+00:00</t>
         </is>
       </c>
       <c r="AY159" t="inlineStr">
@@ -26354,7 +26354,7 @@
       </c>
       <c r="AT160" t="inlineStr">
         <is>
-          <t>batch_164c8f2ccaa64eaf</t>
+          <t>batch_4e3853438a5d4f9c</t>
         </is>
       </c>
       <c r="AU160" t="inlineStr">
@@ -26370,7 +26370,7 @@
       <c r="AW160" t="inlineStr"/>
       <c r="AX160" t="inlineStr">
         <is>
-          <t>2026-05-20T00:13:57+00:00</t>
+          <t>2026-05-20T00:48:39+00:00</t>
         </is>
       </c>
       <c r="AY160" t="inlineStr">
@@ -26514,7 +26514,7 @@
       </c>
       <c r="AT161" t="inlineStr">
         <is>
-          <t>batch_164c8f2ccaa64eaf</t>
+          <t>batch_4e3853438a5d4f9c</t>
         </is>
       </c>
       <c r="AU161" t="inlineStr">
@@ -26530,7 +26530,7 @@
       <c r="AW161" t="inlineStr"/>
       <c r="AX161" t="inlineStr">
         <is>
-          <t>2026-05-20T00:13:57+00:00</t>
+          <t>2026-05-20T00:48:39+00:00</t>
         </is>
       </c>
       <c r="AY161" t="inlineStr">
@@ -26674,7 +26674,7 @@
       </c>
       <c r="AT162" t="inlineStr">
         <is>
-          <t>batch_164c8f2ccaa64eaf</t>
+          <t>batch_4e3853438a5d4f9c</t>
         </is>
       </c>
       <c r="AU162" t="inlineStr">
@@ -26690,7 +26690,7 @@
       <c r="AW162" t="inlineStr"/>
       <c r="AX162" t="inlineStr">
         <is>
-          <t>2026-05-20T00:13:57+00:00</t>
+          <t>2026-05-20T00:48:39+00:00</t>
         </is>
       </c>
       <c r="AY162" t="inlineStr">
@@ -26834,7 +26834,7 @@
       </c>
       <c r="AT163" t="inlineStr">
         <is>
-          <t>batch_164c8f2ccaa64eaf</t>
+          <t>batch_4e3853438a5d4f9c</t>
         </is>
       </c>
       <c r="AU163" t="inlineStr">
@@ -26850,7 +26850,7 @@
       <c r="AW163" t="inlineStr"/>
       <c r="AX163" t="inlineStr">
         <is>
-          <t>2026-05-20T00:13:57+00:00</t>
+          <t>2026-05-20T00:48:39+00:00</t>
         </is>
       </c>
       <c r="AY163" t="inlineStr">
@@ -26994,7 +26994,7 @@
       </c>
       <c r="AT164" t="inlineStr">
         <is>
-          <t>batch_164c8f2ccaa64eaf</t>
+          <t>batch_4e3853438a5d4f9c</t>
         </is>
       </c>
       <c r="AU164" t="inlineStr">
@@ -27010,7 +27010,7 @@
       <c r="AW164" t="inlineStr"/>
       <c r="AX164" t="inlineStr">
         <is>
-          <t>2026-05-20T00:13:57+00:00</t>
+          <t>2026-05-20T00:48:39+00:00</t>
         </is>
       </c>
       <c r="AY164" t="inlineStr">
@@ -27154,7 +27154,7 @@
       </c>
       <c r="AT165" t="inlineStr">
         <is>
-          <t>batch_164c8f2ccaa64eaf</t>
+          <t>batch_4e3853438a5d4f9c</t>
         </is>
       </c>
       <c r="AU165" t="inlineStr">
@@ -27170,7 +27170,7 @@
       <c r="AW165" t="inlineStr"/>
       <c r="AX165" t="inlineStr">
         <is>
-          <t>2026-05-20T00:13:57+00:00</t>
+          <t>2026-05-20T00:48:39+00:00</t>
         </is>
       </c>
       <c r="AY165" t="inlineStr">
@@ -27314,7 +27314,7 @@
       </c>
       <c r="AT166" t="inlineStr">
         <is>
-          <t>batch_164c8f2ccaa64eaf</t>
+          <t>batch_4e3853438a5d4f9c</t>
         </is>
       </c>
       <c r="AU166" t="inlineStr">
@@ -27330,7 +27330,7 @@
       <c r="AW166" t="inlineStr"/>
       <c r="AX166" t="inlineStr">
         <is>
-          <t>2026-05-20T00:13:57+00:00</t>
+          <t>2026-05-20T00:48:39+00:00</t>
         </is>
       </c>
       <c r="AY166" t="inlineStr">
@@ -27474,7 +27474,7 @@
       </c>
       <c r="AT167" t="inlineStr">
         <is>
-          <t>batch_164c8f2ccaa64eaf</t>
+          <t>batch_4e3853438a5d4f9c</t>
         </is>
       </c>
       <c r="AU167" t="inlineStr">
@@ -27490,7 +27490,7 @@
       <c r="AW167" t="inlineStr"/>
       <c r="AX167" t="inlineStr">
         <is>
-          <t>2026-05-20T00:13:57+00:00</t>
+          <t>2026-05-20T00:48:39+00:00</t>
         </is>
       </c>
       <c r="AY167" t="inlineStr">
@@ -27634,7 +27634,7 @@
       </c>
       <c r="AT168" t="inlineStr">
         <is>
-          <t>batch_164c8f2ccaa64eaf</t>
+          <t>batch_4e3853438a5d4f9c</t>
         </is>
       </c>
       <c r="AU168" t="inlineStr">
@@ -27650,7 +27650,7 @@
       <c r="AW168" t="inlineStr"/>
       <c r="AX168" t="inlineStr">
         <is>
-          <t>2026-05-20T00:13:57+00:00</t>
+          <t>2026-05-20T00:48:39+00:00</t>
         </is>
       </c>
       <c r="AY168" t="inlineStr">
@@ -27794,7 +27794,7 @@
       </c>
       <c r="AT169" t="inlineStr">
         <is>
-          <t>batch_164c8f2ccaa64eaf</t>
+          <t>batch_4e3853438a5d4f9c</t>
         </is>
       </c>
       <c r="AU169" t="inlineStr">
@@ -27810,7 +27810,7 @@
       <c r="AW169" t="inlineStr"/>
       <c r="AX169" t="inlineStr">
         <is>
-          <t>2026-05-20T00:13:57+00:00</t>
+          <t>2026-05-20T00:48:39+00:00</t>
         </is>
       </c>
       <c r="AY169" t="inlineStr">
@@ -27954,7 +27954,7 @@
       </c>
       <c r="AT170" t="inlineStr">
         <is>
-          <t>batch_164c8f2ccaa64eaf</t>
+          <t>batch_4e3853438a5d4f9c</t>
         </is>
       </c>
       <c r="AU170" t="inlineStr">
@@ -27970,7 +27970,7 @@
       <c r="AW170" t="inlineStr"/>
       <c r="AX170" t="inlineStr">
         <is>
-          <t>2026-05-20T00:13:57+00:00</t>
+          <t>2026-05-20T00:48:39+00:00</t>
         </is>
       </c>
       <c r="AY170" t="inlineStr">
@@ -28114,7 +28114,7 @@
       </c>
       <c r="AT171" t="inlineStr">
         <is>
-          <t>batch_164c8f2ccaa64eaf</t>
+          <t>batch_4e3853438a5d4f9c</t>
         </is>
       </c>
       <c r="AU171" t="inlineStr">
@@ -28130,7 +28130,7 @@
       <c r="AW171" t="inlineStr"/>
       <c r="AX171" t="inlineStr">
         <is>
-          <t>2026-05-20T00:13:57+00:00</t>
+          <t>2026-05-20T00:48:39+00:00</t>
         </is>
       </c>
       <c r="AY171" t="inlineStr">
@@ -28274,7 +28274,7 @@
       </c>
       <c r="AT172" t="inlineStr">
         <is>
-          <t>batch_164c8f2ccaa64eaf</t>
+          <t>batch_4e3853438a5d4f9c</t>
         </is>
       </c>
       <c r="AU172" t="inlineStr">
@@ -28290,7 +28290,7 @@
       <c r="AW172" t="inlineStr"/>
       <c r="AX172" t="inlineStr">
         <is>
-          <t>2026-05-20T00:13:57+00:00</t>
+          <t>2026-05-20T00:48:39+00:00</t>
         </is>
       </c>
       <c r="AY172" t="inlineStr">
@@ -28434,7 +28434,7 @@
       </c>
       <c r="AT173" t="inlineStr">
         <is>
-          <t>batch_164c8f2ccaa64eaf</t>
+          <t>batch_4e3853438a5d4f9c</t>
         </is>
       </c>
       <c r="AU173" t="inlineStr">
@@ -28450,7 +28450,7 @@
       <c r="AW173" t="inlineStr"/>
       <c r="AX173" t="inlineStr">
         <is>
-          <t>2026-05-20T00:13:57+00:00</t>
+          <t>2026-05-20T00:48:39+00:00</t>
         </is>
       </c>
       <c r="AY173" t="inlineStr">
@@ -28594,7 +28594,7 @@
       </c>
       <c r="AT174" t="inlineStr">
         <is>
-          <t>batch_164c8f2ccaa64eaf</t>
+          <t>batch_4e3853438a5d4f9c</t>
         </is>
       </c>
       <c r="AU174" t="inlineStr">
@@ -28610,7 +28610,7 @@
       <c r="AW174" t="inlineStr"/>
       <c r="AX174" t="inlineStr">
         <is>
-          <t>2026-05-20T00:13:57+00:00</t>
+          <t>2026-05-20T00:48:39+00:00</t>
         </is>
       </c>
       <c r="AY174" t="inlineStr">
@@ -28754,7 +28754,7 @@
       </c>
       <c r="AT175" t="inlineStr">
         <is>
-          <t>batch_164c8f2ccaa64eaf</t>
+          <t>batch_4e3853438a5d4f9c</t>
         </is>
       </c>
       <c r="AU175" t="inlineStr">
@@ -28770,7 +28770,7 @@
       <c r="AW175" t="inlineStr"/>
       <c r="AX175" t="inlineStr">
         <is>
-          <t>2026-05-20T00:13:57+00:00</t>
+          <t>2026-05-20T00:48:39+00:00</t>
         </is>
       </c>
       <c r="AY175" t="inlineStr">
@@ -28914,7 +28914,7 @@
       </c>
       <c r="AT176" t="inlineStr">
         <is>
-          <t>batch_164c8f2ccaa64eaf</t>
+          <t>batch_4e3853438a5d4f9c</t>
         </is>
       </c>
       <c r="AU176" t="inlineStr">
@@ -28930,7 +28930,7 @@
       <c r="AW176" t="inlineStr"/>
       <c r="AX176" t="inlineStr">
         <is>
-          <t>2026-05-20T00:13:57+00:00</t>
+          <t>2026-05-20T00:48:39+00:00</t>
         </is>
       </c>
       <c r="AY176" t="inlineStr">
@@ -29074,7 +29074,7 @@
       </c>
       <c r="AT177" t="inlineStr">
         <is>
-          <t>batch_164c8f2ccaa64eaf</t>
+          <t>batch_4e3853438a5d4f9c</t>
         </is>
       </c>
       <c r="AU177" t="inlineStr">
@@ -29090,7 +29090,7 @@
       <c r="AW177" t="inlineStr"/>
       <c r="AX177" t="inlineStr">
         <is>
-          <t>2026-05-20T00:13:57+00:00</t>
+          <t>2026-05-20T00:48:39+00:00</t>
         </is>
       </c>
       <c r="AY177" t="inlineStr">
@@ -29234,7 +29234,7 @@
       </c>
       <c r="AT178" t="inlineStr">
         <is>
-          <t>batch_164c8f2ccaa64eaf</t>
+          <t>batch_4e3853438a5d4f9c</t>
         </is>
       </c>
       <c r="AU178" t="inlineStr">
@@ -29250,7 +29250,7 @@
       <c r="AW178" t="inlineStr"/>
       <c r="AX178" t="inlineStr">
         <is>
-          <t>2026-05-20T00:13:57+00:00</t>
+          <t>2026-05-20T00:48:39+00:00</t>
         </is>
       </c>
       <c r="AY178" t="inlineStr">
@@ -29394,7 +29394,7 @@
       </c>
       <c r="AT179" t="inlineStr">
         <is>
-          <t>batch_164c8f2ccaa64eaf</t>
+          <t>batch_4e3853438a5d4f9c</t>
         </is>
       </c>
       <c r="AU179" t="inlineStr">
@@ -29410,7 +29410,7 @@
       <c r="AW179" t="inlineStr"/>
       <c r="AX179" t="inlineStr">
         <is>
-          <t>2026-05-20T00:13:57+00:00</t>
+          <t>2026-05-20T00:48:39+00:00</t>
         </is>
       </c>
       <c r="AY179" t="inlineStr">
@@ -29554,7 +29554,7 @@
       </c>
       <c r="AT180" t="inlineStr">
         <is>
-          <t>batch_164c8f2ccaa64eaf</t>
+          <t>batch_4e3853438a5d4f9c</t>
         </is>
       </c>
       <c r="AU180" t="inlineStr">
@@ -29570,7 +29570,7 @@
       <c r="AW180" t="inlineStr"/>
       <c r="AX180" t="inlineStr">
         <is>
-          <t>2026-05-20T00:13:57+00:00</t>
+          <t>2026-05-20T00:48:39+00:00</t>
         </is>
       </c>
       <c r="AY180" t="inlineStr">
@@ -29714,7 +29714,7 @@
       </c>
       <c r="AT181" t="inlineStr">
         <is>
-          <t>batch_164c8f2ccaa64eaf</t>
+          <t>batch_4e3853438a5d4f9c</t>
         </is>
       </c>
       <c r="AU181" t="inlineStr">
@@ -29730,7 +29730,7 @@
       <c r="AW181" t="inlineStr"/>
       <c r="AX181" t="inlineStr">
         <is>
-          <t>2026-05-20T00:13:57+00:00</t>
+          <t>2026-05-20T00:48:39+00:00</t>
         </is>
       </c>
       <c r="AY181" t="inlineStr">
@@ -29874,7 +29874,7 @@
       </c>
       <c r="AT182" t="inlineStr">
         <is>
-          <t>batch_164c8f2ccaa64eaf</t>
+          <t>batch_4e3853438a5d4f9c</t>
         </is>
       </c>
       <c r="AU182" t="inlineStr">
@@ -29890,7 +29890,7 @@
       <c r="AW182" t="inlineStr"/>
       <c r="AX182" t="inlineStr">
         <is>
-          <t>2026-05-20T00:13:57+00:00</t>
+          <t>2026-05-20T00:48:39+00:00</t>
         </is>
       </c>
       <c r="AY182" t="inlineStr">
@@ -30031,7 +30031,7 @@
       </c>
       <c r="AT183" t="inlineStr">
         <is>
-          <t>batch_164c8f2ccaa64eaf</t>
+          <t>batch_4e3853438a5d4f9c</t>
         </is>
       </c>
       <c r="AU183" t="inlineStr">
@@ -30047,7 +30047,7 @@
       <c r="AW183" t="inlineStr"/>
       <c r="AX183" t="inlineStr">
         <is>
-          <t>2026-05-20T00:13:57+00:00</t>
+          <t>2026-05-20T00:48:39+00:00</t>
         </is>
       </c>
       <c r="AY183" t="inlineStr">
@@ -30191,7 +30191,7 @@
       </c>
       <c r="AT184" t="inlineStr">
         <is>
-          <t>batch_164c8f2ccaa64eaf</t>
+          <t>batch_4e3853438a5d4f9c</t>
         </is>
       </c>
       <c r="AU184" t="inlineStr">
@@ -30207,7 +30207,7 @@
       <c r="AW184" t="inlineStr"/>
       <c r="AX184" t="inlineStr">
         <is>
-          <t>2026-05-20T00:13:57+00:00</t>
+          <t>2026-05-20T00:48:39+00:00</t>
         </is>
       </c>
       <c r="AY184" t="inlineStr">
@@ -30351,7 +30351,7 @@
       </c>
       <c r="AT185" t="inlineStr">
         <is>
-          <t>batch_164c8f2ccaa64eaf</t>
+          <t>batch_4e3853438a5d4f9c</t>
         </is>
       </c>
       <c r="AU185" t="inlineStr">
@@ -30367,7 +30367,7 @@
       <c r="AW185" t="inlineStr"/>
       <c r="AX185" t="inlineStr">
         <is>
-          <t>2026-05-20T00:13:57+00:00</t>
+          <t>2026-05-20T00:48:39+00:00</t>
         </is>
       </c>
       <c r="AY185" t="inlineStr">
@@ -30511,7 +30511,7 @@
       </c>
       <c r="AT186" t="inlineStr">
         <is>
-          <t>batch_164c8f2ccaa64eaf</t>
+          <t>batch_4e3853438a5d4f9c</t>
         </is>
       </c>
       <c r="AU186" t="inlineStr">
@@ -30527,7 +30527,7 @@
       <c r="AW186" t="inlineStr"/>
       <c r="AX186" t="inlineStr">
         <is>
-          <t>2026-05-20T00:13:57+00:00</t>
+          <t>2026-05-20T00:48:39+00:00</t>
         </is>
       </c>
       <c r="AY186" t="inlineStr">
@@ -30671,7 +30671,7 @@
       </c>
       <c r="AT187" t="inlineStr">
         <is>
-          <t>batch_164c8f2ccaa64eaf</t>
+          <t>batch_4e3853438a5d4f9c</t>
         </is>
       </c>
       <c r="AU187" t="inlineStr">
@@ -30687,7 +30687,7 @@
       <c r="AW187" t="inlineStr"/>
       <c r="AX187" t="inlineStr">
         <is>
-          <t>2026-05-20T00:13:57+00:00</t>
+          <t>2026-05-20T00:48:39+00:00</t>
         </is>
       </c>
       <c r="AY187" t="inlineStr">
@@ -30831,7 +30831,7 @@
       </c>
       <c r="AT188" t="inlineStr">
         <is>
-          <t>batch_164c8f2ccaa64eaf</t>
+          <t>batch_4e3853438a5d4f9c</t>
         </is>
       </c>
       <c r="AU188" t="inlineStr">
@@ -30847,7 +30847,7 @@
       <c r="AW188" t="inlineStr"/>
       <c r="AX188" t="inlineStr">
         <is>
-          <t>2026-05-20T00:13:57+00:00</t>
+          <t>2026-05-20T00:48:39+00:00</t>
         </is>
       </c>
       <c r="AY188" t="inlineStr">
@@ -30991,7 +30991,7 @@
       </c>
       <c r="AT189" t="inlineStr">
         <is>
-          <t>batch_164c8f2ccaa64eaf</t>
+          <t>batch_4e3853438a5d4f9c</t>
         </is>
       </c>
       <c r="AU189" t="inlineStr">
@@ -31007,7 +31007,7 @@
       <c r="AW189" t="inlineStr"/>
       <c r="AX189" t="inlineStr">
         <is>
-          <t>2026-05-20T00:13:57+00:00</t>
+          <t>2026-05-20T00:48:39+00:00</t>
         </is>
       </c>
       <c r="AY189" t="inlineStr">
@@ -31151,7 +31151,7 @@
       </c>
       <c r="AT190" t="inlineStr">
         <is>
-          <t>batch_164c8f2ccaa64eaf</t>
+          <t>batch_4e3853438a5d4f9c</t>
         </is>
       </c>
       <c r="AU190" t="inlineStr">
@@ -31167,7 +31167,7 @@
       <c r="AW190" t="inlineStr"/>
       <c r="AX190" t="inlineStr">
         <is>
-          <t>2026-05-20T00:13:57+00:00</t>
+          <t>2026-05-20T00:48:39+00:00</t>
         </is>
       </c>
       <c r="AY190" t="inlineStr">
@@ -31311,7 +31311,7 @@
       </c>
       <c r="AT191" t="inlineStr">
         <is>
-          <t>batch_164c8f2ccaa64eaf</t>
+          <t>batch_4e3853438a5d4f9c</t>
         </is>
       </c>
       <c r="AU191" t="inlineStr">
@@ -31327,7 +31327,7 @@
       <c r="AW191" t="inlineStr"/>
       <c r="AX191" t="inlineStr">
         <is>
-          <t>2026-05-20T00:13:57+00:00</t>
+          <t>2026-05-20T00:48:39+00:00</t>
         </is>
       </c>
       <c r="AY191" t="inlineStr">
@@ -31471,7 +31471,7 @@
       </c>
       <c r="AT192" t="inlineStr">
         <is>
-          <t>batch_164c8f2ccaa64eaf</t>
+          <t>batch_4e3853438a5d4f9c</t>
         </is>
       </c>
       <c r="AU192" t="inlineStr">
@@ -31487,7 +31487,7 @@
       <c r="AW192" t="inlineStr"/>
       <c r="AX192" t="inlineStr">
         <is>
-          <t>2026-05-20T00:13:57+00:00</t>
+          <t>2026-05-20T00:48:39+00:00</t>
         </is>
       </c>
       <c r="AY192" t="inlineStr">
@@ -31631,7 +31631,7 @@
       </c>
       <c r="AT193" t="inlineStr">
         <is>
-          <t>batch_164c8f2ccaa64eaf</t>
+          <t>batch_4e3853438a5d4f9c</t>
         </is>
       </c>
       <c r="AU193" t="inlineStr">
@@ -31647,7 +31647,7 @@
       <c r="AW193" t="inlineStr"/>
       <c r="AX193" t="inlineStr">
         <is>
-          <t>2026-05-20T00:13:57+00:00</t>
+          <t>2026-05-20T00:48:39+00:00</t>
         </is>
       </c>
       <c r="AY193" t="inlineStr">
@@ -31791,7 +31791,7 @@
       </c>
       <c r="AT194" t="inlineStr">
         <is>
-          <t>batch_164c8f2ccaa64eaf</t>
+          <t>batch_4e3853438a5d4f9c</t>
         </is>
       </c>
       <c r="AU194" t="inlineStr">
@@ -31807,7 +31807,7 @@
       <c r="AW194" t="inlineStr"/>
       <c r="AX194" t="inlineStr">
         <is>
-          <t>2026-05-20T00:13:57+00:00</t>
+          <t>2026-05-20T00:48:39+00:00</t>
         </is>
       </c>
       <c r="AY194" t="inlineStr">
@@ -31951,7 +31951,7 @@
       </c>
       <c r="AT195" t="inlineStr">
         <is>
-          <t>batch_164c8f2ccaa64eaf</t>
+          <t>batch_4e3853438a5d4f9c</t>
         </is>
       </c>
       <c r="AU195" t="inlineStr">
@@ -31967,7 +31967,7 @@
       <c r="AW195" t="inlineStr"/>
       <c r="AX195" t="inlineStr">
         <is>
-          <t>2026-05-20T00:13:57+00:00</t>
+          <t>2026-05-20T00:48:39+00:00</t>
         </is>
       </c>
       <c r="AY195" t="inlineStr">
@@ -32111,7 +32111,7 @@
       </c>
       <c r="AT196" t="inlineStr">
         <is>
-          <t>batch_164c8f2ccaa64eaf</t>
+          <t>batch_4e3853438a5d4f9c</t>
         </is>
       </c>
       <c r="AU196" t="inlineStr">
@@ -32127,7 +32127,7 @@
       <c r="AW196" t="inlineStr"/>
       <c r="AX196" t="inlineStr">
         <is>
-          <t>2026-05-20T00:13:57+00:00</t>
+          <t>2026-05-20T00:48:39+00:00</t>
         </is>
       </c>
       <c r="AY196" t="inlineStr">
@@ -32271,7 +32271,7 @@
       </c>
       <c r="AT197" t="inlineStr">
         <is>
-          <t>batch_164c8f2ccaa64eaf</t>
+          <t>batch_4e3853438a5d4f9c</t>
         </is>
       </c>
       <c r="AU197" t="inlineStr">
@@ -32287,7 +32287,7 @@
       <c r="AW197" t="inlineStr"/>
       <c r="AX197" t="inlineStr">
         <is>
-          <t>2026-05-20T00:13:57+00:00</t>
+          <t>2026-05-20T00:48:39+00:00</t>
         </is>
       </c>
       <c r="AY197" t="inlineStr">
@@ -32431,7 +32431,7 @@
       </c>
       <c r="AT198" t="inlineStr">
         <is>
-          <t>batch_164c8f2ccaa64eaf</t>
+          <t>batch_4e3853438a5d4f9c</t>
         </is>
       </c>
       <c r="AU198" t="inlineStr">
@@ -32447,7 +32447,7 @@
       <c r="AW198" t="inlineStr"/>
       <c r="AX198" t="inlineStr">
         <is>
-          <t>2026-05-20T00:13:57+00:00</t>
+          <t>2026-05-20T00:48:39+00:00</t>
         </is>
       </c>
       <c r="AY198" t="inlineStr">
@@ -32591,7 +32591,7 @@
       </c>
       <c r="AT199" t="inlineStr">
         <is>
-          <t>batch_164c8f2ccaa64eaf</t>
+          <t>batch_4e3853438a5d4f9c</t>
         </is>
       </c>
       <c r="AU199" t="inlineStr">
@@ -32607,7 +32607,7 @@
       <c r="AW199" t="inlineStr"/>
       <c r="AX199" t="inlineStr">
         <is>
-          <t>2026-05-20T00:13:57+00:00</t>
+          <t>2026-05-20T00:48:39+00:00</t>
         </is>
       </c>
       <c r="AY199" t="inlineStr">
@@ -32751,7 +32751,7 @@
       </c>
       <c r="AT200" t="inlineStr">
         <is>
-          <t>batch_164c8f2ccaa64eaf</t>
+          <t>batch_4e3853438a5d4f9c</t>
         </is>
       </c>
       <c r="AU200" t="inlineStr">
@@ -32767,7 +32767,7 @@
       <c r="AW200" t="inlineStr"/>
       <c r="AX200" t="inlineStr">
         <is>
-          <t>2026-05-20T00:13:57+00:00</t>
+          <t>2026-05-20T00:48:39+00:00</t>
         </is>
       </c>
       <c r="AY200" t="inlineStr">
@@ -32920,7 +32920,7 @@
       </c>
       <c r="AT201" t="inlineStr">
         <is>
-          <t>batch_164c8f2ccaa64eaf</t>
+          <t>batch_4e3853438a5d4f9c</t>
         </is>
       </c>
       <c r="AU201" t="inlineStr">
@@ -32936,7 +32936,7 @@
       <c r="AW201" t="inlineStr"/>
       <c r="AX201" t="inlineStr">
         <is>
-          <t>2026-05-20T00:13:57+00:00</t>
+          <t>2026-05-20T00:48:39+00:00</t>
         </is>
       </c>
       <c r="AY201" t="inlineStr">
@@ -33089,7 +33089,7 @@
       </c>
       <c r="AT202" t="inlineStr">
         <is>
-          <t>batch_164c8f2ccaa64eaf</t>
+          <t>batch_4e3853438a5d4f9c</t>
         </is>
       </c>
       <c r="AU202" t="inlineStr">
@@ -33105,7 +33105,7 @@
       <c r="AW202" t="inlineStr"/>
       <c r="AX202" t="inlineStr">
         <is>
-          <t>2026-05-20T00:13:57+00:00</t>
+          <t>2026-05-20T00:48:39+00:00</t>
         </is>
       </c>
       <c r="AY202" t="inlineStr">
@@ -33249,7 +33249,7 @@
       </c>
       <c r="AT203" t="inlineStr">
         <is>
-          <t>batch_164c8f2ccaa64eaf</t>
+          <t>batch_4e3853438a5d4f9c</t>
         </is>
       </c>
       <c r="AU203" t="inlineStr">
@@ -33265,7 +33265,7 @@
       <c r="AW203" t="inlineStr"/>
       <c r="AX203" t="inlineStr">
         <is>
-          <t>2026-05-20T00:13:57+00:00</t>
+          <t>2026-05-20T00:48:39+00:00</t>
         </is>
       </c>
       <c r="AY203" t="inlineStr">
@@ -33409,7 +33409,7 @@
       </c>
       <c r="AT204" t="inlineStr">
         <is>
-          <t>batch_164c8f2ccaa64eaf</t>
+          <t>batch_4e3853438a5d4f9c</t>
         </is>
       </c>
       <c r="AU204" t="inlineStr">
@@ -33425,7 +33425,7 @@
       <c r="AW204" t="inlineStr"/>
       <c r="AX204" t="inlineStr">
         <is>
-          <t>2026-05-20T00:13:57+00:00</t>
+          <t>2026-05-20T00:48:39+00:00</t>
         </is>
       </c>
       <c r="AY204" t="inlineStr">
@@ -33569,7 +33569,7 @@
       </c>
       <c r="AT205" t="inlineStr">
         <is>
-          <t>batch_164c8f2ccaa64eaf</t>
+          <t>batch_4e3853438a5d4f9c</t>
         </is>
       </c>
       <c r="AU205" t="inlineStr">
@@ -33585,7 +33585,7 @@
       <c r="AW205" t="inlineStr"/>
       <c r="AX205" t="inlineStr">
         <is>
-          <t>2026-05-20T00:13:57+00:00</t>
+          <t>2026-05-20T00:48:39+00:00</t>
         </is>
       </c>
       <c r="AY205" t="inlineStr">
@@ -33729,7 +33729,7 @@
       </c>
       <c r="AT206" t="inlineStr">
         <is>
-          <t>batch_164c8f2ccaa64eaf</t>
+          <t>batch_4e3853438a5d4f9c</t>
         </is>
       </c>
       <c r="AU206" t="inlineStr">
@@ -33745,7 +33745,7 @@
       <c r="AW206" t="inlineStr"/>
       <c r="AX206" t="inlineStr">
         <is>
-          <t>2026-05-20T00:13:57+00:00</t>
+          <t>2026-05-20T00:48:39+00:00</t>
         </is>
       </c>
       <c r="AY206" t="inlineStr">
@@ -33889,7 +33889,7 @@
       </c>
       <c r="AT207" t="inlineStr">
         <is>
-          <t>batch_164c8f2ccaa64eaf</t>
+          <t>batch_4e3853438a5d4f9c</t>
         </is>
       </c>
       <c r="AU207" t="inlineStr">
@@ -33905,7 +33905,7 @@
       <c r="AW207" t="inlineStr"/>
       <c r="AX207" t="inlineStr">
         <is>
-          <t>2026-05-20T00:13:57+00:00</t>
+          <t>2026-05-20T00:48:39+00:00</t>
         </is>
       </c>
       <c r="AY207" t="inlineStr">
@@ -34049,7 +34049,7 @@
       </c>
       <c r="AT208" t="inlineStr">
         <is>
-          <t>batch_164c8f2ccaa64eaf</t>
+          <t>batch_4e3853438a5d4f9c</t>
         </is>
       </c>
       <c r="AU208" t="inlineStr">
@@ -34065,7 +34065,7 @@
       <c r="AW208" t="inlineStr"/>
       <c r="AX208" t="inlineStr">
         <is>
-          <t>2026-05-20T00:13:57+00:00</t>
+          <t>2026-05-20T00:48:39+00:00</t>
         </is>
       </c>
       <c r="AY208" t="inlineStr">
@@ -34209,7 +34209,7 @@
       </c>
       <c r="AT209" t="inlineStr">
         <is>
-          <t>batch_164c8f2ccaa64eaf</t>
+          <t>batch_4e3853438a5d4f9c</t>
         </is>
       </c>
       <c r="AU209" t="inlineStr">
@@ -34225,7 +34225,7 @@
       <c r="AW209" t="inlineStr"/>
       <c r="AX209" t="inlineStr">
         <is>
-          <t>2026-05-20T00:13:57+00:00</t>
+          <t>2026-05-20T00:48:39+00:00</t>
         </is>
       </c>
       <c r="AY209" t="inlineStr">
@@ -34369,7 +34369,7 @@
       </c>
       <c r="AT210" t="inlineStr">
         <is>
-          <t>batch_164c8f2ccaa64eaf</t>
+          <t>batch_4e3853438a5d4f9c</t>
         </is>
       </c>
       <c r="AU210" t="inlineStr">
@@ -34385,7 +34385,7 @@
       <c r="AW210" t="inlineStr"/>
       <c r="AX210" t="inlineStr">
         <is>
-          <t>2026-05-20T00:13:57+00:00</t>
+          <t>2026-05-20T00:48:39+00:00</t>
         </is>
       </c>
       <c r="AY210" t="inlineStr">
@@ -34529,7 +34529,7 @@
       </c>
       <c r="AT211" t="inlineStr">
         <is>
-          <t>batch_164c8f2ccaa64eaf</t>
+          <t>batch_4e3853438a5d4f9c</t>
         </is>
       </c>
       <c r="AU211" t="inlineStr">
@@ -34545,7 +34545,7 @@
       <c r="AW211" t="inlineStr"/>
       <c r="AX211" t="inlineStr">
         <is>
-          <t>2026-05-20T00:13:57+00:00</t>
+          <t>2026-05-20T00:48:39+00:00</t>
         </is>
       </c>
       <c r="AY211" t="inlineStr">
@@ -34689,7 +34689,7 @@
       </c>
       <c r="AT212" t="inlineStr">
         <is>
-          <t>batch_164c8f2ccaa64eaf</t>
+          <t>batch_4e3853438a5d4f9c</t>
         </is>
       </c>
       <c r="AU212" t="inlineStr">
@@ -34705,7 +34705,7 @@
       <c r="AW212" t="inlineStr"/>
       <c r="AX212" t="inlineStr">
         <is>
-          <t>2026-05-20T00:13:57+00:00</t>
+          <t>2026-05-20T00:48:39+00:00</t>
         </is>
       </c>
       <c r="AY212" t="inlineStr">
@@ -34849,7 +34849,7 @@
       </c>
       <c r="AT213" t="inlineStr">
         <is>
-          <t>batch_164c8f2ccaa64eaf</t>
+          <t>batch_4e3853438a5d4f9c</t>
         </is>
       </c>
       <c r="AU213" t="inlineStr">
@@ -34865,7 +34865,7 @@
       <c r="AW213" t="inlineStr"/>
       <c r="AX213" t="inlineStr">
         <is>
-          <t>2026-05-20T00:13:57+00:00</t>
+          <t>2026-05-20T00:48:39+00:00</t>
         </is>
       </c>
       <c r="AY213" t="inlineStr">
@@ -35009,7 +35009,7 @@
       </c>
       <c r="AT214" t="inlineStr">
         <is>
-          <t>batch_164c8f2ccaa64eaf</t>
+          <t>batch_4e3853438a5d4f9c</t>
         </is>
       </c>
       <c r="AU214" t="inlineStr">
@@ -35025,7 +35025,7 @@
       <c r="AW214" t="inlineStr"/>
       <c r="AX214" t="inlineStr">
         <is>
-          <t>2026-05-20T00:13:57+00:00</t>
+          <t>2026-05-20T00:48:39+00:00</t>
         </is>
       </c>
       <c r="AY214" t="inlineStr">
@@ -35169,7 +35169,7 @@
       </c>
       <c r="AT215" t="inlineStr">
         <is>
-          <t>batch_164c8f2ccaa64eaf</t>
+          <t>batch_4e3853438a5d4f9c</t>
         </is>
       </c>
       <c r="AU215" t="inlineStr">
@@ -35185,7 +35185,7 @@
       <c r="AW215" t="inlineStr"/>
       <c r="AX215" t="inlineStr">
         <is>
-          <t>2026-05-20T00:13:57+00:00</t>
+          <t>2026-05-20T00:48:39+00:00</t>
         </is>
       </c>
       <c r="AY215" t="inlineStr">
@@ -35329,7 +35329,7 @@
       </c>
       <c r="AT216" t="inlineStr">
         <is>
-          <t>batch_164c8f2ccaa64eaf</t>
+          <t>batch_4e3853438a5d4f9c</t>
         </is>
       </c>
       <c r="AU216" t="inlineStr">
@@ -35345,7 +35345,7 @@
       <c r="AW216" t="inlineStr"/>
       <c r="AX216" t="inlineStr">
         <is>
-          <t>2026-05-20T00:13:57+00:00</t>
+          <t>2026-05-20T00:48:39+00:00</t>
         </is>
       </c>
       <c r="AY216" t="inlineStr">
@@ -35489,7 +35489,7 @@
       </c>
       <c r="AT217" t="inlineStr">
         <is>
-          <t>batch_164c8f2ccaa64eaf</t>
+          <t>batch_4e3853438a5d4f9c</t>
         </is>
       </c>
       <c r="AU217" t="inlineStr">
@@ -35505,7 +35505,7 @@
       <c r="AW217" t="inlineStr"/>
       <c r="AX217" t="inlineStr">
         <is>
-          <t>2026-05-20T00:13:57+00:00</t>
+          <t>2026-05-20T00:48:39+00:00</t>
         </is>
       </c>
       <c r="AY217" t="inlineStr">
@@ -35649,7 +35649,7 @@
       </c>
       <c r="AT218" t="inlineStr">
         <is>
-          <t>batch_164c8f2ccaa64eaf</t>
+          <t>batch_4e3853438a5d4f9c</t>
         </is>
       </c>
       <c r="AU218" t="inlineStr">
@@ -35665,7 +35665,7 @@
       <c r="AW218" t="inlineStr"/>
       <c r="AX218" t="inlineStr">
         <is>
-          <t>2026-05-20T00:13:57+00:00</t>
+          <t>2026-05-20T00:48:39+00:00</t>
         </is>
       </c>
       <c r="AY218" t="inlineStr">
@@ -35809,7 +35809,7 @@
       </c>
       <c r="AT219" t="inlineStr">
         <is>
-          <t>batch_164c8f2ccaa64eaf</t>
+          <t>batch_4e3853438a5d4f9c</t>
         </is>
       </c>
       <c r="AU219" t="inlineStr">
@@ -35825,7 +35825,7 @@
       <c r="AW219" t="inlineStr"/>
       <c r="AX219" t="inlineStr">
         <is>
-          <t>2026-05-20T00:13:57+00:00</t>
+          <t>2026-05-20T00:48:39+00:00</t>
         </is>
       </c>
       <c r="AY219" t="inlineStr">
@@ -35969,7 +35969,7 @@
       </c>
       <c r="AT220" t="inlineStr">
         <is>
-          <t>batch_164c8f2ccaa64eaf</t>
+          <t>batch_4e3853438a5d4f9c</t>
         </is>
       </c>
       <c r="AU220" t="inlineStr">
@@ -35985,7 +35985,7 @@
       <c r="AW220" t="inlineStr"/>
       <c r="AX220" t="inlineStr">
         <is>
-          <t>2026-05-20T00:13:57+00:00</t>
+          <t>2026-05-20T00:48:39+00:00</t>
         </is>
       </c>
       <c r="AY220" t="inlineStr">
@@ -36129,7 +36129,7 @@
       </c>
       <c r="AT221" t="inlineStr">
         <is>
-          <t>batch_164c8f2ccaa64eaf</t>
+          <t>batch_4e3853438a5d4f9c</t>
         </is>
       </c>
       <c r="AU221" t="inlineStr">
@@ -36145,7 +36145,7 @@
       <c r="AW221" t="inlineStr"/>
       <c r="AX221" t="inlineStr">
         <is>
-          <t>2026-05-20T00:13:57+00:00</t>
+          <t>2026-05-20T00:48:39+00:00</t>
         </is>
       </c>
       <c r="AY221" t="inlineStr">
@@ -36289,7 +36289,7 @@
       </c>
       <c r="AT222" t="inlineStr">
         <is>
-          <t>batch_164c8f2ccaa64eaf</t>
+          <t>batch_4e3853438a5d4f9c</t>
         </is>
       </c>
       <c r="AU222" t="inlineStr">
@@ -36305,7 +36305,7 @@
       <c r="AW222" t="inlineStr"/>
       <c r="AX222" t="inlineStr">
         <is>
-          <t>2026-05-20T00:13:57+00:00</t>
+          <t>2026-05-20T00:48:39+00:00</t>
         </is>
       </c>
       <c r="AY222" t="inlineStr">
@@ -36449,7 +36449,7 @@
       </c>
       <c r="AT223" t="inlineStr">
         <is>
-          <t>batch_164c8f2ccaa64eaf</t>
+          <t>batch_4e3853438a5d4f9c</t>
         </is>
       </c>
       <c r="AU223" t="inlineStr">
@@ -36465,7 +36465,7 @@
       <c r="AW223" t="inlineStr"/>
       <c r="AX223" t="inlineStr">
         <is>
-          <t>2026-05-20T00:13:57+00:00</t>
+          <t>2026-05-20T00:48:39+00:00</t>
         </is>
       </c>
       <c r="AY223" t="inlineStr">
@@ -36609,7 +36609,7 @@
       </c>
       <c r="AT224" t="inlineStr">
         <is>
-          <t>batch_164c8f2ccaa64eaf</t>
+          <t>batch_4e3853438a5d4f9c</t>
         </is>
       </c>
       <c r="AU224" t="inlineStr">
@@ -36625,7 +36625,7 @@
       <c r="AW224" t="inlineStr"/>
       <c r="AX224" t="inlineStr">
         <is>
-          <t>2026-05-20T00:13:57+00:00</t>
+          <t>2026-05-20T00:48:39+00:00</t>
         </is>
       </c>
       <c r="AY224" t="inlineStr">
@@ -36769,7 +36769,7 @@
       </c>
       <c r="AT225" t="inlineStr">
         <is>
-          <t>batch_164c8f2ccaa64eaf</t>
+          <t>batch_4e3853438a5d4f9c</t>
         </is>
       </c>
       <c r="AU225" t="inlineStr">
@@ -36785,7 +36785,7 @@
       <c r="AW225" t="inlineStr"/>
       <c r="AX225" t="inlineStr">
         <is>
-          <t>2026-05-20T00:13:57+00:00</t>
+          <t>2026-05-20T00:48:39+00:00</t>
         </is>
       </c>
       <c r="AY225" t="inlineStr">
@@ -36929,7 +36929,7 @@
       </c>
       <c r="AT226" t="inlineStr">
         <is>
-          <t>batch_164c8f2ccaa64eaf</t>
+          <t>batch_4e3853438a5d4f9c</t>
         </is>
       </c>
       <c r="AU226" t="inlineStr">
@@ -36945,7 +36945,7 @@
       <c r="AW226" t="inlineStr"/>
       <c r="AX226" t="inlineStr">
         <is>
-          <t>2026-05-20T00:13:57+00:00</t>
+          <t>2026-05-20T00:48:39+00:00</t>
         </is>
       </c>
       <c r="AY226" t="inlineStr">
@@ -37089,7 +37089,7 @@
       </c>
       <c r="AT227" t="inlineStr">
         <is>
-          <t>batch_164c8f2ccaa64eaf</t>
+          <t>batch_4e3853438a5d4f9c</t>
         </is>
       </c>
       <c r="AU227" t="inlineStr">
@@ -37105,7 +37105,7 @@
       <c r="AW227" t="inlineStr"/>
       <c r="AX227" t="inlineStr">
         <is>
-          <t>2026-05-20T00:13:57+00:00</t>
+          <t>2026-05-20T00:48:39+00:00</t>
         </is>
       </c>
       <c r="AY227" t="inlineStr">
@@ -37249,7 +37249,7 @@
       </c>
       <c r="AT228" t="inlineStr">
         <is>
-          <t>batch_164c8f2ccaa64eaf</t>
+          <t>batch_4e3853438a5d4f9c</t>
         </is>
       </c>
       <c r="AU228" t="inlineStr">
@@ -37265,7 +37265,7 @@
       <c r="AW228" t="inlineStr"/>
       <c r="AX228" t="inlineStr">
         <is>
-          <t>2026-05-20T00:13:57+00:00</t>
+          <t>2026-05-20T00:48:39+00:00</t>
         </is>
       </c>
       <c r="AY228" t="inlineStr">
@@ -37409,7 +37409,7 @@
       </c>
       <c r="AT229" t="inlineStr">
         <is>
-          <t>batch_164c8f2ccaa64eaf</t>
+          <t>batch_4e3853438a5d4f9c</t>
         </is>
       </c>
       <c r="AU229" t="inlineStr">
@@ -37425,7 +37425,7 @@
       <c r="AW229" t="inlineStr"/>
       <c r="AX229" t="inlineStr">
         <is>
-          <t>2026-05-20T00:13:57+00:00</t>
+          <t>2026-05-20T00:48:39+00:00</t>
         </is>
       </c>
       <c r="AY229" t="inlineStr">
@@ -37569,7 +37569,7 @@
       </c>
       <c r="AT230" t="inlineStr">
         <is>
-          <t>batch_164c8f2ccaa64eaf</t>
+          <t>batch_4e3853438a5d4f9c</t>
         </is>
       </c>
       <c r="AU230" t="inlineStr">
@@ -37585,7 +37585,7 @@
       <c r="AW230" t="inlineStr"/>
       <c r="AX230" t="inlineStr">
         <is>
-          <t>2026-05-20T00:13:57+00:00</t>
+          <t>2026-05-20T00:48:39+00:00</t>
         </is>
       </c>
       <c r="AY230" t="inlineStr">
@@ -37729,7 +37729,7 @@
       </c>
       <c r="AT231" t="inlineStr">
         <is>
-          <t>batch_164c8f2ccaa64eaf</t>
+          <t>batch_4e3853438a5d4f9c</t>
         </is>
       </c>
       <c r="AU231" t="inlineStr">
@@ -37745,7 +37745,7 @@
       <c r="AW231" t="inlineStr"/>
       <c r="AX231" t="inlineStr">
         <is>
-          <t>2026-05-20T00:13:57+00:00</t>
+          <t>2026-05-20T00:48:39+00:00</t>
         </is>
       </c>
       <c r="AY231" t="inlineStr">
@@ -37889,7 +37889,7 @@
       </c>
       <c r="AT232" t="inlineStr">
         <is>
-          <t>batch_164c8f2ccaa64eaf</t>
+          <t>batch_4e3853438a5d4f9c</t>
         </is>
       </c>
       <c r="AU232" t="inlineStr">
@@ -37905,7 +37905,7 @@
       <c r="AW232" t="inlineStr"/>
       <c r="AX232" t="inlineStr">
         <is>
-          <t>2026-05-20T00:13:57+00:00</t>
+          <t>2026-05-20T00:48:39+00:00</t>
         </is>
       </c>
       <c r="AY232" t="inlineStr">
@@ -38049,7 +38049,7 @@
       </c>
       <c r="AT233" t="inlineStr">
         <is>
-          <t>batch_164c8f2ccaa64eaf</t>
+          <t>batch_4e3853438a5d4f9c</t>
         </is>
       </c>
       <c r="AU233" t="inlineStr">
@@ -38065,7 +38065,7 @@
       <c r="AW233" t="inlineStr"/>
       <c r="AX233" t="inlineStr">
         <is>
-          <t>2026-05-20T00:13:57+00:00</t>
+          <t>2026-05-20T00:48:39+00:00</t>
         </is>
       </c>
       <c r="AY233" t="inlineStr">
@@ -38209,7 +38209,7 @@
       </c>
       <c r="AT234" t="inlineStr">
         <is>
-          <t>batch_164c8f2ccaa64eaf</t>
+          <t>batch_4e3853438a5d4f9c</t>
         </is>
       </c>
       <c r="AU234" t="inlineStr">
@@ -38225,7 +38225,7 @@
       <c r="AW234" t="inlineStr"/>
       <c r="AX234" t="inlineStr">
         <is>
-          <t>2026-05-20T00:13:57+00:00</t>
+          <t>2026-05-20T00:48:39+00:00</t>
         </is>
       </c>
       <c r="AY234" t="inlineStr">
@@ -38369,7 +38369,7 @@
       </c>
       <c r="AT235" t="inlineStr">
         <is>
-          <t>batch_164c8f2ccaa64eaf</t>
+          <t>batch_4e3853438a5d4f9c</t>
         </is>
       </c>
       <c r="AU235" t="inlineStr">
@@ -38385,7 +38385,7 @@
       <c r="AW235" t="inlineStr"/>
       <c r="AX235" t="inlineStr">
         <is>
-          <t>2026-05-20T00:13:57+00:00</t>
+          <t>2026-05-20T00:48:39+00:00</t>
         </is>
       </c>
       <c r="AY235" t="inlineStr">
@@ -38529,7 +38529,7 @@
       </c>
       <c r="AT236" t="inlineStr">
         <is>
-          <t>batch_164c8f2ccaa64eaf</t>
+          <t>batch_4e3853438a5d4f9c</t>
         </is>
       </c>
       <c r="AU236" t="inlineStr">
@@ -38545,7 +38545,7 @@
       <c r="AW236" t="inlineStr"/>
       <c r="AX236" t="inlineStr">
         <is>
-          <t>2026-05-20T00:13:57+00:00</t>
+          <t>2026-05-20T00:48:39+00:00</t>
         </is>
       </c>
       <c r="AY236" t="inlineStr">
@@ -38689,7 +38689,7 @@
       </c>
       <c r="AT237" t="inlineStr">
         <is>
-          <t>batch_164c8f2ccaa64eaf</t>
+          <t>batch_4e3853438a5d4f9c</t>
         </is>
       </c>
       <c r="AU237" t="inlineStr">
@@ -38705,7 +38705,7 @@
       <c r="AW237" t="inlineStr"/>
       <c r="AX237" t="inlineStr">
         <is>
-          <t>2026-05-20T00:13:57+00:00</t>
+          <t>2026-05-20T00:48:39+00:00</t>
         </is>
       </c>
       <c r="AY237" t="inlineStr">
@@ -38849,7 +38849,7 @@
       </c>
       <c r="AT238" t="inlineStr">
         <is>
-          <t>batch_164c8f2ccaa64eaf</t>
+          <t>batch_4e3853438a5d4f9c</t>
         </is>
       </c>
       <c r="AU238" t="inlineStr">
@@ -38865,7 +38865,7 @@
       <c r="AW238" t="inlineStr"/>
       <c r="AX238" t="inlineStr">
         <is>
-          <t>2026-05-20T00:13:57+00:00</t>
+          <t>2026-05-20T00:48:39+00:00</t>
         </is>
       </c>
       <c r="AY238" t="inlineStr">
@@ -39009,7 +39009,7 @@
       </c>
       <c r="AT239" t="inlineStr">
         <is>
-          <t>batch_164c8f2ccaa64eaf</t>
+          <t>batch_4e3853438a5d4f9c</t>
         </is>
       </c>
       <c r="AU239" t="inlineStr">
@@ -39025,7 +39025,7 @@
       <c r="AW239" t="inlineStr"/>
       <c r="AX239" t="inlineStr">
         <is>
-          <t>2026-05-20T00:13:57+00:00</t>
+          <t>2026-05-20T00:48:39+00:00</t>
         </is>
       </c>
       <c r="AY239" t="inlineStr">
@@ -39169,7 +39169,7 @@
       </c>
       <c r="AT240" t="inlineStr">
         <is>
-          <t>batch_164c8f2ccaa64eaf</t>
+          <t>batch_4e3853438a5d4f9c</t>
         </is>
       </c>
       <c r="AU240" t="inlineStr">
@@ -39185,7 +39185,7 @@
       <c r="AW240" t="inlineStr"/>
       <c r="AX240" t="inlineStr">
         <is>
-          <t>2026-05-20T00:13:57+00:00</t>
+          <t>2026-05-20T00:48:39+00:00</t>
         </is>
       </c>
       <c r="AY240" t="inlineStr">
@@ -39329,7 +39329,7 @@
       </c>
       <c r="AT241" t="inlineStr">
         <is>
-          <t>batch_164c8f2ccaa64eaf</t>
+          <t>batch_4e3853438a5d4f9c</t>
         </is>
       </c>
       <c r="AU241" t="inlineStr">
@@ -39345,7 +39345,7 @@
       <c r="AW241" t="inlineStr"/>
       <c r="AX241" t="inlineStr">
         <is>
-          <t>2026-05-20T00:13:57+00:00</t>
+          <t>2026-05-20T00:48:39+00:00</t>
         </is>
       </c>
       <c r="AY241" t="inlineStr">
@@ -39489,7 +39489,7 @@
       </c>
       <c r="AT242" t="inlineStr">
         <is>
-          <t>batch_164c8f2ccaa64eaf</t>
+          <t>batch_4e3853438a5d4f9c</t>
         </is>
       </c>
       <c r="AU242" t="inlineStr">
@@ -39505,7 +39505,7 @@
       <c r="AW242" t="inlineStr"/>
       <c r="AX242" t="inlineStr">
         <is>
-          <t>2026-05-20T00:13:57+00:00</t>
+          <t>2026-05-20T00:48:39+00:00</t>
         </is>
       </c>
       <c r="AY242" t="inlineStr">
@@ -39649,7 +39649,7 @@
       </c>
       <c r="AT243" t="inlineStr">
         <is>
-          <t>batch_164c8f2ccaa64eaf</t>
+          <t>batch_4e3853438a5d4f9c</t>
         </is>
       </c>
       <c r="AU243" t="inlineStr">
@@ -39665,7 +39665,7 @@
       <c r="AW243" t="inlineStr"/>
       <c r="AX243" t="inlineStr">
         <is>
-          <t>2026-05-20T00:13:57+00:00</t>
+          <t>2026-05-20T00:48:39+00:00</t>
         </is>
       </c>
       <c r="AY243" t="inlineStr">
@@ -39809,7 +39809,7 @@
       </c>
       <c r="AT244" t="inlineStr">
         <is>
-          <t>batch_164c8f2ccaa64eaf</t>
+          <t>batch_4e3853438a5d4f9c</t>
         </is>
       </c>
       <c r="AU244" t="inlineStr">
@@ -39825,7 +39825,7 @@
       <c r="AW244" t="inlineStr"/>
       <c r="AX244" t="inlineStr">
         <is>
-          <t>2026-05-20T00:13:57+00:00</t>
+          <t>2026-05-20T00:48:39+00:00</t>
         </is>
       </c>
       <c r="AY244" t="inlineStr">
@@ -39969,7 +39969,7 @@
       </c>
       <c r="AT245" t="inlineStr">
         <is>
-          <t>batch_164c8f2ccaa64eaf</t>
+          <t>batch_4e3853438a5d4f9c</t>
         </is>
       </c>
       <c r="AU245" t="inlineStr">
@@ -39985,7 +39985,7 @@
       <c r="AW245" t="inlineStr"/>
       <c r="AX245" t="inlineStr">
         <is>
-          <t>2026-05-20T00:13:57+00:00</t>
+          <t>2026-05-20T00:48:39+00:00</t>
         </is>
       </c>
       <c r="AY245" t="inlineStr">
@@ -40129,7 +40129,7 @@
       </c>
       <c r="AT246" t="inlineStr">
         <is>
-          <t>batch_164c8f2ccaa64eaf</t>
+          <t>batch_4e3853438a5d4f9c</t>
         </is>
       </c>
       <c r="AU246" t="inlineStr">
@@ -40145,7 +40145,7 @@
       <c r="AW246" t="inlineStr"/>
       <c r="AX246" t="inlineStr">
         <is>
-          <t>2026-05-20T00:13:57+00:00</t>
+          <t>2026-05-20T00:48:39+00:00</t>
         </is>
       </c>
       <c r="AY246" t="inlineStr">
@@ -40289,7 +40289,7 @@
       </c>
       <c r="AT247" t="inlineStr">
         <is>
-          <t>batch_164c8f2ccaa64eaf</t>
+          <t>batch_4e3853438a5d4f9c</t>
         </is>
       </c>
       <c r="AU247" t="inlineStr">
@@ -40305,7 +40305,7 @@
       <c r="AW247" t="inlineStr"/>
       <c r="AX247" t="inlineStr">
         <is>
-          <t>2026-05-20T00:13:57+00:00</t>
+          <t>2026-05-20T00:48:39+00:00</t>
         </is>
       </c>
       <c r="AY247" t="inlineStr">
@@ -40449,7 +40449,7 @@
       </c>
       <c r="AT248" t="inlineStr">
         <is>
-          <t>batch_164c8f2ccaa64eaf</t>
+          <t>batch_4e3853438a5d4f9c</t>
         </is>
       </c>
       <c r="AU248" t="inlineStr">
@@ -40465,7 +40465,7 @@
       <c r="AW248" t="inlineStr"/>
       <c r="AX248" t="inlineStr">
         <is>
-          <t>2026-05-20T00:13:57+00:00</t>
+          <t>2026-05-20T00:48:39+00:00</t>
         </is>
       </c>
       <c r="AY248" t="inlineStr">
@@ -40609,7 +40609,7 @@
       </c>
       <c r="AT249" t="inlineStr">
         <is>
-          <t>batch_164c8f2ccaa64eaf</t>
+          <t>batch_4e3853438a5d4f9c</t>
         </is>
       </c>
       <c r="AU249" t="inlineStr">
@@ -40625,7 +40625,7 @@
       <c r="AW249" t="inlineStr"/>
       <c r="AX249" t="inlineStr">
         <is>
-          <t>2026-05-20T00:13:57+00:00</t>
+          <t>2026-05-20T00:48:39+00:00</t>
         </is>
       </c>
       <c r="AY249" t="inlineStr">
@@ -40769,7 +40769,7 @@
       </c>
       <c r="AT250" t="inlineStr">
         <is>
-          <t>batch_164c8f2ccaa64eaf</t>
+          <t>batch_4e3853438a5d4f9c</t>
         </is>
       </c>
       <c r="AU250" t="inlineStr">
@@ -40785,7 +40785,7 @@
       <c r="AW250" t="inlineStr"/>
       <c r="AX250" t="inlineStr">
         <is>
-          <t>2026-05-20T00:13:57+00:00</t>
+          <t>2026-05-20T00:48:39+00:00</t>
         </is>
       </c>
       <c r="AY250" t="inlineStr">
@@ -40929,7 +40929,7 @@
       </c>
       <c r="AT251" t="inlineStr">
         <is>
-          <t>batch_164c8f2ccaa64eaf</t>
+          <t>batch_4e3853438a5d4f9c</t>
         </is>
       </c>
       <c r="AU251" t="inlineStr">
@@ -40945,7 +40945,7 @@
       <c r="AW251" t="inlineStr"/>
       <c r="AX251" t="inlineStr">
         <is>
-          <t>2026-05-20T00:13:57+00:00</t>
+          <t>2026-05-20T00:48:39+00:00</t>
         </is>
       </c>
       <c r="AY251" t="inlineStr">
@@ -41089,7 +41089,7 @@
       </c>
       <c r="AT252" t="inlineStr">
         <is>
-          <t>batch_164c8f2ccaa64eaf</t>
+          <t>batch_4e3853438a5d4f9c</t>
         </is>
       </c>
       <c r="AU252" t="inlineStr">
@@ -41105,7 +41105,7 @@
       <c r="AW252" t="inlineStr"/>
       <c r="AX252" t="inlineStr">
         <is>
-          <t>2026-05-20T00:13:57+00:00</t>
+          <t>2026-05-20T00:48:39+00:00</t>
         </is>
       </c>
       <c r="AY252" t="inlineStr">
@@ -41249,7 +41249,7 @@
       </c>
       <c r="AT253" t="inlineStr">
         <is>
-          <t>batch_164c8f2ccaa64eaf</t>
+          <t>batch_4e3853438a5d4f9c</t>
         </is>
       </c>
       <c r="AU253" t="inlineStr">
@@ -41265,7 +41265,7 @@
       <c r="AW253" t="inlineStr"/>
       <c r="AX253" t="inlineStr">
         <is>
-          <t>2026-05-20T00:13:57+00:00</t>
+          <t>2026-05-20T00:48:39+00:00</t>
         </is>
       </c>
       <c r="AY253" t="inlineStr">
@@ -41409,7 +41409,7 @@
       </c>
       <c r="AT254" t="inlineStr">
         <is>
-          <t>batch_164c8f2ccaa64eaf</t>
+          <t>batch_4e3853438a5d4f9c</t>
         </is>
       </c>
       <c r="AU254" t="inlineStr">
@@ -41425,7 +41425,7 @@
       <c r="AW254" t="inlineStr"/>
       <c r="AX254" t="inlineStr">
         <is>
-          <t>2026-05-20T00:13:57+00:00</t>
+          <t>2026-05-20T00:48:39+00:00</t>
         </is>
       </c>
       <c r="AY254" t="inlineStr">
@@ -41569,7 +41569,7 @@
       </c>
       <c r="AT255" t="inlineStr">
         <is>
-          <t>batch_164c8f2ccaa64eaf</t>
+          <t>batch_4e3853438a5d4f9c</t>
         </is>
       </c>
       <c r="AU255" t="inlineStr">
@@ -41585,7 +41585,7 @@
       <c r="AW255" t="inlineStr"/>
       <c r="AX255" t="inlineStr">
         <is>
-          <t>2026-05-20T00:13:57+00:00</t>
+          <t>2026-05-20T00:48:39+00:00</t>
         </is>
       </c>
       <c r="AY255" t="inlineStr">
@@ -41729,7 +41729,7 @@
       </c>
       <c r="AT256" t="inlineStr">
         <is>
-          <t>batch_164c8f2ccaa64eaf</t>
+          <t>batch_4e3853438a5d4f9c</t>
         </is>
       </c>
       <c r="AU256" t="inlineStr">
@@ -41745,7 +41745,7 @@
       <c r="AW256" t="inlineStr"/>
       <c r="AX256" t="inlineStr">
         <is>
-          <t>2026-05-20T00:13:57+00:00</t>
+          <t>2026-05-20T00:48:39+00:00</t>
         </is>
       </c>
       <c r="AY256" t="inlineStr">
@@ -41889,7 +41889,7 @@
       </c>
       <c r="AT257" t="inlineStr">
         <is>
-          <t>batch_164c8f2ccaa64eaf</t>
+          <t>batch_4e3853438a5d4f9c</t>
         </is>
       </c>
       <c r="AU257" t="inlineStr">
@@ -41905,7 +41905,7 @@
       <c r="AW257" t="inlineStr"/>
       <c r="AX257" t="inlineStr">
         <is>
-          <t>2026-05-20T00:13:57+00:00</t>
+          <t>2026-05-20T00:48:39+00:00</t>
         </is>
       </c>
       <c r="AY257" t="inlineStr">
@@ -42049,7 +42049,7 @@
       </c>
       <c r="AT258" t="inlineStr">
         <is>
-          <t>batch_164c8f2ccaa64eaf</t>
+          <t>batch_4e3853438a5d4f9c</t>
         </is>
       </c>
       <c r="AU258" t="inlineStr">
@@ -42065,7 +42065,7 @@
       <c r="AW258" t="inlineStr"/>
       <c r="AX258" t="inlineStr">
         <is>
-          <t>2026-05-20T00:13:57+00:00</t>
+          <t>2026-05-20T00:48:39+00:00</t>
         </is>
       </c>
       <c r="AY258" t="inlineStr">
@@ -42209,7 +42209,7 @@
       </c>
       <c r="AT259" t="inlineStr">
         <is>
-          <t>batch_164c8f2ccaa64eaf</t>
+          <t>batch_4e3853438a5d4f9c</t>
         </is>
       </c>
       <c r="AU259" t="inlineStr">
@@ -42225,7 +42225,7 @@
       <c r="AW259" t="inlineStr"/>
       <c r="AX259" t="inlineStr">
         <is>
-          <t>2026-05-20T00:13:57+00:00</t>
+          <t>2026-05-20T00:48:39+00:00</t>
         </is>
       </c>
       <c r="AY259" t="inlineStr">
@@ -42369,7 +42369,7 @@
       </c>
       <c r="AT260" t="inlineStr">
         <is>
-          <t>batch_164c8f2ccaa64eaf</t>
+          <t>batch_4e3853438a5d4f9c</t>
         </is>
       </c>
       <c r="AU260" t="inlineStr">
@@ -42385,7 +42385,7 @@
       <c r="AW260" t="inlineStr"/>
       <c r="AX260" t="inlineStr">
         <is>
-          <t>2026-05-20T00:13:57+00:00</t>
+          <t>2026-05-20T00:48:39+00:00</t>
         </is>
       </c>
       <c r="AY260" t="inlineStr">
@@ -42529,7 +42529,7 @@
       </c>
       <c r="AT261" t="inlineStr">
         <is>
-          <t>batch_164c8f2ccaa64eaf</t>
+          <t>batch_4e3853438a5d4f9c</t>
         </is>
       </c>
       <c r="AU261" t="inlineStr">
@@ -42545,7 +42545,7 @@
       <c r="AW261" t="inlineStr"/>
       <c r="AX261" t="inlineStr">
         <is>
-          <t>2026-05-20T00:13:57+00:00</t>
+          <t>2026-05-20T00:48:39+00:00</t>
         </is>
       </c>
       <c r="AY261" t="inlineStr">
@@ -42689,7 +42689,7 @@
       </c>
       <c r="AT262" t="inlineStr">
         <is>
-          <t>batch_164c8f2ccaa64eaf</t>
+          <t>batch_4e3853438a5d4f9c</t>
         </is>
       </c>
       <c r="AU262" t="inlineStr">
@@ -42705,7 +42705,7 @@
       <c r="AW262" t="inlineStr"/>
       <c r="AX262" t="inlineStr">
         <is>
-          <t>2026-05-20T00:13:57+00:00</t>
+          <t>2026-05-20T00:48:39+00:00</t>
         </is>
       </c>
       <c r="AY262" t="inlineStr">
@@ -42849,7 +42849,7 @@
       </c>
       <c r="AT263" t="inlineStr">
         <is>
-          <t>batch_164c8f2ccaa64eaf</t>
+          <t>batch_4e3853438a5d4f9c</t>
         </is>
       </c>
       <c r="AU263" t="inlineStr">
@@ -42865,7 +42865,7 @@
       <c r="AW263" t="inlineStr"/>
       <c r="AX263" t="inlineStr">
         <is>
-          <t>2026-05-20T00:13:57+00:00</t>
+          <t>2026-05-20T00:48:39+00:00</t>
         </is>
       </c>
       <c r="AY263" t="inlineStr">
@@ -43009,7 +43009,7 @@
       </c>
       <c r="AT264" t="inlineStr">
         <is>
-          <t>batch_164c8f2ccaa64eaf</t>
+          <t>batch_4e3853438a5d4f9c</t>
         </is>
       </c>
       <c r="AU264" t="inlineStr">
@@ -43025,7 +43025,7 @@
       <c r="AW264" t="inlineStr"/>
       <c r="AX264" t="inlineStr">
         <is>
-          <t>2026-05-20T00:13:57+00:00</t>
+          <t>2026-05-20T00:48:39+00:00</t>
         </is>
       </c>
       <c r="AY264" t="inlineStr">
@@ -43169,7 +43169,7 @@
       </c>
       <c r="AT265" t="inlineStr">
         <is>
-          <t>batch_164c8f2ccaa64eaf</t>
+          <t>batch_4e3853438a5d4f9c</t>
         </is>
       </c>
       <c r="AU265" t="inlineStr">
@@ -43185,7 +43185,7 @@
       <c r="AW265" t="inlineStr"/>
       <c r="AX265" t="inlineStr">
         <is>
-          <t>2026-05-20T00:13:57+00:00</t>
+          <t>2026-05-20T00:48:39+00:00</t>
         </is>
       </c>
       <c r="AY265" t="inlineStr">
@@ -43329,7 +43329,7 @@
       </c>
       <c r="AT266" t="inlineStr">
         <is>
-          <t>batch_164c8f2ccaa64eaf</t>
+          <t>batch_4e3853438a5d4f9c</t>
         </is>
       </c>
       <c r="AU266" t="inlineStr">
@@ -43345,7 +43345,7 @@
       <c r="AW266" t="inlineStr"/>
       <c r="AX266" t="inlineStr">
         <is>
-          <t>2026-05-20T00:13:57+00:00</t>
+          <t>2026-05-20T00:48:39+00:00</t>
         </is>
       </c>
       <c r="AY266" t="inlineStr">
@@ -43489,7 +43489,7 @@
       </c>
       <c r="AT267" t="inlineStr">
         <is>
-          <t>batch_164c8f2ccaa64eaf</t>
+          <t>batch_4e3853438a5d4f9c</t>
         </is>
       </c>
       <c r="AU267" t="inlineStr">
@@ -43505,7 +43505,7 @@
       <c r="AW267" t="inlineStr"/>
       <c r="AX267" t="inlineStr">
         <is>
-          <t>2026-05-20T00:13:57+00:00</t>
+          <t>2026-05-20T00:48:39+00:00</t>
         </is>
       </c>
       <c r="AY267" t="inlineStr">
@@ -43649,7 +43649,7 @@
       </c>
       <c r="AT268" t="inlineStr">
         <is>
-          <t>batch_164c8f2ccaa64eaf</t>
+          <t>batch_4e3853438a5d4f9c</t>
         </is>
       </c>
       <c r="AU268" t="inlineStr">
@@ -43665,7 +43665,7 @@
       <c r="AW268" t="inlineStr"/>
       <c r="AX268" t="inlineStr">
         <is>
-          <t>2026-05-20T00:13:57+00:00</t>
+          <t>2026-05-20T00:48:39+00:00</t>
         </is>
       </c>
       <c r="AY268" t="inlineStr">
@@ -43809,7 +43809,7 @@
       </c>
       <c r="AT269" t="inlineStr">
         <is>
-          <t>batch_164c8f2ccaa64eaf</t>
+          <t>batch_4e3853438a5d4f9c</t>
         </is>
       </c>
       <c r="AU269" t="inlineStr">
@@ -43825,7 +43825,7 @@
       <c r="AW269" t="inlineStr"/>
       <c r="AX269" t="inlineStr">
         <is>
-          <t>2026-05-20T00:13:57+00:00</t>
+          <t>2026-05-20T00:48:39+00:00</t>
         </is>
       </c>
       <c r="AY269" t="inlineStr">
@@ -43969,7 +43969,7 @@
       </c>
       <c r="AT270" t="inlineStr">
         <is>
-          <t>batch_164c8f2ccaa64eaf</t>
+          <t>batch_4e3853438a5d4f9c</t>
         </is>
       </c>
       <c r="AU270" t="inlineStr">
@@ -43985,7 +43985,7 @@
       <c r="AW270" t="inlineStr"/>
       <c r="AX270" t="inlineStr">
         <is>
-          <t>2026-05-20T00:13:57+00:00</t>
+          <t>2026-05-20T00:48:39+00:00</t>
         </is>
       </c>
       <c r="AY270" t="inlineStr">
@@ -44129,7 +44129,7 @@
       </c>
       <c r="AT271" t="inlineStr">
         <is>
-          <t>batch_164c8f2ccaa64eaf</t>
+          <t>batch_4e3853438a5d4f9c</t>
         </is>
       </c>
       <c r="AU271" t="inlineStr">
@@ -44145,7 +44145,7 @@
       <c r="AW271" t="inlineStr"/>
       <c r="AX271" t="inlineStr">
         <is>
-          <t>2026-05-20T00:13:57+00:00</t>
+          <t>2026-05-20T00:48:39+00:00</t>
         </is>
       </c>
       <c r="AY271" t="inlineStr">
@@ -44289,7 +44289,7 @@
       </c>
       <c r="AT272" t="inlineStr">
         <is>
-          <t>batch_164c8f2ccaa64eaf</t>
+          <t>batch_4e3853438a5d4f9c</t>
         </is>
       </c>
       <c r="AU272" t="inlineStr">
@@ -44305,7 +44305,7 @@
       <c r="AW272" t="inlineStr"/>
       <c r="AX272" t="inlineStr">
         <is>
-          <t>2026-05-20T00:13:57+00:00</t>
+          <t>2026-05-20T00:48:39+00:00</t>
         </is>
       </c>
       <c r="AY272" t="inlineStr">
@@ -44449,7 +44449,7 @@
       </c>
       <c r="AT273" t="inlineStr">
         <is>
-          <t>batch_164c8f2ccaa64eaf</t>
+          <t>batch_4e3853438a5d4f9c</t>
         </is>
       </c>
       <c r="AU273" t="inlineStr">
@@ -44465,7 +44465,7 @@
       <c r="AW273" t="inlineStr"/>
       <c r="AX273" t="inlineStr">
         <is>
-          <t>2026-05-20T00:13:57+00:00</t>
+          <t>2026-05-20T00:48:39+00:00</t>
         </is>
       </c>
       <c r="AY273" t="inlineStr">
@@ -44609,7 +44609,7 @@
       </c>
       <c r="AT274" t="inlineStr">
         <is>
-          <t>batch_164c8f2ccaa64eaf</t>
+          <t>batch_4e3853438a5d4f9c</t>
         </is>
       </c>
       <c r="AU274" t="inlineStr">
@@ -44625,7 +44625,7 @@
       <c r="AW274" t="inlineStr"/>
       <c r="AX274" t="inlineStr">
         <is>
-          <t>2026-05-20T00:13:57+00:00</t>
+          <t>2026-05-20T00:48:39+00:00</t>
         </is>
       </c>
       <c r="AY274" t="inlineStr">
@@ -44769,7 +44769,7 @@
       </c>
       <c r="AT275" t="inlineStr">
         <is>
-          <t>batch_164c8f2ccaa64eaf</t>
+          <t>batch_4e3853438a5d4f9c</t>
         </is>
       </c>
       <c r="AU275" t="inlineStr">
@@ -44785,7 +44785,7 @@
       <c r="AW275" t="inlineStr"/>
       <c r="AX275" t="inlineStr">
         <is>
-          <t>2026-05-20T00:13:57+00:00</t>
+          <t>2026-05-20T00:48:39+00:00</t>
         </is>
       </c>
       <c r="AY275" t="inlineStr">
@@ -44929,7 +44929,7 @@
       </c>
       <c r="AT276" t="inlineStr">
         <is>
-          <t>batch_164c8f2ccaa64eaf</t>
+          <t>batch_4e3853438a5d4f9c</t>
         </is>
       </c>
       <c r="AU276" t="inlineStr">
@@ -44945,7 +44945,7 @@
       <c r="AW276" t="inlineStr"/>
       <c r="AX276" t="inlineStr">
         <is>
-          <t>2026-05-20T00:13:57+00:00</t>
+          <t>2026-05-20T00:48:39+00:00</t>
         </is>
       </c>
       <c r="AY276" t="inlineStr">
@@ -45089,7 +45089,7 @@
       </c>
       <c r="AT277" t="inlineStr">
         <is>
-          <t>batch_164c8f2ccaa64eaf</t>
+          <t>batch_4e3853438a5d4f9c</t>
         </is>
       </c>
       <c r="AU277" t="inlineStr">
@@ -45105,7 +45105,7 @@
       <c r="AW277" t="inlineStr"/>
       <c r="AX277" t="inlineStr">
         <is>
-          <t>2026-05-20T00:13:57+00:00</t>
+          <t>2026-05-20T00:48:39+00:00</t>
         </is>
       </c>
       <c r="AY277" t="inlineStr">
@@ -45249,7 +45249,7 @@
       </c>
       <c r="AT278" t="inlineStr">
         <is>
-          <t>batch_164c8f2ccaa64eaf</t>
+          <t>batch_4e3853438a5d4f9c</t>
         </is>
       </c>
       <c r="AU278" t="inlineStr">
@@ -45265,7 +45265,7 @@
       <c r="AW278" t="inlineStr"/>
       <c r="AX278" t="inlineStr">
         <is>
-          <t>2026-05-20T00:13:57+00:00</t>
+          <t>2026-05-20T00:48:39+00:00</t>
         </is>
       </c>
       <c r="AY278" t="inlineStr">
@@ -45409,7 +45409,7 @@
       </c>
       <c r="AT279" t="inlineStr">
         <is>
-          <t>batch_164c8f2ccaa64eaf</t>
+          <t>batch_4e3853438a5d4f9c</t>
         </is>
       </c>
       <c r="AU279" t="inlineStr">
@@ -45425,7 +45425,7 @@
       <c r="AW279" t="inlineStr"/>
       <c r="AX279" t="inlineStr">
         <is>
-          <t>2026-05-20T00:13:57+00:00</t>
+          <t>2026-05-20T00:48:39+00:00</t>
         </is>
       </c>
       <c r="AY279" t="inlineStr">
@@ -45569,7 +45569,7 @@
       </c>
       <c r="AT280" t="inlineStr">
         <is>
-          <t>batch_164c8f2ccaa64eaf</t>
+          <t>batch_4e3853438a5d4f9c</t>
         </is>
       </c>
       <c r="AU280" t="inlineStr">
@@ -45585,7 +45585,7 @@
       <c r="AW280" t="inlineStr"/>
       <c r="AX280" t="inlineStr">
         <is>
-          <t>2026-05-20T00:13:57+00:00</t>
+          <t>2026-05-20T00:48:39+00:00</t>
         </is>
       </c>
       <c r="AY280" t="inlineStr">
@@ -45729,7 +45729,7 @@
       </c>
       <c r="AT281" t="inlineStr">
         <is>
-          <t>batch_164c8f2ccaa64eaf</t>
+          <t>batch_4e3853438a5d4f9c</t>
         </is>
       </c>
       <c r="AU281" t="inlineStr">
@@ -45745,7 +45745,7 @@
       <c r="AW281" t="inlineStr"/>
       <c r="AX281" t="inlineStr">
         <is>
-          <t>2026-05-20T00:13:57+00:00</t>
+          <t>2026-05-20T00:48:39+00:00</t>
         </is>
       </c>
       <c r="AY281" t="inlineStr">
@@ -45889,7 +45889,7 @@
       </c>
       <c r="AT282" t="inlineStr">
         <is>
-          <t>batch_164c8f2ccaa64eaf</t>
+          <t>batch_4e3853438a5d4f9c</t>
         </is>
       </c>
       <c r="AU282" t="inlineStr">
@@ -45905,7 +45905,7 @@
       <c r="AW282" t="inlineStr"/>
       <c r="AX282" t="inlineStr">
         <is>
-          <t>2026-05-20T00:13:57+00:00</t>
+          <t>2026-05-20T00:48:39+00:00</t>
         </is>
       </c>
       <c r="AY282" t="inlineStr">
@@ -46049,7 +46049,7 @@
       </c>
       <c r="AT283" t="inlineStr">
         <is>
-          <t>batch_164c8f2ccaa64eaf</t>
+          <t>batch_4e3853438a5d4f9c</t>
         </is>
       </c>
       <c r="AU283" t="inlineStr">
@@ -46065,7 +46065,7 @@
       <c r="AW283" t="inlineStr"/>
       <c r="AX283" t="inlineStr">
         <is>
-          <t>2026-05-20T00:13:57+00:00</t>
+          <t>2026-05-20T00:48:39+00:00</t>
         </is>
       </c>
       <c r="AY283" t="inlineStr">
@@ -46209,7 +46209,7 @@
       </c>
       <c r="AT284" t="inlineStr">
         <is>
-          <t>batch_164c8f2ccaa64eaf</t>
+          <t>batch_4e3853438a5d4f9c</t>
         </is>
       </c>
       <c r="AU284" t="inlineStr">
@@ -46225,7 +46225,7 @@
       <c r="AW284" t="inlineStr"/>
       <c r="AX284" t="inlineStr">
         <is>
-          <t>2026-05-20T00:13:57+00:00</t>
+          <t>2026-05-20T00:48:39+00:00</t>
         </is>
       </c>
       <c r="AY284" t="inlineStr">
@@ -46369,7 +46369,7 @@
       </c>
       <c r="AT285" t="inlineStr">
         <is>
-          <t>batch_164c8f2ccaa64eaf</t>
+          <t>batch_4e3853438a5d4f9c</t>
         </is>
       </c>
       <c r="AU285" t="inlineStr">
@@ -46385,7 +46385,7 @@
       <c r="AW285" t="inlineStr"/>
       <c r="AX285" t="inlineStr">
         <is>
-          <t>2026-05-20T00:13:57+00:00</t>
+          <t>2026-05-20T00:48:39+00:00</t>
         </is>
       </c>
       <c r="AY285" t="inlineStr">
@@ -46529,7 +46529,7 @@
       </c>
       <c r="AT286" t="inlineStr">
         <is>
-          <t>batch_164c8f2ccaa64eaf</t>
+          <t>batch_4e3853438a5d4f9c</t>
         </is>
       </c>
       <c r="AU286" t="inlineStr">
@@ -46545,7 +46545,7 @@
       <c r="AW286" t="inlineStr"/>
       <c r="AX286" t="inlineStr">
         <is>
-          <t>2026-05-20T00:13:57+00:00</t>
+          <t>2026-05-20T00:48:39+00:00</t>
         </is>
       </c>
       <c r="AY286" t="inlineStr">
@@ -46689,7 +46689,7 @@
       </c>
       <c r="AT287" t="inlineStr">
         <is>
-          <t>batch_164c8f2ccaa64eaf</t>
+          <t>batch_4e3853438a5d4f9c</t>
         </is>
       </c>
       <c r="AU287" t="inlineStr">
@@ -46705,7 +46705,7 @@
       <c r="AW287" t="inlineStr"/>
       <c r="AX287" t="inlineStr">
         <is>
-          <t>2026-05-20T00:13:57+00:00</t>
+          <t>2026-05-20T00:48:39+00:00</t>
         </is>
       </c>
       <c r="AY287" t="inlineStr">
@@ -46849,7 +46849,7 @@
       </c>
       <c r="AT288" t="inlineStr">
         <is>
-          <t>batch_164c8f2ccaa64eaf</t>
+          <t>batch_4e3853438a5d4f9c</t>
         </is>
       </c>
       <c r="AU288" t="inlineStr">
@@ -46865,7 +46865,7 @@
       <c r="AW288" t="inlineStr"/>
       <c r="AX288" t="inlineStr">
         <is>
-          <t>2026-05-20T00:13:57+00:00</t>
+          <t>2026-05-20T00:48:39+00:00</t>
         </is>
       </c>
       <c r="AY288" t="inlineStr">
@@ -47009,7 +47009,7 @@
       </c>
       <c r="AT289" t="inlineStr">
         <is>
-          <t>batch_164c8f2ccaa64eaf</t>
+          <t>batch_4e3853438a5d4f9c</t>
         </is>
       </c>
       <c r="AU289" t="inlineStr">
@@ -47025,7 +47025,7 @@
       <c r="AW289" t="inlineStr"/>
       <c r="AX289" t="inlineStr">
         <is>
-          <t>2026-05-20T00:13:57+00:00</t>
+          <t>2026-05-20T00:48:39+00:00</t>
         </is>
       </c>
       <c r="AY289" t="inlineStr">
@@ -47169,7 +47169,7 @@
       </c>
       <c r="AT290" t="inlineStr">
         <is>
-          <t>batch_164c8f2ccaa64eaf</t>
+          <t>batch_4e3853438a5d4f9c</t>
         </is>
       </c>
       <c r="AU290" t="inlineStr">
@@ -47185,7 +47185,7 @@
       <c r="AW290" t="inlineStr"/>
       <c r="AX290" t="inlineStr">
         <is>
-          <t>2026-05-20T00:13:57+00:00</t>
+          <t>2026-05-20T00:48:39+00:00</t>
         </is>
       </c>
       <c r="AY290" t="inlineStr">
@@ -47329,7 +47329,7 @@
       </c>
       <c r="AT291" t="inlineStr">
         <is>
-          <t>batch_164c8f2ccaa64eaf</t>
+          <t>batch_4e3853438a5d4f9c</t>
         </is>
       </c>
       <c r="AU291" t="inlineStr">
@@ -47345,7 +47345,7 @@
       <c r="AW291" t="inlineStr"/>
       <c r="AX291" t="inlineStr">
         <is>
-          <t>2026-05-20T00:13:57+00:00</t>
+          <t>2026-05-20T00:48:39+00:00</t>
         </is>
       </c>
       <c r="AY291" t="inlineStr">
@@ -47489,7 +47489,7 @@
       </c>
       <c r="AT292" t="inlineStr">
         <is>
-          <t>batch_164c8f2ccaa64eaf</t>
+          <t>batch_4e3853438a5d4f9c</t>
         </is>
       </c>
       <c r="AU292" t="inlineStr">
@@ -47505,7 +47505,7 @@
       <c r="AW292" t="inlineStr"/>
       <c r="AX292" t="inlineStr">
         <is>
-          <t>2026-05-20T00:13:57+00:00</t>
+          <t>2026-05-20T00:48:39+00:00</t>
         </is>
       </c>
       <c r="AY292" t="inlineStr">
@@ -47649,7 +47649,7 @@
       </c>
       <c r="AT293" t="inlineStr">
         <is>
-          <t>batch_164c8f2ccaa64eaf</t>
+          <t>batch_4e3853438a5d4f9c</t>
         </is>
       </c>
       <c r="AU293" t="inlineStr">
@@ -47665,7 +47665,7 @@
       <c r="AW293" t="inlineStr"/>
       <c r="AX293" t="inlineStr">
         <is>
-          <t>2026-05-20T00:13:57+00:00</t>
+          <t>2026-05-20T00:48:39+00:00</t>
         </is>
       </c>
       <c r="AY293" t="inlineStr">
@@ -47809,7 +47809,7 @@
       </c>
       <c r="AT294" t="inlineStr">
         <is>
-          <t>batch_164c8f2ccaa64eaf</t>
+          <t>batch_4e3853438a5d4f9c</t>
         </is>
       </c>
       <c r="AU294" t="inlineStr">
@@ -47825,7 +47825,7 @@
       <c r="AW294" t="inlineStr"/>
       <c r="AX294" t="inlineStr">
         <is>
-          <t>2026-05-20T00:13:57+00:00</t>
+          <t>2026-05-20T00:48:39+00:00</t>
         </is>
       </c>
       <c r="AY294" t="inlineStr">
@@ -47969,7 +47969,7 @@
       </c>
       <c r="AT295" t="inlineStr">
         <is>
-          <t>batch_164c8f2ccaa64eaf</t>
+          <t>batch_4e3853438a5d4f9c</t>
         </is>
       </c>
       <c r="AU295" t="inlineStr">
@@ -47985,7 +47985,7 @@
       <c r="AW295" t="inlineStr"/>
       <c r="AX295" t="inlineStr">
         <is>
-          <t>2026-05-20T00:13:57+00:00</t>
+          <t>2026-05-20T00:48:39+00:00</t>
         </is>
       </c>
       <c r="AY295" t="inlineStr">
@@ -48129,7 +48129,7 @@
       </c>
       <c r="AT296" t="inlineStr">
         <is>
-          <t>batch_164c8f2ccaa64eaf</t>
+          <t>batch_4e3853438a5d4f9c</t>
         </is>
       </c>
       <c r="AU296" t="inlineStr">
@@ -48145,7 +48145,7 @@
       <c r="AW296" t="inlineStr"/>
       <c r="AX296" t="inlineStr">
         <is>
-          <t>2026-05-20T00:13:57+00:00</t>
+          <t>2026-05-20T00:48:39+00:00</t>
         </is>
       </c>
       <c r="AY296" t="inlineStr">
@@ -48289,7 +48289,7 @@
       </c>
       <c r="AT297" t="inlineStr">
         <is>
-          <t>batch_164c8f2ccaa64eaf</t>
+          <t>batch_4e3853438a5d4f9c</t>
         </is>
       </c>
       <c r="AU297" t="inlineStr">
@@ -48305,7 +48305,7 @@
       <c r="AW297" t="inlineStr"/>
       <c r="AX297" t="inlineStr">
         <is>
-          <t>2026-05-20T00:13:57+00:00</t>
+          <t>2026-05-20T00:48:39+00:00</t>
         </is>
       </c>
       <c r="AY297" t="inlineStr">
@@ -48449,7 +48449,7 @@
       </c>
       <c r="AT298" t="inlineStr">
         <is>
-          <t>batch_164c8f2ccaa64eaf</t>
+          <t>batch_4e3853438a5d4f9c</t>
         </is>
       </c>
       <c r="AU298" t="inlineStr">
@@ -48465,7 +48465,7 @@
       <c r="AW298" t="inlineStr"/>
       <c r="AX298" t="inlineStr">
         <is>
-          <t>2026-05-20T00:13:57+00:00</t>
+          <t>2026-05-20T00:48:39+00:00</t>
         </is>
       </c>
       <c r="AY298" t="inlineStr">
@@ -48609,7 +48609,7 @@
       </c>
       <c r="AT299" t="inlineStr">
         <is>
-          <t>batch_164c8f2ccaa64eaf</t>
+          <t>batch_4e3853438a5d4f9c</t>
         </is>
       </c>
       <c r="AU299" t="inlineStr">
@@ -48625,7 +48625,7 @@
       <c r="AW299" t="inlineStr"/>
       <c r="AX299" t="inlineStr">
         <is>
-          <t>2026-05-20T00:13:57+00:00</t>
+          <t>2026-05-20T00:48:39+00:00</t>
         </is>
       </c>
       <c r="AY299" t="inlineStr">
@@ -48769,7 +48769,7 @@
       </c>
       <c r="AT300" t="inlineStr">
         <is>
-          <t>batch_164c8f2ccaa64eaf</t>
+          <t>batch_4e3853438a5d4f9c</t>
         </is>
       </c>
       <c r="AU300" t="inlineStr">
@@ -48785,7 +48785,7 @@
       <c r="AW300" t="inlineStr"/>
       <c r="AX300" t="inlineStr">
         <is>
-          <t>2026-05-20T00:13:57+00:00</t>
+          <t>2026-05-20T00:48:39+00:00</t>
         </is>
       </c>
       <c r="AY300" t="inlineStr">
@@ -48929,7 +48929,7 @@
       </c>
       <c r="AT301" t="inlineStr">
         <is>
-          <t>batch_164c8f2ccaa64eaf</t>
+          <t>batch_4e3853438a5d4f9c</t>
         </is>
       </c>
       <c r="AU301" t="inlineStr">
@@ -48945,7 +48945,7 @@
       <c r="AW301" t="inlineStr"/>
       <c r="AX301" t="inlineStr">
         <is>
-          <t>2026-05-20T00:13:57+00:00</t>
+          <t>2026-05-20T00:48:39+00:00</t>
         </is>
       </c>
       <c r="AY301" t="inlineStr">
@@ -49089,7 +49089,7 @@
       </c>
       <c r="AT302" t="inlineStr">
         <is>
-          <t>batch_164c8f2ccaa64eaf</t>
+          <t>batch_4e3853438a5d4f9c</t>
         </is>
       </c>
       <c r="AU302" t="inlineStr">
@@ -49105,7 +49105,7 @@
       <c r="AW302" t="inlineStr"/>
       <c r="AX302" t="inlineStr">
         <is>
-          <t>2026-05-20T00:13:57+00:00</t>
+          <t>2026-05-20T00:48:39+00:00</t>
         </is>
       </c>
       <c r="AY302" t="inlineStr">
@@ -49249,7 +49249,7 @@
       </c>
       <c r="AT303" t="inlineStr">
         <is>
-          <t>batch_164c8f2ccaa64eaf</t>
+          <t>batch_4e3853438a5d4f9c</t>
         </is>
       </c>
       <c r="AU303" t="inlineStr">
@@ -49265,7 +49265,7 @@
       <c r="AW303" t="inlineStr"/>
       <c r="AX303" t="inlineStr">
         <is>
-          <t>2026-05-20T00:13:57+00:00</t>
+          <t>2026-05-20T00:48:39+00:00</t>
         </is>
       </c>
       <c r="AY303" t="inlineStr">
@@ -49409,7 +49409,7 @@
       </c>
       <c r="AT304" t="inlineStr">
         <is>
-          <t>batch_164c8f2ccaa64eaf</t>
+          <t>batch_4e3853438a5d4f9c</t>
         </is>
       </c>
       <c r="AU304" t="inlineStr">
@@ -49425,7 +49425,7 @@
       <c r="AW304" t="inlineStr"/>
       <c r="AX304" t="inlineStr">
         <is>
-          <t>2026-05-20T00:13:57+00:00</t>
+          <t>2026-05-20T00:48:39+00:00</t>
         </is>
       </c>
       <c r="AY304" t="inlineStr">
@@ -49569,7 +49569,7 @@
       </c>
       <c r="AT305" t="inlineStr">
         <is>
-          <t>batch_164c8f2ccaa64eaf</t>
+          <t>batch_4e3853438a5d4f9c</t>
         </is>
       </c>
       <c r="AU305" t="inlineStr">
@@ -49585,7 +49585,7 @@
       <c r="AW305" t="inlineStr"/>
       <c r="AX305" t="inlineStr">
         <is>
-          <t>2026-05-20T00:13:57+00:00</t>
+          <t>2026-05-20T00:48:39+00:00</t>
         </is>
       </c>
       <c r="AY305" t="inlineStr">
@@ -49729,7 +49729,7 @@
       </c>
       <c r="AT306" t="inlineStr">
         <is>
-          <t>batch_164c8f2ccaa64eaf</t>
+          <t>batch_4e3853438a5d4f9c</t>
         </is>
       </c>
       <c r="AU306" t="inlineStr">
@@ -49745,7 +49745,7 @@
       <c r="AW306" t="inlineStr"/>
       <c r="AX306" t="inlineStr">
         <is>
-          <t>2026-05-20T00:13:57+00:00</t>
+          <t>2026-05-20T00:48:39+00:00</t>
         </is>
       </c>
       <c r="AY306" t="inlineStr">
@@ -49889,7 +49889,7 @@
       </c>
       <c r="AT307" t="inlineStr">
         <is>
-          <t>batch_164c8f2ccaa64eaf</t>
+          <t>batch_4e3853438a5d4f9c</t>
         </is>
       </c>
       <c r="AU307" t="inlineStr">
@@ -49905,7 +49905,7 @@
       <c r="AW307" t="inlineStr"/>
       <c r="AX307" t="inlineStr">
         <is>
-          <t>2026-05-20T00:13:57+00:00</t>
+          <t>2026-05-20T00:48:39+00:00</t>
         </is>
       </c>
       <c r="AY307" t="inlineStr">
@@ -50049,7 +50049,7 @@
       </c>
       <c r="AT308" t="inlineStr">
         <is>
-          <t>batch_164c8f2ccaa64eaf</t>
+          <t>batch_4e3853438a5d4f9c</t>
         </is>
       </c>
       <c r="AU308" t="inlineStr">
@@ -50065,7 +50065,7 @@
       <c r="AW308" t="inlineStr"/>
       <c r="AX308" t="inlineStr">
         <is>
-          <t>2026-05-20T00:13:57+00:00</t>
+          <t>2026-05-20T00:48:39+00:00</t>
         </is>
       </c>
       <c r="AY308" t="inlineStr">
@@ -50209,7 +50209,7 @@
       </c>
       <c r="AT309" t="inlineStr">
         <is>
-          <t>batch_164c8f2ccaa64eaf</t>
+          <t>batch_4e3853438a5d4f9c</t>
         </is>
       </c>
       <c r="AU309" t="inlineStr">
@@ -50225,7 +50225,7 @@
       <c r="AW309" t="inlineStr"/>
       <c r="AX309" t="inlineStr">
         <is>
-          <t>2026-05-20T00:13:57+00:00</t>
+          <t>2026-05-20T00:48:39+00:00</t>
         </is>
       </c>
       <c r="AY309" t="inlineStr">
@@ -50369,7 +50369,7 @@
       </c>
       <c r="AT310" t="inlineStr">
         <is>
-          <t>batch_164c8f2ccaa64eaf</t>
+          <t>batch_4e3853438a5d4f9c</t>
         </is>
       </c>
       <c r="AU310" t="inlineStr">
@@ -50385,7 +50385,7 @@
       <c r="AW310" t="inlineStr"/>
       <c r="AX310" t="inlineStr">
         <is>
-          <t>2026-05-20T00:13:57+00:00</t>
+          <t>2026-05-20T00:48:39+00:00</t>
         </is>
       </c>
       <c r="AY310" t="inlineStr">
@@ -50529,7 +50529,7 @@
       </c>
       <c r="AT311" t="inlineStr">
         <is>
-          <t>batch_164c8f2ccaa64eaf</t>
+          <t>batch_4e3853438a5d4f9c</t>
         </is>
       </c>
       <c r="AU311" t="inlineStr">
@@ -50545,7 +50545,7 @@
       <c r="AW311" t="inlineStr"/>
       <c r="AX311" t="inlineStr">
         <is>
-          <t>2026-05-20T00:13:57+00:00</t>
+          <t>2026-05-20T00:48:39+00:00</t>
         </is>
       </c>
       <c r="AY311" t="inlineStr">
@@ -50689,7 +50689,7 @@
       </c>
       <c r="AT312" t="inlineStr">
         <is>
-          <t>batch_164c8f2ccaa64eaf</t>
+          <t>batch_4e3853438a5d4f9c</t>
         </is>
       </c>
       <c r="AU312" t="inlineStr">
@@ -50705,7 +50705,7 @@
       <c r="AW312" t="inlineStr"/>
       <c r="AX312" t="inlineStr">
         <is>
-          <t>2026-05-20T00:13:57+00:00</t>
+          <t>2026-05-20T00:48:39+00:00</t>
         </is>
       </c>
       <c r="AY312" t="inlineStr">
@@ -50849,7 +50849,7 @@
       </c>
       <c r="AT313" t="inlineStr">
         <is>
-          <t>batch_164c8f2ccaa64eaf</t>
+          <t>batch_4e3853438a5d4f9c</t>
         </is>
       </c>
       <c r="AU313" t="inlineStr">
@@ -50865,7 +50865,7 @@
       <c r="AW313" t="inlineStr"/>
       <c r="AX313" t="inlineStr">
         <is>
-          <t>2026-05-20T00:13:57+00:00</t>
+          <t>2026-05-20T00:48:39+00:00</t>
         </is>
       </c>
       <c r="AY313" t="inlineStr">
@@ -51009,7 +51009,7 @@
       </c>
       <c r="AT314" t="inlineStr">
         <is>
-          <t>batch_164c8f2ccaa64eaf</t>
+          <t>batch_4e3853438a5d4f9c</t>
         </is>
       </c>
       <c r="AU314" t="inlineStr">
@@ -51025,7 +51025,7 @@
       <c r="AW314" t="inlineStr"/>
       <c r="AX314" t="inlineStr">
         <is>
-          <t>2026-05-20T00:13:57+00:00</t>
+          <t>2026-05-20T00:48:39+00:00</t>
         </is>
       </c>
       <c r="AY314" t="inlineStr">
@@ -51169,7 +51169,7 @@
       </c>
       <c r="AT315" t="inlineStr">
         <is>
-          <t>batch_164c8f2ccaa64eaf</t>
+          <t>batch_4e3853438a5d4f9c</t>
         </is>
       </c>
       <c r="AU315" t="inlineStr">
@@ -51185,7 +51185,7 @@
       <c r="AW315" t="inlineStr"/>
       <c r="AX315" t="inlineStr">
         <is>
-          <t>2026-05-20T00:13:57+00:00</t>
+          <t>2026-05-20T00:48:39+00:00</t>
         </is>
       </c>
       <c r="AY315" t="inlineStr">
@@ -51329,7 +51329,7 @@
       </c>
       <c r="AT316" t="inlineStr">
         <is>
-          <t>batch_164c8f2ccaa64eaf</t>
+          <t>batch_4e3853438a5d4f9c</t>
         </is>
       </c>
       <c r="AU316" t="inlineStr">
@@ -51345,7 +51345,7 @@
       <c r="AW316" t="inlineStr"/>
       <c r="AX316" t="inlineStr">
         <is>
-          <t>2026-05-20T00:13:57+00:00</t>
+          <t>2026-05-20T00:48:39+00:00</t>
         </is>
       </c>
       <c r="AY316" t="inlineStr">
@@ -51489,7 +51489,7 @@
       </c>
       <c r="AT317" t="inlineStr">
         <is>
-          <t>batch_164c8f2ccaa64eaf</t>
+          <t>batch_4e3853438a5d4f9c</t>
         </is>
       </c>
       <c r="AU317" t="inlineStr">
@@ -51505,7 +51505,7 @@
       <c r="AW317" t="inlineStr"/>
       <c r="AX317" t="inlineStr">
         <is>
-          <t>2026-05-20T00:13:57+00:00</t>
+          <t>2026-05-20T00:48:39+00:00</t>
         </is>
       </c>
       <c r="AY317" t="inlineStr">
@@ -51649,7 +51649,7 @@
       </c>
       <c r="AT318" t="inlineStr">
         <is>
-          <t>batch_164c8f2ccaa64eaf</t>
+          <t>batch_4e3853438a5d4f9c</t>
         </is>
       </c>
       <c r="AU318" t="inlineStr">
@@ -51665,7 +51665,7 @@
       <c r="AW318" t="inlineStr"/>
       <c r="AX318" t="inlineStr">
         <is>
-          <t>2026-05-20T00:13:57+00:00</t>
+          <t>2026-05-20T00:48:39+00:00</t>
         </is>
       </c>
       <c r="AY318" t="inlineStr">
@@ -51809,7 +51809,7 @@
       </c>
       <c r="AT319" t="inlineStr">
         <is>
-          <t>batch_164c8f2ccaa64eaf</t>
+          <t>batch_4e3853438a5d4f9c</t>
         </is>
       </c>
       <c r="AU319" t="inlineStr">
@@ -51825,7 +51825,7 @@
       <c r="AW319" t="inlineStr"/>
       <c r="AX319" t="inlineStr">
         <is>
-          <t>2026-05-20T00:13:57+00:00</t>
+          <t>2026-05-20T00:48:39+00:00</t>
         </is>
       </c>
       <c r="AY319" t="inlineStr">
@@ -51969,7 +51969,7 @@
       </c>
       <c r="AT320" t="inlineStr">
         <is>
-          <t>batch_164c8f2ccaa64eaf</t>
+          <t>batch_4e3853438a5d4f9c</t>
         </is>
       </c>
       <c r="AU320" t="inlineStr">
@@ -51985,7 +51985,7 @@
       <c r="AW320" t="inlineStr"/>
       <c r="AX320" t="inlineStr">
         <is>
-          <t>2026-05-20T00:13:57+00:00</t>
+          <t>2026-05-20T00:48:39+00:00</t>
         </is>
       </c>
       <c r="AY320" t="inlineStr">
@@ -52129,7 +52129,7 @@
       </c>
       <c r="AT321" t="inlineStr">
         <is>
-          <t>batch_164c8f2ccaa64eaf</t>
+          <t>batch_4e3853438a5d4f9c</t>
         </is>
       </c>
       <c r="AU321" t="inlineStr">
@@ -52145,7 +52145,7 @@
       <c r="AW321" t="inlineStr"/>
       <c r="AX321" t="inlineStr">
         <is>
-          <t>2026-05-20T00:13:57+00:00</t>
+          <t>2026-05-20T00:48:39+00:00</t>
         </is>
       </c>
       <c r="AY321" t="inlineStr">
@@ -52289,7 +52289,7 @@
       </c>
       <c r="AT322" t="inlineStr">
         <is>
-          <t>batch_164c8f2ccaa64eaf</t>
+          <t>batch_4e3853438a5d4f9c</t>
         </is>
       </c>
       <c r="AU322" t="inlineStr">
@@ -52305,7 +52305,7 @@
       <c r="AW322" t="inlineStr"/>
       <c r="AX322" t="inlineStr">
         <is>
-          <t>2026-05-20T00:13:57+00:00</t>
+          <t>2026-05-20T00:48:39+00:00</t>
         </is>
       </c>
       <c r="AY322" t="inlineStr">
@@ -52449,7 +52449,7 @@
       </c>
       <c r="AT323" t="inlineStr">
         <is>
-          <t>batch_164c8f2ccaa64eaf</t>
+          <t>batch_4e3853438a5d4f9c</t>
         </is>
       </c>
       <c r="AU323" t="inlineStr">
@@ -52465,7 +52465,7 @@
       <c r="AW323" t="inlineStr"/>
       <c r="AX323" t="inlineStr">
         <is>
-          <t>2026-05-20T00:13:57+00:00</t>
+          <t>2026-05-20T00:48:39+00:00</t>
         </is>
       </c>
       <c r="AY323" t="inlineStr">
@@ -52609,7 +52609,7 @@
       </c>
       <c r="AT324" t="inlineStr">
         <is>
-          <t>batch_164c8f2ccaa64eaf</t>
+          <t>batch_4e3853438a5d4f9c</t>
         </is>
       </c>
       <c r="AU324" t="inlineStr">
@@ -52625,7 +52625,7 @@
       <c r="AW324" t="inlineStr"/>
       <c r="AX324" t="inlineStr">
         <is>
-          <t>2026-05-20T00:13:57+00:00</t>
+          <t>2026-05-20T00:48:39+00:00</t>
         </is>
       </c>
       <c r="AY324" t="inlineStr">
@@ -52769,7 +52769,7 @@
       </c>
       <c r="AT325" t="inlineStr">
         <is>
-          <t>batch_164c8f2ccaa64eaf</t>
+          <t>batch_4e3853438a5d4f9c</t>
         </is>
       </c>
       <c r="AU325" t="inlineStr">
@@ -52785,7 +52785,7 @@
       <c r="AW325" t="inlineStr"/>
       <c r="AX325" t="inlineStr">
         <is>
-          <t>2026-05-20T00:13:57+00:00</t>
+          <t>2026-05-20T00:48:39+00:00</t>
         </is>
       </c>
       <c r="AY325" t="inlineStr">
@@ -52929,7 +52929,7 @@
       </c>
       <c r="AT326" t="inlineStr">
         <is>
-          <t>batch_164c8f2ccaa64eaf</t>
+          <t>batch_4e3853438a5d4f9c</t>
         </is>
       </c>
       <c r="AU326" t="inlineStr">
@@ -52945,7 +52945,7 @@
       <c r="AW326" t="inlineStr"/>
       <c r="AX326" t="inlineStr">
         <is>
-          <t>2026-05-20T00:13:57+00:00</t>
+          <t>2026-05-20T00:48:39+00:00</t>
         </is>
       </c>
       <c r="AY326" t="inlineStr">
@@ -53089,7 +53089,7 @@
       </c>
       <c r="AT327" t="inlineStr">
         <is>
-          <t>batch_164c8f2ccaa64eaf</t>
+          <t>batch_4e3853438a5d4f9c</t>
         </is>
       </c>
       <c r="AU327" t="inlineStr">
@@ -53105,7 +53105,7 @@
       <c r="AW327" t="inlineStr"/>
       <c r="AX327" t="inlineStr">
         <is>
-          <t>2026-05-20T00:13:57+00:00</t>
+          <t>2026-05-20T00:48:39+00:00</t>
         </is>
       </c>
       <c r="AY327" t="inlineStr">
@@ -53249,7 +53249,7 @@
       </c>
       <c r="AT328" t="inlineStr">
         <is>
-          <t>batch_164c8f2ccaa64eaf</t>
+          <t>batch_4e3853438a5d4f9c</t>
         </is>
       </c>
       <c r="AU328" t="inlineStr">
@@ -53265,7 +53265,7 @@
       <c r="AW328" t="inlineStr"/>
       <c r="AX328" t="inlineStr">
         <is>
-          <t>2026-05-20T00:13:57+00:00</t>
+          <t>2026-05-20T00:48:39+00:00</t>
         </is>
       </c>
       <c r="AY328" t="inlineStr">
@@ -53409,7 +53409,7 @@
       </c>
       <c r="AT329" t="inlineStr">
         <is>
-          <t>batch_164c8f2ccaa64eaf</t>
+          <t>batch_4e3853438a5d4f9c</t>
         </is>
       </c>
       <c r="AU329" t="inlineStr">
@@ -53425,7 +53425,7 @@
       <c r="AW329" t="inlineStr"/>
       <c r="AX329" t="inlineStr">
         <is>
-          <t>2026-05-20T00:13:57+00:00</t>
+          <t>2026-05-20T00:48:39+00:00</t>
         </is>
       </c>
       <c r="AY329" t="inlineStr">
@@ -53569,7 +53569,7 @@
       </c>
       <c r="AT330" t="inlineStr">
         <is>
-          <t>batch_164c8f2ccaa64eaf</t>
+          <t>batch_4e3853438a5d4f9c</t>
         </is>
       </c>
       <c r="AU330" t="inlineStr">
@@ -53585,7 +53585,7 @@
       <c r="AW330" t="inlineStr"/>
       <c r="AX330" t="inlineStr">
         <is>
-          <t>2026-05-20T00:13:57+00:00</t>
+          <t>2026-05-20T00:48:39+00:00</t>
         </is>
       </c>
       <c r="AY330" t="inlineStr">
@@ -53729,7 +53729,7 @@
       </c>
       <c r="AT331" t="inlineStr">
         <is>
-          <t>batch_164c8f2ccaa64eaf</t>
+          <t>batch_4e3853438a5d4f9c</t>
         </is>
       </c>
       <c r="AU331" t="inlineStr">
@@ -53745,7 +53745,7 @@
       <c r="AW331" t="inlineStr"/>
       <c r="AX331" t="inlineStr">
         <is>
-          <t>2026-05-20T00:13:57+00:00</t>
+          <t>2026-05-20T00:48:39+00:00</t>
         </is>
       </c>
       <c r="AY331" t="inlineStr">
@@ -53889,7 +53889,7 @@
       </c>
       <c r="AT332" t="inlineStr">
         <is>
-          <t>batch_164c8f2ccaa64eaf</t>
+          <t>batch_4e3853438a5d4f9c</t>
         </is>
       </c>
       <c r="AU332" t="inlineStr">
@@ -53905,7 +53905,7 @@
       <c r="AW332" t="inlineStr"/>
       <c r="AX332" t="inlineStr">
         <is>
-          <t>2026-05-20T00:13:57+00:00</t>
+          <t>2026-05-20T00:48:39+00:00</t>
         </is>
       </c>
       <c r="AY332" t="inlineStr">
@@ -54049,7 +54049,7 @@
       </c>
       <c r="AT333" t="inlineStr">
         <is>
-          <t>batch_164c8f2ccaa64eaf</t>
+          <t>batch_4e3853438a5d4f9c</t>
         </is>
       </c>
       <c r="AU333" t="inlineStr">
@@ -54065,7 +54065,7 @@
       <c r="AW333" t="inlineStr"/>
       <c r="AX333" t="inlineStr">
         <is>
-          <t>2026-05-20T00:13:57+00:00</t>
+          <t>2026-05-20T00:48:39+00:00</t>
         </is>
       </c>
       <c r="AY333" t="inlineStr">
@@ -54209,7 +54209,7 @@
       </c>
       <c r="AT334" t="inlineStr">
         <is>
-          <t>batch_164c8f2ccaa64eaf</t>
+          <t>batch_4e3853438a5d4f9c</t>
         </is>
       </c>
       <c r="AU334" t="inlineStr">
@@ -54225,7 +54225,7 @@
       <c r="AW334" t="inlineStr"/>
       <c r="AX334" t="inlineStr">
         <is>
-          <t>2026-05-20T00:13:57+00:00</t>
+          <t>2026-05-20T00:48:39+00:00</t>
         </is>
       </c>
       <c r="AY334" t="inlineStr">
@@ -54369,7 +54369,7 @@
       </c>
       <c r="AT335" t="inlineStr">
         <is>
-          <t>batch_164c8f2ccaa64eaf</t>
+          <t>batch_4e3853438a5d4f9c</t>
         </is>
       </c>
       <c r="AU335" t="inlineStr">
@@ -54385,7 +54385,7 @@
       <c r="AW335" t="inlineStr"/>
       <c r="AX335" t="inlineStr">
         <is>
-          <t>2026-05-20T00:13:57+00:00</t>
+          <t>2026-05-20T00:48:39+00:00</t>
         </is>
       </c>
       <c r="AY335" t="inlineStr">
@@ -54529,7 +54529,7 @@
       </c>
       <c r="AT336" t="inlineStr">
         <is>
-          <t>batch_164c8f2ccaa64eaf</t>
+          <t>batch_4e3853438a5d4f9c</t>
         </is>
       </c>
       <c r="AU336" t="inlineStr">
@@ -54545,7 +54545,7 @@
       <c r="AW336" t="inlineStr"/>
       <c r="AX336" t="inlineStr">
         <is>
-          <t>2026-05-20T00:13:57+00:00</t>
+          <t>2026-05-20T00:48:39+00:00</t>
         </is>
       </c>
       <c r="AY336" t="inlineStr">
@@ -54689,7 +54689,7 @@
       </c>
       <c r="AT337" t="inlineStr">
         <is>
-          <t>batch_164c8f2ccaa64eaf</t>
+          <t>batch_4e3853438a5d4f9c</t>
         </is>
       </c>
       <c r="AU337" t="inlineStr">
@@ -54705,7 +54705,7 @@
       <c r="AW337" t="inlineStr"/>
       <c r="AX337" t="inlineStr">
         <is>
-          <t>2026-05-20T00:13:57+00:00</t>
+          <t>2026-05-20T00:48:39+00:00</t>
         </is>
       </c>
       <c r="AY337" t="inlineStr">
@@ -54849,7 +54849,7 @@
       </c>
       <c r="AT338" t="inlineStr">
         <is>
-          <t>batch_164c8f2ccaa64eaf</t>
+          <t>batch_4e3853438a5d4f9c</t>
         </is>
       </c>
       <c r="AU338" t="inlineStr">
@@ -54865,7 +54865,7 @@
       <c r="AW338" t="inlineStr"/>
       <c r="AX338" t="inlineStr">
         <is>
-          <t>2026-05-20T00:13:57+00:00</t>
+          <t>2026-05-20T00:48:39+00:00</t>
         </is>
       </c>
       <c r="AY338" t="inlineStr">
@@ -55009,7 +55009,7 @@
       </c>
       <c r="AT339" t="inlineStr">
         <is>
-          <t>batch_164c8f2ccaa64eaf</t>
+          <t>batch_4e3853438a5d4f9c</t>
         </is>
       </c>
       <c r="AU339" t="inlineStr">
@@ -55025,7 +55025,7 @@
       <c r="AW339" t="inlineStr"/>
       <c r="AX339" t="inlineStr">
         <is>
-          <t>2026-05-20T00:13:57+00:00</t>
+          <t>2026-05-20T00:48:39+00:00</t>
         </is>
       </c>
       <c r="AY339" t="inlineStr">
@@ -55169,7 +55169,7 @@
       </c>
       <c r="AT340" t="inlineStr">
         <is>
-          <t>batch_164c8f2ccaa64eaf</t>
+          <t>batch_4e3853438a5d4f9c</t>
         </is>
       </c>
       <c r="AU340" t="inlineStr">
@@ -55185,7 +55185,7 @@
       <c r="AW340" t="inlineStr"/>
       <c r="AX340" t="inlineStr">
         <is>
-          <t>2026-05-20T00:13:57+00:00</t>
+          <t>2026-05-20T00:48:39+00:00</t>
         </is>
       </c>
       <c r="AY340" t="inlineStr">
@@ -55329,7 +55329,7 @@
       </c>
       <c r="AT341" t="inlineStr">
         <is>
-          <t>batch_164c8f2ccaa64eaf</t>
+          <t>batch_4e3853438a5d4f9c</t>
         </is>
       </c>
       <c r="AU341" t="inlineStr">
@@ -55345,7 +55345,7 @@
       <c r="AW341" t="inlineStr"/>
       <c r="AX341" t="inlineStr">
         <is>
-          <t>2026-05-20T00:13:57+00:00</t>
+          <t>2026-05-20T00:48:39+00:00</t>
         </is>
       </c>
       <c r="AY341" t="inlineStr">
@@ -55489,7 +55489,7 @@
       </c>
       <c r="AT342" t="inlineStr">
         <is>
-          <t>batch_164c8f2ccaa64eaf</t>
+          <t>batch_4e3853438a5d4f9c</t>
         </is>
       </c>
       <c r="AU342" t="inlineStr">
@@ -55505,7 +55505,7 @@
       <c r="AW342" t="inlineStr"/>
       <c r="AX342" t="inlineStr">
         <is>
-          <t>2026-05-20T00:13:57+00:00</t>
+          <t>2026-05-20T00:48:39+00:00</t>
         </is>
       </c>
       <c r="AY342" t="inlineStr">
@@ -55649,7 +55649,7 @@
       </c>
       <c r="AT343" t="inlineStr">
         <is>
-          <t>batch_164c8f2ccaa64eaf</t>
+          <t>batch_4e3853438a5d4f9c</t>
         </is>
       </c>
       <c r="AU343" t="inlineStr">
@@ -55665,7 +55665,7 @@
       <c r="AW343" t="inlineStr"/>
       <c r="AX343" t="inlineStr">
         <is>
-          <t>2026-05-20T00:13:57+00:00</t>
+          <t>2026-05-20T00:48:39+00:00</t>
         </is>
       </c>
       <c r="AY343" t="inlineStr">
@@ -55809,7 +55809,7 @@
       </c>
       <c r="AT344" t="inlineStr">
         <is>
-          <t>batch_164c8f2ccaa64eaf</t>
+          <t>batch_4e3853438a5d4f9c</t>
         </is>
       </c>
       <c r="AU344" t="inlineStr">
@@ -55825,7 +55825,7 @@
       <c r="AW344" t="inlineStr"/>
       <c r="AX344" t="inlineStr">
         <is>
-          <t>2026-05-20T00:13:57+00:00</t>
+          <t>2026-05-20T00:48:39+00:00</t>
         </is>
       </c>
       <c r="AY344" t="inlineStr">
@@ -55969,7 +55969,7 @@
       </c>
       <c r="AT345" t="inlineStr">
         <is>
-          <t>batch_164c8f2ccaa64eaf</t>
+          <t>batch_4e3853438a5d4f9c</t>
         </is>
       </c>
       <c r="AU345" t="inlineStr">
@@ -55985,7 +55985,7 @@
       <c r="AW345" t="inlineStr"/>
       <c r="AX345" t="inlineStr">
         <is>
-          <t>2026-05-20T00:13:57+00:00</t>
+          <t>2026-05-20T00:48:39+00:00</t>
         </is>
       </c>
       <c r="AY345" t="inlineStr">
@@ -56129,7 +56129,7 @@
       </c>
       <c r="AT346" t="inlineStr">
         <is>
-          <t>batch_164c8f2ccaa64eaf</t>
+          <t>batch_4e3853438a5d4f9c</t>
         </is>
       </c>
       <c r="AU346" t="inlineStr">
@@ -56145,7 +56145,7 @@
       <c r="AW346" t="inlineStr"/>
       <c r="AX346" t="inlineStr">
         <is>
-          <t>2026-05-20T00:13:57+00:00</t>
+          <t>2026-05-20T00:48:39+00:00</t>
         </is>
       </c>
       <c r="AY346" t="inlineStr">
@@ -56289,7 +56289,7 @@
       </c>
       <c r="AT347" t="inlineStr">
         <is>
-          <t>batch_164c8f2ccaa64eaf</t>
+          <t>batch_4e3853438a5d4f9c</t>
         </is>
       </c>
       <c r="AU347" t="inlineStr">
@@ -56305,7 +56305,7 @@
       <c r="AW347" t="inlineStr"/>
       <c r="AX347" t="inlineStr">
         <is>
-          <t>2026-05-20T00:13:57+00:00</t>
+          <t>2026-05-20T00:48:39+00:00</t>
         </is>
       </c>
       <c r="AY347" t="inlineStr">
@@ -56449,7 +56449,7 @@
       </c>
       <c r="AT348" t="inlineStr">
         <is>
-          <t>batch_164c8f2ccaa64eaf</t>
+          <t>batch_4e3853438a5d4f9c</t>
         </is>
       </c>
       <c r="AU348" t="inlineStr">
@@ -56465,7 +56465,7 @@
       <c r="AW348" t="inlineStr"/>
       <c r="AX348" t="inlineStr">
         <is>
-          <t>2026-05-20T00:13:57+00:00</t>
+          <t>2026-05-20T00:48:39+00:00</t>
         </is>
       </c>
       <c r="AY348" t="inlineStr">
@@ -56609,7 +56609,7 @@
       </c>
       <c r="AT349" t="inlineStr">
         <is>
-          <t>batch_164c8f2ccaa64eaf</t>
+          <t>batch_4e3853438a5d4f9c</t>
         </is>
       </c>
       <c r="AU349" t="inlineStr">
@@ -56625,7 +56625,7 @@
       <c r="AW349" t="inlineStr"/>
       <c r="AX349" t="inlineStr">
         <is>
-          <t>2026-05-20T00:13:57+00:00</t>
+          <t>2026-05-20T00:48:39+00:00</t>
         </is>
       </c>
       <c r="AY349" t="inlineStr">
@@ -56754,7 +56754,7 @@
       </c>
       <c r="AT350" t="inlineStr">
         <is>
-          <t>batch_164c8f2ccaa64eaf</t>
+          <t>batch_4e3853438a5d4f9c</t>
         </is>
       </c>
       <c r="AU350" t="inlineStr">
@@ -56770,7 +56770,7 @@
       <c r="AW350" t="inlineStr"/>
       <c r="AX350" t="inlineStr">
         <is>
-          <t>2026-05-20T00:13:57+00:00</t>
+          <t>2026-05-20T00:48:39+00:00</t>
         </is>
       </c>
       <c r="AY350" t="inlineStr">
@@ -56899,7 +56899,7 @@
       </c>
       <c r="AT351" t="inlineStr">
         <is>
-          <t>batch_164c8f2ccaa64eaf</t>
+          <t>batch_4e3853438a5d4f9c</t>
         </is>
       </c>
       <c r="AU351" t="inlineStr">
@@ -56915,7 +56915,7 @@
       <c r="AW351" t="inlineStr"/>
       <c r="AX351" t="inlineStr">
         <is>
-          <t>2026-05-20T00:13:57+00:00</t>
+          <t>2026-05-20T00:48:39+00:00</t>
         </is>
       </c>
       <c r="AY351" t="inlineStr">
@@ -57044,7 +57044,7 @@
       </c>
       <c r="AT352" t="inlineStr">
         <is>
-          <t>batch_164c8f2ccaa64eaf</t>
+          <t>batch_4e3853438a5d4f9c</t>
         </is>
       </c>
       <c r="AU352" t="inlineStr">
@@ -57060,7 +57060,7 @@
       <c r="AW352" t="inlineStr"/>
       <c r="AX352" t="inlineStr">
         <is>
-          <t>2026-05-20T00:13:57+00:00</t>
+          <t>2026-05-20T00:48:39+00:00</t>
         </is>
       </c>
       <c r="AY352" t="inlineStr">
@@ -57189,7 +57189,7 @@
       </c>
       <c r="AT353" t="inlineStr">
         <is>
-          <t>batch_164c8f2ccaa64eaf</t>
+          <t>batch_4e3853438a5d4f9c</t>
         </is>
       </c>
       <c r="AU353" t="inlineStr">
@@ -57205,7 +57205,7 @@
       <c r="AW353" t="inlineStr"/>
       <c r="AX353" t="inlineStr">
         <is>
-          <t>2026-05-20T00:13:57+00:00</t>
+          <t>2026-05-20T00:48:39+00:00</t>
         </is>
       </c>
       <c r="AY353" t="inlineStr">
@@ -57334,7 +57334,7 @@
       </c>
       <c r="AT354" t="inlineStr">
         <is>
-          <t>batch_164c8f2ccaa64eaf</t>
+          <t>batch_4e3853438a5d4f9c</t>
         </is>
       </c>
       <c r="AU354" t="inlineStr">
@@ -57350,7 +57350,7 @@
       <c r="AW354" t="inlineStr"/>
       <c r="AX354" t="inlineStr">
         <is>
-          <t>2026-05-20T00:13:57+00:00</t>
+          <t>2026-05-20T00:48:39+00:00</t>
         </is>
       </c>
       <c r="AY354" t="inlineStr">
@@ -57479,7 +57479,7 @@
       </c>
       <c r="AT355" t="inlineStr">
         <is>
-          <t>batch_164c8f2ccaa64eaf</t>
+          <t>batch_4e3853438a5d4f9c</t>
         </is>
       </c>
       <c r="AU355" t="inlineStr">
@@ -57495,7 +57495,7 @@
       <c r="AW355" t="inlineStr"/>
       <c r="AX355" t="inlineStr">
         <is>
-          <t>2026-05-20T00:13:57+00:00</t>
+          <t>2026-05-20T00:48:39+00:00</t>
         </is>
       </c>
       <c r="AY355" t="inlineStr">
@@ -57624,7 +57624,7 @@
       </c>
       <c r="AT356" t="inlineStr">
         <is>
-          <t>batch_164c8f2ccaa64eaf</t>
+          <t>batch_4e3853438a5d4f9c</t>
         </is>
       </c>
       <c r="AU356" t="inlineStr">
@@ -57640,7 +57640,7 @@
       <c r="AW356" t="inlineStr"/>
       <c r="AX356" t="inlineStr">
         <is>
-          <t>2026-05-20T00:13:57+00:00</t>
+          <t>2026-05-20T00:48:39+00:00</t>
         </is>
       </c>
       <c r="AY356" t="inlineStr">
@@ -57769,7 +57769,7 @@
       </c>
       <c r="AT357" t="inlineStr">
         <is>
-          <t>batch_164c8f2ccaa64eaf</t>
+          <t>batch_4e3853438a5d4f9c</t>
         </is>
       </c>
       <c r="AU357" t="inlineStr">
@@ -57785,7 +57785,7 @@
       <c r="AW357" t="inlineStr"/>
       <c r="AX357" t="inlineStr">
         <is>
-          <t>2026-05-20T00:13:57+00:00</t>
+          <t>2026-05-20T00:48:39+00:00</t>
         </is>
       </c>
       <c r="AY357" t="inlineStr">
@@ -57914,7 +57914,7 @@
       </c>
       <c r="AT358" t="inlineStr">
         <is>
-          <t>batch_164c8f2ccaa64eaf</t>
+          <t>batch_4e3853438a5d4f9c</t>
         </is>
       </c>
       <c r="AU358" t="inlineStr">
@@ -57930,7 +57930,7 @@
       <c r="AW358" t="inlineStr"/>
       <c r="AX358" t="inlineStr">
         <is>
-          <t>2026-05-20T00:13:57+00:00</t>
+          <t>2026-05-20T00:48:39+00:00</t>
         </is>
       </c>
       <c r="AY358" t="inlineStr">
@@ -58059,7 +58059,7 @@
       </c>
       <c r="AT359" t="inlineStr">
         <is>
-          <t>batch_164c8f2ccaa64eaf</t>
+          <t>batch_4e3853438a5d4f9c</t>
         </is>
       </c>
       <c r="AU359" t="inlineStr">
@@ -58075,7 +58075,7 @@
       <c r="AW359" t="inlineStr"/>
       <c r="AX359" t="inlineStr">
         <is>
-          <t>2026-05-20T00:13:57+00:00</t>
+          <t>2026-05-20T00:48:39+00:00</t>
         </is>
       </c>
       <c r="AY359" t="inlineStr">
@@ -58204,7 +58204,7 @@
       </c>
       <c r="AT360" t="inlineStr">
         <is>
-          <t>batch_164c8f2ccaa64eaf</t>
+          <t>batch_4e3853438a5d4f9c</t>
         </is>
       </c>
       <c r="AU360" t="inlineStr">
@@ -58220,7 +58220,7 @@
       <c r="AW360" t="inlineStr"/>
       <c r="AX360" t="inlineStr">
         <is>
-          <t>2026-05-20T00:13:57+00:00</t>
+          <t>2026-05-20T00:48:39+00:00</t>
         </is>
       </c>
       <c r="AY360" t="inlineStr">
@@ -58340,7 +58340,7 @@
       </c>
       <c r="AT361" t="inlineStr">
         <is>
-          <t>batch_164c8f2ccaa64eaf</t>
+          <t>batch_4e3853438a5d4f9c</t>
         </is>
       </c>
       <c r="AU361" t="inlineStr">
@@ -58356,7 +58356,7 @@
       <c r="AW361" t="inlineStr"/>
       <c r="AX361" t="inlineStr">
         <is>
-          <t>2026-05-20T00:13:57+00:00</t>
+          <t>2026-05-20T00:48:39+00:00</t>
         </is>
       </c>
       <c r="AY361" t="inlineStr">
@@ -58458,7 +58458,7 @@
       </c>
       <c r="AT362" t="inlineStr">
         <is>
-          <t>batch_164c8f2ccaa64eaf</t>
+          <t>batch_4e3853438a5d4f9c</t>
         </is>
       </c>
       <c r="AU362" t="inlineStr">
@@ -58474,7 +58474,7 @@
       <c r="AW362" t="inlineStr"/>
       <c r="AX362" t="inlineStr">
         <is>
-          <t>2026-05-20T00:13:57+00:00</t>
+          <t>2026-05-20T00:48:39+00:00</t>
         </is>
       </c>
       <c r="AY362" t="inlineStr">
@@ -58576,7 +58576,7 @@
       </c>
       <c r="AT363" t="inlineStr">
         <is>
-          <t>batch_164c8f2ccaa64eaf</t>
+          <t>batch_4e3853438a5d4f9c</t>
         </is>
       </c>
       <c r="AU363" t="inlineStr">
@@ -58592,7 +58592,7 @@
       <c r="AW363" t="inlineStr"/>
       <c r="AX363" t="inlineStr">
         <is>
-          <t>2026-05-20T00:13:57+00:00</t>
+          <t>2026-05-20T00:48:39+00:00</t>
         </is>
       </c>
       <c r="AY363" t="inlineStr">
@@ -58694,7 +58694,7 @@
       </c>
       <c r="AT364" t="inlineStr">
         <is>
-          <t>batch_164c8f2ccaa64eaf</t>
+          <t>batch_4e3853438a5d4f9c</t>
         </is>
       </c>
       <c r="AU364" t="inlineStr">
@@ -58710,7 +58710,7 @@
       <c r="AW364" t="inlineStr"/>
       <c r="AX364" t="inlineStr">
         <is>
-          <t>2026-05-20T00:13:57+00:00</t>
+          <t>2026-05-20T00:48:39+00:00</t>
         </is>
       </c>
       <c r="AY364" t="inlineStr">
@@ -58812,7 +58812,7 @@
       </c>
       <c r="AT365" t="inlineStr">
         <is>
-          <t>batch_164c8f2ccaa64eaf</t>
+          <t>batch_4e3853438a5d4f9c</t>
         </is>
       </c>
       <c r="AU365" t="inlineStr">
@@ -58828,7 +58828,7 @@
       <c r="AW365" t="inlineStr"/>
       <c r="AX365" t="inlineStr">
         <is>
-          <t>2026-05-20T00:13:57+00:00</t>
+          <t>2026-05-20T00:48:39+00:00</t>
         </is>
       </c>
       <c r="AY365" t="inlineStr">
@@ -58930,7 +58930,7 @@
       </c>
       <c r="AT366" t="inlineStr">
         <is>
-          <t>batch_164c8f2ccaa64eaf</t>
+          <t>batch_4e3853438a5d4f9c</t>
         </is>
       </c>
       <c r="AU366" t="inlineStr">
@@ -58946,7 +58946,7 @@
       <c r="AW366" t="inlineStr"/>
       <c r="AX366" t="inlineStr">
         <is>
-          <t>2026-05-20T00:13:57+00:00</t>
+          <t>2026-05-20T00:48:39+00:00</t>
         </is>
       </c>
       <c r="AY366" t="inlineStr">
@@ -59048,7 +59048,7 @@
       </c>
       <c r="AT367" t="inlineStr">
         <is>
-          <t>batch_164c8f2ccaa64eaf</t>
+          <t>batch_4e3853438a5d4f9c</t>
         </is>
       </c>
       <c r="AU367" t="inlineStr">
@@ -59064,7 +59064,7 @@
       <c r="AW367" t="inlineStr"/>
       <c r="AX367" t="inlineStr">
         <is>
-          <t>2026-05-20T00:13:57+00:00</t>
+          <t>2026-05-20T00:48:39+00:00</t>
         </is>
       </c>
       <c r="AY367" t="inlineStr">
@@ -59166,7 +59166,7 @@
       </c>
       <c r="AT368" t="inlineStr">
         <is>
-          <t>batch_164c8f2ccaa64eaf</t>
+          <t>batch_4e3853438a5d4f9c</t>
         </is>
       </c>
       <c r="AU368" t="inlineStr">
@@ -59182,7 +59182,7 @@
       <c r="AW368" t="inlineStr"/>
       <c r="AX368" t="inlineStr">
         <is>
-          <t>2026-05-20T00:13:57+00:00</t>
+          <t>2026-05-20T00:48:39+00:00</t>
         </is>
       </c>
       <c r="AY368" t="inlineStr">
@@ -59284,7 +59284,7 @@
       </c>
       <c r="AT369" t="inlineStr">
         <is>
-          <t>batch_164c8f2ccaa64eaf</t>
+          <t>batch_4e3853438a5d4f9c</t>
         </is>
       </c>
       <c r="AU369" t="inlineStr">
@@ -59300,7 +59300,7 @@
       <c r="AW369" t="inlineStr"/>
       <c r="AX369" t="inlineStr">
         <is>
-          <t>2026-05-20T00:13:57+00:00</t>
+          <t>2026-05-20T00:48:39+00:00</t>
         </is>
       </c>
       <c r="AY369" t="inlineStr">
@@ -59402,7 +59402,7 @@
       </c>
       <c r="AT370" t="inlineStr">
         <is>
-          <t>batch_164c8f2ccaa64eaf</t>
+          <t>batch_4e3853438a5d4f9c</t>
         </is>
       </c>
       <c r="AU370" t="inlineStr">
@@ -59418,7 +59418,7 @@
       <c r="AW370" t="inlineStr"/>
       <c r="AX370" t="inlineStr">
         <is>
-          <t>2026-05-20T00:13:57+00:00</t>
+          <t>2026-05-20T00:48:39+00:00</t>
         </is>
       </c>
       <c r="AY370" t="inlineStr">
@@ -59520,7 +59520,7 @@
       </c>
       <c r="AT371" t="inlineStr">
         <is>
-          <t>batch_164c8f2ccaa64eaf</t>
+          <t>batch_4e3853438a5d4f9c</t>
         </is>
       </c>
       <c r="AU371" t="inlineStr">
@@ -59536,7 +59536,7 @@
       <c r="AW371" t="inlineStr"/>
       <c r="AX371" t="inlineStr">
         <is>
-          <t>2026-05-20T00:13:57+00:00</t>
+          <t>2026-05-20T00:48:39+00:00</t>
         </is>
       </c>
       <c r="AY371" t="inlineStr">
@@ -59638,7 +59638,7 @@
       </c>
       <c r="AT372" t="inlineStr">
         <is>
-          <t>batch_164c8f2ccaa64eaf</t>
+          <t>batch_4e3853438a5d4f9c</t>
         </is>
       </c>
       <c r="AU372" t="inlineStr">
@@ -59654,7 +59654,7 @@
       <c r="AW372" t="inlineStr"/>
       <c r="AX372" t="inlineStr">
         <is>
-          <t>2026-05-20T00:13:57+00:00</t>
+          <t>2026-05-20T00:48:39+00:00</t>
         </is>
       </c>
       <c r="AY372" t="inlineStr">
@@ -61593,7 +61593,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Built 2026-05-20T00:13:57+00:00. Normalization version: v1.2.</t>
+          <t>Built 2026-05-20T00:48:39+00:00. Normalization version: v1.2.</t>
         </is>
       </c>
     </row>
